--- a/Output/Devendra Fadnavis/extracted_links.xlsx
+++ b/Output/Devendra Fadnavis/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B585"/>
+  <dimension ref="A1:B508"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,516 +455,516 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Heavy rain lashes Marathwada; 5 missing in Nanded, says CM Devendra Fadnavis</t>
+          <t>‘Third Mumbai’ will open a new chapter of economic development: Maha CM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/heavy-rain-lashes-marathwada-5-missing-in-nanded-says-cm-devendra-fadnavis-10196321/</t>
+          <t>https://www.ap7am.com/en/107162/third-mumbai-will-open-a-new-chapter-of-economic-development-maha-cm</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mumbai gets 300 mm rain in a day, Devendra Fadnavis warns next 48 hours critical</t>
+          <t>'Bal Thackeray Must Be Blessing Me': Devendra Fadnavis' Jibe At Uddhav, Raj</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/cities/mumbai/story/mumbai-heavy-rains-waterlogging-imd-red-alert-bmc-school-offices-holiday-work-from-home-2773291-2025-08-19</t>
+          <t>https://www.msn.com/en-in/news/India/bal-thackeray-must-be-blessing-me-devendra-fadnavis-jibe-at-uddhav-raj/ar-AA1I1uNG?cvid=4abb379217d14469d8ca5b000d1b6962&amp;ocid=up97dhp</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>'Positive about bringing a law to protect advocates:' Maharashtra CM Fadnavis</t>
+          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by Maharashtra CM Devendra Fadnavis</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://legal.economictimes.indiatimes.com/news/industry/positive-about-bringing-a-law-to-protect-advocates-maharashtra-cm-fadnavis/123378199</t>
+          <t>https://www.tribuneindia.com/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>‘Third Mumbai’ takes shape as CM Fadnavis unveils mega MMR expansion plan</t>
+          <t>Maharashtra CM Devendra Fadnavis seeks Opposition backing for Radhakrishnan</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/city/third-mumbai-takes-shape-as-cm-fadnavis-unveils-mega-mmr-expansion-plan-article-13465350.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-devendra-fadnavis-seeks-opposition-backing-for-radhakrishnan-23590051</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Maharashtra CM Devendra Fadnavis seeks Opposition backing for Radhakrishnan</t>
+          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-devendra-fadnavis-seeks-opposition-backing-for-radhakrishnan-23590051</t>
+          <t>https://www.outlookbusiness.com/news/third-mumbai-to-boost-metropolitan-region-development-fadnavis</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
+          <t>'Positive about bringing a law to protect advocates:' Maharashtra CM Fadnavis</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://www.outlookbusiness.com/news/third-mumbai-to-boost-metropolitan-region-development-fadnavis</t>
+          <t>https://legal.economictimes.indiatimes.com/news/industry/positive-about-bringing-a-law-to-protect-advocates-maharashtra-cm-fadnavis/123378199</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mumbai Rains: Maharashtra CM Devendra Fadnavis Chairs Review Meeting On Excessive Rainfall At Mantralaya</t>
+          <t>Heavy rain lashes Marathwada; 5 missing in Nanded, says CM Devendra Fadnavis</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-rains-cm-devendra-fadnavis-chairs-review-meeting-on-excessive-rainfall-at-mantralaya-video</t>
+          <t>https://indianexpress.com/article/cities/mumbai/heavy-rain-lashes-marathwada-5-missing-in-nanded-says-cm-devendra-fadnavis-10196321/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>‘Third Mumbai’ will open a new chapter of economic development: Maha CM</t>
+          <t>Aakar Patel| New Maharashtra Security Law Open To Abuse, Threatens Rights; Say ‘No’ To It</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://www.ap7am.com/en/107162/third-mumbai-will-open-a-new-chapter-of-economic-development-maha-cm</t>
+          <t>https://www.deccanchronicle.com/opinion/columnists/aakar-patel-new-maharashtra-security-law-open-to-abuse-threatens-rights-say-no-to-it-1898276</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Goldman Sachs opens new, expanded office in Mumbai</t>
+          <t>VP Nominee CP Radhakrishnan Leaves for Delhi, Maha Yuti Leaders Pledge Support</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/business/Industry/goldman-sachs-opens-new-expanded-office-in-mumbai/article69947256.ece</t>
+          <t>https://www.deccanherald.com/india/maharashtra/vp-nominee-radhakrishnan-departs-for-delhi-maha-yuti-leaders-extend-support-3685392</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by Maharashtra CM Devendra Fadnavis</t>
+          <t>Fadnavis hails Maha Guv’s nomination as Vice Presidential candidate</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis/</t>
+          <t>https://www.thestatesman.com/india/fadnavis-hails-maha-guvs-nomination-as-vice-presidential-candidate-1503473264.html</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Future-ready India lies in STEM and AI, says Devendra Fadnavis, Maharashtra CM</t>
+          <t>Third Mumbai: Fadnavis Boosts MMR Development</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://indiacsr.in/brillio-national-stem-challenge-empowers-2500-underserved-students-to-innovate-for-indias-future/</t>
+          <t>https://money.rediff.com/news/market/third-mumbai-fadnavis-boosts-mmr-development/32201020250818</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CM Devendra Fadnavis Meets Netherlands Yogasana Chief on Global Initiatives</t>
+          <t>Cannot achieve affordable housing with ‘business as usual’ approach: Maharashtra CM Fadnavis tells...</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://www.transcontinentaltimes.com/netherlands-yogasana-sports-nysa/</t>
+          <t>https://www.moneycontrol.com/news/business/real-estate/cannot-achieve-affordable-housing-with-business-as-usual-approach-maharashtra-cm-fadnavis-tells-realtors-13462328.html</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Third Mumbai: Fadnavis Boosts MMR Development</t>
+          <t>Aurangzeb Tomb Row: VHP’s Statewide Protests Backed By RSS; CM Devendra Fadnavis Calls For Lawful Dismantling</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/third-mumbai-fadnavis-boosts-mmr-development/32201020250818</t>
+          <t>https://www.msn.com/en-in/news/India/aurangzeb-tomb-row-vhp-s-statewide-protests-backed-by-rss-cm-devendra-fadnavis-calls-for-lawful-dismantling/ar-AA1Bfmct?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
+          <t>Maha CM asks agencies to be on alert mode after heavy rainfall and flash floods</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/business/'third-mumbai'-to-boost-metropolitan-region-development:-fadnavis/2834902</t>
+          <t>https://www.ap7am.com/en/107166/maha-cm-asks-agencies-to-be-on-alert-mode-after-heavy-rainfall-and-flash-floods</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mumbai Records 177 mm Rain In 6 Hours, CM Devendra Fadnavis Urges Caution Amid High Tide Alert</t>
+          <t>Shiv Sena (UBT) Welcomes Radhakrishnan’s Nomination, Fadnavis Seeks All-Party Support</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-records-177-mm-rain-in-6-hours-cm-devendra-fadnavis-urges-caution-amid-high-tide-alert</t>
+          <t>https://www.deccanchronicle.com/nation/shiv-sena-ubt-welcomes-rahakrishans-nomination-fadnavis-seeks-all-party-support-1898266</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Maha CM asks agencies to be on alert mode after heavy rainfall and flash floods</t>
+          <t>NDA Vice President-Nominee CP Radhakrishnan Expresses Gratitude To PM Modi, Amit Shah &amp; Devendra Fadnavis After VP Nomination</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://www.ap7am.com/en/107166/maha-cm-asks-agencies-to-be-on-alert-mode-after-heavy-rainfall-and-flash-floods</t>
+          <t>https://www.msn.com/en-in/news/India/nda-vice-president-nominee-cp-radhakrishnan-expresses-gratitude-to-pm-modi-amit-shah-devendra-fadnavis-after-vp-nomination/ar-AA1KGvyO</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Heavy Rains Ravage State, CM Fadnavis Orders Relief, Surveys Rain-Hit Areas</t>
+          <t>Devendra Fadnavis' first reaction to Raj Thackeray's reunion with Uddhav jibe</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/heavy-rains-ravage-state-cm-fadnavis-orders-relief-surveys-rain-hit-areas/articleshow/123372550.cms</t>
+          <t>http://www.msn.com/en-in/news/india/devendra-fadnavis-first-reaction-to-raj-thackeray-s-reunion-with-uddhav-jibe/ar-AA1I1jzW?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Goldman Sachs Expands In Mumbai, Devendra Fadnavis Inaugurates New Worli Office</t>
+          <t>MNS Morcha: Raj Thackeray's party workers detained; CM Fadnavis says such experiments won’t work here</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/business/goldman-sachs-expands-in-mumbai-devendra-fadnavis-inaugurates-new-worli-office</t>
+          <t>https://www.msn.com/en-in/news/India/mns-morcha-raj-thackerays-party-workers-detained-cm-fadnavis-says-such-experiments-won-t-work-here/ar-AA1Iaint</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sword of Raghuji Bhonsle Unveiled in Mumbai: ‘A Bridge Between Generations,’ Says CM Fadnavis</t>
+          <t>Goldman Sachs opens new, expanded office in Mumbai</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/sword-of-raghuji-bhonsle-unveiled-in-mumbai-a-bridge-between-generations-says-cm-fadnavis/articleshow/123372524.cms</t>
+          <t>https://www.thehindu.com/business/Industry/goldman-sachs-opens-new-expanded-office-in-mumbai/article69947256.ece</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>VIDEO: Historic Sword Of Raghuji Bhonsle Connects Youth With Maharashtra’s Glorious History, Says CM</t>
+          <t>Sword of Raghuji Bhonsle Unveiled in Mumbai: ‘A Bridge Between Generations,’ Says CM Fadnavis</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/video-historic-sword-of-raghuji-bhonsle-connects-youth-with-maharashtras-glorious-history-says-cm-devendra-fadnavis</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/sword-of-raghuji-bhonsle-unveiled-in-mumbai-a-bridge-between-generations-says-cm-fadnavis/articleshow/123372524.cms</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Mumbai AQI: Dia Mirza expresses her concern with CM Devendra Fadnavis to act on city's air pollution</t>
+          <t>Mumbai gets 300 mm rain in a day, Devendra Fadnavis warns next 48 hours critical</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/public-safety-and-emergencies/health-and-safety-alerts/mumbai-aqi-dia-mirza-expresses-her-concern-with-cm-devendra-fadnavis-to-act-on-city-s-air-pollution/ar-AA1xZ0xs?ocid=BingNewsVerp&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.indiatoday.in/cities/mumbai/story/mumbai-heavy-rains-waterlogging-imd-red-alert-bmc-school-offices-holiday-work-from-home-2773291-2025-08-19</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Aurangzeb Tomb Row: VHP’s Statewide Protests Backed By RSS; CM Devendra Fadnavis Calls For Lawful Dismantling</t>
+          <t>Those who speak of Maharashtra 'asmita' should support Radhakrishnan for VP post: Fadnavis</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/aurangzeb-tomb-row-vhp-s-statewide-protests-backed-by-rss-cm-devendra-fadnavis-calls-for-lawful-dismantling/ar-AA1Bfmct?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.ptinews.com/story/national/Those-who-speak-of-Maharashtra--asmita--should-support-Radhakrishnan-for-VP-post--Fadnavis/2832772</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>‘Observe precaution’: Maharashtra CM warns about severe weather conditions in State</t>
+          <t>‘Third Mumbai’ takes shape as CM Fadnavis unveils mega MMR expansion plan</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://www.thehindubusinessline.com/news/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state/article69950172.ece</t>
+          <t>https://www.moneycontrol.com/city/third-mumbai-takes-shape-as-cm-fadnavis-unveils-mega-mmr-expansion-plan-article-13465350.html</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>'Bal Thackeray Must Be Blessing Me': Devendra Fadnavis' Jibe At Uddhav, Raj</t>
+          <t>‘Observe precaution’: Maharashtra CM warns about severe weather conditions in State</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/bal-thackeray-must-be-blessing-me-devendra-fadnavis-jibe-at-uddhav-raj/ar-AA1I1uNG?cvid=4abb379217d14469d8ca5b000d1b6962&amp;ocid=up97dhp</t>
+          <t>https://www.thehindubusinessline.com/news/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state/article69950172.ece</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>VP Nominee CP Radhakrishnan Leaves for Delhi, Maha Yuti Leaders Pledge Support</t>
+          <t>Heavy Rains Ravage State, CM Fadnavis Orders Relief, Surveys Rain-Hit Areas</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/vp-nominee-radhakrishnan-departs-for-delhi-maha-yuti-leaders-extend-support-3685392</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/heavy-rains-ravage-state-cm-fadnavis-orders-relief-surveys-rain-hit-areas/articleshow/123372550.cms</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Shiv Sena (UBT) Welcomes Radhakrishnan’s Nomination, Fadnavis Seeks All-Party Support</t>
+          <t>Those who speak of Maharashtra ‘asmita’ should support Radhakrishnan for VP post: Fadnavis</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/nation/shiv-sena-ubt-welcomes-rahakrishans-nomination-fadnavis-seeks-all-party-support-1898266</t>
+          <t>https://theprint.in/india/those-who-speak-of-maharashtra-asmita-should-support-radhakrishnan-for-vp-post-fadnavis/2723344/?amp</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Aakar Patel| New Maharashtra Security Law Open To Abuse, Threatens Rights; Say ‘No’ To It</t>
+          <t>Why Eknath Shinde is covering little distance despite frequent visits to Delhi</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/opinion/columnists/aakar-patel-new-maharashtra-security-law-open-to-abuse-threatens-rights-say-no-to-it-1898276</t>
+          <t>https://indianexpress.com/article/political-pulse/why-eknath-shinde-is-covering-little-distance-despite-frequent-visits-to-delhi-10197218/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Those who speak of Maharashtra 'asmita' should support Radhakrishnan for VP post: Fadnavis</t>
+          <t>Mumbai rains: Maharashtra CM says 'observe precautions', warns of heavy rainfall, high tide; check BMC's advisory</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/those-who-speak-of-maharashtra--asmita--should-support-radhakrishnan-for-vp-post--fadnavis/2832772</t>
+          <t>https://www.livemint.com/news/mumbai-rains-maharashtra-cm-says-observe-precautions-warns-of-heavy-rainfall-high-tide-check-bmcs-advisory-11755573270369.html</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cannot achieve affordable housing with ‘business as usual’ approach: Maharashtra CM Fadnavis tells...</t>
+          <t>Fadnavis govt’s big Maratha pride push: Legendary sword it ‘bought’ back from London, with a Rs 47L bid</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/business/real-estate/cannot-achieve-affordable-housing-with-business-as-usual-approach-maharashtra-cm-fadnavis-tells-realtors-13462328.html</t>
+          <t>https://theprint.in/politics/fadnavis-govts-big-maratha-pride-push-legendary-sword-it-bought-back-from-london-with-a-rs-47l-bid/2723199/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Fadnavis meets Guv Radhakrishnan, presents him book of Shivaji Maharaj's letters</t>
+          <t>Third Mumbai in Raigad to become Maharashtra’s new economic powerhouse: CM Fadnavis</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/national/Fadnavis-meets-Guv-Radhakrishnan--presents-him-book-of-Shivaji-Maharaj-s-letters/2832581</t>
+          <t>https://www.daijiworld.com/index.php/news/newsDisplay?newsID=1289652</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Mumbai rains: Maharashtra CM says 'observe precautions', warns of heavy rainfall, high tide; check BMC's advisory</t>
+          <t>Mumbai gets 177mm rain in 6-8 hour period, says CM; all agencies asked to remain alert</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/news/mumbai-rains-maharashtra-cm-says-observe-precautions-warns-of-heavy-rainfall-high-tide-check-bmcs-advisory-11755573270369.html</t>
+          <t>https://m.economictimes.com/news/india/mumbai-gets-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/articleshow/123365291.cms</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Maharashtra rains: Five missing, several stranded as heavy rains lash Nanded, rescue operations underway</t>
+          <t>Maharashtra CM Fadnavis, Dy CM Shinde congratulate Governor CP Radhakrishnan on NDA's VP nomination</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/maharashtra/maharashtra-rains-five-missing-several-stranded-as-heavy-rains-lash-nanded-rescue-operations-underway-2025-08-18-1004046</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination-23589945</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Fadnavis Dedicates Goldman Sachs’ New Mumbai Office, Unveils Vision For ‘Third Mumbai’</t>
+          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://www.businessworld.in/article/fadnavis-dedicates-goldman-sachs-new-mumbai-office-unveils-vision-for-third-mumbai-567845</t>
+          <t>https://www.ptinews.com/story/business/'third-mumbai'-to-boost-metropolitan-region-development:-fadnavis/2834902</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Third Mumbai in Raigad to become Maharashtra’s new economic powerhouse: CM Fadnavis</t>
+          <t>Fadnavis meets Guv Radhakrishnan, presents him book of Shivaji Maharaj's letters</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://daijiworld.com/news/newsDisplay?newsID=1289652</t>
+          <t>https://www.ptinews.com/story/national/fadnavis-meets-guv-radhakrishnan,-presents-him-book-of-shivaji-maharaj's-letters/2832581</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>NDA Vice President-Nominee CP Radhakrishnan Expresses Gratitude To PM Modi, Amit Shah &amp; Devendra Fadnavis After VP Nomination</t>
+          <t>Rain fury leaves 7 dead in Maharashtra, 200 villagers stranded</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/nda-vice-president-nominee-cp-radhakrishnan-expresses-gratitude-to-pm-modi-amit-shah-devendra-fadnavis-after-vp-nomination/ar-AA1KGvyO</t>
+          <t>https://www.ptinews.com/story/national/rain-fury-leaves-7-dead-in-maharashtra,-200-villagers-stranded/2834213</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Mumbai gets 177mm rain in 6-8 hour period, says CM; all agencies asked to remain alert</t>
+          <t>Raghuji Bhonsle’s sword brought to India</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/mumbai-gets-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/amp_articleshow/123365291.cms</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/19/raghuji-bhonsles-sword-brought-to-india.html</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis' first reaction to Raj Thackeray's reunion with Uddhav jibe</t>
+          <t>Red alert for Mumbai: Mumbai got 177mm rain in just 6-8 hour period, says CM Fadnavis; more to come amid high tides</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/india/devendra-fadnavis-first-reaction-to-raj-thackeray-s-reunion-with-uddhav-jibe/ar-AA1I1jzW?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/red-alert-for-mumbai-mumbai-got-177mm-rain-in-just-6-8-hour-period-says-cm-fadnavis-more-to-come-amid-high-tides-23589990</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Fadnavis govt’s big Maratha pride push: Legendary sword it ‘bought’ back from London, with a Rs 47L bid</t>
+          <t>Maharashtra rains: Five missing, several stranded as heavy rains lash Nanded, rescue operations underway</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://theprint.in/politics/fadnavis-govts-big-maratha-pride-push-legendary-sword-it-bought-back-from-london-with-a-rs-47l-bid/2723199/</t>
+          <t>https://www.indiatvnews.com/maharashtra/maharashtra-rains-five-missing-several-stranded-as-heavy-rains-lash-nanded-rescue-operations-underway-2025-08-18-1004046</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Those who speak of Maharashtra ‘asmita’ should support Radhakrishnan for VP post: Fadnavis</t>
+          <t>Fadnavis Dedicates Goldman Sachs’ New Mumbai Office, Unveils Vision For ‘Third Mumbai’</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/those-who-speak-of-maharashtra-asmita-should-support-radhakrishnan-for-vp-post-fadnavis/2723344/?amp</t>
+          <t>https://www.businessworld.in/article/fadnavis-dedicates-goldman-sachs-new-mumbai-office-unveils-vision-for-third-mumbai-567845</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Red alert for Mumbai: Mumbai got 177mm rain in just 6-8 hour period, says CM Fadnavis; more to come amid high tides</t>
+          <t>Mumbai got 177mm rain in 6-8 hour period, says CM; all agencies asked to remain alert</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/red-alert-for-mumbai-mumbai-got-177mm-rain-in-just-6-8-hour-period-says-cm-fadnavis-more-to-come-amid-high-tides-23589990</t>
+          <t>https://www.ptinews.com/story/national/mumbai-got-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/2833181</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Fadnavis hails Maha Guv’s nomination as Vice Presidential candidate</t>
+          <t>DH Evening Brief | NDA VP pick in Delhi to meet BJP top brass, Opposition yet to finalise their candidate; I.N.D.I.A. bloc continues attacking EC chief over SIR</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://www.thestatesman.com/india/fadnavis-hails-maha-guvs-nomination-as-vice-presidential-candidate-1503473264.html</t>
+          <t>https://www.deccanherald.com/india/dh-evening-brief-nda-vp-pick-in-delhi-to-meet-bjp-top-brass-opposition-yet-to-finalise-their-candidate-india-bloc-continues-attacking-ec-chief-over-sir-3685866</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MNS Morcha: Raj Thackeray's party workers detained; CM Fadnavis says such experiments won’t work here</t>
+          <t>Maharashtra on high alert as heavy rains batter state; CM, Dy CM lead rescue efforts</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/mns-morcha-raj-thackerays-party-workers-detained-cm-fadnavis-says-such-experiments-won-t-work-here/ar-AA1Iaint</t>
+          <t>https://www.daijiworld.com/news/newsDisplay?newsID=1289634</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Mumbai To Welcome Historic Sword Of Shrimant Raje Raghuji Bhonsale On August 18; To Be Ceremoniously Unveiled</t>
+          <t>Maratha general Raghuji Bhonsle's sword brought to Mumbai</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-to-welcome-historic-sword-of-shrimant-raje-raghuji-bhonsale-on-august-18-to-be-ceremoniously-unveiled-by-cm-fadnavis</t>
+          <t>https://www.ptinews.com/editor-detail/maratha-general-raghuji-bhonsle-s-sword-brought-to-mumbai/2833930</t>
         </is>
       </c>
     </row>
@@ -983,84 +983,84 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Mumbai rain Highlights: 7 people dead across Maharashtra, says CM Devendra Fadnavis</t>
+          <t>Fadnavis meets Guv Radhakrishnan presents him book of Shivaji Maharaj's letters</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://www.india.com/news/india/mumbai-rain-live-updates-heavy-rains-lashes-city-orange-alert-for-today-red-alert-in-pune-satara-ratnagiri-local-trains-delayed-traffic-jams-8017300/</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom20-mh-governor-fadnavis.html</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Raghuji Bhonsle’s sword brought to India</t>
+          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by Maharashtra CM Devendra Fadnavis</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/19/raghuji-bhonsles-sword-brought-to-india.html</t>
+          <t>https://aninews.in/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Rain fury leaves 7 dead in Maharashtra, 200 villagers stranded</t>
+          <t>Mumbai rain Highlights: 7 people dead across Maharashtra, says CM Devendra Fadnavis</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/rain-fury-leaves-7-dead-in-maharashtra-200-villagers-stranded/2834213</t>
+          <t>https://www.india.com/news/india/mumbai-rain-live-updates-heavy-rains-lashes-city-orange-alert-for-today-red-alert-in-pune-satara-ratnagiri-local-trains-delayed-traffic-jams-8017300/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Those who speak of Maharashtra 'asmita' should support Radhakrishnan for VP post Fadnavis</t>
+          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom25-mh-governor-ld-fadnavis.html</t>
+          <t>https://www.millenniumpost.in/nation/third-mumbai-to-boost-metropolitan-region-development-fadnavis-623625</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Fadnavis meets Guv Radhakrishnan presents him book of Shivaji Maharaj's letters</t>
+          <t>Maharashtra rain: Mumbai flooded, 5 missing in Nanded, more showers in store</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom20-mh-governor-fadnavis.html</t>
+          <t>https://thefederal.com/category/states/west/maharashtra/mumbai-flooded-nanded-5-missing-maharashtra-rain-202350</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Maratha general Raghuji Bhonsle's sword brought to Mumbai</t>
+          <t>Mumbai rain: 177 mm recorded in 6-8 hours, public advised to reach homes before 6.30 pm</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/maratha-general-raghuji-bhonsle-s-sword-brought-to-mumbai/2833930</t>
+          <t>https://www.onmanorama.com/news/india/2025/08/18/mumbai-rains-flooding-high-tide-warning-live.html</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Mumbai got 177mm rain in 6-8 hour period, says CM; all agencies asked to remain alert</t>
+          <t>Observe precaution: Maharashtra CM warns about severe weather conditions in state</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/mumbai-got-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/2833181</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state-23590120</t>
         </is>
       </c>
     </row>
@@ -1079,4752 +1079,4752 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Why Eknath Shinde is covering little distance despite frequent visits to Delhi</t>
+          <t>Rain fury leaves 7 dead in Maharashtra 200 villagers stranded</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/political-pulse/why-eknath-shinde-is-covering-little-distance-despite-frequent-visits-to-delhi-10197218/</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom50-mh-2nd-ldall-rains.html</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Fadnavis meets Guv Radhakrishnan, presents him book of Shivaji Maharaj's letters</t>
+          <t>Mumbai got 177mm rain in 6-8 hour period says CM more to come amid high tides</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/india/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharaj-s-letters/ar-AA1KISQ7</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom21-mh-rains-mumbai-cm.html</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Mumbai rain: 177 mm recorded in 6-8 hours, public advised to reach homes before 6.30 pm</t>
+          <t>Pune can get underground road network to beat traffic woes</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://www.onmanorama.com/news/india/2025/08/18/mumbai-rains-flooding-high-tide-warning-live.html</t>
+          <t>https://inshorts.com/en/news/pune-can-get-underground-road-network-to-beat-traffic-woes-1755566759073</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Rain fury leaves 7 dead in Maharashtra 200 villagers stranded</t>
+          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by Maharashtra CM Devendra Fadnavis</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom50-mh-2nd-ldall-rains.html</t>
+          <t>https://www.bignewsnetwork.com/news/278516795/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by Maharashtra CM Devendra Fadnavis</t>
+          <t>CM Devendra Fadnavis Meets Netherlands Yogasana Chief on Global Initiatives</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://english.newsnationtv.com/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322</t>
+          <t>https://www.transcontinentaltimes.com/netherlands-yogasana-sports-nysa/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Mumbai got 177mm rain in 6-8 hour period says CM more to come amid high tides</t>
+          <t>'Third Mumbai' Initiative Sparks New Wave of Economic Growth in Maharashtra</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom21-mh-rains-mumbai-cm.html</t>
+          <t>https://www.devdiscourse.com/article/science-environment/3545659-third-mumbai-initiative-sparks-new-wave-of-economic-growth-in-maharashtra</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Mumbai Weather Today LIVE Updates: Mithi River Crosses Danger Mark; Santacruz Records Highest Rainfall; 300</t>
+          <t>Maharashtra Governor Radhakrishnan: A Voter from Mumbai and NDA's Vice-Presidential Choice</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-rains-live-updates-heavy-showers-wreak-havoc-in-city-schools-colleges-shut-as-imd-issues-red-alert-sion-matunga-dadar-vile-parle-waterlogged-andheri-subway-closed</t>
+          <t>https://www.devdiscourse.com/article/politics/3545404-maharashtra-governor-radhakrishnan-a-voter-from-mumbai-and-ndas-vice-presidential-choice</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Maharashtra rain: Mumbai flooded, 5 missing in Nanded, more showers in store</t>
+          <t>Goldman Sachs Expands In Mumbai, Devendra Fadnavis Inaugurates New Worli Office</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://thefederal.com/category/states/west/maharashtra/mumbai-flooded-nanded-5-missing-maharashtra-rain-202350</t>
+          <t>https://www.freepressjournal.in/business/goldman-sachs-expands-in-mumbai-devendra-fadnavis-inaugurates-new-worli-office</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Heavy rains in Mumbai: IndiGo, SpiceJet, Akasa issue travel advisories</t>
+          <t>Mumbai: CM Devendra Fadnavis meets C.P. Radhakrishnan #Gallery</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://www.newsbytesapp.com/news/india/mumbai-flights-status-airlines-issue-key-advisory-for-passengers/story</t>
+          <t>https://www.socialnews.xyz/2025/08/18/mumbai-cm-devendra-fadnavis-meets-c-p-radhakrishnan-gallery/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DH Evening Brief | NDA VP pick in Delhi to meet BJP top brass, Opposition yet to finalise their candidate; I.N.D.I.A. bloc continues attacking EC chief over SIR</t>
+          <t>Maharashtra CM Devendra Fadnavis Says ‘Third Mumbai’ Being Developed in Raigad District Will Open New</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/dh-evening-brief-nda-vp-pick-in-delhi-to-meet-bjp-top-brass-opposition-yet-to-finalise-their-candidate-india-bloc-continues-attacking-ec-chief-over-sir-3685866</t>
+          <t>https://www.latestly.com/india/news/maharashtra-cm-devendra-fadnavis-says-third-mumbai-being-developed-in-raigad-district-will-open-new-chapter-of-economic-development-7064927.html</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>'Observe precaution': Maharashtra CM warns about severe weather conditions in state</t>
+          <t>India News | ⚡Devendra Fadnavis Says ‘Third Mumbai’ Will Open a New Chapter of Economic Development</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://english.newsnationtv.com/national/general-news/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state20250819025510</t>
+          <t>https://www.latestly.com/quickly/india/news/devendra-fadnavis-says-third-mumbai-will-open-a-new-chapter-of-economic-development-7064927.html</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Pune can get underground road network to beat traffic woes</t>
+          <t>Future-ready India lies in STEM and AI, says Devendra Fadnavis, Maharashtra CM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://inshorts.com/en/news/pune-can-get-underground-road-network-to-beat-traffic-woes-1755566759073</t>
+          <t>https://indiacsr.in/brillio-national-stem-challenge-empowers-2500-underserved-students-to-innovate-for-indias-future/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Heavy rains lash Nanded: Five missing, scores stranded, says Maharashtra CM; Army unit deployed</t>
+          <t>Mumbai Rains: Maharashtra CM Devendra Fadnavis Chairs Review Meeting On Excessive Rainfall At Mantralaya</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/city/heavy-rains-lash-nanded-five-missing-scores-stranded-says-maharashtra-cm-army-unit-deployed-article-13463873.html</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-rains-cm-devendra-fadnavis-chairs-review-meeting-on-excessive-rainfall-at-mantralaya-video</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Maharashtra on high alert as heavy rains batter state; CM, Dy CM lead rescue efforts</t>
+          <t>Mumbai Records 177 mm Rain In 6 Hours, CM Devendra Fadnavis Urges Caution Amid High Tide Alert</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://daijiworld.com/news/newsDisplay?newsID=1289634</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-records-177-mm-rain-in-6-hours-cm-devendra-fadnavis-urges-caution-amid-high-tide-alert</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Maharashtra CM Fadnavis, Dy CM Shinde congratulate Governor CP Radhakrishnan on NDA's VP nomination</t>
+          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by...</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination-23589945</t>
+          <t>https://www.lokmattimes.com/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Observe precaution: Maharashtra CM warns about severe weather conditions in state</t>
+          <t>VIDEO: Historic Sword Of Raghuji Bhonsle Connects Youth With Maharashtra’s Glorious History, Says CM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state-23590120</t>
+          <t>https://www.freepressjournal.in/mumbai/video-historic-sword-of-raghuji-bhonsle-connects-youth-with-maharashtras-glorious-history-says-cm-devendra-fadnavis</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>पुण्यात नवीन महापालिकांवरून देवेंद्र फडणवीस आणि अजित पवार यांच्यात मतभेद का?</t>
+          <t>'Observe precaution': Maharashtra CM warns about severe weather conditions in state</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/devendra-fadnavis-ajit-pawar-dispute-over-new-municipal-corporations-in-pune-district-print-politics-news-css-98-5314697/</t>
+          <t>https://english.newsnationtv.com/national/general-news/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state20250819025510</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Pune News : मुख्यमंत्री फडणवीसांमुळे पुणेकरांना रोज मनस्ताप? काँग्रेसचा गंभीर आरोप</t>
+          <t>Heavy Rain Forecast for Mumbai: CM Fadnavis Reviews Flood Situation Across Maharashtra, with the Next 12...</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/pune/devendra-fadnavis-pune-flyover-inauguration-delay-dk88-sm89</t>
+          <t>https://www.lokmattimes.com/mumbai/heavy-rain-forecast-for-mumbai-cm-fadnavis-reviews-flood-situation-across-maharashtra-with-the-next-12-hours-critical-a475/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>राज्यात अतिवृष्टीमुळे मुख्यमंत्री देवेंद्र फडणवीस यांचे सर्व यंत्रणांना सतर्कतेचे निर्देश; नांदेड जिल्ह्यात लष्कराची मदत</t>
+          <t>Mumbai: C.P. Radhakrishnan departs for Delhi #Gallery</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/chief-minister-devendra-fadnavis-has-directed-all-agencies-to-be-on-alert-due-to-heavy-rains-in-the-maharashtra-mumbai-print-news-amy-95-5313479/</t>
+          <t>https://www.socialnews.xyz/2025/08/18/mumbai-c-p-radhakrishnan-departs-for-delhi-gallery/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>मुख्यमंत्री देवेंद्र फडणवीस ने राज्य में भारी बारिश के मद्देनजर सभी एजेंसियों को सतर्क रहने के निर्देश दिए</t>
+          <t>7 killed as heavy rain batters Maharashtr­a; 800 villages hit</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://www.mumbailive.com/hi/civic/chief-minister-devendra-fadnavis-directed-all-agencies-to-remain-alert-in-view-of-heavy-rains-in-the-state-89633</t>
+          <t>https://www.pressreader.com/india/the-hindu-erode-9WW6/20250819/281994678584394</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>नवीन पिढीला इतिहासाशी जोडण्याचे कार्य सुरू; मुख्यमंत्री देवेंद्र फडणवीस यांचे प्रतिपादन</t>
+          <t>Those who speak of Maharashtra 'asmita' should support Radhakrishnan for VP post: Fadnavis</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/devendra-fadnavis-asserts-that-the-work-of-connecting-the-new-generation-with-history-is-underway-mumbai-print-news-amy-95-5313830/</t>
+          <t>https://www.newsdrum.in/national/those-who-speak-of-maharashtra-asmita-should-support-radhakrishnan-for-vp-post-fadnavis-9672630</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>उप-राष्ट्रपति चुनाव: देवेंद्र फडणवीस का 'मराठी अस्मिता' वाला दांव, क्या करेंगे</t>
+          <t>Pune Patients Receive Over Rs 6.5 Crore in Medical Aid Under Chief Minister Devendra Fadnavis’ Initiative</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/vice-president-election-2025-maharashtra-cm-devendra-fadnavis-request-uddhav-thackeray-and-sharad-pawar-2997542</t>
+          <t>https://www.punekarnews.in/pune-patients-receive-over-rs-6-5-crore-in-medical-aid-under-chief-minister-devendra-fadnavis-initiative/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis : अख्खा पक्ष विरोधात, पण या दिग्गज नेत्याचा फडणवीसांना पाठिंबा, एका पत्राने राजकीय वर्तु...</t>
+          <t>Heavy rains in Mumbai: IndiGo, SpiceJet, Akasa issue travel advisories</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/cm-devendra-fadnavis-gets-support-from-congress-leader-nitin-raut-letter-goes-viral-1461146.html</t>
+          <t>https://www.newsbytesapp.com/news/india/mumbai-flights-status-airlines-issue-key-advisory-for-passengers/story</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Vice President Election: उद्धव ठाकरे और शरद पवार से फडणवीस मांगेंगे सीपी राधाकृष्णन के लिए समर्थन, शिंदे सेना ने दिया सपोर्ट</t>
+          <t>Amid heavy rains in Maharashtra, CM Fadnavis directs all agencies to be on alert</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-governor-radhakrishnan-gets-nda-backing-for-vice-president-post-devendra-fadnavis-uddhav-thackeray-sharad-pawar/articleshow/123371527.cms</t>
+          <t>https://www.thehawk.in/news/india/amid-heavy-rains-in-maharashtra-cm-fadnavis-directs-all-agencies-to-be-on-alert</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>महाराष्ट्र के इस जिले में बसाई जाएगी 'तीसरी मुंबई', मुख्यमंत्री देवेंद्र फडणवीस ने बताईं प्रोजेक्ट की अहम ब</t>
+          <t>Mumbai Rains: Maharashtra CM Says 'Observe Precautions', Warns Of Heavy Rainfall, High Tide Check BMC's Advisory</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/paisa/business/third-mumbai-will-be-settled-in-raigad-district-of-maharashtra-chief-minister-devendra-fadnavis-told-the-important-points-of-the-project-2025-08-19-1156854</t>
+          <t>https://menafn.com/1109945394/Mumbai-Rains-Maharashtra-CM-Says-Observe-Precautions-Warns-Of-Heavy-Rainfall-High-Tide-Check-BMCs-Advisory</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Mumbai Rain News: मुंबईत किती ठिकाणी पाणी साचलं? ट्राफिकची स्थिती काय? मुख्यमंत्र्यांनी दिली A to Z माहिती</t>
+          <t>7 killed as heavy rain batters Maharashtr­a; 800 villages hit</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/mumbai-rain-news-chief-minister-devendra-fadnavis-gave-information-about-the-rainfall-situation-in-mumbai-9107883</t>
+          <t>https://www.pressreader.com/india/the-hindu-mangalore-9WWc/20250819/281947433944151</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>“मुंबईत पुढच्या १२ तासांत तुफान पाऊस, रेड अलर्ट आणि…”; मुख्यमंत्री देवेंद्र फडणवीस यांनी काय माहिती दिली?</t>
+          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by Maharashtra CM Devendra Fadnavis</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/mumbai-rain-alert-cm-devendra-fadnavis-said-mumbai-have-red-alert-school-holiday-declared-know-details-scj-81-5312934/</t>
+          <t>https://english.newsnationtv.com/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>महाराष्ट्र के नांदेड़ में फटा बादल, 15-16 जिलो में अलर्ट, CM फडणवीस बोले- फसलों को नुकसान</t>
+          <t>Business News</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/weather-mumbai-rains-local-train-cloudburst-nanded-alert-in-15-16-districts-in-maharashtra-cm-devendra-fadnavis-said-damage-to-crops-2997472</t>
+          <t>https://www.latestly.com/agency-news/business-news-credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis-7064653.html</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis: 'अंधत्व मुक्त महाराष्ट्र'च्या मुख्यमंत्र्यांच्या संकल्पनेला 'दृष्टी यज्ञ'च्या माध्यमातून बळ</t>
+          <t>Maharashtra Rains: 5 Missing in Nanded, Over 200 Stranded Across Several Districts; Army, NDRF Deployed</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/cm-devendra-fadnavis-blindless-free-maharashtra-checkin-at-7-5-lakhs-students-963609.html</t>
+          <t>https://www.lokmattimes.com/maharashtra/maharashtra-rains-5-missing-in-nanded-over-200-stranded-across-several-districts-army-ndrf-deployed-a517/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Farmers Loan Waiver: बावनकुळेंनंतर महायुती सरकारमधील 'या' मंत्र्याची कर्जमाफीबाबत मोठी अपडेट; म्हणाले,'CM फडणवीस लवकरच...'</t>
+          <t>Mumbai To Welcome Historic Sword Of Shrimant Raje Raghuji Bhonsale On August 18; To Be Ceremoniously Unveiled</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/sanjay-rathod-update-farmer-loan-waiver-devendra-fadnavis-dk88</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-to-welcome-historic-sword-of-shrimant-raje-raghuji-bhonsale-on-august-18-to-be-ceremoniously-unveiled-by-cm-fadnavis</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>शेतकरी कर्जमाफीबाबत महायुतीमधील मंत्र्याने दिली महत्त्वाची माहिती; “देवेंद्र फडणवीस लवकरच….”</t>
+          <t>Fadnavis meets Guv Radhakrishnan, presents him book of Shivaji Maharaj's letters</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/mahayuti-minister-gives-important-information-regarding-farmer-loan-waiver-devendra-fadnavis-soon/</t>
+          <t>https://www.newsdrum.in/national/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharajs-letters-9672415</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CM Devendra Fadnavis : ‘तिसरी मुंबई’ नवा अध्याय उघडेल; रायगड जिल्ह्यात होणार विकसित</t>
+          <t>Rain fury leaves 7 dead in Maharashtra, 200 villagers stranded</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/navi-mumbais-successor-the-rise-of-third-mumbai-in-raigad-district-cm-devendra-fadnavis-pjp78</t>
+          <t>https://www.newsdrum.in/national/rain-fury-leaves-7-dead-in-maharashtra-200-villagers-stranded-9674070</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>काँग्रेस नेते बाळासाहेब थोरात यांना प्रवचनकारांकडून धमकी: सुप्रिया सुळे यांनी व्यक्त केला संताप; कठोर कारवा...</t>
+          <t>CM Fadnavis unveils emblem for Ganeshotsav to be celebrated as Rajya Mahotsav</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/balasaheb-thorat-threats-supriya-sule-demands-action-devendra-fadnavis-pravachankar-135709791.html</t>
+          <t>https://www.thehawk.in/news/india/cm-fadnavis-unveils-emblem-for-ganeshotsav-to-be-celebrated-as-rajya-mahotsav</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis : महाराष्ट्रातील माणसाला सर्वांनी समर्थन द्यावं; फडणवीस यांचे मविआला आवाहन</t>
+          <t>Mumbai Weather Today LIVE Updates: Mithi River Crosses Danger Mark; Santacruz Records Highest Rainfall; 300</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-appeals-to-maharashtra-mps-to-support-cp-radhakrishnan-for-vice-president/913103/</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-rains-live-updates-heavy-showers-wreak-havoc-in-city-schools-colleges-shut-as-imd-issues-red-alert-sion-matunga-dadar-vile-parle-waterlogged-andheri-subway-closed</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>मराठा सेनापति रघुजी भोंसले की 200 साल पुरानी तलवार पहुंची मुंबई, CM फडणवीस बोले-</t>
+          <t>Fadnavis Gifts Unpublished Shivaji Maharaj Letters to Maharashtra Governor at Mumbai Airport</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/london-auction-historic-raghuji-bhosale-sword-brought-to-mumbai-devendra-fadnavis-says-indias-heritage-restored-2997814</t>
+          <t>https://panasiabiz.com/111091/cm-devendra-fadnavis-presents-rare-shivaji-maharaj-letters-to-governor-cp-radhakrishnan/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Manoj Jarange Vs Devendra Fadnavis : आरक्षण घेणारच, आडवा येऊन दाखव ! मनोज जरांगेंचा फडणवीसांना इशारा</t>
+          <t>Heavy rains lash Nanded: Five missing, scores stranded, says CM Fadnavis; Army unit deployed</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/video/mt-originals/manoj-jarange-alligation-on-devendra-fadnavis/videoshow/123365218.cms</t>
+          <t>https://www.newsdrum.in/national/heavy-rains-lash-nanded-five-missing-scores-stranded-says-cm-fadnavis-army-unit-deployed-9672306</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Third Mumbai News: तिसरी मुंबई आणि आर्थिक विकासाबाबत CM फडणवीसांचे मोठे विधान</t>
+          <t>Maharashtra government approves major infra projects</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/third-mumbai-will-open-a-new-chapter-of-economic-development-says-cm-devendra-fadnavis-9110192</t>
+          <t>https://www.thehawk.in/news/india/maharashtra-government-approves-major-infra-projects</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis: चार लाख हेक्टर क्षेत्रावरील पिकांना फटका; मुख्यमंत्र्यांनी घेतला राज्यातील स्थितीचा आढावा</t>
+          <t>महाराष्ट्र के इस जिले में बसाई जाएगी 'तीसरी मुंबई', मुख्यमंत्री देवेंद्र फडणवीस ने बताईं प्रोजेक्ट की अहम ब</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/heavy-rains-damage-crops-on-4-lakh-hectares-cm-devendra-fadnaivs-reviews-situation-in-maharashtra/articleshow/123379831.cms</t>
+          <t>https://www.indiatv.in/paisa/business/third-mumbai-will-be-settled-in-raigad-district-of-maharashtra-chief-minister-devendra-fadnavis-told-the-important-points-of-the-project-2025-08-19-1156854</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>इतिहासाची अमूल्य खुण भारतात! इतिहासाशी पुन्हा जोडणारा क्षण, मुख्यमंत्री फडणवीसांची भावनिक प्रतिक्रिया</t>
+          <t>Mumbai Maharashtra Rains: महाराष्ट्र में भारी बारिश पर सीएम देवेंद्र फडणवीस का सख्त निर्देश, सभी विभाग अलर्ट पर</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/chief-minister-devendra-fadnavis-statement-after-bringing-sword-of-raje-raghuji-bhosale-to-india-vru98</t>
+          <t>https://thecsrjournal.in/mumbai-maharashtra-rains-cm-and-managment-on-alert-hindi/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Mumbai Rain : मुंबईत संध्याकाळी समुद्राला भरती, पुढील 12 तास महत्त्वाचे, पावसाच्या थैमानानंतर</t>
+          <t>दिल्ली पहुंचे देवेंद्र फडणवीस, अमित शाह से मिले, जानें क्यों थी यह मुलाकात खास</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-on-mumbai-maharashtra-rain-today-visit-disaster-management-department-bmc-marathi-news-1377962</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B6-%E0%A4%B9-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A5%87-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%82-%E0%A4%A5-%E0%A4%AF%E0%A4%B9-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4-%E0%A4%96-%E0%A4%B8/ar-AA1Jjy9z</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis| मुख्यमंत्री देवेंद्र फडणवीस १९ रोजी पैठण तालुक्यात</t>
+          <t>उप-राष्ट्रपति चुनाव: देवेंद्र फडणवीस का 'मराठी अस्मिता' वाला दांव, क्या करेंगे</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/marathwada/chhatrapati-sambhajinagar/devendra-fadnavis-visit-paithan-taluka-19-august-ng81</t>
+          <t>https://www.abplive.com/states/maharashtra/vice-president-election-2025-maharashtra-cm-devendra-fadnavis-request-uddhav-thackeray-and-sharad-pawar-2997542</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Maharashtra Politics : एकनाथ शिंदेंची कोण करतंय कोंडी? दिल्ली दौरे वाढण्यामागचं काय कारण?</t>
+          <t>कैसी होगी तीसरी मुंबई, कितनी बड़ी और कहां बन रही, सुविधाओं से लेकर प्लानिंग तक, CM फडणवीस ने सब बताया</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/maharashtra-politics-shiv-sena-eknath-shinde-bjp-devendra-fadnavis-conflict-before-bmc-election-sdp-92-5314661/</t>
+          <t>https://ndtv.in/maharashtra-news/maharashtra-cmdevendra-fadnavis-told-third-mumbai-mmr-will-develop-with-this-know-how-it-will-be-9112502</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CM देवेंद्र फडणवीस लवकरच कर्जमाफीची घोषणा करतील महायुतीच्या मंत्र्यांनी दिली</t>
+          <t>Vice President Election: उद्धव ठाकरे और शरद पवार से फडणवीस मांगेंगे सीपी राधाकृष्णन के लिए समर्थन, शिंदे सेना ने दिया सपोर्ट</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/cm-devendra-fadnavis-will-soon-announce-loan-waiver-farmers-mahayuti-ministers-sanjay-rathod-gave-information-yavatmal-1377983</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-governor-radhakrishnan-gets-nda-backing-for-vice-president-post-devendra-fadnavis-uddhav-thackeray-sharad-pawar/articleshow/123371527.cms</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>CM Devendra Fadnavis : हिंदवी स्वराज्याचा इतिहास नवीन पिढीपर्यंत पोहोचेल; श्रीमंत राजे रघुजी भोसले यांच्या तलवारीचे स्वागत</t>
+          <t>मुख्यमंत्री देवेंद्र फडणवीस ने राज्य में भारी बारिश के मद्देनजर सभी एजेंसियों को सतर्क रहने के निर्देश दिए</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/legacy-of-hindavi-swarajya-rajarshi-raghuji-bhosales-sword-welcomed-history-cm-devendra-fadnavis-pjp78</t>
+          <t>https://www.mumbailive.com/hi/civic/chief-minister-devendra-fadnavis-directed-all-agencies-to-remain-alert-in-view-of-heavy-rains-in-the-state-89633</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Maharashtra Rain Updates: मुंबईसाठी पुढील 12 तास महत्त्वाचे, राज्यात स्थिती काय? CM फडणवीसांनी सगळं सांगितल...</t>
+          <t>मुंबई में सिर्फ 6-8 घंटे में 177 मिमी हुई बारिश, फडणवीस ने दिए सावधानी बरतने के निर्देश</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/maharashtra-rain-update-cm-devendra-fadnavis-hold-meeting-with-district-administration-1460734.html</t>
+          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/mumbai-received-177-mm-of-rain-in-just-6-8-hours-fadnavis-gave-instructions-to-take-precautions-11195</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Fadnavis government contractors payment: कंत्राटदारांचे पैसे फेडताना फडणवीस सरकारच्या नाकीनऊ: हातभर थकबाकी असताना मिळाले चिमूटभरच</t>
+          <t>Mumbai Rain News : मुंबई में बारिश ने मचाया कोहराम, देवेंद्र फडणवीस का आया बयान</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/fadnavis-govt-struggles-to-pay-contractors-pending-dues-sw79</t>
+          <t>https://hindi.oneindia.com/videos/mumbai-rain-news-rain-wreaked-havoc-in-mumbai-devendra-fadnavis-statement-came-4259449.html</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>गौरवशाली इतिहासाशी नव्या पीढीला जोडण्याचं काम रघुजीराजे भोसल्यांची ऐतिहासिक</t>
+          <t>मुंबई में भारी भारिश ने मचाई तबाही, CM देवेंद्र फडणवीस ने बुलाई बैठक</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-mumbai-exhibition-of-nagpur-raghuji-raje-bhosle-historical-sword-marathi-news-1378075</t>
+          <t>https://www.patrika.com/videos/mumbai-news/heavy-rain-wreaks-havoc-in-mumbai-cm-devendra-fadnavis-calls-a-meeting-19874343</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>पूरस्थितीचा सामना करण्यासाठी सरकारकडून सर्वतोपरी प्रयत्न, अतिवृष्टीचा धोका लक्षात घेऊन लोकांनी खबरदारी घ्यावी, मुख्यमंत्र्यांचं आवाहन</t>
+          <t>फडणवीस ने कहा, ‘तीसरी मुंबई’ से एमएमआर का होगा विकास</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/maharashtra-government-is-making-every-effort-to-deal-with-the-flood-situation-the-chief-minister-appeals-to-people-to-be-careful-considering-the-risk-of-heavy-rains-maharashtra-news-mhs25081804221</t>
+          <t>https://hindi.theprint.in/india/economy/fadnavis-said-third-mumbai-will-lead-to-development-of-mmr/856867/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>'औरंगजेब भारत के किसी भी समाज का हीरो नहीं...', मजार को लेकर फडणवीस ने कही बड़ी बात</t>
+          <t>महाराष्ट्र के नांदेड़ में फटा बादल, 15-16 जिलो में अलर्ट, CM फडणवीस बोले- फसलों को नुकसान</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%AD-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AE%E0%A4%9C-%E0%A4%B0-%E0%A4%95-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC-%E0%A4%A4/ar-AA1IRFiN</t>
+          <t>https://www.abplive.com/states/maharashtra/weather-mumbai-rains-local-train-cloudburst-nanded-alert-in-15-16-districts-in-maharashtra-cm-devendra-fadnavis-said-damage-to-crops-2997472</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Manoj Jarange Vs Devendra Fadnavis : आरक्षण घेणारच, आडवा येऊन दाखव ! मनोज जरांगेंचा फडणवीसांना इशारा</t>
+          <t>CP Radhakrishnan को लेकर CM फडणवीस ने बड़ा खुलासा कर चल दिया दांव, अब क्‍या करेंगे उद्धव ठाकरे और शरद पवार?</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/manoj-jarange-vs-devendra-fadnavis-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%98%E0%A5%87%E0%A4%A3-%E0%A4%B0%E0%A4%9A-%E0%A4%86%E0%A4%A1%E0%A4%B5-%E0%A4%AF%E0%A5%87%E0%A4%8A%E0%A4%A8-%E0%A4%A6-%E0%A4%96%E0%A4%B5-%E0%A4%AE%E0%A4%A8-%E0%A4%9C-%E0%A4%9C%E0%A4%B0-%E0%A4%82%E0%A4%97%E0%A5%87%E0%A4%82%E0%A4%9A-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%A8-%E0%A4%87%E0%A4%B6-%E0%A4%B0/vi-AA1KJrkK?ocid=hpmsn</t>
+          <t>https://hindi.oneindia.com/news/maharashtra/vice-presidential-election-cm-devendra-fadnavis-said-cp-radhakrishnan-is-a-mumbai-voter-support-him-1365243.html</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>मराठ्यांच्या इतिहासाची साक्षीदार; श्रीमंत राजे रघुजी भोसलेंच्या ऐतिहासिक तलवारीचं लोकार्पण, पाहा खास PHOTO</t>
+          <t>मैं आपकी वहिनी… देवेंद्र फडणविस के शपथ लेते ही पत्नी अमृता फडणवीस ने महाराष्ट्र से किया ये वादा</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/photogallery/news/raghuji-bhosale-sword-inauguration-in-mumbai-by-cm-devendra-fadnavis/photoshow/123367923.cms</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%88%E0%A4%82-%E0%A4%86%E0%A4%AA%E0%A4%95-%E0%A4%B5%E0%A4%B9-%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%B6%E0%A4%AA%E0%A4%A5-%E0%A4%B2%E0%A5%87%E0%A4%A4%E0%A5%87-%E0%A4%B9-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A8-%E0%A4%85%E0%A4%AE%E0%A5%83%E0%A4%A4-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%AF%E0%A5%87-%E0%A4%B5-%E0%A4%A6/ar-AA1vljO5?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Mumbai Heavy Rain : राज्यभरात पावसाचा कहर, पाहा कुठे कुठे दिलाय रेड आणि ऑरेंज अलर्ट</t>
+          <t>मराठा सेनापति रघुजी भोंसले की 200 साल पुरानी तलवार पहुंची मुंबई, CM फडणवीस बोले-</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-mumbai-rains-heavy-rainfall-lashes-maharashtra-schools-closed-cm-devendra-fadnavis-to-review-situation-1377933</t>
+          <t>https://www.abplive.com/states/maharashtra/london-auction-historic-raghuji-bhosale-sword-brought-to-mumbai-devendra-fadnavis-says-indias-heritage-restored-2997814</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>महाराष्ट्रात महाभयानक पाऊस! मुख्यमंत्री देवेंद्र फडणवीस यांनी तातडीने साधला शेजारील राज्यांशी संपर्क? कारण अतिशय चिंताजनक</t>
+          <t>'औरंगजेब भारत के किसी भी समाज का हीरो नहीं...', मजार को लेकर फडणवीस ने कही बड़ी बात</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/maharashtra-mumbai-rain-alert-update-chief-minister-devendra-fadnavis-immediately-contacted-the-neighboring-states/933328</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%AD-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AE%E0%A4%9C-%E0%A4%B0-%E0%A4%95-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC-%E0%A4%A4/ar-AA1IRFiN</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>पुण्यात मुसळधार पाऊस पडतोय, आम्हाला वर्क फ्रॉम होम द्या! थेट मुख्यमंत्र्यांकडे आयटी कर्मचाऱ्यांची मागणी</t>
+          <t>Maharashtra: फडणवीस बोले- औरंगजेब भारत का हीरो नहीं, सुप्रीम कोर्ट के SC आरक्षण पर फैसले को लागू करेगी सरकार</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/it-company-employees-demand-work-from-home-due-to-heavy-rain-appeals-cm-devendra-fadnavis-pune-print-news-css-98-5314597/</t>
+          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B8%E0%A5%81%E0%A4%AA%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%95%E0%A5%87-sc-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%AA%E0%A4%B0-%E0%A4%AB%E0%A5%88%E0%A4%B8%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B2-%E0%A4%97%E0%A5%82-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%97-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0/ar-AA1IRMGx</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Mumbai News: गोल्डमन सॅक्सचे मुंबई नवे कार्यालय तिसऱ्या मुंबईचा नवा अध्याय - देवेंद्र फडणवीस</t>
+          <t>Maharashtra: 'पुणे के विकास में सबसे बड़ी बाधा बन चुकी है उद्योगों पर दादागीरी', सीएम फडणवीस ने दी चेतावनी</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/goldman-sachs-new-mumbai-office-is-a-new-chapter-for-third-mumbai-devendra-fadnavis-89597</t>
+          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AA%E0%A5%81%E0%A4%A3%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%B5-%E0%A4%95-%E0%A4%B8-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8%E0%A4%AC%E0%A4%B8%E0%A5%87-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC-%E0%A4%A7-%E0%A4%AC%E0%A4%A8-%E0%A4%9A%E0%A5%81%E0%A4%95-%E0%A4%B9%E0%A5%88-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%97-%E0%A4%82-%E0%A4%AA%E0%A4%B0-%E0%A4%A6-%E0%A4%A6-%E0%A4%97-%E0%A4%B0-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%A6-%E0%A4%9A%E0%A5%87%E0%A4%A4-%E0%A4%B5%E0%A4%A8/ar-AA1JMfla?ocid=finance-verthp-feeds&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Mumbai Rain Update : समुद्रातून येतंय मुंबईवर मोठं संकट, पुढच्या 12 तासांत तुफान पाऊस, फडणवीस काय...</t>
+          <t>Mumbai Rains News: भारी बारिश के चलते कल मुंबई के स्कूल-कॉलेजों में छुट्टी, नांदेड़ में 7 लोगों की मौत, CM फडणवीस ने की आपात बैठक</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/mumbai-rain-alert-cm-devendra-fadnavis-said-mumbai-have-red-alert-school-holiday-declared-know-detail-information-in-marathi-1472488.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/heavy-rains-in-mumbai-schools-colleges-closed-7-deaths-in-maharashtra-5-missing-nanded-cm-fadnavis-emergency-meeting/articleshow/123366462.cms</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Third Mumbai महानगर क्षेत्राच्या विकासाचा नवा अध्याय असेल; मुख्यमंत्र्यांनी सांगितलं कशी असेल ‘तिसरी मुंबई’ Third Mumbai in Raigad district to boost metropolitan region development said Devendra Fadnavis</t>
+          <t>फडणवीस की पत्नी के खिलाफ अपमानजनक पोस्ट : दो लोगों की अग्रिम जमानत अर्जी खारिज</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/third-mumbai-in-raigad-district-to-boost-metropolitan-region-development-said-devendra-fadnavis-89724</t>
+          <t>http://www.msn.com/hi-in/news/other/%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%96-%E0%A4%B2-%E0%A4%AB-%E0%A4%85%E0%A4%AA%E0%A4%AE-%E0%A4%A8%E0%A4%9C%E0%A4%A8%E0%A4%95-%E0%A4%AA-%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%A6-%E0%A4%B2-%E0%A4%97-%E0%A4%82-%E0%A4%95-%E0%A4%85%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%9C%E0%A4%AE-%E0%A4%A8%E0%A4%A4-%E0%A4%85%E0%A4%B0%E0%A5%8D%E0%A4%9C-%E0%A4%96-%E0%A4%B0-%E0%A4%9C/ar-AA1Je80j?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>మూడో ముంబై వచ్చేస్తోంది!</t>
+          <t>मुंबई में 6-8 घंटे में 177 मिलीमीटर बारिश हुई: फडणवीस</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>https://www.ap7am.com/tn/838759/third-mumbai-new-city-announced-by-devendra-fadnavis</t>
+          <t>https://hindi.theprint.in/india/mumbai-received-177-mm-of-rain-in-6-8-hours-fadnavis/856688/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>CM Devendra Fadnavis: राज्यातील चार लाख हेक्टर क्षेत्रावरील पिकांना फटका; पिकांचे पंचनामे करण्याचे आदेश</t>
+          <t>नांदेड़ में भारी बारिश के कारण पांच लोग लापता, कई व्यक्ति फंसे : मुख्यमंत्री फडणवीस</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/crops-affected-on-four-lakh-hectares-of-land-in-the-state-orders-to-conduct-crop-surveys/</t>
+          <t>https://hindi.theprint.in/india/five-people-missing-many-people-stranded-due-to-heavy-rains-in-nanded-chief-minister-fadnavis/856679/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में मौसम बरपा रहा कहर: नांदेड़ में फटा बादल, बारिश के चलते 15 से 16 जिलो में अलर्ट, CM फडणवीस ने फसलों से लेकर लोकल ट्रेनों के बारे में दिया ये बड़ा अपडेट | Devendra Fadnavis, Cloudburst, Nan</t>
+          <t>महाराष्ट्र में भारी बारिश का कहर, 16 जिलों में रेड अलर्ट, बचाव दल तैनात</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/politics/devendra-fadnavis-cloudburst-nanded-maharashtra-news-maharashtra-1174025</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-heavy-rainfall-flood-alert-red-and-orange-alerts-issued-relief-operations-mumbai-rain-ann-2997660</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Mumbai Rain Update: मुंबईसाठी पुढील 10 ते 12 तास महत्वाचे! पावसापासून बचावासाठी मुख्यमंत्र्यांनी काय दिलाय इशारा?</t>
+          <t>Mumbai Rain: 24 घंटे की बारिश से मुंबई की सांस फूली, CM देवेंद्र फडणवीस ने पड़ोसी राज्यों से किया संपर्क</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/mumbai-rain-update-next-10-to-12-hours-are-important-for-mumbai-people-cm-devendra-fadnavis-warning-to-stay-safe-from-rain-aau85</t>
+          <t>https://zeenews.india.com/hindi/india/mumbai-rains-today-imd-red-alert-warning-waterlogging-traffic-update/2886161</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis : नांदेड जिल्ह्यातील अतिवृष्टीवर मुख्यमंत्र्यांची नजर, प्रशासनाला सूचना</t>
+          <t>Raghuji Bhosale: आज मुंबई आएगी रघुजी भोसले की की ऐतिहासिक तलवार, सीएम फडणवीस करेंगे स्वागत</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/devendra-fadnavis-chief-ministers-eye-on-heavy-rains-in-nanded-district-instructions-to-the-administration/</t>
+          <t>https://zeenews.india.com/hindi/india/raghuji-bhosale-historic-sword-will-arrive-in-mumbai-today-cm-fadnavis-will-welcome-it/2886138</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>मुंबईसह महाराष्ट्रात मुसळधार: मुंबई व उपनगरांत सगळीकडे पाणीच पाणी; अनेक जिल्ह्यांत रेड अलर्ट, पुणे ते मुंबई...</t>
+          <t>फडणवीस छात्रों को हिंदी पढ़ाने के बारे में सोच रहे, लेकिन प्रवासी मजदूरों को मराठी नहीं: राज ठाकरे</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/maharashtra-heavy-rain-mumbai-red-alert-nanded-army-rescue-cm-fadnavis-statement-135709315.html</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%9B-%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%82-%E0%A4%95-%E0%A4%B9-%E0%A4%82%E0%A4%A6-%E0%A4%AA%E0%A4%A2%E0%A4%BC-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%B0%E0%A5%87-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8-%E0%A4%9A-%E0%A4%B0%E0%A4%B9%E0%A5%87-%E0%A4%B2%E0%A5%87%E0%A4%95-%E0%A4%A8-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%B8-%E0%A4%AE%E0%A4%9C%E0%A4%A6%E0%A5%82%E0%A4%B0-%E0%A4%82-%E0%A4%95-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B0-%E0%A4%9C-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87/ar-AA1JMr77?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>लाटा पाहण्याच्या मोहापाई लोक अडचणीत येतात....: तुफान पावसामुळे मुख्यमंत्री फडणवीसांनी केले आवाहन</t>
+          <t>'Indias Got Latent' विवाद पर अभिनेता से नेता तक भड़के, CM फडणवीस बोले-होना चाहिए एक्शन</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/cm-devendra-fadnavis-live-press-on-mumbai-rain-update-red-alert-963319.html</t>
+          <t>https://www.msn.com/hi-in/news/other/indias-got-latent-%E0%A4%B5-%E0%A4%B5-%E0%A4%A6-%E0%A4%AA%E0%A4%B0-%E0%A4%85%E0%A4%AD-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%B8%E0%A5%87-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%A4%E0%A4%95-%E0%A4%AD%E0%A4%A1%E0%A4%BC%E0%A4%95%E0%A5%87-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%B9-%E0%A4%A8-%E0%A4%9A-%E0%A4%B9-%E0%A4%8F-%E0%A4%8F%E0%A4%95%E0%A5%8D%E0%A4%B6%E0%A4%A8/ar-AA1yKIjb?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>सोलापुरात भाजपची शिंदेंच्या शिवसेनावर कुरघोडी शिवाजी सावंतांनी शिवसेना सोडली,</t>
+          <t>मुंबई में भारी बारिश के बीच सुचारू रूप से चल रही मेट्रो, सीएम फडणवीस ने की तारीफ</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/solapur-shivaji-sawant-leaves-shiv-sena-and-bjp-entry-confirmed-devendra-fadnavis-bjp-attack-on-eknath-shinde-shiv-sena-in-solapur-1377928</t>
+          <t>https://www.m.khaskhabar.com/news/news-metro-running-smoothly-amid-heavy-rains-in-mumbai-cm-fadnavis-praised-news-hindi-1-745323-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>CM Relief Fund: रुग्णांसाठी सरकारचा 'हा' विभाग ठरतोय मदतशीर; अमरावती विभागात तब्बल १०.६१ कोटींची मदत</t>
+          <t>महाराष्ट्र में बन रही है तीसरी मुंबई, इस जिले का होगा आर्थिक विकास, जानें पूरी जानकारी | News Track in...</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/amravati/cm-devendra-fadnavis-cm-relief-fund-help-amravati-1187-patients-for-10-crore-rs-health-marathi-news-963412.html</t>
+          <t>https://newstrack.com/india/third-mumbai-being-built-maharashtra-district-have-economic-development-know-full-details-534715</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>तिसरी मुंबई म्हणजे आर्थिक विकासाचा नवा अध्याय असेल! मुख्यमंत्री देवेंद्र फडणवीस यांचे प्रतिपादन</t>
+          <t>CM फडणवीस ने खेला 'मराठी अस्मिता' का दांव, उपराष्ट्रपति चुनाव में उद्धव-पवार पर बना दबाव</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/mumbai/mumbai-connectivity-coastal-road-atal-setu-worli-shivdi-link</t>
+          <t>https://navbharatlive.com/maharashtra/political-battle-over-nda-candidate-radhakrishnan-cm-fadnavis-seeks-support-from-uddhav-thackeray-and-sharad-pawar-1321873.html</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Maharashtra Rain : राज्यासाठी पुढचे दोन दिवस चिंतेचे, 15-16 जिल्ह्यांना अलर्ट, कुठे होणार अतिवृष्टी?...</t>
+          <t>महाराष्ट्र किसानों को मिलेगी बड़ी राहत, CM फडणवीस जल्द करेंगे कर्जमाफी की घोषणा</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/maharashtra-imd-issues-red-alert-for-16-districts-big-information-by-cm-devendra-fadnavis-reviews-heavy-rains-in-1472606.html</t>
+          <t>https://navbharatlive.com/maharashtra/guardian-minister-sanjay-rathore-claims-cm-fadnavis-may-announce-a-loan-waiver-for-farmers-1322081.html</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Maharashtra Rains: राज्यात अतिवृष्टी, 7 जणांचा मृत्यू; मुख्यमंत्र्यांचे सर्व यंत्रणांना सतर्कतेचे निर्देश Maharashtra Rains: Heavy rains in the state, 7 people died; CM Devendra Fadnavis directs all agencies to be alert</t>
+          <t>बाढ़ संकट पर अबू आजमी का CM फडणवीस को पत्र, प्रभावितों तक तुरंत राहत पहुंचाने की मांग</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-rains-heavy-rains-in-the-state-7-people-died-cm-devendra-fadnavis-directs-all-agencies-to-be-alert-89603</t>
+          <t>https://navbharatlive.com/latest-news/abu-azmi-wrote-a-letter-to-cm-devendra-fadnavis-asking-him-to-send-relief-supplies-to-flood-affected-region-1322005.html</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Mumbai Heavy Rain : मुंबईसाठी पुढील 10-12 तास धोक्याचे, मुख्यमंत्री फडणवीसांनी मुंबईकरांना केलं सावध</t>
+          <t>नांदेड़ में मूसलधार बारिश से हाहाकार, CM फडणवीस की निगरानी में राहत कार्य तेज</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/heavy-rains-in-mumbai-next-48-hours-are-crucial-chief-minister-devendra-fadnavis-warns-citizens-to-be-alert/913099/</t>
+          <t>https://navbharatlive.com/maharashtra/heavy-rains-cause-havoc-in-nanded-rescue-operation-intensified-under-the-supervision-of-cm-fadnavis-1321752.html</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>राज्यात अतिवृष्टीच्या पार्श्वभूमीवर प्रशासन अलर्ट मोडवर! मुख्यमंत्री देवेंद्र फडणवीस यांचे सतर्कतेचे निर्देश</t>
+          <t>Maharashtra News Live: एक क्लिक में पढ़े महाराष्ट्र की दिन भर की बड़ी खब़रें...</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/cm-devendra-fadnavis-took-review-of-rain-situation-at-state-disaster-management-centre-in-the-ministry-963383.html</t>
+          <t>https://navbharatlive.com/maharashtra/latest-live-updates-maharashtra-politics-crime-nagpur-news-mumbai-pune-18-august-1321138.html</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CP Radhakrishnan को लेकर CM फडणवीस ने बड़ा खुलासा कर चल दिया दांव, अब क्‍या करेंगे उद्धव ठाकरे और शरद पवार?</t>
+          <t>CM फडणवीस लगा रहे जोर, अधिकारी कर रहे मनामानी, FIA ने जतायी नाराजगी</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/maharashtra/vice-presidential-election-cm-devendra-fadnavis-said-cp-radhakrishnan-is-a-mumbai-voter-support-him-1365243.html</t>
+          <t>https://navbharatlive.com/maharashtra/federation-of-industries-association-is-angry-due-to-ignorance-of-msme-sector-in-vidarbha-1322498.html</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>देवेंद्र फडणवीस यांच्यासोबतच्या कोल्ड वॉरच्या चर्चेवर एकनाथ शिंदे यांची प्रतिक्रिया, स्पष्टच म्हणाले....</t>
+          <t>कोल्हापुर में CJI गवई ने की सीएम और डिप्टी सीएम के सामने उनकी तारीफ, बोले- "जो लोग शिकायत कर रहे वे देवेंद्र फडणवीस और एकनाथ शिंदे के बारे में नहीं जानते…"</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/national/%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%AC%E0%A4%A4%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%A1-%E0%A4%B5-%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A%E0%A5%87%E0%A4%B5%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A4%9A-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1zqXD8?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://lalluram.com/in-kolhapur-cji-gavai-praised-him-in-front-of-cm-and-deputy-cm-said-those-who-are-complaining-do-not-know-about-devendra-fadnavis-and-eknath-shinde/</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>उपराष्ट्रपतीपदाचे उमेदवार राधाकृष्णन यांना पाठिंबा द्या; देवेंद्र फडणवीस यांची शरद पवार आणि उद्धव ठाकरे यांना साद</t>
+          <t>अबू आजमी ने सीएम देवेंद्र फडणवीस को लिखा पत्र, बाढ़ प्रभावित इलाकों में राहत सामग्री पहुंचाने की मांग की</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/maharashtra/cp-radhakrishnan-vice-president-candidate-fadnavis-appeal-pawar-thackeray</t>
+          <t>https://www.newsnationtv.com/abu-azmi-ne-cm-devendra-fadnavis-ko-likha-patra-badh-prabhavit-ilakon-mein-rahat-pahunchane-ki-mang-ki--20250818191027/</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Marathwada Rain : मराठवाड्यात शेतीचे सर्वाधिक नुकसान; नांदेडमध्ये ढगफुटी सदृष्य पाऊस, पाच जण बेपत्ता</t>
+          <t>Mumbai News: महाराष्ट्र में मूसलाधार बारिश से हाहाकार, मुख्यमंत्री की हाईलेवल बैठक, विशेष सत्र बुलाने की मांग | Heavy rains cause havoc in Maharashtra, high level meeting of Chief Minister, demand for calling special s</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/cloudburst-rain-in-mukhed-nanded-district-five-people-missing-chief-minister-devendra-fadnavis-gave-information/913157/</t>
+          <t>https://www.bhaskarhindi.com/city/mumbai/mumbai-news-heavy-rains-cause-havoc-in-maharashtra-high-level-meeting-of-chief-minister-demand-for-calling-special-session-1174171</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>मुंबई झोपडपट्टीमुक्त होणार का? जलद पुनर्विकासाचा मुख्यमंत्र्यांनी काय सांगितला प्लॅन?</t>
+          <t>महाराष्ट्र में भारी बारिश से कई जिलों में रेड और ऑरेंज अलर्ट</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>https://www.tendernama.com/mahatender/mumbai/will-mumbai-become-slum-free-what-is-the-chief-ministers-plan-for-rapid-redevelopment</t>
+          <t>https://vikalptimes.com/red-and-orange-alert-issued-in-many-districts-of-maharashtra-due-to-heavy-rains/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>मैं आपकी वहिनी… देवेंद्र फडणविस के शपथ लेते ही पत्नी अमृता फडणवीस ने महाराष्ट्र से किया ये वादा</t>
+          <t>CM फडणवीस ने एनडीए के उपराष्ट्रपति पद के नामांकन पर सीपी राधाकृष्णन को शॉल भेंट की</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%88%E0%A4%82-%E0%A4%86%E0%A4%AA%E0%A4%95-%E0%A4%B5%E0%A4%B9-%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%B6%E0%A4%AA%E0%A4%A5-%E0%A4%B2%E0%A5%87%E0%A4%A4%E0%A5%87-%E0%A4%B9-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A8-%E0%A4%85%E0%A4%AE%E0%A5%83%E0%A4%A4-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%AF%E0%A5%87-%E0%A4%B5-%E0%A4%A6/ar-AA1vljO5?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://jantaserishta.com/local/maharashtra/cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vice-president-nomination-4218433</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Devendra Fadnvis | मुख्यमंत्री देवेंद्र फडणवीस १९ रोजी पैठण तालुक्यात</t>
+          <t>उपराष्ट्रपति चुनाव में भाजपा का दांव, सीपी राधाकृष्णन उम्मीदवार, महाराष्ट्र की राजनीति में बढ़ी हलचल</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/devendra-fadnvis-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A5%A7%E0%A5%AF-%E0%A4%B0-%E0%A4%9C-%E0%A4%AA%E0%A5%88%E0%A4%A0%E0%A4%A3-%E0%A4%A4-%E0%A4%B2%E0%A5%81%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%A4/ar-AA1KKgDI</t>
+          <t>https://mpbreakingnews.in/maharashtra/vice-president-election-bjp-candidate-cp-radhakrishnan-devendra-fadnavis-54-803924</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Maharashtra Heavy Rainfall | राज्यभरात अतिवृष्टीचा कहर; १५ जिल्ह्यांत रेड आणि ऑरेंज अलर्ट, नागरिकांनी घराबाहेर पडू नये: मुख्यमंत्री फडणवीस</t>
+          <t>Mumbai Rains: मुंबई में भारी बारिश से 12 लोगों की मौत, जगह-जगह कमर तक भरा पानी, स्कूल-कॉलेज बंद, फ्लाइट्स पर भी असर</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/maharashtra-heavy-rainfall-red-orange-alert-15-districts-cm-fadnavis-advisory-as80</t>
+          <t>https://lalluram.com/mumbai-rains-7-people-died-due-to-rain-water-flooded-on-roads-schools-and-colleges-closed-flights-also-affected/</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>LIVE Update : मुंबईतील सर्व शाळांना उद्या सुट्टी जाहीर</t>
+          <t>महाराष्ट्र : भारी बारिश के बाद नांदेड़ में राहत कार्य तेज, प्रशासन के संपर्क में सीएम फडणवीस</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/live-update-mumbai-rain-best-co-operative-soc-election-live-maharashtra-update-political-rain-update-devendra-fadnavis-ajit-pawar-eknath-shinde-uddhav-thackeray-raj-thackeray/913004/</t>
+          <t>https://www.newsnationtv.com/maharashtra-bhari-barish-ke-baad-nanded-mein-rahat-bachav-karya-tez-jiladhikariyon-ke-sampark-mein-cm-fadnavis--20250818144516/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Maharashtra Rain: राज्यात पावसाचा हाहाकार! १६ जिल्ह्यांना रेड- ऑरेंज अलर्ट, मुख्यमंत्र्यांकडून सतर्क राहण्याचे आवाहन</t>
+          <t>किसानों को जल्द मिल सकता है कर्जमाफी का तोहफा, मंत्री संजय राठोड़ का बड़ा बयान</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/mumbai-pune/maharashtra-floods-cm-fadnavis-reviews-situation-ndrf-and-army-deployed-16-districts-on-red-alert-latest-news-pvm91</t>
+          <t>https://mpbreakingnews.in/maharashtra/farmer-loan-waiver-maharashtra-sanjay-rathod-devendra-fadnavis-54-804134</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>LIVE Update : मुंबईत चौथ्या दिवशीही पावसाची धुवाँधार बॅटिंग; आकाशात काळ्या ढगांची गर्दी</t>
+          <t>Mumbai: राज्यपाल की उपराष्ट्रपति पद की उम्मीदवारी पर मुख्यमंत्री ने जताया हर्ष</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/desh-videsh/live-update-mumbai-rain-best-co-operative-soc-election-live-maharashtra-update-political-rain-update-devendra-fadnavis-ajit-pawar-eknath-shinde-uddhav-thackeray-raj-thackeray-2/913299/</t>
+          <t>https://jantaserishta.com/local/maharashtra/mumbai-chief-minister-expressed-happiness-over-the-candidature-of-the-governor-for-the-post-of-vice-president-mumbai--4218462</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>महाराष्ट्रात इथं पडतोय ढगफुटीसदृष्य पाऊस! गुरं दगावली, लोक अडकले, आर्मीची मदत अन्..; फडणवीसांनी घेतली दखल</t>
+          <t>नांदेड़ में भारी बारिश के कारण पांच लोग लापता, कई व्यक्ति फंसे : मुख्यमंत्री फडणवीस</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/cloud-burst-types-rain-in-nanded-indian-army-called-for-rescue-cm-devendra-fadnavis-reacts/933262</t>
+          <t>https://www.ibc24.in/maharashtra/five-people-missing-several-stranded-due-to-heavy-rains-in-nanded-cm-fadnavis-3212983.html</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Shivaji Sawant : तानाजी सावंतांचे बंधू शिवाजी सावंतांचा भाजप प्रवेश निश्चित; मुख्यमंत्र्यांच्या भेटीनंतर जाहीर केला निर्णय</t>
+          <t>लंदन से आई मराठा साम्राज्य की शान! रघुजी ?...</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/shivaji-sawants-entry-into-bjp-confirmed-decision-announced-after-meeting-with-chief-minister-vd83</t>
+          <t>https://bharatexpress.com/india/raghuji-bhosale-historic-sword-returned-from-london-grand-welcome-in-mumbai-553050</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ज्या राज्याच्या मुख्यमंत्र्यांच्या सुविद्य पत्नी गायिका आहेत, त्या राज्यातील...; ठाकरे सेनेकडून माफीची मागणी</t>
+          <t>महाराष्ट्र की 'अस्मिता' की बात करने वाले उपराष्ट्रपति पद के लिए राधाकृष्णन का समर्थन करें : फडणवीस</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/nanded-umri-tehsildar-suspended-for-singing-while-sitting-on-a-chair-uddhav-thackeray-shivsena-slams-chandrashekhar-bawankule-mention-devendra-fadnavis-wife/933459</t>
+          <t>https://navabharat.news/support-radhakrishnan-for-the-post-of-vice-president-who-talks-about-maharashtras-identity-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Third Mumbai: महाराष्ट्राच्या विकासाचे नवे ग्रोथ सेंटर! काय म्हणाले CM फडणवीस?</t>
+          <t>Rain fury leaves 7 dead in Maharashtra, 200 villagers stranded</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>https://www.tendernama.com/tender-news/third-mumbai-new-growth-center-for-maharashtras-development-what-did-cm-fadnavis-say</t>
+          <t>https://www.ptinews.com/story/national/rain-fury-leaves-7-dead-in-maharashtra-200-villagers-stranded/2834213</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>CM Devendra Fadnavis: मुख्यमंत्र्यांनी राज्यातील पावसाचा घेतला आढावा; 'इतक्या' जिल्ह्यांना पावसाचा रेड अलर्ट, सतर्क राहण्याचे केले आवाहन</t>
+          <t>Mumbai rain highlights: BMC declares holiday for schools, colleges today amid heavy rain forecast</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/cm-fadnavis-takes-reiew-situation-ndrf-and-army-deployed-16-districts-on-red-alert/</t>
+          <t>https://www.hindustantimes.com/india-news/mumbai-rain-live-updates-red-alert-school-closed-heavy-rains-august-18-weather-waterlogging-borivali-thane-powai-bmc-101755498397210.html</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>मुंबई में सिर्फ 6-8 घंटे में 177 मिमी हुई बारिश, फडणवीस ने दिए सावधानी बरतने के निर्देश</t>
+          <t>Mumbai got 177mm rain in 6-8 hour period, says CM; more to come amid high tides</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/mumbai-received-177-mm-of-rain-in-just-6-8-hours-fadnavis-gave-instructions-to-take-precautions-11195</t>
+          <t>https://www.newsdrum.in/national/mumbai-got-177mm-rain-in-6-8-hour-period-says-cm-more-to-come-amid-high-tides-9672488</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Mumbai Rain: मुंबईत उद्या शाळांना सुट्टी? पुढचे १२ तास महत्वाचे, मुख्यमंत्री नेमकं काय म्हणाले?</t>
+          <t>CM देवेंद्र फडणवीस लवकरच कर्जमाफीची घोषणा करतील महायुतीच्या मंत्र्यांनी दिली</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/mumbai-pune/mumbai-rain-alert-cm-devendra-fadnavis-said-mumbai-schools-declared-holiday-on-tomorrow-bmc-to-decide-pvm91</t>
+          <t>https://marathi.abplive.com/news/politics/cm-devendra-fadnavis-will-soon-announce-loan-waiver-farmers-mahayuti-ministers-sanjay-rathod-gave-information-yavatmal-1377983</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Mumbai Rain News : मुंबई में बारिश ने मचाया कोहराम, देवेंद्र फडणवीस का आया बयान</t>
+          <t>राज्यात अतिवृष्टीच्या पार्श्वभूमीवर प्रशासन अलर्ट मोडवर! मुख्यमंत्री देवेंद्र फडणवीस यांचे सतर्कतेचे निर्देश</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/videos/mumbai-rain-news-rain-wreaked-havoc-in-mumbai-devendra-fadnavis-statement-came-4259449.html</t>
+          <t>https://www.navarashtra.com/maharashtra/cm-devendra-fadnavis-took-review-of-rain-situation-at-state-disaster-management-centre-in-the-ministry-963383.html</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>लातूर जिल्ह्यात मुसळधार पाऊस; लेंडी नदीला पूर आल्यानं तेलंगाणातील चार प्रवासी गेले वाहून; मुख्यमंत्र्यांनी घेतला आढावा</t>
+          <t>राज्यात अतिवृष्टीमुळे मुख्यमंत्री देवेंद्र फडणवीस यांचे सर्व यंत्रणांना सतर्कतेचे निर्देश; नांदेड जिल्ह्यात लष्कराची मदत</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/heavy-rains-in-latur-district-cause-flooding-in-many-rivers-cm-devendra-fadnavis-took-a-review-lendi-river-flood-maharashtra-news-mhs25081802447</t>
+          <t>https://www.loksatta.com/mumbai/chief-minister-devendra-fadnavis-has-directed-all-agencies-to-be-on-alert-due-to-heavy-rains-in-the-maharashtra-mumbai-print-news-amy-95-5313479/</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Nanded Rain News: मुखेडमध्ये ढगफुटीसदृश्य पाऊस, CM Devendra Fadanvis यांच्याकडून मदतीच्या सूचना</t>
+          <t>Third Mumbai News: तिसरी मुंबई आणि आर्थिक विकासाबाबत CM फडणवीसांचे मोठे विधान</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/nanded-rain-news-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%87%E0%A4%A1%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A5%87-%E0%A4%A2%E0%A4%97%E0%A4%AB%E0%A5%81%E0%A4%9F-%E0%A4%B8%E0%A4%A6%E0%A5%83%E0%A4%B6%E0%A5%8D%E0%A4%AF-%E0%A4%AA-%E0%A4%8A%E0%A4%B8-cm-devendra-fadanvis-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%AE%E0%A4%A6%E0%A4%A4-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B8%E0%A5%82%E0%A4%9A%E0%A4%A8/vi-AA1KIk6k</t>
+          <t>https://marathi.ndtv.com/maharashtra/third-mumbai-will-open-a-new-chapter-of-economic-development-says-cm-devendra-fadnavis-9110192</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Heavy Rain: राज्यात अतिवृष्टीच्या पार्श्वभूमीवर मुख्यमंत्री देवेंद्र फडणवीस यांचे सर्व यंत्रणांना सतर्कतेचे</t>
+          <t>Devendra Fadnavis : अख्खा पक्ष विरोधात, पण या दिग्गज नेत्याचा फडणवीसांना पाठिंबा, एका पत्राने राजकीय वर्तु...</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/heavy-raincm-devendra-fadnavis-agencies-alert-heavy-rain-state/</t>
+          <t>https://news18marathi.com/maharashtra/cm-devendra-fadnavis-gets-support-from-congress-leader-nitin-raut-letter-goes-viral-1461146.html</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>मुख्यमंत्र्यांनी आज राज्यातल्या पावसाचा घेतला आढावा</t>
+          <t>Devendra Fadnavis : महाराष्ट्रातील माणसाला सर्वांनी समर्थन द्यावं; फडणवीस यांचे मविआला आवाहन</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/mr/devendra-fadnavis-6/</t>
+          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-appeals-to-maharashtra-mps-to-support-cp-radhakrishnan-for-vice-president/913103/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>मोदींचा निर्णय, उमेदवार ठरला अन् अडचणीत उद्धवसेना; 18 वर्षांनी पुन्हा तेच, ठाकरेंसमोर पेच?</t>
+          <t>Mumbai Rain Update : समुद्रातून येतंय मुंबईवर मोठं संकट, पुढच्या 12 तासांत तुफान पाऊस, फडणवीस काय...</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-picks-cp-radhakrishnan-for-vice-president-post-cm-devendra-fadnavis-ask-uddhav-thackeray-for-support/articleshow/123362737.cms</t>
+          <t>https://www.tv9marathi.com/maharashtra/mumbai-rain-alert-cm-devendra-fadnavis-said-mumbai-have-red-alert-school-holiday-declared-know-detail-information-in-marathi-1472488.html</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>मुंबईतील पावसाचा मुख्यमंत्र्यांकडून सातत्याने आढावा</t>
+          <t>Third Mumbai: महाराष्ट्राच्या विकासाचे नवे ग्रोथ सेंटर! काय म्हणाले CM फडणवीस?</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/19/the-chief-minister-is-continuously-reviewing-the-rainfall-in-mumbai.html</t>
+          <t>https://www.tendernama.com/tender-news/third-mumbai-new-growth-center-for-maharashtras-development-what-did-cm-fadnavis-say</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Nanded Rain News: मुखेडमध्ये ढगफुटीसदृश्य पाऊस, CM Devendra Fadanvis यांच्याकडून मदतीच्या सूचना</t>
+          <t>Devendra Fadnavis: चार लाख हेक्टर क्षेत्रावरील पिकांना फटका; मुख्यमंत्र्यांनी घेतला राज्यातील स्थितीचा आढावा</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/videos/video/nanded-rain-news-cloudburst-like-rain-in-mukhed-cm-devendra-fadnavis-issues-help-instructions-1070799.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/heavy-rains-damage-crops-on-4-lakh-hectares-cm-devendra-fadnaivs-reviews-situation-in-maharashtra/articleshow/123379831.cms</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>मुख्यमंत्री फडणवीसांकडून पावसाचा आढावा: मराठवाड्यात 800 गावे बाधित, कोकण-विदर्भात रेड अलर्ट</t>
+          <t>Farmers Loan Waiver: बावनकुळेंनंतर महायुती सरकारमधील 'या' मंत्र्याची कर्जमाफीबाबत मोठी अपडेट; म्हणाले,'CM फडणवीस लवकरच...'</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/cm-fadnavis-reviews-rains-800-villages-affected-in-marathwada-red-alert-in-konkan-vidarbha/</t>
+          <t>https://sarkarnama.esakal.com/amp/story/maharashtra/vidarbha/sanjay-rathod-update-farmer-loan-waiver-devendra-fadnavis-dk88</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Heavy Rainfall : मुख्यमंत्री फडणवीसांचे यंत्रणांना सतर्क राहण्याचे आदेश; राज्यभरातील स्थितीचा घेतला आढावा</t>
+          <t>मुंबईतील पावसाचा मुख्यमंत्र्यांकडून सातत्याने आढावा</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/heavy-rainfall-cm-devendra-fadnavis-orders-agencies-to-be-alert-review-of-the-situation-across-the-state/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/19/the-chief-minister-is-continuously-reviewing-the-rainfall-in-mumbai.html</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Maharashtra Government: शेतकऱ्यांना मिळणार गुड न्यूज: बळीराजासाठी सरकार मोठा निर्णय घेण्याच्या तयारीत</t>
+          <t>नवीन पिढीला इतिहासाशी जोडण्याचे कार्य सुरू; मुख्यमंत्री देवेंद्र फडणवीस यांचे प्रतिपादन</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/sanjay-rathod-big-statement-on-loan-waiver-maharashtra-farmers-get-loan-waiver-minister-give-hint-in-award-ceremony-program-yavatmal-pusad-bbj88</t>
+          <t>https://www.loksatta.com/mumbai/devendra-fadnavis-asserts-that-the-work-of-connecting-the-new-generation-with-history-is-underway-mumbai-print-news-amy-95-5313830/</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Dada Bhuse News: अतिवृष्टीमुळे कोणकोणत्या जिल्ह्यातील शाळांना सुट्टी? जाणून घ्या.. | N18V</t>
+          <t>Mumbai Rain : मुंबईत संध्याकाळी समुद्राला भरती, पुढील 12 तास महत्त्वाचे, पावसाच्या थैमानानंतर</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/dada-bhuse-news-%E0%A4%85%E0%A4%A4-%E0%A4%B5%E0%A5%83%E0%A4%B7%E0%A5%8D%E0%A4%9F-%E0%A4%AE%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%95-%E0%A4%A3%E0%A4%95-%E0%A4%A3%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%9C-%E0%A4%B2%E0%A5%8D%E0%A4%B9%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B2-%E0%A4%B6-%E0%A4%B3-%E0%A4%82%E0%A4%A8-%E0%A4%B8%E0%A5%81%E0%A4%9F%E0%A5%8D%E0%A4%9F-%E0%A4%9C-%E0%A4%A3%E0%A5%82%E0%A4%A8-%E0%A4%98%E0%A5%8D%E0%A4%AF-n18v/vi-AA1KKbyi?ocid=hpmsn</t>
+          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-on-mumbai-maharashtra-rain-today-visit-disaster-management-department-bmc-marathi-news-1377962</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Farmer Loan Waiver | ओला दुष्काळ, नुकसानग्रस्त शेतकऱ्यांना लवकरच CM Fadnavis देणार कर्जमाफीची घोषणा</t>
+          <t>Mumbai Rain News: मुंबईत किती ठिकाणी पाणी साचलं? ट्राफिकची स्थिती काय? मुख्यमंत्र्यांनी दिली A to Z माहिती</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-farmer-loan-waiver-soon-amidst-heavy-rain-and-crop-damage-minister-confirms-cm-devendra-fadnavis-announcement-1378070</t>
+          <t>https://marathi.ndtv.com/cities/mumbai-rain-news-chief-minister-devendra-fadnavis-gave-information-about-the-rainfall-situation-in-mumbai-9107883</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Mumbai Rain : मुख्यमंत्री फडणवीस ॲक्शन मोडमध्ये! राज्यभरात पडत असलेल्या पावसामुळे प्रशासन अलर्ट</t>
+          <t>पुढील १२ तास मुंबईसाठी अत्यंत महत्त्वाचे, मुख्यमंत्री फडणवीस पावसाबाबत काय म्हणाले?</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/mumbai-rain-cm-devendra-fadnavis-in-action-mode-administration-alert-due-to-rains-falling-across-the-state/</t>
+          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-review-mumbai-rain-says-next-12-hours-important-for-mumbai-and-mmr-region-1460967.html</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Maharashtra Politics Live Updates : जगनमोहन रेड्डींच्या पक्षाचा सीपी राधाकृष्णन यांना जाहीर पाठिंबा</t>
+          <t>लाटा पाहण्याच्या मोहापाई लोक अडचणीत येतात....: तुफान पावसामुळे मुख्यमंत्री फडणवीसांनी केले आवाहन</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-18-august-2025-latest-marathi-political-news-eknath-shinde-mumbai-mahayuti-rahul-gandhi-congress-india-aghadi-election-commission-devendra-fadnavis-uddhav-thackeray-india-alliance-mumbai-pune-ajit-pawar-ncp-local-elections-rahul-gandhi-vote-adhikar-yatra-nda-cp-radhakrishnan-vice-presidential-candidat</t>
+          <t>https://www.navarashtra.com/maharashtra/cm-devendra-fadnavis-live-press-on-mumbai-rain-update-red-alert-963319.html</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Heavy Rainfall : रेड ॲलर्ट घोषित केलेल्या ठिकाणी सतर्कता बाळगण्याचे मुख्यमंत्री फडणवीसांचे निर्देश</t>
+          <t>Marathwada Rain : मराठवाड्यात शेतीचे सर्वाधिक नुकसान; नांदेडमध्ये ढगफुटी सदृष्य पाऊस, पाच जण बेपत्ता</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/heavy-rainfall-cm-devendra-fadnavis-instructs-to-remain-vigilant-in-places-where-red-alert-has-been-declared/</t>
+          <t>https://www.mymahanagar.com/maharashtra/cloudburst-rain-in-mukhed-nanded-district-five-people-missing-chief-minister-devendra-fadnavis-gave-information/913157/</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>मुंबई में भारी भारिश ने मचाई तबाही, CM देवेंद्र फडणवीस ने बुलाई बैठक</t>
+          <t>Maharashtra Rain Updates: मुंबईसाठी पुढील 12 तास महत्त्वाचे, राज्यात स्थिती काय? CM फडणवीसांनी सगळं सांगितल...</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/videos/mumbai-news/heavy-rain-wreaks-havoc-in-mumbai-cm-devendra-fadnavis-calls-a-meeting-19874343</t>
+          <t>https://news18marathi.com/maharashtra/maharashtra-rain-update-cm-devendra-fadnavis-hold-meeting-with-district-administration-1460734.html</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>किसानों को जल्द मिल सकता है कर्जमाफी का तोहफा, मंत्री संजय राठोड़ का बड़ा बयान</t>
+          <t>गौरवशाली इतिहासाशी नव्या पीढीला जोडण्याचं काम रघुजीराजे भोसल्यांची ऐतिहासिक</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/maharashtra/farmer-loan-waiver-maharashtra-sanjay-rathod-devendra-fadnavis-54-804134</t>
+          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-mumbai-exhibition-of-nagpur-raghuji-raje-bhosle-historical-sword-marathi-news-1378075</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>मुंबईत पुढील आठ ते दहा तासांसाठी रेड अलर्ट, महत्त्वाचे काम असल्यास घराबाहेर पडण्याचे मुख्यमंत्री फडणवीस यांचे आवाहन</t>
+          <t>Mumbai Heavy Rain : मुंबईसाठी पुढील 10-12 तास धोक्याचे, मुख्यमंत्री फडणवीसांनी मुंबईकरांना केलं सावध</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/in-mumbai-people-have-been-told-to-step-out-only-if-it-is-needed-says-cm-devendra-fadnavis/</t>
+          <t>https://www.mymahanagar.com/maharashtra/heavy-rains-in-mumbai-next-48-hours-are-crucial-chief-minister-devendra-fadnavis-warns-citizens-to-be-alert/913099/</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Pune Patients Receive Over Rs 6.5 Crore in Medical Aid Under Chief Minister Devendra Fadnavis’ Initiative</t>
+          <t>CM Relief Fund: रुग्णांसाठी सरकारचा 'हा' विभाग ठरतोय मदतशीर; अमरावती विभागात तब्बल १०.६१ कोटींची मदत</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-patients-receive-over-rs-6-5-crore-in-medical-aid-under-chief-minister-devendra-fadnavis-initiative/</t>
+          <t>https://www.navarashtra.com/maharashtra/amravati/cm-devendra-fadnavis-cm-relief-fund-help-amravati-1187-patients-for-10-crore-rs-health-marathi-news-963412.html</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Mumbai: CM Devendra Fadnavis meets C.P. Radhakrishnan #Gallery</t>
+          <t>मराठ्यांच्या इतिहासाची साक्षीदार; श्रीमंत राजे रघुजी भोसलेंच्या ऐतिहासिक तलवारीचं लोकार्पण, पाहा खास PHOTO</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/mumbai-cm-devendra-fadnavis-meets-c-p-radhakrishnan-gallery/</t>
+          <t>https://marathi.indiatimes.com/photogallery/news/raghuji-bhosale-sword-inauguration-in-mumbai-by-cm-devendra-fadnavis/photoshow/123367923.cms</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by...</t>
+          <t>मुंबई झोपडपट्टीमुक्त होणार का? जलद पुनर्विकासाचा मुख्यमंत्र्यांनी काय सांगितला प्लॅन?</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis/</t>
+          <t>https://www.tendernama.com/mahatender/mumbai/will-mumbai-become-slum-free-what-is-the-chief-ministers-plan-for-rapid-redevelopment</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Amid heavy rains in Maharashtra, CM Fadnavis directs all agencies to be on alert</t>
+          <t>Mumbai Rains Updates: मुंबईकरांनो पुढील 12 तास अतिशय महत्त्वाचे, CM फडणवीसांनी केले हे आवाहन</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/india/amid-heavy-rains-in-maharashtra-cm-fadnavis-directs-all-agencies-to-be-on-alert</t>
+          <t>https://marathi.ndtv.com/maharashtra/mumbai-rains-update-next-12-hours-are-important-for-mumbai-7-people-died-across-state-in-2-days-cm-fadnavis-appeals-to-citizens-9109288</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by Maharashtra CM Devendra Fadnavis</t>
+          <t>CM Devendra Fadnavis: राज्यातील चार लाख हेक्टर क्षेत्रावरील पिकांना फटका; पिकांचे पंचनामे करण्याचे आदेश</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278516795/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis</t>
+          <t>https://deshdoot.com/crops-affected-on-four-lakh-hectares-of-land-in-the-state-orders-to-conduct-crop-surveys/</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Heavy Rain Forecast for Mumbai: CM Fadnavis Reviews Flood Situation Across Maharashtra, with the Next 12...</t>
+          <t>Maharashtra Rain : राज्यासाठी पुढचे दोन दिवस चिंतेचे, 15-16 जिल्ह्यांना अलर्ट, कुठे होणार अतिवृष्टी?...</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/mumbai/heavy-rain-forecast-for-mumbai-cm-fadnavis-reviews-flood-situation-across-maharashtra-with-the-next-12-hours-critical-a475/</t>
+          <t>https://www.tv9marathi.com/videos/maharashtra-imd-issues-red-alert-for-16-districts-big-information-by-cm-devendra-fadnavis-reviews-heavy-rains-in-1472606.html</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>CM Fadnavis unveils emblem for Ganeshotsav to be celebrated as Rajya Mahotsav</t>
+          <t>महाराष्ट्रातील खासदारांनी राधाकृष्णन यांना समर्थन द्यावे: मुख्यमंत्री देवेंद्र फडणवीसांचे आवाहन; ठाकरे गट अ...</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/india/cm-fadnavis-unveils-emblem-for-ganeshotsav-to-be-celebrated-as-rajya-mahotsav</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/c-p-radhakrishnan-vice-president-candidate-fadnavis-urges-support-135703533.html</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>'Third Mumbai' Initiative Sparks New Wave of Economic Growth in Maharashtra</t>
+          <t>16 जिल्ह्यांना रेड अलर्ट! राज्याच्या ‘या’ भागात अतिवृष्टी, बचाव पथक सज्ज; CM फडणवीसांची...</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/science-environment/3545659-third-mumbai-initiative-sparks-new-wave-of-economic-growth-in-maharashtra</t>
+          <t>https://www.tv9marathi.com/maharashtra/rain-alert-in-16-districts-heavy-rainfall-in-this-part-of-state-cm-fadnavis-give-information-1472499.html</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Fadnavis meets Guv Radhakrishnan, presents him book of Shivaji Maharaj's letters</t>
+          <t>सरदार रघुजी भोसले यांची ऐतिहासिक तलवार मुंबईत दाखल; मुख्यमंत्र्यांच्या हस्ते होणार लोकार्पण</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharajs-letters-9672415</t>
+          <t>https://www.etvbharat.com/mr/!state/sword-of-maratha-commander-raghuji-bhosale-returns-to-mumbai-to-be-unveiled-at-exhibition-by-cm-fadnavis-maharashtra-news-mhs25081803521</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Maharashtra Rains: 5 Missing in Nanded, Over 200 Stranded Across Several Districts; Army, NDRF Deployed</t>
+          <t>CM Devendra Fadnavis: मुख्यमंत्र्यांनी राज्यातील पावसाचा घेतला आढावा; 'इतक्या' जिल्ह्यांना पावसाचा रेड अलर्ट, सतर्क राहण्याचे केले आवाहन</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/maharashtra/maharashtra-rains-5-missing-in-nanded-over-200-stranded-across-several-districts-army-ndrf-deployed-a517/</t>
+          <t>https://deshdoot.com/cm-fadnavis-takes-reiew-situation-ndrf-and-army-deployed-16-districts-on-red-alert/</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Maharashtra government approves major infra projects</t>
+          <t>Mumbai Rain: मुंबईत उद्या शाळांना सुट्टी? पुढचे १२ तास महत्वाचे, मुख्यमंत्री नेमकं काय म्हणाले?</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/india/maharashtra-government-approves-major-infra-projects</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/mumbai-rain-alert-cm-devendra-fadnavis-said-mumbai-schools-declared-holiday-on-tomorrow-bmc-to-decide-pvm91</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Maharashtra CM Devendra Fadnavis Says ‘Third Mumbai’ Being Developed in Raigad District Will Open New</t>
+          <t>Solapur News : शिंदेंच्या सेनेत राज्यातून ‘इन्कमिंग’ पण सोलापुरात गळती, तानाजी सावंतांच्या बंधूंचा भाजप प्रवेश ठरला</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/india/news/maharashtra-cm-devendra-fadnavis-says-third-mumbai-being-developed-in-raigad-district-will-open-new-chapter-of-economic-development-7064927.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/tanaji-sawant-brother-shivajirao-sawant-resign-eknath-shinde-sena-join-bjp-after-meet-fadnavis/913179/</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Rain fury leaves 7 dead in Maharashtra, 200 villagers stranded</t>
+          <t>Mumbai Rain Updates : सात जणांचा मृत्यू ते शेकडो गावे बाधित; राज्यभरात अतिवृष्टीमुळे कुठे काय घडलं?</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/rain-fury-leaves-7-dead-in-maharashtra-200-villagers-stranded-9674070</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-updates-18-august-heavy-rainfall-mumbai-navi-mumbai-kolhapur-raigad-sindhudurag-local-train-latest-updates-traffic-news-rak-94-5312079/</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Mumbai Monsoon Mayhem: Navigating Challenges Amid Torrential Rains</t>
+          <t>मोठी बातमी! शेतकऱ्यांची कर्जमाफी होणार, मुख्यमंत्री घोषणा करणार, बड्या मंत्र्याने दिली माहिती</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/science-environment/3545353-mumbai-monsoon-mayhem-navigating-challenges-amid-torrential-rains</t>
+          <t>https://www.tv9marathi.com/maharashtra/big-update-on-farmer-loan-waiver-cm-fadnavis-will-do-announcement-says-minister-sanjay-rathod-1472819.html</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Mumbai: C.P. Radhakrishnan departs for Delhi #Gallery</t>
+          <t>युवकांसाठी मोठी खुशखबर; ‘या’ ठिकाणी आयटी पार्क उभारणार; मुख्यमंत्र्यांची घोषणा</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/mumbai-c-p-radhakrishnan-departs-for-delhi-gallery/</t>
+          <t>https://www.nagpurtoday.in/great-news-for-youth-it-park-will-be-set-up-at-this-place-chief-ministers-announcement/08181712</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>7 killed as heavy rain batters Maharashtr­a; 800 villages hit</t>
+          <t>Mumbai Rain Update : मुंबईत धो-धो! वाहतुकीचा खोळंबा, लोकलसेवेला फटका; मुंबईकरांची पुरती दैना; पुढील 48 तासही</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>https://www.pressreader.com/india/the-hindu-erode-9WW6/20250819/281994678584394</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-rain-update-heavy-rainfall-started-in-city-resulted-in-disruption-of-life-and-mumbai-local-cm-fadnavis-reviewed/articleshow/123363662.cms</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Fadnavis Gifts Unpublished Shivaji Maharaj Letters to Maharashtra Governor at Mumbai Airport</t>
+          <t>मोदींचा निर्णय, उमेदवार ठरला अन् अडचणीत उद्धवसेना; 18 वर्षांनी पुन्हा तेच, ठाकरेंसमोर पेच?</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>https://panasiabiz.com/111091/cm-devendra-fadnavis-presents-rare-shivaji-maharaj-letters-to-governor-cp-radhakrishnan/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-picks-cp-radhakrishnan-for-vice-president-post-cm-devendra-fadnavis-ask-uddhav-thackeray-for-support/articleshow/123362737.cms</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>7 killed as heavy rain batters Maharashtr­a; 800 villages hit</t>
+          <t>मुंबईतील सर्व शासकीय आणि निमशासकीय कार्यालयांना आज सुट्टी जाहीर!</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>https://www.pressreader.com/india/the-hindu-mangalore-9WWc/20250819/281947433944151</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/19/mumbai-rains-govt-declares-holiday-for-all-government-and-private-offices-amid-heavy-rainfall.html</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>India News | ⚡Devendra Fadnavis Says ‘Third Mumbai’ Will Open a New Chapter of Economic Development</t>
+          <t>मोठी बातमी! नाराजी भोवली, शिवसेना शिंदे गटाला सर्वात मोठा धक्का, बड्या नेत्यानं सोडली एकनाथ शिंदेंची...</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/quickly/india/news/devendra-fadnavis-says-third-mumbai-will-open-a-new-chapter-of-economic-development-7064927.html</t>
+          <t>https://www.tv9marathi.com/maharashtra/big-blow-to-eknath-shinde-big-leader-of-shiv-sena-shinde-group-will-join-bjp-1472541.html</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Business News</t>
+          <t>Heavy Rain: राज्यात अतिवृष्टीच्या पार्श्वभूमीवर मुख्यमंत्री देवेंद्र फडणवीस यांचे सर्व यंत्रणांना सतर्कतेचे</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/business-news-credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis-7064653.html</t>
+          <t>https://deshonnati.com/heavy-raincm-devendra-fadnavis-agencies-alert-heavy-rain-state/</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>'उपराष्ट्रपती'साठी महाराष्ट्राच्या राज्यपालांचे नाव; फडणवीसांचे खासदारांना आवाहन, पवार-ठाकरेंना टोला</t>
+          <t>शेतकरी कर्जमाफीबाबत महायुतीमधील मंत्र्याने दिली महत्त्वाची माहिती; “देवेंद्र फडणवीस लवकरच….”</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-urges-mps-to-support-radhakrishnan-targets-uddhav-thackeray-and-sharad-pawar-035137.html?ref_source=OI-MR&amp;ref_medium=Home-Page&amp;ref_campaign=News-Cards</t>
+          <t>https://www.dainikprabhat.com/mahayuti-minister-gives-important-information-regarding-farmer-loan-waiver-devendra-fadnavis-soon/</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>बाढ़ संकट पर अबू आजमी का CM फडणवीस को पत्र, प्रभावितों तक तुरंत राहत पहुंचाने की मांग</t>
+          <t>Devendra Fadnavis : महाराष्ट्रातील माणसाला सर्वांनी समर्थन द्यावे; मुख्यमंत्री फडणवीस यांचे मविआच्या खासदारांना आवाहन</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/latest-news/abu-azmi-wrote-a-letter-to-cm-devendra-fadnavis-asking-him-to-send-relief-supplies-to-flood-affected-region-1322005.html</t>
+          <t>https://www.dainikprabhat.com/devendra-fadnavis-everyone-should-support-the-people-of-maharashtra-chief-minister-fadnavis-appeals-to-m-v-a-mps/</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>MONSOON UPDATE: १५ ते १६ जिल्ह्यांत रेड आणि ऑरेंज अलर्ट; CM DEVENDRA FADNAVIS म्हणाले…</t>
+          <t>'उपराष्ट्रपती'साठी महाराष्ट्राच्या राज्यपालांचे नाव; फडणवीसांचे खासदारांना आवाहन, पवार-ठाकरेंना टोला</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/monsoon-update-red-and-orange-alert-in-15-to-16-districts-cm-devendra-fadnavis-said/129346/</t>
+          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-urges-mps-to-support-radhakrishnan-targets-uddhav-thackeray-and-sharad-pawar-035137.html?ref_source=OI-MR&amp;ref_medium=Home-Page&amp;ref_campaign=News-Cards</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>नांदेड़ में मूसलधार बारिश से हाहाकार, CM फडणवीस की निगरानी में राहत कार्य तेज</t>
+          <t>प्रशासन सतर्क : नागरिकांनी घराबाहेर पडू नये: मुख्यमंत्री फडणवीस !</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/heavy-rains-cause-havoc-in-nanded-rescue-operation-intensified-under-the-supervision-of-cm-fadnavis-1321752.html</t>
+          <t>https://vishwanewsmarathi.com/administrator-citizens-should-not-stay-home-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>लंदन से आई मराठा साम्राज्य की शान! रघुजी ?...</t>
+          <t>मुख्यमंत्री लवकरच शेतकरी कर्जमाफीची घोषणा करणार ; शिंदेंच्या मंत्र्यांचा दावा !</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>https://bharatexpress.com/india/raghuji-bhosale-historic-sword-returned-from-london-grand-welcome-in-mumbai-553050</t>
+          <t>https://vishwanewsmarathi.com/chief-minister-will-soon-announce-farmer-loan-waiver-shindes-ministers-claim/</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Mumbai : महाराष्ट्र में मूसलाधार बारिश से हाहाकार, सात लोगों की मौत</t>
+          <t>लवकरच कर्जमाफीची घोषणा होणार? महायुती सरकारमधील मंत्र्यांनी दिले संकेत</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>https://indiagroundreport.com/mumbai-torrential-rains-in-maharashtra-cause-havoc-seven-people-died/</t>
+          <t>https://marathi.oneindia.com/maharashtra/maharashtra-cm-fadnavis-loan-waiver-announcement-035127.html</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>भुजबळांची नाराजी दूर करण्याची जबाबदारी पुन्हा फडणवीसांवर? अजितदादांनी केले हात वर</t>
+          <t>मुख्यमंत्री फडणवीस लवकरच शेतकरी कर्जमाफीची घोषणा करण्याची शक्यता</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/politics/guardian-minister-decision-nashik-chhagan-bhujbal-ajit-pawar-devendra-fadnavis/</t>
+          <t>https://www.dainikprabhat.com/cm-fadnavis-likely-to-announce-farm-loan-waiver-soon/</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>महाराष्ट्र किसानों को मिलेगी बड़ी राहत, CM फडणवीस जल्द करेंगे कर्जमाफी की घोषणा</t>
+          <t>महाराष्ट्रातील शेतकऱ्यांना मोठा दिलासा, मुख्यमंत्री फडणवीस लवकरच कर्जमाफीची घोषणा करणार</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/guardian-minister-sanjay-rathore-claims-cm-fadnavis-may-announce-a-loan-waiver-for-farmers-1322081.html</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/big-relief-for-farmers-in-maharashtra-chief-minister-fadnavis-will-soon-announce-loan-waiver-125081900014_1.html</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>CM फडणवीस ने खेला 'मराठी अस्मिता' का दांव, उपराष्ट्रपति चुनाव में उद्धव-पवार पर बना दबाव</t>
+          <t>MONSOON UPDATE: १५ ते १६ जिल्ह्यांत रेड आणि ऑरेंज अलर्ट; CM DEVENDRA FADNAVIS म्हणाले…</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/political-battle-over-nda-candidate-radhakrishnan-cm-fadnavis-seeks-support-from-uddhav-thackeray-and-sharad-pawar-1321873.html/amp</t>
+          <t>https://www.timemaharashtra.com/maharashtra/monsoon-update-red-and-orange-alert-in-15-to-16-districts-cm-devendra-fadnavis-said/129346/</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>महाराष्ट्र की 'अस्मिता' की बात करने वाले उपराष्ट्रपति पद के लिए राधाकृष्णन का समर्थन करें : फडणवीस</t>
+          <t>मुख्यमंत्री फडणवीसांकडून पावसाचा आढावा: मराठवाड्यात 800 गावे बाधित, कोकण-विदर्भात रेड अलर्ट</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/maharashtra/devendra-fadnavis-urges-people-to-support-radhakrishnan-for-vice-presidents-post-3213157.html</t>
+          <t>https://www.dainikprabhat.com/cm-fadnavis-reviews-rains-800-villages-affected-in-marathwada-red-alert-in-konkan-vidarbha/</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में भारी बारिश से कई जिलों में रेड और ऑरेंज अलर्ट</t>
+          <t>10 रुपयांत ‘शिवभोजन थाळी’ योजना थांबणार? शिवभोजन केंद्र चालकांची कोट्यवधींची बिलं थकली</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>https://vikalptimes.com/red-and-orange-alert-issued-in-many-districts-of-maharashtra-due-to-heavy-rains/</t>
+          <t>https://mpbreakingnews.in/marathi/maharashtra/will-the-shiv-bhojan-thali-scheme-for-10-rupees-stop-shiv-bhojan-center-operators-are-facing-bills-worth-crores-02-692694</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Maharashtra News Live: एक क्लिक में पढ़े महाराष्ट्र की दिन भर की बड़ी खब़रें...</t>
+          <t>एकनाथ शिंदेंना सोलापुरात मोठा धक्का : नेत्यांने सोडली साथ !</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/latest-live-updates-maharashtra-politics-crime-nagpur-news-mumbai-pune-18-august-1321138.html</t>
+          <t>https://vishwanewsmarathi.com/big-setback-for-eknath-shinde-in-solapur-leaders-leave-support/</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Mumbai Maharashtra Rains: महाराष्ट्र में भारी बारिश पर सीएम देवेंद्र फडणवीस का सख्त निर्देश, सभी विभाग अलर्ट पर</t>
+          <t>Road Construction: परभणीतील गंगाखेड तालुक्यात ग्रामस्थांचे आगळेवेगळे आंदोलन! - देशोन्नती</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/mumbai-maharashtra-rains-cm-and-managment-on-alert-hindi/</t>
+          <t>https://deshonnati.com/road-constructionvillagers-stage-protest-gangakhed-parbhani/</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>कैसी होगी तीसरी मुंबई, कितनी बड़ी और कहां बन रही, सुविधाओं से लेकर प्लानिंग तक, CM फडणवीस ने सब बताया</t>
+          <t>Mumbai Rains : गुडघाभर पाणी, समोर रस्ताही दिसेना, लोकल रखडल्या आठवड्याच्या सुरुवातीला पावसानं मुंबईकरांची दाणादाण, पहा PHOTO</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>https://ndtv.in/maharashtra-news/maharashtra-cmdevendra-fadnavis-told-third-mumbai-mmr-will-develop-with-this-know-how-it-will-be-9112502</t>
+          <t>https://marathi.asianetnews.com/mumbai/mumbai-heavy-rain-waterlogging-local-delays-school-shutdown/photoshow-at2tgam</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>फडणवीस ने कहा, ‘तीसरी मुंबई’ से एमएमआर का होगा विकास</t>
+          <t>Mumbai News: गोल्डमन सॅक्सचे मुंबई नवे कार्यालय तिसऱ्या मुंबईचा नवा अध्याय - देवेंद्र फडणवीस</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/economy/fadnavis-said-third-mumbai-will-lead-to-development-of-mmr/856867/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/goldman-sachs-new-mumbai-office-is-a-new-chapter-for-third-mumbai-devendra-fadnavis-89597</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>दिल्ली पहुंचे देवेंद्र फडणवीस, अमित शाह से मिले, जानें क्यों थी यह मुलाकात खास</t>
+          <t>“मुंबईत पुढच्या १२ तासांत तुफान पाऊस, रेड अलर्ट आणि…”; मुख्यमंत्री देवेंद्र फडणवीस यांनी काय माहिती दिली?</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B6-%E0%A4%B9-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A5%87-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%82-%E0%A4%A5-%E0%A4%AF%E0%A4%B9-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4-%E0%A4%96-%E0%A4%B8/ar-AA1Jjy9z</t>
+          <t>https://www.loksatta.com/maharashtra/mumbai-rain-alert-cm-devendra-fadnavis-said-mumbai-have-red-alert-school-holiday-declared-know-details-scj-81-5312934/</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Mumbai Rains News: भारी बारिश के चलते कल मुंबई के स्कूल-कॉलेजों में छुट्टी, नांदेड़ में 7 लोगों की मौत, CM फडणवीस ने की आपात बैठक</t>
+          <t>Pune News : मुख्यमंत्री फडणवीसांमुळे पुणेकरांना रोज मनस्ताप? काँग्रेसचा गंभीर आरोप</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/heavy-rains-in-mumbai-schools-colleges-closed-7-deaths-in-maharashtra-5-missing-nanded-cm-fadnavis-emergency-meeting/articleshow/123366462.cms</t>
+          <t>https://sarkarnama.esakal.com/pune/devendra-fadnavis-pune-flyover-inauguration-delay-dk88-sm89</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में भारी बारिश का कहर, 16 जिलों में रेड अलर्ट, बचाव दल तैनात</t>
+          <t>महाराष्ट्रात महाभयानक पाऊस! मुख्यमंत्री देवेंद्र फडणवीस यांनी तातडीने साधला शेजारील राज्यांशी संपर्क? कारण अतिशय चिंताजनक</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-heavy-rainfall-flood-alert-red-and-orange-alerts-issued-relief-operations-mumbai-rain-ann-2997660</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/maharashtra-mumbai-rain-alert-update-chief-minister-devendra-fadnavis-immediately-contacted-the-neighboring-states/933328</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Maharashtra: फडणवीस बोले- औरंगजेब भारत का हीरो नहीं, सुप्रीम कोर्ट के SC आरक्षण पर फैसले को लागू करेगी सरकार</t>
+          <t>Devendra Fadanvis on Rain Update : मुंबईला रेड अलर्ट ! मुख्यमंत्री देवेंद्र फडणवीस यांनी पावसाबद्दल दिली महत्त्वाची अपडेट</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B8%E0%A5%81%E0%A4%AA%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%95%E0%A5%87-sc-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%AA%E0%A4%B0-%E0%A4%AB%E0%A5%88%E0%A4%B8%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B2-%E0%A4%97%E0%A5%82-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%97-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0/ar-AA1IRMGx</t>
+          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/maharashtra-hevey-rain-update-cm-devendra-fadanvis-gives-important-information-know-about-more-/40070</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Raghuji Bhosale: आज मुंबई आएगी रघुजी भोसले की की ऐतिहासिक तलवार, सीएम फडणवीस करेंगे स्वागत</t>
+          <t>पुण्यात नवीन महापालिकांवरून देवेंद्र फडणवीस आणि अजित पवार यांच्यात मतभेद का?</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/india/raghuji-bhosale-historic-sword-will-arrive-in-mumbai-today-cm-fadnavis-will-welcome-it/2886138</t>
+          <t>https://www.loksatta.com/politics/devendra-fadnavis-ajit-pawar-dispute-over-new-municipal-corporations-in-pune-district-print-politics-news-css-98-5314697/</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Mumbai Rain: 24 घंटे की बारिश से मुंबई की सांस फूली, CM देवेंद्र फडणवीस ने पड़ोसी राज्यों से किया संपर्क</t>
+          <t>Cji Bhushan Gavai : सरन्यायाधीशांनी केले शिवेंद्रसिंहराजेंचे जाहीरपणे कौतुक; म्हणाले, ‘गिनिज बुकमध्ये नोंद करण्यासारखे काम...’</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/india/mumbai-rains-today-imd-red-alert-warning-waterlogging-traffic-update/2886161</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chief-justice-bhushan-gavai-praised-shivendrasinghraje-bhosale-vd83</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>मुंबई में 6-8 घंटे में 177 मिलीमीटर बारिश हुई: फडणवीस</t>
+          <t>Crop damage : 4 लाख हेक्टर क्षेत्रावरील पिकांची हानी</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/mumbai-received-177-mm-of-rain-in-6-8-hours-fadnavis/856688/</t>
+          <t>https://pudhari.news/maharashtra/mumbai/crop-damage-4-lakh-hectares-ab96</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>अबू आजमी ने सीएम देवेंद्र फडणवीस को लिखा पत्र, बाढ़ प्रभावित इलाकों में राहत सामग्री पहुंचाने की मांग की</t>
+          <t>Devendra Fadnavis| मुख्यमंत्री देवेंद्र फडणवीस १९ रोजी पैठण तालुक्यात</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>https://www.newsnationtv.com/abu-azmi-ne-cm-devendra-fadnavis-ko-likha-patra-badh-prabhavit-ilakon-mein-rahat-pahunchane-ki-mang-ki--20250818191027/</t>
+          <t>https://pudhari.news/maharashtra/marathwada/chhatrapati-sambhajinagar/devendra-fadnavis-visit-paithan-taluka-19-august-ng81</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>नांदेड़ में भारी बारिश के कारण पांच लोग लापता, कई व्यक्ति फंसे : मुख्यमंत्री फडणवीस</t>
+          <t>तिसरी मुंबई आर्थिक विकासाचा नवा अध्याय – मुख्यमंत्री देवेंद्र फडणवीस</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/five-people-missing-many-people-stranded-due-to-heavy-rains-in-nanded-chief-minister-fadnavis/856679/</t>
+          <t>https://mahasamvad.in/176127/</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Maharashtra: 'पुणे के विकास में सबसे बड़ी बाधा बन चुकी है उद्योगों पर दादागीरी', सीएम फडणवीस ने दी चेतावनी</t>
+          <t>Maharashtra Politics : एकनाथ शिंदेंची कोण करतंय कोंडी? दिल्ली दौरे वाढण्यामागचं काय कारण?</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AA%E0%A5%81%E0%A4%A3%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%B5-%E0%A4%95-%E0%A4%B8-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8%E0%A4%AC%E0%A4%B8%E0%A5%87-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC-%E0%A4%A7-%E0%A4%AC%E0%A4%A8-%E0%A4%9A%E0%A5%81%E0%A4%95-%E0%A4%B9%E0%A5%88-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%97-%E0%A4%82-%E0%A4%AA%E0%A4%B0-%E0%A4%A6-%E0%A4%A6-%E0%A4%97-%E0%A4%B0-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%A6-%E0%A4%9A%E0%A5%87%E0%A4%A4-%E0%A4%B5%E0%A4%A8/ar-AA1JMfla?ocid=finance-verthp-feeds&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.loksatta.com/politics/maharashtra-politics-shiv-sena-eknath-shinde-bjp-devendra-fadnavis-conflict-before-bmc-election-sdp-92-5314661/lite/</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Mumbai News: महाराष्ट्र में मूसलाधार बारिश से हाहाकार, मुख्यमंत्री की हाईलेवल बैठक, विशेष सत्र बुलाने की मांग | Heavy rains cause havoc in Maharashtra, high level meeting of Chief Minister, demand for calling special s</t>
+          <t>Mumbai Rain: मुंबईत उद्या शाळांना सुट्टी? पुढचे १२ तास महत्वाचे, मुख्यमंत्री नेमकं काय म्हणाले?</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/city/mumbai/mumbai-news-heavy-rains-cause-havoc-in-maharashtra-high-level-meeting-of-chief-minister-demand-for-calling-special-session-1174171</t>
+          <t>https://saamtv.esakal.com/amp/story/mumbai-pune/mumbai-rain-alert-cm-devendra-fadnavis-said-mumbai-schools-declared-holiday-on-tomorrow-bmc-to-decide-pvm91</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>उपराष्ट्रपति चुनाव में भाजपा का दांव, सीपी राधाकृष्णन उम्मीदवार, महाराष्ट्र की राजनीति में बढ़ी हलचल</t>
+          <t>Maharashtra Heavy Rainfall | राज्यभरात अतिवृष्टीचा कहर; १५ जिल्ह्यांत रेड आणि ऑरेंज अलर्ट, नागरिकांनी घराबाहेर पडू नये: मुख्यमंत्री फडणवीस</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/maharashtra/vice-president-election-bjp-candidate-cp-radhakrishnan-devendra-fadnavis-54-803924</t>
+          <t>https://pudhari.news/maharashtra/mumbai/maharashtra-heavy-rainfall-red-orange-alert-15-districts-cm-fadnavis-advisory-as80</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>फडणवीस की पत्नी के खिलाफ अपमानजनक पोस्ट : दो लोगों की अग्रिम जमानत अर्जी खारिज</t>
+          <t>पूरस्थितीचा सामना करण्यासाठी सरकारकडून सर्वतोपरी प्रयत्न, अतिवृष्टीचा धोका लक्षात घेऊन लोकांनी खबरदारी घ्यावी, मुख्यमंत्र्यांचं आवाहन</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%96-%E0%A4%B2-%E0%A4%AB-%E0%A4%85%E0%A4%AA%E0%A4%AE-%E0%A4%A8%E0%A4%9C%E0%A4%A8%E0%A4%95-%E0%A4%AA-%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%A6-%E0%A4%B2-%E0%A4%97-%E0%A4%82-%E0%A4%95-%E0%A4%85%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%9C%E0%A4%AE-%E0%A4%A8%E0%A4%A4-%E0%A4%85%E0%A4%B0%E0%A5%8D%E0%A4%9C-%E0%A4%96-%E0%A4%B0-%E0%A4%9C/ar-AA1Je80j?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.etvbharat.com/mr/!state/maharashtra-government-is-making-every-effort-to-deal-with-the-flood-situation-the-chief-minister-appeals-to-people-to-be-careful-considering-the-risk-of-heavy-rains-maharashtra-news-mhs25081804221</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में बन रही है तीसरी मुंबई, इस जिले का होगा आर्थिक विकास, जानें पूरी जानकारी | News Track in...</t>
+          <t>Nanded Breaking : मोठी बातमी! नांदेडमध्ये अनेक गाव पाण्याखाली, 15 जण अडकले तर 40 ते 50 म्हशीचा पाण्यात बुडून मृत्यू</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>https://newstrack.com/india/third-mumbai-being-built-maharashtra-district-have-economic-development-know-full-details-534715</t>
+          <t>https://www.lokshahi.com/news/rains-in-nandeds-mukhed-taluka-have-caused-flash-floods-in-many-villages-and-information-has-emerged-that-15-people-from-the-village-are-stranded</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>महाराष्ट्र : भारी बारिश के बाद नांदेड़ में राहत कार्य तेज, प्रशासन के संपर्क में सीएम फडणवीस</t>
+          <t>Maharashtra Politics Live Updates : जगनमोहन रेड्डींच्या पक्षाचा सीपी राधाकृष्णन यांना जाहीर पाठिंबा</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>https://www.newsnationtv.com/maharashtra-bhari-barish-ke-baad-nanded-mein-rahat-bachav-karya-tez-jiladhikariyon-ke-sampark-mein-cm-fadnavis--20250818144516/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-18-august-2025-latest-marathi-political-news-eknath-shinde-mumbai-mahayuti-rahul-gandhi-congress-india-aghadi-election-commission-devendra-fadnavis-uddhav-thackeray-india-alliance-mumbai-pune-ajit-pawar-ncp-local-elections-rahul-gandhi-vote-adhikar-yatra-nda-cp-radhakrishnan-vice-presidential-candidat</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>मुंबई में भारी बारिश के बीच सुचारू रूप से चल रही मेट्रो, सीएम फडणवीस ने की तारीफ</t>
+          <t>Shivaji Sawant : तानाजी सावंतांचे बंधू शिवाजी सावंतांचा भाजप प्रवेश निश्चित; मुख्यमंत्र्यांच्या भेटीनंतर जाहीर केला निर्णय</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/maharashtra/mumbai-news/news-metro-running-smoothly-amid-heavy-rains-in-mumbai-cm-fadnavis-praised-news-hindi-1-745323-KKN.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/shivaji-sawants-entry-into-bjp-confirmed-decision-announced-after-meeting-with-chief-minister-vd83</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>फडणवीस छात्रों को हिंदी पढ़ाने के बारे में सोच रहे, लेकिन प्रवासी मजदूरों को मराठी नहीं: राज ठाकरे</t>
+          <t>महायुतीच्या 'या' मंत्र्यावर 5 हजार कोटींच्या भ्रष्टाचाराचा आरोप; रोहित पवारांची मुख्यमंत्री फडणवीसांकडे राजीनाम्याची मागणी</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%9B-%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%82-%E0%A4%95-%E0%A4%B9-%E0%A4%82%E0%A4%A6-%E0%A4%AA%E0%A4%A2%E0%A4%BC-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%B0%E0%A5%87-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8-%E0%A4%9A-%E0%A4%B0%E0%A4%B9%E0%A5%87-%E0%A4%B2%E0%A5%87%E0%A4%95-%E0%A4%A8-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%B8-%E0%A4%AE%E0%A4%9C%E0%A4%A6%E0%A5%82%E0%A4%B0-%E0%A4%82-%E0%A4%95-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B0-%E0%A4%9C-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87/ar-AA1JMr77?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://puneprimenews.com/mumbai/this-minister-of-mahayuti-accused-of-corruption-worth-rs-5000-crores-rohit-pawar-demands-resignation-from-chief-minister-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>CM फडणवीस ने खेला 'मराठी अस्मिता' का दांव, उपराष्ट्रपति चुनाव में उद्धव-पवार पर बना दबाव</t>
+          <t>Mukhed cloudburst: मुखेडमध्ये ढगफुटी! 800 गावांना फटका, 226 लोकांची सुटका, 4 गावातले लोक फसले, सैन्याला पाचारण</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/political-battle-over-nda-candidate-radhakrishnan-cm-fadnavis-seeks-support-from-uddhav-thackeray-and-sharad-pawar-1321873.html</t>
+          <t>https://marathi.ndtv.com/maharashtra/rain-big-news-mukhed-cloudburst-nanded-rain-news-calling-out-the-army-maharashtra-rain-alert-9107388</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>कोल्हापुर में CJI गवई ने की सीएम और डिप्टी सीएम के सामने उनकी तारीफ, बोले- "जो लोग शिकायत कर रहे वे देवेंद्र फडणवीस और एकनाथ शिंदे के बारे में नहीं जानते…"</t>
+          <t>Maharashtra Rain Update : शाळांना सुट्टी आहे की नाही? नेमका निर्णय काय? फडणवीसांनीच संभ्रम संपवला;...</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>https://lalluram.com/in-kolhapur-cji-gavai-praised-him-in-front-of-cm-and-deputy-cm-said-those-who-are-complaining-do-not-know-about-devendra-fadnavis-and-eknath-shinde/</t>
+          <t>https://www.tv9marathi.com/photo-gallery/maharashtra-rain-update-mumbai-rain-school-and-college-holiday-decision-will-be-taken-after-weather-forecast-1472649.html</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>CM फडणवीस लगा रहे जोर, अधिकारी कर रहे मनामानी, FIA ने जतायी नाराजगी</t>
+          <t>राजधानीत पावसाचा कहर! मुंबई विद्यापीठाचा परीक्षांबाबत तडकाफडकी मोठा निर्णय!</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/federation-of-industries-association-is-angry-due-to-ignorance-of-msme-sector-in-vidarbha-1322498.html</t>
+          <t>https://www.tv9marathi.com/maharashtra/mumbai-university-postponed-its-all-exam-to-be-held-on-19-august-due-to-heavy-rain-marathi-news-1472932.html/amp</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>CM फडणवीस ने एनडीए के उपराष्ट्रपति पद के नामांकन पर सीपी राधाकृष्णन को शॉल भेंट की</t>
+          <t>Sambhajinagar News : आता शहरवासीयांना मिळणार अतिरिक्त २६ एमएलडी पाणी</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>https://www.jantaserishta.com/local/maharashtra/cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vice-president-nomination-4218433</t>
+          <t>https://pudhari.news/maharashtra/marathwada/chhatrapati-sambhajinagar/now-city-residents-will-get-additional-26-mld-of-water-np88</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>महाराष्ट्र की 'अस्मिता' की बात करने वाले उपराष्ट्रपति पद के लिए राधाकृष्णन का समर्थन करें : फडणवीस</t>
+          <t>अन्वयार्थ : राजकीयीकरणाचा उत्सवी अधर्म</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>https://navabharat.news/support-radhakrishnan-for-the-post-of-vice-president-who-talks-about-maharashtras-identity-fadnavis/</t>
+          <t>https://www.loksatta.com/sampadkiya/columns/dahi-handi-2025-political-grip-on-dahi-handi-festival-10-thar-human-pyramid-25-lakh-cash-prize-zws-70-5314039/</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>नांदेड़ में भारी बारिश के कारण पांच लोग लापता, कई व्यक्ति फंसे : मुख्यमंत्री फडणवीस</t>
+          <t>Mumbai Rains News: मुंबईसह महाराष्ट्रात 3 जिल्ह्यात शाळा-कॉलेज बंद, पावसाने सामान्यांचे झाले हाल; तलाव भरले</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/maharashtra/five-people-missing-several-stranded-due-to-heavy-rains-in-nanded-cm-fadnavis-3212983.html</t>
+          <t>https://www.navarashtra.com/maharashtra/mumbai-rains-news-updates-school-college-closed-due-to-heavy-rains-thane-palghar-has-problem-963739.html</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Mumbai: राज्यपाल की उपराष्ट्रपति पद की उम्मीदवारी पर मुख्यमंत्री ने जताया हर्ष</t>
+          <t>मराठ्यांच्या इतिहासाचं सोनेरी पान उलगडलं, मुख्यमंत्र्यांच्या हस्ते सरदार रघुजी राजे भोसले यांच्या ऐतिहासिक तलवारीचं लोकार्पण</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/mumbai-chief-minister-expressed-happiness-over-the-candidature-of-the-governor-for-the-post-of-vice-president-mumbai--4218462</t>
+          <t>https://www.etvbharat.com/mr/!state/unveiling-the-historic-sword-of-sardar-raghuji-raje-bhosale-in-mumbai-presence-of-chief-minister-devendra-fadnavis-know-history-of-raghuji-raje-sword-maharashtra-news-mhs25081900619</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Mumbai Rains: मुंबई में भारी बारिश से 12 लोगों की मौत, जगह-जगह कमर तक भरा पानी, स्कूल-कॉलेज बंद, फ्लाइट्स पर भी असर</t>
+          <t>लातूर जिल्ह्यात मुसळधार पाऊस; लेंडी नदीला पूर आल्यानं तेलंगाणातील चार प्रवासी गेले वाहून; मुख्यमंत्र्यांनी घेतला आढावा</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>https://lalluram.com/mumbai-rains-7-people-died-due-to-rain-water-flooded-on-roads-schools-and-colleges-closed-flights-also-affected/</t>
+          <t>https://www.etvbharat.com/mr/!state/heavy-rains-in-latur-district-cause-flooding-in-many-rivers-cm-devendra-fadnavis-took-a-review-lendi-river-flood-maharashtra-news-mhs25081802447</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis : महाराष्ट्रातील माणसाला सर्वांनी समर्थन द्यावे; मुख्यमंत्री फडणवीस यांचे मविआच्या खासदारांना आवाहन</t>
+          <t>Jalgaon mob lynching Case: जामनेर मॉब लिंचिंग: युवकाच्या हत्येत मंत्री गिरीश महाजनांच्या ड्रायव्हरचा मुलगा मास्टर माईंड?</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/devendra-fadnavis-everyone-should-support-the-people-of-maharashtra-chief-minister-fadnavis-appeals-to-m-v-a-mps/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/maharashtra-news-jalgaon-jamner-mob-lynching-girish-mahajan-driver-son-mastermind-youth-killed-mm76-sd67</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Farmers Loan Waiver: बावनकुळेंनंतर महायुती सरकारमधील 'या' मंत्र्याची कर्जमाफीबाबत मोठी अपडेट; म्हणाले,'CM फडणवीस लवकरच...'</t>
+          <t>नांदेडमध्ये मुसळधार पावसाने हाहाकार,मुख्यमंत्री फडणवीस यांच्या देखरेखीखाली मदतकार्य तीव्र</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/amp/story/maharashtra/vidarbha/sanjay-rathod-update-farmer-loan-waiver-devendra-fadnavis-dk88</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/heavy-rains-wreak-havoc-in-nanded-relief-work-intensified-under-the-supervision-of-chief-minister-fadnavis-125081800046_1.html</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>बांदा से लेकर चांदा तक सर्वत्र बारिश से हाहाकार</t>
+          <t>महाराष्ट्रात सर्वदूर पावसामुळे हाहाकार; मोठ्या प्रमाणात जीवित आणि वित्तहानी, बळीराज अडचणीत!</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/amravati/from-banda-to-chanda-there-is-chaos-everywhere-due-to-rain/</t>
+          <t>https://mpbreakingnews.in/marathi/maharashtra/rains-wreak-havoc-across-maharashtra-massive-loss-of-life-and-property-farmers-in-trouble-06-692619</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Mumbai Rain News: मुसळधार पावसामुळे मुंबईत वाहतूक कोंडी, लोकांचे हाल</t>
+          <t>डॉ. बाबासाहेब आंबेडकरांच्या स्मारकाची मागणी</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/mumbai-rain-news-%E0%A4%AE%E0%A5%81%E0%A4%B8%E0%A4%B3%E0%A4%A7-%E0%A4%B0-%E0%A4%AA-%E0%A4%B5%E0%A4%B8-%E0%A4%AE%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%A4-%E0%A4%B5-%E0%A4%B9%E0%A4%A4%E0%A5%82%E0%A4%95-%E0%A4%95-%E0%A4%82%E0%A4%A1-%E0%A4%B2-%E0%A4%95-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%B9-%E0%A4%B2/vi-AA1KI8VB?ocid=hpmsn</t>
+          <t>https://aaplaawajnews.com/2025/34067/</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Heavy rains lash Nanded: Five missing, scores stranded, says CM Fadnavis; Army unit deployed</t>
+          <t>Fadnavis meets Guv Radhakrishnan, presents him book of Shivaji Maharaj's letters</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/heavy-rains-lash-nanded-five-missing-scores-stranded-says-cm-fadnavis-army-unit-deployed-9672306</t>
+          <t>https://www.ptinews.com/story/national/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharaj-s-letters/2832582</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Mumbai got 177mm rain in 6-8 hour period, says CM; more to come amid high tides</t>
+          <t>Third Mumbai in Raigad to become Maharashtra’s new economic powerhouse: CM Fadnavis</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/mumbai-got-177mm-rain-in-6-8-hour-period-says-cm-more-to-come-amid-high-tides-9672488</t>
+          <t>https://daijiworld.com/news/newsDisplay?newsID=1289652</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Maharashtra Governor Radhakrishnan: A Voter from Mumbai and NDA's Vice-Presidential Choice</t>
+          <t>Heavy rainfall causes 7 deaths, crop loss in Maharashtra as alerts continue</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3545404-maharashtra-governor-radhakrishnan-a-voter-from-mumbai-and-ndas-vice-presidential-choice</t>
+          <t>https://www.msn.com/en-in/news/India/heavy-rainfall-causes-7-deaths-crop-loss-in-maharashtra-as-alerts-continue/ar-AA1KK6Zt</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>फडणवीस ने राज्यपाल राधाकृष्णन से मुलाकात की, उन्हें शिवाजी महाराज के पत्रों की पुस्तक भेंट की</t>
+          <t>Nanded rains latest UPDATES: Water from Karnataka reach district; Indian Army, SDRF deployed for rescue missions as villagers trapped</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/fadnavis-met-governor-radhakrishnan-presented-him-a-book-of-letters-of-shivaji-maharaj/856681/</t>
+          <t>https://www.theweek.in/news/india/2025/08/18/mumbai-rain-news-nanded-rains-latest-updates-water-from-karnataka-reach-district-indian-army-sdrf-deployed-for-rescue-missions-and-villagers-trapped.html</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>महाराष्ट्र की ‘अस्मिता’ की बात करने वाले उपराष्ट्रपति पद के लिए राधाकृष्णन का समर्थन करें : फडणवीस</t>
+          <t>Sword of Raghuji Bhonsle arrives in Mumbai and will be on display till Aug 25</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/support-radhakrishnan-for-the-post-of-vice-president-who-talks-about-maharashtras-identity-fadnavis/856729/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/sword-of-raghuji-bhonsle-arrives-in-mumbai-and-will-be-on-display-till-aug-25/articleshow/123371745.cms</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>पुढील १२ तास मुंबईसाठी अत्यंत महत्त्वाचे, मुख्यमंत्री फडणवीस पावसाबाबत काय म्हणाले?</t>
+          <t>CREDAI-MCHI appoints Sukhraj Nahar as 18th President</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-review-mumbai-rain-says-next-12-hours-important-for-mumbai-and-mmr-region-1460967.html</t>
+          <t>https://housing.com/news/credai-mchi-appoints-sukhraj-nahar-as-president/</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>16 जिल्ह्यांना रेड अलर्ट! राज्याच्या ‘या’ भागात अतिवृष्टी, बचाव पथक सज्ज; CM फडणवीसांची...</t>
+          <t>"Observe precaution": Maharashtra CM warns about severe weather conditions in state</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/rain-alert-in-16-districts-heavy-rainfall-in-this-part-of-state-cm-fadnavis-give-information-1472499.html</t>
+          <t>https://thenewsmill.com/2025/08/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state/</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Maharashtra Politics : एकनाथ शिंदेंची कोण करतंय कोंडी? दिल्ली दौरे वाढण्यामागचं काय कारण?</t>
+          <t>हवामानाचा अंदाज: आजही पावसाचा कहर? मुंबई, पुण्यासह 7 जिल्ह्यांना रेड अलर्ट; गडचिरोलीसह 4 जिल्ह्यांना यलो अलर्ट</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/maharashtra-politics-shiv-sena-eknath-shinde-bjp-devendra-fadnavis-conflict-before-bmc-election-sdp-92-5314661/lite/</t>
+          <t>https://thefocusindia.com/national-news/maharashtra-weather-red-alert-mumbai-pune-7-districts-281414/amp/</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Cji Bhushan Gavai : सरन्यायाधीशांनी केले शिवेंद्रसिंहराजेंचे जाहीरपणे कौतुक; म्हणाले, ‘गिनिज बुकमध्ये नोंद करण्यासारखे काम...’</t>
+          <t>Ashish Shelar : मुंबईत मुसळधार.. परिस्थितीचा आढावा घेतल्यानंतर शेलारांकडून मुंबईकरांना एकच आवाहन; आज,...</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chief-justice-bhushan-gavai-praised-shivendrasinghraje-bhosale-vd83</t>
+          <t>https://www.tv9marathi.com/videos/ashish-shelar-appeals-to-mumbaikars-after-review-of-rains-at-bmc-stay-at-house-during-mumbai-heavy-rains-1472440.html</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Devendra Fadanvis on Rain Update : मुंबईला रेड अलर्ट ! मुख्यमंत्री देवेंद्र फडणवीस यांनी पावसाबद्दल दिली महत्त्वाची अपडेट</t>
+          <t>Thane Rain: ठाणे जिल्ह्यात झोडपणी; ठाणे, कल्याण, डोंबिवलीतील सखल भाग जलमय, आज शाळांना सुट्टी</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/maharashtra-hevey-rain-update-cm-devendra-fadanvis-gives-important-information-know-about-more-/40070</t>
+          <t>https://marathi.indiatimes.com/maharashtra/thane/waterlogging-in-thane-kalyan-dombivali-schools-closed-today-19-august/articleshow/123374806.cms</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Mumbai Rain Updates : सात जणांचा मृत्यू ते शेकडो गावे बाधित; राज्यभरात अतिवृष्टीमुळे कुठे काय घडलं?</t>
+          <t>Mumbai Rain Alert:मुंबईत पावसाची धुवाँधार बॅटिंग;शाळांना सुट्टी जाहीर</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-updates-18-august-heavy-rainfall-mumbai-navi-mumbai-kolhapur-raigad-sindhudurag-local-train-latest-updates-traffic-news-rak-94-5312079/</t>
+          <t>https://ilovenagar.com/mumbai-rain-alert-schools-declare-holiday-today/</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Crop damage : 4 लाख हेक्टर क्षेत्रावरील पिकांची हानी</t>
+          <t>प्रशांत यादव यांचा आज भाजप प्रवेश</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/crop-damage-4-lakh-hectares-ab96</t>
+          <t>https://ratnagirikhabardar.com/news/74397/</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>मोठी बातमी! शेतकऱ्यांची कर्जमाफी होणार, मुख्यमंत्री घोषणा करणार, बड्या मंत्र्याने दिली माहिती</t>
+          <t>मराठ्यांच्या गौरवशाली इतिहासाची साक्ष!, श्रीमंत राजे रघुजी भोसले यांच्या ऐतिहासिक तलवारीचं भव्य लोकार्पण</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/big-update-on-farmer-loan-waiver-cm-fadnavis-will-do-announcement-says-minister-sanjay-rathod-1472819.html</t>
+          <t>https://marathi.asianetnews.com/maharashtra/raghuji-bhosale-historic-sword-returns-to-mumbai/photoshow-g6glpm3</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>मुख्यमंत्री फडणवीस यांची माहिती, राज्यात अतिवृष्टी, ८०० गावे बाधित, मुंबईत १७० एमएम पाऊस</t>
+          <t>School Closed | मोठी बातमी! पावसामुळे आज महाराष्ट्रातील 'या' जिल्ह्यातील शाळा बंद</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/cm-fadnavis-said-heavy-rains-in-the-state-800-villages-affected-170-mm-rain/</t>
+          <t>https://www.thodkyaat.com/maharashtra-school-closed-tomorrow/</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>मोठी बातमी! नाराजी भोवली, शिवसेना शिंदे गटाला सर्वात मोठा धक्का, बड्या नेत्यानं सोडली एकनाथ शिंदेंची...</t>
+          <t>SUPER 100 : राष्ट्रपति ट्रंप की जेलेंस्की और यूरोपीय नेताओं की साथ बैठक में अमेरिका, रूस और यूक्रेन के बीच त्रिपक्षीय वार्ता पर बनी सहमति...</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/big-blow-to-eknath-shinde-big-leader-of-shiv-sena-shinde-group-will-join-bjp-1472541.html</t>
+          <t>https://www.indiatv.in/video/news-bulletin/super-100-in-the-meeting-of-president-trump-with-zelensky-and-european-leaders-an-agreement-was-reached-on-trilateral-talks-between-america-russia-2025-08-19-1156864</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>मराठ्यांच्या इतिहासाचं सोनेरी पान उलगडलं, मुख्यमंत्र्यांच्या हस्ते सरदार रघुजी राजे भोसले यांच्या ऐतिहासिक तलवारीचं लोकार्पण</t>
+          <t>मुंबई में आज शाम हाई टाइड, लोगों से सावधानी की अपील, भारी बारिश का लोकल ट्रेनों</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/unveiling-the-historic-sword-of-sardar-raghuji-raje-bhosale-in-mumbai-presence-of-chief-minister-devendra-fadnavis-know-history-of-raghuji-raje-sword-maharashtra-news-mhs25081900619</t>
+          <t>https://www.abplive.com/photo-gallery/states/maharashtra-mumbai-heavy-rainfall-waterlogging-imd-red-alert-local-train-delayed-photos-maharashtra-news-2997487</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Mumbai Rains News: मुंबईसह महाराष्ट्रात 3 जिल्ह्यात शाळा-कॉलेज बंद, पावसाने सामान्यांचे झाले हाल; तलाव भरले</t>
+          <t>समाचार संध्या</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/mumbai-rains-news-updates-school-college-closed-due-to-heavy-rains-thane-palghar-has-problem-963739.html</t>
+          <t>https://www.newsonair.gov.in/bulletins-detail/%E0%A4%B8%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%BE%E0%A4%B0-%E0%A4%B8%E0%A4%82%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%BE-508/</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Nanded Breaking : मोठी बातमी! नांदेडमध्ये अनेक गाव पाण्याखाली, 15 जण अडकले तर 40 ते 50 म्हशीचा पाण्यात बुडून मृत्यू</t>
+          <t>नवीन पिढीला इतिहासाशी जोडण्याचे कार्य सुरू – मुख्यमंत्री देवेंद्र फडणवीस</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>https://www.lokshahi.com/news/rains-in-nandeds-mukhed-taluka-have-caused-flash-floods-in-many-villages-and-information-has-emerged-that-15-people-from-the-village-are-stranded</t>
+          <t>https://mahasamvad.in/176229/</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>महाराष्ट्रात सर्वदूर पावसामुळे हाहाकार; मोठ्या प्रमाणात जीवित आणि वित्तहानी, बळीराज अडचणीत!</t>
+          <t>Aaj Ki Baat: Mumbai में बारिश का Red Alert...48 घंटे संभलकर</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/marathi/maharashtra/rains-wreak-havoc-across-maharashtra-massive-loss-of-life-and-property-farmers-in-trouble-06-692619</t>
+          <t>https://www.indiatv.in/video/aaj-ki-baat/aaj-ki-baat-red-alert-for-rain-in-mumbai-be-careful-for-48-hours-2025-08-19-1156835</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>10 रुपयांत ‘शिवभोजन थाळी’ योजना थांबणार? शिवभोजन केंद्र चालकांची कोट्यवधींची बिलं थकली</t>
+          <t>इतिहासाची अमूल्य खुण भारतात! इतिहासाशी पुन्हा जोडणारा क्षण, मुख्यमंत्री फडणवीसांची भावनिक प्रतिक्रिया</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/marathi/maharashtra/will-the-shiv-bhojan-thali-scheme-for-10-rupees-stop-shiv-bhojan-center-operators-are-facing-bills-worth-crores-02-692694</t>
+          <t>https://www.esakal.com/maharashtra/chief-minister-devendra-fadnavis-statement-after-bringing-sword-of-raje-raghuji-bhosale-to-india-vru98</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>प्रशासन सतर्क : नागरिकांनी घराबाहेर पडू नये: मुख्यमंत्री फडणवीस !</t>
+          <t>Nanded Heavy Rain: नांदेडमध्ये ढगफुटीसदृश पाऊस, मुखेड तालुक्यात पूर, पाच जण बेपत्ता, सैन्य दलाला पाचारण</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/administrator-citizens-should-not-stay-home-chief-minister/</t>
+          <t>https://www.msn.com/mr-in/news/other/nanded-heavy-rain-%E0%A4%A8-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%A1%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A5%87-%E0%A4%A2%E0%A4%97%E0%A4%AB%E0%A5%81%E0%A4%9F-%E0%A4%B8%E0%A4%A6%E0%A5%83%E0%A4%B6-%E0%A4%AA-%E0%A4%8A%E0%A4%B8-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%87%E0%A4%A1-%E0%A4%A4-%E0%A4%B2%E0%A5%81%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%AA%E0%A5%82%E0%A4%B0-%E0%A4%AA-%E0%A4%9A-%E0%A4%9C%E0%A4%A3-%E0%A4%AC%E0%A5%87%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A4-%E0%A4%B8%E0%A5%88%E0%A4%A8%E0%A5%8D%E0%A4%AF-%E0%A4%A6%E0%A4%B2-%E0%A4%B2-%E0%A4%AA-%E0%A4%9A-%E0%A4%B0%E0%A4%A3/ar-AA1KIAWQ</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>लवकरच कर्जमाफीची घोषणा होणार? महायुती सरकारमधील मंत्र्यांनी दिले संकेत</t>
+          <t>मुंबईत सर्व शासकीय-निमशासकीय कार्यालयांना सुट्टी जाहीर, फॉर्सबेरी जलाशयाजवळ चार तासात 109 मिमी पावसाची नोंद</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>https://marathi.oneindia.com/maharashtra/maharashtra-cm-fadnavis-loan-waiver-announcement-035127.html</t>
+          <t>https://www.etvbharat.com/mr/!state/mumbai-rain-news-all-government-semi-government-offices-in-mumbai-remain-closed-today-mumbai-local-tracks-under-water-amid-imd-red-alert-for-extremely-heavy-rainfall-maharashtra-news-mhs25081901225</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>मुख्यमंत्री लवकरच शेतकरी कर्जमाफीची घोषणा करणार ; शिंदेंच्या मंत्र्यांचा दावा !</t>
+          <t>Weather Updates : मुंबईत अचानक एवढा पाऊस का पडतोय? पुणे वेधशाळेच्या हवामान शास्त्रज्ञांनी</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/chief-minister-will-soon-announce-farmer-loan-waiver-shindes-ministers-claim/</t>
+          <t>https://marathi.abplive.com/news/pune-imd-on-heavy-rainfall-know-why-is-mumbai-suddenly-getting-so-much-rain-wather-update-imd-alert-for-mumbai-thane-for-next-48-hours-1377940</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Maharashtra on high alert as heavy rains batter state; CM, Dy CM lead rescue efforts</t>
+          <t>Maharashtra Breaking News LIVE : दिवसभरातील महत्त्वाच्या घडामोडी, ब्रेकिंग न्यूजचा आढावा एका क्लिकवर</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>https://www.daijiworld.com/news/newsDisplay?newsID=1289634</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-august-18-political-news-in-marathi-933194</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Mumbai rain highlights: BMC declares holiday for schools, colleges today amid heavy rain forecast</t>
+          <t>School Closed Tomorrow : आदेश आला! पावसामुळे असणार शाळा बंद; कुठे-कुठे सुट्टी जाहीर? जाणून घ्या</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/mumbai-rain-live-updates-red-alert-school-closed-heavy-rains-august-18-weather-waterlogging-borivali-thane-powai-bmc-101755498397210.html</t>
+          <t>https://www.tv9marathi.com/maharashtra/maharashtra-rain-update-government-declared-school-holiday-for-mumbai-thane-kalyan-dombivli-palghar-district-1472791.html</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Mumbai-Pune Latest Rain Updates Maharashtra: दिवसभरातील महत्त्वाच्या घडामोडी वाचा एका क्लिकवर</t>
+          <t>नागपूरच्या राजे रघुजी भोसलेंची तलवार लंडनमधून मुंबईत, इतिहासाशी नवीन पिढीला जोडण्याचं कामं, मुख्यमंत्र्यांकडून कौतुक</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-19-august-2025-mumbai-pune-rain-maharashtra-weather-update-imd-kokan-cm-devendra-fadnavis-stock-market-ajit-pawar-farmer-ahul-gandhi-us-president-donald-trump-supreme-court-railway-sports-entertainment-politics-finance-trending-viral-news-updates</t>
+          <t>https://mpbreakingnews.in/marathi/maharashtra/nagpurs-raja-raghuji-bhosales-sword-arrives-in-mumbai-from-london-02-692697</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>C.P. Radhakrishnan यांची उपराष्ट्रपतीपदासाठी उमेदवारी, नेमकं कारण काय? Marathi News N18V</t>
+          <t>मराठवाड्यात आज आणि उद्याही पावसाचे धुमशान, विभागीय आयुक्तांचा नागरिकांबरोबरच प्रशासनालाही सतर्कतेचा इशारा</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/cp-radhakrishnan-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%89%E0%A4%AA%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A4%AA%E0%A4%A4-%E0%A4%AA%E0%A4%A6-%E0%A4%B8-%E0%A4%A0-%E0%A4%89%E0%A4%AE%E0%A5%87%E0%A4%A6%E0%A4%B5-%E0%A4%B0-%E0%A4%A8%E0%A5%87%E0%A4%AE%E0%A4%95%E0%A4%82-%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%95-%E0%A4%AF-marathi-news-n18v/vi-AA1KKh8T</t>
+          <t>https://newstown.in/weather-alert-heavy-to-very-heavy-rain-predicted-on-18-1nd-19-august-2025-in-marathwada-region-by-imd-administration-on-alert/</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>BJP ने शिंदे गुट में लगाई सेंध! कट्टर शिवसैनिक छोड़ेंगे पार्टी, निकाय चुनाव से पहले दिया बड़ा झटका</t>
+          <t>कोल्हापूर सर्किट बेंच झाले, आता खंडपीठाचा प्रस्ताव द्या; सरन्यायाधीश भूषण गवईंची सूचना</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/maharashtra-politics-bjp-gives-setback-to-eknath-shinde-shiv-sena-before-civic-polls-19873589</t>
+          <t>https://ratnagirikhabardar.com/news/74340/</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Coffee Par Kurukshetra: उपराष्ट्रपति के नाम पर INDI अलायंस टूट जाएगा?</t>
+          <t>Aakar Patel| New Maharashtra Security Law Open To Abuse, Threatens Rights; Say ‘No’ To It</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/kurukshetra/coffee-par-kurukshetra-indi-2025-08-19-1156832</t>
+          <t>https://www.asianage.com/opinion/columnists/aakar-patel-new-maharashtra-security-law-open-to-abuse-threatens-rights-say-no-to-it-1898277</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Muqabla: 'वोट चोरी' पर जीत किसकी...Rahul Gandhi या Election Commission?</t>
+          <t>Upcoming ‘Third Mumbai’ will spur economic growth, says Maharashtra chief minister</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/news-bulletin/muqabla-rahul-gandhi-or-the-election-commission-who-wins-the-vote-theft-battle-2025-08-19-1156831</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/upcoming-third-mumbai-will-spur-economic-growth-says-maharashtra-chief-minister/articleshow/123368667.cms</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Haqiqat Kya Hai: मुनीर के मरने की तारीख भी आने वाली है ?</t>
+          <t>Mumbai gets 177mm rain in 6-8 hour period, says CM; all agencies asked to remain alert</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/hakikat-kya-hai/haqiqat-kya-hai-2025-08-19-1156836</t>
+          <t>https://m.economictimes.com/news/india/mumbai-gets-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/amp_articleshow/123365291.cms</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Yoga With Swami Ramdev :ज़्यादा स्क्रीन टाइम से बच्चों को दिल की बीमारी</t>
+          <t>NCP (SP) targets Maha minister over Rs 5,000 cr scam in Navi Mumbai’s CIDCO land; demands his resignation</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/yoga/yoga-with-swami-ramdev-excessive-screen-time-can-cause-heart-disease-in-children-2025-08-19-1156871</t>
+          <t>https://www.socialnews.xyz/2025/08/18/ncp-sp-targets-maha-minister-over-rs-5000-cr-scam-in-navi-mumbais-cidco-land-demands-his-resignation/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=ncp-sp-targets-maha-minister-over-rs-5000-cr-scam-in-navi-mumbais-cidco-land-demands-his-resignation</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Aaj Ki Baat: Mumbai में बारिश का Red Alert...48 घंटे संभलकर</t>
+          <t>Maha CM asks agencies to be on alert mode after heavy rainfall and flash floods</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/aaj-ki-baat/aaj-ki-baat-red-alert-for-rain-in-mumbai-be-careful-for-48-hours-2025-08-19-1156835</t>
+          <t>https://www.socialnews.xyz/2025/08/18/maha-cm-asks-agencies-to-be-on-alert-mode-after-heavy-rainfall-and-flash-floods/amp/</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>कोल्हापुर में शुरू हुई बॉम्बे हाईकोर्ट की नई खंडपीठ, सीजेआई बोले– महाराष्ट्र न्यायिक ढांचे में आगे</t>
+          <t>CM to inaugurate additional water supply scheme</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/maharashtra/bombay-high-court-kolhapur-bench-cji-b-r-gavai-maharashtra-government-54-803927</t>
+          <t>https://www.lokmattimes.com/aurangabad/cm-to-inaugurate-additional-water-supply-scheme/</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Mumbai Rains: भारी बारिश के चलते रेड अलर्ट पर मुंबई, स्कूल-कॉलेज बंद; अगले 5 दिनों तक बरसेंगे बादल</t>
+          <t>Farmers Loan Waiver: बावनकुळेंनंतर महायुती सरकारमधील 'या' मंत्र्याची कर्जमाफीबाबत मोठी अपडेट; म्हणाले,'CM फडणवीस लवकरच...'</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>https://hindi.business-standard.com/india-news/maharashtra/mumbai-rains-city-on-red-alert-schools-and-colleges-closed-clouds-will-rain-for-5-days-id-465240/amp</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/sanjay-rathod-update-farmer-loan-waiver-devendra-fadnavis-dk88</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>महाराष्ट्र की ‘अस्मिता’ की बात करने वाले उपराष्ट्रपति पद के लिए राधाकृष्णन का समर्थन करें : फडणवीस</t>
+          <t>महाराष्ट्रात महाभयानक पाऊस! मुख्यमंत्री देवेंद्र फडणवीस यांनी तातडीने साधला शेजारील राज्यांशी संपर्क? कारण अतिशय चिंताजनक</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/support-radhakrishnan-for-the-post-of-vice-president-who-talks-about-maharashtras-identity-fadnavis/856729/?amp</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%AE%E0%A4%B9-%E0%A4%AD%E0%A4%AF-%E0%A4%A8%E0%A4%95-%E0%A4%AA-%E0%A4%8A%E0%A4%B8-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A4-%E0%A4%A4%E0%A4%A1-%E0%A4%A8%E0%A5%87-%E0%A4%B8-%E0%A4%A7%E0%A4%B2-%E0%A4%B6%E0%A5%87%E0%A4%9C-%E0%A4%B0-%E0%A4%B2-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B6-%E0%A4%B8%E0%A4%82%E0%A4%AA%E0%A4%B0%E0%A5%8D%E0%A4%95-%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%85%E0%A4%A4-%E0%A4%B6%E0%A4%AF-%E0%A4%9A-%E0%A4%82%E0%A4%A4-%E0%A4%9C%E0%A4%A8%E0%A4%95/ar-AA1KJav3</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>India Squad Asia Cup 2025: शुभमन गिल का कटेगा पत्ता, इस खिलाड़ी को मिल सकती है टीम में जगह</t>
+          <t>पूर परिस्थितीवर अबू आझमी यांचे मुख्यमंत्री फडणवीस यांना पत्र, तातडीने मदत देण्याची मागणी</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/sports/india-squad-asia-cup-2025-2025-08-18-1156798</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/abu-azmi-writes-to-cm-fadnavis-on-flood-situation-demands-urgent-assistance-125081900011_1.html</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में मानसून का कहर: मुखेड तालुका में बादल फटने जैसी घटना, 200 से ज्यादा गांवों में बाढ़</t>
+          <t>Vidarbha Crop Loss: विदर्भात दोन लाख हेक्टरवर पीक नुकसान</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>https://hindi.dynamitenews.com/maharashtra/cloudburst-in-mukhed-taluka-in-maharashtra-flood-in-more-than-200-villages</t>
+          <t>https://agrowon.esakal.com/agro-special/crop-damage-on-two-lakh-hectares-in-vidarbha-rat16</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Asia Cup 2025: पाकिस्तान क्रिकेट के मुख्य चयनकर्ता का बड़ा बयान, बोले- भारत को हराएगा पाकिस्तान</t>
+          <t>देवेंद्र फडणवीस यांच्यासोबतच्या कोल्ड वॉरच्या चर्चेवर एकनाथ शिंदे यांची प्रतिक्रिया, स्पष्टच म्हणाले....</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/sports/asia-cup-2025-2025-08-18-1156799</t>
+          <t>https://www.msn.com/mr-in/news/national/%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%AC%E0%A4%A4%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%A1-%E0%A4%B5-%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A%E0%A5%87%E0%A4%B5%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A4%9A-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1zqXD8?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>मराठा सेनापति रघुजी भोंसले की तलवार मुंबई पहुंची</t>
+          <t>मुख्यमंत्री फडणवीस यांची माहिती, राज्यात अतिवृष्टी, ८०० गावे बाधित, मुंबईत १७० एमएम पाऊस</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/ncr/new-delhi/story-historic-sword-of-maratha-general-raghuji-bhosale-i-repatriated-to-mumbai-201755537654676.html</t>
+          <t>https://www.marathiebatmya.com/political/cm-fadnavis-said-heavy-rains-in-the-state-800-villages-affected-170-mm-rain/</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>मुंबई में 6-8 घंटे में 177 मिलीमीटर बारिश हुई: फडणवीस</t>
+          <t>Heavy Rainfall : रेड ॲलर्ट घोषित केलेल्या ठिकाणी सतर्कता बाळगण्याचे मुख्यमंत्री फडणवीसांचे निर्देश</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/maharashtra/mumbai-received-177-mm-rainfall-in-6-8-hours-fadnavis-3213025.html</t>
+          <t>https://www.marathi.hindusthanpost.com/social/heavy-rainfall-cm-devendra-fadnavis-instructs-to-remain-vigilant-in-places-where-red-alert-has-been-declared/</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Amravati Politics: अमरावती के दरियापुर में कांग्रेस को बड़ा झटका, सलीम घनीवाला भाजपा में शामिल</t>
+          <t>Congress Should Check Voter Lists Now, quips Chandrashekhar Bawankule</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/amravati/major-blow-to-congress-in-dariyapur-of-amravati-salim-ghaniwala-joins-bjp-1321794.html/amp</t>
+          <t>https://www.msn.com/en-in/news/India/congress-should-check-voter-lists-now-quips-chandrashekhar-bawankule/ar-AA1KGGDd</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>SUPER 100 : राष्ट्रपति ट्रंप की जेलेंस्की और यूरोपीय नेताओं की साथ बैठक में अमेरिका, रूस और यूक्रेन के बीच त्रिपक्षीय वार्ता पर बनी सहमति...</t>
+          <t>Rajnath reaches out to DMK, TMC, BJD for consensus on VP nominee</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/news-bulletin/super-100-in-the-meeting-of-president-trump-with-zelensky-and-european-leaders-an-agreement-was-reached-on-trilateral-talks-between-america-russia-2025-08-19-1156864</t>
+          <t>https://timesofindia.indiatimes.com/india/rajnath-reaches-out-to-dmk-tmc-bjd-for-consensus-on-vp-nominee/articleshow/123373035.cms</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>मुंबईतील सर्व शासकीय आणि निमशासकीय कार्यालयांना आज सुट्टी जाहीर!</t>
+          <t>'My karyakarta is with me': Hitendra Thakur shrugs off defections ahead of civic elections</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/19/mumbai-rains-govt-declares-holiday-for-all-government-and-private-offices-amid-heavy-rainfall.html</t>
+          <t>https://www.msn.com/en-in/news/India/my-karyakarta-is-with-me-hitendra-thakur-shrugs-off-defections-ahead-of-civic-elections/ar-AA1KHNiH</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>नागपूरच्या राजे रघुजी भोसलेंची तलवार लंडनमधून मुंबईत, इतिहासाशी नवीन पिढीला जोडण्याचं कामं, मुख्यमंत्र्यांकडून कौतुक</t>
+          <t>NDA’s VP nominee CP Radhakrishnan meets PM Modi in Delhi</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/marathi/maharashtra/nagpurs-raja-raghuji-bhosales-sword-arrives-in-mumbai-from-london-02-692697</t>
+          <t>https://www.news9live.com/india/ndas-vp-nominee-cp-radhakrishnan-meets-pm-modi-in-delhi-2883321</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>मंत्री आशीष शेलार यांनी घेतला आपात्कालीन व्यवस्थापनाचा आढावा</t>
+          <t>'Destroying constitutional institutions': Nishikant Dubey slams Rahul Gandhi as SC dismisses plea challenging 2024 Maharashtra polls</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>https://www.jpnnews.in/2025/08/Ashish-Shelar-reviews-emergency-management.html</t>
+          <t>https://www.malaysiasun.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>समाचार संध्या</t>
+          <t>“जामनेरमधील हत्याकांडात भाजप कार्यकर्ते…” अबू आझमींचा आरोप</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/bulletins-detail/%E0%A4%B8%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%BE%E0%A4%B0-%E0%A4%B8%E0%A4%82%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%BE-508/</t>
+          <t>https://www.loksatta.com/nashik/abu-azmi-alleges-bjp-workers-involved-in-jalgaon-mob-lynching-case-of-suleman-pathan-vsd-99-5314556/</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>नवीन पिढीला इतिहासाशी जोडण्याचे कार्य सुरू – मुख्यमंत्री देवेंद्र फडणवीस</t>
+          <t>Mumbai Rain Alert : मुंबईकरांनो सावध रहा.. पुढील 4 तास धोक्याचे… रेड अलर्ट अन् हवामान खात्याचा...</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176229/</t>
+          <t>https://www.tv9marathi.com/videos/mumbai-weather-forecast-imd-red-alert-for-mumbai-for-next-4-hours-extremely-important-for-mumbaikars-1473139.html/amp</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>मुंबई में आज शाम हाई टाइड, लोगों से सावधानी की अपील, भारी बारिश का लोकल ट्रेनों</t>
+          <t>Eknath Shinde : एकनाथ शिंदेंना मोठा धक्का ! ‘या’ नेत्याने निवडणुकीच्या तोंडावर सोडली साथ</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/photo-gallery/states/maharashtra-mumbai-heavy-rainfall-waterlogging-imd-red-alert-local-train-delayed-photos-maharashtra-news-2997487</t>
+          <t>https://www.dainikprabhat.com/big-blow-to-eknath-shinde-big-leader-of-shiv-sena-shinde-group-will-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>मुंबईत सर्व शासकीय-निमशासकीय कार्यालयांना सुट्टी जाहीर, फॉर्सबेरी जलाशयाजवळ चार तासात 109 मिमी पावसाची नोंद</t>
+          <t>राष्ट्रवादीचे प्रशांत यादव यांचा आज भाजप प्रवेश</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/mumbai-rain-news-all-government-semi-government-offices-in-mumbai-remain-closed-today-mumbai-local-tracks-under-water-amid-imd-red-alert-for-extremely-heavy-rainfall-maharashtra-news-mhs25081901225</t>
+          <t>https://pudhari.news/maharashtra/kokan/ratnagiri/ncp-prashant-yadav-joins-bjp-today-dc95</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>सरदार रघुजी भोसले यांची ऐतिहासिक तलवार मुंबईत दाखल; मुख्यमंत्र्यांच्या हस्ते होणार लोकार्पण</t>
+          <t>Ashish Shelar: मुंबईत जोरदार पाऊस! पावसाचा आढावा घेतल्यानंतर मंत्री शेलार म्हणाले, 'अत्यंत गरज असल्यास...'</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/sword-of-maratha-commander-raghuji-bhosale-returns-to-mumbai-to-be-unveiled-at-exhibition-by-cm-fadnavis-maharashtra-news-mhs25081803521</t>
+          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/mumbai-rain-updates-ashish-shelar-reviewed-the-rainfall-and-said-stay-safe-at-home/40069</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Maharashtra Breaking News LIVE : दिवसभरातील महत्त्वाच्या घडामोडी, ब्रेकिंग न्यूजचा आढावा एका क्लिकवर</t>
+          <t>Uddhav Thackeray: मनसेसोबत युती महापालिका निवडणुकीत घातक ठरणार; उद्धव ठाकरेंना 'या' नेत्यानं केलं सावध?</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-august-18-political-news-in-marathi-933194</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/mns-alliance-risk-municipal-elections-uddhav-thackeray-warning-dk88-rc70</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>मराठवाड्यात आज आणि उद्याही पावसाचे धुमशान, विभागीय आयुक्तांचा नागरिकांबरोबरच प्रशासनालाही सतर्कतेचा इशारा</t>
+          <t>Congress Mohan Joshi Pune | Don't wait for BJP's 'event', open the flyover</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>https://newstown.in/weather-alert-heavy-to-very-heavy-rain-predicted-on-18-1nd-19-august-2025-in-marathwada-region-by-imd-administration-on-alert/</t>
+          <t>https://policenama.com/congress-mohan-joshi-pune-dont-wait-for-bjps-event-open-the-flyover-former-mla-mohan-joshis-letter-to-the-municipal-commissioner/</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>महाराष्ट्रातील या जिल्ह्यात 'तिसरी मुंबई' वसवली जाईल, मुख्यमंत्री देवेंद्र फडणवीस यांनी प्रकल्पाचे महत्त्वाचे मुद्दे सांगितले</t>
+          <t>राज्यात ‘ओला दुष्काळ’ जाहीर करा, एकरी ५० हजार रुपयांची मदत द्या -शशिकांत शिंदे</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/third-mumbai-will-be-settled-in-this-district-of-maharashtra-125081900017_1.html</t>
+          <t>https://politicalmaharashtra.in/declare-wet-drought-in-the-state-provide-assistance-of-rs-50000-per-acre-shashikant-shinde-97623/</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Aakar Patel| New Maharashtra Security Law Open To Abuse, Threatens Rights; Say ‘No’ To It</t>
+          <t>‘गँग्स ऑफ गद्दार’: शिंदेचा मंत्री ‘रोहित पवारांच्या’ निशाण्यावर</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>https://www.asianage.com/opinion/columnists/aakar-patel-new-maharashtra-security-law-open-to-abuse-threatens-rights-say-no-to-it-1898277</t>
+          <t>https://politicalmaharashtra.in/gangs-of-traitors-shindes-minister-targeted-by-rohit-pawar-97619/</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>CM to inaugurate additional water supply scheme</t>
+          <t>Nagpur’s Councils Starved Again: Pennies for a Region in Ruin</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/aurangabad/cm-to-inaugurate-additional-water-supply-scheme/</t>
+          <t>https://thelivenagpur.com/2025/08/18/nagpurs-councils-starved-again-pennies-for-a-region-in-ruin/</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Vidarbha Crop Loss: विदर्भात दोन लाख हेक्टरवर पीक नुकसान</t>
+          <t>Ahead of Civic Polls, Hitendra Thakur Backs Loyalists: ‘My Karyakarta Is With Me, They Ensure Our Party Wins</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/crop-damage-on-two-lakh-hectares-in-vidarbha-rat16</t>
+          <t>https://www.lokmattimes.com/maharashtra/ahead-of-civic-polls-hitendra-thakur-backs-loyalists-my-karyakarta-is-with-me-they-ensure-our-party-wins-a475/</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Rajnath reaches out to DMK, TMC, BJD for consensus on VP nominee</t>
+          <t>Maha CM asks agencies to be on alert mode after heavy rainfall and flash floods</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/rajnath-reaches-out-to-dmk-tmc-bjd-for-consensus-on-vp-nominee/articleshow/123373035.cms</t>
+          <t>https://www.socialnews.xyz/2025/08/18/maha-cm-asks-agencies-to-be-on-alert-mode-after-heavy-rainfall-and-flash-floods/</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Congress Should Check Voter Lists Now, quips Chandrashekhar Bawankule</t>
+          <t>Mumbai rains: IMD issues red alert as downpour continues; schools, colleges &amp; Govt offices shut</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/congress-should-check-voter-lists-now-quips-chandrashekhar-bawankule/ar-AA1KGGDd</t>
+          <t>https://newslivetv.com/mumbai-rains-imd-issues-red-alert/</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>'My karyakarta is with me': Hitendra Thakur shrugs off defections ahead of civic elections</t>
+          <t>BJP ने शिंदे गुट में लगाई सेंध! कट्टर शिवसैनिक छोड़ेंगे पार्टी, निकाय चुनाव से पहले दिया बड़ा झटका</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/my-karyakarta-is-with-me-hitendra-thakur-shrugs-off-defections-ahead-of-civic-elections/ar-AA1KHNiH</t>
+          <t>https://www.patrika.com/mumbai-news/maharashtra-politics-bjp-gives-setback-to-eknath-shinde-shiv-sena-before-civic-polls-19873589</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>CP Radhakrishnan vs who? Why DMK’s pushing INDIA bloc for a Tamil vs Tamil contest for India’s V-P</t>
+          <t>Maharashtra politics : मुख्यमंत्र्यांच्या पत्नी गायिका, तरीही गाणे गाणाऱ्या तहसीलदारांना शिक्षा? बावनकुळे या चुकीला माफी असायलाच हवी; सामनातून हल्लाबोल</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/cp-radhakrishnan-vs-who-why-dmks-pushing-india-bloc-for-a-tamil-vs-tamil-contest-for-indias-v-p/2723136/</t>
+          <t>https://sarkarnama.esakal.com/mumbai/nanded-tehsildar-prashant-thorat-suspension-shiv-sena-ubt-criticism-sanjay-raut-devendra-fadnavis-jap93</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>'Destroying constitutional institutions': Nishikant Dubey slams Rahul Gandhi as SC dismisses plea challenging 2024 Maharashtra polls</t>
+          <t>'ऑपरेशन लोटस वगैरे काही नाही; लवकरच ऑपरेशन टायगर दिसेल', सोलापूरच्या राजकारणात पडद्यामागे काय घडतंय?</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>http://www.malaysiasun.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
+          <t>https://marathi.indiatimes.com/maharashtra/solapur/solapur-politics-over-shiv-sena-leader-shivaji-sawant-may-join-bjp/articleshow/123369493.cms</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Eknath Shinde : एकनाथ शिंदेंना मोठा धक्का ! ‘या’ नेत्याने निवडणुकीच्या तोंडावर सोडली साथ</t>
+          <t>Coffee Par Kurukshetra: उपराष्ट्रपति के नाम पर INDI अलायंस टूट जाएगा?</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/big-blow-to-eknath-shinde-big-leader-of-shiv-sena-shinde-group-will-join-bjp/</t>
+          <t>https://www.indiatv.in/video/kurukshetra/coffee-par-kurukshetra-indi-2025-08-19-1156832</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Kokan Politics : शरद पवार गटाला धक्का; प्रदेश सरचिटणीस प्रशांत यादव भाजपाच्या वाटेवर</t>
+          <t>खरगे, स्टॉलिन, नवीन पटनायक... उपराष्ट्रपति चुनाव से पहले राजनाथ सिंह को बीजेपी ने दी खास जिम्मेदारी</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/kokan-politics-sharad-pawar-group-suffers-setback-state-general-secretary-prashant-yadav-on-bjps-path/</t>
+          <t>https://navbharattimes.indiatimes.com/india/vice-president-election-defence-minister-rajnath-singh-reaches-out-to-dmk-tmc-bjd-for-consensus-for-cp-radhakrishnan/articleshow/123375990.cms</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Those who speak of Maharashtra 'asmita' should support Radhakrishnan for VP post: Fadnavis</t>
+          <t>महाराष्ट्र में मौसम बरपा रहा कहर: नांदेड़ में फटा बादल, बारिश के चलते 15 से 16 जिलो में अलर्ट, CM फडणवीस ने फसलों से लेकर लोकल ट्रेनों के बारे में दिया ये बड़ा अपडेट | Devendra Fadnavis, Cloudburst, Nan</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/those-who-speak-of-maharashtra-asmita-should-support-radhakrishnan-for-vp-post-fadnavis-9672630</t>
+          <t>https://www.bhaskarhindi.com/politics/devendra-fadnavis-cloudburst-nanded-maharashtra-news-maharashtra-1174025</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>NDA’s VP nominee CP Radhakrishnan meets PM Modi in Delhi</t>
+          <t>Kokan Politics : शरद पवार गटाला धक्का; प्रदेश सरचिटणीस प्रशांत यादव भाजपाच्या वाटेवर</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>https://www.news9live.com/india/ndas-vp-nominee-cp-radhakrishnan-meets-pm-modi-in-delhi-2883321</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/kokan-politics-sharad-pawar-group-suffers-setback-state-general-secretary-prashant-yadav-on-bjps-path/</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>राज्यात पावसाचा हाहाकार! मुख्यमंत्री फडणवीस अॅक्टीव्ह मोडवर, सतर्क राहण्याचे आवाहन</t>
+          <t>Amravati Politics: अमरावती के दरियापुर में कांग्रेस को बड़ा झटका, सलीम घनीवाला भाजपा में शामिल</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/maharashtra-rain-cm-fadnavis-reviews-situation-16-districts-on-red-alert/</t>
+          <t>https://navbharatlive.com/maharashtra/amravati/major-blow-to-congress-in-dariyapur-of-amravati-salim-ghaniwala-joins-bjp-1321794.html</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>‘पवार मला सतत टॉर्चर करतायत’, अजित पवारांनी मारलेला ‘तो’ टॉन्ट भाजप नेत्याच्या जिव्हारी</t>
+          <t>शिवसेना एकनाथ शिंदे गुट को बड़ा झटका, शिवाजी सावंत भाजपा में होगें शामिल | Maharastra - Paliwalwani - Latest Hindi News</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/city/pune/ajit-pawar-is-torturing-me-bjp-ram-shinde-big-statement-rohit-pawar/</t>
+          <t>https://paliwalwani.com/maharastra/shiv-sena-eknath-shinde-faction-is-a-big-shock-shivaji-sawant-will-be-involved-in-bjp</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>नगर रस्ता परिसरातील पाणीपुरवठा गुरुवारी बंद राहणार</t>
+          <t>Amravati News : अमरावतीच्या दर्यापुरात काँग्रेसला मोठा धक्का, सलीम घाणीवालांचा भाजपमध्ये प्रवेश</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/city/pune/water-supply-in-nagar-road-area-will-be-closed-on-thursday/</t>
+          <t>https://marathi.ndtv.com/politics/salim-ghaniwala-joins-bjp-big-blow-to-congress-in-daryapur-amravati-9106782</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>मुंबईत कोसळधारा! शासकीय आणि खासगी कार्यालयांना सुट्टी जाहीर</t>
+          <t>Mumbai Rain Red Alert : पावसामुळे आतापर्यंत 7 जणांचा मृत्यू; साचलेल्या पाण्यामुळे प्रवाशांचे हाल अन् राजकारणही तापलं</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/bmc-big-decision-holiday-declared-for-government-and-private-offices-heavy-rain-mumbai/</t>
+          <t>https://sarkarnama.esakal.com/mumbai/mumbai-rain-red-alert-heavy-rainfall-maharashtra-floods-bmc-pune-schooll-jap93</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>बारामतीत हा काय प्रकार? रयत शिक्षण संस्थेच्या प्रांगणात अश्लील ‘डान्स’, Video</t>
+          <t>मंत्री आशीष शेलार यांनी घेतला आपात्कालीन व्यवस्थापनाचा आढावा</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/obscene-dance-premises-of-renowned-rayat-shikshan-sanstha-baramati/</t>
+          <t>https://www.jpnnews.in/2025/08/Ashish-Shelar-reviews-emergency-management.html</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>देशभरात टेलिकॉम कोलमडले! Airtel-Jio-Vi नेटवर्क ठप्प</t>
+          <t>‘शिंदेंच्या सेनेला’ दे धक्का : या आमदार बंधूंनी सोडला पक्ष</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/nation/telecom-collapses-across-the-country-airtel-jio-vi-network-down/</t>
+          <t>https://politicalmaharashtra.in/a-blow-to-shindes-army-these-mla-brothers-left-the-party-97625/</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>"दीदी, मला तुमच्या मदतीची गरज आहे", दहावीच्या मुलीचा फोन अन् पोलिसांच्या संवेदनशीलतेने वाचलं कुटुंब</t>
+          <t>Historic sword of Raje Raghuji Bhonsle arrives in Mumbai to royal welcome</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/crime/sister-i-need-your-help-a-10th-grade-girls-phone-call-and-the-sensitivity-of-the-police-saved-the-family/</t>
+          <t>https://www.nagpurtoday.in/historic-sword-of-raje-raghuji-bhonsle-arrives-in-mumbai-to-royal-welcome/08181446</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>कार्यकर्त्यांना मतदार यादी तपासायला लावा; राहुल गांधींना बावनकुळेंचा सल्ला</t>
+          <t>Heritage India: Iconic Sword of Maratha Commander Raghuji Raje Bhonsle Arrives in Mumbai</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/bawankule-advises-rahul-gandhi-to-get-workers-to-check-voter-list/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-govt-brings-back-iconic-sword-of-maratha-commander-raghuji-raje-bhonsle-auctioned-for-rs-4715-lakh-to-mumbai-3685565</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>दरियापुर में कांग्रेस को बड़ा झटका, सलीम घाणीवाला भाजपा में शामिल</t>
+          <t>Seize assets of school directors in Shalarth ID scam: Bawankule</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>https://www.ucnnews.live/politics/big-blow-to-congress-in-dariyapur-salim-ghaniwala-joins-bjp-1755509472280</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/seize-assets-of-school-directors-in-shalarth-id-scam-bawankule/articleshow/123371134.cms</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>उद्यमी सलीम सेठ घानीवाला की बीजेपी में एन्ट्री</t>
+          <t>Nagpur Smart City projects near closure with 7 works still pending</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/maharashtra/entrepreneur-salim-seth-ghaniwala-enters-bjp/</t>
+          <t>https://infra.economictimes.indiatimes.com/news/urban-infrastructure/nagpur-smart-city-projects-face-delay-7-projects-pending-completion/123360909</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>शिवसेना शिंदे गुट को बड़ा झटका, बड़ा नेता छोड़ेगा एकनाथ शिंदे का साथ</t>
+          <t>NMC pushes ahead with land acquisition for 2 STPs amid reluctance from VNIT, PKV</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/maharashtra/shivaji-sawant-bjp-solapur-eknath-shinde-54-804117</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/nmc-pushes-ahead-with-land-acquisition-for-2-stps-amid-reluctance-from-vnit-pkv/articleshow/123372521.cms</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Mumbai News: चव्हाण ने कहा - श्रमिकों की एक साल में दो बार होगी वेतन वृद्धि</t>
+          <t>MBBS admission quota in unaided colleges cut by 50%, students erupt</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/city/mumbai/mumbai-news-chavan-said-workers-will-get-salary-hike-twice-in-a-year-1174137</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/mbbs-admission-quota-in-unaided-colleges-cut-by-50-students-erupt/articleshow/123372541.cms</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>कौन लेगा CP राधाकृष्णन की जगह? BJP की एक खोज खत्म होते ही शुरू हुई दूसरी तलाश</t>
+          <t>Nagpur Politics | भाईंनी घातला पक्ष प्रवेशाचा दुपट्टा,आता शिवसेनेचे घुमजाव</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/maharashtra-new-governor-who-will-replace-cp-radhakrishnan-bjp-new-search-begins-1321951.html</t>
+          <t>https://www.msn.com/mr-in/news/other/nagpur-politics-%E0%A4%AD-%E0%A4%88%E0%A4%82%E0%A4%A8-%E0%A4%98-%E0%A4%A4%E0%A4%B2-%E0%A4%AA%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6-%E0%A4%9A-%E0%A4%A6%E0%A5%81%E0%A4%AA%E0%A4%9F%E0%A5%8D%E0%A4%9F-%E0%A4%86%E0%A4%A4-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%9A%E0%A5%87-%E0%A4%98%E0%A5%81%E0%A4%AE%E0%A4%9C-%E0%A4%B5/ar-AA1HHJp9</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Amravati Politics: अमरावती के दरियापुर में कांग्रेस को बड़ा झटका, सलीम घनीवाला भाजपा में शामिल</t>
+          <t>३१ खासदार निवडून आले तेव्हा मतदारयाद्या बरोबर होत्या का ?</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/amravati/major-blow-to-congress-in-dariyapur-of-amravati-salim-ghaniwala-joins-bjp-1321794.html</t>
+          <t>https://www.lokmat.com/nagpur/were-the-voter-lists-correct-when-31-mps-were-elected-a-a1000/</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>राष्ट्रवादीचे प्रशांत यादव यांचा आज भाजप प्रवेश</t>
+          <t>रघुजी राजे यांची तलवार आणि ‘स्व’चा बोध</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kokan/ratnagiri/ncp-prashant-yadav-joins-bjp-today-dc95</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/historic-sword-of-shrimant-raghuji-bhosle-back-in-mumbai.html</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>भाजपला स्थानिक ची निवडणूक महायुती म्हणूनच का लढवायची आहे?</t>
+          <t>Teacher Recruitment Scam: बोगस शालार्थ आयडी घोटाळ्यातील संचालकांची मालमत्ता जप्त होणार !</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>https://aaplaawajnews.com/2025/34070/</t>
+          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/bogus-teacher-scam-school-id-fraud-directors-property-to-be-seized-ng81</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Congress Mohan Joshi Pune | Don't wait for BJP's 'event', open the flyover</t>
+          <t>Chandrashekhar Bawankule: 'आताच मतदार याद्या तपासा', महसूल मंत्र्यांचा काँग्रेस नेत्यांना टोला</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>https://policenama.com/congress-mohan-joshi-pune-dont-wait-for-bjps-event-open-the-flyover-former-mla-mohan-joshis-letter-to-the-municipal-commissioner/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/chandrashekhar-bawankule-demands-to-check-voter-lists-against-congress-allegations/articleshow/123356783.cms</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Solapur News : शिंदेंच्या सेनेत राज्यातून ‘इन्कमिंग’ पण सोलापुरात गळती, तानाजी सावंतांच्या बंधूंचा भाजप प्रवेश ठरला</t>
+          <t>Nagpur Accident : नागपुरातील हिट अँड रन प्रकरणाचा AI तंत्रज्ञानाच्या मदतीने उलगडा राज्यातील</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/tanaji-sawant-brother-shivajirao-sawant-resign-eknath-shinde-sena-join-bjp-after-meet-fadnavis/913179/</t>
+          <t>https://marathi.abplive.com/crime/nagpur-hit-and-run-accident-news-update-case-solved-with-the-help-of-ai-technology-first-experiment-in-the-state-driver-arrested-from-uttar-pradesh-1377914</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>'ऑपरेशन लोटस वगैरे काही नाही; लवकरच ऑपरेशन टायगर दिसेल', सोलापूरच्या राजकारणात पडद्यामागे काय घडतंय?</t>
+          <t>Sambhajinagar News : आता शहरवासीयांना मिळणार अतिरिक्त २६ एमएलडी पाणी</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/solapur/solapur-politics-over-shiv-sena-leader-shivaji-sawant-may-join-bjp/articleshow/123369493.cms</t>
+          <t>https://pudhari.news/amp/story/maharashtra/marathwada/chhatrapati-sambhajinagar/now-city-residents-will-get-additional-26-mld-of-water-np88</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में यह क्या हुआ? एकनाथ शिंदे का साथ छोड़ BJP में शामिल हुए कई भरोसेमंद</t>
+          <t>kolhapur | सर्किट बेंचचे स्वप्न साकारले; न्यायाचे दरवाजे खुले झाले!</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/eknath-shinde-shiv-sena-solapur-leaders-join-bjp-amid-internal-feud-2997781</t>
+          <t>https://pudhari.news/amp/story/maharashtra/kolhapur/circuit-bench-dream-realized-doors-of-justice-now-open-ap84</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Uddhav Thackeray: मनसेसोबत युती महापालिका निवडणुकीत घातक ठरणार; उद्धव ठाकरेंना 'या' नेत्यानं केलं सावध?</t>
+          <t>वरूणराजा कोपला! पिकांमध्ये पाणीच पाणी, पुढील 48 तासांत या जिल्ह्यांना पुन्हा रेड अलर्ट</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/mns-alliance-risk-municipal-elections-uddhav-thackeray-warning-dk88-rc70</t>
+          <t>https://news18marathi.com/agriculture/18-august-maharashtra-heavy-rain-update-monsoon-2025-mumbai-red-alert-1460576.html</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Amravati News : अमरावतीच्या दर्यापुरात काँग्रेसला मोठा धक्का, सलीम घाणीवालांचा भाजपमध्ये प्रवेश</t>
+          <t>kolhapur | सर्किट बेंचचे स्वप्न साकारले; न्यायाचे दरवाजे खुले झाले!</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/salim-ghaniwala-joins-bjp-big-blow-to-congress-in-daryapur-amravati-9106782</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/circuit-bench-dream-realized-doors-of-justice-now-open-ap84</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>पश्चिम महाराष्ट्रात शिंदेंना भाजपचा धक्का, आमदाराच्या भावासह ४० पदाधिकाऱ्यांचा शिवसेनेला जय महाराष्ट्र!</t>
+          <t>Vice Presidential Election: सीपी राधाकृष्णन को NDA उम्मीदवार बनाने पर कांग्रेस को लगी मिर्ची, INDI गठबंधन कैंडिडेट पर खोले पत्ते</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/solapur-political-news-bjp-strengthens-in-solapur-as-40-sena-leaders-join-with-shivaji-sawant-bdk97</t>
+          <t>https://www.republicbharat.com/india/congress-angry-cp-radhakrishnan-nda-vice-presidential-candidate-opened-cards-on-indi-alliance-meeting</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>भाजप आमदाराचा डाव प्रशासनाने हाणून पाडला, आईच्या नावाने बांधलेले अम्मा स्मारक अवैध ठरवून हटवले</t>
+          <t>Those who speak of Maharashtra 'asmita' should support Radhakrishnan for VP post: Fadnavis</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/chandrapur-bjp-mla-kishor-jorgewar-faces-setback-as-administration-demolishes-illegal-amma-memorial-construction-as11-rc70</t>
+          <t>https://www.ptinews.com/story/national/those-who-speak-of-maharashtra-'asmita'-should-support-radhakrishnan-for-vp-post:-fadnavis/2832772</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Jalgaon mob lynching Case: जामनेर मॉब लिंचिंग: युवकाच्या हत्येत मंत्री गिरीश महाजनांच्या ड्रायव्हरचा मुलगा मास्टर माईंड?</t>
+          <t>Vice President Election: NDA उम्मीदवार सीपी राधाकृष्णन को मिल सकता है विपक्षी दलों का समर्थन, इन पार्टियों पर सबकी नजर</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/maharashtra-news-jalgaon-jamner-mob-lynching-girish-mahajan-driver-son-mastermind-youth-killed-mm76-sd67</t>
+          <t>https://www.jagran.com/politics/national-rajya-sabha-election-opposition-parties-may-support-nda-candidate-cp-radhakrishnan-24017212.html</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Mumbai Rain Alert : मुंबईकरांनो सावध रहा.. पुढील 4 तास धोक्याचे… रेड अलर्ट अन् हवामान खात्याचा...</t>
+          <t>महाराष्ट्र की ‘अस्मिता’ की बात करने वाले उपराष्ट्रपति पद के लिए राधाकृष्णन का समर्थन करें : फडणवीस</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/mumbai-weather-forecast-imd-red-alert-for-mumbai-for-next-4-hours-extremely-important-for-mumbaikars-1473139.html/amp</t>
+          <t>https://hindi.theprint.in/india/support-radhakrishnan-for-the-post-of-vice-president-who-talks-about-maharashtras-identity-fadnavis/856729/</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>डॉ. बाबासाहेब आंबेडकरांच्या स्मारकाची मागणी</t>
+          <t>Asia Cup 2025: पाकिस्तान क्रिकेट के मुख्य चयनकर्ता का बड़ा बयान, बोले- भारत को हराएगा पाकिस्तान</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>https://aaplaawajnews.com/2025/34067/</t>
+          <t>https://www.indiatv.in/video/sports/asia-cup-2025-2025-08-18-1156799</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Ashish Shelar: मुंबईत जोरदार पाऊस! पावसाचा आढावा घेतल्यानंतर मंत्री शेलार म्हणाले, 'अत्यंत गरज असल्यास...'</t>
+          <t>India Squad Asia Cup 2025: शुभमन गिल का कटेगा पत्ता, इस खिलाड़ी को मिल सकती है टीम में जगह</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>https://www.jaimaharashtranews.com/politics/mumbai-rain-updates-ashish-shelar-reviewed-the-rainfall-and-said-stay-safe-at-home/40069</t>
+          <t>https://www.indiatv.in/video/sports/india-squad-asia-cup-2025-2025-08-18-1156798</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>लाडक्या बहिणींनंतर आता लाडक्या सूना…एकनाथ शिंदेंची मोठी घोषणा</t>
+          <t>Haqiqat Kya Hai: मुनीर के मरने की तारीख भी आने वाली है ?</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/eknath-shinde-big-announcement-ladki-soon-yojana-shiv-senato-implement-scheme/</t>
+          <t>https://www.indiatv.in/video/hakikat-kya-hai/haqiqat-kya-hai-2025-08-19-1156836</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>राज्यात ‘ओला दुष्काळ’ जाहीर करा, एकरी ५० हजार रुपयांची मदत द्या -शशिकांत शिंदे</t>
+          <t>Yoga With Swami Ramdev :ज़्यादा स्क्रीन टाइम से बच्चों को दिल की बीमारी</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>https://politicalmaharashtra.in/declare-wet-drought-in-the-state-provide-assistance-of-rs-50000-per-acre-shashikant-shinde-97623/</t>
+          <t>https://www.indiatv.in/video/yoga/yoga-with-swami-ramdev-excessive-screen-time-can-cause-heart-disease-in-children-2025-08-19-1156871</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>‘गँग्स ऑफ गद्दार’: शिंदेचा मंत्री ‘रोहित पवारांच्या’ निशाण्यावर</t>
+          <t>कौन लेगा CP राधाकृष्णन की जगह? BJP की एक खोज खत्म होते ही शुरू हुई दूसरी तलाश</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>https://politicalmaharashtra.in/gangs-of-traitors-shindes-minister-targeted-by-rohit-pawar-97619/</t>
+          <t>https://navbharatlive.com/maharashtra/maharashtra-new-governor-who-will-replace-cp-radhakrishnan-bjp-new-search-begins-1321951.html</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Nagpur’s Councils Starved Again: Pennies for a Region in Ruin</t>
+          <t>NDA से उपराष्ट्रपति पद के उम्मीदवार चुने जाने पर C.P Radhakrishnan को PM मोदी ने दी बधाई</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/08/18/nagpurs-councils-starved-again-pennies-for-a-region-in-ruin/</t>
+          <t>https://www.primetvindia.com/pm-modi-congratulated-c-p-radhakrishnan/</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>LIVE Update : मुंबईत चौथ्या दिवशीही पावसाची धुवाँधार बॅटिंग; आकाशात काळ्या ढगांची गर्दी</t>
+          <t>22-kg Golden Kalash Installed at Sant Dnyaneshwar Temple, Crafted by Shripad Shankar Nagarkar Jewellers Pune</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/desh-videsh/live-update-mumbai-rain-best-co-operative-soc-election-live-maharashtra-update-political-rain-update-devendra-fadnavis-ajit-pawar-eknath-shinde-uddhav-thackeray-raj-thackeray-2/913299/amp</t>
+          <t>https://www.ptinews.com/press-release/22-kg-golden-kalash-installed-at-sant-dnyaneshwar-temple-crafted-by-shripad-shankar-nagarkar-jewellers-pune/2835628</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Ahead of Civic Polls, Hitendra Thakur Backs Loyalists: ‘My Karyakarta Is With Me, They Ensure Our Party Wins</t>
+          <t>CP Radhakrishnan vs who? Why DMK’s pushing INDIA bloc for a Tamil vs Tamil contest for India’s V-P</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/maharashtra/ahead-of-civic-polls-hitendra-thakur-backs-loyalists-my-karyakarta-is-with-me-they-ensure-our-party-wins-a475/</t>
+          <t>https://theprint.in/india/cp-radhakrishnan-vs-who-why-dmks-pushing-india-bloc-for-a-tamil-vs-tamil-contest-for-indias-v-p/2723136/</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Maha CM asks agencies to be on alert mode after heavy rainfall and flash floods</t>
+          <t>'Political opinions or...': Supreme Court quashes plea challenging validity of Maharashtra Assembly polls</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/maha-cm-asks-agencies-to-be-on-alert-mode-after-heavy-rainfall-and-flash-floods/amp/</t>
+          <t>https://www.deccanherald.com/india/political-opinions-or-supreme-court-quashes-plea-challenging-validity-of-maharashtra-assembly-polls-3686244</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Mumbai rains: IMD issues red alert as downpour continues; schools, colleges &amp; Govt offices shut</t>
+          <t>Shiv Sena, NCP support Maha Governor’s nomination for Vice President</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>https://newslivetv.com/mumbai-rains-imd-issues-red-alert/</t>
+          <t>https://www.indianewsstream.com/shiv-sena-ncp-support-maha-governors-nomination-for-vice-president/</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>NCP (SP) targets Maha minister over Rs 5,000 cr scam in Navi Mumbai’s CIDCO land; demands his resignation</t>
+          <t>'Destroying constitutional institutions': Nishikant Dubey slams Rahul Gandhi as SC dismisses plea challenging 2024 Maharashtra polls</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/ncp-sp-targets-maha-minister-over-rs-5000-cr-scam-in-navi-mumbais-cidco-land-demands-his-resignation/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=ncp-sp-targets-maha-minister-over-rs-5000-cr-scam-in-navi-mumbais-cidco-land-demands-his-resignation</t>
+          <t>https://www.aninews.in/news/national/politics/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls20250819085747/</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>NDA से उपराष्ट्रपति पद के उम्मीदवार चुने जाने पर C.P Radhakrishnan को PM मोदी ने दी बधाई</t>
+          <t>Monsoon mayhem: Heavy rains flood this state, schools and colleges shut</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>https://www.primetvindia.com/pm-modi-congratulated-c-p-radhakrishnan/</t>
+          <t>https://www.patrika.com/en/national-news/monsoon-mayhem-heavy-rains-flood-this-state-schools-and-colleges-shut-19874810</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>अन्वयार्थ : राजकीयीकरणाचा उत्सवी अधर्म</t>
+          <t>PM Modi appeals for unanimous election of Radhakrishnan as vice president</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/sampadkiya/columns/dahi-handi-2025-political-grip-on-dahi-handi-festival-10-thar-human-pyramid-25-lakh-cash-prize-zws-70-5314039/</t>
+          <t>https://english.varthabharati.in/india/pm-modi-appeals-for-unanimous-election-of-radhakrishnan-as-vice-president</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>एकनाथ शिंदेंना सोलापुरात मोठा धक्का : नेत्यांने सोडली साथ !</t>
+          <t>Supreme Court dismisses plea alleging 75 lakh bogus votes in Maharashtra Assembly polls</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/big-setback-for-eknath-shinde-in-solapur-leaders-leave-support/</t>
+          <t>https://organiser.org/2025/08/19/308844/bharat/supreme-court-dismisses-plea-alleging-75-lakh-bogus-votes-in-maharashtra-assembly-polls/</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>‘शिंदेंच्या सेनेला’ दे धक्का : या आमदार बंधूंनी सोडला पक्ष</t>
+          <t>Muqabla: 'वोट चोरी' पर जीत किसकी...Rahul Gandhi या Election Commission?</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>https://politicalmaharashtra.in/a-blow-to-shindes-army-these-mla-brothers-left-the-party-97625/</t>
+          <t>https://www.indiatv.in/video/news-bulletin/muqabla-rahul-gandhi-or-the-election-commission-who-wins-the-vote-theft-battle-2025-08-19-1156831</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Historic sword of Raje Raghuji Bhonsle arrives in Mumbai to royal welcome</t>
+          <t>'संवैधानिक संस्थाओं को कर रहे हैं नष्ट...' भाजपा सांसद निशिकांत दुबे ने राहुल गांधी पर साधा निशाना</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/historic-sword-of-raje-raghuji-bhonsle-arrives-in-mumbai-to-royal-welcome/08181446</t>
+          <t>https://www.timesnowhindi.com/india/constitutional-institutions-are-being-destroyed-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls-article-152485768</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Heritage India: Iconic Sword of Maratha Commander Raghuji Raje Bhonsle Arrives in Mumbai</t>
+          <t>चुनाव आयोग की प्रेस कॉन्फ्रेंस में इन दो पत्रकारों के सवालों ने बोलती बंद कर दी, देखें वीडियो – No. 1 Indian Media News Portal</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-govt-brings-back-iconic-sword-of-maratha-commander-raghuji-raje-bhonsle-auctioned-for-rs-4715-lakh-to-mumbai-3685565</t>
+          <t>https://www.bhadas4media.com/eci-press-confrence-journalist-question/</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Nagpur Smart City projects near closure with 7 works still pending</t>
+          <t>उपराष्ट्रपतीपदाचे उमेदवार राधाकृष्णन यांना पाठिंबा द्या; देवेंद्र फडणवीस यांची शरद पवार आणि उद्धव ठाकरे यांना साद</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>https://infra.economictimes.indiatimes.com/news/urban-infrastructure/nagpur-smart-city-projects-face-delay-7-projects-pending-completion/123360909</t>
+          <t>https://marathi.freepressjournal.in/maharashtra/cp-radhakrishnan-vice-president-candidate-fadnavis-appeal-pawar-thackeray</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Seize assets of school directors in Shalarth ID scam: Bawankule</t>
+          <t>Maharashtra Politics : बीएमसी निवडणुकीच्या तोंडावर ठाकरे बंधूंच्या युतीची लिटमस टेस्ट, जागावाटप ठरलंय 'बेस्ट', फडणवीसांना थेट भिडणार</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/seize-assets-of-school-directors-in-shalarth-id-scam-bawankule/articleshow/123371134.cms</t>
+          <t>http://www.msn.com/mr-in/news/other/maharashtra-politics-%E0%A4%AC-%E0%A4%8F%E0%A4%AE%E0%A4%B8-%E0%A4%A8-%E0%A4%B5%E0%A4%A1%E0%A4%A3%E0%A5%81%E0%A4%95-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%82%E0%A4%A1-%E0%A4%B5%E0%A4%B0-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%AC%E0%A4%82%E0%A4%A7%E0%A5%82%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%9A-%E0%A4%B2-%E0%A4%9F%E0%A4%AE%E0%A4%B8-%E0%A4%9F%E0%A5%87%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%9C-%E0%A4%97-%E0%A4%B5-%E0%A4%9F%E0%A4%AA-%E0%A4%A0%E0%A4%B0%E0%A4%B2%E0%A4%82%E0%A4%AF-%E0%A4%AC%E0%A5%87%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%A8-%E0%A4%A5%E0%A5%87%E0%A4%9F-%E0%A4%AD-%E0%A4%A1%E0%A4%A3-%E0%A4%B0/ar-AA1KCf0p?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Chandrashekhar Bawankule Exclusive News Nagpur, Khabar 24</t>
+          <t>राहुल गांधी पक्ष टिकवण्यासाठी निवडणूक आयोगाचा आधार घेतात; मंत्री चंद्रशेखर बावनकुळे यांची टीका</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>https://www.khabar24.tv/2025/08/19/nagpur-district-planning-committee-meeting-chaired-by-revenue-minister-chandrashekhar-bawankule-review-of-2025-26-annual-plan/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/rahul-gandhi-takes-support-from-election-commission-to-save-party-minister-chandrashekhar-bawankule-criticizes.html</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>मराठा सेनापति रघुजी भोंसले की तलवार मुंबई लाई गई</t>
+          <t>Pravin Darekar: राज्य सहकारी संघाच्या अध्यक्षपदी आमदार प्रवीण दरेकर</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/maratha-commander-raghuji-bhosales-sword-brought-to-mumbai/856774/</t>
+          <t>https://pudhari.news/maharashtra/pune/pravin-darekar-elected-cooperative-president-maharashtra-ac90</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Revenue Minister बावनकुले का रुख</t>
+          <t>१९८७च्या काश्मीर निवडणूक गैरप्रकाराचा काँग्रेसला विसर - राजीव गांधींकडून विरोधकांच्या आरोपांकडे दुर्लक्ष</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/amp/local/maharashtra/revenue-minister-bawankules-stance-4218277</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/congress-forgets-1987-kashmir-election-malpractices-rajiv-gandhi-ignores-opposition-allegations.html</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>सिमट गई स्मार्ट सिटी योजना...7 प्रोजेक्ट अब भी अधूरे, NMC पर बढ़ रहा आर्थिक बोझ</t>
+          <t>Shivaji Sawant : शिवाजी सावंतांचा भाजपा प्रवेश निश्चित !</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/nagpur/nagpur-smart-city-scheme-7-projects-are-still-incomplete-financial-burden-on-nmc-1322638.html</t>
+          <t>https://thefocusindia.com/maharashtra-news/shivaji-sawants-admission-to-bjp-is-certain-281398/</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>यंदा पावसाचा ‘जोर’ ठराविक काही दिवसांपुरताच</t>
+          <t>'उपराष्ट्रपती'साठी महाराष्ट्राच्या राज्यपालांचे नाव; फडणवीसांचे खासदारांना आवाहन, पवार-ठाकरेंना टोला</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/heavy-rains-in-mumbai-limited-to-a-few-days-mumbai-print-news-amy-95-5313543/</t>
+          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-urges-mps-to-support-radhakrishnan-targets-uddhav-thackeray-and-sharad-pawar-035137.html</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>आरेतील परिसर पाण्याखाली, युनिट २२ मधील नाला भरुन वाहू लागला; पिकनिक पाँईट ते मरोळ रस्त्यावरील भुयारी मार्गही पाण्याखाली</t>
+          <t>‘Third Mumbai’ will open a new chapter of economic development: Maha CM</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/areas-in-aarey-submerged-due-to-heavy-rains-mumbai-print-news-amy-95-5313545/</t>
+          <t>https://www.lokmattimes.com/national/third-mumbai-will-open-a-new-chapter-of-economic-development-maha-cm/</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Lendi Dam Flood Situation: नांदेडमधील ‘लेंडी’ धरणावरील घळभरणी; ९ गावांमध्ये प्रचंड हानी!</t>
+          <t>Maharashtra News: Dy CM Eknath Shinde Launches ‘Ladki Sun – Surakshit Sun’ Campaign To Protect Women</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/nanded-lendi-dam-flood-massive-damage-in-nine-villages-css-98-5312665/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-dy-cm-eknath-shinde-launches-ladki-sun-surakshit-sun-campaign-to-protect-women-victims</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>भर पावसात शक्तिपीठ विरोधात आजऱ्यात शेतकऱ्यांचे आंदोलन; महामार्ग होऊ न देण्याचा निर्धार…</t>
+          <t>Fadnavis meets Guv Radhakrishnan, presents him book of Shivaji Maharaj's letters</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/kolhapur-ajara-farmers-march-in-heavy-rain-against-shaktipeeth-highway-ocd-94-5313564/</t>
+          <t>https://www.ptinews.com/detail/national/Fadnavis-meets-Guv-Radhakrishnan--presents-him-book-of-Shivaji-Maharaj-s-letters/2832581</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>पालकमंत्री ऍड आशिष शेलार यांनी घेतला आपात्कालीन व्यवस्थापनाचा आढावा</t>
+          <t>'Slap, but don't make video': Raj Thackeray's blunt advice to MNS workers after Marathi 'slapgate' case</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/guardian-minister-adv-ashish-shelar-reviewed-emergency-management-mumbai-print-news-amy-95-5313321/</t>
+          <t>https://www.msn.com/en-in/news/India/slap-but-dont-make-video-raj-thackerays-blunt-advice-to-mns-workers-after-marathi-slapgate-case/ar-AA1I11OF</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>दाऊद टोळीशी संबंधीत कारखान्यातून ९२ कोटींचा एमडी जप्त; मुंबई डीआरआयची कारवाई</t>
+          <t>Mumbai: Iconic Sword of Raghuji Bhonsle Arrives from London; Bike Rally Cancelled Due to Rains, Grand...</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/md-worth-rs-92-crore-seized-from-factory-linked-to-dawood-gang-mumbai-print-news-amy-95-5313544/</t>
+          <t>https://www.lokmattimes.com/mumbai/mumbai-iconic-sword-of-raghuji-bhonsle-arrives-from-london-bike-rally-cancelled-due-to-rains-grand-inauguration-tonight-a525/</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>धार्मिक भावना आणि परंपरेचा आदर करूनच कुलस्वामिनी तुळजाभवानी मंदिर जीर्णोद्धाराचे काम; सांस्कृतिक कार्यमंत्री ॲड. आशिष शेलार यांचे प्रतिपादन</t>
+          <t>How CP Radhakrishnan Broke The Taboo Around Modi And Changed The Narrative After 2002 Gujarat Episode - The</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/ashish-shelars-statement-regarding-the-renovation-work-of-kulswamini-tuljabhawani-temple-mumbai-print-news-amy-95-5313829/</t>
+          <t>https://thecommunemag.com/how-cpr-broke-the-taboo-around-modi/</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Vice Presidential Election : उपराष्ट्रपती पदासाठी विरोधकांचा उमेदवार कोण? दिल्लीत घडामोडींना वेग; राहुल गांधी काय भूमिका घेणार?</t>
+          <t>पश्चिम महाराष्ट्रात शिंदेंना भाजपचा धक्का, आमदाराच्या भावासह ४० पदाधिकाऱ्यांचा शिवसेनेला जय महाराष्ट्र!</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/desh-videsh/who-is-the-opposition-candidate-for-the-post-of-vice-president-events-in-delhi-are-gaining-momentum-what-decision-will-mallikarjun-kharge-take-gkt-96-5313155/</t>
+          <t>https://saamtv.esakal.com/maharashtra/solapur-political-news-bjp-strengthens-in-solapur-as-40-sena-leaders-join-with-shivaji-sawant-bdk97</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>युवकांसाठी मोठी खुशखबर; ‘या’ ठिकाणी आयटी पार्क उभारणार; मुख्यमंत्र्यांची घोषणा</t>
+          <t>सोलापुरात भाजपची शिंदेंच्या शिवसेनावर कुरघोडी शिवाजी सावंतांनी शिवसेना सोडली,</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/great-news-for-youth-it-park-will-be-set-up-at-this-place-chief-ministers-announcement/08181712</t>
+          <t>https://marathi.abplive.com/news/politics/solapur-shivaji-sawant-leaves-shiv-sena-and-bjp-entry-confirmed-devendra-fadnavis-bjp-attack-on-eknath-shinde-shiv-sena-in-solapur-1377928</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>रघुजी राजे यांची तलवार आणि ‘स्व’चा बोध</t>
+          <t>सोलापूरच्या राजकारणात मोठी खळबळ; तानाजी सावंत यांचा भाऊ करणार भाजपात प्रवेश</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/historic-sword-of-shrimant-raghuji-bhosle-back-in-mumbai.html</t>
+          <t>https://www.timemaharashtra.com/politics/big-stir-in-solapur-politics-tanaji-sawants-brother-to-join-bjp/129377/</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Chandrashekhar Bawankule: 'आताच मतदार याद्या तपासा', महसूल मंत्र्यांचा काँग्रेस नेत्यांना टोला</t>
+          <t>Rohit Pawar on Sanjay Shirsath: रोहित पवारांचे मंत्री संजय शिरसाटांवर भ्रष्टाचाराचे गंभीर आरोप; पहा काय म्हणाले</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/chandrashekhar-bawankule-demands-to-check-voter-lists-against-congress-allegations/articleshow/123356783.cms</t>
+          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/amp</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Nagpur Politics | भाईंनी घातला पक्ष प्रवेशाचा दुपट्टा,आता शिवसेनेचे घुमजाव</t>
+          <t>राजधानीत पावसाचा कहर! मुंबई विद्यापीठाचा परीक्षांबाबत तडकाफडकी मोठा निर्णय!</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/nagpur-politics-%E0%A4%AD-%E0%A4%88%E0%A4%82%E0%A4%A8-%E0%A4%98-%E0%A4%A4%E0%A4%B2-%E0%A4%AA%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6-%E0%A4%9A-%E0%A4%A6%E0%A5%81%E0%A4%AA%E0%A4%9F%E0%A5%8D%E0%A4%9F-%E0%A4%86%E0%A4%A4-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%9A%E0%A5%87-%E0%A4%98%E0%A5%81%E0%A4%AE%E0%A4%9C-%E0%A4%B5/ar-AA1HHJp9</t>
+          <t>https://www.tv9marathi.com/maharashtra/mumbai-university-postponed-its-all-exam-to-be-held-on-19-august-due-to-heavy-rain-marathi-news-1472932.html</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>पुण्यातील उड्डाणपूल खुले करा अन्यथा…! काँग्रेसचा इशारा</t>
+          <t>Rohit Pawar: मंत्री संजय शिरसाटांनी केला ५ हजार कोटींचा घोटाळा; आमदार रोहित पवारांच्या आरोपाने खळबळ</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/pune-congress-demand-to-open-bridges-to-avoid-traffic-jams-in-the-city-pune-print-news-css-98-5314845/</t>
+          <t>https://deshdoot.com/rohit-pawar-alleges-sanjay-shirsat-over-5000-crore-worth-land-to-bivalkar-family/</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Nagpur Accident : नागपुरातील हिट अँड रन प्रकरणाचा AI तंत्रज्ञानाच्या मदतीने उलगडा राज्यातील</t>
+          <t>Shivsena | नाराजी भोवली! शिंदे गटातून बड्या नेत्याचा राजीनामा, राजकीय वर्तुळात खळबळ</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/crime/nagpur-hit-and-run-accident-news-update-case-solved-with-the-help-of-ai-technology-first-experiment-in-the-state-driver-arrested-from-uttar-pradesh-1377914</t>
+          <t>https://www.thodkyaat.com/big-setback-for-eknath-shinde-faction-as-senior-leader-shivaji-sawant-joins-bjp-ahead-of-local-body-polls/</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Thane News: वजनदार नगरसेवक सुरक्षित, नवख्यांना धक्का; बदलापूर पालिकेच्या प्रारूप प्रभाग रचनेत मोठी उलथापालथ</t>
+          <t>राज ठाकरेंच्या भाषणात मराठीचा मुद्दा, उद्धव ठाकरेंच्या भाषणात मात्र पराभवाचीच सल; विजयी मेळाव्यावर शिंदे गटाची पहिली प्रतिक्रिया</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/thane/big-change-in-the-draft-ward-structure-of-badlapur-municipal-council-ssb-93-5314359/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B0-%E0%A4%9C-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AD-%E0%A4%B7%E0%A4%A3-%E0%A4%A4-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%9A-%E0%A4%AE%E0%A5%81%E0%A4%A6%E0%A5%8D%E0%A4%A6-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AD-%E0%A4%B7%E0%A4%A3-%E0%A4%A4-%E0%A4%AE-%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A4%B0-%E0%A4%AD%E0%A4%B5-%E0%A4%9A-%E0%A4%9A-%E0%A4%B8%E0%A4%B2-%E0%A4%B5-%E0%A4%9C%E0%A4%AF-%E0%A4%AE%E0%A5%87%E0%A4%B3-%E0%A4%B5%E0%A5%8D%E0%A4%AF-%E0%A4%B5%E0%A4%B0-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%97%E0%A4%9F-%E0%A4%9A-%E0%A4%AA%E0%A4%B9-%E0%A4%B2-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF/ar-AA1I0OWR</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>पुणे : स्थानिक आमदाराच्या हस्तक्षेपामुळे लोकमान्य नगरमधील ८०३ कुटुंबियांच्या घराचा स्वप्नभंग ?</t>
+          <t>NCP demands : राज्यात ओला दुष्काळ जाहीर करा अन्…; राष्ट्रवादी शरद पवार गटाची मागणी</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/pune-lokmanya-nagar-redevelopment-project-of-803-houses-stalled-due-to-interference-of-local-mla-pune-print-news-css-98-5312737/</t>
+          <t>https://deshdoot.com/heavy-rains-wreak-havoc-in-maharashtra-sharad-pawar-ncp-demands-wet-drought-declaration-and-farmer-relief/</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>त्र्यंबकेश्वर मंदिर प्रशासन काही बोध घेणार का ?…भाविकांना कायमच सुरक्षारक्षकांकडून त्रास</t>
+          <t>शिंदे गटाचे आमदार तानाजी सावंतांचे बंधू भाजपच्या वाटेवर</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nashik/scuffle-between-devotees-and-security-guards-at-trimbakeshwar-temple-raises-concerns-about-devotee-safety-again-sud-02-5312804/</t>
+          <t>https://pcbtoday.in/%E0%A4%B6%E0%A4%BF%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%97%E0%A4%9F%E0%A4%BE%E0%A4%9A%E0%A5%87-%E0%A4%86%E0%A4%AE%E0%A4%A6%E0%A4%BE%E0%A4%B0-%E0%A4%A4%E0%A4%BE%E0%A4%A8%E0%A4%BE%E0%A4%9C%E0%A5%80/</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Teacher Recruitment Scam: बोगस शालार्थ आयडी घोटाळ्यातील संचालकांची मालमत्ता जप्त होणार !</t>
+          <t>Supreme Industries - Apollo Tyres, Adani Ports, MRF among 8 stocks closed crossing above VWAP on August 18</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/bogus-teacher-scam-school-id-fraud-directors-property-to-be-seized-ng81</t>
+          <t>https://m.economictimes.com/markets/stocks/news/apollo-tyres-adani-ports-mrf-among-8-stocks-closed-crossing-above-vwap-on-august-18/supreme-industries/slideshow/123377083.cms</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>वरूणराजा कोपला! पिकांमध्ये पाणीच पाणी, पुढील 48 तासांत या जिल्ह्यांना पुन्हा रेड अलर्ट</t>
+          <t>MSRTC और पुलिस की पहल, गढ़चिरौली के आदिवासी गांव को मिला पहला सार्वजनिक परिवहन, ग्रामीणों ने लहराया तिरंगा</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/agriculture/18-august-maharashtra-heavy-rain-update-monsoon-2025-mumbai-red-alert-1460576.html</t>
+          <t>https://hindi.mid-day.com/news/india-news/photo/initiative-of-msrtc-and-police-tribal-village-of-gadchiroli-gets-first-public-transport-1558</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Sambhajinagar News : आता शहरवासीयांना मिळणार अतिरिक्त २६ एमएलडी पाणी</t>
+          <t>LIVE Update : मुंबईतील सर्व शाळांना उद्या सुट्टी जाहीर</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>https://pudhari.news/amp/story/maharashtra/marathwada/chhatrapati-sambhajinagar/now-city-residents-will-get-additional-26-mld-of-water-np88</t>
+          <t>https://www.mymahanagar.com/maharashtra/live-update-mumbai-rain-best-co-operative-soc-election-live-maharashtra-update-political-rain-update-devendra-fadnavis-ajit-pawar-eknath-shinde-uddhav-thackeray-raj-thackeray/913004/</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>kolhapur | सर्किट बेंचचे स्वप्न साकारले; न्यायाचे दरवाजे खुले झाले!</t>
+          <t>अमित शहा हे महाराष्ट्रातल्या गुंडांचे आणि भ्रष्टाचाऱ्यांचे दिल्लीतले सेनापती, संजय राऊत यांचा घणाघात</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>https://pudhari.news/amp/story/maharashtra/kolhapur/circuit-bench-dream-realized-doors-of-justice-now-open-ap84</t>
+          <t>https://www.saamana.com/amit-shah-is-leader-of-maharashtra-corrupt-leader-says-sanjay-raut/</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Third Mumbai in Raigad to become Maharashtra’s new economic powerhouse: CM Fadnavis</t>
+          <t>Sanjay Raut : निसाकाचा संघर्ष उफाळला, अनिल कदमांनी साकडं घातलं आता संजय राऊत मैदानात</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>https://www.daijiworld.com/index.php/news/newsDisplay?newsID=1289652</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/niphad-sugar-factory-crisis-sanjay-raut-anil-kadam-memorandum-farmers-workers-protest-nashik-gs97</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>kolhapur | सर्किट बेंचचे स्वप्न साकारले; न्यायाचे दरवाजे खुले झाले!</t>
+          <t>न्यायिक सेवा स्पर्धा परीक्षेसाठी सीईटी २०२५ जाहीर</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/circuit-bench-dream-realized-doors-of-justice-now-open-ap84</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/cet-2025-announced-for-judicial-services-competitive-examination.html</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Vice Presidential Election: सीपी राधाकृष्णन को NDA उम्मीदवार बनाने पर कांग्रेस को लगी मिर्ची, INDI गठबंधन कैंडिडेट पर खोले पत्ते</t>
+          <t>राधाकृष्णन यांना राज्यातील सर्वपक्षीय खासदारांनी पाठिंबा द्यावा</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>https://www.republicbharat.com/india/congress-angry-cp-radhakrishnan-nda-vice-presidential-candidate-opened-cards-on-indi-alliance-meeting</t>
+          <t>https://dainikekmat.com/radhakrishnan-should-be-supported-by-mps-from-all-parties-in-the-state/114185/</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>VIDEO: महाराष्ट्र में भारी बारिश के बीच एक्शन में डिप्टी CM अजित पवार, मंत्रालय के आपदा नियंत्रण</t>
+          <t>22-kg Golden Kalash Installed at Sant Dnyaneshwar Temple, Crafted by Shripad Shankar Nagarkar Jewellers Pune</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>https://hindi.latestly.com/india/maharashtra-deputy-cm-ajit-pawar-visits-mantralaya-disaster-control-room-to-review-heavy-rain-situation-2732241.html</t>
+          <t>https://www.ptinews.com/press-release/22-kg-golden-kalash-installed-at-sant-dnyaneshwar-temple,-crafted-by-shripad-shankar-nagarkar-jewellers-pune/2835628</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Those who speak of Maharashtra 'asmita' should support Radhakrishnan for VP post: Fadnavis</t>
+          <t>उप-राष्ट्रपति चुनाव: देवेंद्र फडणवीस का 'मराठी अस्मिता' वाला दांव, क्या करेंगे उद्धव ठाकरे और शरद पवार?</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/those-who-speak-of-maharashtra-'asmita'-should-support-radhakrishnan-for-vp-post:-fadnavis/2832772</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%89%E0%A4%AA-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A4%AA%E0%A4%A4-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%85%E0%A4%B8%E0%A5%8D%E0%A4%AE-%E0%A4%A4-%E0%A4%B5-%E0%A4%B2-%E0%A4%A6-%E0%A4%82%E0%A4%B5-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%94%E0%A4%B0-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0/ar-AA1KJ5pi</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>India News | 12-day Himachal Pradesh Assembly Session Opens; Opposition Seeks Adjournment on Disaster</t>
+          <t>Mumbai rains HIGHLIGHTS: Civic body declares holiday for all schools on August 19</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/india-news-12-day-himachal-pradesh-assembly-session-opens-opposition-seeks-adjournment-on-disaster-7064955.html</t>
+          <t>https://www.business-standard.com/india-news/live-news-updates-mumbai-rain-waterlogging-traffic-heavy-rain-orange-alert-125081800291_1.html</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Vice President Election: NDA उम्मीदवार सीपी राधाकृष्णन को मिल सकता है विपक्षी दलों का समर्थन, इन पार्टियों पर सबकी नजर</t>
+          <t>Demand to release list of property-holders affected due to road-widening in 5 days</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/politics/national-rajya-sabha-election-opposition-parties-may-support-nda-candidate-cp-radhakrishnan-24017212.html</t>
+          <t>https://www.lokmattimes.com/aurangabad/demand-to-release-list-of-property-holders-affected-due-to-road-widening-in-5-days/</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>मुंबई में कबूतरखानों पर विवाद, महापालिका ने नागरिकों से आपत्तियां और सुझाव मांगे</t>
+          <t>Maharashtra Politics: Rohit Pawar Alleges ₹5,000-Crore Land Scam Against Minister Sanjay Shirsat</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/maharashtra/mumbai-municipal-corporation-pigeon-shelters-public-consultation-high-court-54-803921</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-rohit-pawar-alleges-5000-crore-land-scam-against-minister-sanjay-shirsat</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Aaj Ka Rashifal, 19 Aug, 2025 : आचार्य इंदु प्रकाश जी से जानिए आज क्या कह रहे हैं आपके सितारे</t>
+          <t>Sanjay Shirsat : मंत्री शिरसाट यांच्यावर ५ हजार कोटींच्या जमीन घोटाळ्याचा आरोप</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/bhavishyawani/aaj-ka-rashifal-19-aug-2025-know-from-acharya-indu-prakash-ji-what-your-stars-are-saying-today-2025-08-19-1156865</t>
+          <t>https://pudhari.news/maharashtra/mumbai/minister-shirsat-accused-of-rs-5000-crore-land-scam-np88</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>'Vote Chori' row heats up: 'Election Commission's Presser a comedy show...,' AAP's Sanjay Singh raps EC</t>
+          <t>'ऑपरेशन लोटस वगैरे काही नाही; लवकरच ऑपरेशन टायगर दिसेल', सोलापूरच्या राजकारणात पडद्यामागे काय घडतंय?</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/politics-and-nation/vote-chori-row-heats-up-election-commissions-presser-a-comedy-show-aaps-sanjay-singh-raps-ec/videoshow/123358629.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%B2-%E0%A4%9F%E0%A4%B8-%E0%A4%B5%E0%A4%97%E0%A5%88%E0%A4%B0%E0%A5%87-%E0%A4%95-%E0%A4%B9-%E0%A4%A8-%E0%A4%B9-%E0%A4%B2%E0%A4%B5%E0%A4%95%E0%A4%B0%E0%A4%9A-%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%9F-%E0%A4%AF%E0%A4%97%E0%A4%B0-%E0%A4%A6-%E0%A4%B8%E0%A5%87%E0%A4%B2-%E0%A4%B8-%E0%A4%B2-%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B0-%E0%A4%9C%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A4-%E0%A4%AA%E0%A4%A1%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%AE-%E0%A4%97%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%98%E0%A4%A1%E0%A4%A4%E0%A4%82%E0%A4%AF/ar-AA1KKoUc</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>PM Modi appeals for unanimous election of Radhakrishnan as vice president</t>
+          <t>Mumbai Rain Mayhem: City Comes To Standstill As Life Thrown Out Of Gear; MonoRail Gets Stuck</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>https://english.varthabharati.in/india/pm-modi-appeals-for-unanimous-election-of-radhakrishnan-as-vice-president</t>
+          <t>https://www.etvbharat.com/en/!state/mumbai-rains-update-august-19-govt-semi-govt-offices-shut-bmc-urges-wfh-for-pvt-employees-enn25081901231</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>'Destroying constitutional institutions': Nishikant Dubey slams Rahul Gandhi as SC dismisses plea challenging 2024 Maharashtra polls</t>
+          <t>To collect outstanding transportation fines, the Maha government is planning an amnesty scheme</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/politics/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls20250819085747</t>
+          <t>https://assamtribune.com/national/to-collect-outstanding-transportation-fines-the-mahagovernment-is-planning-an-amnesty-scheme-1588536</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>22-kg Golden Kalash Installed at Sant Dnyaneshwar Temple, Crafted by Shripad Shankar Nagarkar Jewellers Pune</t>
+          <t>‘Third Mumbai’ will open a new chapter of economic development: Maha CM</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/press-release/22-kg-golden-kalash-installed-at-sant-dnyaneshwar-temple-crafted-by-shripad-shankar-nagarkar-jewellers-pune/2835628</t>
+          <t>https://www.sakshipost.com/news/third-mumbai-will-open-new-chapter-economic-development-maha-cm-441953</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Vice President Election: Uddhav Thackeray यांच्या सेनेची भूमिका काय? Sanjay Raut स्पष्टच बोलले N18S</t>
+          <t>Shortage of teachers hits rollout of NEP in govt, aided Maha colleges</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/vice-president-election-uddhav-thackeray-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%9A-%E0%A4%AD%E0%A5%82%E0%A4%AE-%E0%A4%95-%E0%A4%95-%E0%A4%AF-sanjay-raut-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A4%9A-%E0%A4%AC-%E0%A4%B2%E0%A4%B2%E0%A5%87-n18s/vi-AA1KIbM2</t>
+          <t>https://www.pressreader.com/india/hindustan-times-st-jaipur/20250819/281681145971378</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>BEST Election News: मनसेच्या Sandeep Deshpande यांचा सत्ताधाऱ्यांवर गंभीर आरोप N18S</t>
+          <t>Maha govt waives Stamp Duty worth Rs 38.99 lakh for Tata Cancer Hospital in Raigad (Ld)</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/best-election-news-%E0%A4%AE%E0%A4%A8%E0%A4%B8%E0%A5%87%E0%A4%9A%E0%A5%8D%E0%A4%AF-sandeep-deshpande-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%B8%E0%A4%A4%E0%A5%8D%E0%A4%A4-%E0%A4%A7-%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B5%E0%A4%B0-%E0%A4%97%E0%A4%82%E0%A4%AD-%E0%A4%B0-%E0%A4%86%E0%A4%B0-%E0%A4%AA-n18s/vi-AA1KIfwO</t>
+          <t>https://www.thehawk.in/news/india/maha-govt-waives-stamp-duty-worth-rs-3899-lakh-for-tata-cancer-hospital-in-raigad-ld</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>BEST Election News: Uddhav Thackeray - Raj Thackeray यांच्या कसोटीचा दिवस,बाजी मारणार?</t>
+          <t>कैसी होगी तीसरी मुंबई, कितनी बड़ी और कहां बन रही, सुविधाओं से लेकर प्लानिंग तक, CM फडणवीस ने सब बताया</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/best-election-news-uddhav-thackeray-raj-thackeray-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%95%E0%A4%B8-%E0%A4%9F-%E0%A4%9A-%E0%A4%A6-%E0%A4%B5%E0%A4%B8%E0%A4%AC-%E0%A4%9C-%E0%A4%AE-%E0%A4%B0%E0%A4%A3-%E0%A4%B0/vi-AA1KLt69</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%95%E0%A5%88%E0%A4%B8-%E0%A4%B9-%E0%A4%97-%E0%A4%A4-%E0%A4%B8%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%95-%E0%A4%A4%E0%A4%A8-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%94%E0%A4%B0-%E0%A4%95%E0%A4%B9-%E0%A4%82-%E0%A4%AC%E0%A4%A8-%E0%A4%B0%E0%A4%B9-%E0%A4%B8%E0%A5%81%E0%A4%B5-%E0%A4%A7-%E0%A4%93%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AA%E0%A5%8D%E0%A4%B2-%E0%A4%A8-%E0%A4%82%E0%A4%97-%E0%A4%A4%E0%A4%95-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%AF/ar-AA1KLMl6?ocid=finance-verthp-feeds</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Road Construction: परभणीतील गंगाखेड तालुक्यात ग्रामस्थांचे आगळेवेगळे आंदोलन! - देशोन्नती</t>
+          <t>महाराष्ट्र में भारी बारिश से सात लोगों की मौत, 200 ग्रामीण फंसे</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/road-constructionvillagers-stage-protest-gangakhed-parbhani/</t>
+          <t>https://hindi.theprint.in/india/seven-people-died-due-to-heavy-rains-in-maharashtra-200-villagers-stranded/856903/?amp</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>खरगे, स्टॉलिन, नवीन पटनायक... उपराष्ट्रपति चुनाव से पहले राजनाथ सिंह को बीजेपी ने दी खास जिम्मेदारी</t>
+          <t>Maharashtra: मंत्री शंभूराज देसाई को मिला बचपन वाला वही सरकारी बंगला, मां के जन्मदिन पर किया भावुक गृहप्रवेश</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/india/vice-president-election-defence-minister-rajnath-singh-reaches-out-to-dmk-tmc-bjd-for-consensus-for-cp-radhakrishnan/articleshow/123375990.cms</t>
+          <t>http://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%B6%E0%A4%82%E0%A4%AD%E0%A5%82%E0%A4%B0-%E0%A4%9C-%E0%A4%A6%E0%A5%87%E0%A4%B8-%E0%A4%88-%E0%A4%95-%E0%A4%AE-%E0%A4%B2-%E0%A4%AC%E0%A4%9A%E0%A4%AA%E0%A4%A8-%E0%A4%B5-%E0%A4%B2-%E0%A4%B5%E0%A4%B9-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%AC%E0%A4%82%E0%A4%97%E0%A4%B2-%E0%A4%AE-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%9C%E0%A4%A8%E0%A5%8D%E0%A4%AE%E0%A4%A6-%E0%A4%A8-%E0%A4%AA%E0%A4%B0-%E0%A4%95-%E0%A4%AF-%E0%A4%AD-%E0%A4%B5%E0%A5%81%E0%A4%95-%E0%A4%97%E0%A5%83%E0%A4%B9%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6/ar-AA1JRinD?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>'संवैधानिक संस्थाओं को कर रहे हैं नष्ट...' भाजपा सांसद निशिकांत दुबे ने राहुल गांधी पर साधा निशाना</t>
+          <t>महाराष्ट्र के बीड, लातूर और नांदेड में भारी बारिश से बाढ़ की स्थिति गंभीर, NDRF और सेना तैनात</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>https://www.timesnowhindi.com/india/constitutional-institutions-are-being-destroyed-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls-article-152485768</t>
+          <t>https://navbharattimes.indiatimes.com/state/maharashtra/pune/heavy-rains-in-maharashtra-flood-havoc-in-beed-latur-and-nanded-ndrf-and-army-deployed/articleshow/123370629.cms</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>चुनाव आयोग की प्रेस कॉन्फ्रेंस में इन दो पत्रकारों के सवालों ने बोलती बंद कर दी, देखें वीडियो – No. 1 Indian Media News Portal</t>
+          <t>महाराष्ट्र में मानसून का कहर: मुखेड तालुका में बादल फटने जैसी घटना, 200 से ज्यादा गांवों में बाढ़</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>https://www.bhadas4media.com/eci-press-confrence-journalist-question/</t>
+          <t>https://hindi.dynamitenews.com/maharashtra/cloudburst-in-mukhed-taluka-in-maharashtra-flood-in-more-than-200-villages</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>शिवसेना एकनाथ शिंदे गुट को बड़ा झटका, शिवाजी सावंत भाजपा में होगें शामिल | Maharastra - Paliwalwani - Latest Hindi News</t>
+          <t>महाराष्ट्र में माफ हो सकते हैं पुराने ट्रैफिक चालान, माफी योजना लाने की तैयारी में सरकार</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>https://paliwalwani.com/maharastra/shiv-sena-eknath-shinde-faction-is-a-big-shock-shivaji-sawant-will-be-involved-in-bjp</t>
+          <t>https://navbharattimes.indiatimes.com/government-schemes/others/maharashtra-government-is-set-to-roll-out-an-amnesty-scheme-for-one-time-settlement-of-pending-traffic-challan/articleshow/123367444.cms</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Maharashtra Politics : बीएमसी निवडणुकीच्या तोंडावर ठाकरे बंधूंच्या युतीची लिटमस टेस्ट, जागावाटप ठरलंय 'बेस्ट', फडणवीसांना थेट भिडणार</t>
+          <t>Maharashtra Rains: महाराष्ट्र में बाढ़ से हालात गंभीर, मराठवाड़ा में NDRF और सेना तैनात, सरकार की क्या है तैयारी?</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>http://www.msn.com/mr-in/news/other/maharashtra-politics-%E0%A4%AC-%E0%A4%8F%E0%A4%AE%E0%A4%B8-%E0%A4%A8-%E0%A4%B5%E0%A4%A1%E0%A4%A3%E0%A5%81%E0%A4%95-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%82%E0%A4%A1-%E0%A4%B5%E0%A4%B0-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%AC%E0%A4%82%E0%A4%A7%E0%A5%82%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%9A-%E0%A4%B2-%E0%A4%9F%E0%A4%AE%E0%A4%B8-%E0%A4%9F%E0%A5%87%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%9C-%E0%A4%97-%E0%A4%B5-%E0%A4%9F%E0%A4%AA-%E0%A4%A0%E0%A4%B0%E0%A4%B2%E0%A4%82%E0%A4%AF-%E0%A4%AC%E0%A5%87%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%A8-%E0%A4%A5%E0%A5%87%E0%A4%9F-%E0%A4%AD-%E0%A4%A1%E0%A4%A3-%E0%A4%B0/ar-AA1KCf0p?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/mumbai-heavy-rain-maharashtra-flood-situation-serious-ndrf-and-indian-army-deployed-in-marathwada/articleshow/123370824.cms</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>राहुल गांधी पक्ष टिकवण्यासाठी निवडणूक आयोगाचा आधार घेतात; मंत्री चंद्रशेखर बावनकुळे यांची टीका</t>
+          <t>मराठा सेनापति रघुजी भोंसले की तलवार मुंबई पहुंची</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/rahul-gandhi-takes-support-from-election-commission-to-save-party-minister-chandrashekhar-bawankule-criticizes.html</t>
+          <t>https://www.livehindustan.com/ncr/new-delhi/story-historic-sword-of-maratha-general-raghuji-bhosale-i-repatriated-to-mumbai-201755537654676.html</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>१९८७च्या काश्मीर निवडणूक गैरप्रकाराचा काँग्रेसला विसर - राजीव गांधींकडून विरोधकांच्या आरोपांकडे दुर्लक्ष</t>
+          <t>Third Mumbai महानगर क्षेत्राच्या विकासाचा नवा अध्याय असेल; मुख्यमंत्र्यांनी सांगितलं कशी असेल ‘तिसरी मुंबई’ Third Mumbai in Raigad district to boost metropolitan region development said Devendra Fadnavis</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/congress-forgets-1987-kashmir-election-malpractices-rajiv-gandhi-ignores-opposition-allegations.html</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/third-mumbai-in-raigad-district-to-boost-metropolitan-region-development-said-devendra-fadnavis-89724</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Chandrashekhar Bawankule : आताच मतदार याद्या तपासून घ्या.! चंद्रशेखर बावनकुळेंकडून कॉंग्रेसला चिमटा</t>
+          <t>राज्यातील पूरस्थितीवर सरकारचे लक्ष, मदत कार्य सुरू – बावनकुळे</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/chandrashekhar-bawankule-check-the-voter-lists-now-chandrashekhar-bawankules-pinch-to-congress/</t>
+          <t>https://www.loksatta.com/nagpur/governments-attention-on-flood-situation-in-the-state-information-from-chandrashekhar-bawankule-amy-95-5313292/</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Pravin Darekar: राज्य सहकारी संघाच्या अध्यक्षपदी आमदार प्रवीण दरेकर</t>
+          <t>‘पीएम आवास’च्या तीस लाख घरांना मोफत वीज; राज्य सरकार देणार ५० हजारांचे अनुदान: मुख्यमंत्री</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/pravin-darekar-elected-cooperative-president-maharashtra-ac90</t>
+          <t>https://www.lokmat.com/maharashtra/free-electricity-to-three-lakh-houses-of-pm-awas-yojana-state-government-will-provide-subsidy-of-rs-50-thousand-chief-minister-a-a747/</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>पहले हाईकोर्ट और अब सुप्रीम कोर्ट... महाराष्ट्र चुनाव में गड़बड़ी वाली याचिका खारिज, बताया 'समय की बर्बादी'...</t>
+          <t>Maharashtra Government: शेतकऱ्यांना मिळणार गुड न्यूज: बळीराजासाठी सरकार मोठा निर्णय घेण्याच्या तयारीत</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/nation/supreme-court-reject-petition-on-maharashtra-assembly-elections-eci-reaction-9523295.html</t>
+          <t>https://saamtv.esakal.com/maharashtra/sanjay-rathod-big-statement-on-loan-waiver-maharashtra-farmers-get-loan-waiver-minister-give-hint-in-award-ceremony-program-yavatmal-pusad-bbj88</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>३१ खासदार निवडून आले तेव्हा मतदारयाद्या बरोबर होत्या का ?</t>
+          <t>Crop Loss: महाराष्‍ट्र में बारिश ने किया किसानों को बर्बाद, विदर्भ से लेकर मराठवाड़ा तक फसलें चौपट</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/nagpur/were-the-voter-lists-correct-when-31-mps-were-elected-a-a1000/</t>
+          <t>https://www.kisantak.in/crops/story/heavy-rains-in-maharashtra-cause-huge-damage-to-farmers-after-crop-loss-and-land-submerged-in-water-1263471-2025-08-19</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>बेस्टच्या पतपेढीची निवडणूक ८३ टक्के मतदान, ठाकरे बंधू आणि भाजपसाठी प्रतिष्ठेची लढाई, आज निकाल</t>
+          <t>कोल्हापुर में शुरू हुई बॉम्बे हाईकोर्ट की नई खंडपीठ, सीजेआई बोले– महाराष्ट्र न्यायिक ढांचे में आगे</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/mumbai-best-bus-credit-society-polls-result-today-bjp-vs-thackeray-brothers-mumbai-print-news-css-98-5314138/</t>
+          <t>https://mpbreakingnews.in/maharashtra/bombay-high-court-kolhapur-bench-cji-b-r-gavai-maharashtra-government-54-803927</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>हवामानाचा अंदाज: आजही पावसाचा कहर? मुंबई, पुण्यासह 7 जिल्ह्यांना रेड अलर्ट; गडचिरोलीसह 4 जिल्ह्यांना यलो अलर्ट</t>
+          <t>श्रीमती प्रज्ञा वाळकेंचा भ्रष्टाचारामध्ये उच्चांक ; सरकारविरोधी चळवळीतीही सक्रिय सहभाग ?</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/national-news/maharashtra-weather-red-alert-mumbai-pune-7-districts-281414/amp/</t>
+          <t>https://lokmanthan.com/mrs-pragya-walkens-high-score-in-corruption-active-participation-in-anti-government-movement/</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Shivaji Sawant : शिवाजी सावंतांचा भाजपा प्रवेश निश्चित !</t>
+          <t>देशभर में बारिश का कहर: मुंबई-बेहद जाम, दिल्ली में यमुना उफान पर, स्कूल-कॉलेज बंद</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/shivaji-sawants-admission-to-bjp-is-certain-281398/</t>
+          <t>https://dainikdehat.com/india/rain-wreaks-havoc-across-the-country-mumbai-is-jam-packed-yamuna-is-in-spate-in-delhi-schools-and-colleges-are-closed/</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>'उपराष्ट्रपती'साठी महाराष्ट्राच्या राज्यपालांचे नाव; फडणवीसांचे खासदारांना आवाहन, पवार-ठाकरेंना टोला</t>
+          <t>इस दिन खाते में आ सकती है माझी लड़की बहिन योजना की अगली किस्त, इन महिलाओं को नहीं मिलेंगे पैसे</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-urges-mps-to-support-radhakrishnan-targets-uddhav-thackeray-and-sharad-pawar-035137.html</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%87%E0%A4%B8-%E0%A4%A6-%E0%A4%A8-%E0%A4%96-%E0%A4%A4%E0%A5%87-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%86-%E0%A4%B8%E0%A4%95%E0%A4%A4-%E0%A4%B9%E0%A5%88-%E0%A4%AE-%E0%A4%9D-%E0%A4%B2%E0%A4%A1%E0%A4%BC%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A8-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%95-%E0%A4%85%E0%A4%97%E0%A4%B2-%E0%A4%95-%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%87%E0%A4%A8-%E0%A4%AE%E0%A4%B9-%E0%A4%B2-%E0%A4%93%E0%A4%82-%E0%A4%95-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AE-%E0%A4%B2%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AA%E0%A5%88%E0%A4%B8%E0%A5%87/ar-AA1vsznB?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>महाराष्ट्रातील शेतकऱ्यांना मोठा दिलासा, मुख्यमंत्री फडणवीस लवकरच कर्जमाफीची घोषणा करणार</t>
+          <t>तिसरी मुंबई म्हणजे आर्थिक विकासाचा नवा अध्याय असेल! मुख्यमंत्री देवेंद्र फडणवीस यांचे प्रतिपादन</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/big-relief-for-farmers-in-maharashtra-chief-minister-fadnavis-will-soon-announce-loan-waiver-125081900014_1.html</t>
+          <t>https://marathi.freepressjournal.in/mumbai/mumbai-connectivity-coastal-road-atal-setu-worli-shivdi-link</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>एनडीएकडून महाराष्ट्राचे राज्यपाल राधाकृष्णन उमेदवार; विरोधकांचे ‘डीएमके कार्ड’</t>
+          <t>Mumbai Chawl Redevelopment | चाळ झाली आधुनिक वस्ती</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/nation/maharashtra-governor-radhakrishnan-is-the-candidate-from-nda-oppositions-dmk-card/</t>
+          <t>https://pudhari.news/sampadakiy/mumbai-chawl-redevelopment-displaced-workers-problem-sp96</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Tiruchi Siva : इंडिया आघाडी उपराष्ट्रपती पदाची निवडणूक लढणार? नेमकं कोणाचं नावं आघाडीवर?</t>
+          <t>Heavy Rains Batter Mumbai: Red Alert Issued, Schools and Colleges Closed on August 19 in Thane and...</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/tiruchi-siva-will-india-aghadi-contest-the-vice-presidential-election-whose-name-is-in-the-lead/129400/</t>
+          <t>https://www.thehansindia.com/news/national/heavy-rains-batter-mumbai-red-alert-issued-schools-and-colleges-closed-on-august-19-in-thane-and-palghar-998357</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Maharashtra News: Dy CM Eknath Shinde Launches ‘Ladki Sun – Surakshit Sun’ Campaign To Protect Women</t>
+          <t>Mumbai Rains: Are Private and Public offices shut today? BMC issues statement, says...</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-dy-cm-eknath-shinde-launches-ladki-sun-surakshit-sun-campaign-to-protect-women-victims</t>
+          <t>https://www.india.com/news/india/mumbai-rains-are-private-and-public-offices-shut-today-bmc-work-from-home-schools-colleges-devendra-fadnavis-markets-8019561/</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>LIVE: Rahul Gandhi &amp; Tejashwi Yadav at Voter Adhikar Rally, Nawada Bihar</t>
+          <t>Surya Roshni to invest Rs 25 cr for biz expansion</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/live-rahul-gandhi-tejashwi-yadav-at-voter-adhikar-rally-nawada-bihar/videoshow/123379809.cms</t>
+          <t>https://www.theweek.in/wire-updates/business/2025/08/18/dcm62-biz-briefs-3.html</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>‘Third Mumbai’ will open a new chapter of economic development: Maha CM</t>
+          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/third-mumbai-will-open-a-new-chapter-of-economic-development-maha-cm/</t>
+          <t>https://www.newsdrum.in/business/third-mumbai-to-boost-metropolitan-region-development-fadnavis-9674858</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>ट्रंप और ज़ेलेंस्की की मुलाक़ात, सीज़फ़ायर को लेकर दोनों नेताओं ने क्या कहा?</t>
+          <t>Mumbai got 177mm rain in 6-8 hour period, says CM; all agencies asked to remain alert</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/hindi/live/c23pr7x3kmgt</t>
+          <t>https://www.newsdrum.in/national/mumbai-got-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert-9673094</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>सोलापूरच्या राजकारणात मोठी खळबळ; तानाजी सावंत यांचा भाऊ करणार भाजपात प्रवेश</t>
+          <t>803 Families Stranded as Lokmanya Nagar Redevelopment Hits Political Roadblock</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/big-stir-in-solapur-politics-tanaji-sawants-brother-to-join-bjp/129377/</t>
+          <t>https://punemirror.com/city/civic/803-families-stranded-as-lokmanya-nagar-redevelopment-hits-political-roadblock/</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>'Slap, but don't make video': Raj Thackeray's blunt advice to MNS workers after Marathi 'slapgate' case</t>
+          <t>How much rain did Mumbai receive on Monday? Check area-wise list</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/slap-but-dont-make-video-raj-thackerays-blunt-advice-to-mns-workers-after-marathi-slapgate-case/ar-AA1I11OF</t>
+          <t>https://indianexpress.com/article/cities/mumbai/how-much-rain-did-mumbai-areas-receive-on-monday-check-list-bandra-juhu-chembur/</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Mumbai: Iconic Sword of Raghuji Bhonsle Arrives from London; Bike Rally Cancelled Due to Rains, Grand...</t>
+          <t>NCP (SP) targets Maha minister over Rs 5,000 cr scam in Navi Mumbai’s CIDCO land; demands his resignation</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/mumbai/mumbai-iconic-sword-of-raghuji-bhonsle-arrives-from-london-bike-rally-cancelled-due-to-rains-grand-inauguration-tonight-a525/</t>
+          <t>https://www.socialnews.xyz/2025/08/18/ncp-sp-targets-maha-minister-over-rs-5000-cr-scam-in-navi-mumbais-cidco-land-demands-his-resignation/</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>MBBS admission quota in unaided colleges cut by 50%, students erupt</t>
+          <t>Maha govt plans amnesty scheme to recover pending transport fines</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/mbbs-admission-quota-in-unaided-colleges-cut-by-50-students-erupt/articleshow/123372541.cms</t>
+          <t>https://www.socialnews.xyz/2025/08/18/maha-govt-plans-amnesty-scheme-to-recover-pending-transport-fines/</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>महाराष्ट्र के बीड, लातूर और नांदेड में भारी बारिश से बाढ़ की स्थिति गंभीर, NDRF और सेना तैनात</t>
+          <t>CM to join Kawad yatra, TV center chowk shut for 5 hours</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/maharashtra/pune/heavy-rains-in-maharashtra-flood-havoc-in-beed-latur-and-nanded-ndrf-and-army-deployed/articleshow/123370629.cms</t>
+          <t>https://www.lokmattimes.com/aurangabad/cm-to-join-kawad-yatra-tv-center-chowk-shut-for-5-hours/</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>राज्यात अतिवृष्टीच्या पार्श्वभूमीवर मुख्यमंत्री देवेंद्र फडणवीस यांचे सर्व यंत्रणांना सतर्कतेचे निर्देश</t>
+          <t>चुनाव के बाद होगा महामंडलों का वितरण, महायुति के इच्छुक नेताओं पर प्रदर्शन का दबाव</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176121/</t>
+          <t>https://navbharatlive.com/maharashtra/nagpur/distribution-of-maha-mandals-will-happen-after-the-elections-pressure-of-demonstration-on-the-aspiring-leaders-of-mahayuti-1322474.html</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>राजधानीत पावसाचा कहर! मुंबई विद्यापीठाचा परीक्षांबाबत तडकाफडकी मोठा निर्णय!</t>
+          <t>राज्यात ओला दुष्काळ जाहीर करा, विशेष अधिवेशन बोलवा मुसळधार पावसानंतर शरद पवारांच्या</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/mumbai-university-postponed-its-all-exam-to-be-held-on-19-august-due-to-heavy-rain-marathi-news-1472932.html</t>
+          <t>https://marathi.abplive.com/news/politics/sharad-pawar-ncp-demands-after-heavy-rains-declaring-a-wet-drought-in-the-state-calling-a-special-session-shashikant-shinde-1377947</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Maharashtra Rain Update : शाळांना सुट्टी आहे की नाही? नेमका निर्णय काय? फडणवीसांनीच संभ्रम संपवला;...</t>
+          <t>सिडको जमिन वाटप प्रकरणावरून राजकारण तापले; पवारांचा शिरसाठांवर घणाघाती हल्ला</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/photo-gallery/maharashtra-rain-update-mumbai-rain-school-and-college-holiday-decision-will-be-taken-after-weather-forecast-1472649.html</t>
+          <t>https://civicmirror.in/maharashtra/politics-heats-up-over-cidco-land-allocation-issue-pawar-attacks-shirsath/</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Maharashtra Rain Update : आदेश आला! पावसामुळे असणार शाळा बंद; कुठे-कुठे सुट्टी जाहीर? जाणून घ्या</t>
+          <t>Rohit Pawar on Sanjay Shirsath: रोहित पवारांचे मंत्री संजय शिरसाटांवर भ्रष्टाचाराचे गंभीर आरोप; पहा काय म्हणाले</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/maharashtra-rain-update-government-declared-school-holiday-for-mumbai-thane-kalyan-dombivli-palghar-district-1472791.html/amp</t>
+          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>पावसाचा रुद्रावतार! मुंबईच्या रस्त्यांवर पाणीच पाणी; वाहतूककोंडीमुळे प्रवासी त्रस्त, रेल्वे वाहतुकीचे तीनतेरा</t>
+          <t>'Destroying constitutional institutions': Nishikant Dubey slams Rahul Gandhi as SC dismisses plea challenging 2024 Maharashtra polls</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/mumbai/mumbai-rains-waterlogging-traffic-disruption</t>
+          <t>https://www.bignewsnetwork.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Maharashtra Rain Update : मोठा निर्णय! अतिवृष्टीमुळे विद्यार्थ्यांना सुट्टी जाहीर; 'या' जिल्ह्यांमध्ये शाळा राहणार बंद, जाणून घ्या</t>
+          <t>Mumbai Rain LIVE Updates: मुंबईत सखल भागात साचलेल्या पाण्याचा निचरा</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/due-to-heavy-rain-government-declared-holiday-for-students-in-mumbai-thane-kalyan-dombivli-palghar-district/40074</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/mumbai-rain-live-updates-18-august-imd-red-alert-in-mumbai-weather-waterlogging-traffic-jam-local-train-train-latest-updates-in-marathi-933169</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Rohit Pawar: मंत्री संजय शिरसाटांनी केला ५ हजार कोटींचा घोटाळा; आमदार रोहित पवारांच्या आरोपाने खळबळ</t>
+          <t>मुंबई में कबूतरखानों पर विवाद, महापालिका ने नागरिकों से आपत्तियां और सुझाव मांगे</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/rohit-pawar-alleges-sanjay-shirsat-over-5000-crore-worth-land-to-bivalkar-family/</t>
+          <t>https://mpbreakingnews.in/maharashtra/mumbai-municipal-corporation-pigeon-shelters-public-consultation-high-court-54-803921</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Uttarakhand : राज्यातील मदरश्यांना मोठा धक्का; अल्पसंख्याकांच्या शैक्षणिक संस्थांना मान्यता देणारे देशातील पहिले राज्य बनणार</t>
+          <t>Maharashtra govt plans amnesty scheme to recover pending transport fines</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/uttarakhand-cm-dhamis-cabinet-decided-to-establish-closed-madarsa-system/</t>
+          <t>https://auto.economictimes.indiatimes.com/amp/news/industry/maharashtras-new-amnesty-scheme-settle-transport-fines-and-save-big/123364146</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Shivsena | नाराजी भोवली! शिंदे गटातून बड्या नेत्याचा राजीनामा, राजकीय वर्तुळात खळबळ</t>
+          <t>Mah plans amnestyscheme to recoverpending transport fines</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>https://www.thodkyaat.com/big-setback-for-eknath-shinde-faction-as-senior-leader-shivaji-sawant-joins-bjp-ahead-of-local-body-polls/</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/19/mah-plans-amnesty-scheme-to-recover-pending-transport-fines.html</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Rohit Pawar on Sanjay Shirsath: रोहित पवारांचे मंत्री संजय शिरसाटांवर भ्रष्टाचाराचे गंभीर आरोप; पहा काय म्हणाले</t>
+          <t>CSMC Commissions New 26 MLD Water Scheme, Reduces Supply Gap For Residents</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/</t>
+          <t>https://www.freepressjournal.in/pune/csmc-commissions-new-26-mld-water-scheme-reduces-supply-gap-for-residents</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>शिंदे गटाचे आमदार तानाजी सावंतांचे बंधू भाजपच्या वाटेवर</t>
+          <t>Pratap Sarnaik : राज्यातील वाहनांवर तब्‍बल 2500 कोटींचा दंड; सरकार एकरकमी परतफेडीची अभय योजना आणणार</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>https://pcbtoday.in/%E0%A4%B6%E0%A4%BF%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%97%E0%A4%9F%E0%A4%BE%E0%A4%9A%E0%A5%87-%E0%A4%86%E0%A4%AE%E0%A4%A6%E0%A4%BE%E0%A4%B0-%E0%A4%A4%E0%A4%BE%E0%A4%A8%E0%A4%BE%E0%A4%9C%E0%A5%80/</t>
+          <t>https://www.dainikprabhat.com/fines-of-around-rs-2500-crore-on-vehicles-in-the-state-government-to-introduce-a-lump-sum-repayment-scheme/</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Ekanath Shinde Shivsena : शिंदे गटाला धक्का; आमदाराचा भाऊ व 40 पदाधिकाऱ्यांचा पक्षप्रवेश</t>
+          <t>Maratha general Raghuji Bhonsle's sword brought to Mumbai</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>https://www.lokshahi.com/news/mla-tanaji-sawants-brother-shivaji-sawant-has-decided-to-quit-the-group-and-join-the-bjp</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom14-mh-maratha-sword.html</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>NCP demands : राज्यात ओला दुष्काळ जाहीर करा अन्…; राष्ट्रवादी शरद पवार गटाची मागणी</t>
+          <t>Cases from 6 districts to be heard | ‘A dream comes true after 40-45 years of struggle’: CJI inaugurates HC bench in Kolhapur</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/heavy-rains-wreak-havoc-in-maharashtra-sharad-pawar-ncp-demands-wet-drought-declaration-and-farmer-relief/</t>
+          <t>https://indianexpress.com/article/cities/pune/cases-dream-struggle-cji-inaugurates-hc-bench-kolhapur-10195928/</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>राज ठाकरेंच्या भाषणात मराठीचा मुद्दा, उद्धव ठाकरेंच्या भाषणात मात्र पराभवाचीच सल; विजयी मेळाव्यावर शिंदे गटाची पहिली प्रतिक्रिया</t>
+          <t>Maratha commander Raghuji Bhonsle's sword brought to Mumbai!!</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B0-%E0%A4%9C-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AD-%E0%A4%B7%E0%A4%A3-%E0%A4%A4-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%9A-%E0%A4%AE%E0%A5%81%E0%A4%A6%E0%A5%8D%E0%A4%A6-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AD-%E0%A4%B7%E0%A4%A3-%E0%A4%A4-%E0%A4%AE-%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A4%B0-%E0%A4%AD%E0%A4%B5-%E0%A4%9A-%E0%A4%9A-%E0%A4%B8%E0%A4%B2-%E0%A4%B5-%E0%A4%9C%E0%A4%AF-%E0%A4%AE%E0%A5%87%E0%A4%B3-%E0%A4%B5%E0%A5%8D%E0%A4%AF-%E0%A4%B5%E0%A4%B0-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%97%E0%A4%9F-%E0%A4%9A-%E0%A4%AA%E0%A4%B9-%E0%A4%B2-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF/ar-AA1I0OWR</t>
+          <t>https://www.indiaherald.com/Breaking/Read/994842382/Maratha-commander-Raghuji-Bhonsles-sword-brought-to-Mumbai</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Shashikant Shinde on Heavy Rain: राज्यात अतिवृष्टीमुळे ओला दुष्काळ जाहीर करण्याची मागणी तीव्र</t>
+          <t>मराठा सेनापति रघुजी भोंसले की तलवार मुंबई लाई गई</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/demand-to-declare-a-wet-drought-due-to-heavy-rains-in-the-state-is-strong/129359/</t>
+          <t>https://hindi.theprint.in/india/maratha-commander-raghuji-bhosales-sword-brought-to-mumbai/856774/</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>MSRTC और पुलिस की पहल, गढ़चिरौली के आदिवासी गांव को मिला पहला सार्वजनिक परिवहन, ग्रामीणों ने लहराया तिरंगा</t>
+          <t>Revenue Minister बावनकुले का रुख</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/news/india-news/photo/initiative-of-msrtc-and-police-tribal-village-of-gadchiroli-gets-first-public-transport-1558</t>
+          <t>https://jantaserishta.com/amp/local/maharashtra/revenue-minister-bawankules-stance-4218277</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>महाराष्ट्रातील खासदारांनी राधाकृष्णन यांना समर्थन द्यावे: मुख्यमंत्री देवेंद्र फडणवीसांचे आवाहन; ठाकरे गट अ...</t>
+          <t>राज्य को बाढ़ आपदा घोषित करो… विशेष अधिवेशन बुलाओ… एनसीपी प्रदेश अध्यक्ष ने की सीएम से मांग</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/c-p-radhakrishnan-vice-president-candidate-fadnavis-urges-support-135703533.html</t>
+          <t>https://www.hindisaamana.com/declare-the-state-a-flood-disaster-call-a-special-session-ncp-state-president-made-a-demand-to-the-cm/</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Marathi News Headlines | 7 AM | News18 Lokmat | 19 Aug 2025 | Maharashtra Rain Update | Mumbai Local</t>
+          <t>Shashikant Shinde on Heavy Rain: राज्यात अतिवृष्टीमुळे ओला दुष्काळ जाहीर करण्याची मागणी तीव्र</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/marathi-news-headlines-7-am-news18-lokmat-19-aug-2025-maharashtra-rain-update-mumbai-local/vi-AA1KLIwf?ocid=hpmsn</t>
+          <t>https://www.timemaharashtra.com/maharashtra/demand-to-declare-a-wet-drought-due-to-heavy-rains-in-the-state-is-strong/129359/</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Bade Mudde: Rahul Gandhi Vs EC News: बोगस मतदारांचा आरोप भाजपने फेटाळला</t>
+          <t>मराठा सेनापती रघुजी भोसले यांची तलवार मुंबईत आणली, लंडनमध्ये झालेल्या लिलावात महाराष्ट्र सरकारने घेतली</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/bade-mudde-rahul-gandhi-vs-ec-news-%E0%A4%AC-%E0%A4%97%E0%A4%B8-%E0%A4%AE%E0%A4%A4%E0%A4%A6-%E0%A4%B0-%E0%A4%82%E0%A4%9A-%E0%A4%86%E0%A4%B0-%E0%A4%AA-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%A8%E0%A5%87-%E0%A4%AB%E0%A5%87%E0%A4%9F-%E0%A4%B3%E0%A4%B2/vi-AA1KKJ81?ocid=hpmsn</t>
+          <t>https://marathi.webdunia.com/article/mumbai-news/maratha-commander-raghuji-bhonsle-s-sword-brought-to-mumbai-125081800027_1.html</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Mumbai News Today: Navi Mumbai चे लोक Dadar Station ला येऊन अडकले! N18S #shorts</t>
+          <t>राज्यात ओला दुष्काळ जाहीर करा</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/mumbai-news-today-navi-mumbai-%E0%A4%9A%E0%A5%87-%E0%A4%B2-%E0%A4%95-dadar-station-%E0%A4%B2-%E0%A4%AF%E0%A5%87%E0%A4%8A%E0%A4%A8-%E0%A4%85%E0%A4%A1%E0%A4%95%E0%A4%B2%E0%A5%87-n18s-shorts/vi-AA1KIFxI</t>
+          <t>https://dainikekmat.com/%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%A4-%E0%A4%93%E0%A4%B2%E0%A4%BE-%E0%A4%A6%E0%A5%81%E0%A4%B7%E0%A5%8D%E0%A4%95%E0%A4%BE%E0%A4%B3-%E0%A4%9C%E0%A4%BE%E0%A4%B9%E0%A5%80/114152/</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>अमित शहा हे महाराष्ट्रातल्या गुंडांचे आणि भ्रष्टाचाऱ्यांचे दिल्लीतले सेनापती, संजय राऊत यांचा घणाघात</t>
+          <t>Those who speak of Maharashtra 'asmita' should support Radhakrishnan for VP post: Fadnavis</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/amit-shah-is-leader-of-maharashtra-corrupt-leader-says-sanjay-raut/</t>
+          <t>https://www.ptinews.com/editor-detail/those-who-speak-of-maharashtra--asmita--should-support-radhakrishnan-for-vp-post--fadnavis/2832772</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Jalgoan Rain Update : पारोळात शेतकऱ्यांचं पीक पाण्याखाली, पंचनामा करून तातडीने आर्थिक मदतीची मागणी</t>
+          <t>भाजप आमदाराचा डाव प्रशासनाने हाणून पाडला, आईच्या नावाने बांधलेले अम्मा स्मारक अवैध ठरवून हटवले</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/jalgoan-rain-update-%E0%A4%AA-%E0%A4%B0-%E0%A4%B3-%E0%A4%A4-%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%AA-%E0%A4%95-%E0%A4%AA-%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%96-%E0%A4%B2-%E0%A4%AA%E0%A4%82%E0%A4%9A%E0%A4%A8-%E0%A4%AE-%E0%A4%95%E0%A4%B0%E0%A5%82%E0%A4%A8-%E0%A4%A4-%E0%A4%A4%E0%A4%A1-%E0%A4%A8%E0%A5%87-%E0%A4%86%E0%A4%B0%E0%A5%8D%E0%A4%A5-%E0%A4%95-%E0%A4%AE%E0%A4%A6%E0%A4%A4-%E0%A4%9A-%E0%A4%AE-%E0%A4%97%E0%A4%A3/vi-AA1KIgOa</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/chandrapur-bjp-mla-kishor-jorgewar-faces-setback-as-administration-demolishes-illegal-amma-memorial-construction-as11-rc70</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Body Weight Impact: लठ्ठ व्यक्ती मेल्यावर भरावा लागेल कर, कोणत्या देशात हा कर लावला जातो? NW18S</t>
+          <t>मनसे कामगार संघटनेच्या अनेक पदाधिका-यांचा भाजपामध्ये प्रवेश</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/body-weight-impact-%E0%A4%B2%E0%A4%A0%E0%A5%8D%E0%A4%A0-%E0%A4%B5%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%A4-%E0%A4%AE%E0%A5%87%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%B5%E0%A4%B0-%E0%A4%AD%E0%A4%B0-%E0%A4%B5-%E0%A4%B2-%E0%A4%97%E0%A5%87%E0%A4%B2-%E0%A4%95%E0%A4%B0-%E0%A4%95-%E0%A4%A3%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%A4-%E0%A4%B9-%E0%A4%95%E0%A4%B0-%E0%A4%B2-%E0%A4%B5%E0%A4%B2-%E0%A4%9C-%E0%A4%A4-nw18s/vi-AA1KKrZe</t>
+          <t>https://www.marathiebatmya.com/political/many-office-bearers-of-mns-workers-organization-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Mumbai Rain Update: मुसळधार पावसामुळे शाळा सुटली पण गुडघाभर पाण्यातून विद्यार्थ्यांनी घरी जायचं कसं?</t>
+          <t>महाराष्ट्र में यह क्या हुआ? एकनाथ शिंदे का साथ छोड़ BJP में शामिल हुए कई भरोसेमंद</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/mumbai-rain-update-%E0%A4%AE%E0%A5%81%E0%A4%B8%E0%A4%B3%E0%A4%A7-%E0%A4%B0-%E0%A4%AA-%E0%A4%B5%E0%A4%B8-%E0%A4%AE%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%B6-%E0%A4%B3-%E0%A4%B8%E0%A5%81%E0%A4%9F%E0%A4%B2-%E0%A4%AA%E0%A4%A3-%E0%A4%97%E0%A5%81%E0%A4%A1%E0%A4%98-%E0%A4%AD%E0%A4%B0-%E0%A4%AA-%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%A4%E0%A5%82%E0%A4%A8-%E0%A4%B5-%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%B0%E0%A5%8D%E0%A4%A5%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%98%E0%A4%B0-%E0%A4%9C-%E0%A4%AF%E0%A4%9A%E0%A4%82-%E0%A4%95%E0%A4%B8%E0%A4%82/vi-AA1KIDWr</t>
+          <t>https://www.abplive.com/states/maharashtra/eknath-shinde-shiv-sena-solapur-leaders-join-bjp-amid-internal-feud-2997781</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Thane Monsoon Update : ट्रेन उशिरा, रस्त्यावर पाणी, मुसळधार पावसाचा ठाणेकरांना फटका</t>
+          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by Maharashtra CM Devendra Fadnavis</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/thane-monsoon-update-%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%A8-%E0%A4%89%E0%A4%B6-%E0%A4%B0-%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%B5%E0%A4%B0-%E0%A4%AA-%E0%A4%A3-%E0%A4%AE%E0%A5%81%E0%A4%B8%E0%A4%B3%E0%A4%A7-%E0%A4%B0-%E0%A4%AA-%E0%A4%B5%E0%A4%B8-%E0%A4%9A-%E0%A4%A0-%E0%A4%A3%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%82%E0%A4%A8-%E0%A4%AB%E0%A4%9F%E0%A4%95/vi-AA1KIytZ</t>
+          <t>https://www.tribuneindia.com/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis/amp/?utm=relatedarticles</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Chembur Land Slide Video : चेंबुरमध्ये भिंत कोसळली, 7 झोपड्यांचं नुकसान | News18 Lokmat</t>
+          <t>Rs 40kcr of investors’ money stuck with credit societies, Maharashtra govt to announce SOP for recovery</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/chembur-land-slide-video-%E0%A4%9A%E0%A5%87%E0%A4%82%E0%A4%AC%E0%A5%81%E0%A4%B0%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A5%87-%E0%A4%AD-%E0%A4%82%E0%A4%A4-%E0%A4%95-%E0%A4%B8%E0%A4%B3%E0%A4%B2-7-%E0%A4%9D-%E0%A4%AA%E0%A4%A1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%A8%E0%A5%81%E0%A4%95%E0%A4%B8-%E0%A4%A8-news18-lokmat/vi-AA1KJ3O8</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/rs-40kcr-of-investors-money-stuck-with-credit-societies-maharashtra-govt-to-announce-sop-for-recovery/articleshow/123367502.cms</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Mumbai Rain Update: सायनच्या गांधी मार्केटमध्ये पावसामुळे रस्त्यावर साचलं पाणी, सकाळी 10.40ची दृश्यं</t>
+          <t>NCP (SP) targets Maha minister over Rs 5,000 cr scam in Navi Mumbai’s CIDCO land; demands his resignation</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/mumbai-rain-update-%E0%A4%B8-%E0%A4%AF%E0%A4%A8%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%97-%E0%A4%82%E0%A4%A7-%E0%A4%AE-%E0%A4%B0%E0%A5%8D%E0%A4%95%E0%A5%87%E0%A4%9F%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A5%87-%E0%A4%AA-%E0%A4%B5%E0%A4%B8-%E0%A4%AE%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%B5%E0%A4%B0-%E0%A4%B8-%E0%A4%9A%E0%A4%B2%E0%A4%82-%E0%A4%AA-%E0%A4%A3-%E0%A4%B8%E0%A4%95-%E0%A4%B3-1040%E0%A4%9A-%E0%A4%A6%E0%A5%83%E0%A4%B6%E0%A5%8D%E0%A4%AF%E0%A4%82/vi-AA1KHYOZ</t>
+          <t>https://tennews.in/ncp-sp-targets-maha-minister-over-rs-5000-cr-scam-in-navi-mumbais-cidco-land-demands-his-resignation/</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>राधाकृष्णन यांना राज्यातील सर्वपक्षीय खासदारांनी पाठिंबा द्यावा</t>
+          <t>'Modi Govt Selling Dreams Of 2047, Ignoring Present': Rahul Gandhi Slams Centre After Maharashtra's Thane Train Tragedy</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/radhakrishnan-should-be-supported-by-mps-from-all-parties-in-the-state/114185/</t>
+          <t>http://www.msn.com/en-in/news/India/modi-govt-selling-dreams-of-2047-ignoring-present-rahul-gandhi-slams-centre-after-maharashtras-thane-train-tragedy/ar-AA1Gm3WY?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Rohit Pawar on Sanjay Shirsath: रोहित पवारांचे मंत्री संजय शिरसाटांवर भ्रष्टाचाराचे गंभीर आरोप; पहा काय म्हणाले</t>
+          <t>Maha govt signs MoUs worth Rs 42,000 crore and creation of 28,000 jobs</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/amp</t>
+          <t>https://www.thehawk.in/news/states-and-uts/maharashtra/maha-govt-signs-mous-worth-rs-42000-crore-and-creation-of-28000-jobs</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>22-kg Golden Kalash Installed at Sant Dnyaneshwar Temple, Crafted by Shripad Shankar Nagarkar Jewellers Pune</t>
+          <t>पंतप्रधान नरेंद्र मोदी आणि व्लादिमीर पुतीन यांच्यात संवाद - संघर्षाच्या शांततामय तोडग्यासाठी भारताचा ठाम पाठिंबा</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/press-release/22-kg-golden-kalash-installed-at-sant-dnyaneshwar-temple,-crafted-by-shripad-shankar-nagarkar-jewellers-pune/2835628</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/dialogue-between-prime-minister-narendra-modi-and-vladimir-putin-indias-strong-support-for-peaceful-resolution.html</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Ajit Pawar ‘torturing’ me, claims Ram Shinde</t>
+          <t>वैविध्यपूर्ण विषयांवरील पुस्तक प्रकाशित करणे हे चपराकचं साहित्यिक आंदोलन; लेखक अभिराम भडकमकर यांचे प्रतिपादन</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/ajit-pawar-torturing-me-claims-ram-shinde/articleshow/123372969.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/publishing-books-on-diverse-topics-is-a-literary-movement-of-the-chaparak-author-abhiram-bhadkamkar-asserts.html</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: Rohit Pawar Alleges ₹5,000-Crore Land Scam Against Minister Sanjay Shirsat</t>
+          <t>ठाण्यात शालेय ९-साईड हॉकी लीगला सुरुवात ; ७६ संघांचा उत्साही सहभाग</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-rohit-pawar-alleges-5000-crore-land-scam-against-minister-sanjay-shirsat</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/school-9-a-side-hockey-league-begins-in-thane-76-teams-participate-enthusiastically.html</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Mumbai rains HIGHLIGHTS: Civic body declares holiday for all schools on August 19</t>
+          <t>Rain fury: 5 missing, 200 stranded in Nanded; local trains, flights hit in Mumbai</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/live-news-updates-mumbai-rain-waterlogging-traffic-heavy-rain-orange-alert-125081800291_1.html</t>
+          <t>https://www.ptinews.com/editor-detail/Rain-fury--5-missing--200-stranded-in-Nanded;-local-trains--flights-hit-in-Mumbai/2832995</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Demand to release list of property-holders affected due to road-widening in 5 days</t>
+          <t>Rains Wreak Havoc Across States, Toll In Kishtwar Cloudburst Touches 63</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/aurangabad/demand-to-release-list-of-property-holders-affected-due-to-road-widening-in-5-days/</t>
+          <t>https://www.etvbharat.com/en/!bharat/rains-wreak-havoc-across-states-over-200-stranded-in-worst-hit-maharashtra-toll-in-kishtwar-cloudburst-touches-63-enn25081807219</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Sanjay Shirsat : मंत्री शिरसाट यांच्यावर ५ हजार कोटींच्या जमीन घोटाळ्याचा आरोप</t>
+          <t>Maharashtra Rain Update: महाराष्ट्र में बारिश ने मचाई तबाही, अब तक सात लोगों की मौत, 200 ग्रामीण फंसे</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/minister-shirsat-accused-of-rs-5000-crore-land-scam-np88</t>
+          <t>https://www.ibc24.in/maharashtra/seven-people-died-due-to-rain-in-maharashtra-3213688.html</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>'ऑपरेशन लोटस वगैरे काही नाही; लवकरच ऑपरेशन टायगर दिसेल', सोलापूरच्या राजकारणात पडद्यामागे काय घडतंय?</t>
+          <t>Vice Presidential Election : उपराष्ट्रपती पदासाठी विरोधकांचा उमेदवार कोण? दिल्लीत घडामोडींना वेग; राहुल गांधी काय भूमिका घेणार?</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%B2-%E0%A4%9F%E0%A4%B8-%E0%A4%B5%E0%A4%97%E0%A5%88%E0%A4%B0%E0%A5%87-%E0%A4%95-%E0%A4%B9-%E0%A4%A8-%E0%A4%B9-%E0%A4%B2%E0%A4%B5%E0%A4%95%E0%A4%B0%E0%A4%9A-%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%9F-%E0%A4%AF%E0%A4%97%E0%A4%B0-%E0%A4%A6-%E0%A4%B8%E0%A5%87%E0%A4%B2-%E0%A4%B8-%E0%A4%B2-%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B0-%E0%A4%9C%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A4-%E0%A4%AA%E0%A4%A1%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%AE-%E0%A4%97%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%98%E0%A4%A1%E0%A4%A4%E0%A4%82%E0%A4%AF/ar-AA1KKoUc</t>
+          <t>https://www.loksatta.com/desh-videsh/who-is-the-opposition-candidate-for-the-post-of-vice-president-events-in-delhi-are-gaining-momentum-what-decision-will-mallikarjun-kharge-take-gkt-96-5313155/</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Mumbai Rain Mayhem: City Comes To Standstill As Life Thrown Out Of Gear; MonoRail Gets Stuck</t>
+          <t>पूजेसाठी परवानगी नाही, नमाजसाठी जागाच जागा; कम्युनिस्टांचा हिंदुविरोधी चेहरा पुन्हा समोर</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!state/mumbai-rains-update-august-19-govt-semi-govt-offices-shut-bmc-urges-wfh-for-pvt-employees-enn25081901231</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/no-permission-for-worship-plenty-of-space-for-namaz-cpims-different-rules-for-hindus-and-muslims-in-kerala-the.html</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>To collect outstanding transportation fines, the Maha government is planning an amnesty scheme</t>
+          <t>कर्नाटकातील हिंदू धर्मस्थळांना बदनाम करण्याची शहरी नक्षलवाद्यांची मोहिम; कर्नाटक भाजप आमदार हरीश पुंजा यांचा आरोप</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>https://assamtribune.com/national/to-collect-outstanding-transportation-fines-the-mahagovernment-is-planning-an-amnesty-scheme-1588536</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/urban-naxalites-campaign-to-defame-hindu-religious-places-karnataka-bjp-mla-harish-punja-alleges.html</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>‘Third Mumbai’ will open a new chapter of economic development: Maha CM</t>
+          <t>मुसळधार पावसामुळे राज्यात सात जणांचा मत्यू; मुंबईत पावसामुळे जनजीवन विस्कळित</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/third-mumbai-will-open-new-chapter-economic-development-maha-cm-441953</t>
+          <t>https://www.etvbharat.com/mr/!state/mumbai-rains-updates-imd-red-alert-mumbai-city-suburbs-schools-and-colleges-remain-closed-today-mumbai-university-exams-postponed-to-23-august-maharashtra-rain-news-today-maharashtra-news-mhs25081900792</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Maha govt waives Stamp Duty worth Rs 38.99 lakh for Tata Cancer Hospital in Raigad (Ld)</t>
+          <t>Will Bajirao Mastani Come Alive in Movie Halls Today?</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/india/maha-govt-waives-stamp-duty-worth-rs-3899-lakh-for-tata-cancer-hospital-in-raigad-ld</t>
+          <t>https://caleidoscope.in/art-culture/will-bajirao-mastani-come-alive-in-movie-halls-today</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Shortage of teachers hits rollout of NEP in govt, aided Maha colleges</t>
+          <t>Red alert in Mumbai; BMC shuts all afternoon schools, colleges</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>https://www.pressreader.com/india/hindustan-times-st-jaipur/20250819/281681145971378</t>
+          <t>https://www.newsbytesapp.com/news/india/mumbai-rain-havoc-to-continue-for-next-4-days/story</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Maharashtra: मंत्री शंभूराज देसाई को मिला बचपन वाला वही सरकारी बंगला, मां के जन्मदिन पर किया भावुक गृहप्रवेश</t>
+          <t>Nanded Rain: नांदेड़ में भारी बारिश के बाद 200 लोग बाढ़ में फंसे! बादल फटने से 5 लापता, रेस्क्यू के लिए सेना बुलाई गई</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%B6%E0%A4%82%E0%A4%AD%E0%A5%82%E0%A4%B0-%E0%A4%9C-%E0%A4%A6%E0%A5%87%E0%A4%B8-%E0%A4%88-%E0%A4%95-%E0%A4%AE-%E0%A4%B2-%E0%A4%AC%E0%A4%9A%E0%A4%AA%E0%A4%A8-%E0%A4%B5-%E0%A4%B2-%E0%A4%B5%E0%A4%B9-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%AC%E0%A4%82%E0%A4%97%E0%A4%B2-%E0%A4%AE-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%9C%E0%A4%A8%E0%A5%8D%E0%A4%AE%E0%A4%A6-%E0%A4%A8-%E0%A4%AA%E0%A4%B0-%E0%A4%95-%E0%A4%AF-%E0%A4%AD-%E0%A4%B5%E0%A5%81%E0%A4%95-%E0%A4%97%E0%A5%83%E0%A4%B9%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6/ar-AA1JRinD?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://hindi.moneycontrol.com/india/heavy-rains-in-maharashtra-nanded-leave-over-200-stranded-in-flood-waters-five-people-missing-article-2104052.html</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में भारी बारिश से सात लोगों की मौत, 200 ग्रामीण फंसे</t>
+          <t>Historic Sword of Raghuji Bhonsle Returns to Mumbai, To Be Unveiled in Grand Ceremony</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/seven-people-died-due-to-heavy-rains-in-maharashtra-200-villagers-stranded/856903/</t>
+          <t>https://thelivenagpur.com/2025/08/18/historic-sword-of-raghuji-bhonsle-returns-to-mumbai-to-be-unveiled-in-grand-ceremony/</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>कैसी होगी तीसरी मुंबई, कितनी बड़ी और कहां बन रही, सुविधाओं से लेकर प्लानिंग तक, CM फडणवीस ने सब बताया</t>
+          <t>Vande Bharat Express: नागपूर ते पुणे एक आठवड्यापूर्वी सुरु झालेल्या ‘वंदे भारत’ला पावणेदोन तास उशीर</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%95%E0%A5%88%E0%A4%B8-%E0%A4%B9-%E0%A4%97-%E0%A4%A4-%E0%A4%B8%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%95-%E0%A4%A4%E0%A4%A8-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%94%E0%A4%B0-%E0%A4%95%E0%A4%B9-%E0%A4%82-%E0%A4%AC%E0%A4%A8-%E0%A4%B0%E0%A4%B9-%E0%A4%B8%E0%A5%81%E0%A4%B5-%E0%A4%A7-%E0%A4%93%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AA%E0%A5%8D%E0%A4%B2-%E0%A4%A8-%E0%A4%82%E0%A4%97-%E0%A4%A4%E0%A4%95-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%AF/ar-AA1KLMl6?ocid=finance-verthp-feeds</t>
+          <t>https://www.lokmat.com/pune/the-vande-bharat-train-from-nagpur-to-pune-which-started-a-week-ago-was-delayed-by-two-and-a-half-hours-a-a727/</t>
         </is>
       </c>
     </row>
@@ -5843,1606 +5843,682 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>‘कमलाबाई’ की नई योजना… सहयोगी दलों का करना है सफाया!.. २०२९ तक शिंदे-दादा का फडणवीस करेंगे गेम</t>
+          <t>What happened in the Trump-Putin meeting? | Chandrashekhar Nene Maha MTB</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/kamalabais-new-plan-allies-have-to-be-wiped-out-fadnavis-will-play-the-game-of-shinde-dada-till-2029/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/what-happened-in-the-trump-putin-meeting-chandrashekhar-nene-maha-mtb.html</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में माफ हो सकते हैं पुराने ट्रैफिक चालान, माफी योजना लाने की तैयारी में सरकार</t>
+          <t>IBM to support Maharashtra in developing quantum computing initiative</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/government-schemes/others/maharashtra-government-is-set-to-roll-out-an-amnesty-scheme-for-one-time-settlement-of-pending-traffic-challan/articleshow/123367444.cms</t>
+          <t>https://www.communicationstoday.co.in/ibm-to-support-maharashtra-in-developing-quantum-computing-initiative/</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Ladki Bahin Yojana: 'लाडकी बहिन योजना' के बाद 'लाडकी सुनबाई योजना' का ऐलान जल्द? डिप्टी सीएम ने कही ये बड़ी बात</t>
+          <t>Heavy rainfall causes 7 deaths, crop loss in Maharashtra as alerts continue</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>https://www.punjabkesari.in/national/news/after-ladki-bahin-yojana-will-ladki-sunbai-yojana-be-an-2198473</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/heavy-rainfall-causes-7-deaths-crop-loss-in-maharashtra-as-alerts-continue/articleshow/123368187.cms</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>इस दिन खाते में आ सकती है माझी लड़की बहिन योजना की अगली किस्त, इन महिलाओं को नहीं मिलेंगे पैसे</t>
+          <t>Maratha general Raghuji Bhonsle's sword brought to Mumbai</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%87%E0%A4%B8-%E0%A4%A6-%E0%A4%A8-%E0%A4%96-%E0%A4%A4%E0%A5%87-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%86-%E0%A4%B8%E0%A4%95%E0%A4%A4-%E0%A4%B9%E0%A5%88-%E0%A4%AE-%E0%A4%9D-%E0%A4%B2%E0%A4%A1%E0%A4%BC%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A8-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%95-%E0%A4%85%E0%A4%97%E0%A4%B2-%E0%A4%95-%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%87%E0%A4%A8-%E0%A4%AE%E0%A4%B9-%E0%A4%B2-%E0%A4%93%E0%A4%82-%E0%A4%95-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AE-%E0%A4%B2%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AA%E0%A5%88%E0%A4%B8%E0%A5%87/ar-AA1vsznB?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.ptinews.com/story/national/maratha-general-raghuji-bhonsle's-sword-brought-to-mumbai/2833930</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>तिसरी मुंबई आर्थिक विकासाचा नवा अध्याय – मुख्यमंत्री देवेंद्र फडणवीस</t>
+          <t>Mumbai rains: Heavy showers flood roads, railway tracks; bring city to standstill - video</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176127/</t>
+          <t>https://timesofindia.indiatimes.com/india/mumbai-rains-heavy-showers-flood-roads-railway-tracks-bring-city-to-standstill-video/articleshow/123362740.cms</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Mumbai Chawl Redevelopment | चाळ झाली आधुनिक वस्ती</t>
+          <t>Monday mayhem: Mumbai's suburbs recorded over 100 mm rainfall in 12 hours, says IMD</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>https://pudhari.news/sampadakiy/mumbai-chawl-redevelopment-displaced-workers-problem-sp96</t>
+          <t>https://www.ptinews.com/story/national/monday-mayhem:-mumbai's-suburbs-recorded-over-100-mm-rainfall-in-12-hours,-says-imd/2834156</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Heavy Rains Batter Mumbai: Red Alert Issued, Schools and Colleges Closed on August 19 in Thane and...</t>
+          <t>Mumbai reels under 177 mm rain in 8 hours; flights hit, schools shut as red alert issued</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/news/national/heavy-rains-batter-mumbai-red-alert-issued-schools-and-colleges-closed-on-august-19-in-thane-and-palghar-998357</t>
+          <t>https://www.newindianexpress.com/nation/2025/Aug/18/mumbai-rains-flight-operations-hit-schools-colleges-shut-as-imd-issues-red-alert</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Mumbai Rains: Are Private and Public offices shut today? BMC issues statement, says...</t>
+          <t>Rain fury: 5 missing, 200 stranded in Nanded; local trains, flights hit in Mumbai</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>https://www.india.com/news/india/mumbai-rains-are-private-and-public-offices-shut-today-bmc-work-from-home-schools-colleges-devendra-fadnavis-markets-8019561/</t>
+          <t>https://odishatv.in/news/national/rain-fury-5-missing-200-stranded-in-nanded-local-trains-flights-hit-in-mumbai-270189</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Surya Roshni to invest Rs 25 cr for biz expansion</t>
+          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by Maharashtra CM Devendra Fadnavis</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/business/2025/08/18/dcm62-biz-briefs-3.html</t>
+          <t>https://www.aninews.in/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>मुंबई में भारी बारिश के बीच सुचारू रूप से चल रही मेट्रो, सीएम फडणवीस ने की तारीफ</t>
+          <t>Mumbai rains: Heavy rainfall batter city as Vihar lake overflows</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>https://www.m.khaskhabar.com/news/news-metro-running-smoothly-amid-heavy-rains-in-mumbai-cm-fadnavis-praised-news-hindi-1-745323-KKN.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-rains-heavy-rainfall-batter-city-as-vihar-lake-overflows-23590062</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Maharashtra politics : मुख्यमंत्र्यांच्या पत्नी गायिका, तरीही गाणे गाणाऱ्या तहसीलदारांना शिक्षा? बावनकुळे या चुकीला माफी असायलाच हवी; सामनातून हल्लाबोल</t>
+          <t>IndiGo Airlines issues travel advisory for passengers flying out of Mumbai due to heavy rainfall, waterlogging in the city</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/nanded-tehsildar-prashant-thorat-suspension-shiv-sena-ubt-criticism-sanjay-raut-devendra-fadnavis-jap93</t>
+          <t>https://newsroompost.com/india/indigo-airlines-issues-travel-advisory-for-passengers-flying-out-of-mumbai-due-to-heavy-rainfall-waterlogging-in-the-city/5347388.html</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>‘Third Mumbai’ will open a new chapter of economic development: Maha CM</t>
+          <t>18.08.2025 : मुख्यमंत्री देवेंद्र फडणवीस व सांस्कृतिक कार्य मंत्री आशिष शेलार यांनी घेतली राज्यपालांची भेट</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/third-mumbai-will-open-a-new-chapter-of-economic-development-maha-cm/</t>
+          <t>https://rajbhavan-maharashtra.gov.in/18-08-2025-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB/</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Maha CM asks agencies to be on alert mode after heavy rainfall and flash floods</t>
+          <t>Maharashtra Rains: राज्यात अतिवृष्टी, 7 जणांचा मृत्यू; मुख्यमंत्र्यांचे सर्व यंत्रणांना सतर्कतेचे निर्देश Maharashtra Rains: Heavy rains in the state, 7 people died; CM Devendra Fadnavis directs all agencies to be alert</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/maha-cm-asks-agencies-to-be-on-alert-mode-after-heavy-rainfall-and-flash-floods/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-rains-heavy-rains-in-the-state-7-people-died-cm-devendra-fadnavis-directs-all-agencies-to-be-alert-89603</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>CM to join Kawad yatra, TV center chowk shut for 5 hours</t>
+          <t>CM Devendra Fadnavis : ‘तिसरी मुंबई’ नवा अध्याय उघडेल; रायगड जिल्ह्यात होणार विकसित</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/aurangabad/cm-to-join-kawad-yatra-tv-center-chowk-shut-for-5-hours/</t>
+          <t>https://www.esakal.com/mumbai/navi-mumbais-successor-the-rise-of-third-mumbai-in-raigad-district-cm-devendra-fadnavis-pjp78</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>चुनाव के बाद होगा महामंडलों का वितरण, महायुति के इच्छुक नेताओं पर प्रदर्शन का दबाव</t>
+          <t>CM Devendra Fadnavis : हिंदवी स्वराज्याचा इतिहास नवीन पिढीपर्यंत पोहोचेल; श्रीमंत राजे रघुजी भोसले यांच्या तलवारीचे स्वागत</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/nagpur/distribution-of-maha-mandals-will-happen-after-the-elections-pressure-of-demonstration-on-the-aspiring-leaders-of-mahayuti-1322474.html</t>
+          <t>https://www.esakal.com/mumbai/legacy-of-hindavi-swarajya-rajarshi-raghuji-bhosales-sword-welcomed-history-cm-devendra-fadnavis-pjp78</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Mumbai Rain Red Alert : पावसामुळे आतापर्यंत 7 जणांचा मृत्यू; साचलेल्या पाण्यामुळे प्रवाशांचे हाल अन् राजकारणही तापलं</t>
+          <t>मुंबईत पुढील आठ ते दहा तासांसाठी रेड अलर्ट, महत्त्वाचे काम असल्यास घराबाहेर पडण्याचे मुख्यमंत्री फडणवीस यांचे आवाहन</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/mumbai-rain-red-alert-heavy-rainfall-maharashtra-floods-bmc-pune-schooll-jap93</t>
+          <t>https://www.saamana.com/in-mumbai-people-have-been-told-to-step-out-only-if-it-is-needed-says-cm-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>राज्यात ओला दुष्काळ जाहीर करा, विशेष अधिवेशन बोलवा मुसळधार पावसानंतर शरद पवारांच्या</t>
+          <t>Kolhapur : सरन्यायाधीश Bhushan Gavai यांच्या हस्ते सर्किट बेंच इमारतीचे उद्घाटन</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/sharad-pawar-ncp-demands-after-heavy-rains-declaring-a-wet-drought-in-the-state-calling-a-special-session-shashikant-shinde-1377947</t>
+          <t>https://www.tarunbharat.com/kolhapur-circuit-bench-inauguration-with-chief-justice-bhushan-gavai-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>सिडको जमिन वाटप प्रकरणावरून राजकारण तापले; पवारांचा शिरसाठांवर घणाघाती हल्ला</t>
+          <t>Maharashtra Rain: राज्यात पावसाचा हाहाकार! १६ जिल्ह्यांना रेड- ऑरेंज अलर्ट, मुख्यमंत्र्यांकडून सतर्क राहण्याचे आवाहन</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/politics-heats-up-over-cidco-land-allocation-issue-pawar-attacks-shirsath/</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/maharashtra-floods-cm-fadnavis-reviews-situation-ndrf-and-army-deployed-16-districts-on-red-alert-latest-news-pvm91</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>'Destroying constitutional institutions': Nishikant Dubey slams Rahul Gandhi as SC dismisses plea challenging 2024 Maharashtra polls</t>
+          <t>Mumbai Rain Update : मुंबईत धो-धो! वाहतुकीचा खोळंबा, लोकलसेवेला फटका; मुंबईकरांची पुरती दैना; पुढील 48 तासही धोक्याचे</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>https://www.malaysiasun.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-rain-update-heavy-rainfall-started-in-city-resulted-in-disruption-of-life-and-mumbai-local-cm-fadnavis-reviewed/articleshow/123363662.cms</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>'Political opinions or...': Supreme Court quashes plea challenging validity of Maharashtra Assembly polls</t>
+          <t>रघुजीराजे भोसले यांची तलवार मुंबईत शौर्याचा वारसा इतिहाप्रेमींसाठी खुला; मराठा साम्राज्याचा वारसा परत मिळवण्याचा प्रयत्न – मुख्यमंत्री</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/political-opinions-or-supreme-court-quashes-plea-challenging-validity-of-maharashtra-assembly-polls-3686244</t>
+          <t>https://www.saamana.com/raghujiraje-bhosale-sword-a-legacy-of-bravery-is-open-to-history-lovers-in-mumbai-an-attempt-to-reclaim-the-legacy-of-the-maratha-empire-said-by-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Supreme Court dismisses plea alleging 75 lakh bogus votes in Maharashtra Assembly polls</t>
+          <t>राष्ट्रीय: मुंबई में भारी बारिश के बीच सुचारू रूप से चल रही मेट्रो, सीएम फडणवीस ने की तारीफ</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>https://organiser.org/2025/08/19/308844/bharat/supreme-court-dismisses-plea-alleging-75-lakh-bogus-votes-in-maharashtra-assembly-polls/</t>
+          <t>https://www.bhaskarhindi.com/other/news-1174019</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>'Destroying constitutional institutions': Nishikant Dubey slams Rahul Gandhi as SC dismisses plea challenging 2024 Maharashtra polls</t>
+          <t>तिसरी MUMBAI आर्थिक विकासाचा नवा अध्याय, गोल्डमन सॅक्सच्या नव्या मुंबई कार्यालयाचे उद्घाटन</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
+          <t>https://www.timemaharashtra.com/maharashtra/mumbai/third-mumbai-a-new-chapter-in-economic-development-goldman-sachs-new-mumbai-office-inaugurated/129385/</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>महाराष्ट्र विधानसभा चुनाव को लेकर सुप्रीम कोर्ट का बड़ा फैसला, खारिज की परिणाम रद्द करने वाली याचिका</t>
+          <t>Mumbai Rain : मुख्यमंत्री फडणवीस ॲक्शन मोडमध्ये! राज्यभरात पडत असलेल्या पावसामुळे प्रशासन अलर्ट</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>https://hindi.news24online.com/india/supreme-court-rejects-maharashtra-assembly-election-2024-result-cancellation-petition/1288385/</t>
+          <t>https://www.marathi.hindusthanpost.com/social/mumbai-rain-cm-devendra-fadnavis-in-action-mode-administration-alert-due-to-rains-falling-across-the-state/</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Maharashtra govt plans amnesty scheme to recover pending transport fines</t>
+          <t>Devendra Fadnavis : नांदेड जिल्ह्यातील अतिवृष्टीवर मुख्यमंत्र्यांची नजर, प्रशासनाला सूचना</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>https://auto.economictimes.indiatimes.com/amp/news/industry/maharashtras-new-amnesty-scheme-settle-transport-fines-and-save-big/123364146</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/devendra-fadnavis-chief-ministers-eye-on-heavy-rains-in-nanded-district-instructions-to-the-administration/</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Mah plans amnestyscheme to recoverpending transport fines</t>
+          <t>Heavy Rainfall : मुख्यमंत्री फडणवीसांचे यंत्रणांना सतर्क राहण्याचे आदेश; राज्यभरातील स्थितीचा घेतला आढावा</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/19/mah-plans-amnesty-scheme-to-recover-pending-transport-fines.html</t>
+          <t>https://www.marathi.hindusthanpost.com/social/heavy-rainfall-cm-devendra-fadnavis-orders-agencies-to-be-alert-review-of-the-situation-across-the-state/</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Cases from 6 districts to be heard | ‘A dream comes true after 40-45 years of struggle’: CJI inaugurates HC bench in Kolhapur</t>
+          <t>Rain wreaks havoc in Maharashtra, brings Mumbai to a standstill</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/pune/cases-dream-struggle-cji-inaugurates-hc-bench-kolhapur-10195928/</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/rain-wreaks-havoc-in-maharashtra-brings-mumbai-to-a-standstill/article69948564.ece</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Maratha general Raghuji Bhonsle's sword brought to Mumbai</t>
+          <t>Transformative Leadership: Sukhraj Nahar Steers CREDAI-MCHI Towards Urban Revolution</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>https://english.metrovaartha.com/news/mumbai/maratha-general-raghuji-bhonsles-sword-brought-to-mumbai</t>
+          <t>https://www.devdiscourse.com/article/business/3545330-transformative-leadership-sukhraj-nahar-steers-credai-mchi-towards-urban-revolution</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Maratha commander Raghuji Bhonsle's sword brought to Mumbai!!</t>
+          <t>The perks and costs of ‘Ladki Bahin’</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>https://www.indiaherald.com/Breaking/Read/994842382/Maratha-commander-Raghuji-Bhonsles-sword-brought-to-Mumbai</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/the-perks-and-costs-of-ladki-bahin-101755575344332.html</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>राज्य को बाढ़ आपदा घोषित करो… विशेष अधिवेशन बुलाओ… एनसीपी प्रदेश अध्यक्ष ने की सीएम से मांग</t>
+          <t>LGEC 2025: 'लाडकी बहीण' योजनेमुळे महाराष्ट्रातील अर्थव्यवस्थेला चालनाच मिळाली; सुनील तटकरेंनी समजावलं 'गणित'</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/declare-the-state-a-flood-disaster-call-a-special-session-ncp-state-president-made-a-demand-to-the-cm/</t>
+          <t>https://www.lokmat.com/international/lgec-2025-ladki-bahin-scheme-has-given-a-boost-to-the-economy-of-maharashtra-sunil-tatkare-rahul-narvekar-explained-a-a629/</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>महाराष्ट्रातील 'या' जिल्ह्यात उभारणार 'स्टॅच्यू ऑफ युनिटी'; सरकारचा काय आहे प्लॅन?</t>
+          <t>Those who speak of Maharashtra 'asmita' should support Radhakrishnan for VP post Fadnavis</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>https://www.tendernama.com/mahatender/paschim-maharashtra/statue-of-unity-style-memorial-in-maharashtra-soon</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom25-mh-governor-ld-fadnavis.html</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Kolhapur : सरन्यायाधीश Bhushan Gavai यांच्या हस्ते सर्किट बेंच इमारतीचे उद्घाटन</t>
+          <t>Marathi News Headlines | 7 AM | News18 Lokmat | 19 Aug 2025 | Maharashtra Rain Update | Mumbai Rain</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/kolhapur-circuit-bench-inauguration-with-chief-justice-bhushan-gavai-marathi-news/</t>
+          <t>https://www.msn.com/mr-in/news/other/marathi-news-headlines-7-am-news18-lokmat-19-aug-2025-maharashtra-rain-update-mumbai-rain/vi-AA1KLnMI?ocid=hpmsn</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Ganesh Naik, Eknath Shinde, Thane, Maharashtra Politics</t>
+          <t>Aaj Ka Rashifal, 19 Aug, 2025 : आचार्य इंदु प्रकाश जी से जानिए आज क्या कह रहे हैं आपके सितारे</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/maharashtra/ganesh-naik-eknath-shinde-thane-maharashtra-politics-54-804112</t>
+          <t>https://www.indiatv.in/video/bhavishyawani/aaj-ka-rashifal-19-aug-2025-know-from-acharya-indu-prakash-ji-what-your-stars-are-saying-today-2025-08-19-1156865</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>राज्यात ओला दुष्काळ जाहीर करा</t>
+          <t>मुंबई में भारी बारिश का कहर, 19 अगस्त को बंद रहेंगे सभी स्कूल-कॉलेज</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%A4-%E0%A4%93%E0%A4%B2%E0%A4%BE-%E0%A4%A6%E0%A5%81%E0%A4%B7%E0%A5%8D%E0%A4%95%E0%A4%BE%E0%A4%B3-%E0%A4%9C%E0%A4%BE%E0%A4%B9%E0%A5%80/114152/</t>
+          <t>https://hindi.news24online.com/india/mumbai-and-jammu-kashmir-heavy-rain-rain-school-and-college-closed/1288306/</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>मराठा सेनापति रघुजी भोंसले की तलवार मुंबई लाई गई, लंदन में हुई नीलामी में महाराष्ट्र सरकार ने हासिल की</t>
+          <t>मानसून में हाल बेहाल, भारी बारिश से इस राज्य में जगह-जगह भरा पानी, स्कूल-कॉलेज किए बंद</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>https://samarsaleel.com/%E0%A4%AE%E0%A4%B0%E0%A4%BE%E0%A4%A0%E0%A4%BE-%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A4%BE%E0%A4%AA%E0%A4%A4%E0%A4%BF-%E0%A4%B0%E0%A4%98%E0%A5%81%E0%A4%9C%E0%A5%80-%E0%A4%AD%E0%A5%8B%E0%A4%82%E0%A4%B8/490978</t>
+          <t>https://www.patrika.com/national-news/heavy-rain-alert-in-mumbai-monsoon-gained-momentum-know-imd-weather-update-19874723</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>राज्यभरात ‘कोसळ’धार, पावसाने मराठवाड्याला झोडपले, तब्बल १२०० गावांना अतिवृष्टीचा फटका</t>
+          <t>Mumbai Rains: भारी बारिश का कहर, 7 की मौत, आदित्य ठाकरे ने BMC पर लगाए आरोप</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/kosal-torrential-rains-hit-marathwada-1200-villages-affected-by-heavy-rains/</t>
+          <t>https://www.thesandeshwahak.com/mumbai-rains-heavy-rain-wreaks-havoc-7-dead-aditya-thackeray-blames-bmc/</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>मराठा सेनापती रघुजी भोसले यांची तलवार मुंबईत आणली, लंडनमध्ये झालेल्या लिलावात महाराष्ट्र सरकारने घेतली</t>
+          <t>Ganesh Naik, Eknath Shinde, Thane, Maharashtra Politics</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/mumbai-news/maratha-commander-raghuji-bhonsle-s-sword-brought-to-mumbai-125081800027_1.html</t>
+          <t>https://mpbreakingnews.in/maharashtra/ganesh-naik-eknath-shinde-thane-maharashtra-politics-54-804112</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>How CP Radhakrishnan Broke The Taboo Around Modi And Changed The Narrative After 2002 Gujarat Episode - The</t>
+          <t>रमेश बिधूड़ी ने राधाकृष्णन को दी शुभकामनाएं, कहा- 'अच्छे उपराष्ट्रपति साबित होंगे'</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>https://thecommunemag.com/how-cpr-broke-the-taboo-around-modi/</t>
+          <t>https://www.khaskhabar.com/local/delhi-ncr/delhi-news/news-ramesh-bidhuri-congratulated-radhakrishnan-said---he-will-prove-to-be-a-good-vice-president-news-hindi-1-745268-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>राजनीति: सरकार मुंबई में जलभराव की समस्या को दूर करने के लिए गंभीरता से काम कर रही भाजपा नेता रामकदम</t>
+          <t>Cabinet sends back note regarding GMR with multiple queries</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/bjp-leader-ram-kadam-1174256</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/18/cabinet-sends-back-note-regarding-gmr-with-multiple-queries.html</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>मनसे कामगार संघटनेच्या अनेक पदाधिका-यांचा भाजपामध्ये प्रवेश</t>
+          <t>Mumbai on red alert; BMC declares holiday for schools, colleges on August 19</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/many-office-bearers-of-mns-workers-organization-join-bjp/</t>
+          <t>https://m.economictimes.com/news/india/bmc-declares-holiday-for-mumbai-schools-colleges-on-august-19-as-city-braces-for-heavy-rain/articleshow/123366693.cms</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>रमेश बिधूड़ी ने राधाकृष्णन को दी शुभकामनाएं, कहा- 'अच्छे उपराष्ट्रपति साबित होंगे'</t>
+          <t>Mumbai rains: BMC announces holiday for schools, colleges on August 19</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/delhi-ncr/delhi-news/news-ramesh-bidhuri-congratulated-radhakrishnan-said---he-will-prove-to-be-a-good-vice-president-news-hindi-1-745268-KKN.html</t>
+          <t>https://www.cnbctv18.com/india/are-mumbai-schools-colleges-open-or-close-on-august-19-19655564.htm</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>मुंबई-बेंगलोर महामार्गावर बसला मध्यरात्री आग; प्रवासी थोडक्यात बचावले</t>
+          <t>Heavy rains lash Mumbai; red alert issued, Vihar Lake overflows, CM urges caution</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/city/pune/bus-catches-fire-on-mumbai-bangalore-highway-at-midnight-passengers-narrowly-escape/</t>
+          <t>https://www.thehindu.com/news/cities/mumbai/mumbai-rain-updates-august-18-2025/article69946286.ece</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>मुंबईत रेड अलर्ट; तीन ते चार तासात ‘अतिमुसळधार’ कोसळणार, शाळांना सुट्टी जाहीर</t>
+          <t>India monsoon updates: Heavy to very heavy rainfall at few places in Mumbai; residents told to ‘avoid unnecessary travel’</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/mumbai-on-red-alert-due-to-heavy-rain-schools-and-colleges-closed/</t>
+          <t>https://www.thehindu.com/news/national/india-monsoon-live-mumbai-rains-yamuna-river-flood-alert-delhi-kashmir-cloudburst-updates-august-18/article69946105.ece</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>गणेशोत्सवात ध्वनिप्रदूषण नियमभंग; एनजीटीची पुणे पोलिस व प्रदूषण मंडळाला नोटीस</t>
+          <t>Are Mumbai schools, colleges open today? Details here | Latest News India - Hindustan Times</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/city/pune/noise-pollution-rules-violated-during-ganeshotsav-ngt-issues-notice-to-pune-police-and-pollution-board/</t>
+          <t>https://www.hindustantimes.com/india-news/are-mumbai-schools-colleges-open-today-details-here-mumbai-rains-mumbai-weather-imd-red-alert-101755561079277.html</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>“जामनेरमधील हत्याकांडात भाजप कार्यकर्ते…” अबू आझमींचा आरोप</t>
+          <t>Mumbai Rains Live News: Torrential rains cripple Mumbai; roads flooded, local trains delayed and schools, colleges closed amid ‘Red’ alert</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nashik/abu-azmi-alleges-bjp-workers-involved-in-jalgaon-mob-lynching-case-of-suleman-pathan-vsd-99-5314556/</t>
+          <t>https://www.thehindubusinessline.com/news/mumbai-weather-mumbai-rains-live-news-updates/article69946123.ece</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>कोट्यधीशांचे स्थलांतर</t>
+          <t>Pune Can Get Underground Road Network To Beat Traffic Woes</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/editorial/migration-of-billionaires/</t>
+          <t>https://trak.in/stories/pune-can-get-underground-road-network-to-beat-traffic-woes/</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>सीपी राधाकृष्णन के उपराष्ट्रपति उम्मीदवार बनाने पर कांग्रेस को लगी मिर्ची; INDI ब्लॉक भी जल्द कर सकता है प्रत्याशी का ऐलान</t>
+          <t>Rainfall Alert: All schools and colleges closed due to heavy rains, IMD issued red alert</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>https://sudarshannews.in/news-detail.aspx?id=131383</t>
+          <t>https://www.informalnewz.com/rainfall-alert-all-schools-and-colleges-closed-due-to-heavy-rains-imd-issued-red-alert/</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by Maharashtra CM Devendra Fadnavis</t>
+          <t>शाळा अंतर्गत फेरीमध्ये विद्यार्थ्यांचा सत्कार सोहळा</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/student-felicitation-ceremony-during-the-schools-internal-parade.html</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में भारी बारिश से सात लोगों की मौत, 200 ग्रामीण फंसे</t>
+          <t>सामाजिक कामात कार्यरत राहून मिळणारा आनंद मोठा: पांडुरंग चोरमले</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/seven-people-died-due-to-heavy-rains-in-maharashtra-200-villagers-stranded/856903/?amp</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/the-joy-of-working-in-social-work-is-immense-pandurang-chormale.html</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
+          <t>Maharashtra Rain Update: 19 ऑगस्टलाही सावधान..., महाराष्ट्रातील 'या' जिल्ह्यांना रेड अलर्ट</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>https://www.millenniumpost.in/nation/third-mumbai-to-boost-metropolitan-region-development-fadnavis-623625</t>
+          <t>https://www.navarashtra.com/maharashtra/mahrashtra-mumbai-rain-latest-update-orange-alert-till-august-20-red-alert-issued-in-several-districts-963438.html</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>Sword of Raghuji Bhonsle arrives in Mumbai and will be on display till Aug 25</t>
+          <t>Mumbai Rain Update: मुंबईत पुढील चार तास धो-धो, रेड अलर्ट जारी, लोकल ट्रेन उशिराने, नागरिकांना घराबाहेर न पडण्याचं आवाहन</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/sword-of-raghuji-bhonsle-arrives-in-mumbai-and-will-be-on-display-till-aug-25/articleshow/123371745.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-heavy-rain-expected-by-imd-red-alert-heavy-rainfall-local-train-updates/articleshow/123376293.cms</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>Rs 40kcr of investors’ money stuck with credit societies, Maharashtra govt to announce SOP for recovery</t>
+          <t>ABP Majha Top 10 Headlines : ABP माझा टॉप 10 हेडलाईन्स | 18 ऑगस्ट 2025 | सोमवार</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/rs-40kcr-of-investors-money-stuck-with-credit-societies-maharashtra-govt-to-announce-sop-for-recovery/articleshow/123367502.cms</t>
+          <t>https://marathi.abplive.com/news/maharashtra/abp-majha-top-10-headlines-18-august-2025-monday-latest-marathi-news-update-maharashtra-politics-marathi-news-1378004</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>'Modi Govt Selling Dreams Of 2047, Ignoring Present': Rahul Gandhi Slams Centre After Maharashtra's Thane Train Tragedy</t>
+          <t>राजधानीत पावसाचा कहर! मुंबई विद्यापीठाचा परीक्षांबाबत तडकाफडकी मोठा निर्णय!</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/India/modi-govt-selling-dreams-of-2047-ignoring-present-rahul-gandhi-slams-centre-after-maharashtras-thane-train-tragedy/ar-AA1Gm3WY?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B0-%E0%A4%9C%E0%A4%A7-%E0%A4%A8-%E0%A4%A4-%E0%A4%AA-%E0%A4%B5%E0%A4%B8-%E0%A4%9A-%E0%A4%95%E0%A4%B9%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%B5-%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%AA-%E0%A4%A0-%E0%A4%9A-%E0%A4%AA%E0%A4%B0-%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%82%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%A4%E0%A4%A1%E0%A4%95-%E0%A4%AB%E0%A4%A1%E0%A4%95-%E0%A4%AE-%E0%A4%A0-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF/ar-AA1KKmSa</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Maha govt signs MoUs worth Rs 42,000 crore and creation of 28,000 jobs</t>
+          <t>22-kg Golden Kalash Installed at Sant Dnyaneshwar Temple, Crafted by Shripad Shankar Nagarkar Jewellers Pune</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/states-and-uts/maharashtra/maha-govt-signs-mous-worth-rs-42000-crore-and-creation-of-28000-jobs</t>
+          <t>https://www.aninews.in/news/business/22-kg-golden-kalash-installed-at-sant-dnyaneshwar-temple-crafted-by-shripad-shankar-nagarkar-jewellers-pune20250819111423/</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>NCP (SP) targets Maha minister over Rs 5,000 cr scam in Navi Mumbai’s CIDCO land; demands his resignation</t>
+          <t>MMRDA launches SCLR bridge, metro institute and flyovers to ease city commute</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/ncp-sp-targets-maha-minister-over-rs-5000-cr-scam-navi-mumbai-s-cidco-land-demands-his</t>
+          <t>https://propnewstime.com/getdetailsStories/MjA1NTQ=/mmrda-launches-sclr-bridge-metro-institute-and-flyovers-to-ease-city-commute</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>ट्रंप-ज़ेलेंस्की की बैठक से पहले रूसी राष्ट्रपति पुतिन ने उठाया ये कदम</t>
+          <t>Mumbai continues to be on red alert; heavy rain disrupts travel, shuts offices &amp; educational institutions</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/hindi/live/c23pr7x3kmgt?page=1</t>
+          <t>https://m.economictimes.com/news/weather/mumbai-on-red-alert-for-second-consecutive-day-heavy-rain-disrupts-travel-shuts-educational-institutions/articleshow/123375296.cms</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Satyapal Malik PM Modi, former governor Satyapal Malik breaking</t>
+          <t>Maha CM asks agencies to be on alert mode after heavy rainfall and flash floods</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>https://www.khabar24.tv/2025/08/05/satyapal-malik-pm-modi-former-governor-satyapal-malik-breaking-news/</t>
+          <t>https://www.lokmattimes.com/national/maha-cm-asks-agencies-to-be-on-alert-mode-after-heavy-rainfall-and-flash-floods/</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Maharashtra Rain Update: महाराष्ट्र में बारिश ने मचाई तबाही, अब तक सात लोगों की मौत, 200 ग्रामीण फंसे</t>
+          <t>Over ₹6.52 Crore Medical Aid Distributed To 5,000 Beneficiaries In Pune District</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
-        <is>
-          <t>https://www.ibc24.in/maharashtra/seven-people-died-due-to-rain-in-maharashtra-3213688.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="509">
-      <c r="A509" t="inlineStr">
-        <is>
-          <t>राज्यातील पूरस्थितीवर सरकारचे लक्ष, मदत कार्य सुरू – बावनकुळे</t>
-        </is>
-      </c>
-      <c r="B509" t="inlineStr">
-        <is>
-          <t>https://www.loksatta.com/nagpur/governments-attention-on-flood-situation-in-the-state-information-from-chandrashekhar-bawankule-amy-95-5313292/</t>
-        </is>
-      </c>
-    </row>
-    <row r="510">
-      <c r="A510" t="inlineStr">
-        <is>
-          <t>पूजेसाठी परवानगी नाही, नमाजसाठी जागाच जागा; कम्युनिस्टांचा हिंदुविरोधी चेहरा पुन्हा समोर</t>
-        </is>
-      </c>
-      <c r="B510" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/no-permission-for-worship-plenty-of-space-for-namaz-cpims-different-rules-for-hindus-and-muslims-in-kerala-the.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="511">
-      <c r="A511" t="inlineStr">
-        <is>
-          <t>Mumbai Rain LIVE Updates: मुंबईत सखल भागात साचलेल्या पाण्याचा निचरा</t>
-        </is>
-      </c>
-      <c r="B511" t="inlineStr">
-        <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/mumbai-rain-live-updates-18-august-imd-red-alert-in-mumbai-weather-waterlogging-traffic-jam-local-train-train-latest-updates-in-marathi-933169</t>
-        </is>
-      </c>
-    </row>
-    <row r="512">
-      <c r="A512" t="inlineStr">
-        <is>
-          <t>लोकसभेत जनविश्वास सुधारणा विधेयक सादर</t>
-        </is>
-      </c>
-      <c r="B512" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/public-trust-amendment-bill-introduced-in-lok-sabha.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="513">
-      <c r="A513" t="inlineStr">
-        <is>
-          <t>Red alert in Mumbai; BMC shuts all afternoon schools, colleges</t>
-        </is>
-      </c>
-      <c r="B513" t="inlineStr">
-        <is>
-          <t>https://www.newsbytesapp.com/news/india/mumbai-rain-havoc-to-continue-for-next-4-days/story</t>
-        </is>
-      </c>
-    </row>
-    <row r="514">
-      <c r="A514" t="inlineStr">
-        <is>
-          <t>Nanded Rain: नांदेड़ में भारी बारिश के बाद 200 लोग बाढ़ में फंसे! बादल फटने से 5 लापता, रेस्क्यू के लिए सेना बुलाई गई</t>
-        </is>
-      </c>
-      <c r="B514" t="inlineStr">
-        <is>
-          <t>https://hindi.moneycontrol.com/india/heavy-rains-in-maharashtra-nanded-leave-over-200-stranded-in-flood-waters-five-people-missing-article-2104052.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="515">
-      <c r="A515" t="inlineStr">
-        <is>
-          <t>Historic Sword of Raghuji Bhonsle Returns to Mumbai, To Be Unveiled in Grand Ceremony</t>
-        </is>
-      </c>
-      <c r="B515" t="inlineStr">
-        <is>
-          <t>https://thelivenagpur.com/2025/08/18/historic-sword-of-raghuji-bhonsle-returns-to-mumbai-to-be-unveiled-in-grand-ceremony/</t>
-        </is>
-      </c>
-    </row>
-    <row r="516">
-      <c r="A516" t="inlineStr">
-        <is>
-          <t>Parikrama</t>
-        </is>
-      </c>
-      <c r="B516" t="inlineStr">
-        <is>
-          <t>https://www.newsonair.gov.in/bulletins-detail/parikrama-471/</t>
-        </is>
-      </c>
-    </row>
-    <row r="517">
-      <c r="A517" t="inlineStr">
-        <is>
-          <t>What happened in the Trump-Putin meeting? | Chandrashekhar Nene Maha MTB</t>
-        </is>
-      </c>
-      <c r="B517" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/what-happened-in-the-trump-putin-meeting-chandrashekhar-nene-maha-mtb.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="518">
-      <c r="A518" t="inlineStr">
-        <is>
-          <t>Upcoming ‘Third Mumbai’ will spur economic growth, says Maharashtra chief minister</t>
-        </is>
-      </c>
-      <c r="B518" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/upcoming-third-mumbai-will-spur-economic-growth-says-maharashtra-chief-minister/articleshow/123368667.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="519">
-      <c r="A519" t="inlineStr">
-        <is>
-          <t>IBM to support Maharashtra in developing quantum computing initiative</t>
-        </is>
-      </c>
-      <c r="B519" t="inlineStr">
-        <is>
-          <t>https://www.communicationstoday.co.in/ibm-to-support-maharashtra-in-developing-quantum-computing-initiative/</t>
-        </is>
-      </c>
-    </row>
-    <row r="520">
-      <c r="A520" t="inlineStr">
-        <is>
-          <t>Heavy rainfall causes 7 deaths, crop loss in Maharashtra as alerts continue</t>
-        </is>
-      </c>
-      <c r="B520" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/heavy-rainfall-causes-7-deaths-crop-loss-in-maharashtra-as-alerts-continue/articleshow/123368187.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="521">
-      <c r="A521" t="inlineStr">
-        <is>
-          <t>Rain fury leaves 7 dead in Maharashtra, 200 villagers stranded</t>
-        </is>
-      </c>
-      <c r="B521" t="inlineStr">
-        <is>
-          <t>https://www.ptinews.com/story/national/rain-fury-leaves-7-dead-in-maharashtra,-200-villagers-stranded/2834213</t>
-        </is>
-      </c>
-    </row>
-    <row r="522">
-      <c r="A522" t="inlineStr">
-        <is>
-          <t>CREDAI-MCHI appoints Sukhraj Nahar as 18th President</t>
-        </is>
-      </c>
-      <c r="B522" t="inlineStr">
-        <is>
-          <t>https://housing.com/news/credai-mchi-appoints-sukhraj-nahar-as-president/</t>
-        </is>
-      </c>
-    </row>
-    <row r="523">
-      <c r="A523" t="inlineStr">
-        <is>
-          <t>Mumbai gets 177mm rain in 6-8 hour period, says CM; all agencies asked to remain alert</t>
-        </is>
-      </c>
-      <c r="B523" t="inlineStr">
-        <is>
-          <t>https://m.economictimes.com/news/india/mumbai-gets-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/articleshow/123365291.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="524">
-      <c r="A524" t="inlineStr">
-        <is>
-          <t>Mumbai reels under 177 mm rain in 8 hours; flights hit, schools shut as red alert issued</t>
-        </is>
-      </c>
-      <c r="B524" t="inlineStr">
-        <is>
-          <t>https://www.newindianexpress.com/nation/2025/Aug/18/mumbai-rains-flight-operations-hit-schools-colleges-shut-as-imd-issues-red-alert</t>
-        </is>
-      </c>
-    </row>
-    <row r="525">
-      <c r="A525" t="inlineStr">
-        <is>
-          <t>Mumbai rains: Heavy showers flood roads, railway tracks; bring city to standstill - video</t>
-        </is>
-      </c>
-      <c r="B525" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/india/mumbai-rains-heavy-showers-flood-roads-railway-tracks-bring-city-to-standstill-video/articleshow/123362740.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="526">
-      <c r="A526" t="inlineStr">
-        <is>
-          <t>Mumbai rains: Torrential downpour cripples normal life, roads flooded — in pics</t>
-        </is>
-      </c>
-      <c r="B526" t="inlineStr">
-        <is>
-          <t>https://www.livemint.com/photos/mumbai-rains-torrential-downpour-cripples-normal-life-train-services-hit-roads-flooded-see-pics-11755525808666.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="527">
-      <c r="A527" t="inlineStr">
-        <is>
-          <t>Rain fury: 5 missing, 200 stranded in Nanded; local trains, flights hit in Mumbai</t>
-        </is>
-      </c>
-      <c r="B527" t="inlineStr">
-        <is>
-          <t>https://odishatv.in/news/national/rain-fury-5-missing-200-stranded-in-nanded-local-trains-flights-hit-in-mumbai-270189</t>
-        </is>
-      </c>
-    </row>
-    <row r="528">
-      <c r="A528" t="inlineStr">
-        <is>
-          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by Maharashtra CM Devendra Fadnavis</t>
-        </is>
-      </c>
-      <c r="B528" t="inlineStr">
-        <is>
-          <t>https://aninews.in/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322/</t>
-        </is>
-      </c>
-    </row>
-    <row r="529">
-      <c r="A529" t="inlineStr">
-        <is>
-          <t>Mumbai rains: Heavy rainfall batter city as Vihar lake overflows</t>
-        </is>
-      </c>
-      <c r="B529" t="inlineStr">
-        <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-rains-heavy-rainfall-batter-city-as-vihar-lake-overflows-23590062</t>
-        </is>
-      </c>
-    </row>
-    <row r="530">
-      <c r="A530" t="inlineStr">
-        <is>
-          <t>Mumbai Rains : पुढचे १२ तास महत्त्वाचे; समुद्राला येणार मोठी भरती, मुंबईकरांनो, काळजी घ्या !</t>
-        </is>
-      </c>
-      <c r="B530" t="inlineStr">
-        <is>
-          <t>https://www.marathi.hindusthanpost.com/social/mumbai-rains-the-next-12-hours-high-tide/</t>
-        </is>
-      </c>
-    </row>
-    <row r="531">
-      <c r="A531" t="inlineStr">
-        <is>
-          <t>Mumbai-Pune Latest Rain Updates Maharashtra: दिवसभरातील महत्त्वाच्या घडामोडी वाचा एका क्लिकवर</t>
-        </is>
-      </c>
-      <c r="B531" t="inlineStr">
-        <is>
-          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-19-august-2025-rahul-gandhi-election-commission-maharashtra-rain-mumabai-rain-local-body-election-nandani-elephant-vantara-gujarat-shravan-weather-update-imd-kokan-pune-mumbai-us-president-donald-trump-supreme-court-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-pm-narendra-modi-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
-        </is>
-      </c>
-    </row>
-    <row r="532">
-      <c r="A532" t="inlineStr">
-        <is>
-          <t>Mumbai Rain Update : मुंबईत धो-धो! वाहतुकीचा खोळंबा, लोकलसेवेला फटका; मुंबईकरांची पुरती दैना; पुढील 48 तासही धोक्याचे</t>
-        </is>
-      </c>
-      <c r="B532" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-rain-update-heavy-rainfall-started-in-city-resulted-in-disruption-of-life-and-mumbai-local-cm-fadnavis-reviewed/articleshow/123363662.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="533">
-      <c r="A533" t="inlineStr">
-        <is>
-          <t>Mumbai Rains: Maharashtra CM Says 'Observe Precautions', Warns Of Heavy Rainfall, High Tide Check BMC's Advisory</t>
-        </is>
-      </c>
-      <c r="B533" t="inlineStr">
-        <is>
-          <t>https://menafn.com/1109945394/Mumbai-Rains-Maharashtra-CM-Says-Observe-Precautions-Warns-Of-Heavy-Rainfall-High-Tide-Check-BMCs-Advisory</t>
-        </is>
-      </c>
-    </row>
-    <row r="534">
-      <c r="A534" t="inlineStr">
-        <is>
-          <t>IndiGo Airlines issues travel advisory for passengers flying out of Mumbai due to heavy rainfall, waterlogging in the city</t>
-        </is>
-      </c>
-      <c r="B534" t="inlineStr">
-        <is>
-          <t>https://newsroompost.com/india/indigo-airlines-issues-travel-advisory-for-passengers-flying-out-of-mumbai-due-to-heavy-rainfall-waterlogging-in-the-city/5347388.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="535">
-      <c r="A535" t="inlineStr">
-        <is>
-          <t>तिसरी MUMBAI आर्थिक विकासाचा नवा अध्याय, गोल्डमन सॅक्सच्या नव्या मुंबई कार्यालयाचे उद्घाटन</t>
-        </is>
-      </c>
-      <c r="B535" t="inlineStr">
-        <is>
-          <t>https://www.timemaharashtra.com/maharashtra/mumbai/third-mumbai-a-new-chapter-in-economic-development-goldman-sachs-new-mumbai-office-inaugurated/129385/</t>
-        </is>
-      </c>
-    </row>
-    <row r="536">
-      <c r="A536" t="inlineStr">
-        <is>
-          <t>Mumbai Rains Updates: मुंबईकरांनो पुढील 12 तास अतिशय महत्त्वाचे, CM फडणवीसांनी केले हे आवाहन</t>
-        </is>
-      </c>
-      <c r="B536" t="inlineStr">
-        <is>
-          <t>https://marathi.ndtv.com/maharashtra/mumbai-rains-update-next-12-hours-are-important-for-mumbai-7-people-died-across-state-in-2-days-cm-fadnavis-appeals-to-citizens-9109288</t>
-        </is>
-      </c>
-    </row>
-    <row r="537">
-      <c r="A537" t="inlineStr">
-        <is>
-          <t>राष्ट्रीय: मुंबई में भारी बारिश के बीच सुचारू रूप से चल रही मेट्रो, सीएम फडणवीस ने की तारीफ</t>
-        </is>
-      </c>
-      <c r="B537" t="inlineStr">
-        <is>
-          <t>https://www.bhaskarhindi.com/other/news-1174019</t>
-        </is>
-      </c>
-    </row>
-    <row r="538">
-      <c r="A538" t="inlineStr">
-        <is>
-          <t>रघुजीराजे भोसले यांची तलवार मुंबईत शौर्याचा वारसा इतिहाप्रेमींसाठी खुला; मराठा साम्राज्याचा वारसा परत मिळवण्याचा प्रयत्न – मुख्यमंत्री</t>
-        </is>
-      </c>
-      <c r="B538" t="inlineStr">
-        <is>
-          <t>https://www.saamana.com/raghujiraje-bhosale-sword-a-legacy-of-bravery-is-open-to-history-lovers-in-mumbai-an-attempt-to-reclaim-the-legacy-of-the-maratha-empire-said-by-chief-minister-devendra-fadnavis/</t>
-        </is>
-      </c>
-    </row>
-    <row r="539">
-      <c r="A539" t="inlineStr">
-        <is>
-          <t>Mumbai Rains : गुडघाभर पाणी, समोर रस्ताही दिसेना, लोकल रखडल्या आठवड्याच्या सुरुवातीला पावसानं मुंबईकरांची दाणादाण, पहा PHOTO</t>
-        </is>
-      </c>
-      <c r="B539" t="inlineStr">
-        <is>
-          <t>https://marathi.asianetnews.com/mumbai/mumbai-heavy-rain-waterlogging-local-delays-school-shutdown/photoshow-at2tgam</t>
-        </is>
-      </c>
-    </row>
-    <row r="540">
-      <c r="A540" t="inlineStr">
-        <is>
-          <t>Mumbai Rain Alert:मुंबईत पावसाची धुवाँधार बॅटिंग;शाळांना सुट्टी जाहीर</t>
-        </is>
-      </c>
-      <c r="B540" t="inlineStr">
-        <is>
-          <t>https://ilovenagar.com/mumbai-rain-alert-schools-declare-holiday-today/</t>
-        </is>
-      </c>
-    </row>
-    <row r="541">
-      <c r="A541" t="inlineStr">
-        <is>
-          <t>'Third Mumbai' to boost metropolitan region development Fadnavis</t>
-        </is>
-      </c>
-      <c r="B541" t="inlineStr">
-        <is>
-          <t>https://www.theweek.in/wire-updates/business/2025/08/19/bom3-mh-third-mumbai-cm.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="542">
-      <c r="A542" t="inlineStr">
-        <is>
-          <t>Nanded rains latest UPDATES: Water from Karnataka reach district; Indian Army, SDRF deployed for rescue missions as villagers trapped</t>
-        </is>
-      </c>
-      <c r="B542" t="inlineStr">
-        <is>
-          <t>https://www.theweek.in/news/india/2025/08/18/mumbai-rain-news-nanded-rains-latest-updates-water-from-karnataka-reach-district-indian-army-sdrf-deployed-for-rescue-missions-and-villagers-trapped.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="543">
-      <c r="A543" t="inlineStr">
-        <is>
-          <t>Transformative Leadership: Sukhraj Nahar Steers CREDAI-MCHI Towards Urban Revolution</t>
-        </is>
-      </c>
-      <c r="B543" t="inlineStr">
-        <is>
-          <t>https://www.devdiscourse.com/article/business/3545330-transformative-leadership-sukhraj-nahar-steers-credai-mchi-towards-urban-revolution</t>
-        </is>
-      </c>
-    </row>
-    <row r="544">
-      <c r="A544" t="inlineStr">
-        <is>
-          <t>‘लाडकी बहीन’ के बाद ‘लाडकी सुनबाई’… क्या है ये नई योजना, जिसका डिप्टी सीएम ने किया ऐलान</t>
-        </is>
-      </c>
-      <c r="B544" t="inlineStr">
-        <is>
-          <t>https://www.patrika.com/mumbai-news/maharashtra-after-ladki-bahin-now-ladki-sunbai-yojana-announced-how-this-benefits-to-women-19873910</t>
-        </is>
-      </c>
-    </row>
-    <row r="545">
-      <c r="A545" t="inlineStr">
-        <is>
-          <t>LGEC 2025: 'लाडकी बहीण' योजनेमुळे महाराष्ट्रातील अर्थव्यवस्थेला चालनाच मिळाली; सुनील तटकरेंनी समजावलं 'गणित'</t>
-        </is>
-      </c>
-      <c r="B545" t="inlineStr">
-        <is>
-          <t>https://www.lokmat.com/international/lgec-2025-ladki-bahin-scheme-has-given-a-boost-to-the-economy-of-maharashtra-sunil-tatkare-rahul-narvekar-explained-a-a629/</t>
-        </is>
-      </c>
-    </row>
-    <row r="546">
-      <c r="A546" t="inlineStr">
-        <is>
-          <t>803 Families Stranded as Lokmanya Nagar Redevelopment Hits Political Roadblock</t>
-        </is>
-      </c>
-      <c r="B546" t="inlineStr">
-        <is>
-          <t>https://punemirror.com/city/civic/803-families-stranded-as-lokmanya-nagar-redevelopment-hits-political-roadblock/</t>
-        </is>
-      </c>
-    </row>
-    <row r="547">
-      <c r="A547" t="inlineStr">
-        <is>
-          <t>Marathi News Headlines | 2 PM | News18 Lokmat | 18 Aug 2025 | Maharashtra Rain Update | Mumbai Rain</t>
-        </is>
-      </c>
-      <c r="B547" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/mr-in/news/other/marathi-news-headlines-2-pm-news18-lokmat-18-aug-2025-maharashtra-rain-update-mumbai-rain/vi-AA1KIyNJ?ocid=hpmsn</t>
-        </is>
-      </c>
-    </row>
-    <row r="548">
-      <c r="A548" t="inlineStr">
-        <is>
-          <t>मुंबई में भारी बारिश का कहर, 19 अगस्त को बंद रहेंगे सभी स्कूल-कॉलेज</t>
-        </is>
-      </c>
-      <c r="B548" t="inlineStr">
-        <is>
-          <t>https://hindi.news24online.com/india/mumbai-and-jammu-kashmir-heavy-rain-rain-school-and-college-closed/1288306/</t>
-        </is>
-      </c>
-    </row>
-    <row r="549">
-      <c r="A549" t="inlineStr">
-        <is>
-          <t>Mumbai Rains: भारी बारिश का कहर, 7 की मौत, आदित्य ठाकरे ने BMC पर लगाए आरोप</t>
-        </is>
-      </c>
-      <c r="B549" t="inlineStr">
-        <is>
-          <t>https://www.thesandeshwahak.com/mumbai-rains-heavy-rain-wreaks-havoc-7-dead-aditya-thackeray-blames-bmc/</t>
-        </is>
-      </c>
-    </row>
-    <row r="550">
-      <c r="A550" t="inlineStr">
-        <is>
-          <t>ABP Majha Top 10 Headlines : ABP माझा टॉप 10 हेडलाईन्स | 18 ऑगस्ट 2025 | सोमवार</t>
-        </is>
-      </c>
-      <c r="B550" t="inlineStr">
-        <is>
-          <t>https://marathi.abplive.com/news/maharashtra/abp-majha-top-10-headlines-18-august-2025-monday-latest-marathi-news-update-maharashtra-politics-marathi-news-1378004</t>
-        </is>
-      </c>
-    </row>
-    <row r="551">
-      <c r="A551" t="inlineStr">
-        <is>
-          <t>श्रीमती प्रज्ञा वाळकेंचा भ्रष्टाचारामध्ये उच्चांक ; सरकारविरोधी चळवळीतीही सक्रिय सहभाग ?</t>
-        </is>
-      </c>
-      <c r="B551" t="inlineStr">
-        <is>
-          <t>https://lokmanthan.com/mrs-pragya-walkens-high-score-in-corruption-active-participation-in-anti-government-movement/</t>
-        </is>
-      </c>
-    </row>
-    <row r="552">
-      <c r="A552" t="inlineStr">
-        <is>
-          <t>Nanded Rain : नांदेडमध्ये ढगफुटीसदृष्य पाऊस; 200 लोक अडकले, 5 जण दगावल्याची भीती, लष्कराला पाचारण</t>
-        </is>
-      </c>
-      <c r="B552" t="inlineStr">
-        <is>
-          <t>https://www.marathijagran.com/maharashtra/chhatrapati-sambhajinagar/nanded-heavy-rain-over-200-stranded-after-heavy-rains-army-called-in-for-rescue-89509</t>
-        </is>
-      </c>
-    </row>
-    <row r="553">
-      <c r="A553" t="inlineStr">
-        <is>
-          <t>Maharashtra Rain: महाराष्ट्र में तेज बारिश से हाल बेहाल, 2 दिनों में 7 की मौत, मुंबई समेत कई इलाकों में स्कूल-कॉलेज बंद</t>
-        </is>
-      </c>
-      <c r="B553" t="inlineStr">
-        <is>
-          <t>https://www.republicbharat.com/india/maharashtra-rain-7-died-in-2-days-schools-and-colleges-closed-in-many-areas-including-mumbai</t>
-        </is>
-      </c>
-    </row>
-    <row r="554">
-      <c r="A554" t="inlineStr">
-        <is>
-          <t>Crop Loss: महाराष्‍ट्र में बारिश ने किया किसानों को बर्बाद, विदर्भ से लेकर मराठवाड़ा तक फसलें चौपट</t>
-        </is>
-      </c>
-      <c r="B554" t="inlineStr">
-        <is>
-          <t>https://www.kisantak.in/crops/story/heavy-rains-in-maharashtra-cause-huge-damage-to-farmers-after-crop-loss-and-land-submerged-in-water-1263471-2025-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="555">
-      <c r="A555" t="inlineStr">
-        <is>
-          <t>महाराष्ट्र में बाढ़ का कहर: मुंबई समेत राज्यभर में मूसलाधार बारिश, नांदेड़ में 5 लोग बहे</t>
-        </is>
-      </c>
-      <c r="B555" t="inlineStr">
-        <is>
-          <t>https://hindi.asianetnews.com/state/maharashtra/maharashtra-floods-2025-nanded-latur-beed-rescue-update/articleshow-43f4xn3</t>
-        </is>
-      </c>
-    </row>
-    <row r="556">
-      <c r="A556" t="inlineStr">
-        <is>
-          <t>आज का मौसम, 19 अगस्‍त: मुंबई में भारी बारिश से हालात बदतर; स्कूल-कॉलेज बंद! दिल्ली में बाढ़ का खतरा, जानें बाकी राज्यों का हाल</t>
-        </is>
-      </c>
-      <c r="B556" t="inlineStr">
-        <is>
-          <t>https://hindi.etnownews.com/news/mumbai-rain-alert-delhi-yamuna-flood-imd-weather-forecast-heavy-rainfall-india-article-152485258</t>
-        </is>
-      </c>
-    </row>
-    <row r="557">
-      <c r="A557" t="inlineStr">
-        <is>
-          <t>मुंबई में भारी बारिश से हालात खराब, 19 अगस्त को स्कूल-कॉलेज रहेंगे बंद, IMD के रेड अलर्ट के बाद आया BMC का आदेश</t>
-        </is>
-      </c>
-      <c r="B557" t="inlineStr">
-        <is>
-          <t>https://www.theindiadaily.com/india/mumbai-civic-body-declares-holiday-for-all-schools-and-colleges-on-august-19-amid-heavy-rain-forecast-news-90572</t>
-        </is>
-      </c>
-    </row>
-    <row r="558">
-      <c r="A558" t="inlineStr">
-        <is>
-          <t>Mumbai heavy Rain: ट्रेन से लेकर प्लेन तक, मुंबई में भारी बारिश ने बिगाड़ा काम, बाहर निकलना दुस्वार, अगले 4 दिनों तक रहेगा यही हाल</t>
-        </is>
-      </c>
-      <c r="B558" t="inlineStr">
-        <is>
-          <t>https://www.theindiadaily.com/india/maharashtra-mumbai-heavy-rain-in-several-cities-local-train-to-flight-affecting-imd-alert-for-next-coming-4-days-news-90608</t>
-        </is>
-      </c>
-    </row>
-    <row r="559">
-      <c r="A559" t="inlineStr">
-        <is>
-          <t>'Positive about bringing a law to protect advocates:' Maharashtra CM Fadnavis</t>
-        </is>
-      </c>
-      <c r="B559" t="inlineStr">
-        <is>
-          <t>https://legal.economictimes.indiatimes.com/amp/news/industry/positive-about-bringing-a-law-to-protect-advocates-maharashtra-cm-fadnavis/123378199</t>
-        </is>
-      </c>
-    </row>
-    <row r="560">
-      <c r="A560" t="inlineStr">
-        <is>
-          <t>Rain wreaks havoc in Maharashtra, brings Mumbai to a standstill</t>
-        </is>
-      </c>
-      <c r="B560" t="inlineStr">
-        <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/rain-wreaks-havoc-in-maharashtra-brings-mumbai-to-a-standstill/article69948564.ece</t>
-        </is>
-      </c>
-    </row>
-    <row r="561">
-      <c r="A561" t="inlineStr">
-        <is>
-          <t>Mumbai rains: BMC announces holiday for schools, colleges on August 19</t>
-        </is>
-      </c>
-      <c r="B561" t="inlineStr">
-        <is>
-          <t>https://www.cnbctv18.com/india/are-mumbai-schools-colleges-open-or-close-on-august-19-19655564.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="562">
-      <c r="A562" t="inlineStr">
-        <is>
-          <t>India monsoon updates: Heavy to very heavy rainfall at few places in Mumbai; residents told to ‘avoid unnecessary travel’</t>
-        </is>
-      </c>
-      <c r="B562" t="inlineStr">
-        <is>
-          <t>https://www.thehindu.com/news/national/india-monsoon-live-mumbai-rains-yamuna-river-flood-alert-delhi-kashmir-cloudburst-updates-august-18/article69946105.ece</t>
-        </is>
-      </c>
-    </row>
-    <row r="563">
-      <c r="A563" t="inlineStr">
-        <is>
-          <t>Mumbai Rains News LIVE Updates: Offices, Schools Shut Amid Red Alert, 14 Flights Delayed, Traffic Hit</t>
-        </is>
-      </c>
-      <c r="B563" t="inlineStr">
-        <is>
-          <t>https://www.timesnownews.com/mumbai/mumbai-rains-news-live-pune-weather-lake-levels-local-train-status-traffic-imd-forecast-waterlogging-schools-closed-red-alert-liveblog-152480215</t>
-        </is>
-      </c>
-    </row>
-    <row r="564">
-      <c r="A564" t="inlineStr">
-        <is>
-          <t>Heavy rains lash Mumbai; red alert issued, Vihar Lake overflows, CM urges caution</t>
-        </is>
-      </c>
-      <c r="B564" t="inlineStr">
-        <is>
-          <t>https://www.thehindu.com/news/cities/mumbai/mumbai-rain-updates-august-18-2025/article69946286.ece</t>
-        </is>
-      </c>
-    </row>
-    <row r="565">
-      <c r="A565" t="inlineStr">
-        <is>
-          <t>Mumbai on red alert; BMC declares holiday for schools, colleges on August 19</t>
-        </is>
-      </c>
-      <c r="B565" t="inlineStr">
-        <is>
-          <t>https://m.economictimes.com/news/india/bmc-declares-holiday-for-mumbai-schools-colleges-on-august-19-as-city-braces-for-heavy-rain/articleshow/123366693.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="566">
-      <c r="A566" t="inlineStr">
-        <is>
-          <t>Mumbai Rains Live News: Torrential rains cripple Mumbai; roads flooded, local trains delayed and schools, colleges closed amid ‘Red’ alert</t>
-        </is>
-      </c>
-      <c r="B566" t="inlineStr">
-        <is>
-          <t>https://www.thehindubusinessline.com/news/mumbai-weather-mumbai-rains-live-news-updates/article69946123.ece</t>
-        </is>
-      </c>
-    </row>
-    <row r="567">
-      <c r="A567" t="inlineStr">
-        <is>
-          <t>Rainfall Alert: All schools and colleges closed due to heavy rains, IMD issued red alert</t>
-        </is>
-      </c>
-      <c r="B567" t="inlineStr">
-        <is>
-          <t>https://www.informalnewz.com/rainfall-alert-all-schools-and-colleges-closed-due-to-heavy-rains-imd-issued-red-alert/</t>
-        </is>
-      </c>
-    </row>
-    <row r="568">
-      <c r="A568" t="inlineStr">
-        <is>
-          <t>18.08.2025 : मुख्यमंत्री देवेंद्र फडणवीस व सांस्कृतिक कार्य मंत्री आशिष शेलार यांनी घेतली राज्यपालांची भेट</t>
-        </is>
-      </c>
-      <c r="B568" t="inlineStr">
-        <is>
-          <t>https://rajbhavan-maharashtra.gov.in/18-08-2025-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB/</t>
-        </is>
-      </c>
-    </row>
-    <row r="569">
-      <c r="A569" t="inlineStr">
-        <is>
-          <t>Mumbai: मराठा सेनापति रघुजी भोंसले की तलवार मुंबई लाई गई, लंदन में हुई नीलामी में महाराष्ट्र सरकार ने हासिल की</t>
-        </is>
-      </c>
-      <c r="B569" t="inlineStr">
-        <is>
-          <t>https://www.amarujala.com/india-news/maratha-general-raghuji-bhonsle-sword-brought-to-mumbai-maharashtra-government-acquired-in-auction-2025-08-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="570">
-      <c r="A570" t="inlineStr">
-        <is>
-          <t>महाराष्ट्रात महाभयानक पाऊस! मुख्यमंत्री देवेंद्र फडणवीस यांनी तातडीने साधला शेजारील राज्यांशी संपर्क? कारण अतिशय चिंताजनक</t>
-        </is>
-      </c>
-      <c r="B570" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%AE%E0%A4%B9-%E0%A4%AD%E0%A4%AF-%E0%A4%A8%E0%A4%95-%E0%A4%AA-%E0%A4%8A%E0%A4%B8-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A4-%E0%A4%A4%E0%A4%A1-%E0%A4%A8%E0%A5%87-%E0%A4%B8-%E0%A4%A7%E0%A4%B2-%E0%A4%B6%E0%A5%87%E0%A4%9C-%E0%A4%B0-%E0%A4%B2-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B6-%E0%A4%B8%E0%A4%82%E0%A4%AA%E0%A4%B0%E0%A5%8D%E0%A4%95-%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%85%E0%A4%A4-%E0%A4%B6%E0%A4%AF-%E0%A4%9A-%E0%A4%82%E0%A4%A4-%E0%A4%9C%E0%A4%A8%E0%A4%95/ar-AA1KJav3</t>
-        </is>
-      </c>
-    </row>
-    <row r="571">
-      <c r="A571" t="inlineStr">
-        <is>
-          <t>न्यायिक सेवा स्पर्धा परीक्षेसाठी सीईटी २०२५ जाहीर</t>
-        </is>
-      </c>
-      <c r="B571" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/cet-2025-announced-for-judicial-services-competitive-examination.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="572">
-      <c r="A572" t="inlineStr">
-        <is>
-          <t>सामाजिक कामात कार्यरत राहून मिळणारा आनंद मोठा: पांडुरंग चोरमले</t>
-        </is>
-      </c>
-      <c r="B572" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/the-joy-of-working-in-social-work-is-immense-pandurang-chormale.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="573">
-      <c r="A573" t="inlineStr">
-        <is>
-          <t>शाळा अंतर्गत फेरीमध्ये विद्यार्थ्यांचा सत्कार सोहळा</t>
-        </is>
-      </c>
-      <c r="B573" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/student-felicitation-ceremony-during-the-schools-internal-parade.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="574">
-      <c r="A574" t="inlineStr">
-        <is>
-          <t>School holiday: मुंबईत पावसामुळे शाळांना सुटी जाहीर, पुढील ४८ तासांचा अतिवृष्टीचा इशारा; काळजी घेण्याचे आवाहन</t>
-        </is>
-      </c>
-      <c r="B574" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/career/career-news/school-holiday-in-mumbai-due-to-rain-heavy-rainfall-alert-for-the-next-48-hours/articleshow/123357322.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="575">
-      <c r="A575" t="inlineStr">
-        <is>
-          <t>देशभर में बारिश का कहर: मुंबई-बेहद जाम, दिल्ली में यमुना उफान पर, स्कूल-कॉलेज बंद</t>
-        </is>
-      </c>
-      <c r="B575" t="inlineStr">
-        <is>
-          <t>https://dainikdehat.com/india/rain-wreaks-havoc-across-the-country-mumbai-is-jam-packed-yamuna-is-in-spate-in-delhi-schools-and-colleges-are-closed/</t>
-        </is>
-      </c>
-    </row>
-    <row r="576">
-      <c r="A576" t="inlineStr">
-        <is>
-          <t>Maharashtra Rain : राज्यात पावसाचा हाहाकार, ‘या’ जिल्ह्यांत रेड अलर्ट जारी, शाळांना सुट्ट्या</t>
-        </is>
-      </c>
-      <c r="B576" t="inlineStr">
-        <is>
-          <t>https://hellokrushi.com/maharashtra-rain-updates-on-19-august-2025/</t>
-        </is>
-      </c>
-    </row>
-    <row r="577">
-      <c r="A577" t="inlineStr">
-        <is>
-          <t>Mumbai Rain: मुंबई में भारी बारिश का कहर, मुंबई में जलभराव, दिल्ली में यमुना उफान पर, कई राज्यों में बाढ़ का अलर्ट</t>
-        </is>
-      </c>
-      <c r="B577" t="inlineStr">
-        <is>
-          <t>https://kadwaghut.com/mumbai-rain-heavy-rains-in-mumbai/</t>
-        </is>
-      </c>
-    </row>
-    <row r="578">
-      <c r="A578" t="inlineStr">
-        <is>
-          <t>Mumbai Rains News: भारी बारिश के चलते कल मुंबई के स्कूल-कॉलेजों में छुट्टी, नांदेड़ में 7 लोगों की मौत, CM फडणवीस ने की आपात बैठक</t>
-        </is>
-      </c>
-      <c r="B578" t="inlineStr">
-        <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/heavy-rains-in-mumbai-schools-colleges-closed-7-deaths-in-maharashtra-5-missing-nanded-cm-fadnavis-emergency-meeting/articleshow/123366462.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="579">
-      <c r="A579" t="inlineStr">
-        <is>
-          <t>Mumbai Rains: मुंबई में भारी बारिश से हाहाकार! स्कूल-कॉलेज बंद, IMD ने जारी किया रेड अलर्ट</t>
-        </is>
-      </c>
-      <c r="B579" t="inlineStr">
-        <is>
-          <t>https://hindi.moneycontrol.com/india/mumbai-rains-updates-imd-alert-schools-colleges-closed-as-imd-issues-red-alert-flights-delayed-article-2105260.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="580">
-      <c r="A580" t="inlineStr">
-        <is>
-          <t>Maharashtra Rain Update: 19 ऑगस्टलाही सावधान..., महाराष्ट्रातील 'या' जिल्ह्यांना रेड अलर्ट</t>
-        </is>
-      </c>
-      <c r="B580" t="inlineStr">
-        <is>
-          <t>https://www.navarashtra.com/maharashtra/mahrashtra-mumbai-rain-latest-update-orange-alert-till-august-20-red-alert-issued-in-several-districts-963438.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="581">
-      <c r="A581" t="inlineStr">
-        <is>
-          <t>Mumbai Rain Update: मुंबईत पुढील चार तास धो-धो, रेड अलर्ट जारी, लोकल ट्रेन उशिराने, नागरिकांना घराबाहेर न पडण्याचं आवाहन</t>
-        </is>
-      </c>
-      <c r="B581" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-heavy-rain-expected-by-imd-red-alert-heavy-rainfall-local-train-updates/articleshow/123376293.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="582">
-      <c r="A582" t="inlineStr">
-        <is>
-          <t>महाराष्ट्र में बारिश का कहर, मुंबई विश्वविद्यालय की परीक्षाएं स्थगित, कई जिलों में स्कूल बंद</t>
-        </is>
-      </c>
-      <c r="B582" t="inlineStr">
-        <is>
-          <t>https://mpbreakingnews.in/maharashtra/mumbai-university-heavy-rain-maharashtra-schools-closed-54-804125</t>
-        </is>
-      </c>
-    </row>
-    <row r="583">
-      <c r="A583" t="inlineStr">
-        <is>
-          <t>MMRDA launches SCLR bridge, metro institute and flyovers to ease city commute</t>
-        </is>
-      </c>
-      <c r="B583" t="inlineStr">
-        <is>
-          <t>https://propnewstime.com/getdetailsStories/MjA1NTQ=/mmrda-launches-sclr-bridge-metro-institute-and-flyovers-to-ease-city-commute</t>
-        </is>
-      </c>
-    </row>
-    <row r="584">
-      <c r="A584" t="inlineStr">
-        <is>
-          <t>Maha CM asks agencies to be on alert mode after heavy rainfall and flash floods</t>
-        </is>
-      </c>
-      <c r="B584" t="inlineStr">
-        <is>
-          <t>https://www.lokmattimes.com/national/maha-cm-asks-agencies-to-be-on-alert-mode-after-heavy-rainfall-and-flash-floods/</t>
-        </is>
-      </c>
-    </row>
-    <row r="585">
-      <c r="A585" t="inlineStr">
-        <is>
-          <t>Over ₹6.52 Crore Medical Aid Distributed To 5,000 Beneficiaries In Pune District</t>
-        </is>
-      </c>
-      <c r="B585" t="inlineStr">
         <is>
           <t>https://www.mypunepulse.com/over-%E2%82%B96-52-crore-medical-aid-distributed-to-5000-beneficiaries-in-pune-district/</t>
         </is>

--- a/Output/Devendra Fadnavis/extracted_links.xlsx
+++ b/Output/Devendra Fadnavis/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,6102 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>'Third Mumbai' to boost MMR's development, CM Devendra Fadnavis says</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/business/third-mumbai-to-boost-mmrs-development-cm-devendra-fadnavis-says-101755577376569.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Maharashtra CM Devendra Fadnavis seeks Opposition backing for Radhakrishnan</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-devendra-fadnavis-seeks-opposition-backing-for-radhakrishnan-23590051</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aurangzeb Tomb Row: VHP’s Statewide Protests Backed By RSS; CM Devendra Fadnavis Calls For Lawful Dismantling</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/en-in/news/India/aurangzeb-tomb-row-vhp-s-statewide-protests-backed-by-rss-cm-devendra-fadnavis-calls-for-lawful-dismantling/ar-AA1Bfmct?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by Maharashtra CM Devendra Fadnavis</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://www.tribuneindia.com/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://www.outlookbusiness.com/news/third-mumbai-to-boost-metropolitan-region-development-fadnavis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>'Positive about bringing a law to protect advocates:' Maharashtra CM Fadnavis</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>https://legal.economictimes.indiatimes.com/news/industry/positive-about-bringing-a-law-to-protect-advocates-maharashtra-cm-fadnavis/123378199</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Maha CM asks agencies to be on alert mode after heavy rainfall and flash floods</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>https://www.ap7am.com/en/107166/maha-cm-asks-agencies-to-be-on-alert-mode-after-heavy-rainfall-and-flash-floods</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Shiv Sena (UBT) Welcomes Radhakrishnan’s Nomination, Fadnavis Seeks All-Party Support</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://www.deccanchronicle.com/nation/shiv-sena-ubt-welcomes-rahakrishans-nomination-fadnavis-seeks-all-party-support-1898266</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Heavy rain lashes Marathwada; 5 missing in Nanded, says CM Devendra Fadnavis</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/mumbai/heavy-rain-lashes-marathwada-5-missing-in-nanded-says-cm-devendra-fadnavis-10196321/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Mumbai gets 300 mm rain in a day, Devendra Fadnavis warns next 48 hours critical</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>https://www.indiatoday.in/cities/mumbai/story/mumbai-heavy-rains-waterlogging-imd-red-alert-bmc-school-offices-holiday-work-from-home-2773291-2025-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Goldman Sachs opens new, expanded office in Mumbai</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/business/Industry/goldman-sachs-opens-new-expanded-office-in-mumbai/article69947256.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Third Mumbai: Fadnavis Boosts MMR Development</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>https://money.rediff.com/news/market/third-mumbai-fadnavis-boosts-mmr-development/32201020250818</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Fadnavis hails Maha Guv’s nomination as Vice Presidential candidate</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://www.thestatesman.com/india/fadnavis-hails-maha-guvs-nomination-as-vice-presidential-candidate-1503473264.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>VP Nominee CP Radhakrishnan Leaves for Delhi, Maha Yuti Leaders Pledge Support</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>https://www.deccanherald.com/india/maharashtra/vp-nominee-radhakrishnan-departs-for-delhi-maha-yuti-leaders-extend-support-3685392</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Devendra Fadnavis' first reaction to Raj Thackeray's reunion with Uddhav jibe</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>http://www.msn.com/en-in/news/india/devendra-fadnavis-first-reaction-to-raj-thackeray-s-reunion-with-uddhav-jibe/ar-AA1I1jzW?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Aakar Patel| New Maharashtra Security Law Open To Abuse, Threatens Rights; Say ‘No’ To It</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>https://www.deccanchronicle.com/opinion/columnists/aakar-patel-new-maharashtra-security-law-open-to-abuse-threatens-rights-say-no-to-it-1898276</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Sword of Raghuji Bhonsle Unveiled in Mumbai: ‘A Bridge Between Generations,’ Says CM Fadnavis</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/sword-of-raghuji-bhonsle-unveiled-in-mumbai-a-bridge-between-generations-says-cm-fadnavis/articleshow/123372524.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>NDA Vice President-Nominee CP Radhakrishnan Expresses Gratitude To PM Modi, Amit Shah &amp; Devendra Fadnavis After VP Nomination</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/en-in/news/India/nda-vice-president-nominee-cp-radhakrishnan-expresses-gratitude-to-pm-modi-amit-shah-devendra-fadnavis-after-vp-nomination/ar-AA1KGvyO</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>MNS Morcha: Raj Thackeray's party workers detained; CM Fadnavis says such experiments won’t work here</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/en-in/news/India/mns-morcha-raj-thackerays-party-workers-detained-cm-fadnavis-says-such-experiments-won-t-work-here/ar-AA1Iaint</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>‘Third Mumbai’ takes shape as CM Fadnavis unveils mega MMR expansion plan</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/city/third-mumbai-takes-shape-as-cm-fadnavis-unveils-mega-mmr-expansion-plan-article-13465350.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Cannot achieve affordable housing with ‘business as usual’ approach: Maharashtra CM Fadnavis tells...</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/news/business/real-estate/cannot-achieve-affordable-housing-with-business-as-usual-approach-maharashtra-cm-fadnavis-tells-realtors-13462328.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Heavy Rains Ravage State, CM Fadnavis Orders Relief, Surveys Rain-Hit Areas</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/heavy-rains-ravage-state-cm-fadnavis-orders-relief-surveys-rain-hit-areas/articleshow/123372550.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Those who speak of Maharashtra 'asmita' should support Radhakrishnan for VP post: Fadnavis</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>https://www.ptinews.com/story/national/those-who-speak-of-maharashtra-'asmita'-should-support-radhakrishnan-for-vp-post:-fadnavis/2832772</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Mumbai rains: Maharashtra CM says 'observe precautions', warns of heavy rainfall, high tide; check BMC's advisory</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>https://www.livemint.com/news/mumbai-rains-maharashtra-cm-says-observe-precautions-warns-of-heavy-rainfall-high-tide-check-bmcs-advisory-11755573270369.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>"Observe precaution": Maharashtra CM warns about severe weather conditions in state</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>https://www.aninews.in/news/national/general-news/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state20250819025510</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Third Mumbai in Raigad to become Maharashtra’s new economic powerhouse: CM Fadnavis</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>https://daijiworld.com/news/newsDisplay?newsID=1289652</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Mumbai received 177mm rain in just 6-8 hour period, says CM Fadnavis; more to come amid high tides</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/red-alert-for-mumbai-mumbai-got-177mm-rain-in-just-6-8-hour-period-says-cm-fadnavis-more-to-come-amid-high-tides-23589990</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Those who speak of Maharashtra ‘asmita’ should support Radhakrishnan for VP post: Fadnavis</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>https://theprint.in/india/those-who-speak-of-maharashtra-asmita-should-support-radhakrishnan-for-vp-post-fadnavis/2723344/?amp</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Fadnavis govt’s big Maratha pride push: Legendary sword it ‘bought’ back from London, with a Rs 47L bid</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>https://theprint.in/politics/fadnavis-govts-big-maratha-pride-push-legendary-sword-it-bought-back-from-london-with-a-rs-47l-bid/2723199/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Mumbai gets 177mm rain in 6-8 hour period, says CM; all agencies asked to remain alert</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/news/india/mumbai-gets-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/articleshow/123365291.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Raghuji Bhonsle’s sword brought to India</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>https://www.thehitavada.com/Encyc/2025/8/19/raghuji-bhonsles-sword-brought-to-india.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Rain fury leaves 7 dead in Maharashtra, 200 villagers stranded</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>https://www.ptinews.com/story/national/Rain-fury-leaves-7-dead-in-Maharashtra--200-villagers-stranded/2834213</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Maharashtra CM Fadnavis, Dy CM Shinde congratulate Governor CP Radhakrishnan on NDA's VP nomination</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination-23589945</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>https://www.ptinews.com/detail/business/-Third-Mumbai--to-boost-metropolitan-region-development--Fadnavis/2834902</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Fadnavis meets Guv Radhakrishnan, presents him book of Shivaji Maharaj's letters</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>https://www.ptinews.com/story/national/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharaj-s-letters/2832582</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Schools shut, red alert as Mumbai braces for another day of heavy rain | Latest News India - Hindustan Times</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/india-news/mumbai-rains-schools-shut-as-mumbai-under-imd-red-alert-braces-for-another-day-of-heavy-rain-10-updates-101755564432674-amp.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Fadnavis Dedicates Goldman Sachs’ New Mumbai Office, Unveils Vision For ‘Third Mumbai’</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>https://www.businessworld.in/article/fadnavis-dedicates-goldman-sachs-new-mumbai-office-unveils-vision-for-third-mumbai-567845</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>https://udayavani.com/national/third-mumbai-to-boost-metropolitan-region-development-fadnavis-20250819T044623387Z?lang=en</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>DH Evening Brief | NDA VP pick in Delhi to meet BJP top brass, Opposition yet to finalise their candidate; I.N.D.I.A. bloc continues attacking EC chief over SIR</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>https://www.deccanherald.com/india/dh-evening-brief-nda-vp-pick-in-delhi-to-meet-bjp-top-brass-opposition-yet-to-finalise-their-candidate-india-bloc-continues-attacking-ec-chief-over-sir-3685866</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Mumbai rain Highlights: 7 people dead across Maharashtra, says CM Devendra Fadnavis</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>https://www.india.com/news/india/mumbai-rain-live-updates-heavy-rains-lashes-city-orange-alert-for-today-red-alert-in-pune-satara-ratnagiri-local-trains-delayed-traffic-jams-8017300/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Mumbai got 177mm rain in 6-8 hour period, says CM; all agencies asked to remain alert</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>https://www.ptinews.com/story/national/mumbai-got-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/2833181</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Maharashtra on high alert as heavy rains batter state; CM, Dy CM lead rescue efforts</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>https://www.daijiworld.com/news/newsDisplay?newsID=1289634</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Maratha general Raghuji Bhonsle's sword brought to Mumbai</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>https://www.ptinews.com/editor-detail/maratha-general-raghuji-bhonsle-s-sword-brought-to-mumbai/2833930</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>https://www.millenniumpost.in/nation/third-mumbai-to-boost-metropolitan-region-development-fadnavis-623625</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Maharashtra rain: Mumbai flooded, 5 missing in Nanded, more showers in store</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>https://thefederal.com/category/states/west/maharashtra/mumbai-flooded-nanded-5-missing-maharashtra-rain-202350</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Fadnavis meets Guv Radhakrishnan presents him book of Shivaji Maharaj's letters</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom20-mh-governor-fadnavis.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by Maharashtra CM Devendra Fadnavis</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>https://aninews.in/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Observe precaution: Maharashtra CM warns about severe weather conditions in state</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state-23590120</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Rain fury leaves 7 dead in Maharashtra 200 villagers stranded</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom50-mh-2nd-ldall-rains.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Heavy rains lash Nanded Five missing scores stranded says CM Fadnavis Army unit deployed</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom17-mh-rains-nanded.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Pune can get underground road network to beat traffic woes</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>https://inshorts.com/en/news/pune-can-get-underground-road-network-to-beat-traffic-woes-1755566759073</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Mumbai got 177mm rain in 6-8 hour period says CM more to come amid high tides</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom21-mh-rains-mumbai-cm.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by Maharashtra CM Devendra Fadnavis</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>https://www.bignewsnetwork.com/news/278516795/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>CM Devendra Fadnavis Meets Netherlands Yogasana Chief on Global Initiatives</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>https://www.transcontinentaltimes.com/netherlands-yogasana-sports-nysa/</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>'Third Mumbai' Initiative Sparks New Wave of Economic Growth in Maharashtra</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>https://www.devdiscourse.com/article/science-environment/3545659-third-mumbai-initiative-sparks-new-wave-of-economic-growth-in-maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Goldman Sachs Expands In Mumbai, Devendra Fadnavis Inaugurates New Worli Office</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/business/goldman-sachs-expands-in-mumbai-devendra-fadnavis-inaugurates-new-worli-office</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Mumbai: CM Devendra Fadnavis meets C.P. Radhakrishnan #Gallery</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>https://www.socialnews.xyz/2025/08/18/mumbai-cm-devendra-fadnavis-meets-c-p-radhakrishnan-gallery/</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Maharashtra CM Devendra Fadnavis Says ‘Third Mumbai’ Being Developed in Raigad District Will Open New</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>https://www.latestly.com/india/news/maharashtra-cm-devendra-fadnavis-says-third-mumbai-being-developed-in-raigad-district-will-open-new-chapter-of-economic-development-7064927.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Mumbai Rains: Maharashtra CM Devendra Fadnavis Chairs Review Meeting On Excessive Rainfall At Mantralaya</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-rains-cm-devendra-fadnavis-chairs-review-meeting-on-excessive-rainfall-at-mantralaya-video</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>India News | ⚡Devendra Fadnavis Says ‘Third Mumbai’ Will Open a New Chapter of Economic Development</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>https://www.latestly.com/quickly/india/news/devendra-fadnavis-says-third-mumbai-will-open-a-new-chapter-of-economic-development-7064927.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Mumbai Records 177 mm Rain In 6 Hours, CM Devendra Fadnavis Urges Caution Amid High Tide Alert</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-records-177-mm-rain-in-6-hours-cm-devendra-fadnavis-urges-caution-amid-high-tide-alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Future-ready India lies in STEM and AI, says Devendra Fadnavis, Maharashtra CM</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>https://indiacsr.in/brillio-national-stem-challenge-empowers-2500-underserved-students-to-innovate-for-indias-future/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>‘Third Mumbai’ will open a new chapter of economic development: Maha CM</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>https://www.lokmattimes.com/national/third-mumbai-will-open-a-new-chapter-of-economic-development-maha-cm/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>VIDEO: Historic Sword Of Raghuji Bhonsle Connects Youth With Maharashtra’s Glorious History, Says CM</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/video-historic-sword-of-raghuji-bhonsle-connects-youth-with-maharashtras-glorious-history-says-cm-devendra-fadnavis</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Mumbai: C.P. Radhakrishnan departs for Delhi #Gallery</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>https://www.socialnews.xyz/2025/08/18/mumbai-c-p-radhakrishnan-departs-for-delhi-gallery/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>'Observe precaution': Maharashtra CM warns about severe weather conditions in state</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>https://english.newsnationtv.com/national/general-news/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state20250819025510</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>7 killed as heavy rain batters Maharashtr­a; 800 villages hit</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>https://www.pressreader.com/india/the-hindu-erode-9WW6/20250819/281994678584394</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Heavy Rain Forecast for Mumbai: CM Fadnavis Reviews Flood Situation Across Maharashtra, with the Next 12...</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>https://www.lokmattimes.com/mumbai/heavy-rain-forecast-for-mumbai-cm-fadnavis-reviews-flood-situation-across-maharashtra-with-the-next-12-hours-critical-a475/</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Mumbai Rains: Maharashtra CM Says 'Observe Precautions', Warns Of Heavy Rainfall, High Tide Check BMC's Advisory</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>https://menafn.com/1109945394/Mumbai-Rains-Maharashtra-CM-Says-Observe-Precautions-Warns-Of-Heavy-Rainfall-High-Tide-Check-BMCs-Advisory</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Heavy rains in Mumbai: IndiGo, SpiceJet, Akasa issue travel advisories</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>https://www.newsbytesapp.com/news/india/mumbai-flights-status-airlines-issue-key-advisory-for-passengers/story</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Amid heavy rains in Maharashtra, CM Fadnavis directs all agencies to be on alert</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>https://www.thehawk.in/news/india/amid-heavy-rains-in-maharashtra-cm-fadnavis-directs-all-agencies-to-be-on-alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>7 killed as heavy rain batters Maharashtr­a; 800 villages hit</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>https://www.pressreader.com/india/the-hindu-mangalore-9WWc/20250819/281947433944151</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Pune Patients Receive Over Rs 6.5 Crore in Medical Aid Under Chief Minister Devendra Fadnavis’ Initiative</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>https://www.punekarnews.in/pune-patients-receive-over-rs-6-5-crore-in-medical-aid-under-chief-minister-devendra-fadnavis-initiative/</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Those who speak of Maharashtra 'asmita' should support Radhakrishnan for VP post: Fadnavis</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>https://www.newsdrum.in/national/those-who-speak-of-maharashtra-asmita-should-support-radhakrishnan-for-vp-post-fadnavis-9672630</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Business News</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>https://www.latestly.com/agency-news/business-news-credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis-7064653.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Maharashtra Rains: 5 Missing in Nanded, Over 200 Stranded Across Several Districts; Army, NDRF Deployed</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>https://www.lokmattimes.com/maharashtra/maharashtra-rains-5-missing-in-nanded-over-200-stranded-across-several-districts-army-ndrf-deployed-a517/</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by Maharashtra CM Devendra Fadnavis</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>https://english.newsnationtv.com/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Mumbai To Welcome Historic Sword Of Shrimant Raje Raghuji Bhonsale On August 18; To Be Ceremoniously Unveiled</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-to-welcome-historic-sword-of-shrimant-raje-raghuji-bhonsale-on-august-18-to-be-ceremoniously-unveiled-by-cm-fadnavis</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>CM Fadnavis unveils emblem for Ganeshotsav to be celebrated as Rajya Mahotsav</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>https://www.thehawk.in/news/india/cm-fadnavis-unveils-emblem-for-ganeshotsav-to-be-celebrated-as-rajya-mahotsav</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Fadnavis meets Guv Radhakrishnan, presents him book of Shivaji Maharaj's letters</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>https://www.newsdrum.in/national/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharajs-letters-9672415</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Mumbai Weather Today LIVE Updates: Mithi River Crosses Danger Mark; Santacruz Records Highest Rainfall; 300</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-rains-live-updates-heavy-showers-wreak-havoc-in-city-schools-colleges-shut-as-imd-issues-red-alert-sion-matunga-dadar-vile-parle-waterlogged-andheri-subway-closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Fadnavis Gifts Unpublished Shivaji Maharaj Letters to Maharashtra Governor at Mumbai Airport</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>https://panasiabiz.com/111091/cm-devendra-fadnavis-presents-rare-shivaji-maharaj-letters-to-governor-cp-radhakrishnan/</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Maharashtra government approves major infra projects</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>https://www.thehawk.in/news/india/maharashtra-government-approves-major-infra-projects</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Heavy rains lash Nanded: Five missing, scores stranded, says CM Fadnavis; Army unit deployed</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>https://www.newsdrum.in/national/heavy-rains-lash-nanded-five-missing-scores-stranded-says-cm-fadnavis-army-unit-deployed-9672306</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>महाराष्ट्र के इस जिले में बसाई जाएगी 'तीसरी मुंबई', मुख्यमंत्री देवेंद्र फडणवीस ने बताईं प्रोजेक्ट की अहम ब</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>https://www.indiatv.in/paisa/business/third-mumbai-will-be-settled-in-raigad-district-of-maharashtra-chief-minister-devendra-fadnavis-told-the-important-points-of-the-project-2025-08-19-1156854</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>दिल्ली पहुंचे देवेंद्र फडणवीस, अमित शाह से मिले, जानें क्यों थी यह मुलाकात खास</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B6-%E0%A4%B9-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A5%87-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%82-%E0%A4%A5-%E0%A4%AF%E0%A4%B9-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4-%E0%A4%96-%E0%A4%B8/ar-AA1Jjy9z</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Mumbai Maharashtra Rains: महाराष्ट्र में भारी बारिश पर सीएम देवेंद्र फडणवीस का सख्त निर्देश, सभी विभाग अलर्ट पर</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>https://thecsrjournal.in/mumbai-maharashtra-rains-cm-and-managment-on-alert-hindi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>उप-राष्ट्रपति चुनाव: देवेंद्र फडणवीस का 'मराठी अस्मिता' वाला दांव, क्या करेंगे</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>https://www.abplive.com/states/maharashtra/vice-president-election-2025-maharashtra-cm-devendra-fadnavis-request-uddhav-thackeray-and-sharad-pawar-2997542</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>कैसी होगी तीसरी मुंबई, कितनी बड़ी और कहां बन रही, सुविधाओं से लेकर प्लानिंग तक, CM फडणवीस ने सब बताया</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>https://ndtv.in/maharashtra-news/maharashtra-cmdevendra-fadnavis-told-third-mumbai-mmr-will-develop-with-this-know-how-it-will-be-9112502</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Vice President Election: उद्धव ठाकरे और शरद पवार से फडणवीस मांगेंगे सीपी राधाकृष्णन के लिए समर्थन, शिंदे सेना ने दिया सपोर्ट</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-governor-radhakrishnan-gets-nda-backing-for-vice-president-post-devendra-fadnavis-uddhav-thackeray-sharad-pawar/articleshow/123371527.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>मुख्यमंत्री देवेंद्र फडणवीस ने राज्य में भारी बारिश के मद्देनजर सभी एजेंसियों को सतर्क रहने के निर्देश दिए</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>https://www.mumbailive.com/hi/civic/chief-minister-devendra-fadnavis-directed-all-agencies-to-remain-alert-in-view-of-heavy-rains-in-the-state-89633</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>मुंबई में सिर्फ 6-8 घंटे में 177 मिमी हुई बारिश, फडणवीस ने दिए सावधानी बरतने के निर्देश</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/mumbai-received-177-mm-of-rain-in-just-6-8-hours-fadnavis-gave-instructions-to-take-precautions-11195</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Mumbai Rain News : मुंबई में बारिश ने मचाया कोहराम, देवेंद्र फडणवीस का आया बयान</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>https://hindi.oneindia.com/videos/mumbai-rain-news-rain-wreaked-havoc-in-mumbai-devendra-fadnavis-statement-came-4259449.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>मुंबई में भारी भारिश ने मचाई तबाही, CM देवेंद्र फडणवीस ने बुलाई बैठक</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>https://www.patrika.com/videos/mumbai-news/heavy-rain-wreaks-havoc-in-mumbai-cm-devendra-fadnavis-calls-a-meeting-19874343</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>फडणवीस ने कहा, ‘तीसरी मुंबई’ से एमएमआर का होगा विकास</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>https://hindi.theprint.in/india/economy/fadnavis-said-third-mumbai-will-lead-to-development-of-mmr/856867/</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>महाराष्ट्र के नांदेड़ में फटा बादल, 15-16 जिलो में अलर्ट, CM फडणवीस बोले- फसलों को नुकसान</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>https://www.abplive.com/states/maharashtra/weather-mumbai-rains-local-train-cloudburst-nanded-alert-in-15-16-districts-in-maharashtra-cm-devendra-fadnavis-said-damage-to-crops-2997472</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Mumbai Rains News: भारी बारिश के चलते कल मुंबई के स्कूल-कॉलेजों में छुट्टी, नांदेड़ में 7 लोगों की मौत, CM फडणवीस ने की आपात बैठक</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/heavy-rains-in-mumbai-schools-colleges-closed-7-deaths-in-maharashtra-5-missing-nanded-cm-fadnavis-emergency-meeting/articleshow/123366462.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>'औरंगजेब भारत के किसी भी समाज का हीरो नहीं...', मजार को लेकर फडणवीस ने कही बड़ी बात</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%AD-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AE%E0%A4%9C-%E0%A4%B0-%E0%A4%95-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC-%E0%A4%A4/ar-AA1IRFiN</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>मराठा सेनापति रघुजी भोंसले की 200 साल पुरानी तलवार पहुंची मुंबई, CM फडणवीस बोले-</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>https://www.abplive.com/states/maharashtra/london-auction-historic-raghuji-bhosale-sword-brought-to-mumbai-devendra-fadnavis-says-indias-heritage-restored-2997814</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>मैं आपकी वहिनी… देवेंद्र फडणविस के शपथ लेते ही पत्नी अमृता फडणवीस ने महाराष्ट्र से किया ये वादा</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%88%E0%A4%82-%E0%A4%86%E0%A4%AA%E0%A4%95-%E0%A4%B5%E0%A4%B9-%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%B6%E0%A4%AA%E0%A4%A5-%E0%A4%B2%E0%A5%87%E0%A4%A4%E0%A5%87-%E0%A4%B9-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A8-%E0%A4%85%E0%A4%AE%E0%A5%83%E0%A4%A4-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%AF%E0%A5%87-%E0%A4%B5-%E0%A4%A6/ar-AA1vljO5?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>इसमें उनका घाटा...हिंदी-मराठी भाषा विवाद के बीच फडणवीस का बड़ा दावा, बोले- मुंबई का मेयर तो हमारा ही होगा</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%87%E0%A4%B8%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%89%E0%A4%A8%E0%A4%95-%E0%A4%98-%E0%A4%9F-%E0%A4%B9-%E0%A4%82%E0%A4%A6-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%AD-%E0%A4%B7-%E0%A4%B5-%E0%A4%B5-%E0%A4%A6-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%9A-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%A6-%E0%A4%B5-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%95-%E0%A4%AE%E0%A5%87%E0%A4%AF%E0%A4%B0-%E0%A4%A4-%E0%A4%B9%E0%A4%AE-%E0%A4%B0-%E0%A4%B9-%E0%A4%B9-%E0%A4%97/ar-AA1ImpaC?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Maharashtra: फडणवीस बोले- औरंगजेब भारत का हीरो नहीं, सुप्रीम कोर्ट के SC आरक्षण पर फैसले को लागू करेगी सरकार</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B8%E0%A5%81%E0%A4%AA%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%95%E0%A5%87-sc-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%AA%E0%A4%B0-%E0%A4%AB%E0%A5%88%E0%A4%B8%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B2-%E0%A4%97%E0%A5%82-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%97-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0/ar-AA1IRMGx</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Maharashtra: 'पुणे के विकास में सबसे बड़ी बाधा बन चुकी है उद्योगों पर दादागीरी', सीएम फडणवीस ने दी चेतावनी</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AA%E0%A5%81%E0%A4%A3%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%B5-%E0%A4%95-%E0%A4%B8-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8%E0%A4%AC%E0%A4%B8%E0%A5%87-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC-%E0%A4%A7-%E0%A4%AC%E0%A4%A8-%E0%A4%9A%E0%A5%81%E0%A4%95-%E0%A4%B9%E0%A5%88-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%97-%E0%A4%82-%E0%A4%AA%E0%A4%B0-%E0%A4%A6-%E0%A4%A6-%E0%A4%97-%E0%A4%B0-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%A6-%E0%A4%9A%E0%A5%87%E0%A4%A4-%E0%A4%B5%E0%A4%A8/ar-AA1JMfla?ocid=finance-verthp-feeds&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>CP Radhakrishnan को लेकर CM फडणवीस ने बड़ा खुलासा कर चल दिया दांव, अब क्‍या करेंगे उद्धव ठाकरे और शरद पवार?</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>https://hindi.oneindia.com/news/maharashtra/vice-presidential-election-cm-devendra-fadnavis-said-cp-radhakrishnan-is-a-mumbai-voter-support-him-1365243.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>फडणवीस की पत्नी के खिलाफ अपमानजनक पोस्ट : दो लोगों की अग्रिम जमानत अर्जी खारिज</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>http://www.msn.com/hi-in/news/other/%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%96-%E0%A4%B2-%E0%A4%AB-%E0%A4%85%E0%A4%AA%E0%A4%AE-%E0%A4%A8%E0%A4%9C%E0%A4%A8%E0%A4%95-%E0%A4%AA-%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%A6-%E0%A4%B2-%E0%A4%97-%E0%A4%82-%E0%A4%95-%E0%A4%85%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%9C%E0%A4%AE-%E0%A4%A8%E0%A4%A4-%E0%A4%85%E0%A4%B0%E0%A5%8D%E0%A4%9C-%E0%A4%96-%E0%A4%B0-%E0%A4%9C/ar-AA1Je80j?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>मुंबई में 6-8 घंटे में 177 मिलीमीटर बारिश हुई: फडणवीस</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>https://hindi.theprint.in/india/mumbai-received-177-mm-of-rain-in-6-8-hours-fadnavis/856688/</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>महाराष्ट्र में भारी बारिश का कहर, 16 जिलों में रेड अलर्ट, बचाव दल तैनात</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-heavy-rainfall-flood-alert-red-and-orange-alerts-issued-relief-operations-mumbai-rain-ann-2997660</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>नांदेड़ में भारी बारिश के कारण पांच लोग लापता, कई व्यक्ति फंसे : मुख्यमंत्री फडणवीस</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>https://hindi.theprint.in/india/five-people-missing-many-people-stranded-due-to-heavy-rains-in-nanded-chief-minister-fadnavis/856679/</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Mumbai Rain: 24 घंटे की बारिश से मुंबई की सांस फूली, CM देवेंद्र फडणवीस ने पड़ोसी राज्यों से किया संपर्क</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>https://zeenews.india.com/hindi/india/mumbai-rains-today-imd-red-alert-warning-waterlogging-traffic-update/2886161</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Raghuji Bhosale: आज मुंबई आएगी रघुजी भोसले की की ऐतिहासिक तलवार, सीएम फडणवीस करेंगे स्वागत</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>https://zeenews.india.com/hindi/india/raghuji-bhosale-historic-sword-will-arrive-in-mumbai-today-cm-fadnavis-will-welcome-it/2886138</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>'Indias Got Latent' विवाद पर अभिनेता से नेता तक भड़के, CM फडणवीस बोले-होना चाहिए एक्शन</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/hi-in/news/other/indias-got-latent-%E0%A4%B5-%E0%A4%B5-%E0%A4%A6-%E0%A4%AA%E0%A4%B0-%E0%A4%85%E0%A4%AD-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%B8%E0%A5%87-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%A4%E0%A4%95-%E0%A4%AD%E0%A4%A1%E0%A4%BC%E0%A4%95%E0%A5%87-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%B9-%E0%A4%A8-%E0%A4%9A-%E0%A4%B9-%E0%A4%8F-%E0%A4%8F%E0%A4%95%E0%A5%8D%E0%A4%B6%E0%A4%A8/ar-AA1yKIjb?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>महाराष्ट्र में बन रही है तीसरी मुंबई, इस जिले का होगा आर्थिक विकास, जानें पूरी जानकारी | News Track in...</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>https://newstrack.com/india/third-mumbai-being-built-maharashtra-district-have-economic-development-know-full-details-534715</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>मुंबई में भारी बारिश के बीच सुचारू रूप से चल रही मेट्रो, सीएम फडणवीस ने की तारीफ</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>https://www.m.khaskhabar.com/news/news-metro-running-smoothly-amid-heavy-rains-in-mumbai-cm-fadnavis-praised-news-hindi-1-745323-KKN.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>CM फडणवीस ने खेला 'मराठी अस्मिता' का दांव, उपराष्ट्रपति चुनाव में उद्धव-पवार पर बना दबाव</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>https://navbharatlive.com/maharashtra/political-battle-over-nda-candidate-radhakrishnan-cm-fadnavis-seeks-support-from-uddhav-thackeray-and-sharad-pawar-1321873.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>बाढ़ संकट पर अबू आजमी का CM फडणवीस को पत्र, प्रभावितों तक तुरंत राहत पहुंचाने की मांग</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>https://navbharatlive.com/latest-news/abu-azmi-wrote-a-letter-to-cm-devendra-fadnavis-asking-him-to-send-relief-supplies-to-flood-affected-region-1322005.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>महाराष्ट्र किसानों को मिलेगी बड़ी राहत, CM फडणवीस जल्द करेंगे कर्जमाफी की घोषणा</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>https://navbharatlive.com/maharashtra/guardian-minister-sanjay-rathore-claims-cm-fadnavis-may-announce-a-loan-waiver-for-farmers-1322081.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>नांदेड़ में मूसलधार बारिश से हाहाकार, CM फडणवीस की निगरानी में राहत कार्य तेज</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>https://navbharatlive.com/maharashtra/heavy-rains-cause-havoc-in-nanded-rescue-operation-intensified-under-the-supervision-of-cm-fadnavis-1321752.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>अबू आजमी ने सीएम देवेंद्र फडणवीस को लिखा पत्र, बाढ़ प्रभावित इलाकों में राहत सामग्री पहुंचाने की मांग की</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>https://www.newsnationtv.com/abu-azmi-ne-cm-devendra-fadnavis-ko-likha-patra-badh-prabhavit-ilakon-mein-rahat-pahunchane-ki-mang-ki--20250818191027/</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>कोल्हापुर में CJI गवई ने की सीएम और डिप्टी सीएम के सामने उनकी तारीफ, बोले- "जो लोग शिकायत कर रहे वे देवेंद्र फडणवीस और एकनाथ शिंदे के बारे में नहीं जानते…"</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>https://lalluram.com/in-kolhapur-cji-gavai-praised-him-in-front-of-cm-and-deputy-cm-said-those-who-are-complaining-do-not-know-about-devendra-fadnavis-and-eknath-shinde/</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Mumbai News: महाराष्ट्र में मूसलाधार बारिश से हाहाकार, मुख्यमंत्री की हाईलेवल बैठक, विशेष सत्र बुलाने की मांग | Heavy rains cause havoc in Maharashtra, high level meeting of Chief Minister, demand for calling special s</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>https://www.bhaskarhindi.com/city/mumbai/mumbai-news-heavy-rains-cause-havoc-in-maharashtra-high-level-meeting-of-chief-minister-demand-for-calling-special-session-1174171</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Maharashtra Live News Updates: एक क्लिक में पढ़े महाराष्ट्र की दिन भर की बड़ी खब़रें...</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>https://navbharatlive.com/maharashtra/latest-live-updates-maharashtra-politics-crime-nagpur-news-mumbai-pune-18-august-1321138.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>महाराष्ट्र में भारी बारिश से कई जिलों में रेड और ऑरेंज अलर्ट</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>https://vikalptimes.com/red-and-orange-alert-issued-in-many-districts-of-maharashtra-due-to-heavy-rains/</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>CM फडणवीस ने एनडीए के उपराष्ट्रपति पद के नामांकन पर सीपी राधाकृष्णन को शॉल भेंट की</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>https://jantaserishta.com/local/maharashtra/cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vice-president-nomination-4218433</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Mumbai Rains: मुंबई में भारी बारिश से 12 लोगों की मौत, जगह-जगह कमर तक भरा पानी, स्कूल-कॉलेज बंद, फ्लाइट्स पर भी असर</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>https://lalluram.com/mumbai-rains-7-people-died-due-to-rain-water-flooded-on-roads-schools-and-colleges-closed-flights-also-affected/</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>किसानों को जल्द मिल सकता है कर्जमाफी का तोहफा, मंत्री संजय राठोड़ का बड़ा बयान</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>https://mpbreakingnews.in/maharashtra/farmer-loan-waiver-maharashtra-sanjay-rathod-devendra-fadnavis-54-804134</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>उपराष्ट्रपति चुनाव में भाजपा का दांव, सीपी राधाकृष्णन उम्मीदवार, महाराष्ट्र की राजनीति में बढ़ी हलचल</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>https://mpbreakingnews.in/maharashtra/vice-president-election-bjp-candidate-cp-radhakrishnan-devendra-fadnavis-54-803924</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>महाराष्ट्र : भारी बारिश के बाद नांदेड़ में राहत कार्य तेज, प्रशासन के संपर्क में सीएम फडणवीस</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>https://www.newsnationtv.com/maharashtra-bhari-barish-ke-baad-nanded-mein-rahat-bachav-karya-tez-jiladhikariyon-ke-sampark-mein-cm-fadnavis--20250818144516/</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Mumbai: राज्यपाल की उपराष्ट्रपति पद की उम्मीदवारी पर मुख्यमंत्री ने जताया हर्ष</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>https://jantaserishta.com/local/maharashtra/mumbai-chief-minister-expressed-happiness-over-the-candidature-of-the-governor-for-the-post-of-vice-president-mumbai--4218462</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>नांदेड़ में भारी बारिश के कारण पांच लोग लापता, कई व्यक्ति फंसे : मुख्यमंत्री फडणवीस</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>https://www.ibc24.in/maharashtra/five-people-missing-several-stranded-due-to-heavy-rains-in-nanded-cm-fadnavis-3212983.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Mumbai : महाराष्ट्र में मूसलाधार बारिश से हाहाकार, सात लोगों की मौत</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>https://indiagroundreport.com/mumbai-torrential-rains-in-maharashtra-cause-havoc-seven-people-died/</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>लंदन से आई मराठा साम्राज्य की शान! रघुजी ?...</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>https://bharatexpress.com/india/raghuji-bhosale-historic-sword-returned-from-london-grand-welcome-in-mumbai-553050</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>महाराष्ट्र की 'अस्मिता' की बात करने वाले उपराष्ट्रपति पद के लिए राधाकृष्णन का समर्थन करें : फडणवीस</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>https://navabharat.news/support-radhakrishnan-for-the-post-of-vice-president-who-talks-about-maharashtras-identity-fadnavis/</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Aakar Patel| New Maharashtra Security Law Open To Abuse, Threatens Rights; Say ‘No’ To It</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>https://www.asianage.com/opinion/columnists/aakar-patel-new-maharashtra-security-law-open-to-abuse-threatens-rights-say-no-to-it-1898277</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Shinde and BJP: The saga continues</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/en-in/news/India/shinde-and-bjp-the-saga-continues/ar-AA1KHn3K</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Heavy rainfall causes 7 deaths, crop loss in Maharashtra as alerts continue</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/en-in/news/India/heavy-rainfall-causes-7-deaths-crop-loss-in-maharashtra-as-alerts-continue/ar-AA1KK6Zt</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>CREDAI-MCHI appoints Sukhraj Nahar as 18th President</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>https://housing.com/news/credai-mchi-appoints-sukhraj-nahar-as-president/</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>"Observe precaution": Maharashtra CM warns about severe weather conditions in state</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>https://thenewsmill.com/2025/08/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state/</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Mumbai got 177mm rain in 6-8 hour period, says CM; more to come amid high tides</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>https://www.newsdrum.in/national/mumbai-got-177mm-rain-in-6-8-hour-period-says-cm-more-to-come-amid-high-tides-9672488</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>NCP (SP) targets Maha minister over Rs 5,000 cr scam in Navi Mumbai’s CIDCO land; demands his resignation</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>https://www.socialnews.xyz/2025/08/18/ncp-sp-targets-maha-minister-over-rs-5000-cr-scam-in-navi-mumbais-cidco-land-demands-his-resignation/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=ncp-sp-targets-maha-minister-over-rs-5000-cr-scam-in-navi-mumbais-cidco-land-demands-his-resignation</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>CM to inaugurate additional water supply scheme</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>https://www.lokmattimes.com/aurangabad/cm-to-inaugurate-additional-water-supply-scheme/</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Mumbai rains: IMD issues red alert as downpour continues; schools, colleges &amp; Govt offices shut</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>https://newslivetv.com/mumbai-rains-imd-issues-red-alert/</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Devendra Fadnavis : अख्खा पक्ष विरोधात, पण या दिग्गज नेत्याचा फडणवीसांना पाठिंबा, एका पत्राने राजकीय वर्तु...</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>https://news18marathi.com/maharashtra/cm-devendra-fadnavis-gets-support-from-congress-leader-nitin-raut-letter-goes-viral-1461146.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>राज्यात अतिवृष्टीमुळे मुख्यमंत्री देवेंद्र फडणवीस यांचे सर्व यंत्रणांना सतर्कतेचे निर्देश; नांदेड जिल्ह्यात लष्कराची मदत</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/mumbai/chief-minister-devendra-fadnavis-has-directed-all-agencies-to-be-on-alert-due-to-heavy-rains-in-the-maharashtra-mumbai-print-news-amy-95-5313479/</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Mumbai Rain : मुंबईत संध्याकाळी समुद्राला भरती, पुढील 12 तास महत्त्वाचे, पावसाच्या थैमानानंतर</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-on-mumbai-maharashtra-rain-today-visit-disaster-management-department-bmc-marathi-news-1377962</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>राज्यात अतिवृष्टीच्या पार्श्वभूमीवर प्रशासन अलर्ट मोडवर! मुख्यमंत्री देवेंद्र फडणवीस यांचे सतर्कतेचे निर्देश</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>https://www.navarashtra.com/maharashtra/cm-devendra-fadnavis-took-review-of-rain-situation-at-state-disaster-management-centre-in-the-ministry-963383.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Farmers Loan Waiver: बावनकुळेंनंतर महायुती सरकारमधील 'या' मंत्र्याची कर्जमाफीबाबत मोठी अपडेट; म्हणाले,'CM फडणवीस लवकरच...'</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>https://sarkarnama.esakal.com/amp/story/maharashtra/vidarbha/sanjay-rathod-update-farmer-loan-waiver-devendra-fadnavis-dk88</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Devendra Fadnavis : महाराष्ट्रातील माणसाला सर्वांनी समर्थन द्यावं; फडणवीस यांचे मविआला आवाहन</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-appeals-to-maharashtra-mps-to-support-cp-radhakrishnan-for-vice-president/913103/</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>पुढील १२ तास मुंबईसाठी अत्यंत महत्त्वाचे, मुख्यमंत्री फडणवीस पावसाबाबत काय म्हणाले?</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-review-mumbai-rain-says-next-12-hours-important-for-mumbai-and-mmr-region-1460967.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>सरदार रघुजी भोसले यांची ऐतिहासिक तलवार मुंबईत दाखल; मुख्यमंत्र्यांच्या हस्ते होणार लोकार्पण</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/mr/!state/sword-of-maratha-commander-raghuji-bhosale-returns-to-mumbai-to-be-unveiled-at-exhibition-by-cm-fadnavis-maharashtra-news-mhs25081803521</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>नवीन पिढीला इतिहासाशी जोडण्याचे कार्य सुरू; मुख्यमंत्री देवेंद्र फडणवीस यांचे प्रतिपादन</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/mumbai/devendra-fadnavis-asserts-that-the-work-of-connecting-the-new-generation-with-history-is-underway-mumbai-print-news-amy-95-5313830/</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>मोठी बातमी! शेतकऱ्यांची कर्जमाफी होणार, मुख्यमंत्री घोषणा करणार, बड्या मंत्र्याने दिली माहिती</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>https://www.tv9marathi.com/maharashtra/big-update-on-farmer-loan-waiver-cm-fadnavis-will-do-announcement-says-minister-sanjay-rathod-1472819.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>CM देवेंद्र फडणवीस लवकरच कर्जमाफीची घोषणा करतील महायुतीच्या मंत्र्यांनी दिली</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/politics/cm-devendra-fadnavis-will-soon-announce-loan-waiver-farmers-mahayuti-ministers-sanjay-rathod-gave-information-yavatmal-1377983</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Mumbai Rain: मुंबईत उद्या शाळांना सुट्टी? पुढचे १२ तास महत्वाचे, मुख्यमंत्री नेमकं काय म्हणाले?</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>https://saamtv.esakal.com/amp/story/mumbai-pune/mumbai-rain-alert-cm-devendra-fadnavis-said-mumbai-schools-declared-holiday-on-tomorrow-bmc-to-decide-pvm91</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Maharashtra Rain Updates: मुंबईसाठी पुढील 12 तास महत्त्वाचे, राज्यात स्थिती काय? CM फडणवीसांनी सगळं सांगितल...</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>https://news18marathi.com/maharashtra/maharashtra-rain-update-cm-devendra-fadnavis-hold-meeting-with-district-administration-1460734.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>मोठी बातमी! नाराजी भोवली, शिवसेना शिंदे गटाला सर्वात मोठा धक्का, बड्या नेत्यानं सोडली एकनाथ शिंदेंची...</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>https://www.tv9marathi.com/maharashtra/big-blow-to-eknath-shinde-big-leader-of-shiv-sena-shinde-group-will-join-bjp-1472541.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>गौरवशाली इतिहासाशी नव्या पीढीला जोडण्याचं काम रघुजीराजे भोसल्यांची ऐतिहासिक</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-mumbai-exhibition-of-nagpur-raghuji-raje-bhosle-historical-sword-marathi-news-1378075</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Mumbai Rain Updates : सात जणांचा मृत्यू ते शेकडो गावे बाधित; राज्यभरात अतिवृष्टीमुळे कुठे काय घडलं?</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-updates-18-august-heavy-rainfall-mumbai-navi-mumbai-kolhapur-raigad-sindhudurag-local-train-latest-updates-traffic-news-rak-94-5312079/</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>School holiday: मुंबईत पावसामुळे शाळांना सुटी जाहीर, पुढील ४८ तासांचा अतिवृष्टीचा इशारा; काळजी घेण्याचे आवाहन</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/career/career-news/school-holiday-in-mumbai-due-to-rain-heavy-rainfall-alert-for-the-next-48-hours/articleshow/123357322.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>मुख्यमंत्री लवकरच शेतकरी कर्जमाफीची घोषणा करणार ; शिंदेंच्या मंत्र्यांचा दावा !</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>https://vishwanewsmarathi.com/chief-minister-will-soon-announce-farmer-loan-waiver-shindes-ministers-claim/</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Heavy Rain: राज्यात अतिवृष्टीच्या पार्श्वभूमीवर मुख्यमंत्री देवेंद्र फडणवीस यांचे सर्व यंत्रणांना सतर्कतेचे</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>https://deshonnati.com/heavy-raincm-devendra-fadnavis-agencies-alert-heavy-rain-state/</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>प्रशासन सतर्क : नागरिकांनी घराबाहेर पडू नये: मुख्यमंत्री फडणवीस !</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>https://vishwanewsmarathi.com/administrator-citizens-should-not-stay-home-chief-minister/</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>शेतकरी कर्जमाफीबाबत महायुतीमधील मंत्र्याने दिली महत्त्वाची माहिती; “देवेंद्र फडणवीस लवकरच….”</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>https://www.dainikprabhat.com/mahayuti-minister-gives-important-information-regarding-farmer-loan-waiver-devendra-fadnavis-soon/</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>लवकरच कर्जमाफीची घोषणा होणार? महायुती सरकारमधील मंत्र्यांनी दिले संकेत</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>https://marathi.oneindia.com/maharashtra/maharashtra-cm-fadnavis-loan-waiver-announcement-035127.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>मुख्यमंत्री फडणवीस लवकरच शेतकरी कर्जमाफीची घोषणा करण्याची शक्यता</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>https://www.dainikprabhat.com/cm-fadnavis-likely-to-announce-farm-loan-waiver-soon/</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>महाराष्ट्रातील शेतकऱ्यांना मोठा दिलासा, मुख्यमंत्री फडणवीस लवकरच कर्जमाफीची घोषणा करणार</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/big-relief-for-farmers-in-maharashtra-chief-minister-fadnavis-will-soon-announce-loan-waiver-125081900014_1.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Devendra Fadnavis : महाराष्ट्रातील माणसाला सर्वांनी समर्थन द्यावे; मुख्यमंत्री फडणवीस यांचे मविआच्या खासदारांना आवाहन</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>https://www.dainikprabhat.com/devendra-fadnavis-everyone-should-support-the-people-of-maharashtra-chief-minister-fadnavis-appeals-to-m-v-a-mps/</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>एकनाथ शिंदेंना सोलापुरात मोठा धक्का : नेत्यांने सोडली साथ !</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>https://vishwanewsmarathi.com/big-setback-for-eknath-shinde-in-solapur-leaders-leave-support/</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>School Closed | मोठी बातमी! पावसामुळे आज महाराष्ट्रातील 'या' जिल्ह्यातील शाळा बंद</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>https://www.thodkyaat.com/maharashtra-school-closed-tomorrow/</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>ना. पंकजाताई मुंडे यांना ‘कोहिनूर ऑफ इंडिया’ अवाॅर्ड, लोकमत वृतपत्र समुहाने केला सन्मान; लंडन येथे पार पडला दिमाखदार सोहळा</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>https://lokashanews.com/28165/</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Mumbai Rains : गुडघाभर पाणी, समोर रस्ताही दिसेना, लोकल रखडल्या आठवड्याच्या सुरुवातीला पावसानं मुंबईकरांची दाणादाण, पहा PHOTO</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>https://marathi.asianetnews.com/mumbai/mumbai-heavy-rain-waterlogging-local-delays-school-shutdown/photoshow-at2tgam</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Mumbai News: गोल्डमन सॅक्सचे मुंबई नवे कार्यालय तिसऱ्या मुंबईचा नवा अध्याय - देवेंद्र फडणवीस</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/goldman-sachs-new-mumbai-office-is-a-new-chapter-for-third-mumbai-devendra-fadnavis-89597</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Mumbai Rain News: मुंबईत किती ठिकाणी पाणी साचलं? ट्राफिकची स्थिती काय? मुख्यमंत्र्यांनी दिली A to Z माहिती</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>https://marathi.ndtv.com/cities/mumbai-rain-news-chief-minister-devendra-fadnavis-gave-information-about-the-rainfall-situation-in-mumbai-9107883</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>“मुंबईत पुढच्या १२ तासांत तुफान पाऊस, रेड अलर्ट आणि…”; मुख्यमंत्री देवेंद्र फडणवीस यांनी काय माहिती दिली?</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/maharashtra/mumbai-rain-alert-cm-devendra-fadnavis-said-mumbai-have-red-alert-school-holiday-declared-know-details-scj-81-5312934/</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Mumbai Rain Update : समुद्रातून येतंय मुंबईवर मोठं संकट, पुढच्या 12 तासांत तुफान पाऊस, फडणवीस काय...</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>https://www.tv9marathi.com/maharashtra/mumbai-rain-alert-cm-devendra-fadnavis-said-mumbai-have-red-alert-school-holiday-declared-know-detail-information-in-marathi-1472488.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Pune News : मुख्यमंत्री फडणवीसांमुळे पुणेकरांना रोज मनस्ताप? काँग्रेसचा गंभीर आरोप</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>https://sarkarnama.esakal.com/pune/devendra-fadnavis-pune-flyover-inauguration-delay-dk88-sm89</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>महाराष्ट्रात महाभयानक पाऊस! मुख्यमंत्री देवेंद्र फडणवीस यांनी तातडीने साधला शेजारील राज्यांशी संपर्क? कारण अतिशय चिंताजनक</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>https://zeenews.india.com/marathi/maharashtra/maharashtra-mumbai-rain-alert-update-chief-minister-devendra-fadnavis-immediately-contacted-the-neighboring-states/933328</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Devendra Fadanvis on Rain Update : मुंबईला रेड अलर्ट ! मुख्यमंत्री देवेंद्र फडणवीस यांनी पावसाबद्दल दिली महत्त्वाची अपडेट</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/maharashtra-hevey-rain-update-cm-devendra-fadanvis-gives-important-information-know-about-more-/40070</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Third Mumbai News: तिसरी मुंबई आणि आर्थिक विकासाबाबत CM फडणवीसांचे मोठे विधान</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>https://marathi.ndtv.com/maharashtra/third-mumbai-will-open-a-new-chapter-of-economic-development-says-cm-devendra-fadnavis-9110192</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>पुण्यात नवीन महापालिकांवरून देवेंद्र फडणवीस आणि अजित पवार यांच्यात मतभेद का?</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/politics/devendra-fadnavis-ajit-pawar-dispute-over-new-municipal-corporations-in-pune-district-print-politics-news-css-98-5314697/</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Cji Bhushan Gavai : सरन्यायाधीशांनी केले शिवेंद्रसिंहराजेंचे जाहीरपणे कौतुक; म्हणाले, ‘गिनिज बुकमध्ये नोंद करण्यासारखे काम...’</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chief-justice-bhushan-gavai-praised-shivendrasinghraje-bhosale-vd83</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Maharashtra Rain : राज्यासाठी पुढचे दोन दिवस चिंतेचे, 15-16 जिल्ह्यांना अलर्ट, कुठे होणार अतिवृष्टी?...</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>https://www.tv9marathi.com/videos/maharashtra-imd-issues-red-alert-for-16-districts-big-information-by-cm-devendra-fadnavis-reviews-heavy-rains-in-1472606.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Mumbai Rains Updates: मुंबईकरांनो पुढील 12 तास अतिशय महत्त्वाचे, CM फडणवीसांनी केले हे आवाहन</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>https://marathi.ndtv.com/maharashtra/mumbai-rains-update-next-12-hours-are-important-for-mumbai-7-people-died-across-state-in-2-days-cm-fadnavis-appeals-to-citizens-9109288</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Maharashtra Politics : एकनाथ शिंदेंची कोण करतंय कोंडी? दिल्ली दौरे वाढण्यामागचं काय कारण?</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/politics/maharashtra-politics-shiv-sena-eknath-shinde-bjp-devendra-fadnavis-conflict-before-bmc-election-sdp-92-5314661/lite/</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>16 जिल्ह्यांना रेड अलर्ट! राज्याच्या ‘या’ भागात अतिवृष्टी, बचाव पथक सज्ज; CM फडणवीसांची...</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>https://www.tv9marathi.com/maharashtra/rain-alert-in-16-districts-heavy-rainfall-in-this-part-of-state-cm-fadnavis-give-information-1472499.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Crop damage : 4 लाख हेक्टर क्षेत्रावरील पिकांची हानी</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>https://pudhari.news/maharashtra/mumbai/crop-damage-4-lakh-hectares-ab96</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>मुख्यमंत्री देवेंद्र फडणवीसांकडून पावसाचा आढावा: महाराष्ट्रात 4 लाख हेक्टरवरील पिके पाण्यात, उपाययोजनांचे ज...</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/cm-devendra-fadnavis-review-maharashtra-flood-135703334.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Devendra Fadnavis| मुख्यमंत्री देवेंद्र फडणवीस १९ रोजी पैठण तालुक्यात</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>https://pudhari.news/maharashtra/marathwada/chhatrapati-sambhajinagar/devendra-fadnavis-visit-paithan-taluka-19-august-ng81</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>तिसरी मुंबई आर्थिक विकासाचा नवा अध्याय – मुख्यमंत्री देवेंद्र फडणवीस</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>https://mahasamvad.in/176127/</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Maharashtra Heavy Rainfall | राज्यभरात अतिवृष्टीचा कहर; १५ जिल्ह्यांत रेड आणि ऑरेंज अलर्ट, नागरिकांनी घराबाहेर पडू नये: मुख्यमंत्री फडणवीस</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>https://pudhari.news/maharashtra/mumbai/maharashtra-heavy-rainfall-red-orange-alert-15-districts-cm-fadnavis-advisory-as80</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Mumbai Rains News: मुंबईसह महाराष्ट्रात 3 जिल्ह्यात शाळा-कॉलेज बंद, पावसाने सामान्यांचे झाले हाल; तलाव भरले</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>https://www.navarashtra.com/maharashtra/mumbai-rains-news-updates-school-college-closed-due-to-heavy-rains-thane-palghar-has-problem-963739.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>महाराष्ट्रातील खासदारांनी राधाकृष्णन यांना समर्थन द्यावे: मुख्यमंत्री देवेंद्र फडणवीसांचे आवाहन; ठाकरे गट अ...</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/c-p-radhakrishnan-vice-president-candidate-fadnavis-urges-support-135703533.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>CM Relief Fund: रुग्णांसाठी सरकारचा 'हा' विभाग ठरतोय मदतशीर; अमरावती विभागात तब्बल १०.६१ कोटींची मदत</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>https://www.navarashtra.com/maharashtra/amravati/cm-devendra-fadnavis-cm-relief-fund-help-amravati-1187-patients-for-10-crore-rs-health-marathi-news-963412.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Marathwada Rain : मराठवाड्यात शेतीचे सर्वाधिक नुकसान; नांदेडमध्ये ढगफुटी सदृष्य पाऊस, पाच जण बेपत्ता</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>https://www.mymahanagar.com/maharashtra/cloudburst-rain-in-mukhed-nanded-district-five-people-missing-chief-minister-devendra-fadnavis-gave-information/913157/</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>पूरस्थितीचा सामना करण्यासाठी सरकारकडून सर्वतोपरी प्रयत्न, अतिवृष्टीचा धोका लक्षात घेऊन लोकांनी खबरदारी घ्यावी, मुख्यमंत्र्यांचं आवाहन</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/mr/!state/maharashtra-government-is-making-every-effort-to-deal-with-the-flood-situation-the-chief-minister-appeals-to-people-to-be-careful-considering-the-risk-of-heavy-rains-maharashtra-news-mhs25081804221</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Nanded Breaking : मोठी बातमी! नांदेडमध्ये अनेक गाव पाण्याखाली, 15 जण अडकले तर 40 ते 50 म्हशीचा पाण्यात बुडून मृत्यू</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>https://www.lokshahi.com/news/rains-in-nandeds-mukhed-taluka-have-caused-flash-floods-in-many-villages-and-information-has-emerged-that-15-people-from-the-village-are-stranded</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Solapur News : शिंदेंच्या सेनेत राज्यातून ‘इन्कमिंग’ पण सोलापुरात गळती, तानाजी सावंतांच्या बंधूंचा भाजप प्रवेश ठरला</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>https://www.mymahanagar.com/maharashtra/tanaji-sawant-brother-shivajirao-sawant-resign-eknath-shinde-sena-join-bjp-after-meet-fadnavis/913179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Maharashtra Politics Live Updates : जगनमोहन रेड्डींच्या पक्षाचा सीपी राधाकृष्णन यांना जाहीर पाठिंबा</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-18-august-2025-latest-marathi-political-news-eknath-shinde-mumbai-mahayuti-rahul-gandhi-congress-india-aghadi-election-commission-devendra-fadnavis-uddhav-thackeray-india-alliance-mumbai-pune-ajit-pawar-ncp-local-elections-rahul-gandhi-vote-adhikar-yatra-nda-cp-radhakrishnan-vice-presidential-candidat</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>लातूर जिल्ह्यात मुसळधार पाऊस; लेंडी नदीला पूर आल्यानं तेलंगाणातील चार प्रवासी गेले वाहून; मुख्यमंत्र्यांनी घेतला आढावा</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/mr/!state/heavy-rains-in-latur-district-cause-flooding-in-many-rivers-cm-devendra-fadnavis-took-a-review-lendi-river-flood-maharashtra-news-mhs25081802447</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>CM Devendra Fadnavis: राज्यातील चार लाख हेक्टर क्षेत्रावरील पिकांना फटका; पिकांचे पंचनामे करण्याचे आदेश</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>https://deshdoot.com/crops-affected-on-four-lakh-hectares-of-land-in-the-state-orders-to-conduct-crop-surveys/</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>CM Devendra Fadnavis: मुख्यमंत्र्यांनी राज्यातील पावसाचा घेतला आढावा; 'इतक्या' जिल्ह्यांना पावसाचा रेड अलर्ट, सतर्क राहण्याचे केले आवाहन</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>https://deshdoot.com/cm-fadnavis-takes-reiew-situation-ndrf-and-army-deployed-16-districts-on-red-alert/</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Shivaji Sawant : तानाजी सावंतांचे बंधू शिवाजी सावंतांचा भाजप प्रवेश निश्चित; मुख्यमंत्र्यांच्या भेटीनंतर जाहीर केला निर्णय</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/shivaji-sawants-entry-into-bjp-confirmed-decision-announced-after-meeting-with-chief-minister-vd83</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>मोदींचा निर्णय, उमेदवार ठरला अन् अडचणीत उद्धवसेना; 18 वर्षांनी पुन्हा तेच, ठाकरेंसमोर पेच?</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-picks-cp-radhakrishnan-for-vice-president-post-cm-devendra-fadnavis-ask-uddhav-thackeray-for-support/articleshow/123362737.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>महायुतीच्या 'या' मंत्र्यावर 5 हजार कोटींच्या भ्रष्टाचाराचा आरोप; रोहित पवारांची मुख्यमंत्री फडणवीसांकडे राजीनाम्याची मागणी</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>https://puneprimenews.com/mumbai/this-minister-of-mahayuti-accused-of-corruption-worth-rs-5000-crores-rohit-pawar-demands-resignation-from-chief-minister-fadnavis/</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Maharashtra Rain Update : शाळांना सुट्टी आहे की नाही? नेमका निर्णय काय? फडणवीसांनीच संभ्रम संपवला;...</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>https://www.tv9marathi.com/photo-gallery/maharashtra-rain-update-mumbai-rain-school-and-college-holiday-decision-will-be-taken-after-weather-forecast-1472649.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Mukhed cloudburst: मुखेडमध्ये ढगफुटी! 800 गावांना फटका, 226 लोकांची सुटका, 4 गावातले लोक फसले, सैन्याला पाचारण</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>https://marathi.ndtv.com/maharashtra/rain-big-news-mukhed-cloudburst-nanded-rain-news-calling-out-the-army-maharashtra-rain-alert-9107388</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>राजधानीत पावसाचा कहर! मुंबई विद्यापीठाचा परीक्षांबाबत तडकाफडकी मोठा निर्णय!</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>https://www.tv9marathi.com/maharashtra/mumbai-university-postponed-its-all-exam-to-be-held-on-19-august-due-to-heavy-rain-marathi-news-1472932.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Sambhajinagar News : आता शहरवासीयांना मिळणार अतिरिक्त २६ एमएलडी पाणी</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>https://pudhari.news/maharashtra/marathwada/chhatrapati-sambhajinagar/now-city-residents-will-get-additional-26-mld-of-water-np88</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>अन्वयार्थ : राजकीयीकरणाचा उत्सवी अधर्म</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/sampadkiya/columns/dahi-handi-2025-political-grip-on-dahi-handi-festival-10-thar-human-pyramid-25-lakh-cash-prize-zws-70-5314039/</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>मराठ्यांच्या इतिहासाचं सोनेरी पान उलगडलं, मुख्यमंत्र्यांच्या हस्ते सरदार रघुजी राजे भोसले यांच्या ऐतिहासिक तलवारीचं लोकार्पण</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/mr/!state/unveiling-the-historic-sword-of-sardar-raghuji-raje-bhosale-in-mumbai-presence-of-chief-minister-devendra-fadnavis-know-history-of-raghuji-raje-sword-maharashtra-news-mhs25081900619</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Rain Update : मराठवाड्यात मृत्यूचं तांडव, तुफान पावसाने सगळं उद्ध्वस्त; मदतीसाठी थेट मिलिटरी दाखल!</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>https://www.tv9marathi.com/maharashtra/maharashtra-rain-update-marathwada-all-district-affected-by-heavy-rain-total-6-people-died-marathi-news-1472571.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Jalgaon mob lynching Case: जामनेर मॉब लिंचिंग: युवकाच्या हत्येत मंत्री गिरीश महाजनांच्या ड्रायव्हरचा मुलगा मास्टर माईंड?</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/maharashtra-news-jalgaon-jamner-mob-lynching-girish-mahajan-driver-son-mastermind-youth-killed-mm76-sd67</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>'उपराष्ट्रपती'साठी महाराष्ट्राच्या राज्यपालांचे नाव; फडणवीसांचे खासदारांना आवाहन, पवार-ठाकरेंना टोला</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-urges-mps-to-support-radhakrishnan-targets-uddhav-thackeray-and-sharad-pawar-035137.html?ref_source=OI-MR&amp;ref_medium=Home-Page&amp;ref_campaign=News-Cards</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>नांदेडमध्ये मुसळधार पावसाने हाहाकार,मुख्यमंत्री फडणवीस यांच्या देखरेखीखाली मदतकार्य तीव्र</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/heavy-rains-wreak-havoc-in-nanded-relief-work-intensified-under-the-supervision-of-chief-minister-fadnavis-125081800046_1.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>महाराष्ट्रात सर्वदूर पावसामुळे हाहाकार; मोठ्या प्रमाणात जीवित आणि वित्तहानी, बळीराज अडचणीत!</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>https://mpbreakingnews.in/marathi/maharashtra/rains-wreak-havoc-across-maharashtra-massive-loss-of-life-and-property-farmers-in-trouble-06-692619</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>भाजपला स्थानिक ची निवडणूक महायुती म्हणूनच का लढवायची आहे?</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>https://aaplaawajnews.com/2025/34070/</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>युवकांसाठी मोठी खुशखबर; ‘या’ ठिकाणी आयटी पार्क उभारणार; मुख्यमंत्र्यांची घोषणा</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>https://www.nagpurtoday.in/great-news-for-youth-it-park-will-be-set-up-at-this-place-chief-ministers-announcement/08181712</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>10 रुपयांत ‘शिवभोजन थाळी’ योजना थांबणार? शिवभोजन केंद्र चालकांची कोट्यवधींची बिलं थकली</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>https://mpbreakingnews.in/marathi/maharashtra/will-the-shiv-bhojan-thali-scheme-for-10-rupees-stop-shiv-bhojan-center-operators-are-facing-bills-worth-crores-02-692694</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>MONSOON UPDATE: १५ ते १६ जिल्ह्यांत रेड आणि ऑरेंज अलर्ट; CM DEVENDRA FADNAVIS म्हणाले…</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>https://www.timemaharashtra.com/maharashtra/monsoon-update-red-and-orange-alert-in-15-to-16-districts-cm-devendra-fadnavis-said/129346/</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>नागपूरच्या राजे रघुजी भोसलेंची तलवार लंडनमधून मुंबईत, इतिहासाशी नवीन पिढीला जोडण्याचं कामं, मुख्यमंत्र्यांकडून कौतुक</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>https://mpbreakingnews.in/marathi/maharashtra/nagpurs-raja-raghuji-bhosales-sword-arrives-in-mumbai-from-london-02-692697</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Those who speak of Maharashtra 'asmita' should support Radhakrishnan for VP post Fadnavis</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom25-mh-governor-ld-fadnavis.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Nanded rains latest UPDATES: Water from Karnataka reach district; Indian Army, SDRF deployed for rescue missions as villagers trapped</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>https://www.theweek.in/news/india/2025/08/18/mumbai-rain-news-nanded-rains-latest-updates-water-from-karnataka-reach-district-indian-army-sdrf-deployed-for-rescue-missions-and-villagers-trapped.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Sword of Raghuji Bhonsle arrives in Mumbai and will be on display till Aug 25</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/sword-of-raghuji-bhonsle-arrives-in-mumbai-and-will-be-on-display-till-aug-25/articleshow/123371745.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Mumbai rain highlights: BMC declares holiday for schools, colleges today amid heavy rain forecast</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/india-news/mumbai-rain-live-updates-red-alert-school-closed-heavy-rains-august-18-weather-waterlogging-borivali-thane-powai-bmc-101755498397210.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Mumbai rains HIGHLIGHTS: Civic body declares holiday for all schools on August 19</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>https://www.business-standard.com/india-news/live-news-updates-mumbai-rain-waterlogging-traffic-heavy-rain-orange-alert-125081800291_1.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Monsoon mayhem: Heavy rains flood this state, schools and colleges shut</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>https://www.patrika.com/en/national-news/monsoon-mayhem-heavy-rains-flood-this-state-schools-and-colleges-shut-19874810</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>मुंबईतील सर्व शासकीय आणि निमशासकीय कार्यालयांना आज सुट्टी जाहीर!</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/8/19/mumbai-rains-govt-declares-holiday-for-all-government-and-private-offices-amid-heavy-rainfall.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Ashish Shelar : मुंबईत मुसळधार.. परिस्थितीचा आढावा घेतल्यानंतर शेलारांकडून मुंबईकरांना एकच आवाहन; आज,...</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>https://www.tv9marathi.com/videos/ashish-shelar-appeals-to-mumbaikars-after-review-of-rains-at-bmc-stay-at-house-during-mumbai-heavy-rains-1472440.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Thane Rain: ठाणे जिल्ह्यात झोडपणी; ठाणे, कल्याण, डोंबिवलीतील सखल भाग जलमय, आज शाळांना सुट्टी</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/maharashtra/thane/waterlogging-in-thane-kalyan-dombivali-schools-closed-today-19-august/articleshow/123374806.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Mumbai Rain Alert:मुंबईत पावसाची धुवाँधार बॅटिंग;शाळांना सुट्टी जाहीर</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>https://ilovenagar.com/mumbai-rain-alert-schools-declare-holiday-today/</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>SUPER 100 : राष्ट्रपति ट्रंप की जेलेंस्की और यूरोपीय नेताओं की साथ बैठक में अमेरिका, रूस और यूक्रेन के बीच त्रिपक्षीय वार्ता पर बनी सहमति...</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>https://www.indiatv.in/video/news-bulletin/super-100-in-the-meeting-of-president-trump-with-zelensky-and-european-leaders-an-agreement-was-reached-on-trilateral-talks-between-america-russia-2025-08-19-1156864</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>मुंबई में आज शाम हाई टाइड, लोगों से सावधानी की अपील, भारी बारिश का लोकल ट्रेनों</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>https://www.abplive.com/photo-gallery/states/maharashtra-mumbai-heavy-rainfall-waterlogging-imd-red-alert-local-train-delayed-photos-maharashtra-news-2997487</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>समाचार संध्या</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>https://www.newsonair.gov.in/bulletins-detail/%E0%A4%B8%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%BE%E0%A4%B0-%E0%A4%B8%E0%A4%82%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%BE-508/</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>नवीन पिढीला इतिहासाशी जोडण्याचे कार्य सुरू – मुख्यमंत्री देवेंद्र फडणवीस</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>https://mahasamvad.in/176229/</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Aaj Ki Baat: Mumbai में बारिश का Red Alert...48 घंटे संभलकर</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>https://www.indiatv.in/video/aaj-ki-baat/aaj-ki-baat-red-alert-for-rain-in-mumbai-be-careful-for-48-hours-2025-08-19-1156835</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>CM Devendra Fadnavis यांच्या हस्ते अद्ययावत पोलीस सदनिकेचे उद्घाटन</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>https://www.tarunbharat.com/cm-devendra-fadnavis-inauguration-of-new-police-building-kolhapur-marathi-news/</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Third Mumbai: महाराष्ट्राच्या विकासाचे नवे ग्रोथ सेंटर! काय म्हणाले CM फडणवीस?</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>https://www.tendernama.com/tender-news/third-mumbai-new-growth-center-for-maharashtras-development-what-did-cm-fadnavis-say</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>इतिहासाची अमूल्य खुण भारतात! इतिहासाशी पुन्हा जोडणारा क्षण, मुख्यमंत्री फडणवीसांची भावनिक प्रतिक्रिया</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>https://www.esakal.com/maharashtra/chief-minister-devendra-fadnavis-statement-after-bringing-sword-of-raje-raghuji-bhosale-to-india-vru98</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Maharashtra Breaking News LIVE : दिवसभरातील महत्त्वाच्या घडामोडी, ब्रेकिंग न्यूजचा आढावा एका क्लिकवर</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-august-18-political-news-in-marathi-933194</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>मुंबईत सर्व शासकीय-निमशासकीय कार्यालयांना सुट्टी जाहीर, फॉर्सबेरी जलाशयाजवळ चार तासात 109 मिमी पावसाची नोंद</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/mr/!state/mumbai-rain-news-all-government-semi-government-offices-in-mumbai-remain-closed-today-mumbai-local-tracks-under-water-amid-imd-red-alert-for-extremely-heavy-rainfall-maharashtra-news-mhs25081901225</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Weather Updates : मुंबईत अचानक एवढा पाऊस का पडतोय? पुणे वेधशाळेच्या हवामान शास्त्रज्ञांनी</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/pune-imd-on-heavy-rainfall-know-why-is-mumbai-suddenly-getting-so-much-rain-wather-update-imd-alert-for-mumbai-thane-for-next-48-hours-1377940</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>School Student Stuck in Bus : बसमध्ये अडकलेल्या लहानग्यांना गुढघाभर पाण्यातून काढले बाहेर, पोलिसांच्या कृतीचे कौतुक, Video Viral</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/maharashtra-rain-news-update-mumbai-matunga-school-bus-stuck-children-rescued-by-police-video-viral-/40071</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>उत्तराखंड विधानसभेत सादर होणार नवे अल्पसंख्यांक शिक्षण विधेयक</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/new-minority-education-bill-to-be-introduced-in-uttarakhand-assembly.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>मराठवाड्यात आज आणि उद्याही पावसाचे धुमशान, विभागीय आयुक्तांचा नागरिकांबरोबरच प्रशासनालाही सतर्कतेचा इशारा</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>https://newstown.in/weather-alert-heavy-to-very-heavy-rain-predicted-on-18-1nd-19-august-2025-in-marathwada-region-by-imd-administration-on-alert/</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>कोल्हापूर सर्किट बेंच झाले, आता खंडपीठाचा प्रस्ताव द्या; सरन्यायाधीश भूषण गवईंची सूचना</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>https://ratnagirikhabardar.com/news/74340/</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>प्रशांत यादव यांचा आज भाजप प्रवेश</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>https://ratnagirikhabardar.com/news/74397/</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Mumbai gets 177mm rain in 6-8 hour period, says CM; all agencies asked to remain alert</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/news/india/mumbai-gets-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/amp_articleshow/123365291.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Upcoming ‘Third Mumbai’ will spur economic growth, says Maharashtra chief minister</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/upcoming-third-mumbai-will-spur-economic-growth-says-maharashtra-chief-minister/articleshow/123368667.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>CM’s nod for new terminal bldg at Nashik airport received: Min</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/nashik/cms-nod-for-new-terminal-bldg-at-nashik-airport-received-min/articleshow/123372835.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Maharashtra rains: Five missing, several stranded as heavy rains lash Nanded, rescue operations underway</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>https://www.indiatvnews.com/maharashtra/maharashtra-rains-five-missing-several-stranded-as-heavy-rains-lash-nanded-rescue-operations-underway-2025-08-18-1004046</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Heavy rains lash Mumbai; red alert issued, Vihar Lake overflows, CM urges caution</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/cities/mumbai/mumbai-rain-updates-august-18-2025/article69946286.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>225 trapped in Nanded floods; Army, NDRF deployed for rescue ops</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>https://tripurachronicle.in/national-news/225-trapped-in-nanded-floods-army-ndrf-deployed-for-rescue-ops/</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Maha CM asks agencies to be on alert mode after heavy rainfall and flash floods</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>https://www.socialnews.xyz/2025/08/18/maha-cm-asks-agencies-to-be-on-alert-mode-after-heavy-rainfall-and-flash-floods/</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Devendra Fadnvis | मुख्यमंत्री देवेंद्र फडणवीस १९ रोजी पैठण तालुक्यात</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/mr-in/news/other/devendra-fadnvis-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A5%A7%E0%A5%AF-%E0%A4%B0-%E0%A4%9C-%E0%A4%AA%E0%A5%88%E0%A4%A0%E0%A4%A3-%E0%A4%A4-%E0%A4%B2%E0%A5%81%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%A4/ar-AA1KKgDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>देवेंद्र फडणवीस यांच्यासोबतच्या कोल्ड वॉरच्या चर्चेवर एकनाथ शिंदे यांची प्रतिक्रिया, स्पष्टच म्हणाले....</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/mr-in/news/national/%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%AC%E0%A4%A4%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%A1-%E0%A4%B5-%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A%E0%A5%87%E0%A4%B5%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A4%9A-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1zqXD8?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Devendra Fadnavis | डॉ. आंबेडकर महाविद्यालयाने समाज परिवर्तनाचे केंद्र बनावे : मुख्यमंत्री देवेंद्र फडणवीस</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-%E0%A4%A1-%E0%A4%86%E0%A4%82%E0%A4%AC%E0%A5%87%E0%A4%A1%E0%A4%95%E0%A4%B0-%E0%A4%AE%E0%A4%B9-%E0%A4%B5-%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%B2%E0%A4%AF-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%AA%E0%A4%B0-%E0%A4%B5%E0%A4%B0%E0%A5%8D%E0%A4%A4%E0%A4%A8-%E0%A4%9A%E0%A5%87-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AC%E0%A4%A8-%E0%A4%B5%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8/ar-AA1JMyQJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>महाराष्ट्रात महाभयानक पाऊस! मुख्यमंत्री देवेंद्र फडणवीस यांनी तातडीने साधला शेजारील राज्यांशी संपर्क? कारण अतिशय चिंताजनक</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%AE%E0%A4%B9-%E0%A4%AD%E0%A4%AF-%E0%A4%A8%E0%A4%95-%E0%A4%AA-%E0%A4%8A%E0%A4%B8-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A4-%E0%A4%A4%E0%A4%A1-%E0%A4%A8%E0%A5%87-%E0%A4%B8-%E0%A4%A7%E0%A4%B2-%E0%A4%B6%E0%A5%87%E0%A4%9C-%E0%A4%B0-%E0%A4%B2-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B6-%E0%A4%B8%E0%A4%82%E0%A4%AA%E0%A4%B0%E0%A5%8D%E0%A4%95-%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%85%E0%A4%A4-%E0%A4%B6%E0%A4%AF-%E0%A4%9A-%E0%A4%82%E0%A4%A4-%E0%A4%9C%E0%A4%A8%E0%A4%95/ar-AA1KJav3</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>मुंबईतील पावसाचा मुख्यमंत्र्यांकडून सातत्याने आढावा</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/8/19/the-chief-minister-is-continuously-reviewing-the-rainfall-in-mumbai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>राजधानीत पावसाचा कहर! मुंबई विद्यापीठाचा परीक्षांबाबत तडकाफडकी मोठा निर्णय!</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>https://www.tv9marathi.com/maharashtra/mumbai-university-postponed-its-all-exam-to-be-held-on-19-august-due-to-heavy-rain-marathi-news-1472932.html/amp</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>BJP ने शिंदे गुट में लगाई सेंध! कट्टर शिवसैनिक छोड़ेंगे पार्टी, निकाय चुनाव से पहले दिया बड़ा झटका</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>https://www.patrika.com/mumbai-news/maharashtra-politics-bjp-gives-setback-to-eknath-shinde-shiv-sena-before-civic-polls-19873589</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>महाराष्ट्र में भारी बारिश से सात लोगों की मौत, 200 ग्रामीण फंसे</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>https://hindi.theprint.in/india/seven-people-died-due-to-heavy-rains-in-maharashtra-200-villagers-stranded/856903/?amp</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>महाराष्ट्र में मानसून का कहर: मुखेड तालुका में बादल फटने जैसी घटना, 200 से ज्यादा गांवों में बाढ़</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>https://hindi.dynamitenews.com/maharashtra/cloudburst-in-mukhed-taluka-in-maharashtra-flood-in-more-than-200-villages</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>CM फडणवीस ने खेला 'मराठी अस्मिता' का दांव, उपराष्ट्रपति चुनाव में उद्धव-पवार पर बना दबाव</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>https://navbharatlive.com/maharashtra/political-battle-over-nda-candidate-radhakrishnan-cm-fadnavis-seeks-support-from-uddhav-thackeray-and-sharad-pawar-1321873.html/amp</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Mumbai News: चव्हाण ने कहा - श्रमिकों की एक साल में दो बार होगी वेतन वृद्धि</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>https://www.bhaskarhindi.com/city/mumbai/mumbai-news-chavan-said-workers-will-get-salary-hike-twice-in-a-year-1174137</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Vidarbha Crop Loss: विदर्भात दोन लाख हेक्टरवर पीक नुकसान</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>https://agrowon.esakal.com/agro-special/crop-damage-on-two-lakh-hectares-in-vidarbha-rat16</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>मुख्यमंत्री फडणवीस यांची माहिती, राज्यात अतिवृष्टी, ८०० गावे बाधित, मुंबईत १७० एमएम पाऊस</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>https://www.marathiebatmya.com/political/cm-fadnavis-said-heavy-rains-in-the-state-800-villages-affected-170-mm-rain/</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Heavy Rainfall : रेड ॲलर्ट घोषित केलेल्या ठिकाणी सतर्कता बाळगण्याचे मुख्यमंत्री फडणवीसांचे निर्देश</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>https://www.marathi.hindusthanpost.com/social/heavy-rainfall-cm-devendra-fadnavis-instructs-to-remain-vigilant-in-places-where-red-alert-has-been-declared/</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>'My karyakarta is with me': Hitendra Thakur shrugs off defections ahead of civic elections</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/en-in/news/India/my-karyakarta-is-with-me-hitendra-thakur-shrugs-off-defections-ahead-of-civic-elections/ar-AA1KHNiH</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Why Eknath Shinde is covering little distance despite frequent visits to Delhi</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/political-pulse/why-eknath-shinde-is-covering-little-distance-despite-frequent-visits-to-delhi-10197218/</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>NDA’s VP nominee CP Radhakrishnan meets PM Modi in Delhi</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>https://www.news9live.com/india/ndas-vp-nominee-cp-radhakrishnan-meets-pm-modi-in-delhi-2883321</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>'Destroying constitutional institutions': Nishikant Dubey slams Rahul Gandhi as SC dismisses plea challenging 2024 Maharashtra polls</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>https://www.malaysiasun.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>BJP man accuses Trinamool leaders of supporting Rohingyas, threatens to bulldoze them into Bangladesh</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>https://www.socialnews.xyz/2025/08/18/bjp-man-accuses-trinamool-leaders-of-supporting-rohingyas-threatens-to-bulldoze-them-into-bangladesh/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=bjp-man-accuses-trinamool-leaders-of-supporting-rohingyas-threatens-to-bulldoze-them-into-bangladesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Shivaji Sawant : शिवाजी सावंतांचा भाजपा प्रवेश निश्चित !</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>https://thefocusindia.com/maharashtra-news/shivaji-sawants-admission-to-bjp-is-certain-281398/amp/</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>राष्ट्रवादीचे प्रशांत यादव यांचा आज भाजप प्रवेश</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>https://pudhari.news/maharashtra/kokan/ratnagiri/ncp-prashant-yadav-joins-bjp-today-dc95</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Mumbai Rain Alert : मुंबईकरांनो सावध रहा.. पुढील 4 तास धोक्याचे… रेड अलर्ट अन् हवामान खात्याचा...</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>https://www.tv9marathi.com/videos/mumbai-weather-forecast-imd-red-alert-for-mumbai-for-next-4-hours-extremely-important-for-mumbaikars-1473139.html/amp</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Ashish Shelar: मुंबईत जोरदार पाऊस! पावसाचा आढावा घेतल्यानंतर मंत्री शेलार म्हणाले, 'अत्यंत गरज असल्यास...'</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/mumbai-rain-updates-ashish-shelar-reviewed-the-rainfall-and-said-stay-safe-at-home/40069</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Uddhav Thackeray: मनसेसोबत युती महापालिका निवडणुकीत घातक ठरणार; उद्धव ठाकरेंना 'या' नेत्यानं केलं सावध?</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/mns-alliance-risk-municipal-elections-uddhav-thackeray-warning-dk88-rc70</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Congress Mohan Joshi Pune | Don't wait for BJP's 'event', open the flyover</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>https://policenama.com/congress-mohan-joshi-pune-dont-wait-for-bjps-event-open-the-flyover-former-mla-mohan-joshis-letter-to-the-municipal-commissioner/</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>राज्यात ‘ओला दुष्काळ’ जाहीर करा, एकरी ५० हजार रुपयांची मदत द्या -शशिकांत शिंदे</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>https://politicalmaharashtra.in/declare-wet-drought-in-the-state-provide-assistance-of-rs-50000-per-acre-shashikant-shinde-97623/</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>‘गँग्स ऑफ गद्दार’: शिंदेचा मंत्री ‘रोहित पवारांच्या’ निशाण्यावर</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>https://politicalmaharashtra.in/gangs-of-traitors-shindes-minister-targeted-by-rohit-pawar-97619/</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>To collect outstanding transportation fines, the Maha government is planning an amnesty scheme</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>https://assamtribune.com/national/to-collect-outstanding-transportation-fines-the-mahagovernment-is-planning-an-amnesty-scheme-1588536</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>NCP (SP) targets Maha minister over Rs 5,000 cr scam in Navi Mumbai’s CIDCO land; demands his resignation</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>https://www.socialnews.xyz/2025/08/18/ncp-sp-targets-maha-minister-over-rs-5000-cr-scam-in-navi-mumbais-cidco-land-demands-his-resignation/</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Ahead of Civic Polls, Hitendra Thakur Backs Loyalists: ‘My Karyakarta Is With Me, They Ensure Our Party Wins</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>https://www.lokmattimes.com/maharashtra/ahead-of-civic-polls-hitendra-thakur-backs-loyalists-my-karyakarta-is-with-me-they-ensure-our-party-wins-a475/</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Muqabla: 'वोट चोरी' पर जीत किसकी...Rahul Gandhi या Election Commission?</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>https://www.indiatv.in/video/news-bulletin/muqabla-rahul-gandhi-or-the-election-commission-who-wins-the-vote-theft-battle-2025-08-19-1156831</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>'ऑपरेशन लोटस वगैरे काही नाही; लवकरच ऑपरेशन टायगर दिसेल', सोलापूरच्या राजकारणात पडद्यामागे काय घडतंय?</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/maharashtra/solapur/solapur-politics-over-shiv-sena-leader-shivaji-sawant-may-join-bjp/articleshow/123369493.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Nagpur Politics | भाईंनी घातला पक्ष प्रवेशाचा दुपट्टा,आता शिवसेनेचे घुमजाव</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/mr-in/news/other/nagpur-politics-%E0%A4%AD-%E0%A4%88%E0%A4%82%E0%A4%A8-%E0%A4%98-%E0%A4%A4%E0%A4%B2-%E0%A4%AA%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6-%E0%A4%9A-%E0%A4%A6%E0%A5%81%E0%A4%AA%E0%A4%9F%E0%A5%8D%E0%A4%9F-%E0%A4%86%E0%A4%A4-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%9A%E0%A5%87-%E0%A4%98%E0%A5%81%E0%A4%AE%E0%A4%9C-%E0%A4%B5/ar-AA1HHJp9</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Coffee Par Kurukshetra: उपराष्ट्रपति के नाम पर INDI अलायंस टूट जाएगा?</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>https://www.indiatv.in/video/kurukshetra/coffee-par-kurukshetra-indi-2025-08-19-1156832</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>मुंबई में 19 अगस्त को भी जारी रहेगा बारिश का कहर, मौसम विभाग ने दी बड़ी चेतावनी, जारी किया रेड अलर्ट</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>https://hindi.asianetnews.com/national-news/mumbai-braces-for-more-heavy-rain-on-19-august-imd-issued-red-and-orange-alert/articleshow-9knobps</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>महाराष्ट्र में मौसम बरपा रहा कहर: नांदेड़ में फटा बादल, बारिश के चलते 15 से 16 जिलो में अलर्ट, CM फडणवीस ने फसलों से लेकर लोकल ट्रेनों के बारे में दिया ये बड़ा अपडेट | Devendra Fadnavis, Cloudburst, Nan</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>https://www.bhaskarhindi.com/politics/devendra-fadnavis-cloudburst-nanded-maharashtra-news-maharashtra-1174025</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Amravati Politics: अमरावती के दरियापुर में कांग्रेस को बड़ा झटका, सलीम घनीवाला भाजपा में शामिल</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>https://navbharatlive.com/maharashtra/amravati/major-blow-to-congress-in-dariyapur-of-amravati-salim-ghaniwala-joins-bjp-1321794.html/amp</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>शिवसेना शिंदे गुट को बड़ा झटका, बड़ा नेता छोड़ेगा एकनाथ शिंदे का साथ</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>https://mpbreakingnews.in/maharashtra/shivaji-sawant-bjp-solapur-eknath-shinde-54-804117</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>NDA से उपराष्ट्रपति पद के उम्मीदवार चुने जाने पर C.P Radhakrishnan को PM मोदी ने दी बधाई</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>https://www.primetvindia.com/pm-modi-congratulated-c-p-radhakrishnan/</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Devendra Fadnavis: चार लाख हेक्टर क्षेत्रावरील पिकांना फटका; मुख्यमंत्र्यांनी घेतला राज्यातील स्थितीचा आढावा</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/heavy-rains-damage-crops-on-4-lakh-hectares-cm-devendra-fadnaivs-reviews-situation-in-maharashtra/articleshow/123379831.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Amravati News : अमरावतीच्या दर्यापुरात काँग्रेसला मोठा धक्का, सलीम घाणीवालांचा भाजपमध्ये प्रवेश</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>https://marathi.ndtv.com/politics/salim-ghaniwala-joins-bjp-big-blow-to-congress-in-daryapur-amravati-9106782</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>ABP Majha Top 10 Headlines : ABP माझा टॉप 10 हेडलाईन्स | 18 ऑगस्ट 2025 | सोमवार</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/maharashtra/abp-majha-top-10-headlines-18-august-2025-monday-latest-marathi-news-update-maharashtra-politics-marathi-news-1378004</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Mumbai Rain Red Alert : पावसामुळे आतापर्यंत 7 जणांचा मृत्यू; साचलेल्या पाण्यामुळे प्रवाशांचे हाल अन् राजकारणही तापलं</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>https://sarkarnama.esakal.com/mumbai/mumbai-rain-red-alert-heavy-rainfall-maharashtra-floods-bmc-pune-schooll-jap93</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>मंत्री आशीष शेलार यांनी घेतला आपात्कालीन व्यवस्थापनाचा आढावा</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>https://www.jpnnews.in/2025/08/Ashish-Shelar-reviews-emergency-management.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>राज्यात पावसाचा हाहाकार! मुख्यमंत्री फडणवीस अॅक्टीव्ह मोडवर, सतर्क राहण्याचे आवाहन</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>https://civicmirror.in/maharashtra/maharashtra-rain-cm-fadnavis-reviews-situation-16-districts-on-red-alert/</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>‘शिंदेंच्या सेनेला’ दे धक्का : या आमदार बंधूंनी सोडला पक्ष</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>https://politicalmaharashtra.in/a-blow-to-shindes-army-these-mla-brothers-left-the-party-97625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Historic sword of Raje Raghuji Bhonsle arrives in Mumbai to royal welcome</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>https://www.nagpurtoday.in/historic-sword-of-raje-raghuji-bhonsle-arrives-in-mumbai-to-royal-welcome/08181446</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Seize assets of school directors in Shalarth ID scam: Bawankule</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/seize-assets-of-school-directors-in-shalarth-id-scam-bawankule/articleshow/123371134.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Nagpur Smart City projects near closure with 7 works still pending</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>https://infra.economictimes.indiatimes.com/news/urban-infrastructure/nagpur-smart-city-projects-face-delay-7-projects-pending-completion/123360909</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>NMC pushes ahead with land acquisition for 2 STPs amid reluctance from VNIT, PKV</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/nmc-pushes-ahead-with-land-acquisition-for-2-stps-amid-reluctance-from-vnit-pkv/articleshow/123372521.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>MBBS admission quota in unaided colleges cut by 50%, students erupt</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/mbbs-admission-quota-in-unaided-colleges-cut-by-50-students-erupt/articleshow/123372541.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>३१ खासदार निवडून आले तेव्हा मतदारयाद्या बरोबर होत्या का ?</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>https://www.lokmat.com/nagpur/were-the-voter-lists-correct-when-31-mps-were-elected-a-a1000/</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>रघुजी राजे यांची तलवार आणि ‘स्व’चा बोध</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/historic-sword-of-shrimant-raghuji-bhosle-back-in-mumbai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Sambhajinagar News : आता शहरवासीयांना मिळणार अतिरिक्त २६ एमएलडी पाणी</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>https://pudhari.news/amp/story/maharashtra/marathwada/chhatrapati-sambhajinagar/now-city-residents-will-get-additional-26-mld-of-water-np88</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Chandrashekhar Bawankule: 'आताच मतदार याद्या तपासा', महसूल मंत्र्यांचा काँग्रेस नेत्यांना टोला</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/chandrashekhar-bawankule-demands-to-check-voter-lists-against-congress-allegations/articleshow/123356783.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Nagpur News: नव्या नागपूरला मिळणार तिसऱ्या रिंग रोडची जोड; ३६ गावांतील सुमारे ८८० हेक्टर जमिनीचे अधिग्रहण</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>https://www.esakal.com/vidarbha/nagpur/nagpur-to-get-third-ring-road-with-land-acquisition-from-36-villages-vsb99</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Nagpur Accident : नागपुरातील हिट अँड रन प्रकरणाचा AI तंत्रज्ञानाच्या मदतीने उलगडा राज्यातील</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/crime/nagpur-hit-and-run-accident-news-update-case-solved-with-the-help-of-ai-technology-first-experiment-in-the-state-driver-arrested-from-uttar-pradesh-1377914</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Teacher Recruitment Scam: बोगस शालार्थ आयडी घोटाळ्यातील संचालकांची मालमत्ता जप्त होणार !</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/bogus-teacher-scam-school-id-fraud-directors-property-to-be-seized-ng81</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>kolhapur | सर्किट बेंचचे स्वप्न साकारले; न्यायाचे दरवाजे खुले झाले!</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>https://pudhari.news/amp/story/maharashtra/kolhapur/circuit-bench-dream-realized-doors-of-justice-now-open-ap84</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>वरूणराजा कोपला! पिकांमध्ये पाणीच पाणी, पुढील 48 तासांत या जिल्ह्यांना पुन्हा रेड अलर्ट</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>https://news18marathi.com/agriculture/18-august-maharashtra-heavy-rain-update-monsoon-2025-mumbai-red-alert-1460576.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Third Mumbai in Raigad to become Maharashtra’s new economic powerhouse: CM Fadnavis</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>https://www.daijiworld.com/index.php/news/newsDisplay?newsID=1289652</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>kolhapur | सर्किट बेंचचे स्वप्न साकारले; न्यायाचे दरवाजे खुले झाले!</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>https://pudhari.news/maharashtra/kolhapur/circuit-bench-dream-realized-doors-of-justice-now-open-ap84</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Vice Presidential Election: सीपी राधाकृष्णन को NDA उम्मीदवार बनाने पर कांग्रेस को लगी मिर्ची, INDI गठबंधन कैंडिडेट पर खोले पत्ते</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>https://www.republicbharat.com/india/congress-angry-cp-radhakrishnan-nda-vice-presidential-candidate-opened-cards-on-indi-alliance-meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>India News | 12-day Himachal Pradesh Assembly Session Opens; Opposition Seeks Adjournment on Disaster</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>https://www.latestly.com/agency-news/india-news-12-day-himachal-pradesh-assembly-session-opens-opposition-seeks-adjournment-on-disaster-7064955.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Vice President Election: NDA उम्मीदवार सीपी राधाकृष्णन को मिल सकता है विपक्षी दलों का समर्थन, इन पार्टियों पर सबकी नजर</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>https://www.jagran.com/politics/national-rajya-sabha-election-opposition-parties-may-support-nda-candidate-cp-radhakrishnan-24017212.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>महाराष्ट्र की ‘अस्मिता’ की बात करने वाले उपराष्ट्रपति पद के लिए राधाकृष्णन का समर्थन करें : फडणवीस</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>https://hindi.theprint.in/india/support-radhakrishnan-for-the-post-of-vice-president-who-talks-about-maharashtras-identity-fadnavis/856729/</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Asia Cup 2025: पाकिस्तान क्रिकेट के मुख्य चयनकर्ता का बड़ा बयान, बोले- भारत को हराएगा पाकिस्तान</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>https://www.indiatv.in/video/sports/asia-cup-2025-2025-08-18-1156799</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Haqiqat Kya Hai: मुनीर के मरने की तारीख भी आने वाली है ?</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>https://www.indiatv.in/video/hakikat-kya-hai/haqiqat-kya-hai-2025-08-19-1156836</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>कौन लेगा CP राधाकृष्णन की जगह? BJP की एक खोज खत्म होते ही शुरू हुई दूसरी तलाश</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>https://navbharatlive.com/maharashtra/maharashtra-new-governor-who-will-replace-cp-radhakrishnan-bjp-new-search-begins-1321951.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Aaj Ka Rashifal, 19 Aug, 2025 : आचार्य इंदु प्रकाश जी से जानिए आज क्या कह रहे हैं आपके सितारे</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>https://www.indiatv.in/video/bhavishyawani/aaj-ka-rashifal-19-aug-2025-know-from-acharya-indu-prakash-ji-what-your-stars-are-saying-today-2025-08-19-1156865</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Yoga With Swami Ramdev :ज़्यादा स्क्रीन टाइम से बच्चों को दिल की बीमारी</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>https://www.indiatv.in/video/yoga/yoga-with-swami-ramdev-excessive-screen-time-can-cause-heart-disease-in-children-2025-08-19-1156871</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Farmers Loan Waiver: बावनकुळेंनंतर महायुती सरकारमधील 'या' मंत्र्याची कर्जमाफीबाबत मोठी अपडेट; म्हणाले,'CM फडणवीस लवकरच...'</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/sanjay-rathod-update-farmer-loan-waiver-devendra-fadnavis-dk88</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Election Commission Of India &amp; The “Politics Of Jugaad”</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>https://madrascourier.com/opinion/election-commission-of-india-the-politics-of-jugaad/</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Video | Bihar Elections | RJD Leader Tejaswi Yadav Takes On PM Modi Over Bihar Polls: "Stop Fooling..."</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>https://www.ndtv.com/video/bihar-elections-rjd-leader-tejaswi-yadav-takes-on-pm-modi-over-bihar-polls-stop-fooling-981918</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>CP Radhakrishnan vs who? Why DMK’s pushing INDIA bloc for a Tamil vs Tamil contest for India’s V-P</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>https://theprint.in/india/cp-radhakrishnan-vs-who-why-dmks-pushing-india-bloc-for-a-tamil-vs-tamil-contest-for-indias-v-p/2723136/</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>'Political opinions or...': Supreme Court quashes plea challenging validity of Maharashtra Assembly polls</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>https://www.deccanherald.com/india/political-opinions-or-supreme-court-quashes-plea-challenging-validity-of-maharashtra-assembly-polls-3686244</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Shiv Sena, NCP support Maha Governor’s nomination for Vice President</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>https://www.indianewsstream.com/shiv-sena-ncp-support-maha-governors-nomination-for-vice-president/</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>'Destroying constitutional institutions': Nishikant Dubey slams Rahul Gandhi as SC dismisses plea challenging 2024 Maharashtra polls</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>https://www.aninews.in/news/national/politics/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls20250819085747/</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Video | Parliament News | INDIA Bloc Continues Protest Against Bihar SIR At Parliament</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>https://www.ndtv.com/video/parliament-news-india-bloc-continues-protest-against-bihar-sir-at-parliament-982014</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>PM Modi appeals for unanimous election of Radhakrishnan as vice president</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>https://english.varthabharati.in/india/pm-modi-appeals-for-unanimous-election-of-radhakrishnan-as-vice-president</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Supreme Court dismisses plea alleging 75 lakh bogus votes in Maharashtra Assembly polls</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>https://organiser.org/2025/08/19/308844/bharat/supreme-court-dismisses-plea-alleging-75-lakh-bogus-votes-in-maharashtra-assembly-polls/</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Alcaraz wins the Cincinnati Open after Sinner retires in the first set because of illness</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>https://english.varthabharati.in/sports/alcaraz-wins-the-cincinnati-open-after-sinner-retires-in-the-first-set-because-of-illness</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>'संवैधानिक संस्थाओं को कर रहे हैं नष्ट...' भाजपा सांसद निशिकांत दुबे ने राहुल गांधी पर साधा निशाना</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>https://www.timesnowhindi.com/india/constitutional-institutions-are-being-destroyed-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls-article-152485768</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>खरगे, स्टॉलिन, नवीन पटनायक... उपराष्ट्रपति चुनाव से पहले राजनाथ सिंह को बीजेपी ने दी खास जिम्मेदारी</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/india/vice-president-election-defence-minister-rajnath-singh-reaches-out-to-dmk-tmc-bjd-for-consensus-for-cp-radhakrishnan/articleshow/123375990.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>शिवसेना एकनाथ शिंदे गुट को बड़ा झटका, शिवाजी सावंत भाजपा में होगें शामिल | Maharastra - Paliwalwani - Latest Hindi News</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>https://paliwalwani.com/maharastra/shiv-sena-eknath-shinde-faction-is-a-big-shock-shivaji-sawant-will-be-involved-in-bjp</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>चुनाव आयोग की प्रेस कॉन्फ्रेंस में इन दो पत्रकारों के सवालों ने बोलती बंद कर दी, देखें वीडियो – No. 1 Indian Media News Portal</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>https://www.bhadas4media.com/eci-press-confrence-journalist-question/</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>उपराष्ट्रपतीपदाचे उमेदवार राधाकृष्णन यांना पाठिंबा द्या; देवेंद्र फडणवीस यांची शरद पवार आणि उद्धव ठाकरे यांना साद</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>https://marathi.freepressjournal.in/maharashtra/cp-radhakrishnan-vice-president-candidate-fadnavis-appeal-pawar-thackeray</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>राहुल गांधी पक्ष टिकवण्यासाठी निवडणूक आयोगाचा आधार घेतात; मंत्री चंद्रशेखर बावनकुळे यांची टीका</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/rahul-gandhi-takes-support-from-election-commission-to-save-party-minister-chandrashekhar-bawankule-criticizes.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>‘मत चोरी’चा वाद वाढला, विरोधक मुख्य निवडणूक आयुक्तांविरोधात महाभियोग प्रस्ताव आणण्याच्या तयारीत - Marathi News | The controversy over 'vote theft' escalates, the opposition is preparing to bring an impeachment motio</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>https://www.lokmat.com/shorts/national/vote-theft-row-escalates-opposition-mulls-impeachment-of-election-commissioner/</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>हवामानाचा अंदाज: आजही पावसाचा कहर? मुंबई, पुण्यासह 7 जिल्ह्यांना रेड अलर्ट; गडचिरोलीसह 4 जिल्ह्यांना यलो अलर्ट</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>https://thefocusindia.com/national-news/maharashtra-weather-red-alert-mumbai-pune-7-districts-281414/amp/</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Pravin Darekar: राज्य सहकारी संघाच्या अध्यक्षपदी आमदार प्रवीण दरेकर</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>https://pudhari.news/maharashtra/pune/pravin-darekar-elected-cooperative-president-maharashtra-ac90</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>१९८७च्या काश्मीर निवडणूक गैरप्रकाराचा काँग्रेसला विसर - राजीव गांधींकडून विरोधकांच्या आरोपांकडे दुर्लक्ष</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/congress-forgets-1987-kashmir-election-malpractices-rajiv-gandhi-ignores-opposition-allegations.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Eknath Shinde : एकनाथ शिंदेंना मोठा धक्का ! ‘या’ नेत्याने निवडणुकीच्या तोंडावर सोडली साथ</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>https://www.dainikprabhat.com/big-blow-to-eknath-shinde-big-leader-of-shiv-sena-shinde-group-will-join-bjp/</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>'उपराष्ट्रपती'साठी महाराष्ट्राच्या राज्यपालांचे नाव; फडणवीसांचे खासदारांना आवाहन, पवार-ठाकरेंना टोला</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-urges-mps-to-support-radhakrishnan-targets-uddhav-thackeray-and-sharad-pawar-035137.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Maharashtra News: Dy CM Eknath Shinde Launches ‘Ladki Sun – Surakshit Sun’ Campaign To Protect Women</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-dy-cm-eknath-shinde-launches-ladki-sun-surakshit-sun-campaign-to-protect-women-victims</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Fadnavis meets Guv Radhakrishnan, presents him book of Shivaji Maharaj's letters</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>https://www.ptinews.com/detail/national/Fadnavis-meets-Guv-Radhakrishnan--presents-him-book-of-Shivaji-Maharaj-s-letters/2832581</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>'Slap, but don't make video': Raj Thackeray's blunt advice to MNS workers after Marathi 'slapgate' case</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/en-in/news/India/slap-but-dont-make-video-raj-thackerays-blunt-advice-to-mns-workers-after-marathi-slapgate-case/ar-AA1I11OF</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Mumbai: Iconic Sword of Raghuji Bhonsle Arrives from London; Bike Rally Cancelled Due to Rains, Grand...</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>https://www.lokmattimes.com/mumbai/mumbai-iconic-sword-of-raghuji-bhonsle-arrives-from-london-bike-rally-cancelled-due-to-rains-grand-inauguration-tonight-a525/</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>How CP Radhakrishnan Broke The Taboo Around Modi And Changed The Narrative After 2002 Gujarat Episode - The</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>https://thecommunemag.com/how-cpr-broke-the-taboo-around-modi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>पश्चिम महाराष्ट्रात शिंदेंना भाजपचा धक्का, आमदाराच्या भावासह ४० पदाधिकाऱ्यांचा शिवसेनेला जय महाराष्ट्र!</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>https://saamtv.esakal.com/maharashtra/solapur-political-news-bjp-strengthens-in-solapur-as-40-sena-leaders-join-with-shivaji-sawant-bdk97</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>सोलापुरात भाजपची शिंदेंच्या शिवसेनावर कुरघोडी शिवाजी सावंतांनी शिवसेना सोडली,</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/politics/solapur-shivaji-sawant-leaves-shiv-sena-and-bjp-entry-confirmed-devendra-fadnavis-bjp-attack-on-eknath-shinde-shiv-sena-in-solapur-1377928</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>सोलापूरच्या राजकारणात मोठी खळबळ; तानाजी सावंत यांचा भाऊ करणार भाजपात प्रवेश</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>https://www.timemaharashtra.com/politics/big-stir-in-solapur-politics-tanaji-sawants-brother-to-join-bjp/129377/</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Rohit Pawar on Sanjay Shirsath: रोहित पवारांचे मंत्री संजय शिरसाटांवर भ्रष्टाचाराचे गंभीर आरोप; पहा काय म्हणाले</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/amp</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Rohit Pawar: मंत्री संजय शिरसाटांनी केला ५ हजार कोटींचा घोटाळा; आमदार रोहित पवारांच्या आरोपाने खळबळ</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>https://deshdoot.com/rohit-pawar-alleges-sanjay-shirsat-over-5000-crore-worth-land-to-bivalkar-family/</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Shivsena | नाराजी भोवली! शिंदे गटातून बड्या नेत्याचा राजीनामा, राजकीय वर्तुळात खळबळ</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>https://www.thodkyaat.com/big-setback-for-eknath-shinde-faction-as-senior-leader-shivaji-sawant-joins-bjp-ahead-of-local-body-polls/</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Ekanath Shinde Shivsena : शिंदे गटाला धक्का; आमदाराचा भाऊ व 40 पदाधिकाऱ्यांचा पक्षप्रवेश</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>https://www.lokshahi.com/news/mla-tanaji-sawants-brother-shivaji-sawant-has-decided-to-quit-the-group-and-join-the-bjp</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>NCP demands : राज्यात ओला दुष्काळ जाहीर करा अन्…; राष्ट्रवादी शरद पवार गटाची मागणी</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>https://deshdoot.com/heavy-rains-wreak-havoc-in-maharashtra-sharad-pawar-ncp-demands-wet-drought-declaration-and-farmer-relief/</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>शिंदे गटाचे आमदार तानाजी सावंतांचे बंधू भाजपच्या वाटेवर</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>https://pcbtoday.in/%E0%A4%B6%E0%A4%BF%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%97%E0%A4%9F%E0%A4%BE%E0%A4%9A%E0%A5%87-%E0%A4%86%E0%A4%AE%E0%A4%A6%E0%A4%BE%E0%A4%B0-%E0%A4%A4%E0%A4%BE%E0%A4%A8%E0%A4%BE%E0%A4%9C%E0%A5%80/</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Rajnath reaches out to DMK, TMC, BJD for consensus on VP nominee</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/india/rajnath-reaches-out-to-dmk-tmc-bjd-for-consensus-on-vp-nominee/articleshow/123373035.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>MSRTC और पुलिस की पहल, गढ़चिरौली के आदिवासी गांव को मिला पहला सार्वजनिक परिवहन, ग्रामीणों ने लहराया तिरंगा</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>https://hindi.mid-day.com/news/india-news/photo/initiative-of-msrtc-and-police-tribal-village-of-gadchiroli-gets-first-public-transport-1558</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>LIVE Update : मुंबईतील सर्व शाळांना उद्या सुट्टी जाहीर</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>https://www.mymahanagar.com/maharashtra/live-update-mumbai-rain-best-co-operative-soc-election-live-maharashtra-update-political-rain-update-devendra-fadnavis-ajit-pawar-eknath-shinde-uddhav-thackeray-raj-thackeray/913004/</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>अमित शहा हे महाराष्ट्रातल्या गुंडांचे आणि भ्रष्टाचाऱ्यांचे दिल्लीतले सेनापती, संजय राऊत यांचा घणाघात</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>https://www.saamana.com/amit-shah-is-leader-of-maharashtra-corrupt-leader-says-sanjay-raut/</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Sanjay Raut : निसाकाचा संघर्ष उफाळला, अनिल कदमांनी साकडं घातलं आता संजय राऊत मैदानात</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/niphad-sugar-factory-crisis-sanjay-raut-anil-kadam-memorandum-farmers-workers-protest-nashik-gs97</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>राधाकृष्णन यांना राज्यातील सर्वपक्षीय खासदारांनी पाठिंबा द्यावा</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>https://dainikekmat.com/radhakrishnan-should-be-supported-by-mps-from-all-parties-in-the-state/114185/</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>उपराष्ट्रपतीपदाचे एनडीए उमेदवार सीपी राधाकृष्णन यांच्यावर राजकीय पक्षांच्या प्रतिक्रिया</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>https://www.dainikprabhat.com/parties-reaction-to-nda-vice-presidential-candidate-cp-radhakrishnan/</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>22-kg Golden Kalash Installed at Sant Dnyaneshwar Temple, Crafted by Shripad Shankar Nagarkar Jewellers Pune</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>https://www.tribuneindia.com/news/business/22-kg-golden-kalash-installed-at-sant-dnyaneshwar-temple-crafted-by-shripad-shankar-nagarkar-jewellers-pune/</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>उप-राष्ट्रपति चुनाव: देवेंद्र फडणवीस का 'मराठी अस्मिता' वाला दांव, क्या करेंगे उद्धव ठाकरे और शरद पवार?</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%89%E0%A4%AA-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A4%AA%E0%A4%A4-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%85%E0%A4%B8%E0%A5%8D%E0%A4%AE-%E0%A4%A4-%E0%A4%B5-%E0%A4%B2-%E0%A4%A6-%E0%A4%82%E0%A4%B5-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%94%E0%A4%B0-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0/ar-AA1KJ5pi</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Heavy rainfall causes 7 deaths, crop loss in Maharashtra as alerts continue</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/heavy-rainfall-causes-7-deaths-crop-loss-in-maharashtra-as-alerts-continue/articleshow/123368187.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Demand to release list of property-holders affected due to road-widening in 5 days</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>https://www.lokmattimes.com/aurangabad/demand-to-release-list-of-property-holders-affected-due-to-road-widening-in-5-days/</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Maharashtra Politics: Rohit Pawar Alleges ₹5,000-Crore Land Scam Against Minister Sanjay Shirsat</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-rohit-pawar-alleges-5000-crore-land-scam-against-minister-sanjay-shirsat</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Sanjay Shirsat : मंत्री शिरसाट यांच्यावर ५ हजार कोटींच्या जमीन घोटाळ्याचा आरोप</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>https://pudhari.news/maharashtra/mumbai/minister-shirsat-accused-of-rs-5000-crore-land-scam-np88</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>'ऑपरेशन लोटस वगैरे काही नाही; लवकरच ऑपरेशन टायगर दिसेल', सोलापूरच्या राजकारणात पडद्यामागे काय घडतंय?</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%B2-%E0%A4%9F%E0%A4%B8-%E0%A4%B5%E0%A4%97%E0%A5%88%E0%A4%B0%E0%A5%87-%E0%A4%95-%E0%A4%B9-%E0%A4%A8-%E0%A4%B9-%E0%A4%B2%E0%A4%B5%E0%A4%95%E0%A4%B0%E0%A4%9A-%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%9F-%E0%A4%AF%E0%A4%97%E0%A4%B0-%E0%A4%A6-%E0%A4%B8%E0%A5%87%E0%A4%B2-%E0%A4%B8-%E0%A4%B2-%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B0-%E0%A4%9C%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A4-%E0%A4%AA%E0%A4%A1%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%AE-%E0%A4%97%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%98%E0%A4%A1%E0%A4%A4%E0%A4%82%E0%A4%AF/ar-AA1KKoUc</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Mumbai Rain Mayhem: City Comes To Standstill As Life Thrown Out Of Gear; MonoRail Gets Stuck</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/en/!state/mumbai-rains-update-august-19-govt-semi-govt-offices-shut-bmc-urges-wfh-for-pvt-employees-enn25081901231</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Heritage India: Iconic Sword of Maratha Commander Raghuji Raje Bhonsle Arrives in Mumbai</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-govt-brings-back-iconic-sword-of-maratha-commander-raghuji-raje-bhonsle-auctioned-for-rs-4715-lakh-to-mumbai-3685565</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>https://www.ptinews.com/story/business/'third-mumbai'-to-boost-metropolitan-region-development:-fadnavis/2834902</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Maha CM asks agencies to be on alert mode after heavy rainfall and flash floods - Sakshi Post</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>https://www.sakshipost.com/news/maha-cm-asks-agencies-be-alert-mode-after-heavy-rainfall-and-flash-floods-441978</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Shortage of teachers hits rollout of NEP in govt, aided Maha colleges</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>https://www.pressreader.com/india/hindustan-times-st-jaipur/20250819/281681145971378</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Maha govt waives Stamp Duty worth Rs 38.99 lakh for Tata Cancer Hospital in Raigad (Ld)</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>https://www.thehawk.in/news/india/maha-govt-waives-stamp-duty-worth-rs-3899-lakh-for-tata-cancer-hospital-in-raigad-ld</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>कैसी होगी तीसरी मुंबई, कितनी बड़ी और कहां बन रही, सुविधाओं से लेकर प्लानिंग तक, CM फडणवीस ने सब बताया</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%95%E0%A5%88%E0%A4%B8-%E0%A4%B9-%E0%A4%97-%E0%A4%A4-%E0%A4%B8%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%95-%E0%A4%A4%E0%A4%A8-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%94%E0%A4%B0-%E0%A4%95%E0%A4%B9-%E0%A4%82-%E0%A4%AC%E0%A4%A8-%E0%A4%B0%E0%A4%B9-%E0%A4%B8%E0%A5%81%E0%A4%B5-%E0%A4%A7-%E0%A4%93%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AA%E0%A5%8D%E0%A4%B2-%E0%A4%A8-%E0%A4%82%E0%A4%97-%E0%A4%A4%E0%A4%95-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%AF/ar-AA1KLMl6?ocid=finance-verthp-feeds</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Maharashtra: मंत्री शंभूराज देसाई को मिला बचपन वाला वही सरकारी बंगला, मां के जन्मदिन पर किया भावुक गृहप्रवेश</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>http://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%B6%E0%A4%82%E0%A4%AD%E0%A5%82%E0%A4%B0-%E0%A4%9C-%E0%A4%A6%E0%A5%87%E0%A4%B8-%E0%A4%88-%E0%A4%95-%E0%A4%AE-%E0%A4%B2-%E0%A4%AC%E0%A4%9A%E0%A4%AA%E0%A4%A8-%E0%A4%B5-%E0%A4%B2-%E0%A4%B5%E0%A4%B9-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%AC%E0%A4%82%E0%A4%97%E0%A4%B2-%E0%A4%AE-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%9C%E0%A4%A8%E0%A5%8D%E0%A4%AE%E0%A4%A6-%E0%A4%A8-%E0%A4%AA%E0%A4%B0-%E0%A4%95-%E0%A4%AF-%E0%A4%AD-%E0%A4%B5%E0%A5%81%E0%A4%95-%E0%A4%97%E0%A5%83%E0%A4%B9%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6/ar-AA1JRinD?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>महाराष्ट्र के बीड, लातूर और नांदेड में भारी बारिश से बाढ़ की स्थिति गंभीर, NDRF और सेना तैनात</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/state/maharashtra/pune/heavy-rains-in-maharashtra-flood-havoc-in-beed-latur-and-nanded-ndrf-and-army-deployed/articleshow/123370629.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>महाराष्ट्र में माफ हो सकते हैं पुराने ट्रैफिक चालान, माफी योजना लाने की तैयारी में सरकार</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/government-schemes/others/maharashtra-government-is-set-to-roll-out-an-amnesty-scheme-for-one-time-settlement-of-pending-traffic-challan/articleshow/123367444.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Maharashtra Rains: महाराष्ट्र में बाढ़ से हालात गंभीर, मराठवाड़ा में NDRF और सेना तैनात, सरकार की क्या है तैयारी?</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/mumbai-heavy-rain-maharashtra-flood-situation-serious-ndrf-and-indian-army-deployed-in-marathwada/articleshow/123370824.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>मराठा सेनापति रघुजी भोंसले की तलवार मुंबई पहुंची</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>https://www.livehindustan.com/ncr/new-delhi/story-historic-sword-of-maratha-general-raghuji-bhosale-i-repatriated-to-mumbai-201755537654676.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Third Mumbai महानगर क्षेत्राच्या विकासाचा नवा अध्याय असेल; मुख्यमंत्र्यांनी सांगितलं कशी असेल ‘तिसरी मुंबई’ Third Mumbai in Raigad district to boost metropolitan region development said Devendra Fadnavis</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/third-mumbai-in-raigad-district-to-boost-metropolitan-region-development-said-devendra-fadnavis-89724</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>राज्यातील पूरस्थितीवर सरकारचे लक्ष, मदत कार्य सुरू – बावनकुळे</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/nagpur/governments-attention-on-flood-situation-in-the-state-information-from-chandrashekhar-bawankule-amy-95-5313292/</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>‘पीएम आवास’च्या तीस लाख घरांना मोफत वीज; राज्य सरकार देणार ५० हजारांचे अनुदान: मुख्यमंत्री</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>https://www.lokmat.com/maharashtra/free-electricity-to-three-lakh-houses-of-pm-awas-yojana-state-government-will-provide-subsidy-of-rs-50-thousand-chief-minister-a-a747/</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Maharashtra Government: शेतकऱ्यांना मिळणार गुड न्यूज: बळीराजासाठी सरकार मोठा निर्णय घेण्याच्या तयारीत</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>https://saamtv.esakal.com/maharashtra/sanjay-rathod-big-statement-on-loan-waiver-maharashtra-farmers-get-loan-waiver-minister-give-hint-in-award-ceremony-program-yavatmal-pusad-bbj88</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Crop Loss: महाराष्‍ट्र में बारिश ने किया किसानों को बर्बाद, विदर्भ से लेकर मराठवाड़ा तक फसलें चौपट</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>https://www.kisantak.in/crops/story/heavy-rains-in-maharashtra-cause-huge-damage-to-farmers-after-crop-loss-and-land-submerged-in-water-1263471-2025-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>कोल्हापुर में शुरू हुई बॉम्बे हाईकोर्ट की नई खंडपीठ, सीजेआई बोले– महाराष्ट्र न्यायिक ढांचे में आगे</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>https://mpbreakingnews.in/maharashtra/bombay-high-court-kolhapur-bench-cji-b-r-gavai-maharashtra-government-54-803927</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>श्रीमती प्रज्ञा वाळकेंचा भ्रष्टाचारामध्ये उच्चांक ; सरकारविरोधी चळवळीतीही सक्रिय सहभाग ?</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>https://lokmanthan.com/mrs-pragya-walkens-high-score-in-corruption-active-participation-in-anti-government-movement/</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>देशभर में बारिश का कहर: मुंबई-बेहद जाम, दिल्ली में यमुना उफान पर, स्कूल-कॉलेज बंद</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>https://dainikdehat.com/india/rain-wreaks-havoc-across-the-country-mumbai-is-jam-packed-yamuna-is-in-spate-in-delhi-schools-and-colleges-are-closed/</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>मुंबई झोपडपट्टीमुक्त होणार का? जलद पुनर्विकासाचा मुख्यमंत्र्यांनी काय सांगितला प्लॅन?</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>https://www.tendernama.com/mahatender/mumbai/will-mumbai-become-slum-free-what-is-the-chief-ministers-plan-for-rapid-redevelopment</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Mumbai Chawl Redevelopment | चाळ झाली आधुनिक वस्ती</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>https://pudhari.news/sampadakiy/mumbai-chawl-redevelopment-displaced-workers-problem-sp96</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Heavy Rains Batter Mumbai: Red Alert Issued, Schools and Colleges Closed on August 19 in Thane and...</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>https://www.thehansindia.com/news/national/heavy-rains-batter-mumbai-red-alert-issued-schools-and-colleges-closed-on-august-19-in-thane-and-palghar-998357</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Mumbai Rains: Are Private and Public offices shut today? BMC issues statement, says...</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>https://www.india.com/news/india/mumbai-rains-are-private-and-public-offices-shut-today-bmc-work-from-home-schools-colleges-devendra-fadnavis-markets-8019561/</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Surya Roshni to invest Rs 25 cr for biz expansion</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>https://www.theweek.in/wire-updates/business/2025/08/18/dcm62-biz-briefs-3.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>https://www.newsdrum.in/business/third-mumbai-to-boost-metropolitan-region-development-fadnavis-9674858</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Mumbai got 177mm rain in 6-8 hour period, says CM; all agencies asked to remain alert</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>https://www.newsdrum.in/national/mumbai-got-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert-9673094</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>How much rain did Mumbai receive on Monday? Check area-wise list</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/mumbai/how-much-rain-did-mumbai-areas-receive-on-monday-check-list-bandra-juhu-chembur-10196732/</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Nagpur’s Councils Starved Again: Pennies for a Region in Ruin</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>https://thelivenagpur.com/2025/08/18/nagpurs-councils-starved-again-pennies-for-a-region-in-ruin/</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>CM to join Kawad yatra, TV center chowk shut for 5 hours</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>https://www.lokmattimes.com/aurangabad/cm-to-join-kawad-yatra-tv-center-chowk-shut-for-5-hours/</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>चुनाव के बाद होगा महामंडलों का वितरण, महायुति के इच्छुक नेताओं पर प्रदर्शन का दबाव</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>https://navbharatlive.com/maharashtra/nagpur/distribution-of-maha-mandals-will-happen-after-the-elections-pressure-of-demonstration-on-the-aspiring-leaders-of-mahayuti-1322474.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>राज्यात ओला दुष्काळ जाहीर करा, विशेष अधिवेशन बोलवा मुसळधार पावसानंतर शरद पवारांच्या</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/politics/sharad-pawar-ncp-demands-after-heavy-rains-declaring-a-wet-drought-in-the-state-calling-a-special-session-shashikant-shinde-1377947</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Kokan Politics : शरद पवार गटाला धक्का; प्रदेश सरचिटणीस प्रशांत यादव भाजपाच्या वाटेवर</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>https://www.marathi.hindusthanpost.com/politics/kokan-politics-sharad-pawar-group-suffers-setback-state-general-secretary-prashant-yadav-on-bjps-path/</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>सिडको जमिन वाटप प्रकरणावरून राजकारण तापले; पवारांचा शिरसाठांवर घणाघाती हल्ला</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>https://civicmirror.in/maharashtra/politics-heats-up-over-cidco-land-allocation-issue-pawar-attacks-shirsath/</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Rohit Pawar on Sanjay Shirsath: रोहित पवारांचे मंत्री संजय शिरसाटांवर भ्रष्टाचाराचे गंभीर आरोप; पहा काय म्हणाले</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>'Destroying constitutional institutions': Nishikant Dubey slams Rahul Gandhi as SC dismisses plea challenging 2024 Maharashtra polls</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>https://www.bignewsnetwork.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>India News | SC Dismisses Plea Alleging Discrepancies in 2024 Maharashtra Assembly Polls</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>https://www.latestly.com/agency-news/india-news-sc-dismisses-plea-alleging-discrepancies-in-2024-maharashtra-assembly-polls-7065753.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Mumbai Rain LIVE Updates: मुंबईत सखल भागात साचलेल्या पाण्याचा निचरा</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/mumbai-rain-live-updates-18-august-imd-red-alert-in-mumbai-weather-waterlogging-traffic-jam-local-train-train-latest-updates-in-marathi-933169</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>मुंबई में कबूतरखानों पर विवाद, महापालिका ने नागरिकों से आपत्तियां और सुझाव मांगे</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>https://mpbreakingnews.in/maharashtra/mumbai-municipal-corporation-pigeon-shelters-public-consultation-high-court-54-803921</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Maharashtra govt plans amnesty scheme to recover pending transport fines</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>https://auto.economictimes.indiatimes.com/amp/news/industry/maharashtras-new-amnesty-scheme-settle-transport-fines-and-save-big/123364146</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Mah plans amnestyscheme to recoverpending transport fines</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>https://www.thehitavada.com/Encyc/2025/8/19/mah-plans-amnesty-scheme-to-recover-pending-transport-fines.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Pratap Sarnaik : राज्यातील वाहनांवर तब्‍बल 2500 कोटींचा दंड; सरकार एकरकमी परतफेडीची अभय योजना आणणार</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>https://www.dainikprabhat.com/fines-of-around-rs-2500-crore-on-vehicles-in-the-state-government-to-introduce-a-lump-sum-repayment-scheme/</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Cases from 6 districts to be heard | ‘A dream comes true after 40-45 years of struggle’: CJI inaugurates HC bench in Kolhapur</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/pune/cases-dream-struggle-cji-inaugurates-hc-bench-kolhapur-10195928/</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>CJI Gavai: "Maharashtra Govt At Forefront Of Efforts To Provide Infrastructure For Judiciary"</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>https://lawchakra.in/legal-updates/cji-gavai-infrastructure-for-judiciary/</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Maratha general Raghuji Bhonsle's sword brought to Mumbai</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>https://english.metrovaartha.com/news/mumbai/maratha-general-raghuji-bhonsles-sword-brought-to-mumbai</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>मराठा सेनापति रघुजी भोंसले की तलवार मुंबई लाई गई</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>https://hindi.theprint.in/india/maratha-commander-raghuji-bhosales-sword-brought-to-mumbai/856774/</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Revenue Minister बावनकुले का रुख</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>https://jantaserishta.com/amp/local/maharashtra/revenue-minister-bawankules-stance-4218277</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>राज्य को बाढ़ आपदा घोषित करो… विशेष अधिवेशन बुलाओ… एनसीपी प्रदेश अध्यक्ष ने की सीएम से मांग</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>https://www.hindisaamana.com/declare-the-state-a-flood-disaster-call-a-special-session-ncp-state-president-made-a-demand-to-the-cm/</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Shashikant Shinde on Heavy Rain: राज्यात अतिवृष्टीमुळे ओला दुष्काळ जाहीर करण्याची मागणी तीव्र</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>https://www.timemaharashtra.com/maharashtra/demand-to-declare-a-wet-drought-due-to-heavy-rains-in-the-state-is-strong/129359/</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>मराठा सेनापती रघुजी भोसले यांची तलवार मुंबईत आणली, लंडनमध्ये झालेल्या लिलावात महाराष्ट्र सरकारने घेतली</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>https://marathi.webdunia.com/article/mumbai-news/maratha-commander-raghuji-bhonsle-s-sword-brought-to-mumbai-125081800027_1.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>राज्यात ओला दुष्काळ जाहीर करा</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>https://dainikekmat.com/%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%A4-%E0%A4%93%E0%A4%B2%E0%A4%BE-%E0%A4%A6%E0%A5%81%E0%A4%B7%E0%A5%8D%E0%A4%95%E0%A4%BE%E0%A4%B3-%E0%A4%9C%E0%A4%BE%E0%A4%B9%E0%A5%80/114152/</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>भाजप आमदाराचा डाव प्रशासनाने हाणून पाडला, आईच्या नावाने बांधलेले अम्मा स्मारक अवैध ठरवून हटवले</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/chandrapur-bjp-mla-kishor-jorgewar-faces-setback-as-administration-demolishes-illegal-amma-memorial-construction-as11-rc70</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>मनसे कामगार संघटनेच्या अनेक पदाधिका-यांचा भाजपामध्ये प्रवेश</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>https://www.marathiebatmya.com/political/many-office-bearers-of-mns-workers-organization-join-bjp/</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>महाराष्ट्र में यह क्या हुआ? एकनाथ शिंदे का साथ छोड़ BJP में शामिल हुए कई भरोसेमंद</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>https://www.abplive.com/states/maharashtra/eknath-shinde-shiv-sena-solapur-leaders-join-bjp-amid-internal-feud-2997781</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>सीपी राधाकृष्णन के उपराष्ट्रपति उम्मीदवार बनाने पर कांग्रेस को लगी मिर्ची; INDI ब्लॉक भी जल्द कर सकता है प्रत्याशी का ऐलान</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>https://www.sudarshannews.in/news-detail.aspx?id=131383</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by Maharashtra CM Devendra Fadnavis</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>https://www.tribuneindia.com/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis/amp/?utm=relatedarticles</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>'Modi Govt Selling Dreams Of 2047, Ignoring Present': Rahul Gandhi Slams Centre After Maharashtra's Thane Train Tragedy</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>http://www.msn.com/en-in/news/India/modi-govt-selling-dreams-of-2047-ignoring-present-rahul-gandhi-slams-centre-after-maharashtras-thane-train-tragedy/ar-AA1Gm3WY?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Rs 40kcr of investors’ money stuck with credit societies, Maharashtra govt to announce SOP for recovery</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/rs-40kcr-of-investors-money-stuck-with-credit-societies-maharashtra-govt-to-announce-sop-for-recovery/articleshow/123367502.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Red alert issued as heavy rain batters Mumbai; schools and colleges closed due to waterlogging</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>https://ddnews.gov.in/en/red-alert-issued-as-heavy-rain-batters-mumbai-schools-and-colleges-closed-due-to-waterlogging/</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Maha govt signs MoUs worth Rs 42,000 crore and creation of 28,000 jobs</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>https://www.thehawk.in/news/states-and-uts/maharashtra/maha-govt-signs-mous-worth-rs-42000-crore-and-creation-of-28000-jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>NCP (SP) targets Maha minister over Rs 5,000 cr scam in Navi Mumbai’s CIDCO land; demands his resignation</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>https://www.sakshipost.com/news/ncp-sp-targets-maha-minister-over-rs-5000-cr-scam-navi-mumbai-s-cidco-land-demands-his</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>पंतप्रधान नरेंद्र मोदी आणि व्लादिमीर पुतीन यांच्यात संवाद - संघर्षाच्या शांततामय तोडग्यासाठी भारताचा ठाम पाठिंबा</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/dialogue-between-prime-minister-narendra-modi-and-vladimir-putin-indias-strong-support-for-peaceful-resolution.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>वैविध्यपूर्ण विषयांवरील पुस्तक प्रकाशित करणे हे चपराकचं साहित्यिक आंदोलन; लेखक अभिराम भडकमकर यांचे प्रतिपादन</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/publishing-books-on-diverse-topics-is-a-literary-movement-of-the-chaparak-author-abhiram-bhadkamkar-asserts.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>ठाण्यात शालेय ९-साईड हॉकी लीगला सुरुवात ; ७६ संघांचा उत्साही सहभाग</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/school-9-a-side-hockey-league-begins-in-thane-76-teams-participate-enthusiastically.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Rains Wreak Havoc Across States, Toll In Kishtwar Cloudburst Touches 63</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/en/!bharat/rains-wreak-havoc-across-states-over-200-stranded-in-worst-hit-maharashtra-toll-in-kishtwar-cloudburst-touches-63-enn25081807219</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Vice Presidential Election : उपराष्ट्रपती पदासाठी विरोधकांचा उमेदवार कोण? दिल्लीत घडामोडींना वेग; राहुल गांधी काय भूमिका घेणार?</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/desh-videsh/who-is-the-opposition-candidate-for-the-post-of-vice-president-events-in-delhi-are-gaining-momentum-what-decision-will-mallikarjun-kharge-take-gkt-96-5313155/</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Maharashtra politics : मुख्यमंत्र्यांच्या पत्नी गायिका, तरीही गाणे गाणाऱ्या तहसीलदारांना शिक्षा? बावनकुळे या चुकीला माफी असायलाच हवी; सामनातून हल्लाबोल</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>https://sarkarnama.esakal.com/mumbai/nanded-tehsildar-prashant-thorat-suspension-shiv-sena-ubt-criticism-sanjay-raut-devendra-fadnavis-jap93</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>पूजेसाठी परवानगी नाही, नमाजसाठी जागाच जागा; कम्युनिस्टांचा हिंदुविरोधी चेहरा पुन्हा समोर</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/no-permission-for-worship-plenty-of-space-for-namaz-cpims-different-rules-for-hindus-and-muslims-in-kerala-the.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Shivaji Sawant : शिवाजी सावंतांचा भाजपा प्रवेश निश्चित !</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>https://thefocusindia.com/maharashtra-news/shivaji-sawants-admission-to-bjp-is-certain-281398/</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>मुसळधार पावसामुळे राज्यात सात जणांचा मत्यू; मुंबईत पावसामुळे जनजीवन विस्कळित</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/mr/!state/mumbai-rains-updates-imd-red-alert-mumbai-city-suburbs-schools-and-colleges-remain-closed-today-mumbai-university-exams-postponed-to-23-august-maharashtra-rain-news-today-maharashtra-news-mhs25081900792</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Will Bajirao Mastani Come Alive in Movie Halls Today?</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>https://caleidoscope.in/art-culture/will-bajirao-mastani-come-alive-in-movie-halls-today</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Red alert in Mumbai; BMC shuts all afternoon schools, colleges</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>https://www.newsbytesapp.com/news/india/mumbai-rain-havoc-to-continue-for-next-4-days/story</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Nanded Rain: नांदेड़ में भारी बारिश के बाद 200 लोग बाढ़ में फंसे! बादल फटने से 5 लापता, रेस्क्यू के लिए सेना बुलाई गई</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>https://hindi.moneycontrol.com/india/heavy-rains-in-maharashtra-nanded-leave-over-200-stranded-in-flood-waters-five-people-missing-article-2104052.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Maharashtra approves amendments for Dharavi project land transfer</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/en-in/news/India/maharashtra-approves-amendments-for-dharavi-project-land-transfer/ar-AA1G1ze9</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>What happened in the Trump-Putin meeting? | Chandrashekhar Nene Maha MTB</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/what-happened-in-the-trump-putin-meeting-chandrashekhar-nene-maha-mtb.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>IBM to support Maharashtra in developing quantum computing initiative</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>https://www.communicationstoday.co.in/ibm-to-support-maharashtra-in-developing-quantum-computing-initiative/</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Mumbai rains: Heavy showers flood roads, railway tracks; bring city to standstill - video</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/india/mumbai-rains-heavy-showers-flood-roads-railway-tracks-bring-city-to-standstill-video/articleshow/123362740.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Maratha general Raghuji Bhonsle's sword brought to Mumbai</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>https://www.ptinews.com/story/national/maratha-general-raghuji-bhonsle's-sword-brought-to-mumbai/2833930</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Mumbai rain: 177 mm recorded in 6-8 hours, public advised to reach homes before 6.30 pm</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>https://www.onmanorama.com/news/india/2025/08/18/mumbai-rains-flooding-high-tide-warning-live.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Monday mayhem: Mumbai's suburbs recorded over 100 mm rainfall in 12 hours, says IMD</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>https://www.ptinews.com/story/national/monday-mayhem:-mumbai's-suburbs-recorded-over-100-mm-rainfall-in-12-hours,-says-imd/2834156</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Mumbai rains: Torrential downpour cripples normal life, roads flooded — in pics</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>https://www.livemint.com/photos/mumbai-rains-torrential-downpour-cripples-normal-life-train-services-hit-roads-flooded-see-pics-11755525808666.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Mumbai reels under 177 mm rain in 8 hours; flights hit, schools shut as red alert issued</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>https://www.newindianexpress.com/nation/2025/Aug/18/mumbai-rains-flight-operations-hit-schools-colleges-shut-as-imd-issues-red-alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Mumbai rains: Heavy rainfall batter city as Vihar lake overflows</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-rains-heavy-rainfall-batter-city-as-vihar-lake-overflows-23590062</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Rain fury: 5 missing, 200 stranded in Nanded; local trains, flights hit in Mumbai</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>https://odishatv.in/news/national/rain-fury-5-missing-200-stranded-in-nanded-local-trains-flights-hit-in-mumbai-270189</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>IndiGo Airlines issues travel advisory for passengers flying out of Mumbai due to heavy rainfall, waterlogging in the city</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>https://newsroompost.com/india/indigo-airlines-issues-travel-advisory-for-passengers-flying-out-of-mumbai-due-to-heavy-rainfall-waterlogging-in-the-city/5347388.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>मुंबई में भारी बारिश का कहर, 19 अगस्त को बंद रहेंगे सभी स्कूल-कॉलेज</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>https://hindi.news24online.com/india/mumbai-and-jammu-kashmir-heavy-rain-rain-school-and-college-closed/1288306/</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>महाराष्ट्र में भारी बारिश से सात लोगों की मौत, 200 ग्रामीण फंसे</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AD-%E0%A4%B0-%E0%A4%AC-%E0%A4%B0-%E0%A4%B6-%E0%A4%B8%E0%A5%87-%E0%A4%B8-%E0%A4%A4-%E0%A4%B2-%E0%A4%97-%E0%A4%82-%E0%A4%95-%E0%A4%AE-%E0%A4%A4-200-%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%A3-%E0%A4%AB%E0%A4%82%E0%A4%B8%E0%A5%87/ar-AA1KKl3K</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>लाटा पाहण्याच्या मोहापाई लोक अडचणीत येतात....: तुफान पावसामुळे मुख्यमंत्री फडणवीसांनी केले आवाहन</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>https://www.navarashtra.com/maharashtra/cm-devendra-fadnavis-live-press-on-mumbai-rain-update-red-alert-963319.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Mumbai Heavy Rain : मुंबईसाठी पुढील 10-12 तास धोक्याचे, मुख्यमंत्री फडणवीसांनी मुंबईकरांना केलं सावध</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>https://www.mymahanagar.com/maharashtra/heavy-rains-in-mumbai-next-48-hours-are-crucial-chief-minister-devendra-fadnavis-warns-citizens-to-be-alert/913099/</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>मराठ्यांच्या इतिहासाची साक्षीदार; श्रीमंत राजे रघुजी भोसलेंच्या ऐतिहासिक तलवारीचं लोकार्पण, पाहा खास PHOTO</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/photogallery/news/raghuji-bhosale-sword-inauguration-in-mumbai-by-cm-devendra-fadnavis/photoshow/123367923.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Mumbai Rain: मुंबईत उद्या शाळांना सुट्टी? पुढचे १२ तास महत्वाचे, मुख्यमंत्री नेमकं काय म्हणाले?</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>https://saamtv.esakal.com/mumbai-pune/mumbai-rain-alert-cm-devendra-fadnavis-said-mumbai-schools-declared-holiday-on-tomorrow-bmc-to-decide-pvm91</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Maharashtra Rains: राज्यात अतिवृष्टी, 7 जणांचा मृत्यू; मुख्यमंत्र्यांचे सर्व यंत्रणांना सतर्कतेचे निर्देश Maharashtra Rains: Heavy rains in the state, 7 people died; CM Devendra Fadnavis directs all agencies to be alert</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-rains-heavy-rains-in-the-state-7-people-died-cm-devendra-fadnavis-directs-all-agencies-to-be-alert-89603</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>श्रीमंत राजे रघूजी भोसले यांची ऐतिहासिक तलवार उद्या मुंबईत दाखल</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>https://mahasamvad.in/176009/</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>CM Devendra Fadnavis : ‘तिसरी मुंबई’ नवा अध्याय उघडेल; रायगड जिल्ह्यात होणार विकसित</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>https://www.esakal.com/mumbai/navi-mumbais-successor-the-rise-of-third-mumbai-in-raigad-district-cm-devendra-fadnavis-pjp78</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>CM Devendra Fadnavis : हिंदवी स्वराज्याचा इतिहास नवीन पिढीपर्यंत पोहोचेल; श्रीमंत राजे रघुजी भोसले यांच्या तलवारीचे स्वागत</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>https://www.esakal.com/mumbai/legacy-of-hindavi-swarajya-rajarshi-raghuji-bhosales-sword-welcomed-history-cm-devendra-fadnavis-pjp78</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>मुंबईत पुढील आठ ते दहा तासांसाठी रेड अलर्ट, महत्त्वाचे काम असल्यास घराबाहेर पडण्याचे मुख्यमंत्री फडणवीस यांचे आवाहन</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>https://www.saamana.com/in-mumbai-people-have-been-told-to-step-out-only-if-it-is-needed-says-cm-devendra-fadnavis/</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>Maharashtra Rain: राज्यात पावसाचा हाहाकार! १६ जिल्ह्यांना रेड- ऑरेंज अलर्ट, मुख्यमंत्र्यांकडून सतर्क राहण्याचे आवाहन</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>https://saamtv.esakal.com/mumbai-pune/maharashtra-floods-cm-fadnavis-reviews-situation-ndrf-and-army-deployed-16-districts-on-red-alert-latest-news-pvm91</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Kolhapur : सरन्यायाधीश Bhushan Gavai यांच्या हस्ते सर्किट बेंच इमारतीचे उद्घाटन</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>https://www.tarunbharat.com/kolhapur-circuit-bench-inauguration-with-chief-justice-bhushan-gavai-marathi-news/</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>मुख्यमंत्री वैद्यकीय सहाय्यता निधीच्या पुढाकाराने चिमुकल्या देवांशीवर यशस्वी शस्त्रक्रिया</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>https://mahasamvad.in/176143/</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Mumbai Rain Update : मुंबईत धो-धो! वाहतुकीचा खोळंबा, लोकलसेवेला फटका; मुंबईकरांची पुरती दैना; पुढील 48 तासही धोक्याचे</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-rain-update-heavy-rainfall-started-in-city-resulted-in-disruption-of-life-and-mumbai-local-cm-fadnavis-reviewed/articleshow/123363662.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>रघुजीराजे भोसले यांची तलवार मुंबईत शौर्याचा वारसा इतिहाप्रेमींसाठी खुला; मराठा साम्राज्याचा वारसा परत मिळवण्याचा प्रयत्न – मुख्यमंत्री</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>https://www.saamana.com/raghujiraje-bhosale-sword-a-legacy-of-bravery-is-open-to-history-lovers-in-mumbai-an-attempt-to-reclaim-the-legacy-of-the-maratha-empire-said-by-chief-minister-devendra-fadnavis/</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>राष्ट्रीय: मुंबई में भारी बारिश के बीच सुचारू रूप से चल रही मेट्रो, सीएम फडणवीस ने की तारीफ</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>https://www.bhaskarhindi.com/other/news-1174019</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>तिसरी MUMBAI आर्थिक विकासाचा नवा अध्याय, गोल्डमन सॅक्सच्या नव्या मुंबई कार्यालयाचे उद्घाटन</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>https://www.timemaharashtra.com/maharashtra/mumbai/third-mumbai-a-new-chapter-in-economic-development-goldman-sachs-new-mumbai-office-inaugurated/129385/</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Mumbai Rain : मुख्यमंत्री फडणवीस ॲक्शन मोडमध्ये! राज्यभरात पडत असलेल्या पावसामुळे प्रशासन अलर्ट</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>https://www.marathi.hindusthanpost.com/social/mumbai-rain-cm-devendra-fadnavis-in-action-mode-administration-alert-due-to-rains-falling-across-the-state/</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Devendra Fadnavis : नांदेड जिल्ह्यातील अतिवृष्टीवर मुख्यमंत्र्यांची नजर, प्रशासनाला सूचना</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>https://www.marathi.hindusthanpost.com/politics/devendra-fadnavis-chief-ministers-eye-on-heavy-rains-in-nanded-district-instructions-to-the-administration/</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>'Third Mumbai' to boost metropolitan region development Fadnavis</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>https://www.theweek.in/wire-updates/business/2025/08/19/bom3-mh-third-mumbai-cm.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Transformative Leadership: Sukhraj Nahar Steers CREDAI-MCHI Towards Urban Revolution</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>https://www.devdiscourse.com/article/business/3545330-transformative-leadership-sukhraj-nahar-steers-credai-mchi-towards-urban-revolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>The perks and costs of ‘Ladki Bahin’</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/the-perks-and-costs-of-ladki-bahin-101755575344332.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>LGEC 2025: 'लाडकी बहीण' योजनेमुळे महाराष्ट्रातील अर्थव्यवस्थेला चालनाच मिळाली; सुनील तटकरेंनी समजावलं 'गणित'</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>https://www.lokmat.com/international/lgec-2025-ladki-bahin-scheme-has-given-a-boost-to-the-economy-of-maharashtra-sunil-tatkare-rahul-narvekar-explained-a-a629/</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>महाराष्ट्र के नांदेड़ जिले में मूसलाधार बारिश से आई बाढ़ में 225 नागरिक फंसे,बचाव कार्य जारी</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>https://www.yugwarta.com/Encyc/2025/8/18/nanded-flood-resues-continew.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>मानसून में हाल बेहाल, भारी बारिश से इस राज्य में जगह-जगह भरा पानी, स्कूल-कॉलेज किए बंद</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>https://www.patrika.com/national-news/heavy-rain-alert-in-mumbai-monsoon-gained-momentum-know-imd-weather-update-19874723</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>Mumbai Rains: भारी बारिश का कहर, 7 की मौत, आदित्य ठाकरे ने BMC पर लगाए आरोप</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>https://www.thesandeshwahak.com/mumbai-rains-heavy-rain-wreaks-havoc-7-dead-aditya-thackeray-blames-bmc/</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Ganesh Naik, Eknath Shinde, Thane, Maharashtra Politics</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>https://mpbreakingnews.in/maharashtra/ganesh-naik-eknath-shinde-thane-maharashtra-politics-54-804112</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>रमेश बिधूड़ी ने राधाकृष्णन को दी शुभकामनाएं, कहा- 'अच्छे उपराष्ट्रपति साबित होंगे'</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>https://www.khaskhabar.com/local/delhi-ncr/delhi-news/news-ramesh-bidhuri-congratulated-radhakrishnan-said---he-will-prove-to-be-a-good-vice-president-news-hindi-1-745268-KKN.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Rain wreaks havoc in Maharashtra, brings Mumbai to a standstill</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/maharashtra/rain-wreaks-havoc-in-maharashtra-brings-mumbai-to-a-standstill/article69948564.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Mumbai rains: BMC announces holiday for schools, colleges on August 19</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>https://www.cnbctv18.com/india/are-mumbai-schools-colleges-open-or-close-on-august-19-19655564.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>India monsoon updates: Heavy to very heavy rainfall at few places in Mumbai; residents told to ‘avoid unnecessary travel’</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/india-monsoon-live-mumbai-rains-yamuna-river-flood-alert-delhi-kashmir-cloudburst-updates-august-18/article69946105.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Cabinet sends back note regarding GMR with multiple queries</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>https://www.thehitavada.com/Encyc/2025/8/18/cabinet-sends-back-note-regarding-gmr-with-multiple-queries.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Maharashtra govt plans amnesty scheme to recover pending transport fines</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>https://auto.economictimes.indiatimes.com/news/industry/maharashtras-new-amnesty-scheme-settle-transport-fines-and-save-big/123364146</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Mumbai on red alert; BMC declares holiday for schools, colleges on August 19</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/news/india/bmc-declares-holiday-for-mumbai-schools-colleges-on-august-19-as-city-braces-for-heavy-rain/articleshow/123366693.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>Are Mumbai schools, colleges open today? Details here | Latest News India - Hindustan Times</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/india-news/are-mumbai-schools-colleges-open-today-details-here-mumbai-rains-mumbai-weather-imd-red-alert-101755561079277.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Mumbai Rains Live News: Torrential rains cripple Mumbai; roads flooded, local trains delayed and schools, colleges closed amid ‘Red’ alert</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>https://www.thehindubusinessline.com/news/mumbai-weather-mumbai-rains-live-news-updates/article69946123.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Pune Can Get Underground Road Network To Beat Traffic Woes</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>https://trak.in/stories/pune-can-get-underground-road-network-to-beat-traffic-woes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>Rainfall Alert: All schools and colleges closed due to heavy rains, IMD issued red alert</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>https://www.informalnewz.com/rainfall-alert-all-schools-and-colleges-closed-due-to-heavy-rains-imd-issued-red-alert/</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>शाळा अंतर्गत फेरीमध्ये विद्यार्थ्यांचा सत्कार सोहळा</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/student-felicitation-ceremony-during-the-schools-internal-parade.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>अतिवृष्टीमुळे होणाऱ्या नुकसानीचे तातडीने पंचनामे करा; मंत्री मकरंद जाधव-पाटील यांचे निर्देश</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/immediately-conduct-a-panchnama-of-the-damage-caused-by-heavy-rains-minister-makarand-jadhav-patil-directs.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>सामाजिक कामात कार्यरत राहून मिळणारा आनंद मोठा: पांडुरंग चोरमले</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/the-joy-of-working-in-social-work-is-immense-pandurang-chormale.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Maharashtra Rain Update: 19 ऑगस्टलाही सावधान..., महाराष्ट्रातील 'या' जिल्ह्यांना रेड अलर्ट</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>https://www.navarashtra.com/maharashtra/mahrashtra-mumbai-rain-latest-update-orange-alert-till-august-20-red-alert-issued-in-several-districts-963438.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Mumbai Rain Update: मुंबईत पुढील चार तास धो-धो, रेड अलर्ट जारी, लोकल ट्रेन उशिराने, नागरिकांना घराबाहेर न पडण्याचं आवाहन</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-heavy-rain-expected-by-imd-red-alert-heavy-rainfall-local-train-updates/articleshow/123376293.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>मुख्यमंत्री फडणवीसांकडून पावसाचा आढावा: मराठवाड्यात 800 गावे बाधित, कोकण-विदर्भात रेड अलर्ट</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>https://www.dainikprabhat.com/cm-fadnavis-reviews-rains-800-villages-affected-in-marathwada-red-alert-in-konkan-vidarbha/</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>MMRDA launches SCLR bridge, metro institute and flyovers to ease city commute</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>https://propnewstime.com/getdetailsStories/MjA1NTQ=/mmrda-launches-sclr-bridge-metro-institute-and-flyovers-to-ease-city-commute</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Mumbai continues to be on red alert; heavy rain disrupts travel, shuts offices &amp; educational institutions</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/news/weather/mumbai-on-red-alert-for-second-consecutive-day-heavy-rain-disrupts-travel-shuts-educational-institutions/articleshow/123375296.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>Maha CM asks agencies to be on alert mode after heavy rainfall and flash floods</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>https://www.lokmattimes.com/national/maha-cm-asks-agencies-to-be-on-alert-mode-after-heavy-rainfall-and-flash-floods/</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>Over ₹6.52 Crore Medical Aid Distributed To 5,000 Beneficiaries In Pune District</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>https://www.mypunepulse.com/over-%E2%82%B96-52-crore-medical-aid-distributed-to-5000-beneficiaries-in-pune-district/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Output/Devendra Fadnavis/extracted_links.xlsx
+++ b/Output/Devendra Fadnavis/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B509"/>
+  <dimension ref="A1:B512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,36 +455,36 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Maharashtra CM Devendra Fadnavis seeks Opposition backing for Radhakrishnan</t>
+          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by Maharashtra CM Devendra Fadnavis</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-devendra-fadnavis-seeks-opposition-backing-for-radhakrishnan-23590051</t>
+          <t>https://www.tribuneindia.com/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Aurangzeb Tomb Row: VHP’s Statewide Protests Backed By RSS; CM Devendra Fadnavis Calls For Lawful Dismantling</t>
+          <t>Maharashtra CM Devendra Fadnavis seeks Opposition backing for Radhakrishnan</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/aurangzeb-tomb-row-vhp-s-statewide-protests-backed-by-rss-cm-devendra-fadnavis-calls-for-lawful-dismantling/ar-AA1Bfmct?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-devendra-fadnavis-seeks-opposition-backing-for-radhakrishnan-23590051</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by Maharashtra CM Devendra Fadnavis</t>
+          <t>Mumbai AQI: Dia Mirza expresses her concern with CM Devendra Fadnavis to act on city's air pollution</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis/</t>
+          <t>https://www.msn.com/en-in/public-safety-and-emergencies/health-and-safety-alerts/mumbai-aqi-dia-mirza-expresses-her-concern-with-cm-devendra-fadnavis-to-act-on-city-s-air-pollution/ar-AA1xZ0xs?ocid=BingNewsVerp&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
@@ -503,12 +503,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>'Positive about bringing a law to protect advocates:' Maharashtra CM Fadnavis</t>
+          <t>Heavy rain lashes Marathwada; 5 missing in Nanded, says CM Devendra Fadnavis</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://legal.economictimes.indiatimes.com/news/industry/positive-about-bringing-a-law-to-protect-advocates-maharashtra-cm-fadnavis/123378199</t>
+          <t>https://indianexpress.com/article/cities/mumbai/heavy-rain-lashes-marathwada-5-missing-in-nanded-says-cm-devendra-fadnavis-10196321/</t>
         </is>
       </c>
     </row>
@@ -527,228 +527,228 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Shiv Sena (UBT) Welcomes Radhakrishnan’s Nomination, Fadnavis Seeks All-Party Support</t>
+          <t>'Positive about bringing a law to protect advocates:' Maharashtra CM Fadnavis</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/nation/shiv-sena-ubt-welcomes-rahakrishans-nomination-fadnavis-seeks-all-party-support-1898266</t>
+          <t>https://legal.economictimes.indiatimes.com/news/industry/positive-about-bringing-a-law-to-protect-advocates-maharashtra-cm-fadnavis/123378199</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Heavy rain lashes Marathwada; 5 missing in Nanded, says CM Devendra Fadnavis</t>
+          <t>Shiv Sena (UBT) Welcomes Radhakrishnan’s Nomination, Fadnavis Seeks All-Party Support</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/heavy-rain-lashes-marathwada-5-missing-in-nanded-says-cm-devendra-fadnavis-10196321/</t>
+          <t>https://www.deccanchronicle.com/nation/shiv-sena-ubt-welcomes-rahakrishans-nomination-fadnavis-seeks-all-party-support-1898266</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mumbai gets 300 mm rain in a day, Devendra Fadnavis warns next 48 hours critical</t>
+          <t>VP Nominee CP Radhakrishnan Leaves for Delhi, Maha Yuti Leaders Pledge Support</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/cities/mumbai/story/mumbai-heavy-rains-waterlogging-imd-red-alert-bmc-school-offices-holiday-work-from-home-2773291-2025-08-19</t>
+          <t>https://www.deccanherald.com/india/maharashtra/vp-nominee-radhakrishnan-departs-for-delhi-maha-yuti-leaders-extend-support-3685392</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Goldman Sachs opens new, expanded office in Mumbai</t>
+          <t>Cannot achieve affordable housing with ‘business as usual’ approach: Maharashtra CM Fadnavis tells...</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/business/Industry/goldman-sachs-opens-new-expanded-office-in-mumbai/article69947256.ece</t>
+          <t>https://www.moneycontrol.com/news/business/real-estate/cannot-achieve-affordable-housing-with-business-as-usual-approach-maharashtra-cm-fadnavis-tells-realtors-13462328.html</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Third Mumbai: Fadnavis Boosts MMR Development</t>
+          <t>Fadnavis hails Maha Guv’s nomination as Vice Presidential candidate</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/third-mumbai-fadnavis-boosts-mmr-development/32201020250818</t>
+          <t>https://www.thestatesman.com/india/fadnavis-hails-maha-guvs-nomination-as-vice-presidential-candidate-1503473264.html</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Fadnavis hails Maha Guv’s nomination as Vice Presidential candidate</t>
+          <t>Third Mumbai: Fadnavis Boosts MMR Development</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://www.thestatesman.com/india/fadnavis-hails-maha-guvs-nomination-as-vice-presidential-candidate-1503473264.html</t>
+          <t>https://money.rediff.com/news/market/third-mumbai-fadnavis-boosts-mmr-development/32201020250818</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VP Nominee CP Radhakrishnan Leaves for Delhi, Maha Yuti Leaders Pledge Support</t>
+          <t>Aurangzeb Tomb Row: VHP’s Statewide Protests Backed By RSS; CM Devendra Fadnavis Calls For Lawful Dismantling</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/vp-nominee-radhakrishnan-departs-for-delhi-maha-yuti-leaders-extend-support-3685392</t>
+          <t>https://www.msn.com/en-in/news/India/aurangzeb-tomb-row-vhp-s-statewide-protests-backed-by-rss-cm-devendra-fadnavis-calls-for-lawful-dismantling/ar-AA1Bfmct?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis' first reaction to Raj Thackeray's reunion with Uddhav jibe</t>
+          <t>Aakar Patel| New Maharashtra Security Law Open To Abuse, Threatens Rights; Say ‘No’ To It</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/india/devendra-fadnavis-first-reaction-to-raj-thackeray-s-reunion-with-uddhav-jibe/ar-AA1I1jzW?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.deccanchronicle.com/opinion/columnists/aakar-patel-new-maharashtra-security-law-open-to-abuse-threatens-rights-say-no-to-it-1898276</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Aakar Patel| New Maharashtra Security Law Open To Abuse, Threatens Rights; Say ‘No’ To It</t>
+          <t>Devendra Fadnavis' first reaction to Raj Thackeray's reunion with Uddhav jibe</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/opinion/columnists/aakar-patel-new-maharashtra-security-law-open-to-abuse-threatens-rights-say-no-to-it-1898276</t>
+          <t>http://www.msn.com/en-in/news/india/devendra-fadnavis-first-reaction-to-raj-thackeray-s-reunion-with-uddhav-jibe/ar-AA1I1jzW?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sword of Raghuji Bhonsle Unveiled in Mumbai: ‘A Bridge Between Generations,’ Says CM Fadnavis</t>
+          <t>NDA Vice President-Nominee CP Radhakrishnan Expresses Gratitude To PM Modi, Amit Shah &amp; Devendra Fadnavis After VP Nomination</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/sword-of-raghuji-bhonsle-unveiled-in-mumbai-a-bridge-between-generations-says-cm-fadnavis/articleshow/123372524.cms</t>
+          <t>https://www.msn.com/en-in/news/India/nda-vice-president-nominee-cp-radhakrishnan-expresses-gratitude-to-pm-modi-amit-shah-devendra-fadnavis-after-vp-nomination/ar-AA1KGvyO</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NDA Vice President-Nominee CP Radhakrishnan Expresses Gratitude To PM Modi, Amit Shah &amp; Devendra Fadnavis After VP Nomination</t>
+          <t>MNS Morcha: Raj Thackeray's party workers detained; CM Fadnavis says such experiments won’t work here</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/nda-vice-president-nominee-cp-radhakrishnan-expresses-gratitude-to-pm-modi-amit-shah-devendra-fadnavis-after-vp-nomination/ar-AA1KGvyO</t>
+          <t>https://www.msn.com/en-in/news/India/mns-morcha-raj-thackerays-party-workers-detained-cm-fadnavis-says-such-experiments-won-t-work-here/ar-AA1Iaint</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MNS Morcha: Raj Thackeray's party workers detained; CM Fadnavis says such experiments won’t work here</t>
+          <t>Those who speak of Maharashtra 'asmita' should support Radhakrishnan for VP post: Fadnavis</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/mns-morcha-raj-thackerays-party-workers-detained-cm-fadnavis-says-such-experiments-won-t-work-here/ar-AA1Iaint</t>
+          <t>https://www.msn.com/en-in/news/India/those-who-speak-of-maharashtra-asmita-should-support-radhakrishnan-for-vp-post-fadnavis/ar-AA1KJ362</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>‘Third Mumbai’ takes shape as CM Fadnavis unveils mega MMR expansion plan</t>
+          <t>Goldman Sachs opens new, expanded office in Mumbai</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/city/third-mumbai-takes-shape-as-cm-fadnavis-unveils-mega-mmr-expansion-plan-article-13465350.html</t>
+          <t>https://www.thehindu.com/business/Industry/goldman-sachs-opens-new-expanded-office-in-mumbai/article69947256.ece</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cannot achieve affordable housing with ‘business as usual’ approach: Maharashtra CM Fadnavis tells...</t>
+          <t>Mumbai gets 300 mm rain in a day, Devendra Fadnavis warns next 48 hours critical</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/business/real-estate/cannot-achieve-affordable-housing-with-business-as-usual-approach-maharashtra-cm-fadnavis-tells-realtors-13462328.html</t>
+          <t>https://www.indiatoday.in/cities/mumbai/story/mumbai-heavy-rains-waterlogging-imd-red-alert-bmc-school-offices-holiday-work-from-home-2773291-2025-08-19</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Heavy Rains Ravage State, CM Fadnavis Orders Relief, Surveys Rain-Hit Areas</t>
+          <t>Those who speak of Maharashtra 'asmita' should support Radhakrishnan for VP post: Fadnavis</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/heavy-rains-ravage-state-cm-fadnavis-orders-relief-surveys-rain-hit-areas/articleshow/123372550.cms</t>
+          <t>https://www.ptinews.com/story/national/those-who-speak-of-maharashtra-'asmita'-should-support-radhakrishnan-for-vp-post:-fadnavis/2832772</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Those who speak of Maharashtra 'asmita' should support Radhakrishnan for VP post: Fadnavis</t>
+          <t>Sword of Raghuji Bhonsle Unveiled in Mumbai: ‘A Bridge Between Generations,’ Says CM Fadnavis</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/those-who-speak-of-maharashtra-'asmita'-should-support-radhakrishnan-for-vp-post:-fadnavis/2832772</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/sword-of-raghuji-bhonsle-unveiled-in-mumbai-a-bridge-between-generations-says-cm-fadnavis/articleshow/123372524.cms</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Mumbai rains: Maharashtra CM says 'observe precautions', warns of heavy rainfall, high tide; check BMC's advisory</t>
+          <t>Why Eknath Shinde is covering little distance despite frequent visits to Delhi</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/news/mumbai-rains-maharashtra-cm-says-observe-precautions-warns-of-heavy-rainfall-high-tide-check-bmcs-advisory-11755573270369.html</t>
+          <t>https://indianexpress.com/article/political-pulse/why-eknath-shinde-is-covering-little-distance-despite-frequent-visits-to-delhi-10197218/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>"Observe precaution": Maharashtra CM warns about severe weather conditions in state</t>
+          <t>‘Observe precaution’: Maharashtra CM warns about severe weather conditions in State</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state20250819025510</t>
+          <t>https://www.thehindubusinessline.com/news/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state/article69950172.ece</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Third Mumbai in Raigad to become Maharashtra’s new economic powerhouse: CM Fadnavis</t>
+          <t>Heavy Rains Ravage State, CM Fadnavis Orders Relief, Surveys Rain-Hit Areas</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://daijiworld.com/news/newsDisplay?newsID=1289652</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/heavy-rains-ravage-state-cm-fadnavis-orders-relief-surveys-rain-hit-areas/articleshow/123372550.cms</t>
         </is>
       </c>
     </row>
@@ -767,72 +767,72 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Those who speak of Maharashtra ‘asmita’ should support Radhakrishnan for VP post: Fadnavis</t>
+          <t>Third Mumbai in Raigad to become Maharashtra’s new economic powerhouse: CM Fadnavis</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/those-who-speak-of-maharashtra-asmita-should-support-radhakrishnan-for-vp-post-fadnavis/2723344/?amp</t>
+          <t>https://daijiworld.com/news/newsDisplay?newsID=1289652</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Fadnavis govt’s big Maratha pride push: Legendary sword it ‘bought’ back from London, with a Rs 47L bid</t>
+          <t>Mumbai gets 177mm rain in 6-8 hour period, says CM; all agencies asked to remain alert</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://theprint.in/politics/fadnavis-govts-big-maratha-pride-push-legendary-sword-it-bought-back-from-london-with-a-rs-47l-bid/2723199/</t>
+          <t>https://m.economictimes.com/news/india/mumbai-gets-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/articleshow/123365291.cms</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Mumbai gets 177mm rain in 6-8 hour period, says CM; all agencies asked to remain alert</t>
+          <t>Mumbai rains: Maharashtra CM says 'observe precautions', warns of heavy rainfall, high tide; check BMC's advisory</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/mumbai-gets-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/articleshow/123365291.cms</t>
+          <t>https://www.livemint.com/news/mumbai-rains-maharashtra-cm-says-observe-precautions-warns-of-heavy-rainfall-high-tide-check-bmcs-advisory-11755573270369.html</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Raghuji Bhonsle’s sword brought to India</t>
+          <t>Fadnavis govt’s big Maratha pride push: Legendary sword it ‘bought’ back from London, with a Rs 47L bid</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/19/raghuji-bhonsles-sword-brought-to-india.html</t>
+          <t>https://theprint.in/politics/fadnavis-govts-big-maratha-pride-push-legendary-sword-it-bought-back-from-london-with-a-rs-47l-bid/2723199/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Rain fury leaves 7 dead in Maharashtra, 200 villagers stranded</t>
+          <t>Maharashtra CM Fadnavis, Dy CM Shinde congratulate Governor CP Radhakrishnan on NDA's VP nomination</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/Rain-fury-leaves-7-dead-in-Maharashtra--200-villagers-stranded/2834213</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination-23589945</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Maharashtra CM Fadnavis, Dy CM Shinde congratulate Governor CP Radhakrishnan on NDA's VP nomination</t>
+          <t>Fadnavis meets Guv Radhakrishnan, presents him book of Shivaji Maharaj's letters</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination-23589945</t>
+          <t>https://www.ptinews.com/story/national/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharaj-s-letters/2832582</t>
         </is>
       </c>
     </row>
@@ -844,451 +844,451 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/business/-Third-Mumbai--to-boost-metropolitan-region-development--Fadnavis/2834902</t>
+          <t>https://www.ptinews.com/editor-detail/-third-mumbai--to-boost-metropolitan-region-development--fadnavis/2834902</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Fadnavis meets Guv Radhakrishnan, presents him book of Shivaji Maharaj's letters</t>
+          <t>‘Third Mumbai’ takes shape as CM Fadnavis unveils mega MMR expansion plan</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharaj-s-letters/2832582</t>
+          <t>https://www.moneycontrol.com/city/third-mumbai-takes-shape-as-cm-fadnavis-unveils-mega-mmr-expansion-plan-article-13465350.html</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Schools shut, red alert as Mumbai braces for another day of heavy rain | Latest News India - Hindustan Times</t>
+          <t>Raghuji Bhonsle’s sword brought to India</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/mumbai-rains-schools-shut-as-mumbai-under-imd-red-alert-braces-for-another-day-of-heavy-rain-10-updates-101755564432674-amp.html</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/19/raghuji-bhonsles-sword-brought-to-india.html</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Fadnavis Dedicates Goldman Sachs’ New Mumbai Office, Unveils Vision For ‘Third Mumbai’</t>
+          <t>Fadnavis meets Guv Radhakrishnan presents him book of Shivaji Maharaj's letters</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://www.businessworld.in/article/fadnavis-dedicates-goldman-sachs-new-mumbai-office-unveils-vision-for-third-mumbai-567845</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom20-mh-governor-fadnavis.html</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
+          <t>Rain fury leaves 7 dead in Maharashtra, 200 villagers stranded</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://udayavani.com/national/third-mumbai-to-boost-metropolitan-region-development-fadnavis-20250819T044623387Z?lang=en</t>
+          <t>https://www.ptinews.com/story/national/Rain-fury-leaves-7-dead-in-Maharashtra--200-villagers-stranded/2834213</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DH Evening Brief | NDA VP pick in Delhi to meet BJP top brass, Opposition yet to finalise their candidate; I.N.D.I.A. bloc continues attacking EC chief over SIR</t>
+          <t>Mumbai got 177mm rain in 6-8 hour period, says CM; all agencies asked to remain alert</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/dh-evening-brief-nda-vp-pick-in-delhi-to-meet-bjp-top-brass-opposition-yet-to-finalise-their-candidate-india-bloc-continues-attacking-ec-chief-over-sir-3685866</t>
+          <t>https://www.ptinews.com/story/national/mumbai-got-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/2833181</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Mumbai rain Highlights: 7 people dead across Maharashtra, says CM Devendra Fadnavis</t>
+          <t>Fadnavis Dedicates Goldman Sachs’ New Mumbai Office, Unveils Vision For ‘Third Mumbai’</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://www.india.com/news/india/mumbai-rain-live-updates-heavy-rains-lashes-city-orange-alert-for-today-red-alert-in-pune-satara-ratnagiri-local-trains-delayed-traffic-jams-8017300/</t>
+          <t>https://www.businessworld.in/article/fadnavis-dedicates-goldman-sachs-new-mumbai-office-unveils-vision-for-third-mumbai-567845</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Mumbai got 177mm rain in 6-8 hour period, says CM; all agencies asked to remain alert</t>
+          <t>Maharashtra on high alert as heavy rains batter state; CM, Dy CM lead rescue efforts</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/mumbai-got-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/2833181</t>
+          <t>https://www.daijiworld.com/news/newsDisplay?newsID=1289634</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Maharashtra on high alert as heavy rains batter state; CM, Dy CM lead rescue efforts</t>
+          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://www.daijiworld.com/news/newsDisplay?newsID=1289634</t>
+          <t>https://udayavani.com/national/third-mumbai-to-boost-metropolitan-region-development-fadnavis-20250819T044623387Z?lang=en</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Maratha general Raghuji Bhonsle's sword brought to Mumbai</t>
+          <t>Schools shut, red alert as Mumbai braces for another day of heavy rain | Latest News India - Hindustan Times</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/maratha-general-raghuji-bhonsle-s-sword-brought-to-mumbai/2833930</t>
+          <t>https://www.hindustantimes.com/india-news/mumbai-rains-schools-shut-as-mumbai-under-imd-red-alert-braces-for-another-day-of-heavy-rain-10-updates-101755564432674-amp.html</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
+          <t>Maratha general Raghuji Bhonsle's sword brought to Mumbai</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://www.millenniumpost.in/nation/third-mumbai-to-boost-metropolitan-region-development-fadnavis-623625</t>
+          <t>https://www.ptinews.com/editor-detail/maratha-general-raghuji-bhonsle-s-sword-brought-to-mumbai/2833930</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Maharashtra rain: Mumbai flooded, 5 missing in Nanded, more showers in store</t>
+          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by Maharashtra CM Devendra Fadnavis</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://thefederal.com/category/states/west/maharashtra/mumbai-flooded-nanded-5-missing-maharashtra-rain-202350</t>
+          <t>https://aninews.in/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Fadnavis meets Guv Radhakrishnan presents him book of Shivaji Maharaj's letters</t>
+          <t>Maharashtra rain: Mumbai flooded, 5 missing in Nanded, more showers in store</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom20-mh-governor-fadnavis.html</t>
+          <t>https://thefederal.com/category/states/west/maharashtra/mumbai-flooded-nanded-5-missing-maharashtra-rain-202350</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by Maharashtra CM Devendra Fadnavis</t>
+          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322/</t>
+          <t>https://www.millenniumpost.in/nation/third-mumbai-to-boost-metropolitan-region-development-fadnavis-623625</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Observe precaution: Maharashtra CM warns about severe weather conditions in state</t>
+          <t>Mumbai rain: 177 mm recorded in 6-8 hours, public advised to reach homes before 6.30 pm</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state-23590120</t>
+          <t>https://www.onmanorama.com/news/india/2025/08/18/mumbai-rains-flooding-high-tide-warning-live.html</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Rain fury leaves 7 dead in Maharashtra 200 villagers stranded</t>
+          <t>Heavy rains lash Nanded Five missing scores stranded says CM Fadnavis Army unit deployed</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom50-mh-2nd-ldall-rains.html</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom17-mh-rains-nanded.html</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Heavy rains lash Nanded Five missing scores stranded says CM Fadnavis Army unit deployed</t>
+          <t>Mumbai rain Highlights: 7 people dead across Maharashtra, says CM Devendra Fadnavis</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom17-mh-rains-nanded.html</t>
+          <t>https://www.india.com/news/india/mumbai-rain-live-updates-heavy-rains-lashes-city-orange-alert-for-today-red-alert-in-pune-satara-ratnagiri-local-trains-delayed-traffic-jams-8017300/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Pune can get underground road network to beat traffic woes</t>
+          <t>Observe precaution: Maharashtra CM warns about severe weather conditions in state</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://inshorts.com/en/news/pune-can-get-underground-road-network-to-beat-traffic-woes-1755566759073</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state-23590120</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Mumbai got 177mm rain in 6-8 hour period says CM more to come amid high tides</t>
+          <t>Rain fury leaves 7 dead in Maharashtra 200 villagers stranded</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom21-mh-rains-mumbai-cm.html</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom50-mh-2nd-ldall-rains.html</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by Maharashtra CM Devendra Fadnavis</t>
+          <t>Mumbai got 177mm rain in 6-8 hour period says CM more to come amid high tides</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278516795/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom21-mh-rains-mumbai-cm.html</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CM Devendra Fadnavis Meets Netherlands Yogasana Chief on Global Initiatives</t>
+          <t>Pune can get underground road network to beat traffic woes</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://www.transcontinentaltimes.com/netherlands-yogasana-sports-nysa/</t>
+          <t>https://inshorts.com/en/news/pune-can-get-underground-road-network-to-beat-traffic-woes-1755566759073</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>'Third Mumbai' Initiative Sparks New Wave of Economic Growth in Maharashtra</t>
+          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by Maharashtra CM Devendra Fadnavis</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/science-environment/3545659-third-mumbai-initiative-sparks-new-wave-of-economic-growth-in-maharashtra</t>
+          <t>https://www.bignewsnetwork.com/news/278516795/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Goldman Sachs Expands In Mumbai, Devendra Fadnavis Inaugurates New Worli Office</t>
+          <t>CM Devendra Fadnavis Meets Netherlands Yogasana Chief on Global Initiatives</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/business/goldman-sachs-expands-in-mumbai-devendra-fadnavis-inaugurates-new-worli-office</t>
+          <t>https://www.transcontinentaltimes.com/netherlands-yogasana-sports-nysa/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Mumbai: CM Devendra Fadnavis meets C.P. Radhakrishnan #Gallery</t>
+          <t>'Third Mumbai' Initiative Sparks New Wave of Economic Growth in Maharashtra</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/mumbai-cm-devendra-fadnavis-meets-c-p-radhakrishnan-gallery/</t>
+          <t>https://www.devdiscourse.com/article/science-environment/3545659-third-mumbai-initiative-sparks-new-wave-of-economic-growth-in-maharashtra</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Maharashtra CM Devendra Fadnavis Says ‘Third Mumbai’ Being Developed in Raigad District Will Open New</t>
+          <t>Mumbai: CM Devendra Fadnavis meets C.P. Radhakrishnan #Gallery</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/india/news/maharashtra-cm-devendra-fadnavis-says-third-mumbai-being-developed-in-raigad-district-will-open-new-chapter-of-economic-development-7064927.html</t>
+          <t>https://www.socialnews.xyz/2025/08/18/mumbai-cm-devendra-fadnavis-meets-c-p-radhakrishnan-gallery/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Mumbai Rains: Maharashtra CM Devendra Fadnavis Chairs Review Meeting On Excessive Rainfall At Mantralaya</t>
+          <t>Goldman Sachs Expands In Mumbai, Devendra Fadnavis Inaugurates New Worli Office</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-rains-cm-devendra-fadnavis-chairs-review-meeting-on-excessive-rainfall-at-mantralaya-video</t>
+          <t>https://www.freepressjournal.in/business/goldman-sachs-expands-in-mumbai-devendra-fadnavis-inaugurates-new-worli-office</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>India News | ⚡Devendra Fadnavis Says ‘Third Mumbai’ Will Open a New Chapter of Economic Development</t>
+          <t>'Third Mumbai' Will Open A New Chapter Of Economic Development: Maha CM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/quickly/india/news/devendra-fadnavis-says-third-mumbai-will-open-a-new-chapter-of-economic-development-7064927.html</t>
+          <t>https://menafn.com/1109941619/Third-Mumbai-Will-Open-A-New-Chapter-Of-Economic-Development-Maha-CM</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Mumbai Records 177 mm Rain In 6 Hours, CM Devendra Fadnavis Urges Caution Amid High Tide Alert</t>
+          <t>Mumbai Rains: Maharashtra CM Devendra Fadnavis Chairs Review Meeting On Excessive Rainfall At Mantralaya</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-records-177-mm-rain-in-6-hours-cm-devendra-fadnavis-urges-caution-amid-high-tide-alert</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-rains-cm-devendra-fadnavis-chairs-review-meeting-on-excessive-rainfall-at-mantralaya-video</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Future-ready India lies in STEM and AI, says Devendra Fadnavis, Maharashtra CM</t>
+          <t>India News | ⚡Devendra Fadnavis Says ‘Third Mumbai’ Will Open a New Chapter of Economic Development</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://indiacsr.in/brillio-national-stem-challenge-empowers-2500-underserved-students-to-innovate-for-indias-future/</t>
+          <t>https://www.latestly.com/quickly/india/news/devendra-fadnavis-says-third-mumbai-will-open-a-new-chapter-of-economic-development-7064927.html</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>‘Third Mumbai’ will open a new chapter of economic development: Maha CM</t>
+          <t>Mumbai Records 177 mm Rain In 6 Hours, CM Devendra Fadnavis Urges Caution Amid High Tide Alert</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/third-mumbai-will-open-a-new-chapter-of-economic-development-maha-cm/</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-records-177-mm-rain-in-6-hours-cm-devendra-fadnavis-urges-caution-amid-high-tide-alert</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>VIDEO: Historic Sword Of Raghuji Bhonsle Connects Youth With Maharashtra’s Glorious History, Says CM</t>
+          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by...</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/video-historic-sword-of-raghuji-bhonsle-connects-youth-with-maharashtras-glorious-history-says-cm-devendra-fadnavis</t>
+          <t>https://www.lokmattimes.com/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Mumbai: C.P. Radhakrishnan departs for Delhi #Gallery</t>
+          <t>Future-ready India lies in STEM and AI, says Devendra Fadnavis, Maharashtra CM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/mumbai-c-p-radhakrishnan-departs-for-delhi-gallery/</t>
+          <t>https://indiacsr.in/brillio-national-stem-challenge-empowers-2500-underserved-students-to-innovate-for-indias-future/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>'Observe precaution': Maharashtra CM warns about severe weather conditions in state</t>
+          <t>‘Third Mumbai’ will open a new chapter of economic development: Maha CM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://english.newsnationtv.com/national/general-news/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state20250819025510</t>
+          <t>https://www.lokmattimes.com/national/third-mumbai-will-open-a-new-chapter-of-economic-development-maha-cm/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>7 killed as heavy rain batters Maharashtr­a; 800 villages hit</t>
+          <t>Mumbai: C.P. Radhakrishnan departs for Delhi #Gallery</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://www.pressreader.com/india/the-hindu-erode-9WW6/20250819/281994678584394</t>
+          <t>https://www.socialnews.xyz/2025/08/18/mumbai-c-p-radhakrishnan-departs-for-delhi-gallery/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Heavy Rain Forecast for Mumbai: CM Fadnavis Reviews Flood Situation Across Maharashtra, with the Next 12...</t>
+          <t>VIDEO: Historic Sword Of Raghuji Bhonsle Connects Youth With Maharashtra’s Glorious History, Says CM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/mumbai/heavy-rain-forecast-for-mumbai-cm-fadnavis-reviews-flood-situation-across-maharashtra-with-the-next-12-hours-critical-a475/</t>
+          <t>https://www.freepressjournal.in/mumbai/video-historic-sword-of-raghuji-bhonsle-connects-youth-with-maharashtras-glorious-history-says-cm-devendra-fadnavis</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Mumbai Rains: Maharashtra CM Says 'Observe Precautions', Warns Of Heavy Rainfall, High Tide Check BMC's Advisory</t>
+          <t>Heavy Rain Forecast for Mumbai: CM Fadnavis Reviews Flood Situation Across Maharashtra, with the Next 12...</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://menafn.com/1109945394/Mumbai-Rains-Maharashtra-CM-Says-Observe-Precautions-Warns-Of-Heavy-Rainfall-High-Tide-Check-BMCs-Advisory</t>
+          <t>https://www.lokmattimes.com/mumbai/heavy-rain-forecast-for-mumbai-cm-fadnavis-reviews-flood-situation-across-maharashtra-with-the-next-12-hours-critical-a475/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Heavy rains in Mumbai: IndiGo, SpiceJet, Akasa issue travel advisories</t>
+          <t>'Observe precaution': Maharashtra CM warns about severe weather conditions in state</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://www.newsbytesapp.com/news/india/mumbai-flights-status-airlines-issue-key-advisory-for-passengers/story</t>
+          <t>https://english.newsnationtv.com/national/general-news/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state20250819025510</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Amid heavy rains in Maharashtra, CM Fadnavis directs all agencies to be on alert</t>
+          <t>Heavy rains in Mumbai: IndiGo, SpiceJet, Akasa issue travel advisories</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/india/amid-heavy-rains-in-maharashtra-cm-fadnavis-directs-all-agencies-to-be-on-alert</t>
+          <t>https://www.newsbytesapp.com/news/india/mumbai-flights-status-airlines-issue-key-advisory-for-passengers/story</t>
         </is>
       </c>
     </row>
@@ -1300,187 +1300,187 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://www.pressreader.com/india/the-hindu-mangalore-9WWc/20250819/281947433944151</t>
+          <t>https://www.pressreader.com/india/the-hindu-erode-9WW6/20250819/281994678584394</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Pune Patients Receive Over Rs 6.5 Crore in Medical Aid Under Chief Minister Devendra Fadnavis’ Initiative</t>
+          <t>Mumbai Rains: Maharashtra CM Says 'Observe Precautions', Warns Of Heavy Rainfall, High Tide Check BMC's Advisory</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-patients-receive-over-rs-6-5-crore-in-medical-aid-under-chief-minister-devendra-fadnavis-initiative/</t>
+          <t>https://menafn.com/1109945394/Mumbai-Rains-Maharashtra-CM-Says-Observe-Precautions-Warns-Of-Heavy-Rainfall-High-Tide-Check-BMCs-Advisory</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Those who speak of Maharashtra 'asmita' should support Radhakrishnan for VP post: Fadnavis</t>
+          <t>Pune Patients Receive Over Rs 6.5 Crore in Medical Aid Under Chief Minister Devendra Fadnavis’ Initiative</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/those-who-speak-of-maharashtra-asmita-should-support-radhakrishnan-for-vp-post-fadnavis-9672630</t>
+          <t>https://www.punekarnews.in/pune-patients-receive-over-rs-6-5-crore-in-medical-aid-under-chief-minister-devendra-fadnavis-initiative/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Business News</t>
+          <t>Maharashtra Rains: 5 Missing in Nanded, Over 200 Stranded Across Several Districts; Army, NDRF Deployed</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/business-news-credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis-7064653.html</t>
+          <t>https://www.lokmattimes.com/maharashtra/maharashtra-rains-5-missing-in-nanded-over-200-stranded-across-several-districts-army-ndrf-deployed-a517/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Maharashtra Rains: 5 Missing in Nanded, Over 200 Stranded Across Several Districts; Army, NDRF Deployed</t>
+          <t>Amid heavy rains in Maharashtra, CM Fadnavis directs all agencies to be on alert</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/maharashtra/maharashtra-rains-5-missing-in-nanded-over-200-stranded-across-several-districts-army-ndrf-deployed-a517/</t>
+          <t>https://www.thehawk.in/news/india/amid-heavy-rains-in-maharashtra-cm-fadnavis-directs-all-agencies-to-be-on-alert</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by Maharashtra CM Devendra Fadnavis</t>
+          <t>7 killed as heavy rain batters Maharashtr­a; 800 villages hit</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://english.newsnationtv.com/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322</t>
+          <t>https://www.pressreader.com/india/the-hindu-mangalore-9WWc/20250819/281947433944151</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Mumbai To Welcome Historic Sword Of Shrimant Raje Raghuji Bhonsale On August 18; To Be Ceremoniously Unveiled</t>
+          <t>Business News</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-to-welcome-historic-sword-of-shrimant-raje-raghuji-bhonsale-on-august-18-to-be-ceremoniously-unveiled-by-cm-fadnavis</t>
+          <t>https://www.latestly.com/agency-news/business-news-credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis-7064653.html</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CM Fadnavis unveils emblem for Ganeshotsav to be celebrated as Rajya Mahotsav</t>
+          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by Maharashtra CM Devendra Fadnavis</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/india/cm-fadnavis-unveils-emblem-for-ganeshotsav-to-be-celebrated-as-rajya-mahotsav</t>
+          <t>https://english.newsnationtv.com/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Fadnavis meets Guv Radhakrishnan, presents him book of Shivaji Maharaj's letters</t>
+          <t>Mumbai To Welcome Historic Sword Of Shrimant Raje Raghuji Bhonsale On August 18; To Be Ceremoniously Unveiled</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharajs-letters-9672415</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-to-welcome-historic-sword-of-shrimant-raje-raghuji-bhonsale-on-august-18-to-be-ceremoniously-unveiled-by-cm-fadnavis</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Mumbai Weather Today LIVE Updates: Mithi River Crosses Danger Mark; Santacruz Records Highest Rainfall; 300</t>
+          <t>Fadnavis meets Guv Radhakrishnan, presents him book of Shivaji Maharaj's letters</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-rains-live-updates-heavy-showers-wreak-havoc-in-city-schools-colleges-shut-as-imd-issues-red-alert-sion-matunga-dadar-vile-parle-waterlogged-andheri-subway-closed</t>
+          <t>https://www.newsdrum.in/national/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharajs-letters-9672415</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Fadnavis Gifts Unpublished Shivaji Maharaj Letters to Maharashtra Governor at Mumbai Airport</t>
+          <t>Rain fury leaves 7 dead in Maharashtra, 200 villagers stranded</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://panasiabiz.com/111091/cm-devendra-fadnavis-presents-rare-shivaji-maharaj-letters-to-governor-cp-radhakrishnan/</t>
+          <t>https://www.newsdrum.in/national/rain-fury-leaves-7-dead-in-maharashtra-200-villagers-stranded-9674070</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Maharashtra government approves major infra projects</t>
+          <t>CM Fadnavis unveils emblem for Ganeshotsav to be celebrated as Rajya Mahotsav</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/india/maharashtra-government-approves-major-infra-projects</t>
+          <t>https://www.thehawk.in/news/india/cm-fadnavis-unveils-emblem-for-ganeshotsav-to-be-celebrated-as-rajya-mahotsav</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Heavy rains lash Nanded: Five missing, scores stranded, says CM Fadnavis; Army unit deployed</t>
+          <t>Fadnavis Gifts Unpublished Shivaji Maharaj Letters to Maharashtra Governor at Mumbai Airport</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/heavy-rains-lash-nanded-five-missing-scores-stranded-says-cm-fadnavis-army-unit-deployed-9672306</t>
+          <t>https://panasiabiz.com/111091/cm-devendra-fadnavis-presents-rare-shivaji-maharaj-letters-to-governor-cp-radhakrishnan/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>महाराष्ट्र के इस जिले में बसाई जाएगी 'तीसरी मुंबई', मुख्यमंत्री देवेंद्र फडणवीस ने बताईं प्रोजेक्ट की अहम ब</t>
+          <t>Heavy rains lash Nanded: Five missing, scores stranded, says CM Fadnavis; Army unit deployed</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/paisa/business/third-mumbai-will-be-settled-in-raigad-district-of-maharashtra-chief-minister-devendra-fadnavis-told-the-important-points-of-the-project-2025-08-19-1156854</t>
+          <t>https://www.newsdrum.in/national/heavy-rains-lash-nanded-five-missing-scores-stranded-says-cm-fadnavis-army-unit-deployed-9672306</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>दिल्ली पहुंचे देवेंद्र फडणवीस, अमित शाह से मिले, जानें क्यों थी यह मुलाकात खास</t>
+          <t>Mumbai Weather Today LIVE Updates: Mithi River Crosses Danger Mark; Santacruz Records Highest Rainfall; 300</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B6-%E0%A4%B9-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A5%87-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%82-%E0%A4%A5-%E0%A4%AF%E0%A4%B9-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4-%E0%A4%96-%E0%A4%B8/ar-AA1Jjy9z</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-rains-live-updates-heavy-showers-wreak-havoc-in-city-schools-colleges-shut-as-imd-issues-red-alert-sion-matunga-dadar-vile-parle-waterlogged-andheri-subway-closed</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Mumbai Maharashtra Rains: महाराष्ट्र में भारी बारिश पर सीएम देवेंद्र फडणवीस का सख्त निर्देश, सभी विभाग अलर्ट पर</t>
+          <t>Maharashtra government approves major infra projects</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/mumbai-maharashtra-rains-cm-and-managment-on-alert-hindi/</t>
+          <t>https://www.thehawk.in/news/india/maharashtra-government-approves-major-infra-projects</t>
         </is>
       </c>
     </row>
@@ -1499,360 +1499,360 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>कैसी होगी तीसरी मुंबई, कितनी बड़ी और कहां बन रही, सुविधाओं से लेकर प्लानिंग तक, CM फडणवीस ने सब बताया</t>
+          <t>महाराष्ट्र के इस जिले में बसाई जाएगी 'तीसरी मुंबई', मुख्यमंत्री देवेंद्र फडणवीस ने बताईं प्रोजेक्ट की अहम ब</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://ndtv.in/maharashtra-news/maharashtra-cmdevendra-fadnavis-told-third-mumbai-mmr-will-develop-with-this-know-how-it-will-be-9112502</t>
+          <t>https://www.indiatv.in/paisa/business/third-mumbai-will-be-settled-in-raigad-district-of-maharashtra-chief-minister-devendra-fadnavis-told-the-important-points-of-the-project-2025-08-19-1156854</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Vice President Election: उद्धव ठाकरे और शरद पवार से फडणवीस मांगेंगे सीपी राधाकृष्णन के लिए समर्थन, शिंदे सेना ने दिया सपोर्ट</t>
+          <t>Mumbai Maharashtra Rains: महाराष्ट्र में भारी बारिश पर सीएम देवेंद्र फडणवीस का सख्त निर्देश, सभी विभाग अलर्ट पर</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-governor-radhakrishnan-gets-nda-backing-for-vice-president-post-devendra-fadnavis-uddhav-thackeray-sharad-pawar/articleshow/123371527.cms</t>
+          <t>https://thecsrjournal.in/mumbai-maharashtra-rains-cm-and-managment-on-alert-hindi/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>मुख्यमंत्री देवेंद्र फडणवीस ने राज्य में भारी बारिश के मद्देनजर सभी एजेंसियों को सतर्क रहने के निर्देश दिए</t>
+          <t>दिल्ली पहुंचे देवेंद्र फडणवीस, अमित शाह से मिले, जानें क्यों थी यह मुलाकात खास</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://www.mumbailive.com/hi/civic/chief-minister-devendra-fadnavis-directed-all-agencies-to-remain-alert-in-view-of-heavy-rains-in-the-state-89633</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B6-%E0%A4%B9-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A5%87-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%82-%E0%A4%A5-%E0%A4%AF%E0%A4%B9-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4-%E0%A4%96-%E0%A4%B8/ar-AA1Jjy9z</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>मुंबई में सिर्फ 6-8 घंटे में 177 मिमी हुई बारिश, फडणवीस ने दिए सावधानी बरतने के निर्देश</t>
+          <t>कैसी होगी तीसरी मुंबई, कितनी बड़ी और कहां बन रही, सुविधाओं से लेकर प्लानिंग तक, CM फडणवीस ने सब बताया</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/mumbai-received-177-mm-of-rain-in-just-6-8-hours-fadnavis-gave-instructions-to-take-precautions-11195</t>
+          <t>https://ndtv.in/maharashtra-news/maharashtra-cmdevendra-fadnavis-told-third-mumbai-mmr-will-develop-with-this-know-how-it-will-be-9112502</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Mumbai Rain News : मुंबई में बारिश ने मचाया कोहराम, देवेंद्र फडणवीस का आया बयान</t>
+          <t>Vice President Election: उद्धव ठाकरे और शरद पवार से फडणवीस मांगेंगे सीपी राधाकृष्णन के लिए समर्थन, शिंदे सेना ने दिया सपोर्ट</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/videos/mumbai-rain-news-rain-wreaked-havoc-in-mumbai-devendra-fadnavis-statement-came-4259449.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-governor-radhakrishnan-gets-nda-backing-for-vice-president-post-devendra-fadnavis-uddhav-thackeray-sharad-pawar/articleshow/123371527.cms</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>मुंबई में भारी भारिश ने मचाई तबाही, CM देवेंद्र फडणवीस ने बुलाई बैठक</t>
+          <t>मुख्यमंत्री देवेंद्र फडणवीस ने राज्य में भारी बारिश के मद्देनजर सभी एजेंसियों को सतर्क रहने के निर्देश दिए</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/videos/mumbai-news/heavy-rain-wreaks-havoc-in-mumbai-cm-devendra-fadnavis-calls-a-meeting-19874343</t>
+          <t>https://www.mumbailive.com/hi/civic/chief-minister-devendra-fadnavis-directed-all-agencies-to-remain-alert-in-view-of-heavy-rains-in-the-state-89633</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>फडणवीस ने कहा, ‘तीसरी मुंबई’ से एमएमआर का होगा विकास</t>
+          <t>मुंबई में सिर्फ 6-8 घंटे में 177 मिमी हुई बारिश, फडणवीस ने दिए सावधानी बरतने के निर्देश</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/economy/fadnavis-said-third-mumbai-will-lead-to-development-of-mmr/856867/</t>
+          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/mumbai-received-177-mm-of-rain-in-just-6-8-hours-fadnavis-gave-instructions-to-take-precautions-11195</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>महाराष्ट्र के नांदेड़ में फटा बादल, 15-16 जिलो में अलर्ट, CM फडणवीस बोले- फसलों को नुकसान</t>
+          <t>Mumbai Rain News : मुंबई में बारिश ने मचाया कोहराम, देवेंद्र फडणवीस का आया बयान</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/weather-mumbai-rains-local-train-cloudburst-nanded-alert-in-15-16-districts-in-maharashtra-cm-devendra-fadnavis-said-damage-to-crops-2997472</t>
+          <t>https://hindi.oneindia.com/videos/mumbai-rain-news-rain-wreaked-havoc-in-mumbai-devendra-fadnavis-statement-came-4259449.html</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Mumbai Rains News: भारी बारिश के चलते कल मुंबई के स्कूल-कॉलेजों में छुट्टी, नांदेड़ में 7 लोगों की मौत, CM फडणवीस ने की आपात बैठक</t>
+          <t>मुंबई में भारी भारिश ने मचाई तबाही, CM देवेंद्र फडणवीस ने बुलाई बैठक</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/heavy-rains-in-mumbai-schools-colleges-closed-7-deaths-in-maharashtra-5-missing-nanded-cm-fadnavis-emergency-meeting/articleshow/123366462.cms</t>
+          <t>https://www.patrika.com/videos/mumbai-news/heavy-rain-wreaks-havoc-in-mumbai-cm-devendra-fadnavis-calls-a-meeting-19874343</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>'औरंगजेब भारत के किसी भी समाज का हीरो नहीं...', मजार को लेकर फडणवीस ने कही बड़ी बात</t>
+          <t>फडणवीस ने कहा, ‘तीसरी मुंबई’ से एमएमआर का होगा विकास</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%AD-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AE%E0%A4%9C-%E0%A4%B0-%E0%A4%95-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC-%E0%A4%A4/ar-AA1IRFiN</t>
+          <t>https://hindi.theprint.in/india/economy/fadnavis-said-third-mumbai-will-lead-to-development-of-mmr/856867/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>मराठा सेनापति रघुजी भोंसले की 200 साल पुरानी तलवार पहुंची मुंबई, CM फडणवीस बोले-</t>
+          <t>महाराष्ट्र के नांदेड़ में फटा बादल, 15-16 जिलो में अलर्ट, CM फडणवीस बोले- फसलों को नुकसान</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/london-auction-historic-raghuji-bhosale-sword-brought-to-mumbai-devendra-fadnavis-says-indias-heritage-restored-2997814</t>
+          <t>https://www.abplive.com/states/maharashtra/weather-mumbai-rains-local-train-cloudburst-nanded-alert-in-15-16-districts-in-maharashtra-cm-devendra-fadnavis-said-damage-to-crops-2997472</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>मैं आपकी वहिनी… देवेंद्र फडणविस के शपथ लेते ही पत्नी अमृता फडणवीस ने महाराष्ट्र से किया ये वादा</t>
+          <t>Mumbai Rains News: भारी बारिश के चलते कल मुंबई के स्कूल-कॉलेजों में छुट्टी, नांदेड़ में 7 लोगों की मौत, CM फडणवीस ने की आपात बैठक</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%88%E0%A4%82-%E0%A4%86%E0%A4%AA%E0%A4%95-%E0%A4%B5%E0%A4%B9-%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%B6%E0%A4%AA%E0%A4%A5-%E0%A4%B2%E0%A5%87%E0%A4%A4%E0%A5%87-%E0%A4%B9-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A8-%E0%A4%85%E0%A4%AE%E0%A5%83%E0%A4%A4-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%AF%E0%A5%87-%E0%A4%B5-%E0%A4%A6/ar-AA1vljO5?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/heavy-rains-in-mumbai-schools-colleges-closed-7-deaths-in-maharashtra-5-missing-nanded-cm-fadnavis-emergency-meeting/articleshow/123366462.cms</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>इसमें उनका घाटा...हिंदी-मराठी भाषा विवाद के बीच फडणवीस का बड़ा दावा, बोले- मुंबई का मेयर तो हमारा ही होगा</t>
+          <t>CP Radhakrishnan को लेकर CM फडणवीस ने बड़ा खुलासा कर चल दिया दांव, अब क्‍या करेंगे उद्धव ठाकरे और शरद पवार?</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%87%E0%A4%B8%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%89%E0%A4%A8%E0%A4%95-%E0%A4%98-%E0%A4%9F-%E0%A4%B9-%E0%A4%82%E0%A4%A6-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%AD-%E0%A4%B7-%E0%A4%B5-%E0%A4%B5-%E0%A4%A6-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%9A-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%A6-%E0%A4%B5-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%95-%E0%A4%AE%E0%A5%87%E0%A4%AF%E0%A4%B0-%E0%A4%A4-%E0%A4%B9%E0%A4%AE-%E0%A4%B0-%E0%A4%B9-%E0%A4%B9-%E0%A4%97/ar-AA1ImpaC?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://hindi.oneindia.com/news/maharashtra/vice-presidential-election-cm-devendra-fadnavis-said-cp-radhakrishnan-is-a-mumbai-voter-support-him-1365243.html</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Maharashtra: फडणवीस बोले- औरंगजेब भारत का हीरो नहीं, सुप्रीम कोर्ट के SC आरक्षण पर फैसले को लागू करेगी सरकार</t>
+          <t>'औरंगजेब भारत के किसी भी समाज का हीरो नहीं...', मजार को लेकर फडणवीस ने कही बड़ी बात</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B8%E0%A5%81%E0%A4%AA%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%95%E0%A5%87-sc-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%AA%E0%A4%B0-%E0%A4%AB%E0%A5%88%E0%A4%B8%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B2-%E0%A4%97%E0%A5%82-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%97-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0/ar-AA1IRMGx</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%AD-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AE%E0%A4%9C-%E0%A4%B0-%E0%A4%95-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC-%E0%A4%A4/ar-AA1IRFiN</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Maharashtra: 'पुणे के विकास में सबसे बड़ी बाधा बन चुकी है उद्योगों पर दादागीरी', सीएम फडणवीस ने दी चेतावनी</t>
+          <t>मराठा सेनापति रघुजी भोंसले की 200 साल पुरानी तलवार पहुंची मुंबई, CM फडणवीस बोले-</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AA%E0%A5%81%E0%A4%A3%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%B5-%E0%A4%95-%E0%A4%B8-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8%E0%A4%AC%E0%A4%B8%E0%A5%87-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC-%E0%A4%A7-%E0%A4%AC%E0%A4%A8-%E0%A4%9A%E0%A5%81%E0%A4%95-%E0%A4%B9%E0%A5%88-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%97-%E0%A4%82-%E0%A4%AA%E0%A4%B0-%E0%A4%A6-%E0%A4%A6-%E0%A4%97-%E0%A4%B0-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%A6-%E0%A4%9A%E0%A5%87%E0%A4%A4-%E0%A4%B5%E0%A4%A8/ar-AA1JMfla?ocid=finance-verthp-feeds&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.abplive.com/states/maharashtra/london-auction-historic-raghuji-bhosale-sword-brought-to-mumbai-devendra-fadnavis-says-indias-heritage-restored-2997814</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>CP Radhakrishnan को लेकर CM फडणवीस ने बड़ा खुलासा कर चल दिया दांव, अब क्‍या करेंगे उद्धव ठाकरे और शरद पवार?</t>
+          <t>मैं आपकी वहिनी… देवेंद्र फडणविस के शपथ लेते ही पत्नी अमृता फडणवीस ने महाराष्ट्र से किया ये वादा</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/maharashtra/vice-presidential-election-cm-devendra-fadnavis-said-cp-radhakrishnan-is-a-mumbai-voter-support-him-1365243.html</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%88%E0%A4%82-%E0%A4%86%E0%A4%AA%E0%A4%95-%E0%A4%B5%E0%A4%B9-%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%B6%E0%A4%AA%E0%A4%A5-%E0%A4%B2%E0%A5%87%E0%A4%A4%E0%A5%87-%E0%A4%B9-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A8-%E0%A4%85%E0%A4%AE%E0%A5%83%E0%A4%A4-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%AF%E0%A5%87-%E0%A4%B5-%E0%A4%A6/ar-AA1vljO5?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>फडणवीस की पत्नी के खिलाफ अपमानजनक पोस्ट : दो लोगों की अग्रिम जमानत अर्जी खारिज</t>
+          <t>इसमें उनका घाटा...हिंदी-मराठी भाषा विवाद के बीच फडणवीस का बड़ा दावा, बोले- मुंबई का मेयर तो हमारा ही होगा</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%96-%E0%A4%B2-%E0%A4%AB-%E0%A4%85%E0%A4%AA%E0%A4%AE-%E0%A4%A8%E0%A4%9C%E0%A4%A8%E0%A4%95-%E0%A4%AA-%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%A6-%E0%A4%B2-%E0%A4%97-%E0%A4%82-%E0%A4%95-%E0%A4%85%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%9C%E0%A4%AE-%E0%A4%A8%E0%A4%A4-%E0%A4%85%E0%A4%B0%E0%A5%8D%E0%A4%9C-%E0%A4%96-%E0%A4%B0-%E0%A4%9C/ar-AA1Je80j?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%87%E0%A4%B8%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%89%E0%A4%A8%E0%A4%95-%E0%A4%98-%E0%A4%9F-%E0%A4%B9-%E0%A4%82%E0%A4%A6-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%AD-%E0%A4%B7-%E0%A4%B5-%E0%A4%B5-%E0%A4%A6-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%9A-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%A6-%E0%A4%B5-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%95-%E0%A4%AE%E0%A5%87%E0%A4%AF%E0%A4%B0-%E0%A4%A4-%E0%A4%B9%E0%A4%AE-%E0%A4%B0-%E0%A4%B9-%E0%A4%B9-%E0%A4%97/ar-AA1ImpaC?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>मुंबई में 6-8 घंटे में 177 मिलीमीटर बारिश हुई: फडणवीस</t>
+          <t>Maharashtra: फडणवीस बोले- औरंगजेब भारत का हीरो नहीं, सुप्रीम कोर्ट के SC आरक्षण पर फैसले को लागू करेगी सरकार</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/mumbai-received-177-mm-of-rain-in-6-8-hours-fadnavis/856688/</t>
+          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B8%E0%A5%81%E0%A4%AA%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%95%E0%A5%87-sc-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%AA%E0%A4%B0-%E0%A4%AB%E0%A5%88%E0%A4%B8%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B2-%E0%A4%97%E0%A5%82-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%97-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0/ar-AA1IRMGx</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में भारी बारिश का कहर, 16 जिलों में रेड अलर्ट, बचाव दल तैनात</t>
+          <t>मुंबई में 6-8 घंटे में 177 मिलीमीटर बारिश हुई: फडणवीस</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-heavy-rainfall-flood-alert-red-and-orange-alerts-issued-relief-operations-mumbai-rain-ann-2997660</t>
+          <t>https://hindi.theprint.in/india/mumbai-received-177-mm-of-rain-in-6-8-hours-fadnavis/856688/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>नांदेड़ में भारी बारिश के कारण पांच लोग लापता, कई व्यक्ति फंसे : मुख्यमंत्री फडणवीस</t>
+          <t>फडणवीस की पत्नी के खिलाफ अपमानजनक पोस्ट : दो लोगों की अग्रिम जमानत अर्जी खारिज</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/five-people-missing-many-people-stranded-due-to-heavy-rains-in-nanded-chief-minister-fadnavis/856679/</t>
+          <t>http://www.msn.com/hi-in/news/other/%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%96-%E0%A4%B2-%E0%A4%AB-%E0%A4%85%E0%A4%AA%E0%A4%AE-%E0%A4%A8%E0%A4%9C%E0%A4%A8%E0%A4%95-%E0%A4%AA-%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%A6-%E0%A4%B2-%E0%A4%97-%E0%A4%82-%E0%A4%95-%E0%A4%85%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%9C%E0%A4%AE-%E0%A4%A8%E0%A4%A4-%E0%A4%85%E0%A4%B0%E0%A5%8D%E0%A4%9C-%E0%A4%96-%E0%A4%B0-%E0%A4%9C/ar-AA1Je80j?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Mumbai Rain: 24 घंटे की बारिश से मुंबई की सांस फूली, CM देवेंद्र फडणवीस ने पड़ोसी राज्यों से किया संपर्क</t>
+          <t>नांदेड़ में भारी बारिश के कारण पांच लोग लापता, कई व्यक्ति फंसे : मुख्यमंत्री फडणवीस</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/india/mumbai-rains-today-imd-red-alert-warning-waterlogging-traffic-update/2886161</t>
+          <t>https://hindi.theprint.in/india/five-people-missing-many-people-stranded-due-to-heavy-rains-in-nanded-chief-minister-fadnavis/856679/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Raghuji Bhosale: आज मुंबई आएगी रघुजी भोसले की की ऐतिहासिक तलवार, सीएम फडणवीस करेंगे स्वागत</t>
+          <t>Mumbai Rain: 24 घंटे की बारिश से मुंबई की सांस फूली, CM देवेंद्र फडणवीस ने पड़ोसी राज्यों से किया संपर्क</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/india/raghuji-bhosale-historic-sword-will-arrive-in-mumbai-today-cm-fadnavis-will-welcome-it/2886138</t>
+          <t>https://zeenews.india.com/hindi/india/mumbai-rains-today-imd-red-alert-warning-waterlogging-traffic-update/2886161</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>'Indias Got Latent' विवाद पर अभिनेता से नेता तक भड़के, CM फडणवीस बोले-होना चाहिए एक्शन</t>
+          <t>Raghuji Bhosale: आज मुंबई आएगी रघुजी भोसले की की ऐतिहासिक तलवार, सीएम फडणवीस करेंगे स्वागत</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/indias-got-latent-%E0%A4%B5-%E0%A4%B5-%E0%A4%A6-%E0%A4%AA%E0%A4%B0-%E0%A4%85%E0%A4%AD-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%B8%E0%A5%87-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%A4%E0%A4%95-%E0%A4%AD%E0%A4%A1%E0%A4%BC%E0%A4%95%E0%A5%87-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%B9-%E0%A4%A8-%E0%A4%9A-%E0%A4%B9-%E0%A4%8F-%E0%A4%8F%E0%A4%95%E0%A5%8D%E0%A4%B6%E0%A4%A8/ar-AA1yKIjb?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://zeenews.india.com/hindi/india/raghuji-bhosale-historic-sword-will-arrive-in-mumbai-today-cm-fadnavis-will-welcome-it/2886138</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में बन रही है तीसरी मुंबई, इस जिले का होगा आर्थिक विकास, जानें पूरी जानकारी | News Track in...</t>
+          <t>महाराष्ट्र में भारी बारिश का कहर, 16 जिलों में रेड अलर्ट, बचाव दल तैनात</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>https://newstrack.com/india/third-mumbai-being-built-maharashtra-district-have-economic-development-know-full-details-534715</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-heavy-rainfall-flood-alert-red-and-orange-alerts-issued-relief-operations-mumbai-rain-ann-2997660</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>मुंबई में भारी बारिश के बीच सुचारू रूप से चल रही मेट्रो, सीएम फडणवीस ने की तारीफ</t>
+          <t>'Indias Got Latent' विवाद पर अभिनेता से नेता तक भड़के, CM फडणवीस बोले-होना चाहिए एक्शन</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>https://www.m.khaskhabar.com/news/news-metro-running-smoothly-amid-heavy-rains-in-mumbai-cm-fadnavis-praised-news-hindi-1-745323-KKN.html</t>
+          <t>https://www.msn.com/hi-in/news/other/indias-got-latent-%E0%A4%B5-%E0%A4%B5-%E0%A4%A6-%E0%A4%AA%E0%A4%B0-%E0%A4%85%E0%A4%AD-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%B8%E0%A5%87-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%A4%E0%A4%95-%E0%A4%AD%E0%A4%A1%E0%A4%BC%E0%A4%95%E0%A5%87-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%B9-%E0%A4%A8-%E0%A4%9A-%E0%A4%B9-%E0%A4%8F-%E0%A4%8F%E0%A4%95%E0%A5%8D%E0%A4%B6%E0%A4%A8/ar-AA1yKIjb?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>CM फडणवीस ने खेला 'मराठी अस्मिता' का दांव, उपराष्ट्रपति चुनाव में उद्धव-पवार पर बना दबाव</t>
+          <t>महाराष्ट्र में बन रही है तीसरी मुंबई, इस जिले का होगा आर्थिक विकास, जानें पूरी जानकारी | News Track in...</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/political-battle-over-nda-candidate-radhakrishnan-cm-fadnavis-seeks-support-from-uddhav-thackeray-and-sharad-pawar-1321873.html</t>
+          <t>https://newstrack.com/india/third-mumbai-being-built-maharashtra-district-have-economic-development-know-full-details-534715</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>बाढ़ संकट पर अबू आजमी का CM फडणवीस को पत्र, प्रभावितों तक तुरंत राहत पहुंचाने की मांग</t>
+          <t>CM फडणवीस ने खेला 'मराठी अस्मिता' का दांव, उपराष्ट्रपति चुनाव में उद्धव-पवार पर बना दबाव</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/latest-news/abu-azmi-wrote-a-letter-to-cm-devendra-fadnavis-asking-him-to-send-relief-supplies-to-flood-affected-region-1322005.html</t>
+          <t>https://navbharatlive.com/maharashtra/political-battle-over-nda-candidate-radhakrishnan-cm-fadnavis-seeks-support-from-uddhav-thackeray-and-sharad-pawar-1321873.html</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>महाराष्ट्र किसानों को मिलेगी बड़ी राहत, CM फडणवीस जल्द करेंगे कर्जमाफी की घोषणा</t>
+          <t>बाढ़ संकट पर अबू आजमी का CM फडणवीस को पत्र, प्रभावितों तक तुरंत राहत पहुंचाने की मांग</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/guardian-minister-sanjay-rathore-claims-cm-fadnavis-may-announce-a-loan-waiver-for-farmers-1322081.html</t>
+          <t>https://navbharatlive.com/latest-news/abu-azmi-wrote-a-letter-to-cm-devendra-fadnavis-asking-him-to-send-relief-supplies-to-flood-affected-region-1322005.html</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>नांदेड़ में मूसलधार बारिश से हाहाकार, CM फडणवीस की निगरानी में राहत कार्य तेज</t>
+          <t>महाराष्ट्र किसानों को मिलेगी बड़ी राहत, CM फडणवीस जल्द करेंगे कर्जमाफी की घोषणा</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/heavy-rains-cause-havoc-in-nanded-rescue-operation-intensified-under-the-supervision-of-cm-fadnavis-1321752.html</t>
+          <t>https://navbharatlive.com/maharashtra/guardian-minister-sanjay-rathore-claims-cm-fadnavis-may-announce-a-loan-waiver-for-farmers-1322081.html</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>अबू आजमी ने सीएम देवेंद्र फडणवीस को लिखा पत्र, बाढ़ प्रभावित इलाकों में राहत सामग्री पहुंचाने की मांग की</t>
+          <t>नांदेड़ में मूसलधार बारिश से हाहाकार, CM फडणवीस की निगरानी में राहत कार्य तेज</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>https://www.newsnationtv.com/abu-azmi-ne-cm-devendra-fadnavis-ko-likha-patra-badh-prabhavit-ilakon-mein-rahat-pahunchane-ki-mang-ki--20250818191027/</t>
+          <t>https://navbharatlive.com/maharashtra/heavy-rains-cause-havoc-in-nanded-rescue-operation-intensified-under-the-supervision-of-cm-fadnavis-1321752.html</t>
         </is>
       </c>
     </row>
@@ -1871,132 +1871,132 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Mumbai News: महाराष्ट्र में मूसलाधार बारिश से हाहाकार, मुख्यमंत्री की हाईलेवल बैठक, विशेष सत्र बुलाने की मांग | Heavy rains cause havoc in Maharashtra, high level meeting of Chief Minister, demand for calling special s</t>
+          <t>Maharashtra Live News 18 Aug: एक क्लिक में पढ़े महाराष्ट्र की दिन भर की बड़ी खब़रें...</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/city/mumbai/mumbai-news-heavy-rains-cause-havoc-in-maharashtra-high-level-meeting-of-chief-minister-demand-for-calling-special-session-1174171</t>
+          <t>https://navbharatlive.com/maharashtra/latest-live-updates-maharashtra-politics-crime-nagpur-news-mumbai-pune-18-august-1321138.html</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Maharashtra Live News Updates: एक क्लिक में पढ़े महाराष्ट्र की दिन भर की बड़ी खब़रें...</t>
+          <t>अबू आजमी ने सीएम देवेंद्र फडणवीस को लिखा पत्र, बाढ़ प्रभावित इलाकों में राहत सामग्री पहुंचाने की मांग की</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/latest-live-updates-maharashtra-politics-crime-nagpur-news-mumbai-pune-18-august-1321138.html</t>
+          <t>https://www.newsnationtv.com/abu-azmi-ne-cm-devendra-fadnavis-ko-likha-patra-badh-prabhavit-ilakon-mein-rahat-pahunchane-ki-mang-ki--20250818191027/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में भारी बारिश से कई जिलों में रेड और ऑरेंज अलर्ट</t>
+          <t>Mumbai News: महाराष्ट्र में मूसलाधार बारिश से हाहाकार, मुख्यमंत्री की हाईलेवल बैठक, विशेष सत्र बुलाने की मांग | Heavy rains cause havoc in Maharashtra, high level meeting of Chief Minister, demand for calling special s</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>https://vikalptimes.com/red-and-orange-alert-issued-in-many-districts-of-maharashtra-due-to-heavy-rains/</t>
+          <t>https://www.bhaskarhindi.com/city/mumbai/mumbai-news-heavy-rains-cause-havoc-in-maharashtra-high-level-meeting-of-chief-minister-demand-for-calling-special-session-1174171</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CM फडणवीस ने एनडीए के उपराष्ट्रपति पद के नामांकन पर सीपी राधाकृष्णन को शॉल भेंट की</t>
+          <t>राष्ट्रीय: मुंबई में भारी बारिश के बीच सुचारू रूप से चल रही मेट्रो, सीएम फडणवीस ने की तारीफ</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vice-president-nomination-4218433</t>
+          <t>https://www.bhaskarhindi.com/other/news-1174019</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Mumbai Rains: मुंबई में भारी बारिश से 12 लोगों की मौत, जगह-जगह कमर तक भरा पानी, स्कूल-कॉलेज बंद, फ्लाइट्स पर भी असर</t>
+          <t>फडणवीस ने कहा, 'तीसरी मुंबई' से एमएमआर का होगा विकास</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>https://lalluram.com/mumbai-rains-7-people-died-due-to-rain-water-flooded-on-roads-schools-and-colleges-closed-flights-also-affected/</t>
+          <t>https://www.ibc24.in/business/third-mumbai-will-lead-to-development-of-mmr-says-fadnavis-3213495.html</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>किसानों को जल्द मिल सकता है कर्जमाफी का तोहफा, मंत्री संजय राठोड़ का बड़ा बयान</t>
+          <t>महाराष्ट्र : भारी बारिश के बाद नांदेड़ में राहत कार्य तेज, प्रशासन के संपर्क में सीएम फडणवीस</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/maharashtra/farmer-loan-waiver-maharashtra-sanjay-rathod-devendra-fadnavis-54-804134</t>
+          <t>https://www.newsnationtv.com/maharashtra-bhari-barish-ke-baad-nanded-mein-rahat-bachav-karya-tez-jiladhikariyon-ke-sampark-mein-cm-fadnavis--20250818144516/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>उपराष्ट्रपति चुनाव में भाजपा का दांव, सीपी राधाकृष्णन उम्मीदवार, महाराष्ट्र की राजनीति में बढ़ी हलचल</t>
+          <t>CM फडणवीस ने एनडीए के उपराष्ट्रपति पद के नामांकन पर सीपी राधाकृष्णन को शॉल भेंट की</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/maharashtra/vice-president-election-bjp-candidate-cp-radhakrishnan-devendra-fadnavis-54-803924</t>
+          <t>https://jantaserishta.com/local/maharashtra/cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vice-president-nomination-4218433</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>महाराष्ट्र : भारी बारिश के बाद नांदेड़ में राहत कार्य तेज, प्रशासन के संपर्क में सीएम फडणवीस</t>
+          <t>उपराष्ट्रपति चुनाव में भाजपा का दांव, सीपी राधाकृष्णन उम्मीदवार, महाराष्ट्र की राजनीति में बढ़ी हलचल</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>https://www.newsnationtv.com/maharashtra-bhari-barish-ke-baad-nanded-mein-rahat-bachav-karya-tez-jiladhikariyon-ke-sampark-mein-cm-fadnavis--20250818144516/</t>
+          <t>https://mpbreakingnews.in/maharashtra/vice-president-election-bjp-candidate-cp-radhakrishnan-devendra-fadnavis-54-803924</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Mumbai: राज्यपाल की उपराष्ट्रपति पद की उम्मीदवारी पर मुख्यमंत्री ने जताया हर्ष</t>
+          <t>किसानों को जल्द मिल सकता है कर्जमाफी का तोहफा, मंत्री संजय राठोड़ का बड़ा बयान</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/mumbai-chief-minister-expressed-happiness-over-the-candidature-of-the-governor-for-the-post-of-vice-president-mumbai--4218462</t>
+          <t>https://mpbreakingnews.in/maharashtra/farmer-loan-waiver-maharashtra-sanjay-rathod-devendra-fadnavis-54-804134</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>नांदेड़ में भारी बारिश के कारण पांच लोग लापता, कई व्यक्ति फंसे : मुख्यमंत्री फडणवीस</t>
+          <t>Mumbai Rains: मुंबई में भारी बारिश से 12 लोगों की मौत, जगह-जगह कमर तक भरा पानी, स्कूल-कॉलेज बंद, फ्लाइट्स पर भी असर</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/maharashtra/five-people-missing-several-stranded-due-to-heavy-rains-in-nanded-cm-fadnavis-3212983.html</t>
+          <t>https://lalluram.com/mumbai-rains-7-people-died-due-to-rain-water-flooded-on-roads-schools-and-colleges-closed-flights-also-affected/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Mumbai : महाराष्ट्र में मूसलाधार बारिश से हाहाकार, सात लोगों की मौत</t>
+          <t>Mumbai: राज्यपाल की उपराष्ट्रपति पद की उम्मीदवारी पर मुख्यमंत्री ने जताया हर्ष</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>https://indiagroundreport.com/mumbai-torrential-rains-in-maharashtra-cause-havoc-seven-people-died/</t>
+          <t>https://jantaserishta.com/local/maharashtra/mumbai-chief-minister-expressed-happiness-over-the-candidature-of-the-governor-for-the-post-of-vice-president-mumbai--4218462</t>
         </is>
       </c>
     </row>
@@ -2039,36 +2039,36 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Shinde and BJP: The saga continues</t>
+          <t>Rain fury leaves 7 dead in Maharashtra, 200 villagers stranded</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/shinde-and-bjp-the-saga-continues/ar-AA1KHn3K</t>
+          <t>https://www.ptinews.com/story/national/rain-fury-leaves-7-dead-in-maharashtra,-200-villagers-stranded/2834213</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Heavy rainfall causes 7 deaths, crop loss in Maharashtra as alerts continue</t>
+          <t>CREDAI-MCHI appoints Sukhraj Nahar as 18th President</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/heavy-rainfall-causes-7-deaths-crop-loss-in-maharashtra-as-alerts-continue/ar-AA1KK6Zt</t>
+          <t>https://housing.com/news/credai-mchi-appoints-sukhraj-nahar-as-president/</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>CREDAI-MCHI appoints Sukhraj Nahar as 18th President</t>
+          <t>Maharashtra CM Devendra Fadnavis Says ‘Third Mumbai’ Being Developed in Raigad District Will Open New</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>https://housing.com/news/credai-mchi-appoints-sukhraj-nahar-as-president/</t>
+          <t>https://www.latestly.com/india/news/maharashtra-cm-devendra-fadnavis-says-third-mumbai-being-developed-in-raigad-district-will-open-new-chapter-of-economic-development-7064927.html</t>
         </is>
       </c>
     </row>
@@ -2135,24 +2135,24 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis : अख्खा पक्ष विरोधात, पण या दिग्गज नेत्याचा फडणवीसांना पाठिंबा, एका पत्राने राजकीय वर्तु...</t>
+          <t>राज्यात अतिवृष्टीमुळे मुख्यमंत्री देवेंद्र फडणवीस यांचे सर्व यंत्रणांना सतर्कतेचे निर्देश; नांदेड जिल्ह्यात लष्कराची मदत</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/cm-devendra-fadnavis-gets-support-from-congress-leader-nitin-raut-letter-goes-viral-1461146.html</t>
+          <t>https://www.loksatta.com/mumbai/chief-minister-devendra-fadnavis-has-directed-all-agencies-to-be-on-alert-due-to-heavy-rains-in-the-maharashtra-mumbai-print-news-amy-95-5313479/</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>राज्यात अतिवृष्टीमुळे मुख्यमंत्री देवेंद्र फडणवीस यांचे सर्व यंत्रणांना सतर्कतेचे निर्देश; नांदेड जिल्ह्यात लष्कराची मदत</t>
+          <t>पुढील १२ तास मुंबईसाठी अत्यंत महत्त्वाचे, मुख्यमंत्री फडणवीस पावसाबाबत काय म्हणाले?</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/chief-minister-devendra-fadnavis-has-directed-all-agencies-to-be-on-alert-due-to-heavy-rains-in-the-maharashtra-mumbai-print-news-amy-95-5313479/</t>
+          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-review-mumbai-rain-says-next-12-hours-important-for-mumbai-and-mmr-region-1460967.html</t>
         </is>
       </c>
     </row>
@@ -2171,48 +2171,48 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>राज्यात अतिवृष्टीच्या पार्श्वभूमीवर प्रशासन अलर्ट मोडवर! मुख्यमंत्री देवेंद्र फडणवीस यांचे सतर्कतेचे निर्देश</t>
+          <t>राज्यभरात पावसाचा हाहाकार, मुख्यमंत्री देवेंद्र फडणवीस यांनी घेतला आढावा; सर्व यंत्रणांना सतर्कतेचे निर्देश</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/cm-devendra-fadnavis-took-review-of-rain-situation-at-state-disaster-management-centre-in-the-ministry-963383.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/rains-lashed-the-state-chief-minister-devendra-fadnavis-took-stock-instructed-all-agencies-to-be-alert.html</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Farmers Loan Waiver: बावनकुळेंनंतर महायुती सरकारमधील 'या' मंत्र्याची कर्जमाफीबाबत मोठी अपडेट; म्हणाले,'CM फडणवीस लवकरच...'</t>
+          <t>Mumbai Rain Update : समुद्रातून येतंय मुंबईवर मोठं संकट, पुढच्या 12 तासांत तुफान पाऊस, फडणवीस काय...</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/amp/story/maharashtra/vidarbha/sanjay-rathod-update-farmer-loan-waiver-devendra-fadnavis-dk88</t>
+          <t>https://www.tv9marathi.com/maharashtra/mumbai-rain-alert-cm-devendra-fadnavis-said-mumbai-have-red-alert-school-holiday-declared-know-detail-information-in-marathi-1472488.html</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis : महाराष्ट्रातील माणसाला सर्वांनी समर्थन द्यावं; फडणवीस यांचे मविआला आवाहन</t>
+          <t>राज्यात अतिवृष्टीच्या पार्श्वभूमीवर प्रशासन अलर्ट मोडवर! मुख्यमंत्री देवेंद्र फडणवीस यांचे सतर्कतेचे निर्देश</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-appeals-to-maharashtra-mps-to-support-cp-radhakrishnan-for-vice-president/913103/</t>
+          <t>https://www.navarashtra.com/maharashtra/cm-devendra-fadnavis-took-review-of-rain-situation-at-state-disaster-management-centre-in-the-ministry-963383.html</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>पुढील १२ तास मुंबईसाठी अत्यंत महत्त्वाचे, मुख्यमंत्री फडणवीस पावसाबाबत काय म्हणाले?</t>
+          <t>Farmers Loan Waiver: बावनकुळेंनंतर महायुती सरकारमधील 'या' मंत्र्याची कर्जमाफीबाबत मोठी अपडेट; म्हणाले,'CM फडणवीस लवकरच...'</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-review-mumbai-rain-says-next-12-hours-important-for-mumbai-and-mmr-region-1460967.html</t>
+          <t>https://sarkarnama.esakal.com/amp/story/maharashtra/vidarbha/sanjay-rathod-update-farmer-loan-waiver-devendra-fadnavis-dk88</t>
         </is>
       </c>
     </row>
@@ -2231,24 +2231,24 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>नवीन पिढीला इतिहासाशी जोडण्याचे कार्य सुरू; मुख्यमंत्री देवेंद्र फडणवीस यांचे प्रतिपादन</t>
+          <t>Devendra Fadnavis : अख्खा पक्ष विरोधात, पण या दिग्गज नेत्याचा फडणवीसांना पाठिंबा, एका पत्राने राजकीय वर्तु...</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/devendra-fadnavis-asserts-that-the-work-of-connecting-the-new-generation-with-history-is-underway-mumbai-print-news-amy-95-5313830/</t>
+          <t>https://news18marathi.com/maharashtra/cm-devendra-fadnavis-gets-support-from-congress-leader-nitin-raut-letter-goes-viral-1461146.html</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>मोठी बातमी! शेतकऱ्यांची कर्जमाफी होणार, मुख्यमंत्री घोषणा करणार, बड्या मंत्र्याने दिली माहिती</t>
+          <t>नवीन पिढीला इतिहासाशी जोडण्याचे कार्य सुरू; मुख्यमंत्री देवेंद्र फडणवीस यांचे प्रतिपादन</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/big-update-on-farmer-loan-waiver-cm-fadnavis-will-do-announcement-says-minister-sanjay-rathod-1472819.html</t>
+          <t>https://www.loksatta.com/mumbai/devendra-fadnavis-asserts-that-the-work-of-connecting-the-new-generation-with-history-is-underway-mumbai-print-news-amy-95-5313830/</t>
         </is>
       </c>
     </row>
@@ -2279,24 +2279,24 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Maharashtra Rain Updates: मुंबईसाठी पुढील 12 तास महत्त्वाचे, राज्यात स्थिती काय? CM फडणवीसांनी सगळं सांगितल...</t>
+          <t>मोठी बातमी! शेतकऱ्यांची कर्जमाफी होणार, मुख्यमंत्री घोषणा करणार, बड्या मंत्र्याने दिली माहिती</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/maharashtra-rain-update-cm-devendra-fadnavis-hold-meeting-with-district-administration-1460734.html</t>
+          <t>https://www.tv9marathi.com/maharashtra/big-update-on-farmer-loan-waiver-cm-fadnavis-will-do-announcement-says-minister-sanjay-rathod-1472819.html</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>मोठी बातमी! नाराजी भोवली, शिवसेना शिंदे गटाला सर्वात मोठा धक्का, बड्या नेत्यानं सोडली एकनाथ शिंदेंची...</t>
+          <t>Maharashtra Rain Updates: मुंबईसाठी पुढील 12 तास महत्त्वाचे, राज्यात स्थिती काय? CM फडणवीसांनी सगळं सांगितल...</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/big-blow-to-eknath-shinde-big-leader-of-shiv-sena-shinde-group-will-join-bjp-1472541.html</t>
+          <t>https://news18marathi.com/maharashtra/maharashtra-rain-update-cm-devendra-fadnavis-hold-meeting-with-district-administration-1460734.html</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>School holiday: मुंबईत पावसामुळे शाळांना सुटी जाहीर, पुढील ४८ तासांचा अतिवृष्टीचा इशारा; काळजी घेण्याचे आवाहन</t>
+          <t>मोठी बातमी! नाराजी भोवली, शिवसेना शिंदे गटाला सर्वात मोठा धक्का, बड्या नेत्यानं सोडली एकनाथ शिंदेंची...</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/school-holiday-in-mumbai-due-to-rain-heavy-rainfall-alert-for-the-next-48-hours/articleshow/123357322.cms</t>
+          <t>https://www.tv9marathi.com/maharashtra/big-blow-to-eknath-shinde-big-leader-of-shiv-sena-shinde-group-will-join-bjp-1472541.html</t>
         </is>
       </c>
     </row>
@@ -2351,12 +2351,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Heavy Rain: राज्यात अतिवृष्टीच्या पार्श्वभूमीवर मुख्यमंत्री देवेंद्र फडणवीस यांचे सर्व यंत्रणांना सतर्कतेचे</t>
+          <t>लवकरच कर्जमाफीची घोषणा होणार? महायुती सरकारमधील मंत्र्यांनी दिले संकेत</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/heavy-raincm-devendra-fadnavis-agencies-alert-heavy-rain-state/</t>
+          <t>https://marathi.oneindia.com/maharashtra/maharashtra-cm-fadnavis-loan-waiver-announcement-035127.html</t>
         </is>
       </c>
     </row>
@@ -2375,24 +2375,24 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>शेतकरी कर्जमाफीबाबत महायुतीमधील मंत्र्याने दिली महत्त्वाची माहिती; “देवेंद्र फडणवीस लवकरच….”</t>
+          <t>Heavy Rain: राज्यात अतिवृष्टीच्या पार्श्वभूमीवर मुख्यमंत्री देवेंद्र फडणवीस यांचे सर्व यंत्रणांना सतर्कतेचे</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/mahayuti-minister-gives-important-information-regarding-farmer-loan-waiver-devendra-fadnavis-soon/</t>
+          <t>https://deshonnati.com/heavy-raincm-devendra-fadnavis-agencies-alert-heavy-rain-state/</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>लवकरच कर्जमाफीची घोषणा होणार? महायुती सरकारमधील मंत्र्यांनी दिले संकेत</t>
+          <t>Devendra Fadnavis : महाराष्ट्रातील माणसाला सर्वांनी समर्थन द्यावे; मुख्यमंत्री फडणवीस यांचे मविआच्या खासदारांना आवाहन</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>https://marathi.oneindia.com/maharashtra/maharashtra-cm-fadnavis-loan-waiver-announcement-035127.html</t>
+          <t>https://www.dainikprabhat.com/devendra-fadnavis-everyone-should-support-the-people-of-maharashtra-chief-minister-fadnavis-appeals-to-m-v-a-mps/</t>
         </is>
       </c>
     </row>
@@ -2411,24 +2411,24 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>महाराष्ट्रातील शेतकऱ्यांना मोठा दिलासा, मुख्यमंत्री फडणवीस लवकरच कर्जमाफीची घोषणा करणार</t>
+          <t>शेतकरी कर्जमाफीबाबत महायुतीमधील मंत्र्याने दिली महत्त्वाची माहिती; “देवेंद्र फडणवीस लवकरच….”</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/big-relief-for-farmers-in-maharashtra-chief-minister-fadnavis-will-soon-announce-loan-waiver-125081900014_1.html</t>
+          <t>https://www.dainikprabhat.com/mahayuti-minister-gives-important-information-regarding-farmer-loan-waiver-devendra-fadnavis-soon/</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis : महाराष्ट्रातील माणसाला सर्वांनी समर्थन द्यावे; मुख्यमंत्री फडणवीस यांचे मविआच्या खासदारांना आवाहन</t>
+          <t>महाराष्ट्रातील शेतकऱ्यांना मोठा दिलासा, मुख्यमंत्री फडणवीस लवकरच कर्जमाफीची घोषणा करणार</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/devendra-fadnavis-everyone-should-support-the-people-of-maharashtra-chief-minister-fadnavis-appeals-to-m-v-a-mps/</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/big-relief-for-farmers-in-maharashtra-chief-minister-fadnavis-will-soon-announce-loan-waiver-125081900014_1.html</t>
         </is>
       </c>
     </row>
@@ -2519,24 +2519,24 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Mumbai Rain Update : समुद्रातून येतंय मुंबईवर मोठं संकट, पुढच्या 12 तासांत तुफान पाऊस, फडणवीस काय...</t>
+          <t>Pune News : मुख्यमंत्री फडणवीसांमुळे पुणेकरांना रोज मनस्ताप? काँग्रेसचा गंभीर आरोप</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/mumbai-rain-alert-cm-devendra-fadnavis-said-mumbai-have-red-alert-school-holiday-declared-know-detail-information-in-marathi-1472488.html</t>
+          <t>https://sarkarnama.esakal.com/pune/devendra-fadnavis-pune-flyover-inauguration-delay-dk88-sm89</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Pune News : मुख्यमंत्री फडणवीसांमुळे पुणेकरांना रोज मनस्ताप? काँग्रेसचा गंभीर आरोप</t>
+          <t>Devendra Fadanvis on Rain Update : मुंबईला रेड अलर्ट ! मुख्यमंत्री देवेंद्र फडणवीस यांनी पावसाबद्दल दिली महत्त्वाची अपडेट</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/pune/devendra-fadnavis-pune-flyover-inauguration-delay-dk88-sm89</t>
+          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/maharashtra-hevey-rain-update-cm-devendra-fadanvis-gives-important-information-know-about-more-/40070</t>
         </is>
       </c>
     </row>
@@ -2555,96 +2555,96 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Devendra Fadanvis on Rain Update : मुंबईला रेड अलर्ट ! मुख्यमंत्री देवेंद्र फडणवीस यांनी पावसाबद्दल दिली महत्त्वाची अपडेट</t>
+          <t>Third Mumbai News: तिसरी मुंबई आणि आर्थिक विकासाबाबत CM फडणवीसांचे मोठे विधान</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/maharashtra-hevey-rain-update-cm-devendra-fadanvis-gives-important-information-know-about-more-/40070</t>
+          <t>https://marathi.ndtv.com/maharashtra/third-mumbai-will-open-a-new-chapter-of-economic-development-says-cm-devendra-fadnavis-9110192</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Third Mumbai News: तिसरी मुंबई आणि आर्थिक विकासाबाबत CM फडणवीसांचे मोठे विधान</t>
+          <t>Maharashtra Rain : राज्यासाठी पुढचे दोन दिवस चिंतेचे, 15-16 जिल्ह्यांना अलर्ट, कुठे होणार अतिवृष्टी?...</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/third-mumbai-will-open-a-new-chapter-of-economic-development-says-cm-devendra-fadnavis-9110192</t>
+          <t>https://www.tv9marathi.com/videos/maharashtra-imd-issues-red-alert-for-16-districts-big-information-by-cm-devendra-fadnavis-reviews-heavy-rains-in-1472606.html</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>पुण्यात नवीन महापालिकांवरून देवेंद्र फडणवीस आणि अजित पवार यांच्यात मतभेद का?</t>
+          <t>Mumbai Rains Updates: मुंबईकरांनो पुढील 12 तास अतिशय महत्त्वाचे, CM फडणवीसांनी केले हे आवाहन</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/devendra-fadnavis-ajit-pawar-dispute-over-new-municipal-corporations-in-pune-district-print-politics-news-css-98-5314697/</t>
+          <t>https://marathi.ndtv.com/maharashtra/mumbai-rains-update-next-12-hours-are-important-for-mumbai-7-people-died-across-state-in-2-days-cm-fadnavis-appeals-to-citizens-9109288</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Cji Bhushan Gavai : सरन्यायाधीशांनी केले शिवेंद्रसिंहराजेंचे जाहीरपणे कौतुक; म्हणाले, ‘गिनिज बुकमध्ये नोंद करण्यासारखे काम...’</t>
+          <t>पुण्यात नवीन महापालिकांवरून देवेंद्र फडणवीस आणि अजित पवार यांच्यात मतभेद का?</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chief-justice-bhushan-gavai-praised-shivendrasinghraje-bhosale-vd83</t>
+          <t>https://www.loksatta.com/politics/devendra-fadnavis-ajit-pawar-dispute-over-new-municipal-corporations-in-pune-district-print-politics-news-css-98-5314697/</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Maharashtra Rain : राज्यासाठी पुढचे दोन दिवस चिंतेचे, 15-16 जिल्ह्यांना अलर्ट, कुठे होणार अतिवृष्टी?...</t>
+          <t>16 जिल्ह्यांना रेड अलर्ट! राज्याच्या ‘या’ भागात अतिवृष्टी, बचाव पथक सज्ज; CM फडणवीसांची...</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/maharashtra-imd-issues-red-alert-for-16-districts-big-information-by-cm-devendra-fadnavis-reviews-heavy-rains-in-1472606.html</t>
+          <t>https://www.tv9marathi.com/maharashtra/rain-alert-in-16-districts-heavy-rainfall-in-this-part-of-state-cm-fadnavis-give-information-1472499.html</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Mumbai Rains Updates: मुंबईकरांनो पुढील 12 तास अतिशय महत्त्वाचे, CM फडणवीसांनी केले हे आवाहन</t>
+          <t>Cji Bhushan Gavai : सरन्यायाधीशांनी केले शिवेंद्रसिंहराजेंचे जाहीरपणे कौतुक; म्हणाले, ‘गिनिज बुकमध्ये नोंद करण्यासारखे काम...’</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/mumbai-rains-update-next-12-hours-are-important-for-mumbai-7-people-died-across-state-in-2-days-cm-fadnavis-appeals-to-citizens-9109288</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chief-justice-bhushan-gavai-praised-shivendrasinghraje-bhosale-vd83</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Maharashtra Politics : एकनाथ शिंदेंची कोण करतंय कोंडी? दिल्ली दौरे वाढण्यामागचं काय कारण?</t>
+          <t>मुख्यमंत्री देवेंद्र फडणवीसांकडून पावसाचा आढावा: महाराष्ट्रात 4 लाख हेक्टरवरील पिके पाण्यात, उपाययोजनांचे ज...</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/maharashtra-politics-shiv-sena-eknath-shinde-bjp-devendra-fadnavis-conflict-before-bmc-election-sdp-92-5314661/lite/</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/cm-devendra-fadnavis-review-maharashtra-flood-135703334.html</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>16 जिल्ह्यांना रेड अलर्ट! राज्याच्या ‘या’ भागात अतिवृष्टी, बचाव पथक सज्ज; CM फडणवीसांची...</t>
+          <t>Maharashtra Politics : एकनाथ शिंदेंची कोण करतंय कोंडी? दिल्ली दौरे वाढण्यामागचं काय कारण?</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/rain-alert-in-16-districts-heavy-rainfall-in-this-part-of-state-cm-fadnavis-give-information-1472499.html</t>
+          <t>https://www.loksatta.com/politics/maharashtra-politics-shiv-sena-eknath-shinde-bjp-devendra-fadnavis-conflict-before-bmc-election-sdp-92-5314661/lite/</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>मुख्यमंत्री देवेंद्र फडणवीसांकडून पावसाचा आढावा: महाराष्ट्रात 4 लाख हेक्टरवरील पिके पाण्यात, उपाययोजनांचे ज...</t>
+          <t>तिसरी मुंबई आर्थिक विकासाचा नवा अध्याय – मुख्यमंत्री देवेंद्र फडणवीस</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/cm-devendra-fadnavis-review-maharashtra-flood-135703334.html</t>
+          <t>https://mahasamvad.in/176127/</t>
         </is>
       </c>
     </row>
@@ -2687,48 +2687,48 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>तिसरी मुंबई आर्थिक विकासाचा नवा अध्याय – मुख्यमंत्री देवेंद्र फडणवीस</t>
+          <t>Maharashtra Heavy Rainfall | राज्यभरात अतिवृष्टीचा कहर; १५ जिल्ह्यांत रेड आणि ऑरेंज अलर्ट, नागरिकांनी घराबाहेर पडू नये: मुख्यमंत्री फडणवीस</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176127/</t>
+          <t>https://pudhari.news/maharashtra/mumbai/maharashtra-heavy-rainfall-red-orange-alert-15-districts-cm-fadnavis-advisory-as80</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Maharashtra Heavy Rainfall | राज्यभरात अतिवृष्टीचा कहर; १५ जिल्ह्यांत रेड आणि ऑरेंज अलर्ट, नागरिकांनी घराबाहेर पडू नये: मुख्यमंत्री फडणवीस</t>
+          <t>महाराष्ट्रातील खासदारांनी राधाकृष्णन यांना समर्थन द्यावे: मुख्यमंत्री देवेंद्र फडणवीसांचे आवाहन; ठाकरे गट अ...</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/maharashtra-heavy-rainfall-red-orange-alert-15-districts-cm-fadnavis-advisory-as80</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/c-p-radhakrishnan-vice-president-candidate-fadnavis-urges-support-135703533.html</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Mumbai Rains News: मुंबईसह महाराष्ट्रात 3 जिल्ह्यात शाळा-कॉलेज बंद, पावसाने सामान्यांचे झाले हाल; तलाव भरले</t>
+          <t>पूरस्थितीचा सामना करण्यासाठी सरकारकडून सर्वतोपरी प्रयत्न, अतिवृष्टीचा धोका लक्षात घेऊन लोकांनी खबरदारी घ्यावी, मुख्यमंत्र्यांचं आवाहन</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/mumbai-rains-news-updates-school-college-closed-due-to-heavy-rains-thane-palghar-has-problem-963739.html</t>
+          <t>https://www.etvbharat.com/mr/!state/maharashtra-government-is-making-every-effort-to-deal-with-the-flood-situation-the-chief-minister-appeals-to-people-to-be-careful-considering-the-risk-of-heavy-rains-maharashtra-news-mhs25081804221</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>महाराष्ट्रातील खासदारांनी राधाकृष्णन यांना समर्थन द्यावे: मुख्यमंत्री देवेंद्र फडणवीसांचे आवाहन; ठाकरे गट अ...</t>
+          <t>Marathwada Rain : मराठवाड्यात शेतीचे सर्वाधिक नुकसान, 800 गावं जलबाधित; नांदेडमध्ये ढगफुटी, 5 जणांचा मृत्यू</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/c-p-radhakrishnan-vice-president-candidate-fadnavis-urges-support-135703533.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/cloudburst-rain-in-mukhed-nanded-district-five-people-missing-chief-minister-devendra-fadnavis-gave-information/913157/</t>
         </is>
       </c>
     </row>
@@ -2747,3096 +2747,3096 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Marathwada Rain : मराठवाड्यात शेतीचे सर्वाधिक नुकसान; नांदेडमध्ये ढगफुटी सदृष्य पाऊस, पाच जण बेपत्ता</t>
+          <t>Nanded Breaking : मोठी बातमी! नांदेडमध्ये अनेक गाव पाण्याखाली, 15 जण अडकले तर 40 ते 50 म्हशीचा पाण्यात बुडून मृत्यू</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/cloudburst-rain-in-mukhed-nanded-district-five-people-missing-chief-minister-devendra-fadnavis-gave-information/913157/</t>
+          <t>https://www.lokshahi.com/news/rains-in-nandeds-mukhed-taluka-have-caused-flash-floods-in-many-villages-and-information-has-emerged-that-15-people-from-the-village-are-stranded</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>पूरस्थितीचा सामना करण्यासाठी सरकारकडून सर्वतोपरी प्रयत्न, अतिवृष्टीचा धोका लक्षात घेऊन लोकांनी खबरदारी घ्यावी, मुख्यमंत्र्यांचं आवाहन</t>
+          <t>Maharashtra Politics Live Updates : जगनमोहन रेड्डींच्या पक्षाचा सीपी राधाकृष्णन यांना जाहीर पाठिंबा</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/maharashtra-government-is-making-every-effort-to-deal-with-the-flood-situation-the-chief-minister-appeals-to-people-to-be-careful-considering-the-risk-of-heavy-rains-maharashtra-news-mhs25081804221</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-18-august-2025-latest-marathi-political-news-eknath-shinde-mumbai-mahayuti-rahul-gandhi-congress-india-aghadi-election-commission-devendra-fadnavis-uddhav-thackeray-india-alliance-mumbai-pune-ajit-pawar-ncp-local-elections-rahul-gandhi-vote-adhikar-yatra-nda-cp-radhakrishnan-vice-presidential-candidat</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Nanded Breaking : मोठी बातमी! नांदेडमध्ये अनेक गाव पाण्याखाली, 15 जण अडकले तर 40 ते 50 म्हशीचा पाण्यात बुडून मृत्यू</t>
+          <t>CM Devendra Fadnavis: मुख्यमंत्र्यांनी राज्यातील पावसाचा घेतला आढावा; 'इतक्या' जिल्ह्यांना पावसाचा रेड अलर्ट, सतर्क राहण्याचे केले आवाहन</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>https://www.lokshahi.com/news/rains-in-nandeds-mukhed-taluka-have-caused-flash-floods-in-many-villages-and-information-has-emerged-that-15-people-from-the-village-are-stranded</t>
+          <t>https://deshdoot.com/cm-fadnavis-takes-reiew-situation-ndrf-and-army-deployed-16-districts-on-red-alert/</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Solapur News : शिंदेंच्या सेनेत राज्यातून ‘इन्कमिंग’ पण सोलापुरात गळती, तानाजी सावंतांच्या बंधूंचा भाजप प्रवेश ठरला</t>
+          <t>CM Devendra Fadnavis: राज्यातील चार लाख हेक्टर क्षेत्रावरील पिकांना फटका; पिकांचे पंचनामे करण्याचे आदेश</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/tanaji-sawant-brother-shivajirao-sawant-resign-eknath-shinde-sena-join-bjp-after-meet-fadnavis/913179/</t>
+          <t>https://deshdoot.com/crops-affected-on-four-lakh-hectares-of-land-in-the-state-orders-to-conduct-crop-surveys/</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Maharashtra Politics Live Updates : जगनमोहन रेड्डींच्या पक्षाचा सीपी राधाकृष्णन यांना जाहीर पाठिंबा</t>
+          <t>Solapur News : शिंदेंच्या सेनेत राज्यातून ‘इन्कमिंग’ पण सोलापुरात गळती, तानाजी सावंतांच्या बंधूंचा भाजप प्रवेश ठरला</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-18-august-2025-latest-marathi-political-news-eknath-shinde-mumbai-mahayuti-rahul-gandhi-congress-india-aghadi-election-commission-devendra-fadnavis-uddhav-thackeray-india-alliance-mumbai-pune-ajit-pawar-ncp-local-elections-rahul-gandhi-vote-adhikar-yatra-nda-cp-radhakrishnan-vice-presidential-candidat</t>
+          <t>https://www.mymahanagar.com/maharashtra/tanaji-sawant-brother-shivajirao-sawant-resign-eknath-shinde-sena-join-bjp-after-meet-fadnavis/913179/</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>लातूर जिल्ह्यात मुसळधार पाऊस; लेंडी नदीला पूर आल्यानं तेलंगाणातील चार प्रवासी गेले वाहून; मुख्यमंत्र्यांनी घेतला आढावा</t>
+          <t>Shivaji Sawant : तानाजी सावंतांचे बंधू शिवाजी सावंतांचा भाजप प्रवेश निश्चित; मुख्यमंत्र्यांच्या भेटीनंतर जाहीर केला निर्णय</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/heavy-rains-in-latur-district-cause-flooding-in-many-rivers-cm-devendra-fadnavis-took-a-review-lendi-river-flood-maharashtra-news-mhs25081802447</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/shivaji-sawants-entry-into-bjp-confirmed-decision-announced-after-meeting-with-chief-minister-vd83</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>CM Devendra Fadnavis: राज्यातील चार लाख हेक्टर क्षेत्रावरील पिकांना फटका; पिकांचे पंचनामे करण्याचे आदेश</t>
+          <t>मोदींचा निर्णय, उमेदवार ठरला अन् अडचणीत उद्धवसेना; 18 वर्षांनी पुन्हा तेच, ठाकरेंसमोर पेच?</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/crops-affected-on-four-lakh-hectares-of-land-in-the-state-orders-to-conduct-crop-surveys/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-picks-cp-radhakrishnan-for-vice-president-post-cm-devendra-fadnavis-ask-uddhav-thackeray-for-support/articleshow/123362737.cms</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>CM Devendra Fadnavis: मुख्यमंत्र्यांनी राज्यातील पावसाचा घेतला आढावा; 'इतक्या' जिल्ह्यांना पावसाचा रेड अलर्ट, सतर्क राहण्याचे केले आवाहन</t>
+          <t>Maharashtra Rain Update : शाळांना सुट्टी आहे की नाही? नेमका निर्णय काय? फडणवीसांनीच संभ्रम संपवला;...</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/cm-fadnavis-takes-reiew-situation-ndrf-and-army-deployed-16-districts-on-red-alert/</t>
+          <t>https://www.tv9marathi.com/photo-gallery/maharashtra-rain-update-mumbai-rain-school-and-college-holiday-decision-will-be-taken-after-weather-forecast-1472649.html</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Shivaji Sawant : तानाजी सावंतांचे बंधू शिवाजी सावंतांचा भाजप प्रवेश निश्चित; मुख्यमंत्र्यांच्या भेटीनंतर जाहीर केला निर्णय</t>
+          <t>Mukhed cloudburst: मुखेडमध्ये ढगफुटी! 800 गावांना फटका, 226 लोकांची सुटका, 4 गावातले लोक फसले, सैन्याला पाचारण</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/shivaji-sawants-entry-into-bjp-confirmed-decision-announced-after-meeting-with-chief-minister-vd83</t>
+          <t>https://marathi.ndtv.com/maharashtra/rain-big-news-mukhed-cloudburst-nanded-rain-news-calling-out-the-army-maharashtra-rain-alert-9107388</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>मोदींचा निर्णय, उमेदवार ठरला अन् अडचणीत उद्धवसेना; 18 वर्षांनी पुन्हा तेच, ठाकरेंसमोर पेच?</t>
+          <t>राजधानीत पावसाचा कहर! मुंबई विद्यापीठाचा परीक्षांबाबत तडकाफडकी मोठा निर्णय!</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-picks-cp-radhakrishnan-for-vice-president-post-cm-devendra-fadnavis-ask-uddhav-thackeray-for-support/articleshow/123362737.cms</t>
+          <t>https://www.tv9marathi.com/maharashtra/mumbai-university-postponed-its-all-exam-to-be-held-on-19-august-due-to-heavy-rain-marathi-news-1472932.html/amp</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>महायुतीच्या 'या' मंत्र्यावर 5 हजार कोटींच्या भ्रष्टाचाराचा आरोप; रोहित पवारांची मुख्यमंत्री फडणवीसांकडे राजीनाम्याची मागणी</t>
+          <t>अन्वयार्थ : राजकीयीकरणाचा उत्सवी अधर्म</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>https://puneprimenews.com/mumbai/this-minister-of-mahayuti-accused-of-corruption-worth-rs-5000-crores-rohit-pawar-demands-resignation-from-chief-minister-fadnavis/</t>
+          <t>https://www.loksatta.com/sampadkiya/columns/dahi-handi-2025-political-grip-on-dahi-handi-festival-10-thar-human-pyramid-25-lakh-cash-prize-zws-70-5314039/</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Maharashtra Rain Update : शाळांना सुट्टी आहे की नाही? नेमका निर्णय काय? फडणवीसांनीच संभ्रम संपवला;...</t>
+          <t>Mumbai Rains News: मुंबईसह महाराष्ट्रात 3 जिल्ह्यात शाळा-कॉलेज बंद, पावसाने सामान्यांचे झाले हाल; तलाव भरले</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/photo-gallery/maharashtra-rain-update-mumbai-rain-school-and-college-holiday-decision-will-be-taken-after-weather-forecast-1472649.html</t>
+          <t>https://www.navarashtra.com/maharashtra/mumbai-rains-news-updates-school-college-closed-due-to-heavy-rains-thane-palghar-has-problem-963739.html</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Mukhed cloudburst: मुखेडमध्ये ढगफुटी! 800 गावांना फटका, 226 लोकांची सुटका, 4 गावातले लोक फसले, सैन्याला पाचारण</t>
+          <t>लातूर जिल्ह्यात मुसळधार पाऊस; लेंडी नदीला पूर आल्यानं तेलंगाणातील चार प्रवासी गेले वाहून; मुख्यमंत्र्यांनी घेतला आढावा</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/rain-big-news-mukhed-cloudburst-nanded-rain-news-calling-out-the-army-maharashtra-rain-alert-9107388</t>
+          <t>https://www.etvbharat.com/mr/!state/heavy-rains-in-latur-district-cause-flooding-in-many-rivers-cm-devendra-fadnavis-took-a-review-lendi-river-flood-maharashtra-news-mhs25081802447</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>राजधानीत पावसाचा कहर! मुंबई विद्यापीठाचा परीक्षांबाबत तडकाफडकी मोठा निर्णय!</t>
+          <t>मराठ्यांच्या इतिहासाचं सोनेरी पान उलगडलं, मुख्यमंत्र्यांच्या हस्ते सरदार रघुजी राजे भोसले यांच्या ऐतिहासिक तलवारीचं लोकार्पण</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/mumbai-university-postponed-its-all-exam-to-be-held-on-19-august-due-to-heavy-rain-marathi-news-1472932.html</t>
+          <t>https://www.etvbharat.com/mr/!state/unveiling-the-historic-sword-of-sardar-raghuji-raje-bhosale-in-mumbai-presence-of-chief-minister-devendra-fadnavis-know-history-of-raghuji-raje-sword-maharashtra-news-mhs25081900619</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Sambhajinagar News : आता शहरवासीयांना मिळणार अतिरिक्त २६ एमएलडी पाणी</t>
+          <t>Rain Update : मराठवाड्यात मृत्यूचं तांडव, तुफान पावसाने सगळं उद्ध्वस्त; मदतीसाठी थेट मिलिटरी दाखल!</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/marathwada/chhatrapati-sambhajinagar/now-city-residents-will-get-additional-26-mld-of-water-np88</t>
+          <t>https://www.tv9marathi.com/maharashtra/maharashtra-rain-update-marathwada-all-district-affected-by-heavy-rain-total-6-people-died-marathi-news-1472571.html</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>अन्वयार्थ : राजकीयीकरणाचा उत्सवी अधर्म</t>
+          <t>Jalgaon mob lynching Case: जामनेर मॉब लिंचिंग: युवकाच्या हत्येत मंत्री गिरीश महाजनांच्या ड्रायव्हरचा मुलगा मास्टर माईंड?</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/sampadkiya/columns/dahi-handi-2025-political-grip-on-dahi-handi-festival-10-thar-human-pyramid-25-lakh-cash-prize-zws-70-5314039/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/maharashtra-news-jalgaon-jamner-mob-lynching-girish-mahajan-driver-son-mastermind-youth-killed-mm76-sd67</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>मराठ्यांच्या इतिहासाचं सोनेरी पान उलगडलं, मुख्यमंत्र्यांच्या हस्ते सरदार रघुजी राजे भोसले यांच्या ऐतिहासिक तलवारीचं लोकार्पण</t>
+          <t>'उपराष्ट्रपती'साठी महाराष्ट्राच्या राज्यपालांचे नाव; फडणवीसांचे खासदारांना आवाहन, पवार-ठाकरेंना टोला</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/unveiling-the-historic-sword-of-sardar-raghuji-raje-bhosale-in-mumbai-presence-of-chief-minister-devendra-fadnavis-know-history-of-raghuji-raje-sword-maharashtra-news-mhs25081900619</t>
+          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-urges-mps-to-support-radhakrishnan-targets-uddhav-thackeray-and-sharad-pawar-035137.html</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Rain Update : मराठवाड्यात मृत्यूचं तांडव, तुफान पावसाने सगळं उद्ध्वस्त; मदतीसाठी थेट मिलिटरी दाखल!</t>
+          <t>नांदेडमध्ये मुसळधार पावसाने हाहाकार,मुख्यमंत्री फडणवीस यांच्या देखरेखीखाली मदतकार्य तीव्र</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/maharashtra-rain-update-marathwada-all-district-affected-by-heavy-rain-total-6-people-died-marathi-news-1472571.html</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/heavy-rains-wreak-havoc-in-nanded-relief-work-intensified-under-the-supervision-of-chief-minister-fadnavis-125081800046_1.html</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Jalgaon mob lynching Case: जामनेर मॉब लिंचिंग: युवकाच्या हत्येत मंत्री गिरीश महाजनांच्या ड्रायव्हरचा मुलगा मास्टर माईंड?</t>
+          <t>महाराष्ट्रात सर्वदूर पावसामुळे हाहाकार; मोठ्या प्रमाणात जीवित आणि वित्तहानी, बळीराज अडचणीत!</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/maharashtra-news-jalgaon-jamner-mob-lynching-girish-mahajan-driver-son-mastermind-youth-killed-mm76-sd67</t>
+          <t>https://mpbreakingnews.in/marathi/maharashtra/rains-wreak-havoc-across-maharashtra-massive-loss-of-life-and-property-farmers-in-trouble-06-692619</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>'उपराष्ट्रपती'साठी महाराष्ट्राच्या राज्यपालांचे नाव; फडणवीसांचे खासदारांना आवाहन, पवार-ठाकरेंना टोला</t>
+          <t>युवकांसाठी मोठी खुशखबर; ‘या’ ठिकाणी आयटी पार्क उभारणार; मुख्यमंत्र्यांची घोषणा</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-urges-mps-to-support-radhakrishnan-targets-uddhav-thackeray-and-sharad-pawar-035137.html?ref_source=OI-MR&amp;ref_medium=Home-Page&amp;ref_campaign=News-Cards</t>
+          <t>https://www.nagpurtoday.in/great-news-for-youth-it-park-will-be-set-up-at-this-place-chief-ministers-announcement/08181712</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>नांदेडमध्ये मुसळधार पावसाने हाहाकार,मुख्यमंत्री फडणवीस यांच्या देखरेखीखाली मदतकार्य तीव्र</t>
+          <t>10 रुपयांत ‘शिवभोजन थाळी’ योजना थांबणार? शिवभोजन केंद्र चालकांची कोट्यवधींची बिलं थकली</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/heavy-rains-wreak-havoc-in-nanded-relief-work-intensified-under-the-supervision-of-chief-minister-fadnavis-125081800046_1.html</t>
+          <t>https://mpbreakingnews.in/marathi/maharashtra/will-the-shiv-bhojan-thali-scheme-for-10-rupees-stop-shiv-bhojan-center-operators-are-facing-bills-worth-crores-02-692694</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>महाराष्ट्रात सर्वदूर पावसामुळे हाहाकार; मोठ्या प्रमाणात जीवित आणि वित्तहानी, बळीराज अडचणीत!</t>
+          <t>नागपूरच्या राजे रघुजी भोसलेंची तलवार लंडनमधून मुंबईत, इतिहासाशी नवीन पिढीला जोडण्याचं कामं, मुख्यमंत्र्यांकडून कौतुक</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/marathi/maharashtra/rains-wreak-havoc-across-maharashtra-massive-loss-of-life-and-property-farmers-in-trouble-06-692619</t>
+          <t>https://mpbreakingnews.in/marathi/maharashtra/nagpurs-raja-raghuji-bhosales-sword-arrives-in-mumbai-from-london-02-692697</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>भाजपला स्थानिक ची निवडणूक महायुती म्हणूनच का लढवायची आहे?</t>
+          <t>Shinde and BJP: The saga continues</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>https://aaplaawajnews.com/2025/34070/</t>
+          <t>https://www.msn.com/en-in/news/India/shinde-and-bjp-the-saga-continues/ar-AA1KHn3K</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>युवकांसाठी मोठी खुशखबर; ‘या’ ठिकाणी आयटी पार्क उभारणार; मुख्यमंत्र्यांची घोषणा</t>
+          <t>Heavy rainfall causes 7 deaths, crop loss in Maharashtra as alerts continue</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/great-news-for-youth-it-park-will-be-set-up-at-this-place-chief-ministers-announcement/08181712</t>
+          <t>https://www.msn.com/en-in/news/India/heavy-rainfall-causes-7-deaths-crop-loss-in-maharashtra-as-alerts-continue/ar-AA1KK6Zt</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>10 रुपयांत ‘शिवभोजन थाळी’ योजना थांबणार? शिवभोजन केंद्र चालकांची कोट्यवधींची बिलं थकली</t>
+          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by Maharashtra CM Devendra Fadnavis</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/marathi/maharashtra/will-the-shiv-bhojan-thali-scheme-for-10-rupees-stop-shiv-bhojan-center-operators-are-facing-bills-worth-crores-02-692694</t>
+          <t>https://www.aninews.in/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>MONSOON UPDATE: १५ ते १६ जिल्ह्यांत रेड आणि ऑरेंज अलर्ट; CM DEVENDRA FADNAVIS म्हणाले…</t>
+          <t>Nanded rains latest UPDATES: Water from Karnataka reach district; Indian Army, SDRF deployed for rescue missions as villagers trapped</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/monsoon-update-red-and-orange-alert-in-15-to-16-districts-cm-devendra-fadnavis-said/129346/</t>
+          <t>https://www.theweek.in/news/india/2025/08/18/mumbai-rain-news-nanded-rains-latest-updates-water-from-karnataka-reach-district-indian-army-sdrf-deployed-for-rescue-missions-and-villagers-trapped.html</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>नागपूरच्या राजे रघुजी भोसलेंची तलवार लंडनमधून मुंबईत, इतिहासाशी नवीन पिढीला जोडण्याचं कामं, मुख्यमंत्र्यांकडून कौतुक</t>
+          <t>Sword of Raghuji Bhonsle arrives in Mumbai and will be on display till Aug 25</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/marathi/maharashtra/nagpurs-raja-raghuji-bhosales-sword-arrives-in-mumbai-from-london-02-692697</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/sword-of-raghuji-bhonsle-arrives-in-mumbai-and-will-be-on-display-till-aug-25/articleshow/123371745.cms</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Those who speak of Maharashtra 'asmita' should support Radhakrishnan for VP post Fadnavis</t>
+          <t>Mumbai rain highlights: BMC declares holiday for schools, colleges today amid heavy rain forecast</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom25-mh-governor-ld-fadnavis.html</t>
+          <t>https://www.hindustantimes.com/india-news/mumbai-rain-live-updates-red-alert-school-closed-heavy-rains-august-18-weather-waterlogging-borivali-thane-powai-bmc-101755498397210.html</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Nanded rains latest UPDATES: Water from Karnataka reach district; Indian Army, SDRF deployed for rescue missions as villagers trapped</t>
+          <t>Monsoon mayhem: Heavy rains flood this state, schools and colleges shut</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/news/india/2025/08/18/mumbai-rain-news-nanded-rains-latest-updates-water-from-karnataka-reach-district-indian-army-sdrf-deployed-for-rescue-missions-and-villagers-trapped.html</t>
+          <t>https://www.patrika.com/en/national-news/monsoon-mayhem-heavy-rains-flood-this-state-schools-and-colleges-shut-19874810</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Sword of Raghuji Bhonsle arrives in Mumbai and will be on display till Aug 25</t>
+          <t>मुंबईतील सर्व शासकीय आणि निमशासकीय कार्यालयांना आज सुट्टी जाहीर!</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/sword-of-raghuji-bhonsle-arrives-in-mumbai-and-will-be-on-display-till-aug-25/articleshow/123371745.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/19/mumbai-rains-govt-declares-holiday-for-all-government-and-private-offices-amid-heavy-rainfall.html</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Mumbai rain highlights: BMC declares holiday for schools, colleges today amid heavy rain forecast</t>
+          <t>Thane Rain: ठाणे जिल्ह्यात झोडपणी; ठाणे, कल्याण, डोंबिवलीतील सखल भाग जलमय, आज शाळांना सुट्टी</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/mumbai-rain-live-updates-red-alert-school-closed-heavy-rains-august-18-weather-waterlogging-borivali-thane-powai-bmc-101755498397210.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/thane/waterlogging-in-thane-kalyan-dombivali-schools-closed-today-19-august/articleshow/123374806.cms</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Mumbai rains HIGHLIGHTS: Civic body declares holiday for all schools on August 19</t>
+          <t>Mumbai Rain Alert:मुंबईत पावसाची धुवाँधार बॅटिंग;शाळांना सुट्टी जाहीर</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/live-news-updates-mumbai-rain-waterlogging-traffic-heavy-rain-orange-alert-125081800291_1.html</t>
+          <t>https://ilovenagar.com/mumbai-rain-alert-schools-declare-holiday-today/</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Monsoon mayhem: Heavy rains flood this state, schools and colleges shut</t>
+          <t>SUPER 100 : राष्ट्रपति ट्रंप की जेलेंस्की और यूरोपीय नेताओं की साथ बैठक में अमेरिका, रूस और यूक्रेन के बीच त्रिपक्षीय वार्ता पर बनी सहमति...</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/en/national-news/monsoon-mayhem-heavy-rains-flood-this-state-schools-and-colleges-shut-19874810</t>
+          <t>https://www.indiatv.in/video/news-bulletin/super-100-in-the-meeting-of-president-trump-with-zelensky-and-european-leaders-an-agreement-was-reached-on-trilateral-talks-between-america-russia-2025-08-19-1156864</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>मुंबईतील सर्व शासकीय आणि निमशासकीय कार्यालयांना आज सुट्टी जाहीर!</t>
+          <t>मुंबई में आज शाम हाई टाइड, लोगों से सावधानी की अपील, भारी बारिश का लोकल ट्रेनों</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/19/mumbai-rains-govt-declares-holiday-for-all-government-and-private-offices-amid-heavy-rainfall.html</t>
+          <t>https://www.abplive.com/photo-gallery/states/maharashtra-mumbai-heavy-rainfall-waterlogging-imd-red-alert-local-train-delayed-photos-maharashtra-news-2997487</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Ashish Shelar : मुंबईत मुसळधार.. परिस्थितीचा आढावा घेतल्यानंतर शेलारांकडून मुंबईकरांना एकच आवाहन; आज,...</t>
+          <t>समाचार संध्या</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/ashish-shelar-appeals-to-mumbaikars-after-review-of-rains-at-bmc-stay-at-house-during-mumbai-heavy-rains-1472440.html</t>
+          <t>https://www.newsonair.gov.in/bulletins-detail/%E0%A4%B8%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%BE%E0%A4%B0-%E0%A4%B8%E0%A4%82%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%BE-508/</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Thane Rain: ठाणे जिल्ह्यात झोडपणी; ठाणे, कल्याण, डोंबिवलीतील सखल भाग जलमय, आज शाळांना सुट्टी</t>
+          <t>नवीन पिढीला इतिहासाशी जोडण्याचे कार्य सुरू – मुख्यमंत्री देवेंद्र फडणवीस</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/thane/waterlogging-in-thane-kalyan-dombivali-schools-closed-today-19-august/articleshow/123374806.cms</t>
+          <t>https://mahasamvad.in/176229/</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Mumbai Rain Alert:मुंबईत पावसाची धुवाँधार बॅटिंग;शाळांना सुट्टी जाहीर</t>
+          <t>Aaj Ki Baat: Mumbai में बारिश का Red Alert...48 घंटे संभलकर</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>https://ilovenagar.com/mumbai-rain-alert-schools-declare-holiday-today/</t>
+          <t>https://www.indiatv.in/video/aaj-ki-baat/aaj-ki-baat-red-alert-for-rain-in-mumbai-be-careful-for-48-hours-2025-08-19-1156835</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>SUPER 100 : राष्ट्रपति ट्रंप की जेलेंस्की और यूरोपीय नेताओं की साथ बैठक में अमेरिका, रूस और यूक्रेन के बीच त्रिपक्षीय वार्ता पर बनी सहमति...</t>
+          <t>CM Devendra Fadnavis यांच्या हस्ते अद्ययावत पोलीस सदनिकेचे उद्घाटन</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/news-bulletin/super-100-in-the-meeting-of-president-trump-with-zelensky-and-european-leaders-an-agreement-was-reached-on-trilateral-talks-between-america-russia-2025-08-19-1156864</t>
+          <t>https://www.tarunbharat.com/cm-devendra-fadnavis-inauguration-of-new-police-building-kolhapur-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>मुंबई में आज शाम हाई टाइड, लोगों से सावधानी की अपील, भारी बारिश का लोकल ट्रेनों</t>
+          <t>मुंबईत सर्व शासकीय-निमशासकीय कार्यालयांना सुट्टी जाहीर, फॉर्सबेरी जलाशयाजवळ चार तासात 109 मिमी पावसाची नोंद</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/photo-gallery/states/maharashtra-mumbai-heavy-rainfall-waterlogging-imd-red-alert-local-train-delayed-photos-maharashtra-news-2997487</t>
+          <t>https://www.etvbharat.com/mr/!state/mumbai-rain-news-all-government-semi-government-offices-in-mumbai-remain-closed-today-mumbai-local-tracks-under-water-amid-imd-red-alert-for-extremely-heavy-rainfall-maharashtra-news-mhs25081901225</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>समाचार संध्या</t>
+          <t>Third Mumbai: महाराष्ट्राच्या विकासाचे नवे ग्रोथ सेंटर! काय म्हणाले CM फडणवीस?</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/bulletins-detail/%E0%A4%B8%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%BE%E0%A4%B0-%E0%A4%B8%E0%A4%82%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%BE-508/</t>
+          <t>https://www.tendernama.com/tender-news/third-mumbai-new-growth-center-for-maharashtras-development-what-did-cm-fadnavis-say</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>नवीन पिढीला इतिहासाशी जोडण्याचे कार्य सुरू – मुख्यमंत्री देवेंद्र फडणवीस</t>
+          <t>इतिहासाची अमूल्य खुण भारतात! इतिहासाशी पुन्हा जोडणारा क्षण, मुख्यमंत्री फडणवीसांची भावनिक प्रतिक्रिया</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176229/</t>
+          <t>https://www.esakal.com/maharashtra/chief-minister-devendra-fadnavis-statement-after-bringing-sword-of-raje-raghuji-bhosale-to-india-vru98</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Aaj Ki Baat: Mumbai में बारिश का Red Alert...48 घंटे संभलकर</t>
+          <t>Maharashtra Breaking News LIVE : दिवसभरातील महत्त्वाच्या घडामोडी, ब्रेकिंग न्यूजचा आढावा एका क्लिकवर</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/aaj-ki-baat/aaj-ki-baat-red-alert-for-rain-in-mumbai-be-careful-for-48-hours-2025-08-19-1156835</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-august-18-political-news-in-marathi-933194</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>CM Devendra Fadnavis यांच्या हस्ते अद्ययावत पोलीस सदनिकेचे उद्घाटन</t>
+          <t>Weather Updates : मुंबईत अचानक एवढा पाऊस का पडतोय? पुणे वेधशाळेच्या हवामान शास्त्रज्ञांनी</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/cm-devendra-fadnavis-inauguration-of-new-police-building-kolhapur-marathi-news/</t>
+          <t>https://marathi.abplive.com/news/pune-imd-on-heavy-rainfall-know-why-is-mumbai-suddenly-getting-so-much-rain-wather-update-imd-alert-for-mumbai-thane-for-next-48-hours-1377940</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Third Mumbai: महाराष्ट्राच्या विकासाचे नवे ग्रोथ सेंटर! काय म्हणाले CM फडणवीस?</t>
+          <t>मुसळधार पावसामुळे मुंबईत जनजीवन विस्कळीत; उपमुख्यमंत्री पवार यांनी परिस्थितीचा घेतला आढावा</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>https://www.tendernama.com/tender-news/third-mumbai-new-growth-center-for-maharashtras-development-what-did-cm-fadnavis-say</t>
+          <t>https://www.etvbharat.com/mr/!state/mumbai-rains-updates-imd-red-alert-mumbai-city-suburbs-schools-and-colleges-remain-closed-today-mumbai-university-exams-postponed-to-23-august-maharashtra-rain-news-today-maharashtra-news-mhs25081900792</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>इतिहासाची अमूल्य खुण भारतात! इतिहासाशी पुन्हा जोडणारा क्षण, मुख्यमंत्री फडणवीसांची भावनिक प्रतिक्रिया</t>
+          <t>School Student Stuck in Bus : बसमध्ये अडकलेल्या लहानग्यांना गुढघाभर पाण्यातून काढले बाहेर, पोलिसांच्या कृतीचे कौतुक, Video Viral</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/chief-minister-devendra-fadnavis-statement-after-bringing-sword-of-raje-raghuji-bhosale-to-india-vru98</t>
+          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/maharashtra-rain-news-update-mumbai-matunga-school-bus-stuck-children-rescued-by-police-video-viral-/40071</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Maharashtra Breaking News LIVE : दिवसभरातील महत्त्वाच्या घडामोडी, ब्रेकिंग न्यूजचा आढावा एका क्लिकवर</t>
+          <t>उत्तराखंड विधानसभेत सादर होणार नवे अल्पसंख्यांक शिक्षण विधेयक</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-august-18-political-news-in-marathi-933194</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/new-minority-education-bill-to-be-introduced-in-uttarakhand-assembly.html</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>मुंबईत सर्व शासकीय-निमशासकीय कार्यालयांना सुट्टी जाहीर, फॉर्सबेरी जलाशयाजवळ चार तासात 109 मिमी पावसाची नोंद</t>
+          <t>मराठवाड्यात आज आणि उद्याही पावसाचे धुमशान, विभागीय आयुक्तांचा नागरिकांबरोबरच प्रशासनालाही सतर्कतेचा इशारा</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/mumbai-rain-news-all-government-semi-government-offices-in-mumbai-remain-closed-today-mumbai-local-tracks-under-water-amid-imd-red-alert-for-extremely-heavy-rainfall-maharashtra-news-mhs25081901225</t>
+          <t>https://newstown.in/weather-alert-heavy-to-very-heavy-rain-predicted-on-18-1nd-19-august-2025-in-marathwada-region-by-imd-administration-on-alert/</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Weather Updates : मुंबईत अचानक एवढा पाऊस का पडतोय? पुणे वेधशाळेच्या हवामान शास्त्रज्ञांनी</t>
+          <t>Mumbai gets 177mm rain in 6-8 hour period, says CM; all agencies asked to remain alert</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/pune-imd-on-heavy-rainfall-know-why-is-mumbai-suddenly-getting-so-much-rain-wather-update-imd-alert-for-mumbai-thane-for-next-48-hours-1377940</t>
+          <t>https://m.economictimes.com/news/india/mumbai-gets-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/amp_articleshow/123365291.cms</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>School Student Stuck in Bus : बसमध्ये अडकलेल्या लहानग्यांना गुढघाभर पाण्यातून काढले बाहेर, पोलिसांच्या कृतीचे कौतुक, Video Viral</t>
+          <t>Upcoming ‘Third Mumbai’ will spur economic growth, says Maharashtra chief minister</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/maharashtra-rain-news-update-mumbai-matunga-school-bus-stuck-children-rescued-by-police-video-viral-/40071</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/upcoming-third-mumbai-will-spur-economic-growth-says-maharashtra-chief-minister/articleshow/123368667.cms</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>उत्तराखंड विधानसभेत सादर होणार नवे अल्पसंख्यांक शिक्षण विधेयक</t>
+          <t>CM’s nod for new terminal bldg at Nashik airport received: Min</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/new-minority-education-bill-to-be-introduced-in-uttarakhand-assembly.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/cms-nod-for-new-terminal-bldg-at-nashik-airport-received-min/articleshow/123372835.cms</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>मराठवाड्यात आज आणि उद्याही पावसाचे धुमशान, विभागीय आयुक्तांचा नागरिकांबरोबरच प्रशासनालाही सतर्कतेचा इशारा</t>
+          <t>Maharashtra rains: Five missing, several stranded as heavy rains lash Nanded, rescue operations underway</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>https://newstown.in/weather-alert-heavy-to-very-heavy-rain-predicted-on-18-1nd-19-august-2025-in-marathwada-region-by-imd-administration-on-alert/</t>
+          <t>https://www.indiatvnews.com/maharashtra/maharashtra-rains-five-missing-several-stranded-as-heavy-rains-lash-nanded-rescue-operations-underway-2025-08-18-1004046</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>कोल्हापूर सर्किट बेंच झाले, आता खंडपीठाचा प्रस्ताव द्या; सरन्यायाधीश भूषण गवईंची सूचना</t>
+          <t>Heavy rains lash Mumbai; red alert issued, Vihar Lake overflows, CM urges caution</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/74340/</t>
+          <t>https://www.thehindu.com/news/cities/mumbai/mumbai-rain-updates-august-18-2025/article69946286.ece</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>प्रशांत यादव यांचा आज भाजप प्रवेश</t>
+          <t>Mumbai rains HIGHLIGHTS: Civic body declares holiday for all schools on August 19</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/74397/</t>
+          <t>https://www.business-standard.com/india-news/live-news-updates-mumbai-rain-waterlogging-traffic-heavy-rain-orange-alert-125081800291_1.html</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Mumbai gets 177mm rain in 6-8 hour period, says CM; all agencies asked to remain alert</t>
+          <t>Maha CM asks agencies to be on alert mode after heavy rainfall and flash floods</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/mumbai-gets-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/amp_articleshow/123365291.cms</t>
+          <t>https://www.socialnews.xyz/2025/08/18/maha-cm-asks-agencies-to-be-on-alert-mode-after-heavy-rainfall-and-flash-floods/</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Upcoming ‘Third Mumbai’ will spur economic growth, says Maharashtra chief minister</t>
+          <t>देवेंद्र फडणवीस यांच्यासोबतच्या कोल्ड वॉरच्या चर्चेवर एकनाथ शिंदे यांची प्रतिक्रिया, स्पष्टच म्हणाले....</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/upcoming-third-mumbai-will-spur-economic-growth-says-maharashtra-chief-minister/articleshow/123368667.cms</t>
+          <t>https://www.msn.com/mr-in/news/national/%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%AC%E0%A4%A4%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%A1-%E0%A4%B5-%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A%E0%A5%87%E0%A4%B5%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A4%9A-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1zqXD8?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>CM’s nod for new terminal bldg at Nashik airport received: Min</t>
+          <t>Devendra Fadnvis | मुख्यमंत्री देवेंद्र फडणवीस १९ रोजी पैठण तालुक्यात</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/cms-nod-for-new-terminal-bldg-at-nashik-airport-received-min/articleshow/123372835.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/devendra-fadnvis-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A5%A7%E0%A5%AF-%E0%A4%B0-%E0%A4%9C-%E0%A4%AA%E0%A5%88%E0%A4%A0%E0%A4%A3-%E0%A4%A4-%E0%A4%B2%E0%A5%81%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%A4/ar-AA1KKgDI</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Maharashtra rains: Five missing, several stranded as heavy rains lash Nanded, rescue operations underway</t>
+          <t>Devendra Fadnavis | डॉ. आंबेडकर महाविद्यालयाने समाज परिवर्तनाचे केंद्र बनावे : मुख्यमंत्री देवेंद्र फडणवीस</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/maharashtra/maharashtra-rains-five-missing-several-stranded-as-heavy-rains-lash-nanded-rescue-operations-underway-2025-08-18-1004046</t>
+          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-%E0%A4%A1-%E0%A4%86%E0%A4%82%E0%A4%AC%E0%A5%87%E0%A4%A1%E0%A4%95%E0%A4%B0-%E0%A4%AE%E0%A4%B9-%E0%A4%B5-%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%B2%E0%A4%AF-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%AA%E0%A4%B0-%E0%A4%B5%E0%A4%B0%E0%A5%8D%E0%A4%A4%E0%A4%A8-%E0%A4%9A%E0%A5%87-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AC%E0%A4%A8-%E0%A4%B5%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8/ar-AA1JMyQJ</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Heavy rains lash Mumbai; red alert issued, Vihar Lake overflows, CM urges caution</t>
+          <t>महाराष्ट्रात महाभयानक पाऊस! मुख्यमंत्री देवेंद्र फडणवीस यांनी तातडीने साधला शेजारील राज्यांशी संपर्क? कारण अतिशय चिंताजनक</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/cities/mumbai/mumbai-rain-updates-august-18-2025/article69946286.ece</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%AE%E0%A4%B9-%E0%A4%AD%E0%A4%AF-%E0%A4%A8%E0%A4%95-%E0%A4%AA-%E0%A4%8A%E0%A4%B8-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A4-%E0%A4%A4%E0%A4%A1-%E0%A4%A8%E0%A5%87-%E0%A4%B8-%E0%A4%A7%E0%A4%B2-%E0%A4%B6%E0%A5%87%E0%A4%9C-%E0%A4%B0-%E0%A4%B2-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B6-%E0%A4%B8%E0%A4%82%E0%A4%AA%E0%A4%B0%E0%A5%8D%E0%A4%95-%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%85%E0%A4%A4-%E0%A4%B6%E0%A4%AF-%E0%A4%9A-%E0%A4%82%E0%A4%A4-%E0%A4%9C%E0%A4%A8%E0%A4%95/ar-AA1KJav3</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>225 trapped in Nanded floods; Army, NDRF deployed for rescue ops</t>
+          <t>मुंबईतील पावसाचा मुख्यमंत्र्यांकडून सातत्याने आढावा</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>https://tripurachronicle.in/national-news/225-trapped-in-nanded-floods-army-ndrf-deployed-for-rescue-ops/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/19/the-chief-minister-is-continuously-reviewing-the-rainfall-in-mumbai.html</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Maha CM asks agencies to be on alert mode after heavy rainfall and flash floods</t>
+          <t>BJP ने शिंदे गुट में लगाई सेंध! कट्टर शिवसैनिक छोड़ेंगे पार्टी, निकाय चुनाव से पहले दिया बड़ा झटका</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/maha-cm-asks-agencies-to-be-on-alert-mode-after-heavy-rainfall-and-flash-floods/</t>
+          <t>https://www.patrika.com/mumbai-news/maharashtra-politics-bjp-gives-setback-to-eknath-shinde-shiv-sena-before-civic-polls-19873589</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Devendra Fadnvis | मुख्यमंत्री देवेंद्र फडणवीस १९ रोजी पैठण तालुक्यात</t>
+          <t>महाराष्ट्र में मानसून का कहर: मुखेड तालुका में बादल फटने जैसी घटना, 200 से ज्यादा गांवों में बाढ़</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/devendra-fadnvis-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A5%A7%E0%A5%AF-%E0%A4%B0-%E0%A4%9C-%E0%A4%AA%E0%A5%88%E0%A4%A0%E0%A4%A3-%E0%A4%A4-%E0%A4%B2%E0%A5%81%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%A4/ar-AA1KKgDI</t>
+          <t>https://hindi.dynamitenews.com/maharashtra/cloudburst-in-mukhed-taluka-in-maharashtra-flood-in-more-than-200-villages</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>देवेंद्र फडणवीस यांच्यासोबतच्या कोल्ड वॉरच्या चर्चेवर एकनाथ शिंदे यांची प्रतिक्रिया, स्पष्टच म्हणाले....</t>
+          <t>CM फडणवीस ने खेला 'मराठी अस्मिता' का दांव, उपराष्ट्रपति चुनाव में उद्धव-पवार पर बना दबाव</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/national/%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%AC%E0%A4%A4%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%A1-%E0%A4%B5-%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A%E0%A5%87%E0%A4%B5%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A4%9A-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1zqXD8?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://navbharatlive.com/maharashtra/political-battle-over-nda-candidate-radhakrishnan-cm-fadnavis-seeks-support-from-uddhav-thackeray-and-sharad-pawar-1321873.html/amp</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis | डॉ. आंबेडकर महाविद्यालयाने समाज परिवर्तनाचे केंद्र बनावे : मुख्यमंत्री देवेंद्र फडणवीस</t>
+          <t>Mumbai News: चव्हाण ने कहा - श्रमिकों की एक साल में दो बार होगी वेतन वृद्धि</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-%E0%A4%A1-%E0%A4%86%E0%A4%82%E0%A4%AC%E0%A5%87%E0%A4%A1%E0%A4%95%E0%A4%B0-%E0%A4%AE%E0%A4%B9-%E0%A4%B5-%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%B2%E0%A4%AF-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%AA%E0%A4%B0-%E0%A4%B5%E0%A4%B0%E0%A5%8D%E0%A4%A4%E0%A4%A8-%E0%A4%9A%E0%A5%87-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AC%E0%A4%A8-%E0%A4%B5%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8/ar-AA1JMyQJ</t>
+          <t>https://www.bhaskarhindi.com/city/mumbai/mumbai-news-chavan-said-workers-will-get-salary-hike-twice-in-a-year-1174137</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>महाराष्ट्रात महाभयानक पाऊस! मुख्यमंत्री देवेंद्र फडणवीस यांनी तातडीने साधला शेजारील राज्यांशी संपर्क? कारण अतिशय चिंताजनक</t>
+          <t>नांदेड़ में भारी बारिश के कारण पांच लोग लापता, कई व्यक्ति फंसे : मुख्यमंत्री फडणवीस</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%AE%E0%A4%B9-%E0%A4%AD%E0%A4%AF-%E0%A4%A8%E0%A4%95-%E0%A4%AA-%E0%A4%8A%E0%A4%B8-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A4-%E0%A4%A4%E0%A4%A1-%E0%A4%A8%E0%A5%87-%E0%A4%B8-%E0%A4%A7%E0%A4%B2-%E0%A4%B6%E0%A5%87%E0%A4%9C-%E0%A4%B0-%E0%A4%B2-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B6-%E0%A4%B8%E0%A4%82%E0%A4%AA%E0%A4%B0%E0%A5%8D%E0%A4%95-%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%85%E0%A4%A4-%E0%A4%B6%E0%A4%AF-%E0%A4%9A-%E0%A4%82%E0%A4%A4-%E0%A4%9C%E0%A4%A8%E0%A4%95/ar-AA1KJav3</t>
+          <t>https://www.ibc24.in/maharashtra/five-people-missing-several-stranded-due-to-heavy-rains-in-nanded-cm-fadnavis-3212983.html</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>मुंबईतील पावसाचा मुख्यमंत्र्यांकडून सातत्याने आढावा</t>
+          <t>Vidarbha Crop Loss: विदर्भात दोन लाख हेक्टरवर पीक नुकसान</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/19/the-chief-minister-is-continuously-reviewing-the-rainfall-in-mumbai.html</t>
+          <t>https://agrowon.esakal.com/agro-special/crop-damage-on-two-lakh-hectares-in-vidarbha-rat16</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>राजधानीत पावसाचा कहर! मुंबई विद्यापीठाचा परीक्षांबाबत तडकाफडकी मोठा निर्णय!</t>
+          <t>मुख्यमंत्री फडणवीस यांची माहिती, राज्यात अतिवृष्टी, ८०० गावे बाधित, मुंबईत १७० एमएम पाऊस</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/mumbai-university-postponed-its-all-exam-to-be-held-on-19-august-due-to-heavy-rain-marathi-news-1472932.html/amp</t>
+          <t>https://www.marathiebatmya.com/political/cm-fadnavis-said-heavy-rains-in-the-state-800-villages-affected-170-mm-rain/</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>BJP ने शिंदे गुट में लगाई सेंध! कट्टर शिवसैनिक छोड़ेंगे पार्टी, निकाय चुनाव से पहले दिया बड़ा झटका</t>
+          <t>Heavy Rainfall : रेड ॲलर्ट घोषित केलेल्या ठिकाणी सतर्कता बाळगण्याचे मुख्यमंत्री फडणवीसांचे निर्देश</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/maharashtra-politics-bjp-gives-setback-to-eknath-shinde-shiv-sena-before-civic-polls-19873589</t>
+          <t>https://www.marathi.hindusthanpost.com/social/heavy-rainfall-cm-devendra-fadnavis-instructs-to-remain-vigilant-in-places-where-red-alert-has-been-declared/</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में भारी बारिश से सात लोगों की मौत, 200 ग्रामीण फंसे</t>
+          <t>'My karyakarta is with me': Hitendra Thakur shrugs off defections ahead of civic elections</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/seven-people-died-due-to-heavy-rains-in-maharashtra-200-villagers-stranded/856903/?amp</t>
+          <t>https://www.msn.com/en-in/news/India/my-karyakarta-is-with-me-hitendra-thakur-shrugs-off-defections-ahead-of-civic-elections/ar-AA1KHNiH</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में मानसून का कहर: मुखेड तालुका में बादल फटने जैसी घटना, 200 से ज्यादा गांवों में बाढ़</t>
+          <t>NDA’s VP nominee CP Radhakrishnan meets PM Modi in Delhi</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>https://hindi.dynamitenews.com/maharashtra/cloudburst-in-mukhed-taluka-in-maharashtra-flood-in-more-than-200-villages</t>
+          <t>https://www.news9live.com/india/ndas-vp-nominee-cp-radhakrishnan-meets-pm-modi-in-delhi-2883321</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>CM फडणवीस ने खेला 'मराठी अस्मिता' का दांव, उपराष्ट्रपति चुनाव में उद्धव-पवार पर बना दबाव</t>
+          <t>'Destroying constitutional institutions': Nishikant Dubey slams Rahul Gandhi as SC dismisses plea challenging 2024 Maharashtra polls</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/political-battle-over-nda-candidate-radhakrishnan-cm-fadnavis-seeks-support-from-uddhav-thackeray-and-sharad-pawar-1321873.html/amp</t>
+          <t>https://www.malaysiasun.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Mumbai News: चव्हाण ने कहा - श्रमिकों की एक साल में दो बार होगी वेतन वृद्धि</t>
+          <t>BJP man accuses Trinamool leaders of supporting Rohingyas, threatens to bulldoze them into Bangladesh</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/city/mumbai/mumbai-news-chavan-said-workers-will-get-salary-hike-twice-in-a-year-1174137</t>
+          <t>https://www.socialnews.xyz/2025/08/18/bjp-man-accuses-trinamool-leaders-of-supporting-rohingyas-threatens-to-bulldoze-them-into-bangladesh/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=bjp-man-accuses-trinamool-leaders-of-supporting-rohingyas-threatens-to-bulldoze-them-into-bangladesh</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Vidarbha Crop Loss: विदर्भात दोन लाख हेक्टरवर पीक नुकसान</t>
+          <t>Shivaji Sawant : शिवाजी सावंतांचा भाजपा प्रवेश निश्चित !</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/crop-damage-on-two-lakh-hectares-in-vidarbha-rat16</t>
+          <t>https://thefocusindia.com/maharashtra-news/shivaji-sawants-admission-to-bjp-is-certain-281398/amp/</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>मुख्यमंत्री फडणवीस यांची माहिती, राज्यात अतिवृष्टी, ८०० गावे बाधित, मुंबईत १७० एमएम पाऊस</t>
+          <t>Eknath Shinde : एकनाथ शिंदेंना मोठा धक्का ! ‘या’ नेत्याने निवडणुकीच्या तोंडावर सोडली साथ</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/cm-fadnavis-said-heavy-rains-in-the-state-800-villages-affected-170-mm-rain/</t>
+          <t>https://www.dainikprabhat.com/big-blow-to-eknath-shinde-big-leader-of-shiv-sena-shinde-group-will-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Heavy Rainfall : रेड ॲलर्ट घोषित केलेल्या ठिकाणी सतर्कता बाळगण्याचे मुख्यमंत्री फडणवीसांचे निर्देश</t>
+          <t>राष्ट्रवादीचे प्रशांत यादव यांचा आज भाजप प्रवेश</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/heavy-rainfall-cm-devendra-fadnavis-instructs-to-remain-vigilant-in-places-where-red-alert-has-been-declared/</t>
+          <t>https://pudhari.news/maharashtra/kokan/ratnagiri/ncp-prashant-yadav-joins-bjp-today-dc95</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>'My karyakarta is with me': Hitendra Thakur shrugs off defections ahead of civic elections</t>
+          <t>Ashish Shelar: मुंबईत जोरदार पाऊस! पावसाचा आढावा घेतल्यानंतर मंत्री शेलार म्हणाले, 'अत्यंत गरज असल्यास...'</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/my-karyakarta-is-with-me-hitendra-thakur-shrugs-off-defections-ahead-of-civic-elections/ar-AA1KHNiH</t>
+          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/mumbai-rain-updates-ashish-shelar-reviewed-the-rainfall-and-said-stay-safe-at-home/40069</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Why Eknath Shinde is covering little distance despite frequent visits to Delhi</t>
+          <t>Mumbai Rain Alert : मुंबईकरांनो सावध रहा.. पुढील 4 तास धोक्याचे… रेड अलर्ट अन् हवामान खात्याचा...</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/political-pulse/why-eknath-shinde-is-covering-little-distance-despite-frequent-visits-to-delhi-10197218/</t>
+          <t>https://www.tv9marathi.com/videos/mumbai-weather-forecast-imd-red-alert-for-mumbai-for-next-4-hours-extremely-important-for-mumbaikars-1473139.html/amp</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>NDA’s VP nominee CP Radhakrishnan meets PM Modi in Delhi</t>
+          <t>भाजपला स्थानिक ची निवडणूक महायुती म्हणूनच का लढवायची आहे?</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>https://www.news9live.com/india/ndas-vp-nominee-cp-radhakrishnan-meets-pm-modi-in-delhi-2883321</t>
+          <t>https://aaplaawajnews.com/2025/34070/</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>'Destroying constitutional institutions': Nishikant Dubey slams Rahul Gandhi as SC dismisses plea challenging 2024 Maharashtra polls</t>
+          <t>Congress Mohan Joshi Pune | Don't wait for BJP's 'event', open the flyover</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>https://www.malaysiasun.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
+          <t>https://policenama.com/congress-mohan-joshi-pune-dont-wait-for-bjps-event-open-the-flyover-former-mla-mohan-joshis-letter-to-the-municipal-commissioner/</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>BJP man accuses Trinamool leaders of supporting Rohingyas, threatens to bulldoze them into Bangladesh</t>
+          <t>राज्यात ‘ओला दुष्काळ’ जाहीर करा, एकरी ५० हजार रुपयांची मदत द्या -शशिकांत शिंदे</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/bjp-man-accuses-trinamool-leaders-of-supporting-rohingyas-threatens-to-bulldoze-them-into-bangladesh/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=bjp-man-accuses-trinamool-leaders-of-supporting-rohingyas-threatens-to-bulldoze-them-into-bangladesh</t>
+          <t>https://politicalmaharashtra.in/declare-wet-drought-in-the-state-provide-assistance-of-rs-50000-per-acre-shashikant-shinde-97623/</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Shivaji Sawant : शिवाजी सावंतांचा भाजपा प्रवेश निश्चित !</t>
+          <t>‘गँग्स ऑफ गद्दार’: शिंदेचा मंत्री ‘रोहित पवारांच्या’ निशाण्यावर</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/shivaji-sawants-admission-to-bjp-is-certain-281398/amp/</t>
+          <t>https://politicalmaharashtra.in/gangs-of-traitors-shindes-minister-targeted-by-rohit-pawar-97619/</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>राष्ट्रवादीचे प्रशांत यादव यांचा आज भाजप प्रवेश</t>
+          <t>To collect outstanding transportation fines, the Maha government is planning an amnesty scheme</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kokan/ratnagiri/ncp-prashant-yadav-joins-bjp-today-dc95</t>
+          <t>https://assamtribune.com/national/to-collect-outstanding-transportation-fines-the-mahagovernment-is-planning-an-amnesty-scheme-1588536</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Mumbai Rain Alert : मुंबईकरांनो सावध रहा.. पुढील 4 तास धोक्याचे… रेड अलर्ट अन् हवामान खात्याचा...</t>
+          <t>Muqabla: 'वोट चोरी' पर जीत किसकी...Rahul Gandhi या Election Commission?</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/mumbai-weather-forecast-imd-red-alert-for-mumbai-for-next-4-hours-extremely-important-for-mumbaikars-1473139.html/amp</t>
+          <t>https://www.indiatv.in/video/news-bulletin/muqabla-rahul-gandhi-or-the-election-commission-who-wins-the-vote-theft-battle-2025-08-19-1156831</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Ashish Shelar: मुंबईत जोरदार पाऊस! पावसाचा आढावा घेतल्यानंतर मंत्री शेलार म्हणाले, 'अत्यंत गरज असल्यास...'</t>
+          <t>'ऑपरेशन लोटस वगैरे काही नाही; लवकरच ऑपरेशन टायगर दिसेल', सोलापूरच्या राजकारणात पडद्यामागे काय घडतंय?</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/mumbai-rain-updates-ashish-shelar-reviewed-the-rainfall-and-said-stay-safe-at-home/40069</t>
+          <t>https://marathi.indiatimes.com/maharashtra/solapur/solapur-politics-over-shiv-sena-leader-shivaji-sawant-may-join-bjp/articleshow/123369493.cms</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Uddhav Thackeray: मनसेसोबत युती महापालिका निवडणुकीत घातक ठरणार; उद्धव ठाकरेंना 'या' नेत्यानं केलं सावध?</t>
+          <t>Nagpur Politics | भाईंनी घातला पक्ष प्रवेशाचा दुपट्टा,आता शिवसेनेचे घुमजाव</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/mns-alliance-risk-municipal-elections-uddhav-thackeray-warning-dk88-rc70</t>
+          <t>https://www.msn.com/mr-in/news/other/nagpur-politics-%E0%A4%AD-%E0%A4%88%E0%A4%82%E0%A4%A8-%E0%A4%98-%E0%A4%A4%E0%A4%B2-%E0%A4%AA%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6-%E0%A4%9A-%E0%A4%A6%E0%A5%81%E0%A4%AA%E0%A4%9F%E0%A5%8D%E0%A4%9F-%E0%A4%86%E0%A4%A4-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%9A%E0%A5%87-%E0%A4%98%E0%A5%81%E0%A4%AE%E0%A4%9C-%E0%A4%B5/ar-AA1HHJp9</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Congress Mohan Joshi Pune | Don't wait for BJP's 'event', open the flyover</t>
+          <t>Coffee Par Kurukshetra: उपराष्ट्रपति के नाम पर INDI अलायंस टूट जाएगा?</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>https://policenama.com/congress-mohan-joshi-pune-dont-wait-for-bjps-event-open-the-flyover-former-mla-mohan-joshis-letter-to-the-municipal-commissioner/</t>
+          <t>https://www.indiatv.in/video/kurukshetra/coffee-par-kurukshetra-indi-2025-08-19-1156832</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>राज्यात ‘ओला दुष्काळ’ जाहीर करा, एकरी ५० हजार रुपयांची मदत द्या -शशिकांत शिंदे</t>
+          <t>Haqiqat Kya Hai: मुनीर के मरने की तारीख भी आने वाली है ?</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>https://politicalmaharashtra.in/declare-wet-drought-in-the-state-provide-assistance-of-rs-50000-per-acre-shashikant-shinde-97623/</t>
+          <t>https://www.indiatv.in/video/hakikat-kya-hai/haqiqat-kya-hai-2025-08-19-1156836</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>‘गँग्स ऑफ गद्दार’: शिंदेचा मंत्री ‘रोहित पवारांच्या’ निशाण्यावर</t>
+          <t>Yoga With Swami Ramdev :ज़्यादा स्क्रीन टाइम से बच्चों को दिल की बीमारी</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>https://politicalmaharashtra.in/gangs-of-traitors-shindes-minister-targeted-by-rohit-pawar-97619/</t>
+          <t>https://www.indiatv.in/video/yoga/yoga-with-swami-ramdev-excessive-screen-time-can-cause-heart-disease-in-children-2025-08-19-1156871</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>To collect outstanding transportation fines, the Maha government is planning an amnesty scheme</t>
+          <t>मुंबई में 19 अगस्त को भी जारी रहेगा बारिश का कहर, मौसम विभाग ने दी बड़ी चेतावनी, जारी किया रेड अलर्ट</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>https://assamtribune.com/national/to-collect-outstanding-transportation-fines-the-mahagovernment-is-planning-an-amnesty-scheme-1588536</t>
+          <t>https://hindi.asianetnews.com/national-news/mumbai-braces-for-more-heavy-rain-on-19-august-imd-issued-red-and-orange-alert/articleshow-9knobps</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>NCP (SP) targets Maha minister over Rs 5,000 cr scam in Navi Mumbai’s CIDCO land; demands his resignation</t>
+          <t>महाराष्ट्र में मौसम बरपा रहा कहर: नांदेड़ में फटा बादल, बारिश के चलते 15 से 16 जिलो में अलर्ट, CM फडणवीस ने फसलों से लेकर लोकल ट्रेनों के बारे में दिया ये बड़ा अपडेट | Devendra Fadnavis, Cloudburst, Nan</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/ncp-sp-targets-maha-minister-over-rs-5000-cr-scam-in-navi-mumbais-cidco-land-demands-his-resignation/</t>
+          <t>https://www.bhaskarhindi.com/politics/devendra-fadnavis-cloudburst-nanded-maharashtra-news-maharashtra-1174025</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Ahead of Civic Polls, Hitendra Thakur Backs Loyalists: ‘My Karyakarta Is With Me, They Ensure Our Party Wins</t>
+          <t>Amravati Politics: अमरावती के दरियापुर में कांग्रेस को बड़ा झटका, सलीम घनीवाला भाजपा में शामिल</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/maharashtra/ahead-of-civic-polls-hitendra-thakur-backs-loyalists-my-karyakarta-is-with-me-they-ensure-our-party-wins-a475/</t>
+          <t>https://navbharatlive.com/maharashtra/amravati/major-blow-to-congress-in-dariyapur-of-amravati-salim-ghaniwala-joins-bjp-1321794.html/amp</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Muqabla: 'वोट चोरी' पर जीत किसकी...Rahul Gandhi या Election Commission?</t>
+          <t>शिवसेना शिंदे गुट को बड़ा झटका, बड़ा नेता छोड़ेगा एकनाथ शिंदे का साथ</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/news-bulletin/muqabla-rahul-gandhi-or-the-election-commission-who-wins-the-vote-theft-battle-2025-08-19-1156831</t>
+          <t>https://mpbreakingnews.in/maharashtra/shivaji-sawant-bjp-solapur-eknath-shinde-54-804117</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>'ऑपरेशन लोटस वगैरे काही नाही; लवकरच ऑपरेशन टायगर दिसेल', सोलापूरच्या राजकारणात पडद्यामागे काय घडतंय?</t>
+          <t>Amravati News : अमरावतीच्या दर्यापुरात काँग्रेसला मोठा धक्का, सलीम घाणीवालांचा भाजपमध्ये प्रवेश</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/solapur/solapur-politics-over-shiv-sena-leader-shivaji-sawant-may-join-bjp/articleshow/123369493.cms</t>
+          <t>https://marathi.ndtv.com/politics/salim-ghaniwala-joins-bjp-big-blow-to-congress-in-daryapur-amravati-9106782</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Nagpur Politics | भाईंनी घातला पक्ष प्रवेशाचा दुपट्टा,आता शिवसेनेचे घुमजाव</t>
+          <t>Devendra Fadnavis: चार लाख हेक्टर क्षेत्रावरील पिकांना फटका; मुख्यमंत्र्यांनी घेतला राज्यातील स्थितीचा आढावा</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/nagpur-politics-%E0%A4%AD-%E0%A4%88%E0%A4%82%E0%A4%A8-%E0%A4%98-%E0%A4%A4%E0%A4%B2-%E0%A4%AA%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6-%E0%A4%9A-%E0%A4%A6%E0%A5%81%E0%A4%AA%E0%A4%9F%E0%A5%8D%E0%A4%9F-%E0%A4%86%E0%A4%A4-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%9A%E0%A5%87-%E0%A4%98%E0%A5%81%E0%A4%AE%E0%A4%9C-%E0%A4%B5/ar-AA1HHJp9</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/heavy-rains-damage-crops-on-4-lakh-hectares-cm-devendra-fadnaivs-reviews-situation-in-maharashtra/articleshow/123379831.cms</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Coffee Par Kurukshetra: उपराष्ट्रपति के नाम पर INDI अलायंस टूट जाएगा?</t>
+          <t>ABP Majha Top 10 Headlines : ABP माझा टॉप 10 हेडलाईन्स | 18 ऑगस्ट 2025 | सोमवार</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/kurukshetra/coffee-par-kurukshetra-indi-2025-08-19-1156832</t>
+          <t>https://marathi.abplive.com/news/maharashtra/abp-majha-top-10-headlines-18-august-2025-monday-latest-marathi-news-update-maharashtra-politics-marathi-news-1378004</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>मुंबई में 19 अगस्त को भी जारी रहेगा बारिश का कहर, मौसम विभाग ने दी बड़ी चेतावनी, जारी किया रेड अलर्ट</t>
+          <t>मंत्री आशीष शेलार यांनी घेतला आपात्कालीन व्यवस्थापनाचा आढावा</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>https://hindi.asianetnews.com/national-news/mumbai-braces-for-more-heavy-rain-on-19-august-imd-issued-red-and-orange-alert/articleshow-9knobps</t>
+          <t>https://www.jpnnews.in/2025/08/Ashish-Shelar-reviews-emergency-management.html</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में मौसम बरपा रहा कहर: नांदेड़ में फटा बादल, बारिश के चलते 15 से 16 जिलो में अलर्ट, CM फडणवीस ने फसलों से लेकर लोकल ट्रेनों के बारे में दिया ये बड़ा अपडेट | Devendra Fadnavis, Cloudburst, Nan</t>
+          <t>राज्यात पावसाचा हाहाकार! मुख्यमंत्री फडणवीस अॅक्टीव्ह मोडवर, सतर्क राहण्याचे आवाहन</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/politics/devendra-fadnavis-cloudburst-nanded-maharashtra-news-maharashtra-1174025</t>
+          <t>https://civicmirror.in/maharashtra/maharashtra-rain-cm-fadnavis-reviews-situation-16-districts-on-red-alert/</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Amravati Politics: अमरावती के दरियापुर में कांग्रेस को बड़ा झटका, सलीम घनीवाला भाजपा में शामिल</t>
+          <t>‘शिंदेंच्या सेनेला’ दे धक्का : या आमदार बंधूंनी सोडला पक्ष</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/amravati/major-blow-to-congress-in-dariyapur-of-amravati-salim-ghaniwala-joins-bjp-1321794.html/amp</t>
+          <t>https://politicalmaharashtra.in/a-blow-to-shindes-army-these-mla-brothers-left-the-party-97625/</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>शिवसेना शिंदे गुट को बड़ा झटका, बड़ा नेता छोड़ेगा एकनाथ शिंदे का साथ</t>
+          <t>Seize assets of school directors in Shalarth ID scam: Bawankule</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/maharashtra/shivaji-sawant-bjp-solapur-eknath-shinde-54-804117</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/seize-assets-of-school-directors-in-shalarth-id-scam-bawankule/articleshow/123371134.cms</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>NDA से उपराष्ट्रपति पद के उम्मीदवार चुने जाने पर C.P Radhakrishnan को PM मोदी ने दी बधाई</t>
+          <t>Nagpur Smart City projects near closure with 7 works still pending</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>https://www.primetvindia.com/pm-modi-congratulated-c-p-radhakrishnan/</t>
+          <t>https://infra.economictimes.indiatimes.com/news/urban-infrastructure/nagpur-smart-city-projects-face-delay-7-projects-pending-completion/123360909</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis: चार लाख हेक्टर क्षेत्रावरील पिकांना फटका; मुख्यमंत्र्यांनी घेतला राज्यातील स्थितीचा आढावा</t>
+          <t>NMC pushes ahead with land acquisition for 2 STPs amid reluctance from VNIT, PKV</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/heavy-rains-damage-crops-on-4-lakh-hectares-cm-devendra-fadnaivs-reviews-situation-in-maharashtra/articleshow/123379831.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/nmc-pushes-ahead-with-land-acquisition-for-2-stps-amid-reluctance-from-vnit-pkv/articleshow/123372521.cms</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Amravati News : अमरावतीच्या दर्यापुरात काँग्रेसला मोठा धक्का, सलीम घाणीवालांचा भाजपमध्ये प्रवेश</t>
+          <t>MBBS admission quota in unaided colleges cut by 50%, students erupt</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/salim-ghaniwala-joins-bjp-big-blow-to-congress-in-daryapur-amravati-9106782</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/mbbs-admission-quota-in-unaided-colleges-cut-by-50-students-erupt/articleshow/123372541.cms</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>ABP Majha Top 10 Headlines : ABP माझा टॉप 10 हेडलाईन्स | 18 ऑगस्ट 2025 | सोमवार</t>
+          <t>Historic sword of Raje Raghuji Bhonsle arrives in Mumbai to royal welcome</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/abp-majha-top-10-headlines-18-august-2025-monday-latest-marathi-news-update-maharashtra-politics-marathi-news-1378004</t>
+          <t>https://www.nagpurtoday.in/historic-sword-of-raje-raghuji-bhonsle-arrives-in-mumbai-to-royal-welcome/08181446</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Mumbai Rain Red Alert : पावसामुळे आतापर्यंत 7 जणांचा मृत्यू; साचलेल्या पाण्यामुळे प्रवाशांचे हाल अन् राजकारणही तापलं</t>
+          <t>३१ खासदार निवडून आले तेव्हा मतदारयाद्या बरोबर होत्या का ?</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/mumbai-rain-red-alert-heavy-rainfall-maharashtra-floods-bmc-pune-schooll-jap93</t>
+          <t>https://www.lokmat.com/nagpur/were-the-voter-lists-correct-when-31-mps-were-elected-a-a1000/</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>मंत्री आशीष शेलार यांनी घेतला आपात्कालीन व्यवस्थापनाचा आढावा</t>
+          <t>रघुजी राजे यांची तलवार आणि ‘स्व’चा बोध</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>https://www.jpnnews.in/2025/08/Ashish-Shelar-reviews-emergency-management.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/historic-sword-of-shrimant-raghuji-bhosle-back-in-mumbai.html</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>राज्यात पावसाचा हाहाकार! मुख्यमंत्री फडणवीस अॅक्टीव्ह मोडवर, सतर्क राहण्याचे आवाहन</t>
+          <t>Teacher Recruitment Scam: बोगस शालार्थ आयडी घोटाळ्यातील संचालकांची मालमत्ता जप्त होणार !</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/maharashtra-rain-cm-fadnavis-reviews-situation-16-districts-on-red-alert/</t>
+          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/bogus-teacher-scam-school-id-fraud-directors-property-to-be-seized-ng81</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>‘शिंदेंच्या सेनेला’ दे धक्का : या आमदार बंधूंनी सोडला पक्ष</t>
+          <t>Chandrashekhar Bawankule: 'आताच मतदार याद्या तपासा', महसूल मंत्र्यांचा काँग्रेस नेत्यांना टोला</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>https://politicalmaharashtra.in/a-blow-to-shindes-army-these-mla-brothers-left-the-party-97625/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/chandrashekhar-bawankule-demands-to-check-voter-lists-against-congress-allegations/articleshow/123356783.cms</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Historic sword of Raje Raghuji Bhonsle arrives in Mumbai to royal welcome</t>
+          <t>Nagpur Accident : नागपुरातील हिट अँड रन प्रकरणाचा AI तंत्रज्ञानाच्या मदतीने उलगडा राज्यातील</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/historic-sword-of-raje-raghuji-bhonsle-arrives-in-mumbai-to-royal-welcome/08181446</t>
+          <t>https://marathi.abplive.com/crime/nagpur-hit-and-run-accident-news-update-case-solved-with-the-help-of-ai-technology-first-experiment-in-the-state-driver-arrested-from-uttar-pradesh-1377914</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Seize assets of school directors in Shalarth ID scam: Bawankule</t>
+          <t>Sambhajinagar News : आता शहरवासीयांना मिळणार अतिरिक्त २६ एमएलडी पाणी</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/seize-assets-of-school-directors-in-shalarth-id-scam-bawankule/articleshow/123371134.cms</t>
+          <t>https://pudhari.news/amp/story/maharashtra/marathwada/chhatrapati-sambhajinagar/now-city-residents-will-get-additional-26-mld-of-water-np88</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Nagpur Smart City projects near closure with 7 works still pending</t>
+          <t>kolhapur | सर्किट बेंचचे स्वप्न साकारले; न्यायाचे दरवाजे खुले झाले!</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>https://infra.economictimes.indiatimes.com/news/urban-infrastructure/nagpur-smart-city-projects-face-delay-7-projects-pending-completion/123360909</t>
+          <t>https://pudhari.news/amp/story/maharashtra/kolhapur/circuit-bench-dream-realized-doors-of-justice-now-open-ap84</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>NMC pushes ahead with land acquisition for 2 STPs amid reluctance from VNIT, PKV</t>
+          <t>Nagpur News: नव्या नागपूरला मिळणार तिसऱ्या रिंग रोडची जोड; ३६ गावांतील सुमारे ८८० हेक्टर जमिनीचे अधिग्रहण</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/nmc-pushes-ahead-with-land-acquisition-for-2-stps-amid-reluctance-from-vnit-pkv/articleshow/123372521.cms</t>
+          <t>https://www.esakal.com/vidarbha/nagpur/nagpur-to-get-third-ring-road-with-land-acquisition-from-36-villages-vsb99</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>MBBS admission quota in unaided colleges cut by 50%, students erupt</t>
+          <t>वरूणराजा कोपला! पिकांमध्ये पाणीच पाणी, पुढील 48 तासांत या जिल्ह्यांना पुन्हा रेड अलर्ट</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/mbbs-admission-quota-in-unaided-colleges-cut-by-50-students-erupt/articleshow/123372541.cms</t>
+          <t>https://news18marathi.com/agriculture/18-august-maharashtra-heavy-rain-update-monsoon-2025-mumbai-red-alert-1460576.html</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>३१ खासदार निवडून आले तेव्हा मतदारयाद्या बरोबर होत्या का ?</t>
+          <t>kolhapur | सर्किट बेंचचे स्वप्न साकारले; न्यायाचे दरवाजे खुले झाले!</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/nagpur/were-the-voter-lists-correct-when-31-mps-were-elected-a-a1000/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/circuit-bench-dream-realized-doors-of-justice-now-open-ap84</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>रघुजी राजे यांची तलवार आणि ‘स्व’चा बोध</t>
+          <t>Vice Presidential Election: सीपी राधाकृष्णन को NDA उम्मीदवार बनाने पर कांग्रेस को लगी मिर्ची, INDI गठबंधन कैंडिडेट पर खोले पत्ते</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/historic-sword-of-shrimant-raghuji-bhosle-back-in-mumbai.html</t>
+          <t>https://www.republicbharat.com/india/congress-angry-cp-radhakrishnan-nda-vice-presidential-candidate-opened-cards-on-indi-alliance-meeting</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Sambhajinagar News : आता शहरवासीयांना मिळणार अतिरिक्त २६ एमएलडी पाणी</t>
+          <t>‘Extremely Unfortunate’: Rajnath Singh Raps Opposition for ‘Stalling’ Special Discussion in</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>https://pudhari.news/amp/story/maharashtra/marathwada/chhatrapati-sambhajinagar/now-city-residents-will-get-additional-26-mld-of-water-np88</t>
+          <t>https://www.latestly.com/india/news/extremely-unfortunate-rajnath-singh-raps-opposition-for-stalling-special-discussion-in-parliament-on-astronaut-subhanshu-shuklas-space-mission-7064889.html</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Chandrashekhar Bawankule: 'आताच मतदार याद्या तपासा', महसूल मंत्र्यांचा काँग्रेस नेत्यांना टोला</t>
+          <t>India News | 12-day Himachal Pradesh Assembly Session Opens; Opposition Seeks Adjournment on Disaster</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/chandrashekhar-bawankule-demands-to-check-voter-lists-against-congress-allegations/articleshow/123356783.cms</t>
+          <t>https://www.latestly.com/agency-news/india-news-12-day-himachal-pradesh-assembly-session-opens-opposition-seeks-adjournment-on-disaster-7064955.html</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Nagpur News: नव्या नागपूरला मिळणार तिसऱ्या रिंग रोडची जोड; ३६ गावांतील सुमारे ८८० हेक्टर जमिनीचे अधिग्रहण</t>
+          <t>Vice President Election: NDA उम्मीदवार सीपी राधाकृष्णन को मिल सकता है विपक्षी दलों का समर्थन, इन पार्टियों पर सबकी नजर</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/vidarbha/nagpur/nagpur-to-get-third-ring-road-with-land-acquisition-from-36-villages-vsb99</t>
+          <t>https://www.jagran.com/politics/national-rajya-sabha-election-opposition-parties-may-support-nda-candidate-cp-radhakrishnan-24017212.html</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Nagpur Accident : नागपुरातील हिट अँड रन प्रकरणाचा AI तंत्रज्ञानाच्या मदतीने उलगडा राज्यातील</t>
+          <t>महाराष्ट्र की ‘अस्मिता’ की बात करने वाले उपराष्ट्रपति पद के लिए राधाकृष्णन का समर्थन करें : फडणवीस</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/crime/nagpur-hit-and-run-accident-news-update-case-solved-with-the-help-of-ai-technology-first-experiment-in-the-state-driver-arrested-from-uttar-pradesh-1377914</t>
+          <t>https://hindi.theprint.in/india/support-radhakrishnan-for-the-post-of-vice-president-who-talks-about-maharashtras-identity-fadnavis/856729/</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Teacher Recruitment Scam: बोगस शालार्थ आयडी घोटाळ्यातील संचालकांची मालमत्ता जप्त होणार !</t>
+          <t>कौन लेगा CP राधाकृष्णन की जगह? BJP की एक खोज खत्म होते ही शुरू हुई दूसरी तलाश</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/bogus-teacher-scam-school-id-fraud-directors-property-to-be-seized-ng81</t>
+          <t>https://navbharatlive.com/maharashtra/maharashtra-new-governor-who-will-replace-cp-radhakrishnan-bjp-new-search-begins-1321951.html</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>kolhapur | सर्किट बेंचचे स्वप्न साकारले; न्यायाचे दरवाजे खुले झाले!</t>
+          <t>Farmers Loan Waiver: बावनकुळेंनंतर महायुती सरकारमधील 'या' मंत्र्याची कर्जमाफीबाबत मोठी अपडेट; म्हणाले,'CM फडणवीस लवकरच...'</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>https://pudhari.news/amp/story/maharashtra/kolhapur/circuit-bench-dream-realized-doors-of-justice-now-open-ap84</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/sanjay-rathod-update-farmer-loan-waiver-devendra-fadnavis-dk88</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>वरूणराजा कोपला! पिकांमध्ये पाणीच पाणी, पुढील 48 तासांत या जिल्ह्यांना पुन्हा रेड अलर्ट</t>
+          <t>Election Commission Of India &amp; The “Politics Of Jugaad”</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/agriculture/18-august-maharashtra-heavy-rain-update-monsoon-2025-mumbai-red-alert-1460576.html</t>
+          <t>https://madrascourier.com/opinion/election-commission-of-india-the-politics-of-jugaad/</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Third Mumbai in Raigad to become Maharashtra’s new economic powerhouse: CM Fadnavis</t>
+          <t>Video | Bihar Elections | RJD Leader Tejaswi Yadav Takes On PM Modi Over Bihar Polls: "Stop Fooling..."</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>https://www.daijiworld.com/index.php/news/newsDisplay?newsID=1289652</t>
+          <t>https://www.ndtv.com/video/bihar-elections-rjd-leader-tejaswi-yadav-takes-on-pm-modi-over-bihar-polls-stop-fooling-981918</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>kolhapur | सर्किट बेंचचे स्वप्न साकारले; न्यायाचे दरवाजे खुले झाले!</t>
+          <t>CP Radhakrishnan vs who? Why DMK’s pushing INDIA bloc for a Tamil vs Tamil contest for India’s V-P</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/circuit-bench-dream-realized-doors-of-justice-now-open-ap84</t>
+          <t>https://theprint.in/india/cp-radhakrishnan-vs-who-why-dmks-pushing-india-bloc-for-a-tamil-vs-tamil-contest-for-indias-v-p/2723136/</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Vice Presidential Election: सीपी राधाकृष्णन को NDA उम्मीदवार बनाने पर कांग्रेस को लगी मिर्ची, INDI गठबंधन कैंडिडेट पर खोले पत्ते</t>
+          <t>'Political opinions or...': Supreme Court quashes plea challenging validity of Maharashtra Assembly polls</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>https://www.republicbharat.com/india/congress-angry-cp-radhakrishnan-nda-vice-presidential-candidate-opened-cards-on-indi-alliance-meeting</t>
+          <t>https://www.deccanherald.com/india/political-opinions-or-supreme-court-quashes-plea-challenging-validity-of-maharashtra-assembly-polls-3686244</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>India News | 12-day Himachal Pradesh Assembly Session Opens; Opposition Seeks Adjournment on Disaster</t>
+          <t>Shiv Sena, NCP support Maha Governor’s nomination for Vice President</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/india-news-12-day-himachal-pradesh-assembly-session-opens-opposition-seeks-adjournment-on-disaster-7064955.html</t>
+          <t>https://www.indianewsstream.com/shiv-sena-ncp-support-maha-governors-nomination-for-vice-president/</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Vice President Election: NDA उम्मीदवार सीपी राधाकृष्णन को मिल सकता है विपक्षी दलों का समर्थन, इन पार्टियों पर सबकी नजर</t>
+          <t>'Destroying constitutional institutions': Nishikant Dubey slams Rahul Gandhi as SC dismisses plea challenging 2024 Maharashtra polls</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/politics/national-rajya-sabha-election-opposition-parties-may-support-nda-candidate-cp-radhakrishnan-24017212.html</t>
+          <t>https://www.aninews.in/news/national/politics/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls20250819085747/</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>महाराष्ट्र की ‘अस्मिता’ की बात करने वाले उपराष्ट्रपति पद के लिए राधाकृष्णन का समर्थन करें : फडणवीस</t>
+          <t>PM Modi appeals for unanimous election of Radhakrishnan as vice president</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/support-radhakrishnan-for-the-post-of-vice-president-who-talks-about-maharashtras-identity-fadnavis/856729/</t>
+          <t>https://english.varthabharati.in/india/pm-modi-appeals-for-unanimous-election-of-radhakrishnan-as-vice-president</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Asia Cup 2025: पाकिस्तान क्रिकेट के मुख्य चयनकर्ता का बड़ा बयान, बोले- भारत को हराएगा पाकिस्तान</t>
+          <t>Supreme Court dismisses plea alleging 75 lakh bogus votes in Maharashtra Assembly polls</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/sports/asia-cup-2025-2025-08-18-1156799</t>
+          <t>https://organiser.org/2025/08/19/308844/bharat/supreme-court-dismisses-plea-alleging-75-lakh-bogus-votes-in-maharashtra-assembly-polls/</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Haqiqat Kya Hai: मुनीर के मरने की तारीख भी आने वाली है ?</t>
+          <t>Alcaraz wins the Cincinnati Open after Sinner retires in the first set because of illness</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/hakikat-kya-hai/haqiqat-kya-hai-2025-08-19-1156836</t>
+          <t>https://english.varthabharati.in/sports/alcaraz-wins-the-cincinnati-open-after-sinner-retires-in-the-first-set-because-of-illness</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>कौन लेगा CP राधाकृष्णन की जगह? BJP की एक खोज खत्म होते ही शुरू हुई दूसरी तलाश</t>
+          <t>'संवैधानिक संस्थाओं को कर रहे हैं नष्ट...' भाजपा सांसद निशिकांत दुबे ने राहुल गांधी पर साधा निशाना</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/maharashtra-new-governor-who-will-replace-cp-radhakrishnan-bjp-new-search-begins-1321951.html</t>
+          <t>https://www.timesnowhindi.com/india/constitutional-institutions-are-being-destroyed-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls-article-152485768</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Aaj Ka Rashifal, 19 Aug, 2025 : आचार्य इंदु प्रकाश जी से जानिए आज क्या कह रहे हैं आपके सितारे</t>
+          <t>खरगे, स्टॉलिन, नवीन पटनायक... उपराष्ट्रपति चुनाव से पहले राजनाथ सिंह को बीजेपी ने दी खास जिम्मेदारी</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/bhavishyawani/aaj-ka-rashifal-19-aug-2025-know-from-acharya-indu-prakash-ji-what-your-stars-are-saying-today-2025-08-19-1156865</t>
+          <t>https://navbharattimes.indiatimes.com/india/vice-president-election-defence-minister-rajnath-singh-reaches-out-to-dmk-tmc-bjd-for-consensus-for-cp-radhakrishnan/articleshow/123375990.cms</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Yoga With Swami Ramdev :ज़्यादा स्क्रीन टाइम से बच्चों को दिल की बीमारी</t>
+          <t>शिवसेना एकनाथ शिंदे गुट को बड़ा झटका, शिवाजी सावंत भाजपा में होगें शामिल | Maharastra - Paliwalwani - Latest Hindi News</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/yoga/yoga-with-swami-ramdev-excessive-screen-time-can-cause-heart-disease-in-children-2025-08-19-1156871</t>
+          <t>https://paliwalwani.com/maharastra/shiv-sena-eknath-shinde-faction-is-a-big-shock-shivaji-sawant-will-be-involved-in-bjp</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Farmers Loan Waiver: बावनकुळेंनंतर महायुती सरकारमधील 'या' मंत्र्याची कर्जमाफीबाबत मोठी अपडेट; म्हणाले,'CM फडणवीस लवकरच...'</t>
+          <t>चुनाव आयोग की प्रेस कॉन्फ्रेंस में इन दो पत्रकारों के सवालों ने बोलती बंद कर दी, देखें वीडियो – No. 1 Indian Media News Portal</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/sanjay-rathod-update-farmer-loan-waiver-devendra-fadnavis-dk88</t>
+          <t>https://www.bhadas4media.com/eci-press-confrence-journalist-question/</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Election Commission Of India &amp; The “Politics Of Jugaad”</t>
+          <t>उपराष्ट्रपतीपदाचे उमेदवार राधाकृष्णन यांना पाठिंबा द्या; देवेंद्र फडणवीस यांची शरद पवार आणि उद्धव ठाकरे यांना साद</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>https://madrascourier.com/opinion/election-commission-of-india-the-politics-of-jugaad/</t>
+          <t>https://marathi.freepressjournal.in/maharashtra/cp-radhakrishnan-vice-president-candidate-fadnavis-appeal-pawar-thackeray</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Video | Bihar Elections | RJD Leader Tejaswi Yadav Takes On PM Modi Over Bihar Polls: "Stop Fooling..."</t>
+          <t>राहुल गांधी पक्ष टिकवण्यासाठी निवडणूक आयोगाचा आधार घेतात; मंत्री चंद्रशेखर बावनकुळे यांची टीका</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/video/bihar-elections-rjd-leader-tejaswi-yadav-takes-on-pm-modi-over-bihar-polls-stop-fooling-981918</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/rahul-gandhi-takes-support-from-election-commission-to-save-party-minister-chandrashekhar-bawankule-criticizes.html</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>CP Radhakrishnan vs who? Why DMK’s pushing INDIA bloc for a Tamil vs Tamil contest for India’s V-P</t>
+          <t>‘मत चोरी’चा वाद वाढला, विरोधक मुख्य निवडणूक आयुक्तांविरोधात महाभियोग प्रस्ताव आणण्याच्या तयारीत - Marathi News | The controversy over 'vote theft' escalates, the opposition is preparing to bring an impeachment motio</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/cp-radhakrishnan-vs-who-why-dmks-pushing-india-bloc-for-a-tamil-vs-tamil-contest-for-indias-v-p/2723136/</t>
+          <t>https://www.lokmat.com/shorts/national/vote-theft-row-escalates-opposition-mulls-impeachment-of-election-commissioner/</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>'Political opinions or...': Supreme Court quashes plea challenging validity of Maharashtra Assembly polls</t>
+          <t>Pravin Darekar: राज्य सहकारी संघाच्या अध्यक्षपदी आमदार प्रवीण दरेकर</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/political-opinions-or-supreme-court-quashes-plea-challenging-validity-of-maharashtra-assembly-polls-3686244</t>
+          <t>https://pudhari.news/maharashtra/pune/pravin-darekar-elected-cooperative-president-maharashtra-ac90</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Shiv Sena, NCP support Maha Governor’s nomination for Vice President</t>
+          <t>१९८७च्या काश्मीर निवडणूक गैरप्रकाराचा काँग्रेसला विसर - राजीव गांधींकडून विरोधकांच्या आरोपांकडे दुर्लक्ष</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>https://www.indianewsstream.com/shiv-sena-ncp-support-maha-governors-nomination-for-vice-president/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/congress-forgets-1987-kashmir-election-malpractices-rajiv-gandhi-ignores-opposition-allegations.html</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>'Destroying constitutional institutions': Nishikant Dubey slams Rahul Gandhi as SC dismisses plea challenging 2024 Maharashtra polls</t>
+          <t>हवामानाचा अंदाज: आजही पावसाचा कहर? मुंबई, पुण्यासह 7 जिल्ह्यांना रेड अलर्ट; गडचिरोलीसह 4 जिल्ह्यांना यलो अलर्ट</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/politics/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls20250819085747/</t>
+          <t>https://thefocusindia.com/national-news/maharashtra-weather-red-alert-mumbai-pune-7-districts-281414/</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Video | Parliament News | INDIA Bloc Continues Protest Against Bihar SIR At Parliament</t>
+          <t>Maharashtra News: Dy CM Eknath Shinde Launches ‘Ladki Sun – Surakshit Sun’ Campaign To Protect Women</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/video/parliament-news-india-bloc-continues-protest-against-bihar-sir-at-parliament-982014</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-dy-cm-eknath-shinde-launches-ladki-sun-surakshit-sun-campaign-to-protect-women-victims</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>PM Modi appeals for unanimous election of Radhakrishnan as vice president</t>
+          <t>Fadnavis meets Guv Radhakrishnan, presents him book of Shivaji Maharaj's letters</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>https://english.varthabharati.in/india/pm-modi-appeals-for-unanimous-election-of-radhakrishnan-as-vice-president</t>
+          <t>https://www.ptinews.com/detail/national/Fadnavis-meets-Guv-Radhakrishnan--presents-him-book-of-Shivaji-Maharaj-s-letters/2832581</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Supreme Court dismisses plea alleging 75 lakh bogus votes in Maharashtra Assembly polls</t>
+          <t>'Slap, but don't make video': Raj Thackeray's blunt advice to MNS workers after Marathi 'slapgate' case</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>https://organiser.org/2025/08/19/308844/bharat/supreme-court-dismisses-plea-alleging-75-lakh-bogus-votes-in-maharashtra-assembly-polls/</t>
+          <t>https://www.msn.com/en-in/news/India/slap-but-dont-make-video-raj-thackerays-blunt-advice-to-mns-workers-after-marathi-slapgate-case/ar-AA1I11OF</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Alcaraz wins the Cincinnati Open after Sinner retires in the first set because of illness</t>
+          <t>Mumbai: Iconic Sword of Raghuji Bhonsle Arrives from London; Bike Rally Cancelled Due to Rains, Grand...</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>https://english.varthabharati.in/sports/alcaraz-wins-the-cincinnati-open-after-sinner-retires-in-the-first-set-because-of-illness</t>
+          <t>https://www.lokmattimes.com/mumbai/mumbai-iconic-sword-of-raghuji-bhonsle-arrives-from-london-bike-rally-cancelled-due-to-rains-grand-inauguration-tonight-a525/</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>'संवैधानिक संस्थाओं को कर रहे हैं नष्ट...' भाजपा सांसद निशिकांत दुबे ने राहुल गांधी पर साधा निशाना</t>
+          <t>How CP Radhakrishnan Broke The Taboo Around Modi And Changed The Narrative After 2002 Gujarat Episode - The</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>https://www.timesnowhindi.com/india/constitutional-institutions-are-being-destroyed-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls-article-152485768</t>
+          <t>https://thecommunemag.com/how-cpr-broke-the-taboo-around-modi/</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>खरगे, स्टॉलिन, नवीन पटनायक... उपराष्ट्रपति चुनाव से पहले राजनाथ सिंह को बीजेपी ने दी खास जिम्मेदारी</t>
+          <t>राजधानीत पावसाचा कहर! मुंबई विद्यापीठाचा परीक्षांबाबत तडकाफडकी मोठा निर्णय!</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/india/vice-president-election-defence-minister-rajnath-singh-reaches-out-to-dmk-tmc-bjd-for-consensus-for-cp-radhakrishnan/articleshow/123375990.cms</t>
+          <t>https://www.tv9marathi.com/maharashtra/mumbai-university-postponed-its-all-exam-to-be-held-on-19-august-due-to-heavy-rain-marathi-news-1472932.html</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>शिवसेना एकनाथ शिंदे गुट को बड़ा झटका, शिवाजी सावंत भाजपा में होगें शामिल | Maharastra - Paliwalwani - Latest Hindi News</t>
+          <t>पश्चिम महाराष्ट्रात शिंदेंना भाजपचा धक्का, आमदाराच्या भावासह ४० पदाधिकाऱ्यांचा शिवसेनेला जय महाराष्ट्र!</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>https://paliwalwani.com/maharastra/shiv-sena-eknath-shinde-faction-is-a-big-shock-shivaji-sawant-will-be-involved-in-bjp</t>
+          <t>https://saamtv.esakal.com/maharashtra/solapur-political-news-bjp-strengthens-in-solapur-as-40-sena-leaders-join-with-shivaji-sawant-bdk97</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>चुनाव आयोग की प्रेस कॉन्फ्रेंस में इन दो पत्रकारों के सवालों ने बोलती बंद कर दी, देखें वीडियो – No. 1 Indian Media News Portal</t>
+          <t>सोलापुरात भाजपची शिंदेंच्या शिवसेनावर कुरघोडी शिवाजी सावंतांनी शिवसेना सोडली,</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>https://www.bhadas4media.com/eci-press-confrence-journalist-question/</t>
+          <t>https://marathi.abplive.com/news/politics/solapur-shivaji-sawant-leaves-shiv-sena-and-bjp-entry-confirmed-devendra-fadnavis-bjp-attack-on-eknath-shinde-shiv-sena-in-solapur-1377928</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>उपराष्ट्रपतीपदाचे उमेदवार राधाकृष्णन यांना पाठिंबा द्या; देवेंद्र फडणवीस यांची शरद पवार आणि उद्धव ठाकरे यांना साद</t>
+          <t>सोलापूरच्या राजकारणात मोठी खळबळ; तानाजी सावंत यांचा भाऊ करणार भाजपात प्रवेश</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/maharashtra/cp-radhakrishnan-vice-president-candidate-fadnavis-appeal-pawar-thackeray</t>
+          <t>https://www.timemaharashtra.com/politics/big-stir-in-solapur-politics-tanaji-sawants-brother-to-join-bjp/129377/</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>राहुल गांधी पक्ष टिकवण्यासाठी निवडणूक आयोगाचा आधार घेतात; मंत्री चंद्रशेखर बावनकुळे यांची टीका</t>
+          <t>Rohit Pawar on Sanjay Shirsath: रोहित पवारांचे मंत्री संजय शिरसाटांवर भ्रष्टाचाराचे गंभीर आरोप; पहा काय म्हणाले</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/rahul-gandhi-takes-support-from-election-commission-to-save-party-minister-chandrashekhar-bawankule-criticizes.html</t>
+          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/amp</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>‘मत चोरी’चा वाद वाढला, विरोधक मुख्य निवडणूक आयुक्तांविरोधात महाभियोग प्रस्ताव आणण्याच्या तयारीत - Marathi News | The controversy over 'vote theft' escalates, the opposition is preparing to bring an impeachment motio</t>
+          <t>Maharashtra Rain Update : मोठा निर्णय! अतिवृष्टीमुळे विद्यार्थ्यांना सुट्टी जाहीर; 'या' जिल्ह्यांमध्ये शाळा राहणार बंद, जाणून घ्या</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/shorts/national/vote-theft-row-escalates-opposition-mulls-impeachment-of-election-commissioner/</t>
+          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/due-to-heavy-rain-government-declared-holiday-for-students-in-mumbai-thane-kalyan-dombivli-palghar-district/40074</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>हवामानाचा अंदाज: आजही पावसाचा कहर? मुंबई, पुण्यासह 7 जिल्ह्यांना रेड अलर्ट; गडचिरोलीसह 4 जिल्ह्यांना यलो अलर्ट</t>
+          <t>Rohit Pawar: मंत्री संजय शिरसाटांनी केला ५ हजार कोटींचा घोटाळा; आमदार रोहित पवारांच्या आरोपाने खळबळ</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/national-news/maharashtra-weather-red-alert-mumbai-pune-7-districts-281414/amp/</t>
+          <t>https://deshdoot.com/rohit-pawar-alleges-sanjay-shirsat-over-5000-crore-worth-land-to-bivalkar-family/</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Pravin Darekar: राज्य सहकारी संघाच्या अध्यक्षपदी आमदार प्रवीण दरेकर</t>
+          <t>Mumbai Rain Red Alert : पावसामुळे आतापर्यंत 7 जणांचा मृत्यू; साचलेल्या पाण्यामुळे प्रवाशांचे हाल अन् राजकारणही तापलं</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/pravin-darekar-elected-cooperative-president-maharashtra-ac90</t>
+          <t>https://sarkarnama.esakal.com/mumbai/mumbai-rain-red-alert-heavy-rainfall-maharashtra-floods-bmc-pune-schooll-jap93</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>१९८७च्या काश्मीर निवडणूक गैरप्रकाराचा काँग्रेसला विसर - राजीव गांधींकडून विरोधकांच्या आरोपांकडे दुर्लक्ष</t>
+          <t>Shivsena | नाराजी भोवली! शिंदे गटातून बड्या नेत्याचा राजीनामा, राजकीय वर्तुळात खळबळ</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/congress-forgets-1987-kashmir-election-malpractices-rajiv-gandhi-ignores-opposition-allegations.html</t>
+          <t>https://www.thodkyaat.com/big-setback-for-eknath-shinde-faction-as-senior-leader-shivaji-sawant-joins-bjp-ahead-of-local-body-polls/</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Eknath Shinde : एकनाथ शिंदेंना मोठा धक्का ! ‘या’ नेत्याने निवडणुकीच्या तोंडावर सोडली साथ</t>
+          <t>Rohit Pawar on Sanjay Shirsath: रोहित पवारांचे मंत्री संजय शिरसाटांवर भ्रष्टाचाराचे गंभीर आरोप; पहा काय म्हणाले</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/big-blow-to-eknath-shinde-big-leader-of-shiv-sena-shinde-group-will-join-bjp/</t>
+          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>'उपराष्ट्रपती'साठी महाराष्ट्राच्या राज्यपालांचे नाव; फडणवीसांचे खासदारांना आवाहन, पवार-ठाकरेंना टोला</t>
+          <t>Ekanath Shinde Shivsena : शिंदे गटाला धक्का; आमदाराचा भाऊ व 40 पदाधिकाऱ्यांचा पक्षप्रवेश</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-urges-mps-to-support-radhakrishnan-targets-uddhav-thackeray-and-sharad-pawar-035137.html</t>
+          <t>https://www.lokshahi.com/news/mla-tanaji-sawants-brother-shivaji-sawant-has-decided-to-quit-the-group-and-join-the-bjp</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Maharashtra News: Dy CM Eknath Shinde Launches ‘Ladki Sun – Surakshit Sun’ Campaign To Protect Women</t>
+          <t>NCP demands : राज्यात ओला दुष्काळ जाहीर करा अन्…; राष्ट्रवादी शरद पवार गटाची मागणी</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-dy-cm-eknath-shinde-launches-ladki-sun-surakshit-sun-campaign-to-protect-women-victims</t>
+          <t>https://deshdoot.com/heavy-rains-wreak-havoc-in-maharashtra-sharad-pawar-ncp-demands-wet-drought-declaration-and-farmer-relief/</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Fadnavis meets Guv Radhakrishnan, presents him book of Shivaji Maharaj's letters</t>
+          <t>शिंदे गटाचे आमदार तानाजी सावंतांचे बंधू भाजपच्या वाटेवर</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/national/Fadnavis-meets-Guv-Radhakrishnan--presents-him-book-of-Shivaji-Maharaj-s-letters/2832581</t>
+          <t>https://pcbtoday.in/%E0%A4%B6%E0%A4%BF%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%97%E0%A4%9F%E0%A4%BE%E0%A4%9A%E0%A5%87-%E0%A4%86%E0%A4%AE%E0%A4%A6%E0%A4%BE%E0%A4%B0-%E0%A4%A4%E0%A4%BE%E0%A4%A8%E0%A4%BE%E0%A4%9C%E0%A5%80/</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>'Slap, but don't make video': Raj Thackeray's blunt advice to MNS workers after Marathi 'slapgate' case</t>
+          <t>Kokan Politics : शरद पवार गटाला धक्का; प्रदेश सरचिटणीस प्रशांत यादव भाजपाच्या वाटेवर</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/slap-but-dont-make-video-raj-thackerays-blunt-advice-to-mns-workers-after-marathi-slapgate-case/ar-AA1I11OF</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/kokan-politics-sharad-pawar-group-suffers-setback-state-general-secretary-prashant-yadav-on-bjps-path/</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Mumbai: Iconic Sword of Raghuji Bhonsle Arrives from London; Bike Rally Cancelled Due to Rains, Grand...</t>
+          <t>Rajnath reaches out to DMK, TMC, BJD for consensus on VP nominee</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/mumbai/mumbai-iconic-sword-of-raghuji-bhonsle-arrives-from-london-bike-rally-cancelled-due-to-rains-grand-inauguration-tonight-a525/</t>
+          <t>https://timesofindia.indiatimes.com/india/rajnath-reaches-out-to-dmk-tmc-bjd-for-consensus-on-vp-nominee/articleshow/123373035.cms</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>How CP Radhakrishnan Broke The Taboo Around Modi And Changed The Narrative After 2002 Gujarat Episode - The</t>
+          <t>MSRTC और पुलिस की पहल, गढ़चिरौली के आदिवासी गांव को मिला पहला सार्वजनिक परिवहन, ग्रामीणों ने लहराया तिरंगा</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>https://thecommunemag.com/how-cpr-broke-the-taboo-around-modi/</t>
+          <t>https://hindi.mid-day.com/news/india-news/photo/initiative-of-msrtc-and-police-tribal-village-of-gadchiroli-gets-first-public-transport-1558</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>पश्चिम महाराष्ट्रात शिंदेंना भाजपचा धक्का, आमदाराच्या भावासह ४० पदाधिकाऱ्यांचा शिवसेनेला जय महाराष्ट्र!</t>
+          <t>Uddhav Thackeray: मनसेसोबत युती महापालिका निवडणुकीत घातक ठरणार; उद्धव ठाकरेंना 'या' नेत्यानं केलं सावध?</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/solapur-political-news-bjp-strengthens-in-solapur-as-40-sena-leaders-join-with-shivaji-sawant-bdk97</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/mns-alliance-risk-municipal-elections-uddhav-thackeray-warning-dk88-rc70</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>सोलापुरात भाजपची शिंदेंच्या शिवसेनावर कुरघोडी शिवाजी सावंतांनी शिवसेना सोडली,</t>
+          <t>अमित शहा हे महाराष्ट्रातल्या गुंडांचे आणि भ्रष्टाचाऱ्यांचे दिल्लीतले सेनापती, संजय राऊत यांचा घणाघात</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/solapur-shivaji-sawant-leaves-shiv-sena-and-bjp-entry-confirmed-devendra-fadnavis-bjp-attack-on-eknath-shinde-shiv-sena-in-solapur-1377928</t>
+          <t>https://www.saamana.com/amit-shah-is-leader-of-maharashtra-corrupt-leader-says-sanjay-raut/</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>सोलापूरच्या राजकारणात मोठी खळबळ; तानाजी सावंत यांचा भाऊ करणार भाजपात प्रवेश</t>
+          <t>Sanjay Raut : निसाकाचा संघर्ष उफाळला, अनिल कदमांनी साकडं घातलं आता संजय राऊत मैदानात</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/big-stir-in-solapur-politics-tanaji-sawants-brother-to-join-bjp/129377/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/niphad-sugar-factory-crisis-sanjay-raut-anil-kadam-memorandum-farmers-workers-protest-nashik-gs97</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Rohit Pawar on Sanjay Shirsath: रोहित पवारांचे मंत्री संजय शिरसाटांवर भ्रष्टाचाराचे गंभीर आरोप; पहा काय म्हणाले</t>
+          <t>राधाकृष्णन यांना राज्यातील सर्वपक्षीय खासदारांनी पाठिंबा द्यावा</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/amp</t>
+          <t>https://dainikekmat.com/radhakrishnan-should-be-supported-by-mps-from-all-parties-in-the-state/114185/</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Rohit Pawar: मंत्री संजय शिरसाटांनी केला ५ हजार कोटींचा घोटाळा; आमदार रोहित पवारांच्या आरोपाने खळबळ</t>
+          <t>22-kg Golden Kalash Installed at Sant Dnyaneshwar Temple, Crafted by Shripad Shankar Nagarkar Jewellers Pune</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/rohit-pawar-alleges-sanjay-shirsat-over-5000-crore-worth-land-to-bivalkar-family/</t>
+          <t>https://www.tribuneindia.com/news/business/22-kg-golden-kalash-installed-at-sant-dnyaneshwar-temple-crafted-by-shripad-shankar-nagarkar-jewellers-pune/</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Shivsena | नाराजी भोवली! शिंदे गटातून बड्या नेत्याचा राजीनामा, राजकीय वर्तुळात खळबळ</t>
+          <t>उप-राष्ट्रपति चुनाव: देवेंद्र फडणवीस का 'मराठी अस्मिता' वाला दांव, क्या करेंगे उद्धव ठाकरे और शरद पवार?</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>https://www.thodkyaat.com/big-setback-for-eknath-shinde-faction-as-senior-leader-shivaji-sawant-joins-bjp-ahead-of-local-body-polls/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%89%E0%A4%AA-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A4%AA%E0%A4%A4-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%85%E0%A4%B8%E0%A5%8D%E0%A4%AE-%E0%A4%A4-%E0%A4%B5-%E0%A4%B2-%E0%A4%A6-%E0%A4%82%E0%A4%B5-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%94%E0%A4%B0-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0/ar-AA1KJ5pi</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Ekanath Shinde Shivsena : शिंदे गटाला धक्का; आमदाराचा भाऊ व 40 पदाधिकाऱ्यांचा पक्षप्रवेश</t>
+          <t>Demand to release list of property-holders affected due to road-widening in 5 days</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>https://www.lokshahi.com/news/mla-tanaji-sawants-brother-shivaji-sawant-has-decided-to-quit-the-group-and-join-the-bjp</t>
+          <t>https://www.lokmattimes.com/aurangabad/demand-to-release-list-of-property-holders-affected-due-to-road-widening-in-5-days/</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>NCP demands : राज्यात ओला दुष्काळ जाहीर करा अन्…; राष्ट्रवादी शरद पवार गटाची मागणी</t>
+          <t>Maharashtra Politics: Rohit Pawar Alleges ₹5,000-Crore Land Scam Against Minister Sanjay Shirsat</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/heavy-rains-wreak-havoc-in-maharashtra-sharad-pawar-ncp-demands-wet-drought-declaration-and-farmer-relief/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-rohit-pawar-alleges-5000-crore-land-scam-against-minister-sanjay-shirsat</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>शिंदे गटाचे आमदार तानाजी सावंतांचे बंधू भाजपच्या वाटेवर</t>
+          <t>Sanjay Shirsat : मंत्री शिरसाट यांच्यावर ५ हजार कोटींच्या जमीन घोटाळ्याचा आरोप</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>https://pcbtoday.in/%E0%A4%B6%E0%A4%BF%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%97%E0%A4%9F%E0%A4%BE%E0%A4%9A%E0%A5%87-%E0%A4%86%E0%A4%AE%E0%A4%A6%E0%A4%BE%E0%A4%B0-%E0%A4%A4%E0%A4%BE%E0%A4%A8%E0%A4%BE%E0%A4%9C%E0%A5%80/</t>
+          <t>https://pudhari.news/maharashtra/mumbai/minister-shirsat-accused-of-rs-5000-crore-land-scam-np88</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Rajnath reaches out to DMK, TMC, BJD for consensus on VP nominee</t>
+          <t>'ऑपरेशन लोटस वगैरे काही नाही; लवकरच ऑपरेशन टायगर दिसेल', सोलापूरच्या राजकारणात पडद्यामागे काय घडतंय?</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/rajnath-reaches-out-to-dmk-tmc-bjd-for-consensus-on-vp-nominee/articleshow/123373035.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%B2-%E0%A4%9F%E0%A4%B8-%E0%A4%B5%E0%A4%97%E0%A5%88%E0%A4%B0%E0%A5%87-%E0%A4%95-%E0%A4%B9-%E0%A4%A8-%E0%A4%B9-%E0%A4%B2%E0%A4%B5%E0%A4%95%E0%A4%B0%E0%A4%9A-%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%9F-%E0%A4%AF%E0%A4%97%E0%A4%B0-%E0%A4%A6-%E0%A4%B8%E0%A5%87%E0%A4%B2-%E0%A4%B8-%E0%A4%B2-%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B0-%E0%A4%9C%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A4-%E0%A4%AA%E0%A4%A1%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%AE-%E0%A4%97%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%98%E0%A4%A1%E0%A4%A4%E0%A4%82%E0%A4%AF/ar-AA1KKoUc</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>MSRTC और पुलिस की पहल, गढ़चिरौली के आदिवासी गांव को मिला पहला सार्वजनिक परिवहन, ग्रामीणों ने लहराया तिरंगा</t>
+          <t>Mumbai Rain Mayhem: City Comes To Standstill As Life Thrown Out Of Gear; MonoRail Gets Stuck</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/news/india-news/photo/initiative-of-msrtc-and-police-tribal-village-of-gadchiroli-gets-first-public-transport-1558</t>
+          <t>https://www.etvbharat.com/en/!state/mumbai-rains-update-august-19-govt-semi-govt-offices-shut-bmc-urges-wfh-for-pvt-employees-enn25081901231</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>LIVE Update : मुंबईतील सर्व शाळांना उद्या सुट्टी जाहीर</t>
+          <t>Heritage India: Iconic Sword of Maratha Commander Raghuji Raje Bhonsle Arrives in Mumbai</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/live-update-mumbai-rain-best-co-operative-soc-election-live-maharashtra-update-political-rain-update-devendra-fadnavis-ajit-pawar-eknath-shinde-uddhav-thackeray-raj-thackeray/913004/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-govt-brings-back-iconic-sword-of-maratha-commander-raghuji-raje-bhonsle-auctioned-for-rs-4715-lakh-to-mumbai-3685565</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>अमित शहा हे महाराष्ट्रातल्या गुंडांचे आणि भ्रष्टाचाऱ्यांचे दिल्लीतले सेनापती, संजय राऊत यांचा घणाघात</t>
+          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/amit-shah-is-leader-of-maharashtra-corrupt-leader-says-sanjay-raut/</t>
+          <t>https://www.ptinews.com/story/business/'third-mumbai'-to-boost-metropolitan-region-development:-fadnavis/2834902</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Sanjay Raut : निसाकाचा संघर्ष उफाळला, अनिल कदमांनी साकडं घातलं आता संजय राऊत मैदानात</t>
+          <t>Shortage of teachers hits rollout of NEP in govt, aided Maha colleges</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/niphad-sugar-factory-crisis-sanjay-raut-anil-kadam-memorandum-farmers-workers-protest-nashik-gs97</t>
+          <t>https://www.pressreader.com/india/hindustan-times-st-jaipur/20250819/281681145971378</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>राधाकृष्णन यांना राज्यातील सर्वपक्षीय खासदारांनी पाठिंबा द्यावा</t>
+          <t>कैसी होगी तीसरी मुंबई, कितनी बड़ी और कहां बन रही, सुविधाओं से लेकर प्लानिंग तक, CM फडणवीस ने सब बताया</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/radhakrishnan-should-be-supported-by-mps-from-all-parties-in-the-state/114185/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%95%E0%A5%88%E0%A4%B8-%E0%A4%B9-%E0%A4%97-%E0%A4%A4-%E0%A4%B8%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%95-%E0%A4%A4%E0%A4%A8-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%94%E0%A4%B0-%E0%A4%95%E0%A4%B9-%E0%A4%82-%E0%A4%AC%E0%A4%A8-%E0%A4%B0%E0%A4%B9-%E0%A4%B8%E0%A5%81%E0%A4%B5-%E0%A4%A7-%E0%A4%93%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AA%E0%A5%8D%E0%A4%B2-%E0%A4%A8-%E0%A4%82%E0%A4%97-%E0%A4%A4%E0%A4%95-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%AF/ar-AA1KLMl6?ocid=finance-verthp-feeds</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>उपराष्ट्रपतीपदाचे एनडीए उमेदवार सीपी राधाकृष्णन यांच्यावर राजकीय पक्षांच्या प्रतिक्रिया</t>
+          <t>महाराष्ट्र के बीड, लातूर और नांदेड में भारी बारिश से बाढ़ की स्थिति गंभीर, NDRF और सेना तैनात</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/parties-reaction-to-nda-vice-presidential-candidate-cp-radhakrishnan/</t>
+          <t>https://navbharattimes.indiatimes.com/state/maharashtra/pune/heavy-rains-in-maharashtra-flood-havoc-in-beed-latur-and-nanded-ndrf-and-army-deployed/articleshow/123370629.cms</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>22-kg Golden Kalash Installed at Sant Dnyaneshwar Temple, Crafted by Shripad Shankar Nagarkar Jewellers Pune</t>
+          <t>मराठा सेनापति रघुजी भोंसले की तलवार मुंबई पहुंची</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/business/22-kg-golden-kalash-installed-at-sant-dnyaneshwar-temple-crafted-by-shripad-shankar-nagarkar-jewellers-pune/</t>
+          <t>https://www.livehindustan.com/ncr/new-delhi/story-historic-sword-of-maratha-general-raghuji-bhosale-i-repatriated-to-mumbai-201755537654676.html</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>उप-राष्ट्रपति चुनाव: देवेंद्र फडणवीस का 'मराठी अस्मिता' वाला दांव, क्या करेंगे उद्धव ठाकरे और शरद पवार?</t>
+          <t>महाराष्ट्र में भारी बारिश से सात लोगों की मौत, 200 ग्रामीण फंसे</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%89%E0%A4%AA-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A4%AA%E0%A4%A4-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%85%E0%A4%B8%E0%A5%8D%E0%A4%AE-%E0%A4%A4-%E0%A4%B5-%E0%A4%B2-%E0%A4%A6-%E0%A4%82%E0%A4%B5-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%94%E0%A4%B0-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0/ar-AA1KJ5pi</t>
+          <t>https://hindi.theprint.in/india/seven-people-died-due-to-heavy-rains-in-maharashtra-200-villagers-stranded/856903/?amp</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Heavy rainfall causes 7 deaths, crop loss in Maharashtra as alerts continue</t>
+          <t>महाराष्ट्र में माफ हो सकते हैं पुराने ट्रैफिक चालान, माफी योजना लाने की तैयारी में सरकार</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/heavy-rainfall-causes-7-deaths-crop-loss-in-maharashtra-as-alerts-continue/articleshow/123368187.cms</t>
+          <t>https://navbharattimes.indiatimes.com/government-schemes/others/maharashtra-government-is-set-to-roll-out-an-amnesty-scheme-for-one-time-settlement-of-pending-traffic-challan/articleshow/123367444.cms</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Demand to release list of property-holders affected due to road-widening in 5 days</t>
+          <t>Third Mumbai महानगर क्षेत्राच्या विकासाचा नवा अध्याय असेल; मुख्यमंत्र्यांनी सांगितलं कशी असेल ‘तिसरी मुंबई’ Third Mumbai in Raigad district to boost metropolitan region development said Devendra Fadnavis</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/aurangabad/demand-to-release-list-of-property-holders-affected-due-to-road-widening-in-5-days/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/third-mumbai-in-raigad-district-to-boost-metropolitan-region-development-said-devendra-fadnavis-89724</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: Rohit Pawar Alleges ₹5,000-Crore Land Scam Against Minister Sanjay Shirsat</t>
+          <t>Maharashtra Rains: महाराष्ट्र में बाढ़ से हालात गंभीर, मराठवाड़ा में NDRF और सेना तैनात, सरकार की क्या है तैयारी?</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-rohit-pawar-alleges-5000-crore-land-scam-against-minister-sanjay-shirsat</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/mumbai-heavy-rain-maharashtra-flood-situation-serious-ndrf-and-indian-army-deployed-in-marathwada/articleshow/123370824.cms</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Sanjay Shirsat : मंत्री शिरसाट यांच्यावर ५ हजार कोटींच्या जमीन घोटाळ्याचा आरोप</t>
+          <t>राज्यातील पूरस्थितीवर सरकारचे लक्ष, मदत कार्य सुरू – बावनकुळे</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/minister-shirsat-accused-of-rs-5000-crore-land-scam-np88</t>
+          <t>https://www.loksatta.com/nagpur/governments-attention-on-flood-situation-in-the-state-information-from-chandrashekhar-bawankule-amy-95-5313292/</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>'ऑपरेशन लोटस वगैरे काही नाही; लवकरच ऑपरेशन टायगर दिसेल', सोलापूरच्या राजकारणात पडद्यामागे काय घडतंय?</t>
+          <t>‘पीएम आवास’च्या तीस लाख घरांना मोफत वीज; राज्य सरकार देणार ५० हजारांचे अनुदान: मुख्यमंत्री</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%B2-%E0%A4%9F%E0%A4%B8-%E0%A4%B5%E0%A4%97%E0%A5%88%E0%A4%B0%E0%A5%87-%E0%A4%95-%E0%A4%B9-%E0%A4%A8-%E0%A4%B9-%E0%A4%B2%E0%A4%B5%E0%A4%95%E0%A4%B0%E0%A4%9A-%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%9F-%E0%A4%AF%E0%A4%97%E0%A4%B0-%E0%A4%A6-%E0%A4%B8%E0%A5%87%E0%A4%B2-%E0%A4%B8-%E0%A4%B2-%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B0-%E0%A4%9C%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A4-%E0%A4%AA%E0%A4%A1%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%AE-%E0%A4%97%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%98%E0%A4%A1%E0%A4%A4%E0%A4%82%E0%A4%AF/ar-AA1KKoUc</t>
+          <t>https://www.lokmat.com/maharashtra/free-electricity-to-three-lakh-houses-of-pm-awas-yojana-state-government-will-provide-subsidy-of-rs-50-thousand-chief-minister-a-a747/</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Mumbai Rain Mayhem: City Comes To Standstill As Life Thrown Out Of Gear; MonoRail Gets Stuck</t>
+          <t>Maharashtra Government: शेतकऱ्यांना मिळणार गुड न्यूज: बळीराजासाठी सरकार मोठा निर्णय घेण्याच्या तयारीत</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!state/mumbai-rains-update-august-19-govt-semi-govt-offices-shut-bmc-urges-wfh-for-pvt-employees-enn25081901231</t>
+          <t>https://saamtv.esakal.com/maharashtra/sanjay-rathod-big-statement-on-loan-waiver-maharashtra-farmers-get-loan-waiver-minister-give-hint-in-award-ceremony-program-yavatmal-pusad-bbj88</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Heritage India: Iconic Sword of Maratha Commander Raghuji Raje Bhonsle Arrives in Mumbai</t>
+          <t>कोल्हापुर में शुरू हुई बॉम्बे हाईकोर्ट की नई खंडपीठ, सीजेआई बोले– महाराष्ट्र न्यायिक ढांचे में आगे</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-govt-brings-back-iconic-sword-of-maratha-commander-raghuji-raje-bhonsle-auctioned-for-rs-4715-lakh-to-mumbai-3685565</t>
+          <t>https://mpbreakingnews.in/maharashtra/bombay-high-court-kolhapur-bench-cji-b-r-gavai-maharashtra-government-54-803927</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
+          <t>श्रीमती प्रज्ञा वाळकेंचा भ्रष्टाचारामध्ये उच्चांक ; सरकारविरोधी चळवळीतीही सक्रिय सहभाग ?</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/business/'third-mumbai'-to-boost-metropolitan-region-development:-fadnavis/2834902</t>
+          <t>https://lokmanthan.com/mrs-pragya-walkens-high-score-in-corruption-active-participation-in-anti-government-movement/</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Maha CM asks agencies to be on alert mode after heavy rainfall and flash floods - Sakshi Post</t>
+          <t>देशभर में बारिश का कहर: मुंबई-बेहद जाम, दिल्ली में यमुना उफान पर, स्कूल-कॉलेज बंद</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/maha-cm-asks-agencies-be-alert-mode-after-heavy-rainfall-and-flash-floods-441978</t>
+          <t>https://dainikdehat.com/india/rain-wreaks-havoc-across-the-country-mumbai-is-jam-packed-yamuna-is-in-spate-in-delhi-schools-and-colleges-are-closed/</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Shortage of teachers hits rollout of NEP in govt, aided Maha colleges</t>
+          <t>मुंबई झोपडपट्टीमुक्त होणार का? जलद पुनर्विकासाचा मुख्यमंत्र्यांनी काय सांगितला प्लॅन?</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>https://www.pressreader.com/india/hindustan-times-st-jaipur/20250819/281681145971378</t>
+          <t>https://www.tendernama.com/mahatender/mumbai/will-mumbai-become-slum-free-what-is-the-chief-ministers-plan-for-rapid-redevelopment</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Maha govt waives Stamp Duty worth Rs 38.99 lakh for Tata Cancer Hospital in Raigad (Ld)</t>
+          <t>Mumbai Chawl Redevelopment | चाळ झाली आधुनिक वस्ती</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/india/maha-govt-waives-stamp-duty-worth-rs-3899-lakh-for-tata-cancer-hospital-in-raigad-ld</t>
+          <t>https://pudhari.news/sampadakiy/mumbai-chawl-redevelopment-displaced-workers-problem-sp96</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>कैसी होगी तीसरी मुंबई, कितनी बड़ी और कहां बन रही, सुविधाओं से लेकर प्लानिंग तक, CM फडणवीस ने सब बताया</t>
+          <t>Heavy Rains Batter Mumbai: Red Alert Issued, Schools and Colleges Closed on August 19 in Thane and...</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%95%E0%A5%88%E0%A4%B8-%E0%A4%B9-%E0%A4%97-%E0%A4%A4-%E0%A4%B8%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%95-%E0%A4%A4%E0%A4%A8-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%94%E0%A4%B0-%E0%A4%95%E0%A4%B9-%E0%A4%82-%E0%A4%AC%E0%A4%A8-%E0%A4%B0%E0%A4%B9-%E0%A4%B8%E0%A5%81%E0%A4%B5-%E0%A4%A7-%E0%A4%93%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AA%E0%A5%8D%E0%A4%B2-%E0%A4%A8-%E0%A4%82%E0%A4%97-%E0%A4%A4%E0%A4%95-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%AF/ar-AA1KLMl6?ocid=finance-verthp-feeds</t>
+          <t>https://www.thehansindia.com/news/national/heavy-rains-batter-mumbai-red-alert-issued-schools-and-colleges-closed-on-august-19-in-thane-and-palghar-998357</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Maharashtra: मंत्री शंभूराज देसाई को मिला बचपन वाला वही सरकारी बंगला, मां के जन्मदिन पर किया भावुक गृहप्रवेश</t>
+          <t>Mumbai Rains: Are Private and Public offices shut today? BMC issues statement, says...</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%B6%E0%A4%82%E0%A4%AD%E0%A5%82%E0%A4%B0-%E0%A4%9C-%E0%A4%A6%E0%A5%87%E0%A4%B8-%E0%A4%88-%E0%A4%95-%E0%A4%AE-%E0%A4%B2-%E0%A4%AC%E0%A4%9A%E0%A4%AA%E0%A4%A8-%E0%A4%B5-%E0%A4%B2-%E0%A4%B5%E0%A4%B9-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%AC%E0%A4%82%E0%A4%97%E0%A4%B2-%E0%A4%AE-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%9C%E0%A4%A8%E0%A5%8D%E0%A4%AE%E0%A4%A6-%E0%A4%A8-%E0%A4%AA%E0%A4%B0-%E0%A4%95-%E0%A4%AF-%E0%A4%AD-%E0%A4%B5%E0%A5%81%E0%A4%95-%E0%A4%97%E0%A5%83%E0%A4%B9%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6/ar-AA1JRinD?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.india.com/news/india/mumbai-rains-are-private-and-public-offices-shut-today-bmc-work-from-home-schools-colleges-devendra-fadnavis-markets-8019561/</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>महाराष्ट्र के बीड, लातूर और नांदेड में भारी बारिश से बाढ़ की स्थिति गंभीर, NDRF और सेना तैनात</t>
+          <t>Surya Roshni to invest Rs 25 cr for biz expansion</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/maharashtra/pune/heavy-rains-in-maharashtra-flood-havoc-in-beed-latur-and-nanded-ndrf-and-army-deployed/articleshow/123370629.cms</t>
+          <t>https://www.theweek.in/wire-updates/business/2025/08/18/dcm62-biz-briefs-3.html</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में माफ हो सकते हैं पुराने ट्रैफिक चालान, माफी योजना लाने की तैयारी में सरकार</t>
+          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/government-schemes/others/maharashtra-government-is-set-to-roll-out-an-amnesty-scheme-for-one-time-settlement-of-pending-traffic-challan/articleshow/123367444.cms</t>
+          <t>https://www.newsdrum.in/business/third-mumbai-to-boost-metropolitan-region-development-fadnavis-9674858</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Maharashtra Rains: महाराष्ट्र में बाढ़ से हालात गंभीर, मराठवाड़ा में NDRF और सेना तैनात, सरकार की क्या है तैयारी?</t>
+          <t>'Third Mumbai' to boost MMR development, says Fadnavis; invites pvt sector to join in its creation</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/mumbai-heavy-rain-maharashtra-flood-situation-serious-ndrf-and-indian-army-deployed-in-marathwada/articleshow/123370824.cms</t>
+          <t>https://www.newsdrum.in/business/third-mumbai-to-boost-mmr-development-says-fadnavis-invites-pvt-sector-to-join-in-its-creation-9674122</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>मराठा सेनापति रघुजी भोंसले की तलवार मुंबई पहुंची</t>
+          <t>मुंबई में भारी बारिश के बीच सुचारू रूप से चल रही मेट्रो, सीएम फडणवीस ने की तारीफ</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/ncr/new-delhi/story-historic-sword-of-maratha-general-raghuji-bhosale-i-repatriated-to-mumbai-201755537654676.html</t>
+          <t>https://www.m.khaskhabar.com/news/news-metro-running-smoothly-amid-heavy-rains-in-mumbai-cm-fadnavis-praised-news-hindi-1-745323-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Third Mumbai महानगर क्षेत्राच्या विकासाचा नवा अध्याय असेल; मुख्यमंत्र्यांनी सांगितलं कशी असेल ‘तिसरी मुंबई’ Third Mumbai in Raigad district to boost metropolitan region development said Devendra Fadnavis</t>
+          <t>Asia Cup 2025: पाकिस्तान क्रिकेट के मुख्य चयनकर्ता का बड़ा बयान, बोले- भारत को हराएगा पाकिस्तान</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/third-mumbai-in-raigad-district-to-boost-metropolitan-region-development-said-devendra-fadnavis-89724</t>
+          <t>https://www.indiatv.in/video/sports/asia-cup-2025-2025-08-18-1156799</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>राज्यातील पूरस्थितीवर सरकारचे लक्ष, मदत कार्य सुरू – बावनकुळे</t>
+          <t>मानसून में हाल बेहाल, भारी बारिश से इस राज्य में जगह-जगह भरा पानी, स्कूल-कॉलेज किए बंद</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/governments-attention-on-flood-situation-in-the-state-information-from-chandrashekhar-bawankule-amy-95-5313292/</t>
+          <t>https://www.patrika.com/national-news/heavy-rain-alert-in-mumbai-monsoon-gained-momentum-know-imd-weather-update-19874723</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>‘पीएम आवास’च्या तीस लाख घरांना मोफत वीज; राज्य सरकार देणार ५० हजारांचे अनुदान: मुख्यमंत्री</t>
+          <t>How much rain did Mumbai receive on Monday? Check area-wise list</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/free-electricity-to-three-lakh-houses-of-pm-awas-yojana-state-government-will-provide-subsidy-of-rs-50-thousand-chief-minister-a-a747/</t>
+          <t>https://indianexpress.com/article/cities/mumbai/how-much-rain-did-mumbai-areas-receive-on-monday-check-list-bandra-juhu-chembur-10196732/</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Maharashtra Government: शेतकऱ्यांना मिळणार गुड न्यूज: बळीराजासाठी सरकार मोठा निर्णय घेण्याच्या तयारीत</t>
+          <t>Ahead of Civic Polls, Hitendra Thakur Backs Loyalists: ‘My Karyakarta Is With Me, They Ensure Our Party Wins</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/sanjay-rathod-big-statement-on-loan-waiver-maharashtra-farmers-get-loan-waiver-minister-give-hint-in-award-ceremony-program-yavatmal-pusad-bbj88</t>
+          <t>https://www.lokmattimes.com/maharashtra/ahead-of-civic-polls-hitendra-thakur-backs-loyalists-my-karyakarta-is-with-me-they-ensure-our-party-wins-a475/</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Crop Loss: महाराष्‍ट्र में बारिश ने किया किसानों को बर्बाद, विदर्भ से लेकर मराठवाड़ा तक फसलें चौपट</t>
+          <t>NCP (SP) targets Maha minister over Rs 5,000 cr scam in Navi Mumbai’s CIDCO land; demands his resignation</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/heavy-rains-in-maharashtra-cause-huge-damage-to-farmers-after-crop-loss-and-land-submerged-in-water-1263471-2025-08-19</t>
+          <t>https://www.socialnews.xyz/2025/08/18/ncp-sp-targets-maha-minister-over-rs-5000-cr-scam-in-navi-mumbais-cidco-land-demands-his-resignation/</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>कोल्हापुर में शुरू हुई बॉम्बे हाईकोर्ट की नई खंडपीठ, सीजेआई बोले– महाराष्ट्र न्यायिक ढांचे में आगे</t>
+          <t>CM to join Kawad yatra, TV center chowk shut for 5 hours</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/maharashtra/bombay-high-court-kolhapur-bench-cji-b-r-gavai-maharashtra-government-54-803927</t>
+          <t>https://www.lokmattimes.com/aurangabad/cm-to-join-kawad-yatra-tv-center-chowk-shut-for-5-hours/</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>श्रीमती प्रज्ञा वाळकेंचा भ्रष्टाचारामध्ये उच्चांक ; सरकारविरोधी चळवळीतीही सक्रिय सहभाग ?</t>
+          <t>Maha govt plans amnesty scheme to recover pending transport fines</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>https://lokmanthan.com/mrs-pragya-walkens-high-score-in-corruption-active-participation-in-anti-government-movement/</t>
+          <t>https://www.socialnews.xyz/2025/08/18/maha-govt-plans-amnesty-scheme-to-recover-pending-transport-fines/</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>देशभर में बारिश का कहर: मुंबई-बेहद जाम, दिल्ली में यमुना उफान पर, स्कूल-कॉलेज बंद</t>
+          <t>चुनाव के बाद होगा महामंडलों का वितरण, महायुति के इच्छुक नेताओं पर प्रदर्शन का दबाव</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>https://dainikdehat.com/india/rain-wreaks-havoc-across-the-country-mumbai-is-jam-packed-yamuna-is-in-spate-in-delhi-schools-and-colleges-are-closed/</t>
+          <t>https://navbharatlive.com/maharashtra/nagpur/distribution-of-maha-mandals-will-happen-after-the-elections-pressure-of-demonstration-on-the-aspiring-leaders-of-mahayuti-1322474.html</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>मुंबई झोपडपट्टीमुक्त होणार का? जलद पुनर्विकासाचा मुख्यमंत्र्यांनी काय सांगितला प्लॅन?</t>
+          <t>राज्यात ओला दुष्काळ जाहीर करा, विशेष अधिवेशन बोलवा मुसळधार पावसानंतर शरद पवारांच्या</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>https://www.tendernama.com/mahatender/mumbai/will-mumbai-become-slum-free-what-is-the-chief-ministers-plan-for-rapid-redevelopment</t>
+          <t>https://marathi.abplive.com/news/politics/sharad-pawar-ncp-demands-after-heavy-rains-declaring-a-wet-drought-in-the-state-calling-a-special-session-shashikant-shinde-1377947</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Mumbai Chawl Redevelopment | चाळ झाली आधुनिक वस्ती</t>
+          <t>सिडको जमिन वाटप प्रकरणावरून राजकारण तापले; पवारांचा शिरसाठांवर घणाघाती हल्ला</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>https://pudhari.news/sampadakiy/mumbai-chawl-redevelopment-displaced-workers-problem-sp96</t>
+          <t>https://civicmirror.in/maharashtra/politics-heats-up-over-cidco-land-allocation-issue-pawar-attacks-shirsath/</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Heavy Rains Batter Mumbai: Red Alert Issued, Schools and Colleges Closed on August 19 in Thane and...</t>
+          <t>'Destroying constitutional institutions': Nishikant Dubey slams Rahul Gandhi as SC dismisses plea challenging 2024 Maharashtra polls</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/news/national/heavy-rains-batter-mumbai-red-alert-issued-schools-and-colleges-closed-on-august-19-in-thane-and-palghar-998357</t>
+          <t>https://www.bignewsnetwork.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Mumbai Rains: Are Private and Public offices shut today? BMC issues statement, says...</t>
+          <t>Mumbai Rain LIVE Updates: मुंबईत सखल भागात साचलेल्या पाण्याचा निचरा</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>https://www.india.com/news/india/mumbai-rains-are-private-and-public-offices-shut-today-bmc-work-from-home-schools-colleges-devendra-fadnavis-markets-8019561/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/mumbai-rain-live-updates-18-august-imd-red-alert-in-mumbai-weather-waterlogging-traffic-jam-local-train-train-latest-updates-in-marathi-933169</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Surya Roshni to invest Rs 25 cr for biz expansion</t>
+          <t>'उपराष्ट्रपती'साठी महाराष्ट्राच्या राज्यपालांचे नाव; फडणवीसांचे खासदारांना आवाहन, पवार-ठाकरेंना टोला</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/business/2025/08/18/dcm62-biz-briefs-3.html</t>
+          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-urges-mps-to-support-radhakrishnan-targets-uddhav-thackeray-and-sharad-pawar-035137.html?ref_source=OI-MR&amp;ref_medium=Home-Page&amp;ref_campaign=News-Cards</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
+          <t>मुंबई में कबूतरखानों पर विवाद, महापालिका ने नागरिकों से आपत्तियां और सुझाव मांगे</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/business/third-mumbai-to-boost-metropolitan-region-development-fadnavis-9674858</t>
+          <t>https://mpbreakingnews.in/maharashtra/mumbai-municipal-corporation-pigeon-shelters-public-consultation-high-court-54-803921</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Mumbai got 177mm rain in 6-8 hour period, says CM; all agencies asked to remain alert</t>
+          <t>Maharashtra govt plans amnesty scheme to recover pending transport fines</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/mumbai-got-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert-9673094</t>
+          <t>https://auto.economictimes.indiatimes.com/amp/news/industry/maharashtras-new-amnesty-scheme-settle-transport-fines-and-save-big/123364146</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>How much rain did Mumbai receive on Monday? Check area-wise list</t>
+          <t>Over ₹6.52 Crore Medical Aid Distributed To 5,000 Beneficiaries In Pune District</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/how-much-rain-did-mumbai-areas-receive-on-monday-check-list-bandra-juhu-chembur-10196732/</t>
+          <t>https://www.mypunepulse.com/over-%E2%82%B96-52-crore-medical-aid-distributed-to-5000-beneficiaries-in-pune-district/</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Nagpur’s Councils Starved Again: Pennies for a Region in Ruin</t>
+          <t>Pratap Sarnaik : राज्यातील वाहनांवर तब्‍बल 2500 कोटींचा दंड; सरकार एकरकमी परतफेडीची अभय योजना आणणार</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/08/18/nagpurs-councils-starved-again-pennies-for-a-region-in-ruin/</t>
+          <t>https://www.dainikprabhat.com/fines-of-around-rs-2500-crore-on-vehicles-in-the-state-government-to-introduce-a-lump-sum-repayment-scheme/</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>CM to join Kawad yatra, TV center chowk shut for 5 hours</t>
+          <t>Nagpur’s Councils Starved Again: Pennies for a Region in Ruin</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/aurangabad/cm-to-join-kawad-yatra-tv-center-chowk-shut-for-5-hours/</t>
+          <t>https://thelivenagpur.com/2025/08/18/nagpurs-councils-starved-again-pennies-for-a-region-in-ruin/</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>चुनाव के बाद होगा महामंडलों का वितरण, महायुति के इच्छुक नेताओं पर प्रदर्शन का दबाव</t>
+          <t>Cases from 6 districts to be heard | ‘A dream comes true after 40-45 years of struggle’: CJI inaugurates HC bench in Kolhapur</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/nagpur/distribution-of-maha-mandals-will-happen-after-the-elections-pressure-of-demonstration-on-the-aspiring-leaders-of-mahayuti-1322474.html</t>
+          <t>https://indianexpress.com/article/cities/pune/cases-dream-struggle-cji-inaugurates-hc-bench-kolhapur-10195928/</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>राज्यात ओला दुष्काळ जाहीर करा, विशेष अधिवेशन बोलवा मुसळधार पावसानंतर शरद पवारांच्या</t>
+          <t>Maratha commander Raghuji Bhonsle's sword brought to Mumbai!!</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/sharad-pawar-ncp-demands-after-heavy-rains-declaring-a-wet-drought-in-the-state-calling-a-special-session-shashikant-shinde-1377947</t>
+          <t>https://www.indiaherald.com/Breaking/Read/994842382/Maratha-commander-Raghuji-Bhonsles-sword-brought-to-Mumbai</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Kokan Politics : शरद पवार गटाला धक्का; प्रदेश सरचिटणीस प्रशांत यादव भाजपाच्या वाटेवर</t>
+          <t>CJI Gavai: "Maharashtra Govt At Forefront Of Efforts To Provide Infrastructure For Judiciary"</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/kokan-politics-sharad-pawar-group-suffers-setback-state-general-secretary-prashant-yadav-on-bjps-path/</t>
+          <t>https://lawchakra.in/legal-updates/cji-gavai-infrastructure-for-judiciary/</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>सिडको जमिन वाटप प्रकरणावरून राजकारण तापले; पवारांचा शिरसाठांवर घणाघाती हल्ला</t>
+          <t>Maratha general Raghuji Bhonsle's sword brought to Mumbai</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/politics-heats-up-over-cidco-land-allocation-issue-pawar-attacks-shirsath/</t>
+          <t>https://english.metrovaartha.com/news/mumbai/maratha-general-raghuji-bhonsles-sword-brought-to-mumbai</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Rohit Pawar on Sanjay Shirsath: रोहित पवारांचे मंत्री संजय शिरसाटांवर भ्रष्टाचाराचे गंभीर आरोप; पहा काय म्हणाले</t>
+          <t>महाराष्ट्रातील 'या' जिल्ह्यात उभारणार 'स्टॅच्यू ऑफ युनिटी'; सरकारचा काय आहे प्लॅन?</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/</t>
+          <t>https://www.tendernama.com/mahatender/paschim-maharashtra/statue-of-unity-style-memorial-in-maharashtra-soon</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>'Destroying constitutional institutions': Nishikant Dubey slams Rahul Gandhi as SC dismisses plea challenging 2024 Maharashtra polls</t>
+          <t>मराठा सेनापति रघुजी भोंसले की तलवार मुंबई लाई गई</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
+          <t>https://hindi.theprint.in/india/maratha-commander-raghuji-bhosales-sword-brought-to-mumbai/856774/</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>India News | SC Dismisses Plea Alleging Discrepancies in 2024 Maharashtra Assembly Polls</t>
+          <t>Kolhapur : सरन्यायाधीश Bhushan Gavai यांच्या हस्ते सर्किट बेंच इमारतीचे उद्घाटन</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/india-news-sc-dismisses-plea-alleging-discrepancies-in-2024-maharashtra-assembly-polls-7065753.html</t>
+          <t>https://www.tarunbharat.com/kolhapur-circuit-bench-inauguration-with-chief-justice-bhushan-gavai-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Mumbai Rain LIVE Updates: मुंबईत सखल भागात साचलेल्या पाण्याचा निचरा</t>
+          <t>राज्य को बाढ़ आपदा घोषित करो… विशेष अधिवेशन बुलाओ… एनसीपी प्रदेश अध्यक्ष ने की सीएम से मांग</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/mumbai-rain-live-updates-18-august-imd-red-alert-in-mumbai-weather-waterlogging-traffic-jam-local-train-train-latest-updates-in-marathi-933169</t>
+          <t>https://www.hindisaamana.com/declare-the-state-a-flood-disaster-call-a-special-session-ncp-state-president-made-a-demand-to-the-cm/</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>मुंबई में कबूतरखानों पर विवाद, महापालिका ने नागरिकों से आपत्तियां और सुझाव मांगे</t>
+          <t>Revenue Minister बावनकुले का रुख</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/maharashtra/mumbai-municipal-corporation-pigeon-shelters-public-consultation-high-court-54-803921</t>
+          <t>https://jantaserishta.com/amp/local/maharashtra/revenue-minister-bawankules-stance-4218277</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Maharashtra govt plans amnesty scheme to recover pending transport fines</t>
+          <t>Shashikant Shinde on Heavy Rain: राज्यात अतिवृष्टीमुळे ओला दुष्काळ जाहीर करण्याची मागणी तीव्र</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>https://auto.economictimes.indiatimes.com/amp/news/industry/maharashtras-new-amnesty-scheme-settle-transport-fines-and-save-big/123364146</t>
+          <t>https://www.timemaharashtra.com/maharashtra/demand-to-declare-a-wet-drought-due-to-heavy-rains-in-the-state-is-strong/129359/</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Mah plans amnestyscheme to recoverpending transport fines</t>
+          <t>Ganesh Naik, Eknath Shinde, Thane, Maharashtra Politics</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/19/mah-plans-amnesty-scheme-to-recover-pending-transport-fines.html</t>
+          <t>https://mpbreakingnews.in/maharashtra/ganesh-naik-eknath-shinde-thane-maharashtra-politics-54-804112</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Pratap Sarnaik : राज्यातील वाहनांवर तब्‍बल 2500 कोटींचा दंड; सरकार एकरकमी परतफेडीची अभय योजना आणणार</t>
+          <t>मराठा सेनापति रघुजी भोंसले की तलवार मुंबई लाई गई, लंदन में हुई नीलामी में महाराष्ट्र सरकार ने हासिल की</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/fines-of-around-rs-2500-crore-on-vehicles-in-the-state-government-to-introduce-a-lump-sum-repayment-scheme/</t>
+          <t>https://samarsaleel.com/%E0%A4%AE%E0%A4%B0%E0%A4%BE%E0%A4%A0%E0%A4%BE-%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A4%BE%E0%A4%AA%E0%A4%A4%E0%A4%BF-%E0%A4%B0%E0%A4%98%E0%A5%81%E0%A4%9C%E0%A5%80-%E0%A4%AD%E0%A5%8B%E0%A4%82%E0%A4%B8/490978</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Cases from 6 districts to be heard | ‘A dream comes true after 40-45 years of struggle’: CJI inaugurates HC bench in Kolhapur</t>
+          <t>मराठा सेनापती रघुजी भोसले यांची तलवार मुंबईत आणली, लंडनमध्ये झालेल्या लिलावात महाराष्ट्र सरकारने घेतली</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/pune/cases-dream-struggle-cji-inaugurates-hc-bench-kolhapur-10195928/</t>
+          <t>https://marathi.webdunia.com/article/mumbai-news/maratha-commander-raghuji-bhonsle-s-sword-brought-to-mumbai-125081800027_1.html</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>CJI Gavai: "Maharashtra Govt At Forefront Of Efforts To Provide Infrastructure For Judiciary"</t>
+          <t>MONSOON UPDATE: १५ ते १६ जिल्ह्यांत रेड आणि ऑरेंज अलर्ट; CM DEVENDRA FADNAVIS म्हणाले…</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>https://lawchakra.in/legal-updates/cji-gavai-infrastructure-for-judiciary/</t>
+          <t>https://www.timemaharashtra.com/maharashtra/monsoon-update-red-and-orange-alert-in-15-to-16-districts-cm-devendra-fadnavis-said/129346/</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Maratha general Raghuji Bhonsle's sword brought to Mumbai</t>
+          <t>भाजप आमदाराचा डाव प्रशासनाने हाणून पाडला, आईच्या नावाने बांधलेले अम्मा स्मारक अवैध ठरवून हटवले</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>https://english.metrovaartha.com/news/mumbai/maratha-general-raghuji-bhonsles-sword-brought-to-mumbai</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/chandrapur-bjp-mla-kishor-jorgewar-faces-setback-as-administration-demolishes-illegal-amma-memorial-construction-as11-rc70</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>मराठा सेनापति रघुजी भोंसले की तलवार मुंबई लाई गई</t>
+          <t>मनसे कामगार संघटनेच्या अनेक पदाधिका-यांचा भाजपामध्ये प्रवेश</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/maratha-commander-raghuji-bhosales-sword-brought-to-mumbai/856774/</t>
+          <t>https://www.marathiebatmya.com/political/many-office-bearers-of-mns-workers-organization-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Revenue Minister बावनकुले का रुख</t>
+          <t>सीपी राधाकृष्णन के उपराष्ट्रपति उम्मीदवार बनाने पर कांग्रेस को लगी मिर्ची; INDI ब्लॉक भी जल्द कर सकता है प्रत्याशी का ऐलान</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/amp/local/maharashtra/revenue-minister-bawankules-stance-4218277</t>
+          <t>https://www.sudarshannews.in/news-detail.aspx?id=131383</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>राज्य को बाढ़ आपदा घोषित करो… विशेष अधिवेशन बुलाओ… एनसीपी प्रदेश अध्यक्ष ने की सीएम से मांग</t>
+          <t>MMRDA launches SCLR bridge, metro institute and flyovers to ease city commute</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/declare-the-state-a-flood-disaster-call-a-special-session-ncp-state-president-made-a-demand-to-the-cm/</t>
+          <t>https://propnewstime.com/getdetailsStories/MjA1NTQ=/mmrda-launches-sclr-bridge-metro-institute-and-flyovers-to-ease-city-commute</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Shashikant Shinde on Heavy Rain: राज्यात अतिवृष्टीमुळे ओला दुष्काळ जाहीर करण्याची मागणी तीव्र</t>
+          <t>DH Evening Brief | NDA VP pick in Delhi to meet BJP top brass, Opposition yet to finalise their candidate; I.N.D.I.A. bloc continues attacking EC chief over SIR</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/demand-to-declare-a-wet-drought-due-to-heavy-rains-in-the-state-is-strong/129359/</t>
+          <t>https://www.deccanherald.com/india/dh-evening-brief-nda-vp-pick-in-delhi-to-meet-bjp-top-brass-opposition-yet-to-finalise-their-candidate-india-bloc-continues-attacking-ec-chief-over-sir-3685866</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>मराठा सेनापती रघुजी भोसले यांची तलवार मुंबईत आणली, लंडनमध्ये झालेल्या लिलावात महाराष्ट्र सरकारने घेतली</t>
+          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/mumbai-news/maratha-commander-raghuji-bhonsle-s-sword-brought-to-mumbai-125081800027_1.html</t>
+          <t>https://www.ptinews.com/detail/business/-Third-Mumbai--to-boost-metropolitan-region-development--Fadnavis/2834902</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>राज्यात ओला दुष्काळ जाहीर करा</t>
+          <t>'Modi Govt Selling Dreams Of 2047, Ignoring Present': Rahul Gandhi Slams Centre After Maharashtra's Thane Train Tragedy</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%A4-%E0%A4%93%E0%A4%B2%E0%A4%BE-%E0%A4%A6%E0%A5%81%E0%A4%B7%E0%A5%8D%E0%A4%95%E0%A4%BE%E0%A4%B3-%E0%A4%9C%E0%A4%BE%E0%A4%B9%E0%A5%80/114152/</t>
+          <t>http://www.msn.com/en-in/news/India/modi-govt-selling-dreams-of-2047-ignoring-present-rahul-gandhi-slams-centre-after-maharashtras-thane-train-tragedy/ar-AA1Gm3WY?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>भाजप आमदाराचा डाव प्रशासनाने हाणून पाडला, आईच्या नावाने बांधलेले अम्मा स्मारक अवैध ठरवून हटवले</t>
+          <t>Rs 40kcr of investors’ money stuck with credit societies, Maharashtra govt to announce SOP for recovery</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/chandrapur-bjp-mla-kishor-jorgewar-faces-setback-as-administration-demolishes-illegal-amma-memorial-construction-as11-rc70</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/rs-40kcr-of-investors-money-stuck-with-credit-societies-maharashtra-govt-to-announce-sop-for-recovery/articleshow/123367502.cms</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>मनसे कामगार संघटनेच्या अनेक पदाधिका-यांचा भाजपामध्ये प्रवेश</t>
+          <t>Red alert issued as heavy rain batters Mumbai; schools and colleges closed due to waterlogging</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/many-office-bearers-of-mns-workers-organization-join-bjp/</t>
+          <t>https://ddnews.gov.in/en/red-alert-issued-as-heavy-rain-batters-mumbai-schools-and-colleges-closed-due-to-waterlogging/</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में यह क्या हुआ? एकनाथ शिंदे का साथ छोड़ BJP में शामिल हुए कई भरोसेमंद</t>
+          <t>Maha govt signs MoUs worth Rs 42,000 crore and creation of 28,000 jobs</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/eknath-shinde-shiv-sena-solapur-leaders-join-bjp-amid-internal-feud-2997781</t>
+          <t>https://www.thehawk.in/news/states-and-uts/maharashtra/maha-govt-signs-mous-worth-rs-42000-crore-and-creation-of-28000-jobs</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>सीपी राधाकृष्णन के उपराष्ट्रपति उम्मीदवार बनाने पर कांग्रेस को लगी मिर्ची; INDI ब्लॉक भी जल्द कर सकता है प्रत्याशी का ऐलान</t>
+          <t>NCP (SP) targets Maha minister over Rs 5,000 cr scam in Navi Mumbai’s CIDCO land; demands his resignation</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>https://www.sudarshannews.in/news-detail.aspx?id=131383</t>
+          <t>https://www.sakshipost.com/news/ncp-sp-targets-maha-minister-over-rs-5000-cr-scam-navi-mumbai-s-cidco-land-demands-his</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by Maharashtra CM Devendra Fadnavis</t>
+          <t>पंतप्रधान नरेंद्र मोदी आणि व्लादिमीर पुतीन यांच्यात संवाद - संघर्षाच्या शांततामय तोडग्यासाठी भारताचा ठाम पाठिंबा</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis/amp/?utm=relatedarticles</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/dialogue-between-prime-minister-narendra-modi-and-vladimir-putin-indias-strong-support-for-peaceful-resolution.html</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>'Modi Govt Selling Dreams Of 2047, Ignoring Present': Rahul Gandhi Slams Centre After Maharashtra's Thane Train Tragedy</t>
+          <t>वैविध्यपूर्ण विषयांवरील पुस्तक प्रकाशित करणे हे चपराकचं साहित्यिक आंदोलन; लेखक अभिराम भडकमकर यांचे प्रतिपादन</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/India/modi-govt-selling-dreams-of-2047-ignoring-present-rahul-gandhi-slams-centre-after-maharashtras-thane-train-tragedy/ar-AA1Gm3WY?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/publishing-books-on-diverse-topics-is-a-literary-movement-of-the-chaparak-author-abhiram-bhadkamkar-asserts.html</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Rs 40kcr of investors’ money stuck with credit societies, Maharashtra govt to announce SOP for recovery</t>
+          <t>ठाण्यात शालेय ९-साईड हॉकी लीगला सुरुवात ; ७६ संघांचा उत्साही सहभाग</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/rs-40kcr-of-investors-money-stuck-with-credit-societies-maharashtra-govt-to-announce-sop-for-recovery/articleshow/123367502.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/school-9-a-side-hockey-league-begins-in-thane-76-teams-participate-enthusiastically.html</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Red alert issued as heavy rain batters Mumbai; schools and colleges closed due to waterlogging</t>
+          <t>Rain fury: 5 missing, 200 stranded in Nanded; local trains, flights hit in Mumbai</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/en/red-alert-issued-as-heavy-rain-batters-mumbai-schools-and-colleges-closed-due-to-waterlogging/</t>
+          <t>https://www.ptinews.com/editor-detail/Rain-fury--5-missing--200-stranded-in-Nanded;-local-trains--flights-hit-in-Mumbai/2832995</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Maha govt signs MoUs worth Rs 42,000 crore and creation of 28,000 jobs</t>
+          <t>Aaj Ka Rashifal, 19 Aug, 2025 : आचार्य इंदु प्रकाश जी से जानिए आज क्या कह रहे हैं आपके सितारे</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/states-and-uts/maharashtra/maha-govt-signs-mous-worth-rs-42000-crore-and-creation-of-28000-jobs</t>
+          <t>https://www.indiatv.in/video/bhavishyawani/aaj-ka-rashifal-19-aug-2025-know-from-acharya-indu-prakash-ji-what-your-stars-are-saying-today-2025-08-19-1156865</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>NCP (SP) targets Maha minister over Rs 5,000 cr scam in Navi Mumbai’s CIDCO land; demands his resignation</t>
+          <t>सुप्रीम कोर्ट ने महाराष्ट्र विधानसभा चुनाव रद्द करने की मांग वाली याचिका की खारिज, विपक्ष को बड़ा झटका</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/ncp-sp-targets-maha-minister-over-rs-5000-cr-scam-navi-mumbai-s-cidco-land-demands-his</t>
+          <t>https://samacharnama.com/states/maharashtra-news/supreme-court-dismisses-plea-seeking-cancellation-of/cid17260970.htm</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>पंतप्रधान नरेंद्र मोदी आणि व्लादिमीर पुतीन यांच्यात संवाद - संघर्षाच्या शांततामय तोडग्यासाठी भारताचा ठाम पाठिंबा</t>
+          <t>Vice Presidential Election : उपराष्ट्रपती पदासाठी विरोधकांचा उमेदवार कोण? दिल्लीत घडामोडींना वेग; राहुल गांधी काय भूमिका घेणार?</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/dialogue-between-prime-minister-narendra-modi-and-vladimir-putin-indias-strong-support-for-peaceful-resolution.html</t>
+          <t>https://www.loksatta.com/desh-videsh/who-is-the-opposition-candidate-for-the-post-of-vice-president-events-in-delhi-are-gaining-momentum-what-decision-will-mallikarjun-kharge-take-gkt-96-5313155/</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>वैविध्यपूर्ण विषयांवरील पुस्तक प्रकाशित करणे हे चपराकचं साहित्यिक आंदोलन; लेखक अभिराम भडकमकर यांचे प्रतिपादन</t>
+          <t>Maharashtra politics : मुख्यमंत्र्यांच्या पत्नी गायिका, तरीही गाणे गाणाऱ्या तहसीलदारांना शिक्षा? बावनकुळे या चुकीला माफी असायलाच हवी; सामनातून हल्लाबोल</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/publishing-books-on-diverse-topics-is-a-literary-movement-of-the-chaparak-author-abhiram-bhadkamkar-asserts.html</t>
+          <t>https://sarkarnama.esakal.com/mumbai/nanded-tehsildar-prashant-thorat-suspension-shiv-sena-ubt-criticism-sanjay-raut-devendra-fadnavis-jap93</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>ठाण्यात शालेय ९-साईड हॉकी लीगला सुरुवात ; ७६ संघांचा उत्साही सहभाग</t>
+          <t>हवामानाचा अंदाज: आजही पावसाचा कहर? मुंबई, पुण्यासह 7 जिल्ह्यांना रेड अलर्ट; गडचिरोलीसह 4 जिल्ह्यांना यलो अलर्ट</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/school-9-a-side-hockey-league-begins-in-thane-76-teams-participate-enthusiastically.html</t>
+          <t>https://thefocusindia.com/national-news/maharashtra-weather-red-alert-mumbai-pune-7-districts-281414/amp/</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Rains Wreak Havoc Across States, Toll In Kishtwar Cloudburst Touches 63</t>
+          <t>पूजेसाठी परवानगी नाही, नमाजसाठी जागाच जागा; कम्युनिस्टांचा हिंदुविरोधी चेहरा पुन्हा समोर</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!bharat/rains-wreak-havoc-across-states-over-200-stranded-in-worst-hit-maharashtra-toll-in-kishtwar-cloudburst-touches-63-enn25081807219</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/no-permission-for-worship-plenty-of-space-for-namaz-cpims-different-rules-for-hindus-and-muslims-in-kerala-the.html</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Vice Presidential Election : उपराष्ट्रपती पदासाठी विरोधकांचा उमेदवार कोण? दिल्लीत घडामोडींना वेग; राहुल गांधी काय भूमिका घेणार?</t>
+          <t>Will Bajirao Mastani Come Alive in Movie Halls Today?</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/desh-videsh/who-is-the-opposition-candidate-for-the-post-of-vice-president-events-in-delhi-are-gaining-momentum-what-decision-will-mallikarjun-kharge-take-gkt-96-5313155/</t>
+          <t>https://caleidoscope.in/art-culture/will-bajirao-mastani-come-alive-in-movie-halls-today</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Maharashtra politics : मुख्यमंत्र्यांच्या पत्नी गायिका, तरीही गाणे गाणाऱ्या तहसीलदारांना शिक्षा? बावनकुळे या चुकीला माफी असायलाच हवी; सामनातून हल्लाबोल</t>
+          <t>Red alert in Mumbai; BMC shuts all afternoon schools, colleges</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/nanded-tehsildar-prashant-thorat-suspension-shiv-sena-ubt-criticism-sanjay-raut-devendra-fadnavis-jap93</t>
+          <t>https://www.newsbytesapp.com/news/india/mumbai-rain-havoc-to-continue-for-next-4-days/story</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>पूजेसाठी परवानगी नाही, नमाजसाठी जागाच जागा; कम्युनिस्टांचा हिंदुविरोधी चेहरा पुन्हा समोर</t>
+          <t>Nanded Rain: नांदेड़ में भारी बारिश के बाद 200 लोग बाढ़ में फंसे! बादल फटने से 5 लापता, रेस्क्यू के लिए सेना बुलाई गई</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/no-permission-for-worship-plenty-of-space-for-namaz-cpims-different-rules-for-hindus-and-muslims-in-kerala-the.html</t>
+          <t>https://hindi.moneycontrol.com/india/heavy-rains-in-maharashtra-nanded-leave-over-200-stranded-in-flood-waters-five-people-missing-article-2104052.html</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Shivaji Sawant : शिवाजी सावंतांचा भाजपा प्रवेश निश्चित !</t>
+          <t>फडणवीस ने राज्यपाल राधाकृष्णन से मुलाकात की, उन्हें शिवाजी महाराज के पत्रों की पुस्तक भेंट की</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/shivaji-sawants-admission-to-bjp-is-certain-281398/</t>
+          <t>https://www.ibc24.in/maharashtra/fadnavis-meets-governor-radhakrishnan-presents-him-with-a-book-containing-shivaji-maharajs-letters-3213010.html</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>मुसळधार पावसामुळे राज्यात सात जणांचा मत्यू; मुंबईत पावसामुळे जनजीवन विस्कळित</t>
+          <t>Maharashtra approves amendments for Dharavi project land transfer</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/mumbai-rains-updates-imd-red-alert-mumbai-city-suburbs-schools-and-colleges-remain-closed-today-mumbai-university-exams-postponed-to-23-august-maharashtra-rain-news-today-maharashtra-news-mhs25081900792</t>
+          <t>https://www.msn.com/en-in/news/India/maharashtra-approves-amendments-for-dharavi-project-land-transfer/ar-AA1G1ze9</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Will Bajirao Mastani Come Alive in Movie Halls Today?</t>
+          <t>What happened in the Trump-Putin meeting? | Chandrashekhar Nene Maha MTB</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>https://caleidoscope.in/art-culture/will-bajirao-mastani-come-alive-in-movie-halls-today</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/what-happened-in-the-trump-putin-meeting-chandrashekhar-nene-maha-mtb.html</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Red alert in Mumbai; BMC shuts all afternoon schools, colleges</t>
+          <t>IBM to support Maharashtra in developing quantum computing initiative</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>https://www.newsbytesapp.com/news/india/mumbai-rain-havoc-to-continue-for-next-4-days/story</t>
+          <t>https://www.communicationstoday.co.in/ibm-to-support-maharashtra-in-developing-quantum-computing-initiative/</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Nanded Rain: नांदेड़ में भारी बारिश के बाद 200 लोग बाढ़ में फंसे! बादल फटने से 5 लापता, रेस्क्यू के लिए सेना बुलाई गई</t>
+          <t>Heavy rainfall causes 7 deaths, crop loss in Maharashtra as alerts continue</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>https://hindi.moneycontrol.com/india/heavy-rains-in-maharashtra-nanded-leave-over-200-stranded-in-flood-waters-five-people-missing-article-2104052.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/heavy-rainfall-causes-7-deaths-crop-loss-in-maharashtra-as-alerts-continue/articleshow/123368187.cms</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Maharashtra approves amendments for Dharavi project land transfer</t>
+          <t>Those who speak of Maharashtra 'asmita' should support Radhakrishnan for VP post Fadnavis</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/maharashtra-approves-amendments-for-dharavi-project-land-transfer/ar-AA1G1ze9</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom25-mh-governor-ld-fadnavis.html</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>What happened in the Trump-Putin meeting? | Chandrashekhar Nene Maha MTB</t>
+          <t>Fadnavis meets Guv Radhakrishnan, presents him book of Shivaji Maharaj's letters</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/what-happened-in-the-trump-putin-meeting-chandrashekhar-nene-maha-mtb.html</t>
+          <t>https://www.msn.com/en-in/news/india/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharaj-s-letters/ar-AA1KISQ7</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>IBM to support Maharashtra in developing quantum computing initiative</t>
+          <t>Third Mumbai in Raigad to become Maharashtra’s new economic powerhouse: CM Fadnavis</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>https://www.communicationstoday.co.in/ibm-to-support-maharashtra-in-developing-quantum-computing-initiative/</t>
+          <t>https://www.daijiworld.com/index.php/news/newsDisplay?newsID=1289652</t>
         </is>
       </c>
     </row>
@@ -5867,12 +5867,12 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Mumbai rain: 177 mm recorded in 6-8 hours, public advised to reach homes before 6.30 pm</t>
+          <t>Mumbai reels under 177 mm rain in 8 hours; flights hit, schools shut as red alert issued</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>https://www.onmanorama.com/news/india/2025/08/18/mumbai-rains-flooding-high-tide-warning-live.html</t>
+          <t>https://www.newindianexpress.com/nation/2025/Aug/18/mumbai-rains-flight-operations-hit-schools-colleges-shut-as-imd-issues-red-alert</t>
         </is>
       </c>
     </row>
@@ -5891,7 +5891,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Mumbai rains: Torrential downpour cripples normal life, roads flooded — in pics</t>
+          <t>Mumbai rains: Torrential downpour cripples normal life; train services hit, roads flooded — see pics</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -5903,12 +5903,12 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Mumbai reels under 177 mm rain in 8 hours; flights hit, schools shut as red alert issued</t>
+          <t>Rain fury: 5 missing, 200 stranded in Nanded; local trains, flights hit in Mumbai</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Aug/18/mumbai-rains-flight-operations-hit-schools-colleges-shut-as-imd-issues-red-alert</t>
+          <t>https://odishatv.in/news/national/rain-fury-5-missing-200-stranded-in-nanded-local-trains-flights-hit-in-mumbai-270189</t>
         </is>
       </c>
     </row>
@@ -5927,48 +5927,48 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Rain fury: 5 missing, 200 stranded in Nanded; local trains, flights hit in Mumbai</t>
+          <t>IndiGo Airlines issues travel advisory for passengers flying out of Mumbai due to heavy rainfall, waterlogging in the city</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>https://odishatv.in/news/national/rain-fury-5-missing-200-stranded-in-nanded-local-trains-flights-hit-in-mumbai-270189</t>
+          <t>https://newsroompost.com/india/indigo-airlines-issues-travel-advisory-for-passengers-flying-out-of-mumbai-due-to-heavy-rainfall-waterlogging-in-the-city/5347388.html</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>IndiGo Airlines issues travel advisory for passengers flying out of Mumbai due to heavy rainfall, waterlogging in the city</t>
+          <t>मुंबई में भारी बारिश का कहर, 19 अगस्त को बंद रहेंगे सभी स्कूल-कॉलेज</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>https://newsroompost.com/india/indigo-airlines-issues-travel-advisory-for-passengers-flying-out-of-mumbai-due-to-heavy-rainfall-waterlogging-in-the-city/5347388.html</t>
+          <t>https://hindi.news24online.com/india/mumbai-and-jammu-kashmir-heavy-rain-rain-school-and-college-closed/1288306/</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>मुंबई में भारी बारिश का कहर, 19 अगस्त को बंद रहेंगे सभी स्कूल-कॉलेज</t>
+          <t>महाराष्ट्र में भारी बारिश से सात लोगों की मौत, 200 ग्रामीण फंसे</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>https://hindi.news24online.com/india/mumbai-and-jammu-kashmir-heavy-rain-rain-school-and-college-closed/1288306/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AD-%E0%A4%B0-%E0%A4%AC-%E0%A4%B0-%E0%A4%B6-%E0%A4%B8%E0%A5%87-%E0%A4%B8-%E0%A4%A4-%E0%A4%B2-%E0%A4%97-%E0%A4%82-%E0%A4%95-%E0%A4%AE-%E0%A4%A4-200-%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%A3-%E0%A4%AB%E0%A4%82%E0%A4%B8%E0%A5%87/ar-AA1KKl3K</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में भारी बारिश से सात लोगों की मौत, 200 ग्रामीण फंसे</t>
+          <t>राज्यात अतिवृष्टीच्या पार्श्वभूमीवर मुख्यमंत्री देवेंद्र फडणवीस यांचे सर्व यंत्रणांना सतर्कतेचे निर्देश</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AD-%E0%A4%B0-%E0%A4%AC-%E0%A4%B0-%E0%A4%B6-%E0%A4%B8%E0%A5%87-%E0%A4%B8-%E0%A4%A4-%E0%A4%B2-%E0%A4%97-%E0%A4%82-%E0%A4%95-%E0%A4%AE-%E0%A4%A4-200-%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%A3-%E0%A4%AB%E0%A4%82%E0%A4%B8%E0%A5%87/ar-AA1KKl3K</t>
+          <t>https://mahasamvad.in/176121/</t>
         </is>
       </c>
     </row>
@@ -5987,120 +5987,120 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Mumbai Heavy Rain : मुंबईसाठी पुढील 10-12 तास धोक्याचे, मुख्यमंत्री फडणवीसांनी मुंबईकरांना केलं सावध</t>
+          <t>‘तिसरी मुंबई’ घडवण्यासाठी महाराष्ट्र शासन कार्यरत</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/heavy-rains-in-mumbai-next-48-hours-are-crucial-chief-minister-devendra-fadnavis-warns-citizens-to-be-alert/913099/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/-mumbai-maharashtra-government-third-mumbai-devendra-fadnavis-worli-shivdi.html</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>मराठ्यांच्या इतिहासाची साक्षीदार; श्रीमंत राजे रघुजी भोसलेंच्या ऐतिहासिक तलवारीचं लोकार्पण, पाहा खास PHOTO</t>
+          <t>Mumbai Heavy Rain : मुंबईसाठी पुढील 10-12 तास धोक्याचे, मुख्यमंत्री फडणवीसांनी मुंबईकरांना केलं सावध</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/photogallery/news/raghuji-bhosale-sword-inauguration-in-mumbai-by-cm-devendra-fadnavis/photoshow/123367923.cms</t>
+          <t>https://www.mymahanagar.com/maharashtra/heavy-rains-in-mumbai-next-48-hours-are-crucial-chief-minister-devendra-fadnavis-warns-citizens-to-be-alert/913099/</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Mumbai Rain: मुंबईत उद्या शाळांना सुट्टी? पुढचे १२ तास महत्वाचे, मुख्यमंत्री नेमकं काय म्हणाले?</t>
+          <t>मराठ्यांच्या इतिहासाची साक्षीदार; श्रीमंत राजे रघुजी भोसलेंच्या ऐतिहासिक तलवारीचं लोकार्पण, पाहा खास PHOTO</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/mumbai-pune/mumbai-rain-alert-cm-devendra-fadnavis-said-mumbai-schools-declared-holiday-on-tomorrow-bmc-to-decide-pvm91</t>
+          <t>https://marathi.indiatimes.com/photogallery/news/raghuji-bhosale-sword-inauguration-in-mumbai-by-cm-devendra-fadnavis/photoshow/123367923.cms</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Maharashtra Rains: राज्यात अतिवृष्टी, 7 जणांचा मृत्यू; मुख्यमंत्र्यांचे सर्व यंत्रणांना सतर्कतेचे निर्देश Maharashtra Rains: Heavy rains in the state, 7 people died; CM Devendra Fadnavis directs all agencies to be alert</t>
+          <t>Mumbai Rain: मुंबईत उद्या शाळांना सुट्टी? पुढचे १२ तास महत्वाचे, मुख्यमंत्री नेमकं काय म्हणाले?</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-rains-heavy-rains-in-the-state-7-people-died-cm-devendra-fadnavis-directs-all-agencies-to-be-alert-89603</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/mumbai-rain-alert-cm-devendra-fadnavis-said-mumbai-schools-declared-holiday-on-tomorrow-bmc-to-decide-pvm91</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>श्रीमंत राजे रघूजी भोसले यांची ऐतिहासिक तलवार उद्या मुंबईत दाखल</t>
+          <t>Maharashtra Rains: राज्यात अतिवृष्टी, 7 जणांचा मृत्यू; मुख्यमंत्र्यांचे सर्व यंत्रणांना सतर्कतेचे निर्देश Maharashtra Rains: Heavy rains in the state, 7 people died; CM Devendra Fadnavis directs all agencies to be alert</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176009/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-rains-heavy-rains-in-the-state-7-people-died-cm-devendra-fadnavis-directs-all-agencies-to-be-alert-89603</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>CM Devendra Fadnavis : ‘तिसरी मुंबई’ नवा अध्याय उघडेल; रायगड जिल्ह्यात होणार विकसित</t>
+          <t>श्रीमंत राजे रघूजी भोसले यांची ऐतिहासिक तलवार उद्या मुंबईत दाखल</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/navi-mumbais-successor-the-rise-of-third-mumbai-in-raigad-district-cm-devendra-fadnavis-pjp78</t>
+          <t>https://mahasamvad.in/176009/</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>CM Devendra Fadnavis : हिंदवी स्वराज्याचा इतिहास नवीन पिढीपर्यंत पोहोचेल; श्रीमंत राजे रघुजी भोसले यांच्या तलवारीचे स्वागत</t>
+          <t>LIVE Update : मुंबईतील सर्व शाळांना उद्या सुट्टी जाहीर</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/legacy-of-hindavi-swarajya-rajarshi-raghuji-bhosales-sword-welcomed-history-cm-devendra-fadnavis-pjp78</t>
+          <t>https://www.mymahanagar.com/maharashtra/live-update-mumbai-rain-best-co-operative-soc-election-live-maharashtra-update-political-rain-update-devendra-fadnavis-ajit-pawar-eknath-shinde-uddhav-thackeray-raj-thackeray/913004/</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>मुंबईत पुढील आठ ते दहा तासांसाठी रेड अलर्ट, महत्त्वाचे काम असल्यास घराबाहेर पडण्याचे मुख्यमंत्री फडणवीस यांचे आवाहन</t>
+          <t>CM Devendra Fadnavis : हिंदवी स्वराज्याचा इतिहास नवीन पिढीपर्यंत पोहोचेल; श्रीमंत राजे रघुजी भोसले यांच्या तलवारीचे स्वागत</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/in-mumbai-people-have-been-told-to-step-out-only-if-it-is-needed-says-cm-devendra-fadnavis/</t>
+          <t>https://www.esakal.com/mumbai/legacy-of-hindavi-swarajya-rajarshi-raghuji-bhosales-sword-welcomed-history-cm-devendra-fadnavis-pjp78</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Maharashtra Rain: राज्यात पावसाचा हाहाकार! १६ जिल्ह्यांना रेड- ऑरेंज अलर्ट, मुख्यमंत्र्यांकडून सतर्क राहण्याचे आवाहन</t>
+          <t>मुंबईत पुढील आठ ते दहा तासांसाठी रेड अलर्ट, महत्त्वाचे काम असल्यास घराबाहेर पडण्याचे मुख्यमंत्री फडणवीस यांचे आवाहन</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/mumbai-pune/maharashtra-floods-cm-fadnavis-reviews-situation-ndrf-and-army-deployed-16-districts-on-red-alert-latest-news-pvm91</t>
+          <t>https://www.saamana.com/in-mumbai-people-have-been-told-to-step-out-only-if-it-is-needed-says-cm-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Kolhapur : सरन्यायाधीश Bhushan Gavai यांच्या हस्ते सर्किट बेंच इमारतीचे उद्घाटन</t>
+          <t>Maharashtra Rain: राज्यात पावसाचा हाहाकार! १६ जिल्ह्यांना रेड- ऑरेंज अलर्ट, मुख्यमंत्र्यांकडून सतर्क राहण्याचे आवाहन</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/kolhapur-circuit-bench-inauguration-with-chief-justice-bhushan-gavai-marathi-news/</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/maharashtra-floods-cm-fadnavis-reviews-situation-ndrf-and-army-deployed-16-districts-on-red-alert-latest-news-pvm91</t>
         </is>
       </c>
     </row>
@@ -6131,24 +6131,24 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>रघुजीराजे भोसले यांची तलवार मुंबईत शौर्याचा वारसा इतिहाप्रेमींसाठी खुला; मराठा साम्राज्याचा वारसा परत मिळवण्याचा प्रयत्न – मुख्यमंत्री</t>
+          <t>Ashish Shelar : मुंबईत मुसळधार.. परिस्थितीचा आढावा घेतल्यानंतर शेलारांकडून मुंबईकरांना एकच आवाहन; आज,...</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/raghujiraje-bhosale-sword-a-legacy-of-bravery-is-open-to-history-lovers-in-mumbai-an-attempt-to-reclaim-the-legacy-of-the-maratha-empire-said-by-chief-minister-devendra-fadnavis/</t>
+          <t>https://www.tv9marathi.com/videos/ashish-shelar-appeals-to-mumbaikars-after-review-of-rains-at-bmc-stay-at-house-during-mumbai-heavy-rains-1472440.html</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>राष्ट्रीय: मुंबई में भारी बारिश के बीच सुचारू रूप से चल रही मेट्रो, सीएम फडणवीस ने की तारीफ</t>
+          <t>Maharashtra BIG Decisions : घरांपासून नोकऱ्यांपर्यंत… महाराष्ट्राचे दमदार महानिर्णय, हा व्हिडीओ...</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/news-1174019</t>
+          <t>https://www.tv9marathi.com/videos/maharashtras-major-decisions-police-recruitment-housing-projects-and-historical-artefact-return-1472726.html</t>
         </is>
       </c>
     </row>
@@ -6179,12 +6179,12 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis : नांदेड जिल्ह्यातील अतिवृष्टीवर मुख्यमंत्र्यांची नजर, प्रशासनाला सूचना</t>
+          <t>राज्यात अतिवृष्टीच्या पार्श्वभूमीवर CM DEVENDRA FADNAVIS यांचे सर्व यंत्रणांना सतर्कतेचे निर्देश</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/devendra-fadnavis-chief-ministers-eye-on-heavy-rains-in-nanded-district-instructions-to-the-administration/</t>
+          <t>https://www.timemaharashtra.com/maharashtra/cm-devendra-fadnavis-instructs-all-agencies-to-be-alert-in-the-wake-of-heavy-rains-in-the-state/129378/</t>
         </is>
       </c>
     </row>
@@ -6251,12 +6251,12 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>मानसून में हाल बेहाल, भारी बारिश से इस राज्य में जगह-जगह भरा पानी, स्कूल-कॉलेज किए बंद</t>
+          <t>महाराष्ट्र में भारी बारिश से सात लोगों की मौत, 200 ग्रामीण फंसे</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/national-news/heavy-rain-alert-in-mumbai-monsoon-gained-momentum-know-imd-weather-update-19874723</t>
+          <t>https://hindi.theprint.in/india/seven-people-died-due-to-heavy-rains-in-maharashtra-200-villagers-stranded/856903/</t>
         </is>
       </c>
     </row>
@@ -6275,120 +6275,120 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Ganesh Naik, Eknath Shinde, Thane, Maharashtra Politics</t>
+          <t>रमेश बिधूड़ी ने राधाकृष्णन को दी शुभकामनाएं, कहा- 'अच्छे उपराष्ट्रपति साबित होंगे'</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/maharashtra/ganesh-naik-eknath-shinde-thane-maharashtra-politics-54-804112</t>
+          <t>https://www.khaskhabar.com/local/delhi-ncr/delhi-news/news-ramesh-bidhuri-congratulated-radhakrishnan-said---he-will-prove-to-be-a-good-vice-president-news-hindi-1-745268-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>रमेश बिधूड़ी ने राधाकृष्णन को दी शुभकामनाएं, कहा- 'अच्छे उपराष्ट्रपति साबित होंगे'</t>
+          <t>18.08.2025 : मुख्यमंत्री व सांस्कृतिक कार्य मंत्री यांनी घेतली राज्यपालांची भेट | राजभवन महाराष्ट्र | भारत</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/delhi-ncr/delhi-news/news-ramesh-bidhuri-congratulated-radhakrishnan-said---he-will-prove-to-be-a-good-vice-president-news-hindi-1-745268-KKN.html</t>
+          <t>https://rajbhavan-maharashtra.gov.in/gallery/18-08-2025-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%B5-%E0%A4%B8%E0%A4%BE%E0%A4%82%E0%A4%B8%E0%A5%8D%E0%A4%95%E0%A5%83%E0%A4%A4/</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Rain wreaks havoc in Maharashtra, brings Mumbai to a standstill</t>
+          <t>18.08.2025 : मुख्यमंत्री देवेंद्र फडणवीस व सांस्कृतिक कार्य मंत्री आशिष शेलार यांनी घेतली राज्यपालांची भेट</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/rain-wreaks-havoc-in-maharashtra-brings-mumbai-to-a-standstill/article69948564.ece</t>
+          <t>https://rajbhavan-maharashtra.gov.in/18-08-2025-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB/</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Mumbai rains: BMC announces holiday for schools, colleges on August 19</t>
+          <t>Cabinet sends back note regarding GMR with multiple queries</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>https://www.cnbctv18.com/india/are-mumbai-schools-colleges-open-or-close-on-august-19-19655564.htm</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/18/cabinet-sends-back-note-regarding-gmr-with-multiple-queries.html</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>India monsoon updates: Heavy to very heavy rainfall at few places in Mumbai; residents told to ‘avoid unnecessary travel’</t>
+          <t>Rain wreaks havoc in Maharashtra, brings Mumbai to a standstill</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/india-monsoon-live-mumbai-rains-yamuna-river-flood-alert-delhi-kashmir-cloudburst-updates-august-18/article69946105.ece</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/rain-wreaks-havoc-in-maharashtra-brings-mumbai-to-a-standstill/article69948564.ece</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Cabinet sends back note regarding GMR with multiple queries</t>
+          <t>Mumbai rains: BMC announces holiday for schools, colleges on August 19</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/18/cabinet-sends-back-note-regarding-gmr-with-multiple-queries.html</t>
+          <t>https://www.cnbctv18.com/india/are-mumbai-schools-colleges-open-or-close-on-august-19-19655564.htm</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Maharashtra govt plans amnesty scheme to recover pending transport fines</t>
+          <t>India monsoon updates: Heavy to very heavy rainfall at few places in Mumbai; residents told to ‘avoid unnecessary travel’</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>https://auto.economictimes.indiatimes.com/news/industry/maharashtras-new-amnesty-scheme-settle-transport-fines-and-save-big/123364146</t>
+          <t>https://www.thehindu.com/news/national/india-monsoon-live-mumbai-rains-yamuna-river-flood-alert-delhi-kashmir-cloudburst-updates-august-18/article69946105.ece</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Mumbai on red alert; BMC declares holiday for schools, colleges on August 19</t>
+          <t>Maharashtra govt plans amnesty scheme to recover pending transport fines</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/bmc-declares-holiday-for-mumbai-schools-colleges-on-august-19-as-city-braces-for-heavy-rain/articleshow/123366693.cms</t>
+          <t>https://auto.economictimes.indiatimes.com/news/industry/maharashtras-new-amnesty-scheme-settle-transport-fines-and-save-big/123364146</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>Are Mumbai schools, colleges open today? Details here | Latest News India - Hindustan Times</t>
+          <t>Mumbai Rains Live News: Torrential rains cripple Mumbai; roads flooded, local trains delayed and schools, colleges closed amid ‘Red’ alert</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/are-mumbai-schools-colleges-open-today-details-here-mumbai-rains-mumbai-weather-imd-red-alert-101755561079277.html</t>
+          <t>https://www.thehindubusinessline.com/news/mumbai-weather-mumbai-rains-live-news-updates/article69946123.ece</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>Mumbai Rains Live News: Torrential rains cripple Mumbai; roads flooded, local trains delayed and schools, colleges closed amid ‘Red’ alert</t>
+          <t>School Holiday: Schools in Mumbai, Thane to remain closed on Tuesday amid IMD's Red Alert for heavy rains</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>https://www.thehindubusinessline.com/news/mumbai-weather-mumbai-rains-live-news-updates/article69946123.ece</t>
+          <t>https://www.livemint.com/news/india/school-holiday-schools-in-mumbai-thane-to-remain-closed-on-tuesday-amid-imds-red-alert-for-heavy-rains-11755527340477.html</t>
         </is>
       </c>
     </row>
@@ -6419,12 +6419,12 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>शाळा अंतर्गत फेरीमध्ये विद्यार्थ्यांचा सत्कार सोहळा</t>
+          <t>'मराठी'कडं दुर्लक्ष भोवणार; शासकीय, निमशासकीय कार्यालयांमधील अधिकाऱ्यांवर थेट न्यायिक कारवाई होणार</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/student-felicitation-ceremony-during-the-schools-internal-parade.html</t>
+          <t>https://www.etvbharat.com/mr/!state/penal-action-will-be-taken-against-those-who-ignore-the-marathi-language-in-government-and-semi-government-offices-in-maharashtra-maharashtra-news-mhs25081803599</t>
         </is>
       </c>
     </row>
@@ -6455,84 +6455,120 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>Maharashtra Rain Update: 19 ऑगस्टलाही सावधान..., महाराष्ट्रातील 'या' जिल्ह्यांना रेड अलर्ट</t>
+          <t>मराठी चित्रपटसृष्टीत भव्यतेचं नवं पर्व घेऊन येणाऱ्या ‘दशावतार’ चित्रपटाचं जबरदस्त ट्रेलर प्रदर्शित</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/mahrashtra-mumbai-rain-latest-update-orange-alert-till-august-20-red-alert-issued-in-several-districts-963438.html</t>
+          <t>https://www.etvbharat.com/mr/!entertainment/trailer-of-the-film-dashavatar-which-brings-a-new-era-of-grandeur-to-marathi-cinema-is-released-maharashtra-news-mhs25081901382</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Mumbai Rain Update: मुंबईत पुढील चार तास धो-धो, रेड अलर्ट जारी, लोकल ट्रेन उशिराने, नागरिकांना घराबाहेर न पडण्याचं आवाहन</t>
+          <t>शाळा अंतर्गत फेरीमध्ये विद्यार्थ्यांचा सत्कार सोहळा</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-heavy-rain-expected-by-imd-red-alert-heavy-rainfall-local-train-updates/articleshow/123376293.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/student-felicitation-ceremony-during-the-schools-internal-parade.html</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>मुख्यमंत्री फडणवीसांकडून पावसाचा आढावा: मराठवाड्यात 800 गावे बाधित, कोकण-विदर्भात रेड अलर्ट</t>
+          <t>Mumbai Rain Update: मुंबईत पुढील चार तास धो-धो, रेड अलर्ट जारी, लोकल ट्रेन उशिराने, नागरिकांना घराबाहेर न पडण्याचं आवाहन</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/cm-fadnavis-reviews-rains-800-villages-affected-in-marathwada-red-alert-in-konkan-vidarbha/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-heavy-rain-expected-by-imd-red-alert-heavy-rainfall-local-train-updates/articleshow/123376293.cms</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>MMRDA launches SCLR bridge, metro institute and flyovers to ease city commute</t>
+          <t>Maharashtra Rain Update: 19 ऑगस्टलाही सावधान..., महाराष्ट्रातील 'या' जिल्ह्यांना रेड अलर्ट</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>https://propnewstime.com/getdetailsStories/MjA1NTQ=/mmrda-launches-sclr-bridge-metro-institute-and-flyovers-to-ease-city-commute</t>
+          <t>https://www.navarashtra.com/maharashtra/mahrashtra-mumbai-rain-latest-update-orange-alert-till-august-20-red-alert-issued-in-several-districts-963438.html</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Mumbai continues to be on red alert; heavy rain disrupts travel, shuts offices &amp; educational institutions</t>
+          <t>रत्नागिरीत मुसळधार पावसानं हाहाकार: शाळा महाविद्यालयाला सुटी</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/weather/mumbai-on-red-alert-for-second-consecutive-day-heavy-rain-disrupts-travel-shuts-educational-institutions/articleshow/123375296.cms</t>
+          <t>https://www.etvbharat.com/mr/!state/holiday-for-schools-and-colleges-in-ratnagiri-due-to-heavy-rain-ratnagiri-district-administration-decision-orange-alert-weather-forecast-maharashtra-news-mhs25081806850</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Maha CM asks agencies to be on alert mode after heavy rainfall and flash floods</t>
+          <t>रायगड जिल्हा मुसळधार पावसानं झोडपला; सावित्री नदीचं पाणी महाड शहरात शिरलं</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/maha-cm-asks-agencies-to-be-on-alert-mode-after-heavy-rainfall-and-flash-floods/</t>
+          <t>https://www.etvbharat.com/mr/!state/heavy-rain-in-raigad-district-savitri-river-flood-landslide-in-mangaon-maharashtra-news-mhs25081804820</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>Over ₹6.52 Crore Medical Aid Distributed To 5,000 Beneficiaries In Pune District</t>
+          <t>मंत्री संजय शिरसाट यांच्याकडून अधिकारांचा गैरवापर; 5 हजार कोटींचा गोलमाल झाल्याचा रोहित पवारांचा आरोप</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/over-%E2%82%B96-52-crore-medical-aid-distributed-to-5000-beneficiaries-in-pune-district/</t>
+          <t>https://www.etvbharat.com/mr/!state/minister-sanjay-shirsat-misuses-powers-rohit-pawar-alleges-rs-5000-crore-scam-mumbai-maharashtra-news-mhs25081804077</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>Maharashtra on high alert as heavy rain leaves 6 dead</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/news/india/maharashtra-on-high-alert-as-heavy-rain-leaves-6-dead/articleshow/123371509.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>Mumbai continues to be on red alert; heavy rain disrupts travel, shuts offices &amp; educational institutions</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/news/weather/mumbai-on-red-alert-for-second-consecutive-day-heavy-rain-disrupts-travel-shuts-educational-institutions/articleshow/123375296.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>Maha CM asks agencies to be on alert mode after heavy rainfall and flash floods</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>https://www.lokmattimes.com/national/maha-cm-asks-agencies-to-be-on-alert-mode-after-heavy-rainfall-and-flash-floods/</t>
         </is>
       </c>
     </row>

--- a/Output/Devendra Fadnavis/extracted_links.xlsx
+++ b/Output/Devendra Fadnavis/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B512"/>
+  <dimension ref="A1:B545"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,24 +479,24 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mumbai AQI: Dia Mirza expresses her concern with CM Devendra Fadnavis to act on city's air pollution</t>
+          <t>Maharashtra CM Fadnavis, his Deputy CMs congratulate Radhakrishnan over V-P nomination</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/public-safety-and-emergencies/health-and-safety-alerts/mumbai-aqi-dia-mirza-expresses-her-concern-with-cm-devendra-fadnavis-to-act-on-city-s-air-pollution/ar-AA1xZ0xs?ocid=BingNewsVerp&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.thehindu.com/news/national/maharashtra-cm-fadnavis-his-deputy-cms-congratulate-radhakrishnan-over-v-p-nomination/article69945058.ece</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
+          <t>Aurangzeb Tomb Row: VHP’s Statewide Protests Backed By RSS; CM Devendra Fadnavis Calls For Lawful Dismantling</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.outlookbusiness.com/news/third-mumbai-to-boost-metropolitan-region-development-fadnavis</t>
+          <t>https://www.msn.com/en-in/news/India/aurangzeb-tomb-row-vhp-s-statewide-protests-backed-by-rss-cm-devendra-fadnavis-calls-for-lawful-dismantling/ar-AA1Bfmct?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
@@ -527,108 +527,108 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>'Positive about bringing a law to protect advocates:' Maharashtra CM Fadnavis</t>
+          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://legal.economictimes.indiatimes.com/news/industry/positive-about-bringing-a-law-to-protect-advocates-maharashtra-cm-fadnavis/123378199</t>
+          <t>https://www.outlookbusiness.com/news/third-mumbai-to-boost-metropolitan-region-development-fadnavis</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Shiv Sena (UBT) Welcomes Radhakrishnan’s Nomination, Fadnavis Seeks All-Party Support</t>
+          <t>'Positive about bringing a law to protect advocates:' Maharashtra CM Fadnavis</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/nation/shiv-sena-ubt-welcomes-rahakrishans-nomination-fadnavis-seeks-all-party-support-1898266</t>
+          <t>https://legal.economictimes.indiatimes.com/news/industry/positive-about-bringing-a-law-to-protect-advocates-maharashtra-cm-fadnavis/123378199</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VP Nominee CP Radhakrishnan Leaves for Delhi, Maha Yuti Leaders Pledge Support</t>
+          <t>18.08.2025 : CM Devendra Fadnavis and Cultural Affairs Minister Ashish Shelar meets Governor</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/vp-nominee-radhakrishnan-departs-for-delhi-maha-yuti-leaders-extend-support-3685392</t>
+          <t>https://rajbhavan-maharashtra.gov.in/en/18-08-2025-cm-devendra-fadnavis-and-cultural-affairs-minister-ashish-shelar-meets-governor/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cannot achieve affordable housing with ‘business as usual’ approach: Maharashtra CM Fadnavis tells...</t>
+          <t>Shiv Sena (UBT) Welcomes Radhakrishnan’s Nomination, Fadnavis Seeks All-Party Support</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/business/real-estate/cannot-achieve-affordable-housing-with-business-as-usual-approach-maharashtra-cm-fadnavis-tells-realtors-13462328.html</t>
+          <t>https://www.deccanchronicle.com/nation/shiv-sena-ubt-welcomes-rahakrishans-nomination-fadnavis-seeks-all-party-support-1898266</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fadnavis hails Maha Guv’s nomination as Vice Presidential candidate</t>
+          <t>VP Nominee CP Radhakrishnan Leaves for Delhi, Maha Yuti Leaders Pledge Support</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://www.thestatesman.com/india/fadnavis-hails-maha-guvs-nomination-as-vice-presidential-candidate-1503473264.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/vp-nominee-radhakrishnan-departs-for-delhi-maha-yuti-leaders-extend-support-3685392</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Third Mumbai: Fadnavis Boosts MMR Development</t>
+          <t>Cannot achieve affordable housing with ‘business as usual’ approach: Maharashtra CM Fadnavis tells...</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/third-mumbai-fadnavis-boosts-mmr-development/32201020250818</t>
+          <t>https://www.moneycontrol.com/news/business/real-estate/cannot-achieve-affordable-housing-with-business-as-usual-approach-maharashtra-cm-fadnavis-tells-realtors-13462328.html</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Aurangzeb Tomb Row: VHP’s Statewide Protests Backed By RSS; CM Devendra Fadnavis Calls For Lawful Dismantling</t>
+          <t>Fadnavis hails Maha Guv’s nomination as Vice Presidential candidate</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/aurangzeb-tomb-row-vhp-s-statewide-protests-backed-by-rss-cm-devendra-fadnavis-calls-for-lawful-dismantling/ar-AA1Bfmct?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.thestatesman.com/india/fadnavis-hails-maha-guvs-nomination-as-vice-presidential-candidate-1503473264.html</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Aakar Patel| New Maharashtra Security Law Open To Abuse, Threatens Rights; Say ‘No’ To It</t>
+          <t>Devendra Fadnavis' first reaction to Raj Thackeray's reunion with Uddhav jibe</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/opinion/columnists/aakar-patel-new-maharashtra-security-law-open-to-abuse-threatens-rights-say-no-to-it-1898276</t>
+          <t>http://www.msn.com/en-in/news/india/devendra-fadnavis-first-reaction-to-raj-thackeray-s-reunion-with-uddhav-jibe/ar-AA1I1jzW?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis' first reaction to Raj Thackeray's reunion with Uddhav jibe</t>
+          <t>Aakar Patel| New Maharashtra Security Law Open To Abuse, Threatens Rights; Say ‘No’ To It</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/india/devendra-fadnavis-first-reaction-to-raj-thackeray-s-reunion-with-uddhav-jibe/ar-AA1I1jzW?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.deccanchronicle.com/opinion/columnists/aakar-patel-new-maharashtra-security-law-open-to-abuse-threatens-rights-say-no-to-it-1898276</t>
         </is>
       </c>
     </row>
@@ -671,36 +671,36 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Goldman Sachs opens new, expanded office in Mumbai</t>
+          <t>Third Mumbai: Fadnavis Boosts MMR Development</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/business/Industry/goldman-sachs-opens-new-expanded-office-in-mumbai/article69947256.ece</t>
+          <t>https://money.rediff.com/news/market/third-mumbai-fadnavis-boosts-mmr-development/32201020250818</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Mumbai gets 300 mm rain in a day, Devendra Fadnavis warns next 48 hours critical</t>
+          <t>Goldman Sachs opens new, expanded office in Mumbai</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/cities/mumbai/story/mumbai-heavy-rains-waterlogging-imd-red-alert-bmc-school-offices-holiday-work-from-home-2773291-2025-08-19</t>
+          <t>https://www.thehindu.com/business/Industry/goldman-sachs-opens-new-expanded-office-in-mumbai/article69947256.ece</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Those who speak of Maharashtra 'asmita' should support Radhakrishnan for VP post: Fadnavis</t>
+          <t>Mumbai gets 300 mm rain in a day, Devendra Fadnavis warns next 48 hours critical</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/those-who-speak-of-maharashtra-'asmita'-should-support-radhakrishnan-for-vp-post:-fadnavis/2832772</t>
+          <t>https://www.indiatoday.in/cities/mumbai/story/mumbai-heavy-rains-waterlogging-imd-red-alert-bmc-school-offices-holiday-work-from-home-2773291-2025-08-19</t>
         </is>
       </c>
     </row>
@@ -719,300 +719,300 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Why Eknath Shinde is covering little distance despite frequent visits to Delhi</t>
+          <t>Shinde and BJP: The saga continues</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/political-pulse/why-eknath-shinde-is-covering-little-distance-despite-frequent-visits-to-delhi-10197218/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/shinde-and-bjp-the-saga-continues-101755457833159.html</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>‘Observe precaution’: Maharashtra CM warns about severe weather conditions in State</t>
+          <t>Those who speak of Maharashtra 'asmita' should support Radhakrishnan for VP post: Fadnavis</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://www.thehindubusinessline.com/news/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state/article69950172.ece</t>
+          <t>https://www.ptinews.com/story/national/those-who-speak-of-maharashtra-asmita-should-support-radhakrishnan-for-vp-post-fadnavis/2832772</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Heavy Rains Ravage State, CM Fadnavis Orders Relief, Surveys Rain-Hit Areas</t>
+          <t>Why Eknath Shinde is covering little distance despite frequent visits to Delhi</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/heavy-rains-ravage-state-cm-fadnavis-orders-relief-surveys-rain-hit-areas/articleshow/123372550.cms</t>
+          <t>https://indianexpress.com/article/political-pulse/why-eknath-shinde-is-covering-little-distance-despite-frequent-visits-to-delhi-10197218/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Mumbai received 177mm rain in just 6-8 hour period, says CM Fadnavis; more to come amid high tides</t>
+          <t>Heavy Rains Ravage State, CM Fadnavis Orders Relief, Surveys Rain-Hit Areas</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/red-alert-for-mumbai-mumbai-got-177mm-rain-in-just-6-8-hour-period-says-cm-fadnavis-more-to-come-amid-high-tides-23589990</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/heavy-rains-ravage-state-cm-fadnavis-orders-relief-surveys-rain-hit-areas/articleshow/123372550.cms</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Third Mumbai in Raigad to become Maharashtra’s new economic powerhouse: CM Fadnavis</t>
+          <t>'My karyakarta is with me': Hitendra Thakur shrugs off defections ahead of civic elections</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://daijiworld.com/news/newsDisplay?newsID=1289652</t>
+          <t>https://www.msn.com/en-in/news/India/my-karyakarta-is-with-me-hitendra-thakur-shrugs-off-defections-ahead-of-civic-elections/ar-AA1KHNiH</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Mumbai gets 177mm rain in 6-8 hour period, says CM; all agencies asked to remain alert</t>
+          <t>‘Observe precaution’: Maharashtra CM warns about severe weather conditions in State</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/mumbai-gets-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/articleshow/123365291.cms</t>
+          <t>https://www.thehindubusinessline.com/news/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state/article69950172.ece</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Mumbai rains: Maharashtra CM says 'observe precautions', warns of heavy rainfall, high tide; check BMC's advisory</t>
+          <t>Mumbai received 177mm rain in just 6-8 hour period, says CM Fadnavis; more to come amid high tides</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/news/mumbai-rains-maharashtra-cm-says-observe-precautions-warns-of-heavy-rainfall-high-tide-check-bmcs-advisory-11755573270369.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/red-alert-for-mumbai-mumbai-got-177mm-rain-in-just-6-8-hour-period-says-cm-fadnavis-more-to-come-amid-high-tides-23589990</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Fadnavis govt’s big Maratha pride push: Legendary sword it ‘bought’ back from London, with a Rs 47L bid</t>
+          <t>Third Mumbai in Raigad to become Maharashtra’s new economic powerhouse: CM Fadnavis</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://theprint.in/politics/fadnavis-govts-big-maratha-pride-push-legendary-sword-it-bought-back-from-london-with-a-rs-47l-bid/2723199/</t>
+          <t>https://daijiworld.com/news/newsDisplay?newsID=1289652</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Maharashtra CM Fadnavis, Dy CM Shinde congratulate Governor CP Radhakrishnan on NDA's VP nomination</t>
+          <t>Mumbai gets 177mm rain in 6-8 hour period, says CM; all agencies asked to remain alert</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination-23589945</t>
+          <t>https://m.economictimes.com/news/india/mumbai-gets-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/articleshow/123365291.cms</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Fadnavis meets Guv Radhakrishnan, presents him book of Shivaji Maharaj's letters</t>
+          <t>Fadnavis govt’s big Maratha pride push: Legendary sword it ‘bought’ back from London, with a Rs 47L bid</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharaj-s-letters/2832582</t>
+          <t>https://theprint.in/politics/fadnavis-govts-big-maratha-pride-push-legendary-sword-it-bought-back-from-london-with-a-rs-47l-bid/2723199/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
+          <t>Rain fury leaves 7 dead in Maharashtra, 200 villagers stranded</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/-third-mumbai--to-boost-metropolitan-region-development--fadnavis/2834902</t>
+          <t>https://www.ptinews.com/story/national/rain-fury-leaves-7-dead-in-maharashtra,-200-villagers-stranded/2834213</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>‘Third Mumbai’ takes shape as CM Fadnavis unveils mega MMR expansion plan</t>
+          <t>Maharashtra CM Fadnavis, Dy CM Shinde congratulate Governor CP Radhakrishnan on NDA's VP nomination</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/city/third-mumbai-takes-shape-as-cm-fadnavis-unveils-mega-mmr-expansion-plan-article-13465350.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination-23589945</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Raghuji Bhonsle’s sword brought to India</t>
+          <t>Find suitable land &amp; I will set up IT park through MIDC in Solapur: Fadnavis</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/19/raghuji-bhonsles-sword-brought-to-india.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/find-suitable-land-i-will-set-up-it-park-through-midc-in-solapur-fadnavis/articleshow/123351422.cms</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Fadnavis meets Guv Radhakrishnan presents him book of Shivaji Maharaj's letters</t>
+          <t>Fadnavis meets Guv Radhakrishnan, presents him book of Shivaji Maharaj's letters</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom20-mh-governor-fadnavis.html</t>
+          <t>https://www.ptinews.com/story/national/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharaj-s-letters/2832582</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Rain fury leaves 7 dead in Maharashtra, 200 villagers stranded</t>
+          <t>'Third Mumbai' to boost MMR development, says Fadnavis; invites pvt sector to join in its creation</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/Rain-fury-leaves-7-dead-in-Maharashtra--200-villagers-stranded/2834213</t>
+          <t>https://www.ptinews.com/editor-detail/-third-mumbai--to-boost-mmr-development--says-fadnavis;-invites-pvt-sector-to-join-in-its-creation/2834267</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Mumbai got 177mm rain in 6-8 hour period, says CM; all agencies asked to remain alert</t>
+          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/mumbai-got-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/2833181</t>
+          <t>https://www.ptinews.com/editor-detail/-third-mumbai--to-boost-metropolitan-region-development--fadnavis/2834902</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Fadnavis Dedicates Goldman Sachs’ New Mumbai Office, Unveils Vision For ‘Third Mumbai’</t>
+          <t>‘Third Mumbai’ takes shape as CM Fadnavis unveils mega MMR expansion plan</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://www.businessworld.in/article/fadnavis-dedicates-goldman-sachs-new-mumbai-office-unveils-vision-for-third-mumbai-567845</t>
+          <t>https://www.moneycontrol.com/city/third-mumbai-takes-shape-as-cm-fadnavis-unveils-mega-mmr-expansion-plan-article-13465350.html</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Maharashtra on high alert as heavy rains batter state; CM, Dy CM lead rescue efforts</t>
+          <t>Mumbai rains: Maharashtra CM says 'observe precautions', warns of heavy rainfall, high tide; check BMC's advisory</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://www.daijiworld.com/news/newsDisplay?newsID=1289634</t>
+          <t>https://www.livemint.com/news/mumbai-rains-maharashtra-cm-says-observe-precautions-warns-of-heavy-rainfall-high-tide-check-bmcs-advisory-11755573270369.html</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
+          <t>Raghuji Bhonsle’s sword brought to India</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://udayavani.com/national/third-mumbai-to-boost-metropolitan-region-development-fadnavis-20250819T044623387Z?lang=en</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/19/raghuji-bhonsles-sword-brought-to-india.html</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Schools shut, red alert as Mumbai braces for another day of heavy rain | Latest News India - Hindustan Times</t>
+          <t>Mumbai got 177mm rain in 6-8 hour period, says CM; more to come amid high tides</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/mumbai-rains-schools-shut-as-mumbai-under-imd-red-alert-braces-for-another-day-of-heavy-rain-10-updates-101755564432674-amp.html</t>
+          <t>https://www.ptinews.com/story/national/mumbai-got-177mm-rain-in-6-8-hour-period-says-cm-more-to-come-amid-high-tides/2832660</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Maratha general Raghuji Bhonsle's sword brought to Mumbai</t>
+          <t>Fadnavis Dedicates Goldman Sachs’ New Mumbai Office, Unveils Vision For ‘Third Mumbai’</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/maratha-general-raghuji-bhonsle-s-sword-brought-to-mumbai/2833930</t>
+          <t>https://www.businessworld.in/article/fadnavis-dedicates-goldman-sachs-new-mumbai-office-unveils-vision-for-third-mumbai-567845</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by Maharashtra CM Devendra Fadnavis</t>
+          <t>Schools shut, red alert as Mumbai braces for another day of heavy rain | Latest News India - Hindustan Times</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322/</t>
+          <t>https://www.hindustantimes.com/india-news/mumbai-rains-schools-shut-as-mumbai-under-imd-red-alert-braces-for-another-day-of-heavy-rain-10-updates-101755564432674-amp.html</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Maharashtra rain: Mumbai flooded, 5 missing in Nanded, more showers in store</t>
+          <t>Maratha general Raghuji Bhonsle's sword brought to Mumbai</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://thefederal.com/category/states/west/maharashtra/mumbai-flooded-nanded-5-missing-maharashtra-rain-202350</t>
+          <t>https://www.ptinews.com/editor-detail/maratha-general-raghuji-bhonsle-s-sword-brought-to-mumbai/2833930</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
+          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by Maharashtra CM Devendra Fadnavis</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://www.millenniumpost.in/nation/third-mumbai-to-boost-metropolitan-region-development-fadnavis-623625</t>
+          <t>https://www.aninews.in/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Mumbai rain: 177 mm recorded in 6-8 hours, public advised to reach homes before 6.30 pm</t>
+          <t>Maharashtra rain: Mumbai flooded, 5 missing in Nanded, more showers in store</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://www.onmanorama.com/news/india/2025/08/18/mumbai-rains-flooding-high-tide-warning-live.html</t>
+          <t>https://thefederal.com/category/states/west/maharashtra/mumbai-flooded-nanded-5-missing-maharashtra-rain-202350</t>
         </is>
       </c>
     </row>
@@ -1031,36 +1031,36 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Mumbai rain Highlights: 7 people dead across Maharashtra, says CM Devendra Fadnavis</t>
+          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://www.india.com/news/india/mumbai-rain-live-updates-heavy-rains-lashes-city-orange-alert-for-today-red-alert-in-pune-satara-ratnagiri-local-trains-delayed-traffic-jams-8017300/</t>
+          <t>https://www.millenniumpost.in/nation/third-mumbai-to-boost-metropolitan-region-development-fadnavis-623625</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Observe precaution: Maharashtra CM warns about severe weather conditions in state</t>
+          <t>Mumbai rain Highlights: 7 people dead across Maharashtra, says CM Devendra Fadnavis</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state-23590120</t>
+          <t>https://www.india.com/news/india/mumbai-rain-live-updates-heavy-rains-lashes-city-orange-alert-for-today-red-alert-in-pune-satara-ratnagiri-local-trains-delayed-traffic-jams-8017300/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Rain fury leaves 7 dead in Maharashtra 200 villagers stranded</t>
+          <t>Observe precaution: Maharashtra CM warns about severe weather conditions in state</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom50-mh-2nd-ldall-rains.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state-23590120</t>
         </is>
       </c>
     </row>
@@ -1091,24 +1091,24 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by Maharashtra CM Devendra Fadnavis</t>
+          <t>CM Devendra Fadnavis Meets Netherlands Yogasana Chief on Global Initiatives</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278516795/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis</t>
+          <t>https://www.transcontinentaltimes.com/netherlands-yogasana-sports-nysa/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CM Devendra Fadnavis Meets Netherlands Yogasana Chief on Global Initiatives</t>
+          <t>CM Devendra Fadnavis to Inaugurate India’s First ESG Lab at National STEM Challenge 2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://www.transcontinentaltimes.com/netherlands-yogasana-sports-nysa/</t>
+          <t>https://indiacsr.in/cm-devendra-fadnavis-to-inaugurate-indias-first-esg-lab-at-national-stem-challenge-2025/</t>
         </is>
       </c>
     </row>
@@ -1127,144 +1127,144 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Mumbai: CM Devendra Fadnavis meets C.P. Radhakrishnan #Gallery</t>
+          <t>Goldman Sachs Expands In Mumbai, Devendra Fadnavis Inaugurates New Worli Office</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/mumbai-cm-devendra-fadnavis-meets-c-p-radhakrishnan-gallery/</t>
+          <t>https://www.freepressjournal.in/business/goldman-sachs-expands-in-mumbai-devendra-fadnavis-inaugurates-new-worli-office</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Goldman Sachs Expands In Mumbai, Devendra Fadnavis Inaugurates New Worli Office</t>
+          <t>Maharashtra CM Devendra Fadnavis Says ‘Third Mumbai’ Being Developed in Raigad District Will Open New</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/business/goldman-sachs-expands-in-mumbai-devendra-fadnavis-inaugurates-new-worli-office</t>
+          <t>https://www.latestly.com/india/news/maharashtra-cm-devendra-fadnavis-says-third-mumbai-being-developed-in-raigad-district-will-open-new-chapter-of-economic-development-7064927.html</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>'Third Mumbai' Will Open A New Chapter Of Economic Development: Maha CM</t>
+          <t>Mumbai Rains: Maharashtra CM Devendra Fadnavis Chairs Review Meeting On Excessive Rainfall At Mantralaya</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://menafn.com/1109941619/Third-Mumbai-Will-Open-A-New-Chapter-Of-Economic-Development-Maha-CM</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-rains-cm-devendra-fadnavis-chairs-review-meeting-on-excessive-rainfall-at-mantralaya-video</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Mumbai Rains: Maharashtra CM Devendra Fadnavis Chairs Review Meeting On Excessive Rainfall At Mantralaya</t>
+          <t>India News | ⚡Devendra Fadnavis Says ‘Third Mumbai’ Will Open a New Chapter of Economic Development</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-rains-cm-devendra-fadnavis-chairs-review-meeting-on-excessive-rainfall-at-mantralaya-video</t>
+          <t>https://www.latestly.com/quickly/india/news/devendra-fadnavis-says-third-mumbai-will-open-a-new-chapter-of-economic-development-7064927.html</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>India News | ⚡Devendra Fadnavis Says ‘Third Mumbai’ Will Open a New Chapter of Economic Development</t>
+          <t>Mumbai Records 177 mm Rain In 6 Hours, CM Devendra Fadnavis Urges Caution Amid High Tide Alert</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/quickly/india/news/devendra-fadnavis-says-third-mumbai-will-open-a-new-chapter-of-economic-development-7064927.html</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-records-177-mm-rain-in-6-hours-cm-devendra-fadnavis-urges-caution-amid-high-tide-alert</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Mumbai Records 177 mm Rain In 6 Hours, CM Devendra Fadnavis Urges Caution Amid High Tide Alert</t>
+          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by...</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-records-177-mm-rain-in-6-hours-cm-devendra-fadnavis-urges-caution-amid-high-tide-alert</t>
+          <t>https://www.lokmattimes.com/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by...</t>
+          <t>Future-ready India lies in STEM and AI, says Devendra Fadnavis, Maharashtra CM</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis/</t>
+          <t>https://indiacsr.in/brillio-national-stem-challenge-empowers-2500-underserved-students-to-innovate-for-indias-future/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Future-ready India lies in STEM and AI, says Devendra Fadnavis, Maharashtra CM</t>
+          <t>‘Third Mumbai’ will open a new chapter of economic development: Maha CM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://indiacsr.in/brillio-national-stem-challenge-empowers-2500-underserved-students-to-innovate-for-indias-future/</t>
+          <t>https://www.lokmattimes.com/national/third-mumbai-will-open-a-new-chapter-of-economic-development-maha-cm/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>‘Third Mumbai’ will open a new chapter of economic development: Maha CM</t>
+          <t>Mumbai: C.P. Radhakrishnan departs for Delhi #Gallery</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/third-mumbai-will-open-a-new-chapter-of-economic-development-maha-cm/</t>
+          <t>https://www.socialnews.xyz/2025/08/18/mumbai-c-p-radhakrishnan-departs-for-delhi-gallery/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Mumbai: C.P. Radhakrishnan departs for Delhi #Gallery</t>
+          <t>VIDEO: Historic Sword Of Raghuji Bhonsle Connects Youth With Maharashtra’s Glorious History, Says CM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/mumbai-c-p-radhakrishnan-departs-for-delhi-gallery/</t>
+          <t>https://www.freepressjournal.in/mumbai/video-historic-sword-of-raghuji-bhonsle-connects-youth-with-maharashtras-glorious-history-says-cm-devendra-fadnavis</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>VIDEO: Historic Sword Of Raghuji Bhonsle Connects Youth With Maharashtra’s Glorious History, Says CM</t>
+          <t>Heavy Rain Forecast for Mumbai: CM Fadnavis Reviews Flood Situation Across Maharashtra, with the Next 12...</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/video-historic-sword-of-raghuji-bhonsle-connects-youth-with-maharashtras-glorious-history-says-cm-devendra-fadnavis</t>
+          <t>https://www.lokmattimes.com/mumbai/heavy-rain-forecast-for-mumbai-cm-fadnavis-reviews-flood-situation-across-maharashtra-with-the-next-12-hours-critical-a475/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Heavy Rain Forecast for Mumbai: CM Fadnavis Reviews Flood Situation Across Maharashtra, with the Next 12...</t>
+          <t>Those who speak of Maharashtra 'asmita' should support Radhakrishnan for VP post: Fadnavis</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/mumbai/heavy-rain-forecast-for-mumbai-cm-fadnavis-reviews-flood-situation-across-maharashtra-with-the-next-12-hours-critical-a475/</t>
+          <t>https://www.newsdrum.in/national/those-who-speak-of-maharashtra-asmita-should-support-radhakrishnan-for-vp-post-fadnavis-9672630</t>
         </is>
       </c>
     </row>
@@ -1295,48 +1295,48 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>7 killed as heavy rain batters Maharashtr­a; 800 villages hit</t>
+          <t>Maharashtra Rains: 5 Missing in Nanded, Over 200 Stranded Across Several Districts; Army, NDRF Deployed</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://www.pressreader.com/india/the-hindu-erode-9WW6/20250819/281994678584394</t>
+          <t>https://www.lokmattimes.com/maharashtra/maharashtra-rains-5-missing-in-nanded-over-200-stranded-across-several-districts-army-ndrf-deployed-a517/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Mumbai Rains: Maharashtra CM Says 'Observe Precautions', Warns Of Heavy Rainfall, High Tide Check BMC's Advisory</t>
+          <t>7 killed as heavy rain batters Maharashtr­a; 800 villages hit</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://menafn.com/1109945394/Mumbai-Rains-Maharashtra-CM-Says-Observe-Precautions-Warns-Of-Heavy-Rainfall-High-Tide-Check-BMCs-Advisory</t>
+          <t>https://www.pressreader.com/india/the-hindu-mangalore-9WWc/20250819/281947433944151</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Pune Patients Receive Over Rs 6.5 Crore in Medical Aid Under Chief Minister Devendra Fadnavis’ Initiative</t>
+          <t>Business News</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-patients-receive-over-rs-6-5-crore-in-medical-aid-under-chief-minister-devendra-fadnavis-initiative/</t>
+          <t>https://www.latestly.com/agency-news/business-news-credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis-7064653.html</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Maharashtra Rains: 5 Missing in Nanded, Over 200 Stranded Across Several Districts; Army, NDRF Deployed</t>
+          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by Maharashtra CM Devendra Fadnavis</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/maharashtra/maharashtra-rains-5-missing-in-nanded-over-200-stranded-across-several-districts-army-ndrf-deployed-a517/</t>
+          <t>https://english.newsnationtv.com/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322</t>
         </is>
       </c>
     </row>
@@ -1355,468 +1355,468 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>7 killed as heavy rain batters Maharashtr­a; 800 villages hit</t>
+          <t>Mumbai To Welcome Historic Sword Of Shrimant Raje Raghuji Bhonsale On August 18; To Be Ceremoniously Unveiled</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://www.pressreader.com/india/the-hindu-mangalore-9WWc/20250819/281947433944151</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-to-welcome-historic-sword-of-shrimant-raje-raghuji-bhonsale-on-august-18-to-be-ceremoniously-unveiled-by-cm-fadnavis</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Business News</t>
+          <t>Fadnavis meets Guv Radhakrishnan, presents him book of Shivaji Maharaj's letters</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/business-news-credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis-7064653.html</t>
+          <t>https://www.newsdrum.in/national/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharajs-letters-9672415</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by Maharashtra CM Devendra Fadnavis</t>
+          <t>Rain fury leaves 7 dead in Maharashtra, 200 villagers stranded</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://english.newsnationtv.com/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322</t>
+          <t>https://www.newsdrum.in/national/rain-fury-leaves-7-dead-in-maharashtra-200-villagers-stranded-9674070</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Mumbai To Welcome Historic Sword Of Shrimant Raje Raghuji Bhonsale On August 18; To Be Ceremoniously Unveiled</t>
+          <t>CM Fadnavis unveils emblem for Ganeshotsav to be celebrated as Rajya Mahotsav</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-to-welcome-historic-sword-of-shrimant-raje-raghuji-bhonsale-on-august-18-to-be-ceremoniously-unveiled-by-cm-fadnavis</t>
+          <t>https://www.thehawk.in/news/india/cm-fadnavis-unveils-emblem-for-ganeshotsav-to-be-celebrated-as-rajya-mahotsav</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Fadnavis meets Guv Radhakrishnan, presents him book of Shivaji Maharaj's letters</t>
+          <t>Heavy rains lash Nanded: Five missing, scores stranded, says CM Fadnavis; Army unit deployed</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharajs-letters-9672415</t>
+          <t>https://www.newsdrum.in/national/heavy-rains-lash-nanded-five-missing-scores-stranded-says-cm-fadnavis-army-unit-deployed-9672306</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Rain fury leaves 7 dead in Maharashtra, 200 villagers stranded</t>
+          <t>Mumbai Weather Today LIVE Updates: Mithi River Crosses Danger Mark; Santacruz Records Highest Rainfall; 300</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/rain-fury-leaves-7-dead-in-maharashtra-200-villagers-stranded-9674070</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-rains-live-updates-heavy-showers-wreak-havoc-in-city-schools-colleges-shut-as-imd-issues-red-alert-sion-matunga-dadar-vile-parle-waterlogged-andheri-subway-closed</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CM Fadnavis unveils emblem for Ganeshotsav to be celebrated as Rajya Mahotsav</t>
+          <t>Maharashtra government approves major infra projects</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/india/cm-fadnavis-unveils-emblem-for-ganeshotsav-to-be-celebrated-as-rajya-mahotsav</t>
+          <t>https://www.thehawk.in/news/india/maharashtra-government-approves-major-infra-projects</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Fadnavis Gifts Unpublished Shivaji Maharaj Letters to Maharashtra Governor at Mumbai Airport</t>
+          <t>उप-राष्ट्रपति चुनाव: देवेंद्र फडणवीस का 'मराठी अस्मिता' वाला दांव, क्या करेंगे</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://panasiabiz.com/111091/cm-devendra-fadnavis-presents-rare-shivaji-maharaj-letters-to-governor-cp-radhakrishnan/</t>
+          <t>https://www.abplive.com/states/maharashtra/vice-president-election-2025-maharashtra-cm-devendra-fadnavis-request-uddhav-thackeray-and-sharad-pawar-2997542</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Heavy rains lash Nanded: Five missing, scores stranded, says CM Fadnavis; Army unit deployed</t>
+          <t>महाराष्ट्र के इस जिले में बसाई जाएगी 'तीसरी मुंबई', मुख्यमंत्री देवेंद्र फडणवीस ने बताईं प्रोजेक्ट की अहम ब</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/heavy-rains-lash-nanded-five-missing-scores-stranded-says-cm-fadnavis-army-unit-deployed-9672306</t>
+          <t>https://www.indiatv.in/paisa/business/third-mumbai-will-be-settled-in-raigad-district-of-maharashtra-chief-minister-devendra-fadnavis-told-the-important-points-of-the-project-2025-08-19-1156854</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Mumbai Weather Today LIVE Updates: Mithi River Crosses Danger Mark; Santacruz Records Highest Rainfall; 300</t>
+          <t>लगता है वो लोग देवेंद्र फडणवीस और एकनाथ शिंदे के बारे में नहीं जानते, CJI बीआर गवई ने क्यों कहा ऐसा?</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-rains-live-updates-heavy-showers-wreak-havoc-in-city-schools-colleges-shut-as-imd-issues-red-alert-sion-matunga-dadar-vile-parle-waterlogged-andheri-subway-closed</t>
+          <t>https://hindi.news18.com/news/nation/cji-br-gavai-take-devendra-fadnavis-eknath-shinde-name-bombay-high-court-new-circuit-bench-in-kolhapur-9520456.html</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Maharashtra government approves major infra projects</t>
+          <t>Mumbai Maharashtra Rains: महाराष्ट्र में भारी बारिश पर सीएम देवेंद्र फडणवीस का सख्त निर्देश, सभी विभाग अलर्ट पर</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/india/maharashtra-government-approves-major-infra-projects</t>
+          <t>https://thecsrjournal.in/mumbai-maharashtra-rains-cm-and-managment-on-alert-hindi/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>उप-राष्ट्रपति चुनाव: देवेंद्र फडणवीस का 'मराठी अस्मिता' वाला दांव, क्या करेंगे</t>
+          <t>दिल्ली पहुंचे देवेंद्र फडणवीस, अमित शाह से मिले, जानें क्यों थी यह मुलाकात खास</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/vice-president-election-2025-maharashtra-cm-devendra-fadnavis-request-uddhav-thackeray-and-sharad-pawar-2997542</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B6-%E0%A4%B9-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A5%87-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%82-%E0%A4%A5-%E0%A4%AF%E0%A4%B9-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4-%E0%A4%96-%E0%A4%B8/ar-AA1Jjy9z</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>महाराष्ट्र के इस जिले में बसाई जाएगी 'तीसरी मुंबई', मुख्यमंत्री देवेंद्र फडणवीस ने बताईं प्रोजेक्ट की अहम ब</t>
+          <t>मुख्यमंत्री देवेंद्र फडणवीस ने दी राज्यपाल राधाकृष्णन को उपराष्ट्रपति पद की उम्मीदवारता पर बधाई</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/paisa/business/third-mumbai-will-be-settled-in-raigad-district-of-maharashtra-chief-minister-devendra-fadnavis-told-the-important-points-of-the-project-2025-08-19-1156854</t>
+          <t>https://hindi.mid-day.com/news/india-news/article/chief-minister-devendra-fadnavis-congratulated-governor-radhakrishnan-on-his-candidature-for-the-post-of-vice-president-11180</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Mumbai Maharashtra Rains: महाराष्ट्र में भारी बारिश पर सीएम देवेंद्र फडणवीस का सख्त निर्देश, सभी विभाग अलर्ट पर</t>
+          <t>कैसी होगी तीसरी मुंबई, कितनी बड़ी और कहां बन रही, सुविधाओं से लेकर प्लानिंग तक, CM फडणवीस ने सब बताया</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/mumbai-maharashtra-rains-cm-and-managment-on-alert-hindi/</t>
+          <t>https://ndtv.in/maharashtra-news/maharashtra-cmdevendra-fadnavis-told-third-mumbai-mmr-will-develop-with-this-know-how-it-will-be-9112502</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>दिल्ली पहुंचे देवेंद्र फडणवीस, अमित शाह से मिले, जानें क्यों थी यह मुलाकात खास</t>
+          <t>Vice President Election: उद्धव ठाकरे और शरद पवार से फडणवीस मांगेंगे सीपी राधाकृष्णन के लिए समर्थन, शिंदे सेना ने दिया सपोर्ट</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B6-%E0%A4%B9-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A5%87-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%82-%E0%A4%A5-%E0%A4%AF%E0%A4%B9-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4-%E0%A4%96-%E0%A4%B8/ar-AA1Jjy9z</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-governor-radhakrishnan-gets-nda-backing-for-vice-president-post-devendra-fadnavis-uddhav-thackeray-sharad-pawar/articleshow/123371527.cms</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>कैसी होगी तीसरी मुंबई, कितनी बड़ी और कहां बन रही, सुविधाओं से लेकर प्लानिंग तक, CM फडणवीस ने सब बताया</t>
+          <t>मुख्यमंत्री देवेंद्र फडणवीस ने राज्य में भारी बारिश के मद्देनजर सभी एजेंसियों को सतर्क रहने के निर्देश दिए</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://ndtv.in/maharashtra-news/maharashtra-cmdevendra-fadnavis-told-third-mumbai-mmr-will-develop-with-this-know-how-it-will-be-9112502</t>
+          <t>https://www.mumbailive.com/hi/civic/chief-minister-devendra-fadnavis-directed-all-agencies-to-remain-alert-in-view-of-heavy-rains-in-the-state-89633</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Vice President Election: उद्धव ठाकरे और शरद पवार से फडणवीस मांगेंगे सीपी राधाकृष्णन के लिए समर्थन, शिंदे सेना ने दिया सपोर्ट</t>
+          <t>Mumbai Rain News : मुंबई में बारिश ने मचाया कोहराम, देवेंद्र फडणवीस का आया बयान</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-governor-radhakrishnan-gets-nda-backing-for-vice-president-post-devendra-fadnavis-uddhav-thackeray-sharad-pawar/articleshow/123371527.cms</t>
+          <t>https://hindi.oneindia.com/videos/mumbai-rain-news-rain-wreaked-havoc-in-mumbai-devendra-fadnavis-statement-came-4259449.html</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>मुख्यमंत्री देवेंद्र फडणवीस ने राज्य में भारी बारिश के मद्देनजर सभी एजेंसियों को सतर्क रहने के निर्देश दिए</t>
+          <t>मुंबई में भारी भारिश ने मचाई तबाही, CM देवेंद्र फडणवीस ने बुलाई बैठक</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://www.mumbailive.com/hi/civic/chief-minister-devendra-fadnavis-directed-all-agencies-to-remain-alert-in-view-of-heavy-rains-in-the-state-89633</t>
+          <t>https://www.patrika.com/videos/mumbai-news/heavy-rain-wreaks-havoc-in-mumbai-cm-devendra-fadnavis-calls-a-meeting-19874343</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>मुंबई में सिर्फ 6-8 घंटे में 177 मिमी हुई बारिश, फडणवीस ने दिए सावधानी बरतने के निर्देश</t>
+          <t>फडणवीस ने कहा, ‘तीसरी मुंबई’ से एमएमआर का होगा विकास</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/mumbai-received-177-mm-of-rain-in-just-6-8-hours-fadnavis-gave-instructions-to-take-precautions-11195</t>
+          <t>https://hindi.theprint.in/india/economy/fadnavis-said-third-mumbai-will-lead-to-development-of-mmr/856867/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Mumbai Rain News : मुंबई में बारिश ने मचाया कोहराम, देवेंद्र फडणवीस का आया बयान</t>
+          <t>महाराष्ट्र के नांदेड़ में फटा बादल, 15-16 जिलो में अलर्ट, CM फडणवीस बोले- फसलों को नुकसान</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/videos/mumbai-rain-news-rain-wreaked-havoc-in-mumbai-devendra-fadnavis-statement-came-4259449.html</t>
+          <t>https://www.abplive.com/states/maharashtra/weather-mumbai-rains-local-train-cloudburst-nanded-alert-in-15-16-districts-in-maharashtra-cm-devendra-fadnavis-said-damage-to-crops-2997472</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>मुंबई में भारी भारिश ने मचाई तबाही, CM देवेंद्र फडणवीस ने बुलाई बैठक</t>
+          <t>मैं आपकी वहिनी… देवेंद्र फडणविस के शपथ लेते ही पत्नी अमृता फडणवीस ने महाराष्ट्र से किया ये वादा</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/videos/mumbai-news/heavy-rain-wreaks-havoc-in-mumbai-cm-devendra-fadnavis-calls-a-meeting-19874343</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%88%E0%A4%82-%E0%A4%86%E0%A4%AA%E0%A4%95-%E0%A4%B5%E0%A4%B9-%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%B6%E0%A4%AA%E0%A4%A5-%E0%A4%B2%E0%A5%87%E0%A4%A4%E0%A5%87-%E0%A4%B9-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A8-%E0%A4%85%E0%A4%AE%E0%A5%83%E0%A4%A4-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%AF%E0%A5%87-%E0%A4%B5-%E0%A4%A6/ar-AA1vljO5?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>फडणवीस ने कहा, ‘तीसरी मुंबई’ से एमएमआर का होगा विकास</t>
+          <t>Mumbai Rains News: भारी बारिश के चलते कल मुंबई के स्कूल-कॉलेजों में छुट्टी, नांदेड़ में 7 लोगों की मौत, CM फडणवीस ने की आपात बैठक</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/economy/fadnavis-said-third-mumbai-will-lead-to-development-of-mmr/856867/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/heavy-rains-in-mumbai-schools-colleges-closed-7-deaths-in-maharashtra-5-missing-nanded-cm-fadnavis-emergency-meeting/articleshow/123366462.cms</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>महाराष्ट्र के नांदेड़ में फटा बादल, 15-16 जिलो में अलर्ट, CM फडणवीस बोले- फसलों को नुकसान</t>
+          <t>मुंबई में सिर्फ 6-8 घंटे में 177 मिमी हुई बारिश, फडणवीस ने दिए सावधानी बरतने के निर्देश</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/weather-mumbai-rains-local-train-cloudburst-nanded-alert-in-15-16-districts-in-maharashtra-cm-devendra-fadnavis-said-damage-to-crops-2997472</t>
+          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/mumbai-received-177-mm-of-rain-in-just-6-8-hours-fadnavis-gave-instructions-to-take-precautions-11195</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Mumbai Rains News: भारी बारिश के चलते कल मुंबई के स्कूल-कॉलेजों में छुट्टी, नांदेड़ में 7 लोगों की मौत, CM फडणवीस ने की आपात बैठक</t>
+          <t>CP Radhakrishnan को लेकर CM फडणवीस ने बड़ा खुलासा कर चल दिया दांव, अब क्‍या करेंगे उद्धव ठाकरे और शरद पवार?</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/heavy-rains-in-mumbai-schools-colleges-closed-7-deaths-in-maharashtra-5-missing-nanded-cm-fadnavis-emergency-meeting/articleshow/123366462.cms</t>
+          <t>https://hindi.oneindia.com/news/maharashtra/vice-presidential-election-cm-devendra-fadnavis-said-cp-radhakrishnan-is-a-mumbai-voter-support-him-1365243.html</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CP Radhakrishnan को लेकर CM फडणवीस ने बड़ा खुलासा कर चल दिया दांव, अब क्‍या करेंगे उद्धव ठाकरे और शरद पवार?</t>
+          <t>'औरंगजेब भारत के किसी भी समाज का हीरो नहीं...', मजार को लेकर फडणवीस ने कही बड़ी बात</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/maharashtra/vice-presidential-election-cm-devendra-fadnavis-said-cp-radhakrishnan-is-a-mumbai-voter-support-him-1365243.html</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%AD-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AE%E0%A4%9C-%E0%A4%B0-%E0%A4%95-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC-%E0%A4%A4/ar-AA1IRFiN</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>'औरंगजेब भारत के किसी भी समाज का हीरो नहीं...', मजार को लेकर फडणवीस ने कही बड़ी बात</t>
+          <t>मराठा सेनापति रघुजी भोंसले की 200 साल पुरानी तलवार पहुंची मुंबई, CM फडणवीस बोले-</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%AD-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AE%E0%A4%9C-%E0%A4%B0-%E0%A4%95-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC-%E0%A4%A4/ar-AA1IRFiN</t>
+          <t>https://www.abplive.com/states/maharashtra/london-auction-historic-raghuji-bhosale-sword-brought-to-mumbai-devendra-fadnavis-says-indias-heritage-restored-2997814</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>मराठा सेनापति रघुजी भोंसले की 200 साल पुरानी तलवार पहुंची मुंबई, CM फडणवीस बोले-</t>
+          <t>इसमें उनका घाटा...हिंदी-मराठी भाषा विवाद के बीच फडणवीस का बड़ा दावा, बोले- मुंबई का मेयर तो हमारा ही होगा</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/london-auction-historic-raghuji-bhosale-sword-brought-to-mumbai-devendra-fadnavis-says-indias-heritage-restored-2997814</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%87%E0%A4%B8%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%89%E0%A4%A8%E0%A4%95-%E0%A4%98-%E0%A4%9F-%E0%A4%B9-%E0%A4%82%E0%A4%A6-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%AD-%E0%A4%B7-%E0%A4%B5-%E0%A4%B5-%E0%A4%A6-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%9A-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%A6-%E0%A4%B5-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%95-%E0%A4%AE%E0%A5%87%E0%A4%AF%E0%A4%B0-%E0%A4%A4-%E0%A4%B9%E0%A4%AE-%E0%A4%B0-%E0%A4%B9-%E0%A4%B9-%E0%A4%97/ar-AA1ImpaC?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>मैं आपकी वहिनी… देवेंद्र फडणविस के शपथ लेते ही पत्नी अमृता फडणवीस ने महाराष्ट्र से किया ये वादा</t>
+          <t>मुंबई में 6-8 घंटे में 177 मिलीमीटर बारिश हुई: फडणवीस</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%88%E0%A4%82-%E0%A4%86%E0%A4%AA%E0%A4%95-%E0%A4%B5%E0%A4%B9-%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%B6%E0%A4%AA%E0%A4%A5-%E0%A4%B2%E0%A5%87%E0%A4%A4%E0%A5%87-%E0%A4%B9-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A8-%E0%A4%85%E0%A4%AE%E0%A5%83%E0%A4%A4-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%AF%E0%A5%87-%E0%A4%B5-%E0%A4%A6/ar-AA1vljO5?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://hindi.theprint.in/india/mumbai-received-177-mm-of-rain-in-6-8-hours-fadnavis/856688/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>इसमें उनका घाटा...हिंदी-मराठी भाषा विवाद के बीच फडणवीस का बड़ा दावा, बोले- मुंबई का मेयर तो हमारा ही होगा</t>
+          <t>फडणवीस की पत्नी के खिलाफ अपमानजनक पोस्ट : दो लोगों की अग्रिम जमानत अर्जी खारिज</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%87%E0%A4%B8%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%89%E0%A4%A8%E0%A4%95-%E0%A4%98-%E0%A4%9F-%E0%A4%B9-%E0%A4%82%E0%A4%A6-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%AD-%E0%A4%B7-%E0%A4%B5-%E0%A4%B5-%E0%A4%A6-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%9A-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%A6-%E0%A4%B5-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%95-%E0%A4%AE%E0%A5%87%E0%A4%AF%E0%A4%B0-%E0%A4%A4-%E0%A4%B9%E0%A4%AE-%E0%A4%B0-%E0%A4%B9-%E0%A4%B9-%E0%A4%97/ar-AA1ImpaC?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>http://www.msn.com/hi-in/news/other/%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%96-%E0%A4%B2-%E0%A4%AB-%E0%A4%85%E0%A4%AA%E0%A4%AE-%E0%A4%A8%E0%A4%9C%E0%A4%A8%E0%A4%95-%E0%A4%AA-%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%A6-%E0%A4%B2-%E0%A4%97-%E0%A4%82-%E0%A4%95-%E0%A4%85%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%9C%E0%A4%AE-%E0%A4%A8%E0%A4%A4-%E0%A4%85%E0%A4%B0%E0%A5%8D%E0%A4%9C-%E0%A4%96-%E0%A4%B0-%E0%A4%9C/ar-AA1Je80j?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Maharashtra: फडणवीस बोले- औरंगजेब भारत का हीरो नहीं, सुप्रीम कोर्ट के SC आरक्षण पर फैसले को लागू करेगी सरकार</t>
+          <t>नांदेड़ में भारी बारिश के कारण पांच लोग लापता, कई व्यक्ति फंसे : मुख्यमंत्री फडणवीस</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B8%E0%A5%81%E0%A4%AA%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%95%E0%A5%87-sc-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%AA%E0%A4%B0-%E0%A4%AB%E0%A5%88%E0%A4%B8%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B2-%E0%A4%97%E0%A5%82-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%97-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0/ar-AA1IRMGx</t>
+          <t>https://hindi.theprint.in/india/five-people-missing-many-people-stranded-due-to-heavy-rains-in-nanded-chief-minister-fadnavis/856679/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>मुंबई में 6-8 घंटे में 177 मिलीमीटर बारिश हुई: फडणवीस</t>
+          <t>Raghuji Bhosale: आज मुंबई आएगी रघुजी भोसले की की ऐतिहासिक तलवार, सीएम फडणवीस करेंगे स्वागत</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/mumbai-received-177-mm-of-rain-in-6-8-hours-fadnavis/856688/</t>
+          <t>https://zeenews.india.com/hindi/india/raghuji-bhosale-historic-sword-will-arrive-in-mumbai-today-cm-fadnavis-will-welcome-it/2886138</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>फडणवीस की पत्नी के खिलाफ अपमानजनक पोस्ट : दो लोगों की अग्रिम जमानत अर्जी खारिज</t>
+          <t>Mumbai Rain: 24 घंटे की बारिश से मुंबई की सांस फूली, CM देवेंद्र फडणवीस ने पड़ोसी राज्यों से किया संपर्क</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%96-%E0%A4%B2-%E0%A4%AB-%E0%A4%85%E0%A4%AA%E0%A4%AE-%E0%A4%A8%E0%A4%9C%E0%A4%A8%E0%A4%95-%E0%A4%AA-%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%A6-%E0%A4%B2-%E0%A4%97-%E0%A4%82-%E0%A4%95-%E0%A4%85%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%9C%E0%A4%AE-%E0%A4%A8%E0%A4%A4-%E0%A4%85%E0%A4%B0%E0%A5%8D%E0%A4%9C-%E0%A4%96-%E0%A4%B0-%E0%A4%9C/ar-AA1Je80j?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://zeenews.india.com/hindi/india/mumbai-rains-today-imd-red-alert-warning-waterlogging-traffic-update/2886161</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>नांदेड़ में भारी बारिश के कारण पांच लोग लापता, कई व्यक्ति फंसे : मुख्यमंत्री फडणवीस</t>
+          <t>महाराष्ट्र में भारी बारिश का कहर, 16 जिलों में रेड अलर्ट, बचाव दल तैनात</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/five-people-missing-many-people-stranded-due-to-heavy-rains-in-nanded-chief-minister-fadnavis/856679/</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-heavy-rainfall-flood-alert-red-and-orange-alerts-issued-relief-operations-mumbai-rain-ann-2997660</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Mumbai Rain: 24 घंटे की बारिश से मुंबई की सांस फूली, CM देवेंद्र फडणवीस ने पड़ोसी राज्यों से किया संपर्क</t>
+          <t>आज सपना पूरा हो गया... चीफ जस्टिस गवई ने ऐसा क्यों कहा, सीएम फडणवीस का लिया नाम</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/india/mumbai-rains-today-imd-red-alert-warning-waterlogging-traffic-update/2886161</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/cji-br-gavai-said-our-dream-has-been-fulfilled-over-bombay-high-court-new-circuit-bench-at-kolhapur-mention-cm-fadnavis-name-know-all/articleshow/123350750.cms</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Raghuji Bhosale: आज मुंबई आएगी रघुजी भोसले की की ऐतिहासिक तलवार, सीएम फडणवीस करेंगे स्वागत</t>
+          <t>महाराष्ट्र में भारी बारिश से सात लोगों की मौत, 200 ग्रामीण फंसे</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/india/raghuji-bhosale-historic-sword-will-arrive-in-mumbai-today-cm-fadnavis-will-welcome-it/2886138</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AD-%E0%A4%B0-%E0%A4%AC-%E0%A4%B0-%E0%A4%B6-%E0%A4%B8%E0%A5%87-%E0%A4%B8-%E0%A4%A4-%E0%A4%B2-%E0%A4%97-%E0%A4%82-%E0%A4%95-%E0%A4%AE-%E0%A4%A4-200-%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%A3-%E0%A4%AB%E0%A4%82%E0%A4%B8%E0%A5%87/ar-AA1KKl3K</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में भारी बारिश का कहर, 16 जिलों में रेड अलर्ट, बचाव दल तैनात</t>
+          <t>वो ऐतिहासिक तलवार जिसके लिए बिछाया जा रहा मुंबई में रेड कारपेट… मराठा साम्राज्य से है कनेक्शन</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-heavy-rainfall-flood-alert-red-and-orange-alerts-issued-relief-operations-mumbai-rain-ann-2997660</t>
+          <t>https://www.tv9hindi.com/india/raje-raghuji-bhosale-sword-history-maharashtra-cm-fadnavis-grand-welcome-3441860.html</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>'Indias Got Latent' विवाद पर अभिनेता से नेता तक भड़के, CM फडणवीस बोले-होना चाहिए एक्शन</t>
+          <t>महाराष्ट्र में बन रही है तीसरी मुंबई, इस जिले का होगा आर्थिक विकास, जानें पूरी जानकारी | News Track in...</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/indias-got-latent-%E0%A4%B5-%E0%A4%B5-%E0%A4%A6-%E0%A4%AA%E0%A4%B0-%E0%A4%85%E0%A4%AD-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%B8%E0%A5%87-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%A4%E0%A4%95-%E0%A4%AD%E0%A4%A1%E0%A4%BC%E0%A4%95%E0%A5%87-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%B9-%E0%A4%A8-%E0%A4%9A-%E0%A4%B9-%E0%A4%8F-%E0%A4%8F%E0%A4%95%E0%A5%8D%E0%A4%B6%E0%A4%A8/ar-AA1yKIjb?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://newstrack.com/india/third-mumbai-being-built-maharashtra-district-have-economic-development-know-full-details-534715</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में बन रही है तीसरी मुंबई, इस जिले का होगा आर्थिक विकास, जानें पूरी जानकारी | News Track in...</t>
+          <t>CM फडणवीस ने खेला 'मराठी अस्मिता' का दांव, उपराष्ट्रपति चुनाव में उद्धव-पवार पर बना दबाव</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>https://newstrack.com/india/third-mumbai-being-built-maharashtra-district-have-economic-development-know-full-details-534715</t>
+          <t>https://navbharatlive.com/maharashtra/political-battle-over-nda-candidate-radhakrishnan-cm-fadnavis-seeks-support-from-uddhav-thackeray-and-sharad-pawar-1321873.html</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>CM फडणवीस ने खेला 'मराठी अस्मिता' का दांव, उपराष्ट्रपति चुनाव में उद्धव-पवार पर बना दबाव</t>
+          <t>महाराष्ट्र किसानों को मिलेगी बड़ी राहत, CM फडणवीस जल्द करेंगे कर्जमाफी की घोषणा</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/political-battle-over-nda-candidate-radhakrishnan-cm-fadnavis-seeks-support-from-uddhav-thackeray-and-sharad-pawar-1321873.html</t>
+          <t>https://navbharatlive.com/maharashtra/guardian-minister-sanjay-rathore-claims-cm-fadnavis-may-announce-a-loan-waiver-for-farmers-1322081.html</t>
         </is>
       </c>
     </row>
@@ -1835,24 +1835,24 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>महाराष्ट्र किसानों को मिलेगी बड़ी राहत, CM फडणवीस जल्द करेंगे कर्जमाफी की घोषणा</t>
+          <t>नांदेड़ में मूसलधार बारिश से हाहाकार, CM फडणवीस की निगरानी में राहत कार्य तेज</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/guardian-minister-sanjay-rathore-claims-cm-fadnavis-may-announce-a-loan-waiver-for-farmers-1322081.html</t>
+          <t>https://navbharatlive.com/maharashtra/heavy-rains-cause-havoc-in-nanded-rescue-operation-intensified-under-the-supervision-of-cm-fadnavis-1321752.html</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>नांदेड़ में मूसलधार बारिश से हाहाकार, CM फडणवीस की निगरानी में राहत कार्य तेज</t>
+          <t>CM फडणवीस लगा रहे जोर, अधिकारी कर रहे मनामानी, FIA ने जतायी नाराजगी</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/heavy-rains-cause-havoc-in-nanded-rescue-operation-intensified-under-the-supervision-of-cm-fadnavis-1321752.html</t>
+          <t>https://navbharatlive.com/maharashtra/federation-of-industries-association-is-angry-due-to-ignorance-of-msme-sector-in-vidarbha-1322498.html</t>
         </is>
       </c>
     </row>
@@ -1871,24 +1871,24 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Maharashtra Live News 18 Aug: एक क्लिक में पढ़े महाराष्ट्र की दिन भर की बड़ी खब़रें...</t>
+          <t>अबू आजमी ने सीएम देवेंद्र फडणवीस को लिखा पत्र, बाढ़ प्रभावित इलाकों में राहत सामग्री पहुंचाने की मांग की</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/latest-live-updates-maharashtra-politics-crime-nagpur-news-mumbai-pune-18-august-1321138.html</t>
+          <t>https://www.newsnationtv.com/abu-azmi-ne-cm-devendra-fadnavis-ko-likha-patra-badh-prabhavit-ilakon-mein-rahat-pahunchane-ki-mang-ki--20250818191027/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>अबू आजमी ने सीएम देवेंद्र फडणवीस को लिखा पत्र, बाढ़ प्रभावित इलाकों में राहत सामग्री पहुंचाने की मांग की</t>
+          <t>Maharashtra Live News 18 Aug: एक क्लिक में पढ़े महाराष्ट्र की दिन भर की बड़ी खब़रें...</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>https://www.newsnationtv.com/abu-azmi-ne-cm-devendra-fadnavis-ko-likha-patra-badh-prabhavit-ilakon-mein-rahat-pahunchane-ki-mang-ki--20250818191027/</t>
+          <t>https://navbharatlive.com/maharashtra/latest-live-updates-maharashtra-politics-crime-nagpur-news-mumbai-pune-18-august-1321138.html</t>
         </is>
       </c>
     </row>
@@ -1955,384 +1955,384 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>उपराष्ट्रपति चुनाव में भाजपा का दांव, सीपी राधाकृष्णन उम्मीदवार, महाराष्ट्र की राजनीति में बढ़ी हलचल</t>
+          <t>राज्य को बाढ़ आपदा घोषित करो… विशेष अधिवेशन बुलाओ… एनसीपी प्रदेश अध्यक्ष ने की सीएम से मांग</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/maharashtra/vice-president-election-bjp-candidate-cp-radhakrishnan-devendra-fadnavis-54-803924</t>
+          <t>https://www.hindisaamana.com/declare-the-state-a-flood-disaster-call-a-special-session-ncp-state-president-made-a-demand-to-the-cm/</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>किसानों को जल्द मिल सकता है कर्जमाफी का तोहफा, मंत्री संजय राठोड़ का बड़ा बयान</t>
+          <t>(लीड)महाराष्ट्र में मूसलाधार बारिश से हाहाकार, सात लोगों की मौत</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/maharashtra/farmer-loan-waiver-maharashtra-sanjay-rathod-devendra-fadnavis-54-804134</t>
+          <t>https://livevns.news/National/panic-in-maharashtra-due-to-heavy-rainphp/cid17258961.htm</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Mumbai Rains: मुंबई में भारी बारिश से 12 लोगों की मौत, जगह-जगह कमर तक भरा पानी, स्कूल-कॉलेज बंद, फ्लाइट्स पर भी असर</t>
+          <t>उपराष्ट्रपति चुनाव में भाजपा का दांव, सीपी राधाकृष्णन उम्मीदवार, महाराष्ट्र की राजनीति में बढ़ी हलचल</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>https://lalluram.com/mumbai-rains-7-people-died-due-to-rain-water-flooded-on-roads-schools-and-colleges-closed-flights-also-affected/</t>
+          <t>https://mpbreakingnews.in/maharashtra/vice-president-election-bjp-candidate-cp-radhakrishnan-devendra-fadnavis-54-803924</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Mumbai: राज्यपाल की उपराष्ट्रपति पद की उम्मीदवारी पर मुख्यमंत्री ने जताया हर्ष</t>
+          <t>किसानों को जल्द मिल सकता है कर्जमाफी का तोहफा, मंत्री संजय राठोड़ का बड़ा बयान</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/mumbai-chief-minister-expressed-happiness-over-the-candidature-of-the-governor-for-the-post-of-vice-president-mumbai--4218462</t>
+          <t>https://mpbreakingnews.in/maharashtra/farmer-loan-waiver-maharashtra-sanjay-rathod-devendra-fadnavis-54-804134</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>लंदन से आई मराठा साम्राज्य की शान! रघुजी ?...</t>
+          <t>Mumbai: राज्यपाल की उपराष्ट्रपति पद की उम्मीदवारी पर मुख्यमंत्री ने जताया हर्ष</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>https://bharatexpress.com/india/raghuji-bhosale-historic-sword-returned-from-london-grand-welcome-in-mumbai-553050</t>
+          <t>https://jantaserishta.com/local/maharashtra/mumbai-chief-minister-expressed-happiness-over-the-candidature-of-the-governor-for-the-post-of-vice-president-mumbai--4218462</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>महाराष्ट्र की 'अस्मिता' की बात करने वाले उपराष्ट्रपति पद के लिए राधाकृष्णन का समर्थन करें : फडणवीस</t>
+          <t>अटल सेतु के पास रायगढ़ में बसेगी तीसरी मुंबई, जानें महाराष्ट्र सरकार का पूरा मास्टर प्लान क्या</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>https://navabharat.news/support-radhakrishnan-for-the-post-of-vice-president-who-talks-about-maharashtras-identity-fadnavis/</t>
+          <t>https://samacharnama.com/states/maharashtra-news/maharashtra-governments-master-plan-to-set-up-third-mumbai/cid17261301.htm</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Aakar Patel| New Maharashtra Security Law Open To Abuse, Threatens Rights; Say ‘No’ To It</t>
+          <t>लंदन से आई मराठा साम्राज्य की शान! रघुजी ?...</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>https://www.asianage.com/opinion/columnists/aakar-patel-new-maharashtra-security-law-open-to-abuse-threatens-rights-say-no-to-it-1898277</t>
+          <t>https://bharatexpress.com/india/raghuji-bhosale-historic-sword-returned-from-london-grand-welcome-in-mumbai-553050</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Rain fury leaves 7 dead in Maharashtra, 200 villagers stranded</t>
+          <t>Aakar Patel| New Maharashtra Security Law Open To Abuse, Threatens Rights; Say ‘No’ To It</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/rain-fury-leaves-7-dead-in-maharashtra,-200-villagers-stranded/2834213</t>
+          <t>https://www.asianage.com/opinion/columnists/aakar-patel-new-maharashtra-security-law-open-to-abuse-threatens-rights-say-no-to-it-1898277</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>CREDAI-MCHI appoints Sukhraj Nahar as 18th President</t>
+          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by Maharashtra CM Devendra Fadnavis</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>https://housing.com/news/credai-mchi-appoints-sukhraj-nahar-as-president/</t>
+          <t>https://www.aninews.in/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Maharashtra CM Devendra Fadnavis Says ‘Third Mumbai’ Being Developed in Raigad District Will Open New</t>
+          <t>"Observe precaution": Maharashtra CM warns about severe weather conditions in state</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/india/news/maharashtra-cm-devendra-fadnavis-says-third-mumbai-being-developed-in-raigad-district-will-open-new-chapter-of-economic-development-7064927.html</t>
+          <t>https://thenewsmill.com/2025/08/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state/</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>"Observe precaution": Maharashtra CM warns about severe weather conditions in state</t>
+          <t>CM to inaugurate additional water supply scheme</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/08/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state/</t>
+          <t>https://www.lokmattimes.com/aurangabad/cm-to-inaugurate-additional-water-supply-scheme/</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Mumbai got 177mm rain in 6-8 hour period, says CM; more to come amid high tides</t>
+          <t>Mumbai Rains LIVE Updates: 250–300 mm Downpour Likely Tonight; Schools &amp; Colleges To Remain Shut On Tuesday</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/mumbai-got-177mm-rain-in-6-8-hour-period-says-cm-more-to-come-amid-high-tides-9672488</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-live-updates-check-for-latest-updates-of-all-the-happeneings-in-mumbai</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>NCP (SP) targets Maha minister over Rs 5,000 cr scam in Navi Mumbai’s CIDCO land; demands his resignation</t>
+          <t>Mumbai rains: IMD issues red alert as downpour continues; schools, colleges &amp; Govt offices shut</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/ncp-sp-targets-maha-minister-over-rs-5000-cr-scam-in-navi-mumbais-cidco-land-demands-his-resignation/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=ncp-sp-targets-maha-minister-over-rs-5000-cr-scam-in-navi-mumbais-cidco-land-demands-his-resignation</t>
+          <t>https://newslivetv.com/mumbai-rains-imd-issues-red-alert/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>CM to inaugurate additional water supply scheme</t>
+          <t>राज्यात अतिवृष्टीमुळे मुख्यमंत्री देवेंद्र फडणवीस यांचे सर्व यंत्रणांना सतर्कतेचे निर्देश; नांदेड जिल्ह्यात लष्कराची मदत</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/aurangabad/cm-to-inaugurate-additional-water-supply-scheme/</t>
+          <t>https://www.loksatta.com/mumbai/chief-minister-devendra-fadnavis-has-directed-all-agencies-to-be-on-alert-due-to-heavy-rains-in-the-maharashtra-mumbai-print-news-amy-95-5313479/</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Mumbai rains: IMD issues red alert as downpour continues; schools, colleges &amp; Govt offices shut</t>
+          <t>पुढील १२ तास मुंबईसाठी अत्यंत महत्त्वाचे, मुख्यमंत्री फडणवीस पावसाबाबत काय म्हणाले?</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>https://newslivetv.com/mumbai-rains-imd-issues-red-alert/</t>
+          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-review-mumbai-rain-says-next-12-hours-important-for-mumbai-and-mmr-region-1460967.html</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>राज्यात अतिवृष्टीमुळे मुख्यमंत्री देवेंद्र फडणवीस यांचे सर्व यंत्रणांना सतर्कतेचे निर्देश; नांदेड जिल्ह्यात लष्कराची मदत</t>
+          <t>Mumbai Rain : मुंबईत संध्याकाळी समुद्राला भरती, पुढील 12 तास महत्त्वाचे, पावसाच्या थैमानानंतर</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/chief-minister-devendra-fadnavis-has-directed-all-agencies-to-be-on-alert-due-to-heavy-rains-in-the-maharashtra-mumbai-print-news-amy-95-5313479/</t>
+          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-on-mumbai-maharashtra-rain-today-visit-disaster-management-department-bmc-marathi-news-1377962</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>पुढील १२ तास मुंबईसाठी अत्यंत महत्त्वाचे, मुख्यमंत्री फडणवीस पावसाबाबत काय म्हणाले?</t>
+          <t>Mumbai Rain Update : समुद्रातून येतंय मुंबईवर मोठं संकट, पुढच्या 12 तासांत तुफान पाऊस, फडणवीस काय...</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-review-mumbai-rain-says-next-12-hours-important-for-mumbai-and-mmr-region-1460967.html</t>
+          <t>https://www.tv9marathi.com/maharashtra/mumbai-rain-alert-cm-devendra-fadnavis-said-mumbai-have-red-alert-school-holiday-declared-know-detail-information-in-marathi-1472488.html</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Mumbai Rain : मुंबईत संध्याकाळी समुद्राला भरती, पुढील 12 तास महत्त्वाचे, पावसाच्या थैमानानंतर</t>
+          <t>राज्यभरात पावसाचा हाहाकार, मुख्यमंत्री देवेंद्र फडणवीस यांनी घेतला आढावा; सर्व यंत्रणांना सतर्कतेचे निर्देश</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-on-mumbai-maharashtra-rain-today-visit-disaster-management-department-bmc-marathi-news-1377962</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/rains-lashed-the-state-chief-minister-devendra-fadnavis-took-stock-instructed-all-agencies-to-be-alert.html</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>राज्यभरात पावसाचा हाहाकार, मुख्यमंत्री देवेंद्र फडणवीस यांनी घेतला आढावा; सर्व यंत्रणांना सतर्कतेचे निर्देश</t>
+          <t>राज्यात अतिवृष्टीच्या पार्श्वभूमीवर प्रशासन अलर्ट मोडवर! मुख्यमंत्री देवेंद्र फडणवीस यांचे सतर्कतेचे निर्देश</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/rains-lashed-the-state-chief-minister-devendra-fadnavis-took-stock-instructed-all-agencies-to-be-alert.html</t>
+          <t>https://www.navarashtra.com/maharashtra/cm-devendra-fadnavis-took-review-of-rain-situation-at-state-disaster-management-centre-in-the-ministry-963383.html</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Mumbai Rain Update : समुद्रातून येतंय मुंबईवर मोठं संकट, पुढच्या 12 तासांत तुफान पाऊस, फडणवीस काय...</t>
+          <t>Farmers Loan Waiver: बावनकुळेंनंतर महायुती सरकारमधील 'या' मंत्र्याची कर्जमाफीबाबत मोठी अपडेट; म्हणाले,'CM फडणवीस लवकरच...'</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/mumbai-rain-alert-cm-devendra-fadnavis-said-mumbai-have-red-alert-school-holiday-declared-know-detail-information-in-marathi-1472488.html</t>
+          <t>https://sarkarnama.esakal.com/amp/story/maharashtra/vidarbha/sanjay-rathod-update-farmer-loan-waiver-devendra-fadnavis-dk88</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>राज्यात अतिवृष्टीच्या पार्श्वभूमीवर प्रशासन अलर्ट मोडवर! मुख्यमंत्री देवेंद्र फडणवीस यांचे सतर्कतेचे निर्देश</t>
+          <t>Devendra Fadnavis : महाराष्ट्रातील माणसाला सर्वांनी समर्थन द्यावं; फडणवीस यांचे मविआला आवाहन</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/cm-devendra-fadnavis-took-review-of-rain-situation-at-state-disaster-management-centre-in-the-ministry-963383.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-appeals-to-maharashtra-mps-to-support-cp-radhakrishnan-for-vice-president/913103/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Farmers Loan Waiver: बावनकुळेंनंतर महायुती सरकारमधील 'या' मंत्र्याची कर्जमाफीबाबत मोठी अपडेट; म्हणाले,'CM फडणवीस लवकरच...'</t>
+          <t>सरदार रघुजी भोसले यांची ऐतिहासिक तलवार मुंबईत दाखल; मुख्यमंत्र्यांच्या हस्ते होणार लोकार्पण</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/amp/story/maharashtra/vidarbha/sanjay-rathod-update-farmer-loan-waiver-devendra-fadnavis-dk88</t>
+          <t>https://www.etvbharat.com/mr/!state/sword-of-maratha-commander-raghuji-bhosale-returns-to-mumbai-to-be-unveiled-at-exhibition-by-cm-fadnavis-maharashtra-news-mhs25081803521</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>सरदार रघुजी भोसले यांची ऐतिहासिक तलवार मुंबईत दाखल; मुख्यमंत्र्यांच्या हस्ते होणार लोकार्पण</t>
+          <t>Devendra Fadnavis : अख्खा पक्ष विरोधात, पण या दिग्गज नेत्याचा फडणवीसांना पाठिंबा, एका पत्राने राजकीय वर्तु...</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/sword-of-maratha-commander-raghuji-bhosale-returns-to-mumbai-to-be-unveiled-at-exhibition-by-cm-fadnavis-maharashtra-news-mhs25081803521</t>
+          <t>https://news18marathi.com/maharashtra/cm-devendra-fadnavis-gets-support-from-congress-leader-nitin-raut-letter-goes-viral-1461146.html</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis : अख्खा पक्ष विरोधात, पण या दिग्गज नेत्याचा फडणवीसांना पाठिंबा, एका पत्राने राजकीय वर्तु...</t>
+          <t>नवीन पिढीला इतिहासाशी जोडण्याचे कार्य सुरू; मुख्यमंत्री देवेंद्र फडणवीस यांचे प्रतिपादन</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/cm-devendra-fadnavis-gets-support-from-congress-leader-nitin-raut-letter-goes-viral-1461146.html</t>
+          <t>https://www.loksatta.com/mumbai/devendra-fadnavis-asserts-that-the-work-of-connecting-the-new-generation-with-history-is-underway-mumbai-print-news-amy-95-5313830/</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>नवीन पिढीला इतिहासाशी जोडण्याचे कार्य सुरू; मुख्यमंत्री देवेंद्र फडणवीस यांचे प्रतिपादन</t>
+          <t>CM देवेंद्र फडणवीस लवकरच कर्जमाफीची घोषणा करतील महायुतीच्या मंत्र्यांनी दिली</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/devendra-fadnavis-asserts-that-the-work-of-connecting-the-new-generation-with-history-is-underway-mumbai-print-news-amy-95-5313830/</t>
+          <t>https://marathi.abplive.com/news/politics/cm-devendra-fadnavis-will-soon-announce-loan-waiver-farmers-mahayuti-ministers-sanjay-rathod-gave-information-yavatmal-1377983</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>CM देवेंद्र फडणवीस लवकरच कर्जमाफीची घोषणा करतील महायुतीच्या मंत्र्यांनी दिली</t>
+          <t>Mumbai Rain: मुंबईत उद्या शाळांना सुट्टी? पुढचे १२ तास महत्वाचे, मुख्यमंत्री नेमकं काय म्हणाले?</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/cm-devendra-fadnavis-will-soon-announce-loan-waiver-farmers-mahayuti-ministers-sanjay-rathod-gave-information-yavatmal-1377983</t>
+          <t>https://saamtv.esakal.com/amp/story/mumbai-pune/mumbai-rain-alert-cm-devendra-fadnavis-said-mumbai-schools-declared-holiday-on-tomorrow-bmc-to-decide-pvm91</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Mumbai Rain: मुंबईत उद्या शाळांना सुट्टी? पुढचे १२ तास महत्वाचे, मुख्यमंत्री नेमकं काय म्हणाले?</t>
+          <t>मोठी बातमी! नाराजी भोवली, शिवसेना शिंदे गटाला सर्वात मोठा धक्का, बड्या नेत्यानं सोडली एकनाथ शिंदेंची...</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/mumbai-pune/mumbai-rain-alert-cm-devendra-fadnavis-said-mumbai-schools-declared-holiday-on-tomorrow-bmc-to-decide-pvm91</t>
+          <t>https://www.tv9marathi.com/maharashtra/big-blow-to-eknath-shinde-big-leader-of-shiv-sena-shinde-group-will-join-bjp-1472541.html</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>मोठी बातमी! शेतकऱ्यांची कर्जमाफी होणार, मुख्यमंत्री घोषणा करणार, बड्या मंत्र्याने दिली माहिती</t>
+          <t>Maharashtra Rain Updates: मुंबईसाठी पुढील 12 तास महत्त्वाचे, राज्यात स्थिती काय? CM फडणवीसांनी सगळं सांगितल...</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/big-update-on-farmer-loan-waiver-cm-fadnavis-will-do-announcement-says-minister-sanjay-rathod-1472819.html</t>
+          <t>https://news18marathi.com/maharashtra/maharashtra-rain-update-cm-devendra-fadnavis-hold-meeting-with-district-administration-1460734.html</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Maharashtra Rain Updates: मुंबईसाठी पुढील 12 तास महत्त्वाचे, राज्यात स्थिती काय? CM फडणवीसांनी सगळं सांगितल...</t>
+          <t>गौरवशाली इतिहासाशी नव्या पीढीला जोडण्याचं काम रघुजीराजे भोसल्यांची ऐतिहासिक</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/maharashtra-rain-update-cm-devendra-fadnavis-hold-meeting-with-district-administration-1460734.html</t>
+          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-mumbai-exhibition-of-nagpur-raghuji-raje-bhosle-historical-sword-marathi-news-1378075</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>गौरवशाली इतिहासाशी नव्या पीढीला जोडण्याचं काम रघुजीराजे भोसल्यांची ऐतिहासिक</t>
+          <t>Mumbai Rain Updates : सात जणांचा मृत्यू ते शेकडो गावे बाधित; राज्यभरात अतिवृष्टीमुळे कुठे काय घडलं?</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-mumbai-exhibition-of-nagpur-raghuji-raje-bhosle-historical-sword-marathi-news-1378075</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-updates-18-august-heavy-rainfall-mumbai-navi-mumbai-kolhapur-raigad-sindhudurag-local-train-latest-updates-traffic-news-rak-94-5312079/</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Mumbai Rain Updates : सात जणांचा मृत्यू ते शेकडो गावे बाधित; राज्यभरात अतिवृष्टीमुळे कुठे काय घडलं?</t>
+          <t>मोठी बातमी! शेतकऱ्यांची कर्जमाफी होणार, मुख्यमंत्री घोषणा करणार, बड्या मंत्र्याने दिली माहिती</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-updates-18-august-heavy-rainfall-mumbai-navi-mumbai-kolhapur-raigad-sindhudurag-local-train-latest-updates-traffic-news-rak-94-5312079/</t>
+          <t>https://www.tv9marathi.com/maharashtra/big-update-on-farmer-loan-waiver-cm-fadnavis-will-do-announcement-says-minister-sanjay-rathod-1472819.html</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>मोठी बातमी! नाराजी भोवली, शिवसेना शिंदे गटाला सर्वात मोठा धक्का, बड्या नेत्यानं सोडली एकनाथ शिंदेंची...</t>
+          <t>प्रशासन सतर्क : नागरिकांनी घराबाहेर पडू नये: मुख्यमंत्री फडणवीस !</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/big-blow-to-eknath-shinde-big-leader-of-shiv-sena-shinde-group-will-join-bjp-1472541.html</t>
+          <t>https://vishwanewsmarathi.com/administrator-citizens-should-not-stay-home-chief-minister/</t>
         </is>
       </c>
     </row>
@@ -2363,252 +2363,252 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>प्रशासन सतर्क : नागरिकांनी घराबाहेर पडू नये: मुख्यमंत्री फडणवीस !</t>
+          <t>मुख्यमंत्री फडणवीस लवकरच शेतकरी कर्जमाफीची घोषणा करण्याची शक्यता</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/administrator-citizens-should-not-stay-home-chief-minister/</t>
+          <t>https://www.dainikprabhat.com/cm-fadnavis-likely-to-announce-farm-loan-waiver-soon/</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Heavy Rain: राज्यात अतिवृष्टीच्या पार्श्वभूमीवर मुख्यमंत्री देवेंद्र फडणवीस यांचे सर्व यंत्रणांना सतर्कतेचे</t>
+          <t>शेतकरी कर्जमाफीबाबत महायुतीमधील मंत्र्याने दिली महत्त्वाची माहिती; “देवेंद्र फडणवीस लवकरच….”</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/heavy-raincm-devendra-fadnavis-agencies-alert-heavy-rain-state/</t>
+          <t>https://www.dainikprabhat.com/mahayuti-minister-gives-important-information-regarding-farmer-loan-waiver-devendra-fadnavis-soon/</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis : महाराष्ट्रातील माणसाला सर्वांनी समर्थन द्यावे; मुख्यमंत्री फडणवीस यांचे मविआच्या खासदारांना आवाहन</t>
+          <t>महाराष्ट्रातील शेतकऱ्यांना मोठा दिलासा, मुख्यमंत्री फडणवीस लवकरच कर्जमाफीची घोषणा करणार</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/devendra-fadnavis-everyone-should-support-the-people-of-maharashtra-chief-minister-fadnavis-appeals-to-m-v-a-mps/</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/big-relief-for-farmers-in-maharashtra-chief-minister-fadnavis-will-soon-announce-loan-waiver-125081900014_1.html</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>मुख्यमंत्री फडणवीस लवकरच शेतकरी कर्जमाफीची घोषणा करण्याची शक्यता</t>
+          <t>एकनाथ शिंदेंना सोलापुरात मोठा धक्का : नेत्यांने सोडली साथ !</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/cm-fadnavis-likely-to-announce-farm-loan-waiver-soon/</t>
+          <t>https://vishwanewsmarathi.com/big-setback-for-eknath-shinde-in-solapur-leaders-leave-support/</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>शेतकरी कर्जमाफीबाबत महायुतीमधील मंत्र्याने दिली महत्त्वाची माहिती; “देवेंद्र फडणवीस लवकरच….”</t>
+          <t>युवकांसाठी सुवर्णसंधी! महाराष्ट्रातील 'या' जिल्ह्यात आयटी पार्क होणार, मुख्यमंत्र्यांचा मोठा निर्णय</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/mahayuti-minister-gives-important-information-regarding-farmer-loan-waiver-devendra-fadnavis-soon/</t>
+          <t>https://www.thodkyaat.com/it-park-in-solapur-announced-by-cm-devendra-fadnavis-boost-to-jobs-and-development/</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>महाराष्ट्रातील शेतकऱ्यांना मोठा दिलासा, मुख्यमंत्री फडणवीस लवकरच कर्जमाफीची घोषणा करणार</t>
+          <t>School Closed | मोठी बातमी! पावसामुळे आज महाराष्ट्रातील 'या' जिल्ह्यातील शाळा बंद</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/big-relief-for-farmers-in-maharashtra-chief-minister-fadnavis-will-soon-announce-loan-waiver-125081900014_1.html</t>
+          <t>https://www.thodkyaat.com/maharashtra-school-closed-tomorrow/</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>एकनाथ शिंदेंना सोलापुरात मोठा धक्का : नेत्यांने सोडली साथ !</t>
+          <t>ना. पंकजाताई मुंडे यांना ‘कोहिनूर ऑफ इंडिया’ अवाॅर्ड, लोकमत वृतपत्र समुहाने केला सन्मान; लंडन येथे पार पडला दिमाखदार सोहळा</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/big-setback-for-eknath-shinde-in-solapur-leaders-leave-support/</t>
+          <t>https://lokashanews.com/28165/</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>School Closed | मोठी बातमी! पावसामुळे आज महाराष्ट्रातील 'या' जिल्ह्यातील शाळा बंद</t>
+          <t>Mumbai Rains : गुडघाभर पाणी, समोर रस्ताही दिसेना, लोकल रखडल्या आठवड्याच्या सुरुवातीला पावसानं मुंबईकरांची दाणादाण, पहा PHOTO</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>https://www.thodkyaat.com/maharashtra-school-closed-tomorrow/</t>
+          <t>https://marathi.asianetnews.com/mumbai/mumbai-heavy-rain-waterlogging-local-delays-school-shutdown/photoshow-at2tgam</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ना. पंकजाताई मुंडे यांना ‘कोहिनूर ऑफ इंडिया’ अवाॅर्ड, लोकमत वृतपत्र समुहाने केला सन्मान; लंडन येथे पार पडला दिमाखदार सोहळा</t>
+          <t>Mumbai News: गोल्डमन सॅक्सचे मुंबई नवे कार्यालय तिसऱ्या मुंबईचा नवा अध्याय - देवेंद्र फडणवीस</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>https://lokashanews.com/28165/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/goldman-sachs-new-mumbai-office-is-a-new-chapter-for-third-mumbai-devendra-fadnavis-89597</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Mumbai Rains : गुडघाभर पाणी, समोर रस्ताही दिसेना, लोकल रखडल्या आठवड्याच्या सुरुवातीला पावसानं मुंबईकरांची दाणादाण, पहा PHOTO</t>
+          <t>Mumbai Rain News: मुंबईत किती ठिकाणी पाणी साचलं? ट्राफिकची स्थिती काय? मुख्यमंत्र्यांनी दिली A to Z माहिती</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>https://marathi.asianetnews.com/mumbai/mumbai-heavy-rain-waterlogging-local-delays-school-shutdown/photoshow-at2tgam</t>
+          <t>https://marathi.ndtv.com/cities/mumbai-rain-news-chief-minister-devendra-fadnavis-gave-information-about-the-rainfall-situation-in-mumbai-9107883</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Mumbai News: गोल्डमन सॅक्सचे मुंबई नवे कार्यालय तिसऱ्या मुंबईचा नवा अध्याय - देवेंद्र फडणवीस</t>
+          <t>“मुंबईत पुढच्या १२ तासांत तुफान पाऊस, रेड अलर्ट आणि…”; मुख्यमंत्री देवेंद्र फडणवीस यांनी काय माहिती दिली?</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/goldman-sachs-new-mumbai-office-is-a-new-chapter-for-third-mumbai-devendra-fadnavis-89597</t>
+          <t>https://www.loksatta.com/maharashtra/mumbai-rain-alert-cm-devendra-fadnavis-said-mumbai-have-red-alert-school-holiday-declared-know-details-scj-81-5312934/</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Mumbai Rain News: मुंबईत किती ठिकाणी पाणी साचलं? ट्राफिकची स्थिती काय? मुख्यमंत्र्यांनी दिली A to Z माहिती</t>
+          <t>Pune News : मुख्यमंत्री फडणवीसांमुळे पुणेकरांना रोज मनस्ताप? काँग्रेसचा गंभीर आरोप</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/mumbai-rain-news-chief-minister-devendra-fadnavis-gave-information-about-the-rainfall-situation-in-mumbai-9107883</t>
+          <t>https://sarkarnama.esakal.com/pune/devendra-fadnavis-pune-flyover-inauguration-delay-dk88-sm89</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>“मुंबईत पुढच्या १२ तासांत तुफान पाऊस, रेड अलर्ट आणि…”; मुख्यमंत्री देवेंद्र फडणवीस यांनी काय माहिती दिली?</t>
+          <t>Devendra Fadanvis on Rain Update : मुंबईला रेड अलर्ट ! मुख्यमंत्री देवेंद्र फडणवीस यांनी पावसाबद्दल दिली महत्त्वाची अपडेट</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/mumbai-rain-alert-cm-devendra-fadnavis-said-mumbai-have-red-alert-school-holiday-declared-know-details-scj-81-5312934/</t>
+          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/maharashtra-hevey-rain-update-cm-devendra-fadanvis-gives-important-information-know-about-more-/40070</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Pune News : मुख्यमंत्री फडणवीसांमुळे पुणेकरांना रोज मनस्ताप? काँग्रेसचा गंभीर आरोप</t>
+          <t>महाराष्ट्रात महाभयानक पाऊस! मुख्यमंत्री देवेंद्र फडणवीस यांनी तातडीने साधला शेजारील राज्यांशी संपर्क? कारण अतिशय चिंताजनक</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/pune/devendra-fadnavis-pune-flyover-inauguration-delay-dk88-sm89</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/maharashtra-mumbai-rain-alert-update-chief-minister-devendra-fadnavis-immediately-contacted-the-neighboring-states/933328</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Devendra Fadanvis on Rain Update : मुंबईला रेड अलर्ट ! मुख्यमंत्री देवेंद्र फडणवीस यांनी पावसाबद्दल दिली महत्त्वाची अपडेट</t>
+          <t>Crop damage : 4 लाख हेक्टर क्षेत्रावरील पिकांची हानी</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/maharashtra-hevey-rain-update-cm-devendra-fadanvis-gives-important-information-know-about-more-/40070</t>
+          <t>https://pudhari.news/maharashtra/mumbai/crop-damage-4-lakh-hectares-ab96</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>महाराष्ट्रात महाभयानक पाऊस! मुख्यमंत्री देवेंद्र फडणवीस यांनी तातडीने साधला शेजारील राज्यांशी संपर्क? कारण अतिशय चिंताजनक</t>
+          <t>Third Mumbai News: तिसरी मुंबई आणि आर्थिक विकासाबाबत CM फडणवीसांचे मोठे विधान</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/maharashtra-mumbai-rain-alert-update-chief-minister-devendra-fadnavis-immediately-contacted-the-neighboring-states/933328</t>
+          <t>https://marathi.ndtv.com/maharashtra/third-mumbai-will-open-a-new-chapter-of-economic-development-says-cm-devendra-fadnavis-9110192</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Third Mumbai News: तिसरी मुंबई आणि आर्थिक विकासाबाबत CM फडणवीसांचे मोठे विधान</t>
+          <t>Maharashtra Rain : राज्यासाठी पुढचे दोन दिवस चिंतेचे, 15-16 जिल्ह्यांना अलर्ट, कुठे होणार अतिवृष्टी?...</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/third-mumbai-will-open-a-new-chapter-of-economic-development-says-cm-devendra-fadnavis-9110192</t>
+          <t>https://www.tv9marathi.com/videos/maharashtra-imd-issues-red-alert-for-16-districts-big-information-by-cm-devendra-fadnavis-reviews-heavy-rains-in-1472606.html</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Maharashtra Rain : राज्यासाठी पुढचे दोन दिवस चिंतेचे, 15-16 जिल्ह्यांना अलर्ट, कुठे होणार अतिवृष्टी?...</t>
+          <t>Mumbai Rains Updates: मुंबईकरांनो पुढील 12 तास अतिशय महत्त्वाचे, CM फडणवीसांनी केले हे आवाहन</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/maharashtra-imd-issues-red-alert-for-16-districts-big-information-by-cm-devendra-fadnavis-reviews-heavy-rains-in-1472606.html</t>
+          <t>https://marathi.ndtv.com/maharashtra/mumbai-rains-update-next-12-hours-are-important-for-mumbai-7-people-died-across-state-in-2-days-cm-fadnavis-appeals-to-citizens-9109288</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Mumbai Rains Updates: मुंबईकरांनो पुढील 12 तास अतिशय महत्त्वाचे, CM फडणवीसांनी केले हे आवाहन</t>
+          <t>पुण्यात नवीन महापालिकांवरून देवेंद्र फडणवीस आणि अजित पवार यांच्यात मतभेद का?</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/mumbai-rains-update-next-12-hours-are-important-for-mumbai-7-people-died-across-state-in-2-days-cm-fadnavis-appeals-to-citizens-9109288</t>
+          <t>https://www.loksatta.com/politics/devendra-fadnavis-ajit-pawar-dispute-over-new-municipal-corporations-in-pune-district-print-politics-news-css-98-5314697/</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>पुण्यात नवीन महापालिकांवरून देवेंद्र फडणवीस आणि अजित पवार यांच्यात मतभेद का?</t>
+          <t>16 जिल्ह्यांना रेड अलर्ट! राज्याच्या ‘या’ भागात अतिवृष्टी, बचाव पथक सज्ज; CM फडणवीसांची...</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/devendra-fadnavis-ajit-pawar-dispute-over-new-municipal-corporations-in-pune-district-print-politics-news-css-98-5314697/</t>
+          <t>https://www.tv9marathi.com/maharashtra/rain-alert-in-16-districts-heavy-rainfall-in-this-part-of-state-cm-fadnavis-give-information-1472499.html</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>16 जिल्ह्यांना रेड अलर्ट! राज्याच्या ‘या’ भागात अतिवृष्टी, बचाव पथक सज्ज; CM फडणवीसांची...</t>
+          <t>मुख्यमंत्री देवेंद्र फडणवीसांकडून पावसाचा आढावा: महाराष्ट्रात 4 लाख हेक्टरवरील पिके पाण्यात, उपाययोजनांचे ज...</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/rain-alert-in-16-districts-heavy-rainfall-in-this-part-of-state-cm-fadnavis-give-information-1472499.html</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/cm-devendra-fadnavis-review-maharashtra-flood-135703334.html</t>
         </is>
       </c>
     </row>
@@ -2627,156 +2627,156 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>मुख्यमंत्री देवेंद्र फडणवीसांकडून पावसाचा आढावा: महाराष्ट्रात 4 लाख हेक्टरवरील पिके पाण्यात, उपाययोजनांचे ज...</t>
+          <t>Devendra Fadnavis| मुख्यमंत्री देवेंद्र फडणवीस १९ रोजी पैठण तालुक्यात</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/cm-devendra-fadnavis-review-maharashtra-flood-135703334.html</t>
+          <t>https://pudhari.news/maharashtra/marathwada/chhatrapati-sambhajinagar/devendra-fadnavis-visit-paithan-taluka-19-august-ng81</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Maharashtra Politics : एकनाथ शिंदेंची कोण करतंय कोंडी? दिल्ली दौरे वाढण्यामागचं काय कारण?</t>
+          <t>तिसरी मुंबई आर्थिक विकासाचा नवा अध्याय – मुख्यमंत्री देवेंद्र फडणवीस</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/maharashtra-politics-shiv-sena-eknath-shinde-bjp-devendra-fadnavis-conflict-before-bmc-election-sdp-92-5314661/lite/</t>
+          <t>https://mahasamvad.in/176127/</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Crop damage : 4 लाख हेक्टर क्षेत्रावरील पिकांची हानी</t>
+          <t>Maharashtra Politics : एकनाथ शिंदेंची कोण करतंय कोंडी? दिल्ली दौरे वाढण्यामागचं काय कारण?</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/crop-damage-4-lakh-hectares-ab96</t>
+          <t>https://www.loksatta.com/politics/maharashtra-politics-shiv-sena-eknath-shinde-bjp-devendra-fadnavis-conflict-before-bmc-election-sdp-92-5314661/lite/</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>तिसरी मुंबई आर्थिक विकासाचा नवा अध्याय – मुख्यमंत्री देवेंद्र फडणवीस</t>
+          <t>Maharashtra Heavy Rainfall | राज्यभरात अतिवृष्टीचा कहर; १५ जिल्ह्यांत रेड आणि ऑरेंज अलर्ट, नागरिकांनी घराबाहेर पडू नये: मुख्यमंत्री फडणवीस</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176127/</t>
+          <t>https://pudhari.news/maharashtra/mumbai/maharashtra-heavy-rainfall-red-orange-alert-15-districts-cm-fadnavis-advisory-as80</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis| मुख्यमंत्री देवेंद्र फडणवीस १९ रोजी पैठण तालुक्यात</t>
+          <t>महाराष्ट्रातील खासदारांनी राधाकृष्णन यांना समर्थन द्यावे: मुख्यमंत्री देवेंद्र फडणवीसांचे आवाहन; ठाकरे गट अ...</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/marathwada/chhatrapati-sambhajinagar/devendra-fadnavis-visit-paithan-taluka-19-august-ng81</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/c-p-radhakrishnan-vice-president-candidate-fadnavis-urges-support-135703533.html</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Maharashtra Heavy Rainfall | राज्यभरात अतिवृष्टीचा कहर; १५ जिल्ह्यांत रेड आणि ऑरेंज अलर्ट, नागरिकांनी घराबाहेर पडू नये: मुख्यमंत्री फडणवीस</t>
+          <t>पूरस्थितीचा सामना करण्यासाठी सरकारकडून सर्वतोपरी प्रयत्न, अतिवृष्टीचा धोका लक्षात घेऊन लोकांनी खबरदारी घ्यावी, मुख्यमंत्र्यांचं आवाहन</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/maharashtra-heavy-rainfall-red-orange-alert-15-districts-cm-fadnavis-advisory-as80</t>
+          <t>https://www.etvbharat.com/mr/!state/maharashtra-government-is-making-every-effort-to-deal-with-the-flood-situation-the-chief-minister-appeals-to-people-to-be-careful-considering-the-risk-of-heavy-rains-maharashtra-news-mhs25081804221</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>महाराष्ट्रातील खासदारांनी राधाकृष्णन यांना समर्थन द्यावे: मुख्यमंत्री देवेंद्र फडणवीसांचे आवाहन; ठाकरे गट अ...</t>
+          <t>Marathwada Rain : मराठवाड्यात शेतीचे सर्वाधिक नुकसान, 800 गावं जलबाधित; नांदेडमध्ये ढगफुटी, 5 जणांचा मृत्यू</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/c-p-radhakrishnan-vice-president-candidate-fadnavis-urges-support-135703533.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/cloudburst-rain-in-mukhed-nanded-district-five-people-missing-chief-minister-devendra-fadnavis-gave-information/913157/</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>पूरस्थितीचा सामना करण्यासाठी सरकारकडून सर्वतोपरी प्रयत्न, अतिवृष्टीचा धोका लक्षात घेऊन लोकांनी खबरदारी घ्यावी, मुख्यमंत्र्यांचं आवाहन</t>
+          <t>CM Relief Fund: रुग्णांसाठी सरकारचा 'हा' विभाग ठरतोय मदतशीर; अमरावती विभागात तब्बल १०.६१ कोटींची मदत</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/maharashtra-government-is-making-every-effort-to-deal-with-the-flood-situation-the-chief-minister-appeals-to-people-to-be-careful-considering-the-risk-of-heavy-rains-maharashtra-news-mhs25081804221</t>
+          <t>https://www.navarashtra.com/maharashtra/amravati/cm-devendra-fadnavis-cm-relief-fund-help-amravati-1187-patients-for-10-crore-rs-health-marathi-news-963412.html</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Marathwada Rain : मराठवाड्यात शेतीचे सर्वाधिक नुकसान, 800 गावं जलबाधित; नांदेडमध्ये ढगफुटी, 5 जणांचा मृत्यू</t>
+          <t>Nanded Breaking : मोठी बातमी! नांदेडमध्ये अनेक गाव पाण्याखाली, 15 जण अडकले तर 40 ते 50 म्हशीचा पाण्यात बुडून मृत्यू</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/cloudburst-rain-in-mukhed-nanded-district-five-people-missing-chief-minister-devendra-fadnavis-gave-information/913157/</t>
+          <t>https://www.lokshahi.com/news/rains-in-nandeds-mukhed-taluka-have-caused-flash-floods-in-many-villages-and-information-has-emerged-that-15-people-from-the-village-are-stranded</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>CM Relief Fund: रुग्णांसाठी सरकारचा 'हा' विभाग ठरतोय मदतशीर; अमरावती विभागात तब्बल १०.६१ कोटींची मदत</t>
+          <t>लातूर जिल्ह्यात मुसळधार पाऊस; लेंडी नदीला पूर आल्यानं तेलंगाणातील चार प्रवासी गेले वाहून; मुख्यमंत्र्यांनी घेतला आढावा</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/amravati/cm-devendra-fadnavis-cm-relief-fund-help-amravati-1187-patients-for-10-crore-rs-health-marathi-news-963412.html</t>
+          <t>https://www.etvbharat.com/mr/!state/heavy-rains-in-latur-district-cause-flooding-in-many-rivers-cm-devendra-fadnavis-took-a-review-lendi-river-flood-maharashtra-news-mhs25081802447</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Nanded Breaking : मोठी बातमी! नांदेडमध्ये अनेक गाव पाण्याखाली, 15 जण अडकले तर 40 ते 50 म्हशीचा पाण्यात बुडून मृत्यू</t>
+          <t>इतिहासाची अमूल्य खुण भारतात! इतिहासाशी पुन्हा जोडणारा क्षण, मुख्यमंत्री फडणवीसांची भावनिक प्रतिक्रिया</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>https://www.lokshahi.com/news/rains-in-nandeds-mukhed-taluka-have-caused-flash-floods-in-many-villages-and-information-has-emerged-that-15-people-from-the-village-are-stranded</t>
+          <t>https://www.esakal.com/maharashtra/chief-minister-devendra-fadnavis-statement-after-bringing-sword-of-raje-raghuji-bhosale-to-india-vru98</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Maharashtra Politics Live Updates : जगनमोहन रेड्डींच्या पक्षाचा सीपी राधाकृष्णन यांना जाहीर पाठिंबा</t>
+          <t>Rohit Pawar on Sanjay Shirsat : संजय शिरसाटांकडून 5 हजार कोटींचा भ्रष्टाचार, रोहित पवारांच्या आरोपाने</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-18-august-2025-latest-marathi-political-news-eknath-shinde-mumbai-mahayuti-rahul-gandhi-congress-india-aghadi-election-commission-devendra-fadnavis-uddhav-thackeray-india-alliance-mumbai-pune-ajit-pawar-ncp-local-elections-rahul-gandhi-vote-adhikar-yatra-nda-cp-radhakrishnan-vice-presidential-candidat</t>
+          <t>https://marathi.abplive.com/news/politics/rohit-pawar-accuses-sanjay-shirsat-of-5000-crores-of-corruption-big-demand-to-devendra-fadnavis-maharashtra-politics-marathi-news-1377888</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>CM Devendra Fadnavis: मुख्यमंत्र्यांनी राज्यातील पावसाचा घेतला आढावा; 'इतक्या' जिल्ह्यांना पावसाचा रेड अलर्ट, सतर्क राहण्याचे केले आवाहन</t>
+          <t>Maharashtra Politics Live Updates : जगनमोहन रेड्डींच्या पक्षाचा सीपी राधाकृष्णन यांना जाहीर पाठिंबा</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/cm-fadnavis-takes-reiew-situation-ndrf-and-army-deployed-16-districts-on-red-alert/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-18-august-2025-latest-marathi-political-news-eknath-shinde-mumbai-mahayuti-rahul-gandhi-congress-india-aghadi-election-commission-devendra-fadnavis-uddhav-thackeray-india-alliance-mumbai-pune-ajit-pawar-ncp-local-elections-rahul-gandhi-vote-adhikar-yatra-nda-cp-radhakrishnan-vice-presidential-candidat</t>
         </is>
       </c>
     </row>
@@ -2795,276 +2795,276 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Solapur News : शिंदेंच्या सेनेत राज्यातून ‘इन्कमिंग’ पण सोलापुरात गळती, तानाजी सावंतांच्या बंधूंचा भाजप प्रवेश ठरला</t>
+          <t>CM Devendra Fadnavis: मुख्यमंत्र्यांनी राज्यातील पावसाचा घेतला आढावा; 'इतक्या' जिल्ह्यांना पावसाचा रेड अलर्ट, सतर्क राहण्याचे केले आवाहन</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/tanaji-sawant-brother-shivajirao-sawant-resign-eknath-shinde-sena-join-bjp-after-meet-fadnavis/913179/</t>
+          <t>https://deshdoot.com/cm-fadnavis-takes-reiew-situation-ndrf-and-army-deployed-16-districts-on-red-alert/</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Shivaji Sawant : तानाजी सावंतांचे बंधू शिवाजी सावंतांचा भाजप प्रवेश निश्चित; मुख्यमंत्र्यांच्या भेटीनंतर जाहीर केला निर्णय</t>
+          <t>Solapur News : शिंदेंच्या सेनेत राज्यातून ‘इन्कमिंग’ पण सोलापुरात गळती, तानाजी सावंतांच्या बंधूंचा भाजप प्रवेश ठरला</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/shivaji-sawants-entry-into-bjp-confirmed-decision-announced-after-meeting-with-chief-minister-vd83</t>
+          <t>https://www.mymahanagar.com/maharashtra/tanaji-sawant-brother-shivajirao-sawant-resign-eknath-shinde-sena-join-bjp-after-meet-fadnavis/913179/</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>मोदींचा निर्णय, उमेदवार ठरला अन् अडचणीत उद्धवसेना; 18 वर्षांनी पुन्हा तेच, ठाकरेंसमोर पेच?</t>
+          <t>Shivaji Sawant : तानाजी सावंतांचे बंधू शिवाजी सावंतांचा भाजप प्रवेश निश्चित; मुख्यमंत्र्यांच्या भेटीनंतर जाहीर केला निर्णय</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-picks-cp-radhakrishnan-for-vice-president-post-cm-devendra-fadnavis-ask-uddhav-thackeray-for-support/articleshow/123362737.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/shivaji-sawants-entry-into-bjp-confirmed-decision-announced-after-meeting-with-chief-minister-vd83</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Maharashtra Rain Update : शाळांना सुट्टी आहे की नाही? नेमका निर्णय काय? फडणवीसांनीच संभ्रम संपवला;...</t>
+          <t>मोदींचा निर्णय, उमेदवार ठरला अन् अडचणीत उद्धवसेना; 18 वर्षांनी पुन्हा तेच, ठाकरेंसमोर पेच?</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/photo-gallery/maharashtra-rain-update-mumbai-rain-school-and-college-holiday-decision-will-be-taken-after-weather-forecast-1472649.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-picks-cp-radhakrishnan-for-vice-president-post-cm-devendra-fadnavis-ask-uddhav-thackeray-for-support/articleshow/123362737.cms</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Mukhed cloudburst: मुखेडमध्ये ढगफुटी! 800 गावांना फटका, 226 लोकांची सुटका, 4 गावातले लोक फसले, सैन्याला पाचारण</t>
+          <t>Maharashtra Rain Update : शाळांना सुट्टी आहे की नाही? नेमका निर्णय काय? फडणवीसांनीच संभ्रम संपवला;...</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/rain-big-news-mukhed-cloudburst-nanded-rain-news-calling-out-the-army-maharashtra-rain-alert-9107388</t>
+          <t>https://www.tv9marathi.com/photo-gallery/maharashtra-rain-update-mumbai-rain-school-and-college-holiday-decision-will-be-taken-after-weather-forecast-1472649.html</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>राजधानीत पावसाचा कहर! मुंबई विद्यापीठाचा परीक्षांबाबत तडकाफडकी मोठा निर्णय!</t>
+          <t>Mumbai Rains News: मुंबईसह महाराष्ट्रात 3 जिल्ह्यात शाळा-कॉलेज बंद, पावसाने सामान्यांचे झाले हाल; तलाव भरले</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/mumbai-university-postponed-its-all-exam-to-be-held-on-19-august-due-to-heavy-rain-marathi-news-1472932.html/amp</t>
+          <t>https://www.navarashtra.com/maharashtra/mumbai-rains-news-updates-school-college-closed-due-to-heavy-rains-thane-palghar-has-problem-963739.html</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>अन्वयार्थ : राजकीयीकरणाचा उत्सवी अधर्म</t>
+          <t>मराठ्यांच्या इतिहासाचं सोनेरी पान उलगडलं, मुख्यमंत्र्यांच्या हस्ते सरदार रघुजी राजे भोसले यांच्या ऐतिहासिक तलवारीचं लोकार्पण</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/sampadkiya/columns/dahi-handi-2025-political-grip-on-dahi-handi-festival-10-thar-human-pyramid-25-lakh-cash-prize-zws-70-5314039/</t>
+          <t>https://www.etvbharat.com/mr/!state/unveiling-the-historic-sword-of-sardar-raghuji-raje-bhosale-in-mumbai-presence-of-chief-minister-devendra-fadnavis-know-history-of-raghuji-raje-sword-maharashtra-news-mhs25081900619</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Mumbai Rains News: मुंबईसह महाराष्ट्रात 3 जिल्ह्यात शाळा-कॉलेज बंद, पावसाने सामान्यांचे झाले हाल; तलाव भरले</t>
+          <t>Rain Update : मराठवाड्यात मृत्यूचं तांडव, तुफान पावसाने सगळं उद्ध्वस्त; मदतीसाठी थेट मिलिटरी दाखल!</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/mumbai-rains-news-updates-school-college-closed-due-to-heavy-rains-thane-palghar-has-problem-963739.html</t>
+          <t>https://www.tv9marathi.com/maharashtra/maharashtra-rain-update-marathwada-all-district-affected-by-heavy-rain-total-6-people-died-marathi-news-1472571.html</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>लातूर जिल्ह्यात मुसळधार पाऊस; लेंडी नदीला पूर आल्यानं तेलंगाणातील चार प्रवासी गेले वाहून; मुख्यमंत्र्यांनी घेतला आढावा</t>
+          <t>Jalgaon mob lynching Case: जामनेर मॉब लिंचिंग: युवकाच्या हत्येत मंत्री गिरीश महाजनांच्या ड्रायव्हरचा मुलगा मास्टर माईंड?</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/heavy-rains-in-latur-district-cause-flooding-in-many-rivers-cm-devendra-fadnavis-took-a-review-lendi-river-flood-maharashtra-news-mhs25081802447</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/maharashtra-news-jalgaon-jamner-mob-lynching-girish-mahajan-driver-son-mastermind-youth-killed-mm76-sd67</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>मराठ्यांच्या इतिहासाचं सोनेरी पान उलगडलं, मुख्यमंत्र्यांच्या हस्ते सरदार रघुजी राजे भोसले यांच्या ऐतिहासिक तलवारीचं लोकार्पण</t>
+          <t>सी. पी. राधाकृष्णन यांना उपराष्ट्रपती पदाची उमेदवारी देण्यामागं भाजपाची काय आहेत राजकीय गणितं? जाणून घ्या, सविस्तर माहिती</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/unveiling-the-historic-sword-of-sardar-raghuji-raje-bhosale-in-mumbai-presence-of-chief-minister-devendra-fadnavis-know-history-of-raghuji-raje-sword-maharashtra-news-mhs25081900619</t>
+          <t>https://www.etvbharat.com/mr/!bharat/vice-president-of-india-election-2025-why-modi-of-tamil-nadu-cp-radhakrishnan-is-ndas-vice-presidential-pick-know-his-profile-from-tiruppur-roots-to-ndas-vice-presidential-candidate-maharashtra-news-mhs25081800641</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Rain Update : मराठवाड्यात मृत्यूचं तांडव, तुफान पावसाने सगळं उद्ध्वस्त; मदतीसाठी थेट मिलिटरी दाखल!</t>
+          <t>'उपराष्ट्रपती'साठी महाराष्ट्राच्या राज्यपालांचे नाव; फडणवीसांचे खासदारांना आवाहन, पवार-ठाकरेंना टोला</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/maharashtra-rain-update-marathwada-all-district-affected-by-heavy-rain-total-6-people-died-marathi-news-1472571.html</t>
+          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-urges-mps-to-support-radhakrishnan-targets-uddhav-thackeray-and-sharad-pawar-035137.html</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Jalgaon mob lynching Case: जामनेर मॉब लिंचिंग: युवकाच्या हत्येत मंत्री गिरीश महाजनांच्या ड्रायव्हरचा मुलगा मास्टर माईंड?</t>
+          <t>नांदेडमध्ये मुसळधार पावसाने हाहाकार,मुख्यमंत्री फडणवीस यांच्या देखरेखीखाली मदतकार्य तीव्र</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/maharashtra-news-jalgaon-jamner-mob-lynching-girish-mahajan-driver-son-mastermind-youth-killed-mm76-sd67</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/heavy-rains-wreak-havoc-in-nanded-relief-work-intensified-under-the-supervision-of-chief-minister-fadnavis-125081800046_1.html</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>'उपराष्ट्रपती'साठी महाराष्ट्राच्या राज्यपालांचे नाव; फडणवीसांचे खासदारांना आवाहन, पवार-ठाकरेंना टोला</t>
+          <t>युवकांसाठी मोठी खुशखबर; ‘या’ ठिकाणी आयटी पार्क उभारणार; मुख्यमंत्र्यांची घोषणा</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-urges-mps-to-support-radhakrishnan-targets-uddhav-thackeray-and-sharad-pawar-035137.html</t>
+          <t>https://www.nagpurtoday.in/great-news-for-youth-it-park-will-be-set-up-at-this-place-chief-ministers-announcement/08181712</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>नांदेडमध्ये मुसळधार पावसाने हाहाकार,मुख्यमंत्री फडणवीस यांच्या देखरेखीखाली मदतकार्य तीव्र</t>
+          <t>Eknath Shinde : एकनाथ शिंदेंना मोठा धक्का ! ‘या’ नेत्याने निवडणुकीच्या तोंडावर सोडली साथ</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/heavy-rains-wreak-havoc-in-nanded-relief-work-intensified-under-the-supervision-of-chief-minister-fadnavis-125081800046_1.html</t>
+          <t>https://www.dainikprabhat.com/big-blow-to-eknath-shinde-big-leader-of-shiv-sena-shinde-group-will-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>महाराष्ट्रात सर्वदूर पावसामुळे हाहाकार; मोठ्या प्रमाणात जीवित आणि वित्तहानी, बळीराज अडचणीत!</t>
+          <t>10 रुपयांत ‘शिवभोजन थाळी’ योजना थांबणार? शिवभोजन केंद्र चालकांची कोट्यवधींची बिलं थकली</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/marathi/maharashtra/rains-wreak-havoc-across-maharashtra-massive-loss-of-life-and-property-farmers-in-trouble-06-692619</t>
+          <t>https://mpbreakingnews.in/marathi/maharashtra/will-the-shiv-bhojan-thali-scheme-for-10-rupees-stop-shiv-bhojan-center-operators-are-facing-bills-worth-crores-02-692694</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>युवकांसाठी मोठी खुशखबर; ‘या’ ठिकाणी आयटी पार्क उभारणार; मुख्यमंत्र्यांची घोषणा</t>
+          <t>महाराष्ट्रात सर्वदूर पावसामुळे हाहाकार; मोठ्या प्रमाणात जीवित आणि वित्तहानी, बळीराज अडचणीत!</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/great-news-for-youth-it-park-will-be-set-up-at-this-place-chief-ministers-announcement/08181712</t>
+          <t>https://mpbreakingnews.in/marathi/maharashtra/rains-wreak-havoc-across-maharashtra-massive-loss-of-life-and-property-farmers-in-trouble-06-692619</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>10 रुपयांत ‘शिवभोजन थाळी’ योजना थांबणार? शिवभोजन केंद्र चालकांची कोट्यवधींची बिलं थकली</t>
+          <t>Schools shut, red alert as Mumbai braces for another day of heavy rain | Latest News India - Hindustan Times</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/marathi/maharashtra/will-the-shiv-bhojan-thali-scheme-for-10-rupees-stop-shiv-bhojan-center-operators-are-facing-bills-worth-crores-02-692694</t>
+          <t>https://www.hindustantimes.com/india-news/mumbai-rains-schools-shut-as-mumbai-under-imd-red-alert-braces-for-another-day-of-heavy-rain-10-updates-101755564432674.html</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>नागपूरच्या राजे रघुजी भोसलेंची तलवार लंडनमधून मुंबईत, इतिहासाशी नवीन पिढीला जोडण्याचं कामं, मुख्यमंत्र्यांकडून कौतुक</t>
+          <t>Rain fury leaves 7 dead in Maharashtra, 200 villagers stranded</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/marathi/maharashtra/nagpurs-raja-raghuji-bhosales-sword-arrives-in-mumbai-from-london-02-692697</t>
+          <t>https://www.ptinews.com/story/national/rain-fury-leaves-7-dead-in-maharashtra-200-villagers-stranded/2834213</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Shinde and BJP: The saga continues</t>
+          <t>Maharashtra on high alert as heavy rains batter state; CM, Dy CM lead rescue efforts</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/shinde-and-bjp-the-saga-continues/ar-AA1KHn3K</t>
+          <t>https://www.daijiworld.com/news/newsDisplay?newsID=1289634</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Heavy rainfall causes 7 deaths, crop loss in Maharashtra as alerts continue</t>
+          <t>Nanded rains latest UPDATES: Water from Karnataka reach district; Indian Army, SDRF deployed for rescue missions as villagers trapped</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/heavy-rainfall-causes-7-deaths-crop-loss-in-maharashtra-as-alerts-continue/ar-AA1KK6Zt</t>
+          <t>https://www.theweek.in/news/india/2025/08/18/mumbai-rain-news-nanded-rains-latest-updates-water-from-karnataka-reach-district-indian-army-sdrf-deployed-for-rescue-missions-and-villagers-trapped.html</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by Maharashtra CM Devendra Fadnavis</t>
+          <t>CM hands over keys to new police housing</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/cm-hands-over-keys-to-new-police-housing/articleshow/123350974.cms</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Nanded rains latest UPDATES: Water from Karnataka reach district; Indian Army, SDRF deployed for rescue missions as villagers trapped</t>
+          <t>Low-key launch of Raghuji Bhonsle’s sword in rain-lashed city</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/news/india/2025/08/18/mumbai-rain-news-nanded-rains-latest-updates-water-from-karnataka-reach-district-indian-army-sdrf-deployed-for-rescue-missions-and-villagers-trapped.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/lowkey-launch-of-raghuji-bhonsle-s-sword-in-rain-lashed-city-101755543235713.html</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Sword of Raghuji Bhonsle arrives in Mumbai and will be on display till Aug 25</t>
+          <t>CREDAI-MCHI appoints Sukhraj Nahar as 18th President</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/sword-of-raghuji-bhonsle-arrives-in-mumbai-and-will-be-on-display-till-aug-25/articleshow/123371745.cms</t>
+          <t>https://housing.com/news/credai-mchi-appoints-sukhraj-nahar-as-president/</t>
         </is>
       </c>
     </row>
@@ -3095,3480 +3095,3876 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>मुंबईतील सर्व शासकीय आणि निमशासकीय कार्यालयांना आज सुट्टी जाहीर!</t>
+          <t>Mumbai got 177mm rain in 6-8 hour period, says CM; more to come amid high tides</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/19/mumbai-rains-govt-declares-holiday-for-all-government-and-private-offices-amid-heavy-rainfall.html</t>
+          <t>https://www.newsdrum.in/national/mumbai-got-177mm-rain-in-6-8-hour-period-says-cm-more-to-come-amid-high-tides-9672488</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Thane Rain: ठाणे जिल्ह्यात झोडपणी; ठाणे, कल्याण, डोंबिवलीतील सखल भाग जलमय, आज शाळांना सुट्टी</t>
+          <t>Raghuji Bhosale Sword: रघुजी भोसलेंची ऐतिहासिक तलवार आज मुंबईत; मुख्यमंत्र्यांच्या हस्ते होणार लोकार्पण</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/thane/waterlogging-in-thane-kalyan-dombivali-schools-closed-today-19-august/articleshow/123374806.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/raghuji-bhosale-sword-to-arrive-in-mumbai-today-18-august-inauguration-ceremony-by-cm-devendra-fadnavis/articleshow/123353790.cms</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Mumbai Rain Alert:मुंबईत पावसाची धुवाँधार बॅटिंग;शाळांना सुट्टी जाहीर</t>
+          <t>मुंबईतील सर्व शासकीय आणि निमशासकीय कार्यालयांना आज सुट्टी जाहीर!</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>https://ilovenagar.com/mumbai-rain-alert-schools-declare-holiday-today/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/19/mumbai-rains-govt-declares-holiday-for-all-government-and-private-offices-amid-heavy-rainfall.html</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>SUPER 100 : राष्ट्रपति ट्रंप की जेलेंस्की और यूरोपीय नेताओं की साथ बैठक में अमेरिका, रूस और यूक्रेन के बीच त्रिपक्षीय वार्ता पर बनी सहमति...</t>
+          <t>Thane Rain: ठाणे जिल्ह्यात झोडपणी; ठाणे, कल्याण, डोंबिवलीतील सखल भाग जलमय, आज शाळांना सुट्टी</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/news-bulletin/super-100-in-the-meeting-of-president-trump-with-zelensky-and-european-leaders-an-agreement-was-reached-on-trilateral-talks-between-america-russia-2025-08-19-1156864</t>
+          <t>https://marathi.indiatimes.com/maharashtra/thane/waterlogging-in-thane-kalyan-dombivali-schools-closed-today-19-august/articleshow/123374806.cms</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>मुंबई में आज शाम हाई टाइड, लोगों से सावधानी की अपील, भारी बारिश का लोकल ट्रेनों</t>
+          <t>Mumbai Rain Alert:मुंबईत पावसाची धुवाँधार बॅटिंग;शाळांना सुट्टी जाहीर</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/photo-gallery/states/maharashtra-mumbai-heavy-rainfall-waterlogging-imd-red-alert-local-train-delayed-photos-maharashtra-news-2997487</t>
+          <t>https://ilovenagar.com/mumbai-rain-alert-schools-declare-holiday-today/</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>समाचार संध्या</t>
+          <t>Super 100: आज इंडिया गठबंधन कर सकता है उपराष्ट्रपति चुनाव के लिए उम्मीदवार का एलान.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/bulletins-detail/%E0%A4%B8%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%BE%E0%A4%B0-%E0%A4%B8%E0%A4%82%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%BE-508/</t>
+          <t>https://www.indiatv.in/video/news-bulletin/super-100-today-india-alliance-can-announce-its-candidate-for-vice-presidential-election-2025-08-18-1156635</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>नवीन पिढीला इतिहासाशी जोडण्याचे कार्य सुरू – मुख्यमंत्री देवेंद्र फडणवीस</t>
+          <t>मुंबई में आज शाम हाई टाइड, लोगों से सावधानी की अपील, भारी बारिश का लोकल ट्रेनों</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176229/</t>
+          <t>https://www.abplive.com/photo-gallery/states/maharashtra-mumbai-heavy-rainfall-waterlogging-imd-red-alert-local-train-delayed-photos-maharashtra-news-2997487</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Aaj Ki Baat: Mumbai में बारिश का Red Alert...48 घंटे संभलकर</t>
+          <t>समाचार संध्या</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/aaj-ki-baat/aaj-ki-baat-red-alert-for-rain-in-mumbai-be-careful-for-48-hours-2025-08-19-1156835</t>
+          <t>https://www.newsonair.gov.in/bulletins-detail/%E0%A4%B8%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%BE%E0%A4%B0-%E0%A4%B8%E0%A4%82%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%BE-508/</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>CM Devendra Fadnavis यांच्या हस्ते अद्ययावत पोलीस सदनिकेचे उद्घाटन</t>
+          <t>SUPER 100 : राष्ट्रपति ट्रंप की जेलेंस्की और यूरोपीय नेताओं की साथ बैठक में अमेरिका, रूस और यूक्रेन के बीच त्रिपक्षीय वार्ता पर बनी सहमति...</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/cm-devendra-fadnavis-inauguration-of-new-police-building-kolhapur-marathi-news/</t>
+          <t>https://www.indiatv.in/video/news-bulletin/super-100-in-the-meeting-of-president-trump-with-zelensky-and-european-leaders-an-agreement-was-reached-on-trilateral-talks-between-america-russia-2025-08-19-1156864</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>मुंबईत सर्व शासकीय-निमशासकीय कार्यालयांना सुट्टी जाहीर, फॉर्सबेरी जलाशयाजवळ चार तासात 109 मिमी पावसाची नोंद</t>
+          <t>Modi Aur Musalman: मुस्लिम वोट की 'SIR गर्मी' ठंडी ?</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/mumbai-rain-news-all-government-semi-government-offices-in-mumbai-remain-closed-today-mumbai-local-tracks-under-water-amid-imd-red-alert-for-extremely-heavy-rainfall-maharashtra-news-mhs25081901225</t>
+          <t>https://www.indiatv.in/video/news-bulletin/modi-aur-musalman-sir-2025-08-18-1156613</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Third Mumbai: महाराष्ट्राच्या विकासाचे नवे ग्रोथ सेंटर! काय म्हणाले CM फडणवीस?</t>
+          <t>नवीन पिढीला इतिहासाशी जोडण्याचे कार्य सुरू – मुख्यमंत्री देवेंद्र फडणवीस</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>https://www.tendernama.com/tender-news/third-mumbai-new-growth-center-for-maharashtras-development-what-did-cm-fadnavis-say</t>
+          <t>https://mahasamvad.in/176229/</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>इतिहासाची अमूल्य खुण भारतात! इतिहासाशी पुन्हा जोडणारा क्षण, मुख्यमंत्री फडणवीसांची भावनिक प्रतिक्रिया</t>
+          <t>CM Devendra Fadnavis यांच्या हस्ते अद्ययावत पोलीस सदनिकेचे उद्घाटन</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/chief-minister-devendra-fadnavis-statement-after-bringing-sword-of-raje-raghuji-bhosale-to-india-vru98</t>
+          <t>https://www.tarunbharat.com/cm-devendra-fadnavis-inauguration-of-new-police-building-kolhapur-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Maharashtra Breaking News LIVE : दिवसभरातील महत्त्वाच्या घडामोडी, ब्रेकिंग न्यूजचा आढावा एका क्लिकवर</t>
+          <t>Maharashtra Rain Live News: लातूरच्या अहमदपूरमधून जाणाऱ्या मन्याड नदीला पूर</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-august-18-political-news-in-marathi-933194</t>
+          <t>https://saamtv.esakal.com/maharashtra/maharashtra-marathi-latest-live-news-updates-18th-augest-2025-ajchya-tajya-batmya-maharashtra-rain-update-rahul-gandhi-election-commission-raj-uddhav-thackeray-news-politics-cm-devendra-fadnavis-mumbai-thane-nagpur-pune-nashik-weather-forecast-rain-update-rains-live-news-today-pune-local-crime-top-headlines</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Weather Updates : मुंबईत अचानक एवढा पाऊस का पडतोय? पुणे वेधशाळेच्या हवामान शास्त्रज्ञांनी</t>
+          <t>मुंबईत सर्व शासकीय-निमशासकीय कार्यालयांना सुट्टी जाहीर, फॉर्सबेरी जलाशयाजवळ चार तासात 109 मिमी पावसाची नोंद</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/pune-imd-on-heavy-rainfall-know-why-is-mumbai-suddenly-getting-so-much-rain-wather-update-imd-alert-for-mumbai-thane-for-next-48-hours-1377940</t>
+          <t>https://www.etvbharat.com/mr/!state/mumbai-rain-news-all-government-semi-government-offices-in-mumbai-remain-closed-today-mumbai-local-tracks-under-water-amid-imd-red-alert-for-extremely-heavy-rainfall-maharashtra-news-mhs25081901225</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>मुसळधार पावसामुळे मुंबईत जनजीवन विस्कळीत; उपमुख्यमंत्री पवार यांनी परिस्थितीचा घेतला आढावा</t>
+          <t>Maharashtra Breaking News LIVE : दिवसभरातील महत्त्वाच्या घडामोडी, ब्रेकिंग न्यूजचा आढावा एका क्लिकवर</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/mumbai-rains-updates-imd-red-alert-mumbai-city-suburbs-schools-and-colleges-remain-closed-today-mumbai-university-exams-postponed-to-23-august-maharashtra-rain-news-today-maharashtra-news-mhs25081900792</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-august-18-political-news-in-marathi-933194</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>School Student Stuck in Bus : बसमध्ये अडकलेल्या लहानग्यांना गुढघाभर पाण्यातून काढले बाहेर, पोलिसांच्या कृतीचे कौतुक, Video Viral</t>
+          <t>Mumbai Rains News: मुंबई ठाण्याला पुढील 48 तासांसाठी रेड अलर्ट, शाळांना सुट्टी जाहीर, मुख्यमंत्र्यांकडून</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/maharashtra-rain-news-update-mumbai-matunga-school-bus-stuck-children-rescued-by-police-video-viral-/40071</t>
+          <t>https://marathi.abplive.com/news/mumbai-rain-news-update-red-alert-for-mumbai-thane-for-next-48-hours-imd-forecast-holiday-declared-for-schools-cm-devendra-fadnavis-reviews-flood-hit-areas-1377881</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>उत्तराखंड विधानसभेत सादर होणार नवे अल्पसंख्यांक शिक्षण विधेयक</t>
+          <t>नेवासा येथे फर्निचर दुकानाला भीषण आग; दुकान मालकासह कुटुंबातील चौघांचा मृत्यू</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/new-minority-education-bill-to-be-introduced-in-uttarakhand-assembly.html</t>
+          <t>https://www.etvbharat.com/mr/!state/ahilyanagar-fire-news-massive-fire-breaks-out-at-furniture-shop-in-nevasa-several-dead-including-furniture-shop-owner-wife-two-his-kids-maharashtra-news-mhs25081800839</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>मराठवाड्यात आज आणि उद्याही पावसाचे धुमशान, विभागीय आयुक्तांचा नागरिकांबरोबरच प्रशासनालाही सतर्कतेचा इशारा</t>
+          <t>मुंबईत सकाळपासून मुसळधार पाऊस, दुपारच्या सर्व शाळांसह महाविद्यालयांना सुट्टी जाहीर</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>https://newstown.in/weather-alert-heavy-to-very-heavy-rain-predicted-on-18-1nd-19-august-2025-in-marathwada-region-by-imd-administration-on-alert/</t>
+          <t>https://www.etvbharat.com/mr/!state/mumbai-rains-updates-bmc-declared-holiday-today-for-afternoon-shift-for-all-schools-and-colleges-in-mumbai-amid-imd-red-alert-for-thane-raigad-navi-mumbai-maharashtra-news-mhs25081802005</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Mumbai gets 177mm rain in 6-8 hour period, says CM; all agencies asked to remain alert</t>
+          <t>Kolhapur Weather Update: कोल्हापूर जिल्ह्याला आज रेड अलर्ट मोसमात प्रथमच राधानगरी धरणाचे सर्व</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/mumbai-gets-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/amp_articleshow/123365291.cms</t>
+          <t>https://marathi.abplive.com/news/kolhapur/kolhapur-weather-red-alert-for-kolhapur-district-today-all-automatic-gates-of-radhanagari-dam-opened-for-the-first-time-in-the-season-1377818</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Upcoming ‘Third Mumbai’ will spur economic growth, says Maharashtra chief minister</t>
+          <t>School Student Stuck in Bus : बसमध्ये अडकलेल्या लहानग्यांना गुढघाभर पाण्यातून काढले बाहेर, पोलिसांच्या कृतीचे कौतुक, Video Viral</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/upcoming-third-mumbai-will-spur-economic-growth-says-maharashtra-chief-minister/articleshow/123368667.cms</t>
+          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/maharashtra-rain-news-update-mumbai-matunga-school-bus-stuck-children-rescued-by-police-video-viral-/40071</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>CM’s nod for new terminal bldg at Nashik airport received: Min</t>
+          <t>नागपूरच्या राजे रघुजी भोसलेंची तलवार लंडनमधून मुंबईत, इतिहासाशी नवीन पिढीला जोडण्याचं कामं, मुख्यमंत्र्यांकडून कौतुक</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/cms-nod-for-new-terminal-bldg-at-nashik-airport-received-min/articleshow/123372835.cms</t>
+          <t>https://mpbreakingnews.in/marathi/maharashtra/nagpurs-raja-raghuji-bhosales-sword-arrives-in-mumbai-from-london-02-692697</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Maharashtra rains: Five missing, several stranded as heavy rains lash Nanded, rescue operations underway</t>
+          <t>कोल्हापूर सर्किट बेंच झाले, आता खंडपीठाचा प्रस्ताव द्या; सरन्यायाधीश भूषण गवईंची सूचना</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/maharashtra/maharashtra-rains-five-missing-several-stranded-as-heavy-rains-lash-nanded-rescue-operations-underway-2025-08-18-1004046</t>
+          <t>https://ratnagirikhabardar.com/news/74340/</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Heavy rains lash Mumbai; red alert issued, Vihar Lake overflows, CM urges caution</t>
+          <t>Mumbai gets 177mm rain in 6-8 hour period, says CM; all agencies asked to remain alert</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/cities/mumbai/mumbai-rain-updates-august-18-2025/article69946286.ece</t>
+          <t>https://m.economictimes.com/news/india/mumbai-gets-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/amp_articleshow/123365291.cms</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Mumbai rains HIGHLIGHTS: Civic body declares holiday for all schools on August 19</t>
+          <t>Upcoming ‘Third Mumbai’ will spur economic growth, says Maharashtra chief minister</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/live-news-updates-mumbai-rain-waterlogging-traffic-heavy-rain-orange-alert-125081800291_1.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/upcoming-third-mumbai-will-spur-economic-growth-says-maharashtra-chief-minister/articleshow/123368667.cms</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Maha CM asks agencies to be on alert mode after heavy rainfall and flash floods</t>
+          <t>CM’s nod for new terminal bldg at Nashik airport received: Min</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/maha-cm-asks-agencies-to-be-on-alert-mode-after-heavy-rainfall-and-flash-floods/</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/cms-nod-for-new-terminal-bldg-at-nashik-airport-received-min/articleshow/123372835.cms</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>देवेंद्र फडणवीस यांच्यासोबतच्या कोल्ड वॉरच्या चर्चेवर एकनाथ शिंदे यांची प्रतिक्रिया, स्पष्टच म्हणाले....</t>
+          <t>Maharashtra rains: Five missing, several stranded as heavy rains lash Nanded, rescue operations underway</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/national/%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%AC%E0%A4%A4%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%A1-%E0%A4%B5-%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A%E0%A5%87%E0%A4%B5%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A4%9A-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1zqXD8?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.indiatvnews.com/maharashtra/maharashtra-rains-five-missing-several-stranded-as-heavy-rains-lash-nanded-rescue-operations-underway-2025-08-18-1004046</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Devendra Fadnvis | मुख्यमंत्री देवेंद्र फडणवीस १९ रोजी पैठण तालुक्यात</t>
+          <t>Heavy rains lash Mumbai; red alert issued, Vihar Lake overflows, CM urges caution</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/devendra-fadnvis-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A5%A7%E0%A5%AF-%E0%A4%B0-%E0%A4%9C-%E0%A4%AA%E0%A5%88%E0%A4%A0%E0%A4%A3-%E0%A4%A4-%E0%A4%B2%E0%A5%81%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%A4/ar-AA1KKgDI</t>
+          <t>https://www.thehindu.com/news/cities/mumbai/mumbai-rain-updates-august-18-2025/article69946286.ece</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis | डॉ. आंबेडकर महाविद्यालयाने समाज परिवर्तनाचे केंद्र बनावे : मुख्यमंत्री देवेंद्र फडणवीस</t>
+          <t>Mumbai rains HIGHLIGHTS: Civic body declares holiday for all schools on August 19</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-%E0%A4%A1-%E0%A4%86%E0%A4%82%E0%A4%AC%E0%A5%87%E0%A4%A1%E0%A4%95%E0%A4%B0-%E0%A4%AE%E0%A4%B9-%E0%A4%B5-%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%B2%E0%A4%AF-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%AA%E0%A4%B0-%E0%A4%B5%E0%A4%B0%E0%A5%8D%E0%A4%A4%E0%A4%A8-%E0%A4%9A%E0%A5%87-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AC%E0%A4%A8-%E0%A4%B5%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8/ar-AA1JMyQJ</t>
+          <t>https://www.business-standard.com/india-news/live-news-updates-mumbai-rain-waterlogging-traffic-heavy-rain-orange-alert-125081800291_1.html</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>महाराष्ट्रात महाभयानक पाऊस! मुख्यमंत्री देवेंद्र फडणवीस यांनी तातडीने साधला शेजारील राज्यांशी संपर्क? कारण अतिशय चिंताजनक</t>
+          <t>NCP (SP) targets Maha minister over Rs 5,000 cr scam in Navi Mumbai’s CIDCO land; demands his resignation</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%AE%E0%A4%B9-%E0%A4%AD%E0%A4%AF-%E0%A4%A8%E0%A4%95-%E0%A4%AA-%E0%A4%8A%E0%A4%B8-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A4-%E0%A4%A4%E0%A4%A1-%E0%A4%A8%E0%A5%87-%E0%A4%B8-%E0%A4%A7%E0%A4%B2-%E0%A4%B6%E0%A5%87%E0%A4%9C-%E0%A4%B0-%E0%A4%B2-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B6-%E0%A4%B8%E0%A4%82%E0%A4%AA%E0%A4%B0%E0%A5%8D%E0%A4%95-%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%85%E0%A4%A4-%E0%A4%B6%E0%A4%AF-%E0%A4%9A-%E0%A4%82%E0%A4%A4-%E0%A4%9C%E0%A4%A8%E0%A4%95/ar-AA1KJav3</t>
+          <t>https://www.socialnews.xyz/2025/08/18/ncp-sp-targets-maha-minister-over-rs-5000-cr-scam-in-navi-mumbais-cidco-land-demands-his-resignation/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=ncp-sp-targets-maha-minister-over-rs-5000-cr-scam-in-navi-mumbais-cidco-land-demands-his-resignation</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>मुंबईतील पावसाचा मुख्यमंत्र्यांकडून सातत्याने आढावा</t>
+          <t>Maha CM asks agencies to be on alert mode after heavy rainfall and flash floods</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/19/the-chief-minister-is-continuously-reviewing-the-rainfall-in-mumbai.html</t>
+          <t>https://www.socialnews.xyz/2025/08/18/maha-cm-asks-agencies-to-be-on-alert-mode-after-heavy-rainfall-and-flash-floods/</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>BJP ने शिंदे गुट में लगाई सेंध! कट्टर शिवसैनिक छोड़ेंगे पार्टी, निकाय चुनाव से पहले दिया बड़ा झटका</t>
+          <t>देवेंद्र फडणवीस यांच्यासोबतच्या कोल्ड वॉरच्या चर्चेवर एकनाथ शिंदे यांची प्रतिक्रिया, स्पष्टच म्हणाले....</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/maharashtra-politics-bjp-gives-setback-to-eknath-shinde-shiv-sena-before-civic-polls-19873589</t>
+          <t>https://www.msn.com/mr-in/news/national/%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%AC%E0%A4%A4%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%A1-%E0%A4%B5-%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A%E0%A5%87%E0%A4%B5%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A4%9A-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1zqXD8?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में मानसून का कहर: मुखेड तालुका में बादल फटने जैसी घटना, 200 से ज्यादा गांवों में बाढ़</t>
+          <t>Devendra Fadnavis | डॉ. आंबेडकर महाविद्यालयाने समाज परिवर्तनाचे केंद्र बनावे : मुख्यमंत्री देवेंद्र फडणवीस</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>https://hindi.dynamitenews.com/maharashtra/cloudburst-in-mukhed-taluka-in-maharashtra-flood-in-more-than-200-villages</t>
+          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-%E0%A4%A1-%E0%A4%86%E0%A4%82%E0%A4%AC%E0%A5%87%E0%A4%A1%E0%A4%95%E0%A4%B0-%E0%A4%AE%E0%A4%B9-%E0%A4%B5-%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%B2%E0%A4%AF-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%AA%E0%A4%B0-%E0%A4%B5%E0%A4%B0%E0%A5%8D%E0%A4%A4%E0%A4%A8-%E0%A4%9A%E0%A5%87-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AC%E0%A4%A8-%E0%A4%B5%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8/ar-AA1JMyQJ</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>CM फडणवीस ने खेला 'मराठी अस्मिता' का दांव, उपराष्ट्रपति चुनाव में उद्धव-पवार पर बना दबाव</t>
+          <t>मुंबईतील पावसाचा मुख्यमंत्र्यांकडून सातत्याने आढावा</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/political-battle-over-nda-candidate-radhakrishnan-cm-fadnavis-seeks-support-from-uddhav-thackeray-and-sharad-pawar-1321873.html/amp</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/19/the-chief-minister-is-continuously-reviewing-the-rainfall-in-mumbai.html</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Mumbai News: चव्हाण ने कहा - श्रमिकों की एक साल में दो बार होगी वेतन वृद्धि</t>
+          <t>BJP ने शिंदे गुट में लगाई सेंध! कट्टर शिवसैनिक छोड़ेंगे पार्टी, निकाय चुनाव से पहले दिया बड़ा झटका</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/city/mumbai/mumbai-news-chavan-said-workers-will-get-salary-hike-twice-in-a-year-1174137</t>
+          <t>https://www.patrika.com/mumbai-news/maharashtra-politics-bjp-gives-setback-to-eknath-shinde-shiv-sena-before-civic-polls-19873589</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>नांदेड़ में भारी बारिश के कारण पांच लोग लापता, कई व्यक्ति फंसे : मुख्यमंत्री फडणवीस</t>
+          <t>महाराष्ट्र में मानसून का कहर: मुखेड तालुका में बादल फटने जैसी घटना, 200 से ज्यादा गांवों में बाढ़</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/maharashtra/five-people-missing-several-stranded-due-to-heavy-rains-in-nanded-cm-fadnavis-3212983.html</t>
+          <t>https://hindi.dynamitenews.com/maharashtra/cloudburst-in-mukhed-taluka-in-maharashtra-flood-in-more-than-200-villages</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Vidarbha Crop Loss: विदर्भात दोन लाख हेक्टरवर पीक नुकसान</t>
+          <t>CM फडणवीस ने खेला 'मराठी अस्मिता' का दांव, उपराष्ट्रपति चुनाव में उद्धव-पवार पर बना दबाव</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/crop-damage-on-two-lakh-hectares-in-vidarbha-rat16</t>
+          <t>https://navbharatlive.com/maharashtra/political-battle-over-nda-candidate-radhakrishnan-cm-fadnavis-seeks-support-from-uddhav-thackeray-and-sharad-pawar-1321873.html/amp</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>मुख्यमंत्री फडणवीस यांची माहिती, राज्यात अतिवृष्टी, ८०० गावे बाधित, मुंबईत १७० एमएम पाऊस</t>
+          <t>Mumbai News: चव्हाण ने कहा - श्रमिकों की एक साल में दो बार होगी वेतन वृद्धि</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/cm-fadnavis-said-heavy-rains-in-the-state-800-villages-affected-170-mm-rain/</t>
+          <t>https://www.bhaskarhindi.com/city/mumbai/mumbai-news-chavan-said-workers-will-get-salary-hike-twice-in-a-year-1174137</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Heavy Rainfall : रेड ॲलर्ट घोषित केलेल्या ठिकाणी सतर्कता बाळगण्याचे मुख्यमंत्री फडणवीसांचे निर्देश</t>
+          <t>नांदेड़ में भारी बारिश के कारण पांच लोग लापता, कई व्यक्ति फंसे : मुख्यमंत्री फडणवीस</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/heavy-rainfall-cm-devendra-fadnavis-instructs-to-remain-vigilant-in-places-where-red-alert-has-been-declared/</t>
+          <t>https://www.ibc24.in/maharashtra/five-people-missing-several-stranded-due-to-heavy-rains-in-nanded-cm-fadnavis-3212983.html</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>'My karyakarta is with me': Hitendra Thakur shrugs off defections ahead of civic elections</t>
+          <t>Vidarbha Crop Loss: विदर्भात दोन लाख हेक्टरवर पीक नुकसान</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/my-karyakarta-is-with-me-hitendra-thakur-shrugs-off-defections-ahead-of-civic-elections/ar-AA1KHNiH</t>
+          <t>https://agrowon.esakal.com/agro-special/crop-damage-on-two-lakh-hectares-in-vidarbha-rat16</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>NDA’s VP nominee CP Radhakrishnan meets PM Modi in Delhi</t>
+          <t>मुख्यमंत्री फडणवीस यांची माहिती, राज्यात अतिवृष्टी, ८०० गावे बाधित, मुंबईत १७० एमएम पाऊस</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>https://www.news9live.com/india/ndas-vp-nominee-cp-radhakrishnan-meets-pm-modi-in-delhi-2883321</t>
+          <t>https://www.marathiebatmya.com/political/cm-fadnavis-said-heavy-rains-in-the-state-800-villages-affected-170-mm-rain/</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>'Destroying constitutional institutions': Nishikant Dubey slams Rahul Gandhi as SC dismisses plea challenging 2024 Maharashtra polls</t>
+          <t>Congress Should Check Voter Lists Now, quips Chandrashekhar Bawankule</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>https://www.malaysiasun.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/congress-should-check-voter-lists-now-quips-chandrashekhar-bawankule/articleshow/123351307.cms</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>BJP man accuses Trinamool leaders of supporting Rohingyas, threatens to bulldoze them into Bangladesh</t>
+          <t>After Shankar Dayal Sharma, Another Maharashtra Governor Eyes V-P Post As BJP Picks Radhakrishnan</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/bjp-man-accuses-trinamool-leaders-of-supporting-rohingyas-threatens-to-bulldoze-them-into-bangladesh/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=bjp-man-accuses-trinamool-leaders-of-supporting-rohingyas-threatens-to-bulldoze-them-into-bangladesh</t>
+          <t>https://www.news18.com/india/after-shankar-dayal-sharma-another-maharashtra-governor-eyes-v-p-post-as-bjp-picks-radhakrishnan-ws-kl-9511316.html</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Shivaji Sawant : शिवाजी सावंतांचा भाजपा प्रवेश निश्चित !</t>
+          <t>Shiv Sena, NCP Support Maha Governor’s Nomination For Vice President</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/shivaji-sawants-admission-to-bjp-is-certain-281398/amp/</t>
+          <t>https://ommcomnews.com/india-news/shiv-sena-ncp-support-maha-governors-nomination-for-vice-president/</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Eknath Shinde : एकनाथ शिंदेंना मोठा धक्का ! ‘या’ नेत्याने निवडणुकीच्या तोंडावर सोडली साथ</t>
+          <t>NDA's Vice President nominee CP Radhakrishnan to reach Delhi today: sources</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/big-blow-to-eknath-shinde-big-leader-of-shiv-sena-shinde-group-will-join-bjp/</t>
+          <t>https://www.aninews.in/news/national/general-news/ndas-vice-president-nominee-cp-radhakrishnan-to-reach-delhi-today-sources20250818101908</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>राष्ट्रवादीचे प्रशांत यादव यांचा आज भाजप प्रवेश</t>
+          <t>NCP must get Nashik guardian minister post: Bhujbal</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kokan/ratnagiri/ncp-prashant-yadav-joins-bjp-today-dc95</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/ncp-must-get-nashik-guardian-minister-post-bhujbal-101755457413078.html</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Ashish Shelar: मुंबईत जोरदार पाऊस! पावसाचा आढावा घेतल्यानंतर मंत्री शेलार म्हणाले, 'अत्यंत गरज असल्यास...'</t>
+          <t>DH Evening Brief | NDA VP pick in Delhi to meet BJP top brass, Opposition yet to finalise their candidate; I.N.D.I.A. bloc continues attacking EC chief over SIR</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/mumbai-rain-updates-ashish-shelar-reviewed-the-rainfall-and-said-stay-safe-at-home/40069</t>
+          <t>https://www.deccanherald.com/india/dh-evening-brief-nda-vp-pick-in-delhi-to-meet-bjp-top-brass-opposition-yet-to-finalise-their-candidate-india-bloc-continues-attacking-ec-chief-over-sir-3685866</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Mumbai Rain Alert : मुंबईकरांनो सावध रहा.. पुढील 4 तास धोक्याचे… रेड अलर्ट अन् हवामान खात्याचा...</t>
+          <t>Rajnath reaches out to DMK, TMC, BJD for consensus on VP nominee</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/mumbai-weather-forecast-imd-red-alert-for-mumbai-for-next-4-hours-extremely-important-for-mumbaikars-1473139.html/amp</t>
+          <t>https://timesofindia.indiatimes.com/india/rajnath-reaches-out-to-dmk-tmc-bjd-for-consensus-on-vp-nominee/articleshow/123373035.cms</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>भाजपला स्थानिक ची निवडणूक महायुती म्हणूनच का लढवायची आहे?</t>
+          <t>Breaking News Highlights Updates: Ukrainian President Zelenskyy hails 'historic' US decision to offer sec...</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>https://aaplaawajnews.com/2025/34070/</t>
+          <t>https://m.economictimes.com/news/newsblogs/india-news-live-updates-17-august-2025-earthquake-sikkim-rain-weather-mumbai-delhi-pm-modi-trump-putin-russia-israel-gaza-ukraine/liveblog/123340718.cms</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Congress Mohan Joshi Pune | Don't wait for BJP's 'event', open the flyover</t>
+          <t>NDA’s VP nominee CP Radhakrishnan meets PM Modi in Delhi</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>https://policenama.com/congress-mohan-joshi-pune-dont-wait-for-bjps-event-open-the-flyover-former-mla-mohan-joshis-letter-to-the-municipal-commissioner/</t>
+          <t>https://www.news9live.com/india/ndas-vp-nominee-cp-radhakrishnan-meets-pm-modi-in-delhi-2883321</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>राज्यात ‘ओला दुष्काळ’ जाहीर करा, एकरी ५० हजार रुपयांची मदत द्या -शशिकांत शिंदे</t>
+          <t>Devendra Fadnavis asks agencies to be on alert mode after heavy rainfall and flash floods</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>https://politicalmaharashtra.in/declare-wet-drought-in-the-state-provide-assistance-of-rs-50000-per-acre-shashikant-shinde-97623/</t>
+          <t>https://www.5dariyanews.com/news/464951-Devendra-Fadnavis-asks-agencies-to-be-on-alert-mode-after-heavy-rainfall-and-flash-floods</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>‘गँग्स ऑफ गद्दार’: शिंदेचा मंत्री ‘रोहित पवारांच्या’ निशाण्यावर</t>
+          <t>BJP names CP Radhakrishnan as NDA Vice President candidate, replacing Jagdeep Dhankhar</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>https://politicalmaharashtra.in/gangs-of-traitors-shindes-minister-targeted-by-rohit-pawar-97619/</t>
+          <t>https://apnlive.com/politics/cp-radhakrishnan-nda-vice-president-candidate/</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>To collect outstanding transportation fines, the Maha government is planning an amnesty scheme</t>
+          <t>'Destroying constitutional institutions': Nishikant Dubey slams Rahul Gandhi as SC dismisses plea challenging 2024 Maharashtra polls</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>https://assamtribune.com/national/to-collect-outstanding-transportation-fines-the-mahagovernment-is-planning-an-amnesty-scheme-1588536</t>
+          <t>https://www.bignewsnetwork.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Muqabla: 'वोट चोरी' पर जीत किसकी...Rahul Gandhi या Election Commission?</t>
+          <t>'Destroying constitutional institutions': Nishikant Dubey slams Rahul Gandhi as SC dismisses plea challenging 2024 Maharashtra polls</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/news-bulletin/muqabla-rahul-gandhi-or-the-election-commission-who-wins-the-vote-theft-battle-2025-08-19-1156831</t>
+          <t>https://www.malaysiasun.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>'ऑपरेशन लोटस वगैरे काही नाही; लवकरच ऑपरेशन टायगर दिसेल', सोलापूरच्या राजकारणात पडद्यामागे काय घडतंय?</t>
+          <t>BJP man accuses Trinamool leaders of supporting Rohingyas, threatens to bulldoze them into Bangladesh</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/solapur/solapur-politics-over-shiv-sena-leader-shivaji-sawant-may-join-bjp/articleshow/123369493.cms</t>
+          <t>https://www.socialnews.xyz/2025/08/18/bjp-man-accuses-trinamool-leaders-of-supporting-rohingyas-threatens-to-bulldoze-them-into-bangladesh/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=bjp-man-accuses-trinamool-leaders-of-supporting-rohingyas-threatens-to-bulldoze-them-into-bangladesh</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Nagpur Politics | भाईंनी घातला पक्ष प्रवेशाचा दुपट्टा,आता शिवसेनेचे घुमजाव</t>
+          <t>Shivaji Sawant : शिवाजी सावंतांचा भाजपा प्रवेश निश्चित !</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/nagpur-politics-%E0%A4%AD-%E0%A4%88%E0%A4%82%E0%A4%A8-%E0%A4%98-%E0%A4%A4%E0%A4%B2-%E0%A4%AA%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6-%E0%A4%9A-%E0%A4%A6%E0%A5%81%E0%A4%AA%E0%A4%9F%E0%A5%8D%E0%A4%9F-%E0%A4%86%E0%A4%A4-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%9A%E0%A5%87-%E0%A4%98%E0%A5%81%E0%A4%AE%E0%A4%9C-%E0%A4%B5/ar-AA1HHJp9</t>
+          <t>https://thefocusindia.com/maharashtra-news/shivaji-sawants-admission-to-bjp-is-certain-281398/amp/</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Coffee Par Kurukshetra: उपराष्ट्रपति के नाम पर INDI अलायंस टूट जाएगा?</t>
+          <t>राष्ट्रवादीचे प्रशांत यादव यांचा आज भाजप प्रवेश</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/kurukshetra/coffee-par-kurukshetra-indi-2025-08-19-1156832</t>
+          <t>https://pudhari.news/maharashtra/kokan/ratnagiri/ncp-prashant-yadav-joins-bjp-today-dc95</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Haqiqat Kya Hai: मुनीर के मरने की तारीख भी आने वाली है ?</t>
+          <t>Guardian Minister of Nashik : नाशिकच्या पालकमंत्रीपदाचा वाद पेटला!</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/hakikat-kya-hai/haqiqat-kya-hai-2025-08-19-1156836</t>
+          <t>https://pudhari.news/maharashtra/north-maharashtra/nashik/guardian-minister-of-nashik-controversy-over-the-post-of-guardian-minister-of-nashik-has-flared-up-ar84</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Yoga With Swami Ramdev :ज़्यादा स्क्रीन टाइम से बच्चों को दिल की बीमारी</t>
+          <t>Devendra Fadnavis Politics : देवेंद्र फडणवीसांचा 'मोठा गेम'; अजितदादा, एकनाथ शिंदे गाफील!</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/yoga/yoga-with-swami-ramdev-excessive-screen-time-can-cause-heart-disease-in-children-2025-08-19-1156871</t>
+          <t>https://sarkarnama.esakal.com/vishleshan/devendra-fadnavis-politics-ajit-pawar-eknath-shinde-unaware-bjp-incoming-rm89</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>मुंबई में 19 अगस्त को भी जारी रहेगा बारिश का कहर, मौसम विभाग ने दी बड़ी चेतावनी, जारी किया रेड अलर्ट</t>
+          <t>भाजपला स्थानिक ची निवडणूक महायुती म्हणूनच का लढवायची आहे?</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>https://hindi.asianetnews.com/national-news/mumbai-braces-for-more-heavy-rain-on-19-august-imd-issued-red-and-orange-alert/articleshow-9knobps</t>
+          <t>https://aaplaawajnews.com/2025/34070/</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में मौसम बरपा रहा कहर: नांदेड़ में फटा बादल, बारिश के चलते 15 से 16 जिलो में अलर्ट, CM फडणवीस ने फसलों से लेकर लोकल ट्रेनों के बारे में दिया ये बड़ा अपडेट | Devendra Fadnavis, Cloudburst, Nan</t>
+          <t>Congress Mohan Joshi Pune | Don't wait for BJP's 'event', open the flyover</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/politics/devendra-fadnavis-cloudburst-nanded-maharashtra-news-maharashtra-1174025</t>
+          <t>https://policenama.com/congress-mohan-joshi-pune-dont-wait-for-bjps-event-open-the-flyover-former-mla-mohan-joshis-letter-to-the-municipal-commissioner/</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Amravati Politics: अमरावती के दरियापुर में कांग्रेस को बड़ा झटका, सलीम घनीवाला भाजपा में शामिल</t>
+          <t>राज्यात ‘ओला दुष्काळ’ जाहीर करा, एकरी ५० हजार रुपयांची मदत द्या -शशिकांत शिंदे</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/amravati/major-blow-to-congress-in-dariyapur-of-amravati-salim-ghaniwala-joins-bjp-1321794.html/amp</t>
+          <t>https://politicalmaharashtra.in/declare-wet-drought-in-the-state-provide-assistance-of-rs-50000-per-acre-shashikant-shinde-97623/</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>शिवसेना शिंदे गुट को बड़ा झटका, बड़ा नेता छोड़ेगा एकनाथ शिंदे का साथ</t>
+          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/maharashtra/shivaji-sawant-bjp-solapur-eknath-shinde-54-804117</t>
+          <t>https://www.ptinews.com/detail/business/-Third-Mumbai--to-boost-metropolitan-region-development--Fadnavis/2834902</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Amravati News : अमरावतीच्या दर्यापुरात काँग्रेसला मोठा धक्का, सलीम घाणीवालांचा भाजपमध्ये प्रवेश</t>
+          <t>Cases from 6 districts to be heard | ‘A dream comes true after 40-45 years of struggle’: CJI inaugurates HC bench in Kolhapur</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/salim-ghaniwala-joins-bjp-big-blow-to-congress-in-daryapur-amravati-9106782</t>
+          <t>https://indianexpress.com/article/cities/pune/cases-dream-struggle-cji-inaugurates-hc-bench-kolhapur-10195928/</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis: चार लाख हेक्टर क्षेत्रावरील पिकांना फटका; मुख्यमंत्र्यांनी घेतला राज्यातील स्थितीचा आढावा</t>
+          <t>To collect outstanding transportation fines, the Maha government is planning an amnesty scheme</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/heavy-rains-damage-crops-on-4-lakh-hectares-cm-devendra-fadnaivs-reviews-situation-in-maharashtra/articleshow/123379831.cms</t>
+          <t>https://assamtribune.com/national/to-collect-outstanding-transportation-fines-the-mahagovernment-is-planning-an-amnesty-scheme-1588536</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>ABP Majha Top 10 Headlines : ABP माझा टॉप 10 हेडलाईन्स | 18 ऑगस्ट 2025 | सोमवार</t>
+          <t>NCP (SP) targets Maha minister over Rs 5,000 cr scam in Navi Mumbai’s CIDCO land; demands his resignation</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/abp-majha-top-10-headlines-18-august-2025-monday-latest-marathi-news-update-maharashtra-politics-marathi-news-1378004</t>
+          <t>https://www.socialnews.xyz/2025/08/18/ncp-sp-targets-maha-minister-over-rs-5000-cr-scam-in-navi-mumbais-cidco-land-demands-his-resignation/</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>मंत्री आशीष शेलार यांनी घेतला आपात्कालीन व्यवस्थापनाचा आढावा</t>
+          <t>Heavy rain: Dy CM asks Maha, district agencies to coordinate, prioritise rescue works</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>https://www.jpnnews.in/2025/08/Ashish-Shelar-reviews-emergency-management.html</t>
+          <t>https://www.socialnews.xyz/2025/08/18/heavy-rain-dy-cm-asks-maha-district-agencies-to-coordinate-prioritise-rescue-works/</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>राज्यात पावसाचा हाहाकार! मुख्यमंत्री फडणवीस अॅक्टीव्ह मोडवर, सतर्क राहण्याचे आवाहन</t>
+          <t>Ahead of Civic Polls, Hitendra Thakur Backs Loyalists: ‘My Karyakarta Is With Me, They Ensure Our Party Wins</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/maharashtra-rain-cm-fadnavis-reviews-situation-16-districts-on-red-alert/</t>
+          <t>https://www.lokmattimes.com/maharashtra/ahead-of-civic-polls-hitendra-thakur-backs-loyalists-my-karyakarta-is-with-me-they-ensure-our-party-wins-a475/</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>‘शिंदेंच्या सेनेला’ दे धक्का : या आमदार बंधूंनी सोडला पक्ष</t>
+          <t>Red alert issued as heavy rain batters Mumbai, schools and colleges closed due to waterlogging</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>https://politicalmaharashtra.in/a-blow-to-shindes-army-these-mla-brothers-left-the-party-97625/</t>
+          <t>https://www.socialnews.xyz/2025/08/18/red-alert-issued-as-heavy-rain-batters-mumbai-schools-and-colleges-closed-due-to-waterlogging/</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Seize assets of school directors in Shalarth ID scam: Bawankule</t>
+          <t>Muqabla: 'वोट चोरी' पर जीत किसकी...Rahul Gandhi या Election Commission?</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/seize-assets-of-school-directors-in-shalarth-id-scam-bawankule/articleshow/123371134.cms</t>
+          <t>https://www.indiatv.in/video/news-bulletin/muqabla-rahul-gandhi-or-the-election-commission-who-wins-the-vote-theft-battle-2025-08-19-1156831</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Nagpur Smart City projects near closure with 7 works still pending</t>
+          <t>सिरदर्द है कृषि मंत्रालय...अजित पवार के मंत्री दत्तात्रेय भरणे को नहीं पसंद आई नई जिम्मेदारी, जानें क्या कहा?</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>https://infra.economictimes.indiatimes.com/news/urban-infrastructure/nagpur-smart-city-projects-face-delay-7-projects-pending-completion/123360909</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-manik-rao-kokate-successor-minister-dattatray-bharane-called-agriculture-ministry-is-a-headache-know-all/articleshow/123357471.cms</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>NMC pushes ahead with land acquisition for 2 STPs amid reluctance from VNIT, PKV</t>
+          <t>Nagpur Politics | भाईंनी घातला पक्ष प्रवेशाचा दुपट्टा,आता शिवसेनेचे घुमजाव</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/nmc-pushes-ahead-with-land-acquisition-for-2-stps-amid-reluctance-from-vnit-pkv/articleshow/123372521.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/nagpur-politics-%E0%A4%AD-%E0%A4%88%E0%A4%82%E0%A4%A8-%E0%A4%98-%E0%A4%A4%E0%A4%B2-%E0%A4%AA%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6-%E0%A4%9A-%E0%A4%A6%E0%A5%81%E0%A4%AA%E0%A4%9F%E0%A5%8D%E0%A4%9F-%E0%A4%86%E0%A4%A4-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%9A%E0%A5%87-%E0%A4%98%E0%A5%81%E0%A4%AE%E0%A4%9C-%E0%A4%B5/ar-AA1HHJp9</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>MBBS admission quota in unaided colleges cut by 50%, students erupt</t>
+          <t>Haqiqat Kya Hai: मुनीर के मरने की तारीख भी आने वाली है ?</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/mbbs-admission-quota-in-unaided-colleges-cut-by-50-students-erupt/articleshow/123372541.cms</t>
+          <t>https://www.indiatv.in/video/hakikat-kya-hai/haqiqat-kya-hai-2025-08-19-1156836</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Historic sword of Raje Raghuji Bhonsle arrives in Mumbai to royal welcome</t>
+          <t>जनसंघ से लेकर राज्यपाल तक का सफर! अब CP राधाकृष्णन बने उपराष्ट्रपति के उम्मीदवार, कैसा रहा नेताओं का रिएक्शन?</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/historic-sword-of-raje-raghuji-bhonsle-arrives-in-mumbai-to-royal-welcome/08181446</t>
+          <t>https://hindi.oneindia.com/news/india/maharashtra-governor-cp-radhakrishnan-nda-vice-presidential-candidate-leaders-congratulate-1364687.html</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>३१ खासदार निवडून आले तेव्हा मतदारयाद्या बरोबर होत्या का ?</t>
+          <t>महाराष्ट्र में मौसम बरपा रहा कहर: नांदेड़ में फटा बादल, बारिश के चलते 15 से 16 जिलो में अलर्ट, CM फडणवीस ने फसलों से लेकर लोकल ट्रेनों के बारे में दिया ये बड़ा अपडेट | Devendra Fadnavis, Cloudburst, Nan</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/nagpur/were-the-voter-lists-correct-when-31-mps-were-elected-a-a1000/</t>
+          <t>https://www.bhaskarhindi.com/politics/devendra-fadnavis-cloudburst-nanded-maharashtra-news-maharashtra-1174025</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>रघुजी राजे यांची तलवार आणि ‘स्व’चा बोध</t>
+          <t>Amravati Politics: अमरावती के दरियापुर में कांग्रेस को बड़ा झटका, सलीम घनीवाला भाजपा में शामिल</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/historic-sword-of-shrimant-raghuji-bhosle-back-in-mumbai.html</t>
+          <t>https://navbharatlive.com/maharashtra/amravati/major-blow-to-congress-in-dariyapur-of-amravati-salim-ghaniwala-joins-bjp-1321794.html/amp</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Teacher Recruitment Scam: बोगस शालार्थ आयडी घोटाळ्यातील संचालकांची मालमत्ता जप्त होणार !</t>
+          <t>शिवसेना शिंदे गुट को बड़ा झटका, बड़ा नेता छोड़ेगा एकनाथ शिंदे का साथ</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/bogus-teacher-scam-school-id-fraud-directors-property-to-be-seized-ng81</t>
+          <t>https://mpbreakingnews.in/maharashtra/shivaji-sawant-bjp-solapur-eknath-shinde-54-804117</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Chandrashekhar Bawankule: 'आताच मतदार याद्या तपासा', महसूल मंत्र्यांचा काँग्रेस नेत्यांना टोला</t>
+          <t>नीतिमूल्य समितीला मुहूर्त मिळेना! आमदारांबाबत घोषणा करुन महिना उलटूनही बैठकच नाही</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/chandrashekhar-bawankule-demands-to-check-voter-lists-against-congress-allegations/articleshow/123356783.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/no-meeting-even-after-month-of-announcement-regarding-ethic-committee-mlas/articleshow/123356125.cms</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Nagpur Accident : नागपुरातील हिट अँड रन प्रकरणाचा AI तंत्रज्ञानाच्या मदतीने उलगडा राज्यातील</t>
+          <t>'ऑपरेशन लोटस वगैरे काही नाही; लवकरच ऑपरेशन टायगर दिसेल', सोलापूरच्या राजकारणात पडद्यामागे काय घडतंय?</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/crime/nagpur-hit-and-run-accident-news-update-case-solved-with-the-help-of-ai-technology-first-experiment-in-the-state-driver-arrested-from-uttar-pradesh-1377914</t>
+          <t>https://marathi.indiatimes.com/maharashtra/solapur/solapur-politics-over-shiv-sena-leader-shivaji-sawant-may-join-bjp/articleshow/123369493.cms</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Sambhajinagar News : आता शहरवासीयांना मिळणार अतिरिक्त २६ एमएलडी पाणी</t>
+          <t>Amravati News : अमरावतीच्या दर्यापुरात काँग्रेसला मोठा धक्का, सलीम घाणीवालांचा भाजपमध्ये प्रवेश</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>https://pudhari.news/amp/story/maharashtra/marathwada/chhatrapati-sambhajinagar/now-city-residents-will-get-additional-26-mld-of-water-np88</t>
+          <t>https://marathi.ndtv.com/politics/salim-ghaniwala-joins-bjp-big-blow-to-congress-in-daryapur-amravati-9106782</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>kolhapur | सर्किट बेंचचे स्वप्न साकारले; न्यायाचे दरवाजे खुले झाले!</t>
+          <t>Breaking News Maharashtra LIVE : संतोष देशमुख प्रकरण, सोमवारी सुनावणी</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>https://pudhari.news/amp/story/maharashtra/kolhapur/circuit-bench-dream-realized-doors-of-justice-now-open-ap84</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-maharashtra-politics-rain-flood-updates-election-commission-press-conference-thalak-batmya-sunday-17th-august-2025-1471433.html</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Nagpur News: नव्या नागपूरला मिळणार तिसऱ्या रिंग रोडची जोड; ३६ गावांतील सुमारे ८८० हेक्टर जमिनीचे अधिग्रहण</t>
+          <t>Devendra Fadnavis: चार लाख हेक्टर क्षेत्रावरील पिकांना फटका; मुख्यमंत्र्यांनी घेतला राज्यातील स्थितीचा आढावा</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/vidarbha/nagpur/nagpur-to-get-third-ring-road-with-land-acquisition-from-36-villages-vsb99</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/heavy-rains-damage-crops-on-4-lakh-hectares-cm-devendra-fadnaivs-reviews-situation-in-maharashtra/articleshow/123379831.cms</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>वरूणराजा कोपला! पिकांमध्ये पाणीच पाणी, पुढील 48 तासांत या जिल्ह्यांना पुन्हा रेड अलर्ट</t>
+          <t>मंत्री आशीष शेलार यांनी घेतला आपात्कालीन व्यवस्थापनाचा आढावा</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/agriculture/18-august-maharashtra-heavy-rain-update-monsoon-2025-mumbai-red-alert-1460576.html</t>
+          <t>https://www.jpnnews.in/2025/08/Ashish-Shelar-reviews-emergency-management.html</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>kolhapur | सर्किट बेंचचे स्वप्न साकारले; न्यायाचे दरवाजे खुले झाले!</t>
+          <t>TDR Scam: साडेसातशे कोटींच्या टीडीआर घोटाळ्याचा ‘आका’ कोण?</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/circuit-bench-dream-realized-doors-of-justice-now-open-ap84</t>
+          <t>https://pudhari.news/maharashtra/pune/750-crore-land-tdr-scam-ac90</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Vice Presidential Election: सीपी राधाकृष्णन को NDA उम्मीदवार बनाने पर कांग्रेस को लगी मिर्ची, INDI गठबंधन कैंडिडेट पर खोले पत्ते</t>
+          <t>‘शिंदेंच्या सेनेला’ दे धक्का : या आमदार बंधूंनी सोडला पक्ष</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>https://www.republicbharat.com/india/congress-angry-cp-radhakrishnan-nda-vice-presidential-candidate-opened-cards-on-indi-alliance-meeting</t>
+          <t>https://politicalmaharashtra.in/a-blow-to-shindes-army-these-mla-brothers-left-the-party-97625/</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>‘Extremely Unfortunate’: Rajnath Singh Raps Opposition for ‘Stalling’ Special Discussion in</t>
+          <t>Nagpur Smart City projects near closure with 7 works still pending</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/india/news/extremely-unfortunate-rajnath-singh-raps-opposition-for-stalling-special-discussion-in-parliament-on-astronaut-subhanshu-shuklas-space-mission-7064889.html</t>
+          <t>https://infra.economictimes.indiatimes.com/news/urban-infrastructure/nagpur-smart-city-projects-face-delay-7-projects-pending-completion/123360909</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>India News | 12-day Himachal Pradesh Assembly Session Opens; Opposition Seeks Adjournment on Disaster</t>
+          <t>Seize assets of school directors in Shalarth ID scam: Bawankule</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/india-news-12-day-himachal-pradesh-assembly-session-opens-opposition-seeks-adjournment-on-disaster-7064955.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/seize-assets-of-school-directors-in-shalarth-id-scam-bawankule/articleshow/123371134.cms</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Vice President Election: NDA उम्मीदवार सीपी राधाकृष्णन को मिल सकता है विपक्षी दलों का समर्थन, इन पार्टियों पर सबकी नजर</t>
+          <t>Raghuji Bhonsle’s Sword To Reach Mum Today, Mudhoji Raje To Attend Ceremony</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/politics/national-rajya-sabha-election-opposition-parties-may-support-nda-candidate-cp-radhakrishnan-24017212.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/raghuji-bhonsles-sword-to-reach-mum-today-mudhoji-raje-to-attend-ceremony/articleshow/123351204.cms</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>महाराष्ट्र की ‘अस्मिता’ की बात करने वाले उपराष्ट्रपति पद के लिए राधाकृष्णन का समर्थन करें : फडणवीस</t>
+          <t>Now, Bachchu Kadu claims offer to ‘delete thousands of names’ from voters’ list</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/support-radhakrishnan-for-the-post-of-vice-president-who-talks-about-maharashtras-identity-fadnavis/856729/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/now-bachchu-kadu-claims-offer-to-delete-thousands-of-names-from-voters-list/articleshow/123351305.cms</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>कौन लेगा CP राधाकृष्णन की जगह? BJP की एक खोज खत्म होते ही शुरू हुई दूसरी तलाश</t>
+          <t>Historic sword of Raje Raghuji Bhonsle arrives in Mumbai to royal welcome</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/maharashtra-new-governor-who-will-replace-cp-radhakrishnan-bjp-new-search-begins-1321951.html</t>
+          <t>https://www.nagpurtoday.in/historic-sword-of-raje-raghuji-bhonsle-arrives-in-mumbai-to-royal-welcome/08181446</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Farmers Loan Waiver: बावनकुळेंनंतर महायुती सरकारमधील 'या' मंत्र्याची कर्जमाफीबाबत मोठी अपडेट; म्हणाले,'CM फडणवीस लवकरच...'</t>
+          <t>NMC pushes ahead with land acquisition for 2 STPs amid reluctance from VNIT, PKV</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/sanjay-rathod-update-farmer-loan-waiver-devendra-fadnavis-dk88</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/nmc-pushes-ahead-with-land-acquisition-for-2-stps-amid-reluctance-from-vnit-pkv/articleshow/123372521.cms</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Election Commission Of India &amp; The “Politics Of Jugaad”</t>
+          <t>MBBS admission quota in unaided colleges cut by 50%, students erupt</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>https://madrascourier.com/opinion/election-commission-of-india-the-politics-of-jugaad/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/mbbs-admission-quota-in-unaided-colleges-cut-by-50-students-erupt/articleshow/123372541.cms</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Video | Bihar Elections | RJD Leader Tejaswi Yadav Takes On PM Modi Over Bihar Polls: "Stop Fooling..."</t>
+          <t>३१ खासदार निवडून आले तेव्हा मतदारयाद्या बरोबर होत्या का ?</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/video/bihar-elections-rjd-leader-tejaswi-yadav-takes-on-pm-modi-over-bihar-polls-stop-fooling-981918</t>
+          <t>https://www.lokmat.com/nagpur/were-the-voter-lists-correct-when-31-mps-were-elected-a-a1000/</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>CP Radhakrishnan vs who? Why DMK’s pushing INDIA bloc for a Tamil vs Tamil contest for India’s V-P</t>
+          <t>रघुजी राजे यांची तलवार आणि ‘स्व’चा बोध</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/cp-radhakrishnan-vs-who-why-dmks-pushing-india-bloc-for-a-tamil-vs-tamil-contest-for-indias-v-p/2723136/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/historic-sword-of-shrimant-raghuji-bhosle-back-in-mumbai.html</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>'Political opinions or...': Supreme Court quashes plea challenging validity of Maharashtra Assembly polls</t>
+          <t>Chandrashekhar Bawankule: 'आताच मतदार याद्या तपासा', महसूल मंत्र्यांचा काँग्रेस नेत्यांना टोला</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/political-opinions-or-supreme-court-quashes-plea-challenging-validity-of-maharashtra-assembly-polls-3686244</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/chandrashekhar-bawankule-demands-to-check-voter-lists-against-congress-allegations/articleshow/123356783.cms</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Shiv Sena, NCP support Maha Governor’s nomination for Vice President</t>
+          <t>Teacher Recruitment Scam: बोगस शालार्थ आयडी घोटाळ्यातील संचालकांची मालमत्ता जप्त होणार !</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>https://www.indianewsstream.com/shiv-sena-ncp-support-maha-governors-nomination-for-vice-president/</t>
+          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/bogus-teacher-scam-school-id-fraud-directors-property-to-be-seized-ng81</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>'Destroying constitutional institutions': Nishikant Dubey slams Rahul Gandhi as SC dismisses plea challenging 2024 Maharashtra polls</t>
+          <t>Nagpur Accident : नागपुरातील हिट अँड रन प्रकरणाचा AI तंत्रज्ञानाच्या मदतीने उलगडा राज्यातील</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/politics/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls20250819085747/</t>
+          <t>https://marathi.abplive.com/crime/nagpur-hit-and-run-accident-news-update-case-solved-with-the-help-of-ai-technology-first-experiment-in-the-state-driver-arrested-from-uttar-pradesh-1377914</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>PM Modi appeals for unanimous election of Radhakrishnan as vice president</t>
+          <t>शालार्थ घोटाळ्यातील संचालकांची मालमत्ता जप्त करा; पालकमंत्री चंद्रशेखर बावनकुळे यांचे निर्देश</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>https://english.varthabharati.in/india/pm-modi-appeals-for-unanimous-election-of-radhakrishnan-as-vice-president</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/seize-the-assets-of-directors-involved-in-the-school-id-scam.html</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Supreme Court dismisses plea alleging 75 lakh bogus votes in Maharashtra Assembly polls</t>
+          <t>Sambhajinagar News : आता शहरवासीयांना मिळणार अतिरिक्त २६ एमएलडी पाणी</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>https://organiser.org/2025/08/19/308844/bharat/supreme-court-dismisses-plea-alleging-75-lakh-bogus-votes-in-maharashtra-assembly-polls/</t>
+          <t>https://pudhari.news/amp/story/maharashtra/marathwada/chhatrapati-sambhajinagar/now-city-residents-will-get-additional-26-mld-of-water-np88</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Alcaraz wins the Cincinnati Open after Sinner retires in the first set because of illness</t>
+          <t>kolhapur | सर्किट बेंचचे स्वप्न साकारले; न्यायाचे दरवाजे खुले झाले!</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>https://english.varthabharati.in/sports/alcaraz-wins-the-cincinnati-open-after-sinner-retires-in-the-first-set-because-of-illness</t>
+          <t>https://pudhari.news/amp/story/maharashtra/kolhapur/circuit-bench-dream-realized-doors-of-justice-now-open-ap84</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>'संवैधानिक संस्थाओं को कर रहे हैं नष्ट...' भाजपा सांसद निशिकांत दुबे ने राहुल गांधी पर साधा निशाना</t>
+          <t>वरूणराजा कोपला! पिकांमध्ये पाणीच पाणी, पुढील 48 तासांत या जिल्ह्यांना पुन्हा रेड अलर्ट</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>https://www.timesnowhindi.com/india/constitutional-institutions-are-being-destroyed-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls-article-152485768</t>
+          <t>https://news18marathi.com/agriculture/18-august-maharashtra-heavy-rain-update-monsoon-2025-mumbai-red-alert-1460576.html</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>खरगे, स्टॉलिन, नवीन पटनायक... उपराष्ट्रपति चुनाव से पहले राजनाथ सिंह को बीजेपी ने दी खास जिम्मेदारी</t>
+          <t>kolhapur | सर्किट बेंचचे स्वप्न साकारले; न्यायाचे दरवाजे खुले झाले!</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/india/vice-president-election-defence-minister-rajnath-singh-reaches-out-to-dmk-tmc-bjd-for-consensus-for-cp-radhakrishnan/articleshow/123375990.cms</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/circuit-bench-dream-realized-doors-of-justice-now-open-ap84</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>शिवसेना एकनाथ शिंदे गुट को बड़ा झटका, शिवाजी सावंत भाजपा में होगें शामिल | Maharastra - Paliwalwani - Latest Hindi News</t>
+          <t>Vice Presidential Election: सीपी राधाकृष्णन को NDA उम्मीदवार बनाने पर कांग्रेस को लगी मिर्ची, INDI गठबंधन कैंडिडेट पर खोले पत्ते</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>https://paliwalwani.com/maharastra/shiv-sena-eknath-shinde-faction-is-a-big-shock-shivaji-sawant-will-be-involved-in-bjp</t>
+          <t>https://www.republicbharat.com/india/congress-angry-cp-radhakrishnan-nda-vice-presidential-candidate-opened-cards-on-indi-alliance-meeting</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>चुनाव आयोग की प्रेस कॉन्फ्रेंस में इन दो पत्रकारों के सवालों ने बोलती बंद कर दी, देखें वीडियो – No. 1 Indian Media News Portal</t>
+          <t>VIDEO: महाराष्ट्र में भारी बारिश के बीच एक्शन में डिप्टी CM अजित पवार, मंत्रालय के आपदा नियंत्रण</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>https://www.bhadas4media.com/eci-press-confrence-journalist-question/</t>
+          <t>https://hindi.latestly.com/india/maharashtra-deputy-cm-ajit-pawar-visits-mantralaya-disaster-control-room-to-review-heavy-rain-situation-2732241.html</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>उपराष्ट्रपतीपदाचे उमेदवार राधाकृष्णन यांना पाठिंबा द्या; देवेंद्र फडणवीस यांची शरद पवार आणि उद्धव ठाकरे यांना साद</t>
+          <t>India News | 12-day Himachal Pradesh Assembly Session Opens; Opposition Seeks Adjournment on Disaster</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/maharashtra/cp-radhakrishnan-vice-president-candidate-fadnavis-appeal-pawar-thackeray</t>
+          <t>https://www.latestly.com/agency-news/india-news-12-day-himachal-pradesh-assembly-session-opens-opposition-seeks-adjournment-on-disaster-7064955.html</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>राहुल गांधी पक्ष टिकवण्यासाठी निवडणूक आयोगाचा आधार घेतात; मंत्री चंद्रशेखर बावनकुळे यांची टीका</t>
+          <t>Vice President Election: NDA उम्मीदवार सीपी राधाकृष्णन को मिल सकता है विपक्षी दलों का समर्थन, इन पार्टियों पर सबकी नजर</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/rahul-gandhi-takes-support-from-election-commission-to-save-party-minister-chandrashekhar-bawankule-criticizes.html</t>
+          <t>https://www.jagran.com/politics/national-rajya-sabha-election-opposition-parties-may-support-nda-candidate-cp-radhakrishnan-24017212.html</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>‘मत चोरी’चा वाद वाढला, विरोधक मुख्य निवडणूक आयुक्तांविरोधात महाभियोग प्रस्ताव आणण्याच्या तयारीत - Marathi News | The controversy over 'vote theft' escalates, the opposition is preparing to bring an impeachment motio</t>
+          <t>Coffee Par Kurukshetra: उपराष्ट्रपति के नाम पर INDI अलायंस टूट जाएगा?</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/shorts/national/vote-theft-row-escalates-opposition-mulls-impeachment-of-election-commissioner/</t>
+          <t>https://www.indiatv.in/video/kurukshetra/coffee-par-kurukshetra-indi-2025-08-19-1156832</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Pravin Darekar: राज्य सहकारी संघाच्या अध्यक्षपदी आमदार प्रवीण दरेकर</t>
+          <t>महाराष्ट्र की ‘अस्मिता’ की बात करने वाले उपराष्ट्रपति पद के लिए राधाकृष्णन का समर्थन करें : फडणवीस</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/pravin-darekar-elected-cooperative-president-maharashtra-ac90</t>
+          <t>https://hindi.theprint.in/india/support-radhakrishnan-for-the-post-of-vice-president-who-talks-about-maharashtras-identity-fadnavis/856729/</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>१९८७च्या काश्मीर निवडणूक गैरप्रकाराचा काँग्रेसला विसर - राजीव गांधींकडून विरोधकांच्या आरोपांकडे दुर्लक्ष</t>
+          <t>Aaj Ki Baat: Mumbai में बारिश का Red Alert...48 घंटे संभलकर</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/congress-forgets-1987-kashmir-election-malpractices-rajiv-gandhi-ignores-opposition-allegations.html</t>
+          <t>https://www.indiatv.in/video/aaj-ki-baat/aaj-ki-baat-red-alert-for-rain-in-mumbai-be-careful-for-48-hours-2025-08-19-1156835</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>हवामानाचा अंदाज: आजही पावसाचा कहर? मुंबई, पुण्यासह 7 जिल्ह्यांना रेड अलर्ट; गडचिरोलीसह 4 जिल्ह्यांना यलो अलर्ट</t>
+          <t>Aaj Ka Rashifal, 19 Aug, 2025 : आचार्य इंदु प्रकाश जी से जानिए आज क्या कह रहे हैं आपके सितारे</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/national-news/maharashtra-weather-red-alert-mumbai-pune-7-districts-281414/</t>
+          <t>https://www.indiatv.in/video/bhavishyawani/aaj-ka-rashifal-19-aug-2025-know-from-acharya-indu-prakash-ji-what-your-stars-are-saying-today-2025-08-19-1156865</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Maharashtra News: Dy CM Eknath Shinde Launches ‘Ladki Sun – Surakshit Sun’ Campaign To Protect Women</t>
+          <t>कौन लेगा CP राधाकृष्णन की जगह? BJP की एक खोज खत्म होते ही शुरू हुई दूसरी तलाश</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-dy-cm-eknath-shinde-launches-ladki-sun-surakshit-sun-campaign-to-protect-women-victims</t>
+          <t>https://navbharatlive.com/maharashtra/maharashtra-new-governor-who-will-replace-cp-radhakrishnan-bjp-new-search-begins-1321951.html</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Fadnavis meets Guv Radhakrishnan, presents him book of Shivaji Maharaj's letters</t>
+          <t>Farmers Loan Waiver: बावनकुळेंनंतर महायुती सरकारमधील 'या' मंत्र्याची कर्जमाफीबाबत मोठी अपडेट; म्हणाले,'CM फडणवीस लवकरच...'</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/national/Fadnavis-meets-Guv-Radhakrishnan--presents-him-book-of-Shivaji-Maharaj-s-letters/2832581</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/sanjay-rathod-update-farmer-loan-waiver-devendra-fadnavis-dk88</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>'Slap, but don't make video': Raj Thackeray's blunt advice to MNS workers after Marathi 'slapgate' case</t>
+          <t>Election Commission Of India &amp; The “Politics Of Jugaad”</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/slap-but-dont-make-video-raj-thackerays-blunt-advice-to-mns-workers-after-marathi-slapgate-case/ar-AA1I11OF</t>
+          <t>https://madrascourier.com/opinion/election-commission-of-india-the-politics-of-jugaad/</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Mumbai: Iconic Sword of Raghuji Bhonsle Arrives from London; Bike Rally Cancelled Due to Rains, Grand...</t>
+          <t>'Destroying constitutional institutions': Nishikant Dubey slams Rahul Gandhi as SC dismisses plea challenging 2024 Maharashtra polls</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/mumbai/mumbai-iconic-sword-of-raghuji-bhonsle-arrives-from-london-bike-rally-cancelled-due-to-rains-grand-inauguration-tonight-a525/</t>
+          <t>https://www.aninews.in/news/national/politics/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls20250819085747/</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>How CP Radhakrishnan Broke The Taboo Around Modi And Changed The Narrative After 2002 Gujarat Episode - The</t>
+          <t>CP Radhakrishnan vs who? Why DMK’s pushing INDIA bloc for a Tamil vs Tamil contest for India’s V-P</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>https://thecommunemag.com/how-cpr-broke-the-taboo-around-modi/</t>
+          <t>https://theprint.in/india/cp-radhakrishnan-vs-who-why-dmks-pushing-india-bloc-for-a-tamil-vs-tamil-contest-for-indias-v-p/2723136/</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>राजधानीत पावसाचा कहर! मुंबई विद्यापीठाचा परीक्षांबाबत तडकाफडकी मोठा निर्णय!</t>
+          <t>'Political opinions or...': Supreme Court quashes plea challenging validity of Maharashtra Assembly polls</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/mumbai-university-postponed-its-all-exam-to-be-held-on-19-august-due-to-heavy-rain-marathi-news-1472932.html</t>
+          <t>https://www.deccanherald.com/india/political-opinions-or-supreme-court-quashes-plea-challenging-validity-of-maharashtra-assembly-polls-3686244</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>पश्चिम महाराष्ट्रात शिंदेंना भाजपचा धक्का, आमदाराच्या भावासह ४० पदाधिकाऱ्यांचा शिवसेनेला जय महाराष्ट्र!</t>
+          <t>Fadnavis meets Guv Radhakrishnan, presents him book of Shivaji Maharaj's letters</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/solapur-political-news-bjp-strengthens-in-solapur-as-40-sena-leaders-join-with-shivaji-sawant-bdk97</t>
+          <t>https://www.ptinews.com/detail/national/Fadnavis-meets-Guv-Radhakrishnan--presents-him-book-of-Shivaji-Maharaj-s-letters/2832581</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>सोलापुरात भाजपची शिंदेंच्या शिवसेनावर कुरघोडी शिवाजी सावंतांनी शिवसेना सोडली,</t>
+          <t>Shiv Sena, NCP support Maha Governor’s nomination for Vice President</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/solapur-shivaji-sawant-leaves-shiv-sena-and-bjp-entry-confirmed-devendra-fadnavis-bjp-attack-on-eknath-shinde-shiv-sena-in-solapur-1377928</t>
+          <t>https://morungexpress.com/shiv-sena-ncp-support-maha-governors-nomination-for-vice-president</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>सोलापूरच्या राजकारणात मोठी खळबळ; तानाजी सावंत यांचा भाऊ करणार भाजपात प्रवेश</t>
+          <t>Supreme Court dismisses plea alleging 75 lakh bogus votes in Maharashtra Assembly polls</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/big-stir-in-solapur-politics-tanaji-sawants-brother-to-join-bjp/129377/</t>
+          <t>https://organiser.org/2025/08/19/308844/bharat/supreme-court-dismisses-plea-alleging-75-lakh-bogus-votes-in-maharashtra-assembly-polls/</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Rohit Pawar on Sanjay Shirsath: रोहित पवारांचे मंत्री संजय शिरसाटांवर भ्रष्टाचाराचे गंभीर आरोप; पहा काय म्हणाले</t>
+          <t>Alcaraz wins the Cincinnati Open after Sinner retires in the first set because of illness</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/amp</t>
+          <t>https://english.varthabharati.in/sports/alcaraz-wins-the-cincinnati-open-after-sinner-retires-in-the-first-set-because-of-illness</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Maharashtra Rain Update : मोठा निर्णय! अतिवृष्टीमुळे विद्यार्थ्यांना सुट्टी जाहीर; 'या' जिल्ह्यांमध्ये शाळा राहणार बंद, जाणून घ्या</t>
+          <t>खरगे, स्टॉलिन, नवीन पटनायक... उपराष्ट्रपति चुनाव से पहले राजनाथ सिंह को बीजेपी ने दी खास जिम्मेदारी</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/due-to-heavy-rain-government-declared-holiday-for-students-in-mumbai-thane-kalyan-dombivli-palghar-district/40074</t>
+          <t>https://navbharattimes.indiatimes.com/india/vice-president-election-defence-minister-rajnath-singh-reaches-out-to-dmk-tmc-bjd-for-consensus-for-cp-radhakrishnan/articleshow/123375990.cms</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Rohit Pawar: मंत्री संजय शिरसाटांनी केला ५ हजार कोटींचा घोटाळा; आमदार रोहित पवारांच्या आरोपाने खळबळ</t>
+          <t>'संवैधानिक संस्थाओं को कर रहे हैं नष्ट...' भाजपा सांसद निशिकांत दुबे ने राहुल गांधी पर साधा निशाना</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/rohit-pawar-alleges-sanjay-shirsat-over-5000-crore-worth-land-to-bivalkar-family/</t>
+          <t>https://www.timesnowhindi.com/india/constitutional-institutions-are-being-destroyed-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls-article-152485768</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Mumbai Rain Red Alert : पावसामुळे आतापर्यंत 7 जणांचा मृत्यू; साचलेल्या पाण्यामुळे प्रवाशांचे हाल अन् राजकारणही तापलं</t>
+          <t>शिवसेना एकनाथ शिंदे गुट को बड़ा झटका, शिवाजी सावंत भाजपा में होगें शामिल | Maharastra - Paliwalwani - Latest Hindi News</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/mumbai-rain-red-alert-heavy-rainfall-maharashtra-floods-bmc-pune-schooll-jap93</t>
+          <t>https://paliwalwani.com/maharastra/shiv-sena-eknath-shinde-faction-is-a-big-shock-shivaji-sawant-will-be-involved-in-bjp</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Shivsena | नाराजी भोवली! शिंदे गटातून बड्या नेत्याचा राजीनामा, राजकीय वर्तुळात खळबळ</t>
+          <t>चुनाव आयोग की प्रेस कॉन्फ्रेंस में इन दो पत्रकारों के सवालों ने बोलती बंद कर दी, देखें वीडियो – No. 1 Indian Media News Portal</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>https://www.thodkyaat.com/big-setback-for-eknath-shinde-faction-as-senior-leader-shivaji-sawant-joins-bjp-ahead-of-local-body-polls/</t>
+          <t>https://www.bhadas4media.com/eci-press-confrence-journalist-question/</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Rohit Pawar on Sanjay Shirsath: रोहित पवारांचे मंत्री संजय शिरसाटांवर भ्रष्टाचाराचे गंभीर आरोप; पहा काय म्हणाले</t>
+          <t>उपराष्ट्रपतीपदाचे उमेदवार राधाकृष्णन यांना पाठिंबा द्या; देवेंद्र फडणवीस यांची शरद पवार आणि उद्धव ठाकरे यांना साद</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/</t>
+          <t>https://marathi.freepressjournal.in/maharashtra/cp-radhakrishnan-vice-president-candidate-fadnavis-appeal-pawar-thackeray</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Ekanath Shinde Shivsena : शिंदे गटाला धक्का; आमदाराचा भाऊ व 40 पदाधिकाऱ्यांचा पक्षप्रवेश</t>
+          <t>राहुल गांधी पक्ष टिकवण्यासाठी निवडणूक आयोगाचा आधार घेतात; मंत्री चंद्रशेखर बावनकुळे यांची टीका</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>https://www.lokshahi.com/news/mla-tanaji-sawants-brother-shivaji-sawant-has-decided-to-quit-the-group-and-join-the-bjp</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/rahul-gandhi-takes-support-from-election-commission-to-save-party-minister-chandrashekhar-bawankule-criticizes.html</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>NCP demands : राज्यात ओला दुष्काळ जाहीर करा अन्…; राष्ट्रवादी शरद पवार गटाची मागणी</t>
+          <t>Pravin Darekar: राज्य सहकारी संघाच्या अध्यक्षपदी आमदार प्रवीण दरेकर</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/heavy-rains-wreak-havoc-in-maharashtra-sharad-pawar-ncp-demands-wet-drought-declaration-and-farmer-relief/</t>
+          <t>https://pudhari.news/maharashtra/pune/pravin-darekar-elected-cooperative-president-maharashtra-ac90</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>शिंदे गटाचे आमदार तानाजी सावंतांचे बंधू भाजपच्या वाटेवर</t>
+          <t>१९८७च्या काश्मीर निवडणूक गैरप्रकाराचा काँग्रेसला विसर - राजीव गांधींकडून विरोधकांच्या आरोपांकडे दुर्लक्ष</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>https://pcbtoday.in/%E0%A4%B6%E0%A4%BF%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%97%E0%A4%9F%E0%A4%BE%E0%A4%9A%E0%A5%87-%E0%A4%86%E0%A4%AE%E0%A4%A6%E0%A4%BE%E0%A4%B0-%E0%A4%A4%E0%A4%BE%E0%A4%A8%E0%A4%BE%E0%A4%9C%E0%A5%80/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/congress-forgets-1987-kashmir-election-malpractices-rajiv-gandhi-ignores-opposition-allegations.html</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Kokan Politics : शरद पवार गटाला धक्का; प्रदेश सरचिटणीस प्रशांत यादव भाजपाच्या वाटेवर</t>
+          <t>हवामानाचा अंदाज: आजही पावसाचा कहर? मुंबई, पुण्यासह 7 जिल्ह्यांना रेड अलर्ट; गडचिरोलीसह 4 जिल्ह्यांना यलो अलर्ट</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/kokan-politics-sharad-pawar-group-suffers-setback-state-general-secretary-prashant-yadav-on-bjps-path/</t>
+          <t>https://thefocusindia.com/national-news/maharashtra-weather-red-alert-mumbai-pune-7-districts-281414/</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Rajnath reaches out to DMK, TMC, BJD for consensus on VP nominee</t>
+          <t>Potholes Persist, Rekha Orders Fresh Campaign</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/rajnath-reaches-out-to-dmk-tmc-bjd-for-consensus-on-vp-nominee/articleshow/123373035.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/delhi/potholes-persist-rekha-orders-fresh-campaign/articleshow/123349516.cms</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>MSRTC और पुलिस की पहल, गढ़चिरौली के आदिवासी गांव को मिला पहला सार्वजनिक परिवहन, ग्रामीणों ने लहराया तिरंगा</t>
+          <t>Maharashtra News: Dy CM Eknath Shinde Launches ‘Ladki Sun – Surakshit Sun’ Campaign To Protect Women</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/news/india-news/photo/initiative-of-msrtc-and-police-tribal-village-of-gadchiroli-gets-first-public-transport-1558</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-dy-cm-eknath-shinde-launches-ladki-sun-surakshit-sun-campaign-to-protect-women-victims</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Uddhav Thackeray: मनसेसोबत युती महापालिका निवडणुकीत घातक ठरणार; उद्धव ठाकरेंना 'या' नेत्यानं केलं सावध?</t>
+          <t>Teachers planning violent protest: Cops</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/mns-alliance-risk-municipal-elections-uddhav-thackeray-warning-dk88-rc70</t>
+          <t>https://timesofindia.indiatimes.com/city/kolkata/teachers-planning-violent-protest-cops/articleshow/123350909.cms</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>अमित शहा हे महाराष्ट्रातल्या गुंडांचे आणि भ्रष्टाचाऱ्यांचे दिल्लीतले सेनापती, संजय राऊत यांचा घणाघात</t>
+          <t>'Slap, but don't make video': Raj Thackeray's blunt advice to MNS workers after Marathi 'slapgate' case</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/amit-shah-is-leader-of-maharashtra-corrupt-leader-says-sanjay-raut/</t>
+          <t>https://www.msn.com/en-in/news/India/slap-but-dont-make-video-raj-thackerays-blunt-advice-to-mns-workers-after-marathi-slapgate-case/ar-AA1I11OF</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Sanjay Raut : निसाकाचा संघर्ष उफाळला, अनिल कदमांनी साकडं घातलं आता संजय राऊत मैदानात</t>
+          <t>Mumbai: Iconic Sword of Raghuji Bhonsle Arrives from London; Bike Rally Cancelled Due to Rains, Grand...</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/niphad-sugar-factory-crisis-sanjay-raut-anil-kadam-memorandum-farmers-workers-protest-nashik-gs97</t>
+          <t>https://www.lokmattimes.com/mumbai/mumbai-iconic-sword-of-raghuji-bhonsle-arrives-from-london-bike-rally-cancelled-due-to-rains-grand-inauguration-tonight-a525/</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>राधाकृष्णन यांना राज्यातील सर्वपक्षीय खासदारांनी पाठिंबा द्यावा</t>
+          <t>How CP Radhakrishnan Broke The Taboo Around Modi And Changed The Narrative After 2002 Gujarat Episode - The</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/radhakrishnan-should-be-supported-by-mps-from-all-parties-in-the-state/114185/</t>
+          <t>https://thecommunemag.com/how-cpr-broke-the-taboo-around-modi/</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>22-kg Golden Kalash Installed at Sant Dnyaneshwar Temple, Crafted by Shripad Shankar Nagarkar Jewellers Pune</t>
+          <t>CP Radhakrishnan: A Swayamsevak, Grassroots BJP Organiser, Former MP, Governor - Now NDA’s Pick For Vice</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/business/22-kg-golden-kalash-installed-at-sant-dnyaneshwar-temple-crafted-by-shripad-shankar-nagarkar-jewellers-pune/</t>
+          <t>https://thecommunemag.com/cp-radhakrishnan-grassroots-bjp-organiser-former-mp-governor-now-ndas-pick-for-vice-president/</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>उप-राष्ट्रपति चुनाव: देवेंद्र फडणवीस का 'मराठी अस्मिता' वाला दांव, क्या करेंगे उद्धव ठाकरे और शरद पवार?</t>
+          <t>पश्चिम महाराष्ट्रात शिंदेंना भाजपचा धक्का, आमदाराच्या भावासह ४० पदाधिकाऱ्यांचा शिवसेनेला जय महाराष्ट्र!</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%89%E0%A4%AA-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A4%AA%E0%A4%A4-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%85%E0%A4%B8%E0%A5%8D%E0%A4%AE-%E0%A4%A4-%E0%A4%B5-%E0%A4%B2-%E0%A4%A6-%E0%A4%82%E0%A4%B5-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%94%E0%A4%B0-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0/ar-AA1KJ5pi</t>
+          <t>https://saamtv.esakal.com/maharashtra/solapur-political-news-bjp-strengthens-in-solapur-as-40-sena-leaders-join-with-shivaji-sawant-bdk97</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Demand to release list of property-holders affected due to road-widening in 5 days</t>
+          <t>सोलापुरात भाजपची शिंदेंच्या शिवसेनावर कुरघोडी शिवाजी सावंतांनी शिवसेना सोडली,</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/aurangabad/demand-to-release-list-of-property-holders-affected-due-to-road-widening-in-5-days/</t>
+          <t>https://marathi.abplive.com/news/politics/solapur-shivaji-sawant-leaves-shiv-sena-and-bjp-entry-confirmed-devendra-fadnavis-bjp-attack-on-eknath-shinde-shiv-sena-in-solapur-1377928</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: Rohit Pawar Alleges ₹5,000-Crore Land Scam Against Minister Sanjay Shirsat</t>
+          <t>सोलापूरच्या राजकारणात मोठी खळबळ; तानाजी सावंत यांचा भाऊ करणार भाजपात प्रवेश</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-rohit-pawar-alleges-5000-crore-land-scam-against-minister-sanjay-shirsat</t>
+          <t>https://www.timemaharashtra.com/politics/big-stir-in-solapur-politics-tanaji-sawants-brother-to-join-bjp/129377/</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Sanjay Shirsat : मंत्री शिरसाट यांच्यावर ५ हजार कोटींच्या जमीन घोटाळ्याचा आरोप</t>
+          <t>Rohit Pawar on Sanjay Shirsath: रोहित पवारांचे मंत्री संजय शिरसाटांवर भ्रष्टाचाराचे गंभीर आरोप; पहा काय म्हणाले</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/minister-shirsat-accused-of-rs-5000-crore-land-scam-np88</t>
+          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/amp</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>'ऑपरेशन लोटस वगैरे काही नाही; लवकरच ऑपरेशन टायगर दिसेल', सोलापूरच्या राजकारणात पडद्यामागे काय घडतंय?</t>
+          <t>राजधानीत पावसाचा कहर! मुंबई विद्यापीठाचा परीक्षांबाबत तडकाफडकी मोठा निर्णय!</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%B2-%E0%A4%9F%E0%A4%B8-%E0%A4%B5%E0%A4%97%E0%A5%88%E0%A4%B0%E0%A5%87-%E0%A4%95-%E0%A4%B9-%E0%A4%A8-%E0%A4%B9-%E0%A4%B2%E0%A4%B5%E0%A4%95%E0%A4%B0%E0%A4%9A-%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%9F-%E0%A4%AF%E0%A4%97%E0%A4%B0-%E0%A4%A6-%E0%A4%B8%E0%A5%87%E0%A4%B2-%E0%A4%B8-%E0%A4%B2-%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B0-%E0%A4%9C%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A4-%E0%A4%AA%E0%A4%A1%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%AE-%E0%A4%97%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%98%E0%A4%A1%E0%A4%A4%E0%A4%82%E0%A4%AF/ar-AA1KKoUc</t>
+          <t>https://www.tv9marathi.com/maharashtra/mumbai-university-postponed-its-all-exam-to-be-held-on-19-august-due-to-heavy-rain-marathi-news-1472932.html</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Mumbai Rain Mayhem: City Comes To Standstill As Life Thrown Out Of Gear; MonoRail Gets Stuck</t>
+          <t>Rohit Pawar: मंत्री संजय शिरसाटांनी केला ५ हजार कोटींचा घोटाळा; आमदार रोहित पवारांच्या आरोपाने खळबळ</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!state/mumbai-rains-update-august-19-govt-semi-govt-offices-shut-bmc-urges-wfh-for-pvt-employees-enn25081901231</t>
+          <t>https://deshdoot.com/rohit-pawar-alleges-sanjay-shirsat-over-5000-crore-worth-land-to-bivalkar-family/</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Heritage India: Iconic Sword of Maratha Commander Raghuji Raje Bhonsle Arrives in Mumbai</t>
+          <t>Mumbai Rain Red Alert : पावसामुळे आतापर्यंत 7 जणांचा मृत्यू; साचलेल्या पाण्यामुळे प्रवाशांचे हाल अन् राजकारणही तापलं</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-govt-brings-back-iconic-sword-of-maratha-commander-raghuji-raje-bhonsle-auctioned-for-rs-4715-lakh-to-mumbai-3685565</t>
+          <t>https://sarkarnama.esakal.com/mumbai/mumbai-rain-red-alert-heavy-rainfall-maharashtra-floods-bmc-pune-schooll-jap93</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
+          <t>Shivsena | नाराजी भोवली! शिंदे गटातून बड्या नेत्याचा राजीनामा, राजकीय वर्तुळात खळबळ</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/business/'third-mumbai'-to-boost-metropolitan-region-development:-fadnavis/2834902</t>
+          <t>https://www.thodkyaat.com/big-setback-for-eknath-shinde-faction-as-senior-leader-shivaji-sawant-joins-bjp-ahead-of-local-body-polls/</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Shortage of teachers hits rollout of NEP in govt, aided Maha colleges</t>
+          <t>Rohit Pawar on Sanjay Shirsath: रोहित पवारांचे मंत्री संजय शिरसाटांवर भ्रष्टाचाराचे गंभीर आरोप; पहा काय म्हणाले</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>https://www.pressreader.com/india/hindustan-times-st-jaipur/20250819/281681145971378</t>
+          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>कैसी होगी तीसरी मुंबई, कितनी बड़ी और कहां बन रही, सुविधाओं से लेकर प्लानिंग तक, CM फडणवीस ने सब बताया</t>
+          <t>Ekanath Shinde Shivsena : शिंदे गटाला धक्का; आमदाराचा भाऊ व 40 पदाधिकाऱ्यांचा पक्षप्रवेश</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%95%E0%A5%88%E0%A4%B8-%E0%A4%B9-%E0%A4%97-%E0%A4%A4-%E0%A4%B8%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%95-%E0%A4%A4%E0%A4%A8-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%94%E0%A4%B0-%E0%A4%95%E0%A4%B9-%E0%A4%82-%E0%A4%AC%E0%A4%A8-%E0%A4%B0%E0%A4%B9-%E0%A4%B8%E0%A5%81%E0%A4%B5-%E0%A4%A7-%E0%A4%93%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AA%E0%A5%8D%E0%A4%B2-%E0%A4%A8-%E0%A4%82%E0%A4%97-%E0%A4%A4%E0%A4%95-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%AF/ar-AA1KLMl6?ocid=finance-verthp-feeds</t>
+          <t>https://www.lokshahi.com/news/mla-tanaji-sawants-brother-shivaji-sawant-has-decided-to-quit-the-group-and-join-the-bjp</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>महाराष्ट्र के बीड, लातूर और नांदेड में भारी बारिश से बाढ़ की स्थिति गंभीर, NDRF और सेना तैनात</t>
+          <t>शिंदे गटाचे आमदार तानाजी सावंतांचे बंधू भाजपच्या वाटेवर</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/maharashtra/pune/heavy-rains-in-maharashtra-flood-havoc-in-beed-latur-and-nanded-ndrf-and-army-deployed/articleshow/123370629.cms</t>
+          <t>https://pcbtoday.in/%E0%A4%B6%E0%A4%BF%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%97%E0%A4%9F%E0%A4%BE%E0%A4%9A%E0%A5%87-%E0%A4%86%E0%A4%AE%E0%A4%A6%E0%A4%BE%E0%A4%B0-%E0%A4%A4%E0%A4%BE%E0%A4%A8%E0%A4%BE%E0%A4%9C%E0%A5%80/</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>मराठा सेनापति रघुजी भोंसले की तलवार मुंबई पहुंची</t>
+          <t>Kokan Politics : शरद पवार गटाला धक्का; प्रदेश सरचिटणीस प्रशांत यादव भाजपाच्या वाटेवर</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/ncr/new-delhi/story-historic-sword-of-maratha-general-raghuji-bhosale-i-repatriated-to-mumbai-201755537654676.html</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/kokan-politics-sharad-pawar-group-suffers-setback-state-general-secretary-prashant-yadav-on-bjps-path/</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में भारी बारिश से सात लोगों की मौत, 200 ग्रामीण फंसे</t>
+          <t>Uddhav Thackeray: मनसेसोबत युती महापालिका निवडणुकीत घातक ठरणार; उद्धव ठाकरेंना 'या' नेत्यानं केलं सावध?</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/seven-people-died-due-to-heavy-rains-in-maharashtra-200-villagers-stranded/856903/?amp</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/mns-alliance-risk-municipal-elections-uddhav-thackeray-warning-dk88-rc70</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में माफ हो सकते हैं पुराने ट्रैफिक चालान, माफी योजना लाने की तैयारी में सरकार</t>
+          <t>Mumbai Rain Alert : मुंबईकरांनो सावध रहा.. पुढील 4 तास धोक्याचे… रेड अलर्ट अन् हवामान खात्याचा...</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/government-schemes/others/maharashtra-government-is-set-to-roll-out-an-amnesty-scheme-for-one-time-settlement-of-pending-traffic-challan/articleshow/123367444.cms</t>
+          <t>https://www.tv9marathi.com/videos/mumbai-weather-forecast-imd-red-alert-for-mumbai-for-next-4-hours-extremely-important-for-mumbaikars-1473139.html/amp</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Third Mumbai महानगर क्षेत्राच्या विकासाचा नवा अध्याय असेल; मुख्यमंत्र्यांनी सांगितलं कशी असेल ‘तिसरी मुंबई’ Third Mumbai in Raigad district to boost metropolitan region development said Devendra Fadnavis</t>
+          <t>अमित शहा हे महाराष्ट्रातल्या गुंडांचे आणि भ्रष्टाचाऱ्यांचे दिल्लीतले सेनापती, संजय राऊत यांचा घणाघात</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/third-mumbai-in-raigad-district-to-boost-metropolitan-region-development-said-devendra-fadnavis-89724</t>
+          <t>https://www.saamana.com/amit-shah-is-leader-of-maharashtra-corrupt-leader-says-sanjay-raut/</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Maharashtra Rains: महाराष्ट्र में बाढ़ से हालात गंभीर, मराठवाड़ा में NDRF और सेना तैनात, सरकार की क्या है तैयारी?</t>
+          <t>What happened in the Trump-Putin meeting? | Chandrashekhar Nene Maha MTB</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/mumbai-heavy-rain-maharashtra-flood-situation-serious-ndrf-and-indian-army-deployed-in-marathwada/articleshow/123370824.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/what-happened-in-the-trump-putin-meeting-chandrashekhar-nene-maha-mtb.html</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>राज्यातील पूरस्थितीवर सरकारचे लक्ष, मदत कार्य सुरू – बावनकुळे</t>
+          <t>Sanjay Raut : निसाकाचा संघर्ष उफाळला, अनिल कदमांनी साकडं घातलं आता संजय राऊत मैदानात</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/governments-attention-on-flood-situation-in-the-state-information-from-chandrashekhar-bawankule-amy-95-5313292/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/niphad-sugar-factory-crisis-sanjay-raut-anil-kadam-memorandum-farmers-workers-protest-nashik-gs97</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>‘पीएम आवास’च्या तीस लाख घरांना मोफत वीज; राज्य सरकार देणार ५० हजारांचे अनुदान: मुख्यमंत्री</t>
+          <t>उपराष्ट्रपतीपदाचे एनडीए उमेदवार सीपी राधाकृष्णन यांच्यावर राजकीय पक्षांच्या प्रतिक्रिया</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/free-electricity-to-three-lakh-houses-of-pm-awas-yojana-state-government-will-provide-subsidy-of-rs-50-thousand-chief-minister-a-a747/</t>
+          <t>https://www.dainikprabhat.com/parties-reaction-to-nda-vice-presidential-candidate-cp-radhakrishnan/</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Maharashtra Government: शेतकऱ्यांना मिळणार गुड न्यूज: बळीराजासाठी सरकार मोठा निर्णय घेण्याच्या तयारीत</t>
+          <t>‘गँग्स ऑफ गद्दार’: शिंदेचा मंत्री ‘रोहित पवारांच्या’ निशाण्यावर</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/sanjay-rathod-big-statement-on-loan-waiver-maharashtra-farmers-get-loan-waiver-minister-give-hint-in-award-ceremony-program-yavatmal-pusad-bbj88</t>
+          <t>https://politicalmaharashtra.in/gangs-of-traitors-shindes-minister-targeted-by-rohit-pawar-97619/</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>कोल्हापुर में शुरू हुई बॉम्बे हाईकोर्ट की नई खंडपीठ, सीजेआई बोले– महाराष्ट्र न्यायिक ढांचे में आगे</t>
+          <t>22-kg Golden Kalash Installed at Sant Dnyaneshwar Temple, Crafted by Shripad Shankar Nagarkar Jewellers Pune</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/maharashtra/bombay-high-court-kolhapur-bench-cji-b-r-gavai-maharashtra-government-54-803927</t>
+          <t>https://www.tribuneindia.com/news/business/22-kg-golden-kalash-installed-at-sant-dnyaneshwar-temple-crafted-by-shripad-shankar-nagarkar-jewellers-pune/</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>श्रीमती प्रज्ञा वाळकेंचा भ्रष्टाचारामध्ये उच्चांक ; सरकारविरोधी चळवळीतीही सक्रिय सहभाग ?</t>
+          <t>Demand to release list of property-holders affected due to road-widening in 5 days</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>https://lokmanthan.com/mrs-pragya-walkens-high-score-in-corruption-active-participation-in-anti-government-movement/</t>
+          <t>https://www.lokmattimes.com/aurangabad/demand-to-release-list-of-property-holders-affected-due-to-road-widening-in-5-days/</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>देशभर में बारिश का कहर: मुंबई-बेहद जाम, दिल्ली में यमुना उफान पर, स्कूल-कॉलेज बंद</t>
+          <t>Maharashtra Politics: Rohit Pawar Alleges ₹5,000-Crore Land Scam Against Minister Sanjay Shirsat</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>https://dainikdehat.com/india/rain-wreaks-havoc-across-the-country-mumbai-is-jam-packed-yamuna-is-in-spate-in-delhi-schools-and-colleges-are-closed/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-rohit-pawar-alleges-5000-crore-land-scam-against-minister-sanjay-shirsat</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>मुंबई झोपडपट्टीमुक्त होणार का? जलद पुनर्विकासाचा मुख्यमंत्र्यांनी काय सांगितला प्लॅन?</t>
+          <t>Sanjay Shirsat : मंत्री शिरसाट यांच्यावर ५ हजार कोटींच्या जमीन घोटाळ्याचा आरोप</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>https://www.tendernama.com/mahatender/mumbai/will-mumbai-become-slum-free-what-is-the-chief-ministers-plan-for-rapid-redevelopment</t>
+          <t>https://pudhari.news/maharashtra/mumbai/minister-shirsat-accused-of-rs-5000-crore-land-scam-np88</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Mumbai Chawl Redevelopment | चाळ झाली आधुनिक वस्ती</t>
+          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>https://pudhari.news/sampadakiy/mumbai-chawl-redevelopment-displaced-workers-problem-sp96</t>
+          <t>https://www.ptinews.com/story/business/'third-mumbai'-to-boost-metropolitan-region-development:-fadnavis/2834902</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Heavy Rains Batter Mumbai: Red Alert Issued, Schools and Colleges Closed on August 19 in Thane and...</t>
+          <t>Heritage India: Iconic Sword of Maratha Commander Raghuji Raje Bhonsle Arrives in Mumbai</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/news/national/heavy-rains-batter-mumbai-red-alert-issued-schools-and-colleges-closed-on-august-19-in-thane-and-palghar-998357</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-govt-brings-back-iconic-sword-of-maratha-commander-raghuji-raje-bhonsle-auctioned-for-rs-4715-lakh-to-mumbai-3685565</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Mumbai Rains: Are Private and Public offices shut today? BMC issues statement, says...</t>
+          <t>Mumbai Rain Mayhem: City Comes To Standstill As Life Thrown Out Of Gear; MonoRail Gets Stuck</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>https://www.india.com/news/india/mumbai-rains-are-private-and-public-offices-shut-today-bmc-work-from-home-schools-colleges-devendra-fadnavis-markets-8019561/</t>
+          <t>https://www.etvbharat.com/en/!state/mumbai-rains-update-august-19-govt-semi-govt-offices-shut-bmc-urges-wfh-for-pvt-employees-enn25081901231</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Surya Roshni to invest Rs 25 cr for biz expansion</t>
+          <t>Shortage of teachers hits rollout of NEP in govt, aided Maha colleges</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/business/2025/08/18/dcm62-biz-briefs-3.html</t>
+          <t>https://www.pressreader.com/india/hindustan-times-st-jaipur/20250819/281681145971378</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
+          <t>Maha govt waives Stamp Duty worth Rs 38.99 lakh for Tata Cancer Hospital in Raigad (Ld)</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/business/third-mumbai-to-boost-metropolitan-region-development-fadnavis-9674858</t>
+          <t>https://www.thehawk.in/news/india/maha-govt-waives-stamp-duty-worth-rs-3899-lakh-for-tata-cancer-hospital-in-raigad-ld</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>'Third Mumbai' to boost MMR development, says Fadnavis; invites pvt sector to join in its creation</t>
+          <t>कैसी होगी तीसरी मुंबई, कितनी बड़ी और कहां बन रही, सुविधाओं से लेकर प्लानिंग तक, CM फडणवीस ने सब बताया</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/business/third-mumbai-to-boost-mmr-development-says-fadnavis-invites-pvt-sector-to-join-in-its-creation-9674122</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%95%E0%A5%88%E0%A4%B8-%E0%A4%B9-%E0%A4%97-%E0%A4%A4-%E0%A4%B8%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%95-%E0%A4%A4%E0%A4%A8-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%94%E0%A4%B0-%E0%A4%95%E0%A4%B9-%E0%A4%82-%E0%A4%AC%E0%A4%A8-%E0%A4%B0%E0%A4%B9-%E0%A4%B8%E0%A5%81%E0%A4%B5-%E0%A4%A7-%E0%A4%93%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AA%E0%A5%8D%E0%A4%B2-%E0%A4%A8-%E0%A4%82%E0%A4%97-%E0%A4%A4%E0%A4%95-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%AF/ar-AA1KLMl6?ocid=finance-verthp-feeds</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>मुंबई में भारी बारिश के बीच सुचारू रूप से चल रही मेट्रो, सीएम फडणवीस ने की तारीफ</t>
+          <t>शाहू महाराज की तरह करना होगा न्याय, कोल्हापुर में HC की नई सर्किट बेंच के उद्घाटन पर बोले CJI गवई</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>https://www.m.khaskhabar.com/news/news-metro-running-smoothly-amid-heavy-rains-in-mumbai-cm-fadnavis-praised-news-hindi-1-745323-KKN.html</t>
+          <t>https://www.tv9hindi.com/state/maharashtra/cji-inaugurated-new-circuit-bench-said-a-big-thing-about-maharashtra-government-3441714.html</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Asia Cup 2025: पाकिस्तान क्रिकेट के मुख्य चयनकर्ता का बड़ा बयान, बोले- भारत को हराएगा पाकिस्तान</t>
+          <t>महाराष्ट्र में भारी बारिश से सात लोगों की मौत, 200 ग्रामीण फंसे</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/sports/asia-cup-2025-2025-08-18-1156799</t>
+          <t>https://hindi.theprint.in/india/seven-people-died-due-to-heavy-rains-in-maharashtra-200-villagers-stranded/856903/?amp</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>मानसून में हाल बेहाल, भारी बारिश से इस राज्य में जगह-जगह भरा पानी, स्कूल-कॉलेज किए बंद</t>
+          <t>महाराष्ट्र के बीड, लातूर और नांदेड में भारी बारिश से बाढ़ की स्थिति गंभीर, NDRF और सेना तैनात</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/national-news/heavy-rain-alert-in-mumbai-monsoon-gained-momentum-know-imd-weather-update-19874723</t>
+          <t>https://navbharattimes.indiatimes.com/state/maharashtra/pune/heavy-rains-in-maharashtra-flood-havoc-in-beed-latur-and-nanded-ndrf-and-army-deployed/articleshow/123370629.cms</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>How much rain did Mumbai receive on Monday? Check area-wise list</t>
+          <t>महाराष्ट्र में माफ हो सकते हैं पुराने ट्रैफिक चालान, माफी योजना लाने की तैयारी में सरकार</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/how-much-rain-did-mumbai-areas-receive-on-monday-check-list-bandra-juhu-chembur-10196732/</t>
+          <t>https://navbharattimes.indiatimes.com/government-schemes/others/maharashtra-government-is-set-to-roll-out-an-amnesty-scheme-for-one-time-settlement-of-pending-traffic-challan/articleshow/123367444.cms</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Ahead of Civic Polls, Hitendra Thakur Backs Loyalists: ‘My Karyakarta Is With Me, They Ensure Our Party Wins</t>
+          <t>Maharashtra Rains: महाराष्ट्र में बाढ़ से हालात गंभीर, मराठवाड़ा में NDRF और सेना तैनात, सरकार की क्या है तैयारी?</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/maharashtra/ahead-of-civic-polls-hitendra-thakur-backs-loyalists-my-karyakarta-is-with-me-they-ensure-our-party-wins-a475/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/mumbai-heavy-rain-maharashtra-flood-situation-serious-ndrf-and-indian-army-deployed-in-marathwada/articleshow/123370824.cms</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>NCP (SP) targets Maha minister over Rs 5,000 cr scam in Navi Mumbai’s CIDCO land; demands his resignation</t>
+          <t>मराठा सेनापति रघुजी भोंसले की तलवार मुंबई पहुंची</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/ncp-sp-targets-maha-minister-over-rs-5000-cr-scam-in-navi-mumbais-cidco-land-demands-his-resignation/</t>
+          <t>https://www.livehindustan.com/ncr/new-delhi/story-historic-sword-of-maratha-general-raghuji-bhosale-i-repatriated-to-mumbai-201755537654676.html</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>CM to join Kawad yatra, TV center chowk shut for 5 hours</t>
+          <t>Third Mumbai महानगर क्षेत्राच्या विकासाचा नवा अध्याय असेल; मुख्यमंत्र्यांनी सांगितलं कशी असेल ‘तिसरी मुंबई’ Third Mumbai in Raigad district to boost metropolitan region development said Devendra Fadnavis</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/aurangabad/cm-to-join-kawad-yatra-tv-center-chowk-shut-for-5-hours/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/third-mumbai-in-raigad-district-to-boost-metropolitan-region-development-said-devendra-fadnavis-89724</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Maha govt plans amnesty scheme to recover pending transport fines</t>
+          <t>राज्यातील पूरस्थितीवर सरकारचे लक्ष, मदत कार्य सुरू – बावनकुळे</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/maha-govt-plans-amnesty-scheme-to-recover-pending-transport-fines/</t>
+          <t>https://www.loksatta.com/nagpur/governments-attention-on-flood-situation-in-the-state-information-from-chandrashekhar-bawankule-amy-95-5313292/</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>चुनाव के बाद होगा महामंडलों का वितरण, महायुति के इच्छुक नेताओं पर प्रदर्शन का दबाव</t>
+          <t>‘पीएम आवास’च्या तीस लाख घरांना मोफत वीज; राज्य सरकार देणार ५० हजारांचे अनुदान: मुख्यमंत्री</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/nagpur/distribution-of-maha-mandals-will-happen-after-the-elections-pressure-of-demonstration-on-the-aspiring-leaders-of-mahayuti-1322474.html</t>
+          <t>https://www.lokmat.com/maharashtra/free-electricity-to-three-lakh-houses-of-pm-awas-yojana-state-government-will-provide-subsidy-of-rs-50-thousand-chief-minister-a-a747/</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>राज्यात ओला दुष्काळ जाहीर करा, विशेष अधिवेशन बोलवा मुसळधार पावसानंतर शरद पवारांच्या</t>
+          <t>Maharashtra Government: शेतकऱ्यांना मिळणार गुड न्यूज: बळीराजासाठी सरकार मोठा निर्णय घेण्याच्या तयारीत</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/sharad-pawar-ncp-demands-after-heavy-rains-declaring-a-wet-drought-in-the-state-calling-a-special-session-shashikant-shinde-1377947</t>
+          <t>https://saamtv.esakal.com/maharashtra/sanjay-rathod-big-statement-on-loan-waiver-maharashtra-farmers-get-loan-waiver-minister-give-hint-in-award-ceremony-program-yavatmal-pusad-bbj88</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>सिडको जमिन वाटप प्रकरणावरून राजकारण तापले; पवारांचा शिरसाठांवर घणाघाती हल्ला</t>
+          <t>कोल्हापुर में शुरू हुई बॉम्बे हाईकोर्ट की नई खंडपीठ, सीजेआई बोले– महाराष्ट्र न्यायिक ढांचे में आगे</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/politics-heats-up-over-cidco-land-allocation-issue-pawar-attacks-shirsath/</t>
+          <t>https://mpbreakingnews.in/maharashtra/bombay-high-court-kolhapur-bench-cji-b-r-gavai-maharashtra-government-54-803927</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>'Destroying constitutional institutions': Nishikant Dubey slams Rahul Gandhi as SC dismisses plea challenging 2024 Maharashtra polls</t>
+          <t>श्रीमती प्रज्ञा वाळकेंचा भ्रष्टाचारामध्ये उच्चांक ; सरकारविरोधी चळवळीतीही सक्रिय सहभाग ?</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
+          <t>https://lokmanthan.com/mrs-pragya-walkens-high-score-in-corruption-active-participation-in-anti-government-movement/</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Mumbai Rain LIVE Updates: मुंबईत सखल भागात साचलेल्या पाण्याचा निचरा</t>
+          <t>Sharad Pawar | शासन विमानतळ करणारच ; तर मोबदलासाठी आग्रह धरा – शरद पवार</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/mumbai-rain-live-updates-18-august-imd-red-alert-in-mumbai-weather-waterlogging-traffic-jam-local-train-train-latest-updates-in-marathi-933169</t>
+          <t>https://www.dainikprabhat.com/sharad-pawar-government-will-build-airport-so-insist-on-compensation-sharad-pawar/</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>'उपराष्ट्रपती'साठी महाराष्ट्राच्या राज्यपालांचे नाव; फडणवीसांचे खासदारांना आवाहन, पवार-ठाकरेंना टोला</t>
+          <t>देशभर में बारिश का कहर: मुंबई-बेहद जाम, दिल्ली में यमुना उफान पर, स्कूल-कॉलेज बंद</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-urges-mps-to-support-radhakrishnan-targets-uddhav-thackeray-and-sharad-pawar-035137.html?ref_source=OI-MR&amp;ref_medium=Home-Page&amp;ref_campaign=News-Cards</t>
+          <t>https://dainikdehat.com/india/rain-wreaks-havoc-across-the-country-mumbai-is-jam-packed-yamuna-is-in-spate-in-delhi-schools-and-colleges-are-closed/</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>मुंबई में कबूतरखानों पर विवाद, महापालिका ने नागरिकों से आपत्तियां और सुझाव मांगे</t>
+          <t>Maharashtra approves amendments for Dharavi project land transfer</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/maharashtra/mumbai-municipal-corporation-pigeon-shelters-public-consultation-high-court-54-803921</t>
+          <t>https://www.msn.com/en-in/news/India/maharashtra-approves-amendments-for-dharavi-project-land-transfer/ar-AA1G1ze9</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Maharashtra govt plans amnesty scheme to recover pending transport fines</t>
+          <t>Cabinet sends back note regarding GMR with multiple queries</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>https://auto.economictimes.indiatimes.com/amp/news/industry/maharashtras-new-amnesty-scheme-settle-transport-fines-and-save-big/123364146</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/18/cabinet-sends-back-note-regarding-gmr-with-multiple-queries.html</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Over ₹6.52 Crore Medical Aid Distributed To 5,000 Beneficiaries In Pune District</t>
+          <t>मुंबई झोपडपट्टीमुक्त होणार का? जलद पुनर्विकासाचा मुख्यमंत्र्यांनी काय सांगितला प्लॅन?</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/over-%E2%82%B96-52-crore-medical-aid-distributed-to-5000-beneficiaries-in-pune-district/</t>
+          <t>https://www.tendernama.com/mahatender/mumbai/will-mumbai-become-slum-free-what-is-the-chief-ministers-plan-for-rapid-redevelopment</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Pratap Sarnaik : राज्यातील वाहनांवर तब्‍बल 2500 कोटींचा दंड; सरकार एकरकमी परतफेडीची अभय योजना आणणार</t>
+          <t>Mumbai Local Train: मुंबईतील लोकल प्रवाशांना मोठा दिलासा! एमआरव्हीसीकडून 15,000 कोटींचा नवा प्रकल्पाचा प्रस्ताव</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/fines-of-around-rs-2500-crore-on-vehicles-in-the-state-government-to-introduce-a-lump-sum-repayment-scheme/</t>
+          <t>https://www.msn.com/mr-in/news/other/mumbai-local-train-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%A4-%E0%A4%B2-%E0%A4%B2-%E0%A4%95%E0%A4%B2-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%B6-%E0%A4%82%E0%A4%A8-%E0%A4%AE-%E0%A4%A0-%E0%A4%A6-%E0%A4%B2-%E0%A4%B8-%E0%A4%8F%E0%A4%AE%E0%A4%86%E0%A4%B0%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%B8-%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-15-000-%E0%A4%95-%E0%A4%9F-%E0%A4%82%E0%A4%9A-%E0%A4%A8%E0%A4%B5-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95%E0%A4%B2%E0%A5%8D%E0%A4%AA-%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%B5/ar-AA1KHzxV?ocid=finance-verthp-feeds</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Nagpur’s Councils Starved Again: Pennies for a Region in Ruin</t>
+          <t>Mumbai Chawl Redevelopment | चाळ झाली आधुनिक वस्ती</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/08/18/nagpurs-councils-starved-again-pennies-for-a-region-in-ruin/</t>
+          <t>https://pudhari.news/sampadakiy/mumbai-chawl-redevelopment-displaced-workers-problem-sp96</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Cases from 6 districts to be heard | ‘A dream comes true after 40-45 years of struggle’: CJI inaugurates HC bench in Kolhapur</t>
+          <t>Heavy Rains Batter Mumbai: Red Alert Issued, Schools and Colleges Closed on August 19 in Thane and...</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/pune/cases-dream-struggle-cji-inaugurates-hc-bench-kolhapur-10195928/</t>
+          <t>https://www.thehansindia.com/news/national/heavy-rains-batter-mumbai-red-alert-issued-schools-and-colleges-closed-on-august-19-in-thane-and-palghar-998357</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Maratha commander Raghuji Bhonsle's sword brought to Mumbai!!</t>
+          <t>Mumbai Rains: Are Private and Public offices shut today? BMC issues statement, says...</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>https://www.indiaherald.com/Breaking/Read/994842382/Maratha-commander-Raghuji-Bhonsles-sword-brought-to-Mumbai</t>
+          <t>https://www.india.com/news/india/mumbai-rains-are-private-and-public-offices-shut-today-bmc-work-from-home-schools-colleges-devendra-fadnavis-markets-8019561/</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>CJI Gavai: "Maharashtra Govt At Forefront Of Efforts To Provide Infrastructure For Judiciary"</t>
+          <t>Ajit Pawar ‘torturing’ me, claims Ram Shinde</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>https://lawchakra.in/legal-updates/cji-gavai-infrastructure-for-judiciary/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/ajit-pawar-torturing-me-claims-ram-shinde/articleshow/123372969.cms</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Maratha general Raghuji Bhonsle's sword brought to Mumbai</t>
+          <t>Surya Roshni to invest Rs 25 cr for biz expansion</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>https://english.metrovaartha.com/news/mumbai/maratha-general-raghuji-bhonsles-sword-brought-to-mumbai</t>
+          <t>https://www.theweek.in/wire-updates/business/2025/08/18/dcm62-biz-briefs-3.html</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>महाराष्ट्रातील 'या' जिल्ह्यात उभारणार 'स्टॅच्यू ऑफ युनिटी'; सरकारचा काय आहे प्लॅन?</t>
+          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>https://www.tendernama.com/mahatender/paschim-maharashtra/statue-of-unity-style-memorial-in-maharashtra-soon</t>
+          <t>https://www.newsdrum.in/business/third-mumbai-to-boost-metropolitan-region-development-fadnavis-9674858</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>मराठा सेनापति रघुजी भोंसले की तलवार मुंबई लाई गई</t>
+          <t>'Third Mumbai' to boost MMR development, says Fadnavis; invites pvt sector to join in its creation</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/maratha-commander-raghuji-bhosales-sword-brought-to-mumbai/856774/</t>
+          <t>https://www.newsdrum.in/business/third-mumbai-to-boost-mmr-development-says-fadnavis-invites-pvt-sector-to-join-in-its-creation-9674122</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Kolhapur : सरन्यायाधीश Bhushan Gavai यांच्या हस्ते सर्किट बेंच इमारतीचे उद्घाटन</t>
+          <t>मुंबई में भारी बारिश के बीच सुचारू रूप से चल रही मेट्रो, सीएम फडणवीस ने की तारीफ</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/kolhapur-circuit-bench-inauguration-with-chief-justice-bhushan-gavai-marathi-news/</t>
+          <t>https://www.m.khaskhabar.com/news/news-metro-running-smoothly-amid-heavy-rains-in-mumbai-cm-fadnavis-praised-news-hindi-1-745323-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>राज्य को बाढ़ आपदा घोषित करो… विशेष अधिवेशन बुलाओ… एनसीपी प्रदेश अध्यक्ष ने की सीएम से मांग</t>
+          <t>Asia Cup 2025: पाकिस्तान क्रिकेट के मुख्य चयनकर्ता का बड़ा बयान, बोले- भारत को हराएगा पाकिस्तान</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/declare-the-state-a-flood-disaster-call-a-special-session-ncp-state-president-made-a-demand-to-the-cm/</t>
+          <t>https://www.indiatv.in/video/sports/asia-cup-2025-2025-08-18-1156799</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Revenue Minister बावनकुले का रुख</t>
+          <t>Nagpur’s Councils Starved Again: Pennies for a Region in Ruin</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/amp/local/maharashtra/revenue-minister-bawankules-stance-4218277</t>
+          <t>https://thelivenagpur.com/2025/08/18/nagpurs-councils-starved-again-pennies-for-a-region-in-ruin/</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Shashikant Shinde on Heavy Rain: राज्यात अतिवृष्टीमुळे ओला दुष्काळ जाहीर करण्याची मागणी तीव्र</t>
+          <t>Those who speak of Maharashtra 'asmita' should support Radhakrishnan for VP post Fadnavis</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/demand-to-declare-a-wet-drought-due-to-heavy-rains-in-the-state-is-strong/129359/</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom25-mh-governor-ld-fadnavis.html</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Ganesh Naik, Eknath Shinde, Thane, Maharashtra Politics</t>
+          <t>How much rain did Mumbai receive on Monday? Check area-wise list</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/maharashtra/ganesh-naik-eknath-shinde-thane-maharashtra-politics-54-804112</t>
+          <t>https://indianexpress.com/article/cities/mumbai/how-much-rain-did-mumbai-areas-receive-on-monday-check-list-bandra-juhu-chembur-10196732/</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>मराठा सेनापति रघुजी भोंसले की तलवार मुंबई लाई गई, लंदन में हुई नीलामी में महाराष्ट्र सरकार ने हासिल की</t>
+          <t>CM to join Kawad yatra, TV center chowk shut for 5 hours</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>https://samarsaleel.com/%E0%A4%AE%E0%A4%B0%E0%A4%BE%E0%A4%A0%E0%A4%BE-%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A4%BE%E0%A4%AA%E0%A4%A4%E0%A4%BF-%E0%A4%B0%E0%A4%98%E0%A5%81%E0%A4%9C%E0%A5%80-%E0%A4%AD%E0%A5%8B%E0%A4%82%E0%A4%B8/490978</t>
+          <t>https://www.lokmattimes.com/aurangabad/cm-to-join-kawad-yatra-tv-center-chowk-shut-for-5-hours/</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>मराठा सेनापती रघुजी भोसले यांची तलवार मुंबईत आणली, लंडनमध्ये झालेल्या लिलावात महाराष्ट्र सरकारने घेतली</t>
+          <t>Maha govt plans amnesty scheme to recover pending transport fines</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/mumbai-news/maratha-commander-raghuji-bhonsle-s-sword-brought-to-mumbai-125081800027_1.html</t>
+          <t>https://www.socialnews.xyz/2025/08/18/maha-govt-plans-amnesty-scheme-to-recover-pending-transport-fines/</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>MONSOON UPDATE: १५ ते १६ जिल्ह्यांत रेड आणि ऑरेंज अलर्ट; CM DEVENDRA FADNAVIS म्हणाले…</t>
+          <t>चुनाव के बाद होगा महामंडलों का वितरण, महायुति के इच्छुक नेताओं पर प्रदर्शन का दबाव</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/monsoon-update-red-and-orange-alert-in-15-to-16-districts-cm-devendra-fadnavis-said/129346/</t>
+          <t>https://navbharatlive.com/maharashtra/nagpur/distribution-of-maha-mandals-will-happen-after-the-elections-pressure-of-demonstration-on-the-aspiring-leaders-of-mahayuti-1322474.html</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>भाजप आमदाराचा डाव प्रशासनाने हाणून पाडला, आईच्या नावाने बांधलेले अम्मा स्मारक अवैध ठरवून हटवले</t>
+          <t>राज्यात ओला दुष्काळ जाहीर करा, विशेष अधिवेशन बोलवा मुसळधार पावसानंतर शरद पवारांच्या</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/chandrapur-bjp-mla-kishor-jorgewar-faces-setback-as-administration-demolishes-illegal-amma-memorial-construction-as11-rc70</t>
+          <t>https://marathi.abplive.com/news/politics/sharad-pawar-ncp-demands-after-heavy-rains-declaring-a-wet-drought-in-the-state-calling-a-special-session-shashikant-shinde-1377947</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>मनसे कामगार संघटनेच्या अनेक पदाधिका-यांचा भाजपामध्ये प्रवेश</t>
+          <t>Sanjay Shirsat: संजय शिरसाठ पुन्हा अडचणीत, रोहित पवारांचा नवा आरोप, 15 एकर जमिनीचा वाद काय आहे?</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/many-office-bearers-of-mns-workers-organization-join-bjp/</t>
+          <t>https://pudhari.news/maharashtra/mumbai/sanjay-shirsat-land-dispute-rohit-pawar-allegations-mk94</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>सीपी राधाकृष्णन के उपराष्ट्रपति उम्मीदवार बनाने पर कांग्रेस को लगी मिर्ची; INDI ब्लॉक भी जल्द कर सकता है प्रत्याशी का ऐलान</t>
+          <t>सिडको जमिन वाटप प्रकरणावरून राजकारण तापले; पवारांचा शिरसाठांवर घणाघाती हल्ला</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>https://www.sudarshannews.in/news-detail.aspx?id=131383</t>
+          <t>https://civicmirror.in/maharashtra/politics-heats-up-over-cidco-land-allocation-issue-pawar-attacks-shirsath/</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>MMRDA launches SCLR bridge, metro institute and flyovers to ease city commute</t>
+          <t>India News | SC Dismisses Plea Alleging Discrepancies in 2024 Maharashtra Assembly Polls</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>https://propnewstime.com/getdetailsStories/MjA1NTQ=/mmrda-launches-sclr-bridge-metro-institute-and-flyovers-to-ease-city-commute</t>
+          <t>https://www.latestly.com/agency-news/india-news-sc-dismisses-plea-alleging-discrepancies-in-2024-maharashtra-assembly-polls-7065753.html</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>DH Evening Brief | NDA VP pick in Delhi to meet BJP top brass, Opposition yet to finalise their candidate; I.N.D.I.A. bloc continues attacking EC chief over SIR</t>
+          <t>Mumbai Rain LIVE Updates: मुंबईत सखल भागात साचलेल्या पाण्याचा निचरा</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/dh-evening-brief-nda-vp-pick-in-delhi-to-meet-bjp-top-brass-opposition-yet-to-finalise-their-candidate-india-bloc-continues-attacking-ec-chief-over-sir-3685866</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/mumbai-rain-live-updates-18-august-imd-red-alert-in-mumbai-weather-waterlogging-traffic-jam-local-train-train-latest-updates-in-marathi-933169</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
+          <t>'उपराष्ट्रपती'साठी महाराष्ट्राच्या राज्यपालांचे नाव; फडणवीसांचे खासदारांना आवाहन, पवार-ठाकरेंना टोला</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/business/-Third-Mumbai--to-boost-metropolitan-region-development--Fadnavis/2834902</t>
+          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-urges-mps-to-support-radhakrishnan-targets-uddhav-thackeray-and-sharad-pawar-035137.html?ref_source=OI-MR&amp;ref_medium=Home-Page&amp;ref_campaign=News-Cards</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>'Modi Govt Selling Dreams Of 2047, Ignoring Present': Rahul Gandhi Slams Centre After Maharashtra's Thane Train Tragedy</t>
+          <t>मुंबई में कबूतरखानों पर विवाद, महापालिका ने नागरिकों से आपत्तियां और सुझाव मांगे</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/India/modi-govt-selling-dreams-of-2047-ignoring-present-rahul-gandhi-slams-centre-after-maharashtras-thane-train-tragedy/ar-AA1Gm3WY?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://mpbreakingnews.in/maharashtra/mumbai-municipal-corporation-pigeon-shelters-public-consultation-high-court-54-803921</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Rs 40kcr of investors’ money stuck with credit societies, Maharashtra govt to announce SOP for recovery</t>
+          <t>Maharashtra govt plans amnesty scheme to recover pending transport fines</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/rs-40kcr-of-investors-money-stuck-with-credit-societies-maharashtra-govt-to-announce-sop-for-recovery/articleshow/123367502.cms</t>
+          <t>https://auto.economictimes.indiatimes.com/amp/news/industry/maharashtras-new-amnesty-scheme-settle-transport-fines-and-save-big/123364146</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Red alert issued as heavy rain batters Mumbai; schools and colleges closed due to waterlogging</t>
+          <t>Sickle cell patients await BMT as govt scheme, centres yet to take off in Nagpur</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/en/red-alert-issued-as-heavy-rain-batters-mumbai-schools-and-colleges-closed-due-to-waterlogging/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/sickle-cell-patients-await-bmt-as-govt-scheme-centres-yet-to-take-off-in-nagpur/articleshow/123351316.cms</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Maha govt signs MoUs worth Rs 42,000 crore and creation of 28,000 jobs</t>
+          <t>सरकारी नौकरी: इस राज्य में पुलिस के 15 हजार से ज्यादा पदों पर होगी भर्ती, mahapolice.gov.in पर मिलेगा नोटिफ...</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/states-and-uts/maharashtra/maha-govt-signs-mous-worth-rs-42000-crore-and-creation-of-28000-jobs</t>
+          <t>https://hindi.news18.com/news/career/jobs-maharashtra-police-recruitment-2025-notification-for-more-than-15000-vacancy-mahapolice-gov-in-9518146.html</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>NCP (SP) targets Maha minister over Rs 5,000 cr scam in Navi Mumbai’s CIDCO land; demands his resignation</t>
+          <t>Pratap Sarnaik : राज्यातील वाहनांवर तब्‍बल 2500 कोटींचा दंड; सरकार एकरकमी परतफेडीची अभय योजना आणणार</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/ncp-sp-targets-maha-minister-over-rs-5000-cr-scam-navi-mumbai-s-cidco-land-demands-his</t>
+          <t>https://www.dainikprabhat.com/fines-of-around-rs-2500-crore-on-vehicles-in-the-state-government-to-introduce-a-lump-sum-repayment-scheme/</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>पंतप्रधान नरेंद्र मोदी आणि व्लादिमीर पुतीन यांच्यात संवाद - संघर्षाच्या शांततामय तोडग्यासाठी भारताचा ठाम पाठिंबा</t>
+          <t>CJI Gavai: "Maharashtra Govt At Forefront Of Efforts To Provide Infrastructure For Judiciary"</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/dialogue-between-prime-minister-narendra-modi-and-vladimir-putin-indias-strong-support-for-peaceful-resolution.html</t>
+          <t>https://lawchakra.in/legal-updates/cji-gavai-infrastructure-for-judiciary/</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>वैविध्यपूर्ण विषयांवरील पुस्तक प्रकाशित करणे हे चपराकचं साहित्यिक आंदोलन; लेखक अभिराम भडकमकर यांचे प्रतिपादन</t>
+          <t>Maratha general Raghuji Bhonsle's sword brought to Mumbai</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/publishing-books-on-diverse-topics-is-a-literary-movement-of-the-chaparak-author-abhiram-bhadkamkar-asserts.html</t>
+          <t>https://english.metrovaartha.com/news/mumbai/maratha-general-raghuji-bhonsles-sword-brought-to-mumbai</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>ठाण्यात शालेय ९-साईड हॉकी लीगला सुरुवात ; ७६ संघांचा उत्साही सहभाग</t>
+          <t>महाराष्ट्रातील 'या' जिल्ह्यात उभारणार 'स्टॅच्यू ऑफ युनिटी'; सरकारचा काय आहे प्लॅन?</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/school-9-a-side-hockey-league-begins-in-thane-76-teams-participate-enthusiastically.html</t>
+          <t>https://www.tendernama.com/mahatender/paschim-maharashtra/statue-of-unity-style-memorial-in-maharashtra-soon</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Rain fury: 5 missing, 200 stranded in Nanded; local trains, flights hit in Mumbai</t>
+          <t>मराठा सेनापति रघुजी भोंसले की तलवार मुंबई लाई गई</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Rain-fury--5-missing--200-stranded-in-Nanded;-local-trains--flights-hit-in-Mumbai/2832995</t>
+          <t>https://hindi.theprint.in/india/maratha-commander-raghuji-bhosales-sword-brought-to-mumbai/856774/</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Aaj Ka Rashifal, 19 Aug, 2025 : आचार्य इंदु प्रकाश जी से जानिए आज क्या कह रहे हैं आपके सितारे</t>
+          <t>Kolhapur : सरन्यायाधीश Bhushan Gavai यांच्या हस्ते सर्किट बेंच इमारतीचे उद्घाटन</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/bhavishyawani/aaj-ka-rashifal-19-aug-2025-know-from-acharya-indu-prakash-ji-what-your-stars-are-saying-today-2025-08-19-1156865</t>
+          <t>https://www.tarunbharat.com/kolhapur-circuit-bench-inauguration-with-chief-justice-bhushan-gavai-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>सुप्रीम कोर्ट ने महाराष्ट्र विधानसभा चुनाव रद्द करने की मांग वाली याचिका की खारिज, विपक्ष को बड़ा झटका</t>
+          <t>Shashikant Shinde on Heavy Rain: राज्यात अतिवृष्टीमुळे ओला दुष्काळ जाहीर करण्याची मागणी तीव्र</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>https://samacharnama.com/states/maharashtra-news/supreme-court-dismisses-plea-seeking-cancellation-of/cid17260970.htm</t>
+          <t>https://www.timemaharashtra.com/maharashtra/demand-to-declare-a-wet-drought-due-to-heavy-rains-in-the-state-is-strong/129359/</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Vice Presidential Election : उपराष्ट्रपती पदासाठी विरोधकांचा उमेदवार कोण? दिल्लीत घडामोडींना वेग; राहुल गांधी काय भूमिका घेणार?</t>
+          <t>Ganesh Naik, Eknath Shinde, Thane, Maharashtra Politics</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/desh-videsh/who-is-the-opposition-candidate-for-the-post-of-vice-president-events-in-delhi-are-gaining-momentum-what-decision-will-mallikarjun-kharge-take-gkt-96-5313155/</t>
+          <t>https://mpbreakingnews.in/maharashtra/ganesh-naik-eknath-shinde-thane-maharashtra-politics-54-804112</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Maharashtra politics : मुख्यमंत्र्यांच्या पत्नी गायिका, तरीही गाणे गाणाऱ्या तहसीलदारांना शिक्षा? बावनकुळे या चुकीला माफी असायलाच हवी; सामनातून हल्लाबोल</t>
+          <t>मराठा सेनापति रघुजी भोंसले की तलवार मुंबई लाई गई, लंदन में हुई नीलामी में महाराष्ट्र सरकार ने हासिल की</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/nanded-tehsildar-prashant-thorat-suspension-shiv-sena-ubt-criticism-sanjay-raut-devendra-fadnavis-jap93</t>
+          <t>https://samarsaleel.com/%E0%A4%AE%E0%A4%B0%E0%A4%BE%E0%A4%A0%E0%A4%BE-%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A4%BE%E0%A4%AA%E0%A4%A4%E0%A4%BF-%E0%A4%B0%E0%A4%98%E0%A5%81%E0%A4%9C%E0%A5%80-%E0%A4%AD%E0%A5%8B%E0%A4%82%E0%A4%B8/490978</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>हवामानाचा अंदाज: आजही पावसाचा कहर? मुंबई, पुण्यासह 7 जिल्ह्यांना रेड अलर्ट; गडचिरोलीसह 4 जिल्ह्यांना यलो अलर्ट</t>
+          <t>मराठा सेनापती रघुजी भोसले यांची तलवार मुंबईत आणली, लंडनमध्ये झालेल्या लिलावात महाराष्ट्र सरकारने घेतली</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/national-news/maharashtra-weather-red-alert-mumbai-pune-7-districts-281414/amp/</t>
+          <t>https://marathi.webdunia.com/article/mumbai-news/maratha-commander-raghuji-bhonsle-s-sword-brought-to-mumbai-125081800027_1.html</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>पूजेसाठी परवानगी नाही, नमाजसाठी जागाच जागा; कम्युनिस्टांचा हिंदुविरोधी चेहरा पुन्हा समोर</t>
+          <t>MONSOON UPDATE: १५ ते १६ जिल्ह्यांत रेड आणि ऑरेंज अलर्ट; CM DEVENDRA FADNAVIS म्हणाले…</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/no-permission-for-worship-plenty-of-space-for-namaz-cpims-different-rules-for-hindus-and-muslims-in-kerala-the.html</t>
+          <t>https://www.timemaharashtra.com/maharashtra/monsoon-update-red-and-orange-alert-in-15-to-16-districts-cm-devendra-fadnavis-said/129346/</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Will Bajirao Mastani Come Alive in Movie Halls Today?</t>
+          <t>मनसे कामगार संघटनेच्या अनेक पदाधिका-यांचा भाजपामध्ये प्रवेश</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>https://caleidoscope.in/art-culture/will-bajirao-mastani-come-alive-in-movie-halls-today</t>
+          <t>https://www.marathiebatmya.com/political/many-office-bearers-of-mns-workers-organization-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Red alert in Mumbai; BMC shuts all afternoon schools, colleges</t>
+          <t>Ashish Shelar: मुंबईत जोरदार पाऊस! पावसाचा आढावा घेतल्यानंतर मंत्री शेलार म्हणाले, 'अत्यंत गरज असल्यास...'</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>https://www.newsbytesapp.com/news/india/mumbai-rain-havoc-to-continue-for-next-4-days/story</t>
+          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/mumbai-rain-updates-ashish-shelar-reviewed-the-rainfall-and-said-stay-safe-at-home/40069</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Nanded Rain: नांदेड़ में भारी बारिश के बाद 200 लोग बाढ़ में फंसे! बादल फटने से 5 लापता, रेस्क्यू के लिए सेना बुलाई गई</t>
+          <t>सीपी राधाकृष्णन के उपराष्ट्रपति उम्मीदवार बनाने पर कांग्रेस को लगी मिर्ची; INDI ब्लॉक भी जल्द कर सकता है प्रत्याशी का ऐलान</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>https://hindi.moneycontrol.com/india/heavy-rains-in-maharashtra-nanded-leave-over-200-stranded-in-flood-waters-five-people-missing-article-2104052.html</t>
+          <t>https://www.sudarshannews.in/news-detail.aspx?id=131383</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>फडणवीस ने राज्यपाल राधाकृष्णन से मुलाकात की, उन्हें शिवाजी महाराज के पत्रों की पुस्तक भेंट की</t>
+          <t>MMRDA launches SCLR bridge, metro institute and flyovers to ease city commute</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/maharashtra/fadnavis-meets-governor-radhakrishnan-presents-him-with-a-book-containing-shivaji-maharajs-letters-3213010.html</t>
+          <t>https://propnewstime.com/getdetailsStories/MjA1NTQ=/mmrda-launches-sclr-bridge-metro-institute-and-flyovers-to-ease-city-commute</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Maharashtra approves amendments for Dharavi project land transfer</t>
+          <t>उत्तरकाशीतील धारली पूर : पर्वतीय विकासात हवामान धोक्यांचा समावेश करायला लावणारा आरसा</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/maharashtra-approves-amendments-for-dharavi-project-land-transfer/ar-AA1G1ze9</t>
+          <t>https://www.etvbharat.com/mr/!opinion/uttarkashi-floods-show-why-india-must-integrate-climate-risks-into-mountain-development-mhs25081806533</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>What happened in the Trump-Putin meeting? | Chandrashekhar Nene Maha MTB</t>
+          <t>'Modi Govt Selling Dreams Of 2047, Ignoring Present': Rahul Gandhi Slams Centre After Maharashtra's Thane Train Tragedy</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/what-happened-in-the-trump-putin-meeting-chandrashekhar-nene-maha-mtb.html</t>
+          <t>http://www.msn.com/en-in/news/India/modi-govt-selling-dreams-of-2047-ignoring-present-rahul-gandhi-slams-centre-after-maharashtras-thane-train-tragedy/ar-AA1Gm3WY?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>IBM to support Maharashtra in developing quantum computing initiative</t>
+          <t>Sword of Raghuji Bhonsle arrives in Mumbai and will be on display till Aug 25</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>https://www.communicationstoday.co.in/ibm-to-support-maharashtra-in-developing-quantum-computing-initiative/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/sword-of-raghuji-bhonsle-arrives-in-mumbai-and-will-be-on-display-till-aug-25/articleshow/123371745.cms</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Heavy rainfall causes 7 deaths, crop loss in Maharashtra as alerts continue</t>
+          <t>Red alert issued as heavy rain batters Mumbai; schools and colleges closed due to waterlogging</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/heavy-rainfall-causes-7-deaths-crop-loss-in-maharashtra-as-alerts-continue/articleshow/123368187.cms</t>
+          <t>https://ddnews.gov.in/en/red-alert-issued-as-heavy-rain-batters-mumbai-schools-and-colleges-closed-due-to-waterlogging/</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Those who speak of Maharashtra 'asmita' should support Radhakrishnan for VP post Fadnavis</t>
+          <t>Rs 40kcr of investors’ money stuck with credit societies, Maharashtra govt to announce SOP for recovery</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom25-mh-governor-ld-fadnavis.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/rs-40kcr-of-investors-money-stuck-with-credit-societies-maharashtra-govt-to-announce-sop-for-recovery/articleshow/123367502.cms</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Fadnavis meets Guv Radhakrishnan, presents him book of Shivaji Maharaj's letters</t>
+          <t>Maha govt signs MoUs worth Rs 42,000 crore and creation of 28,000 jobs</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/india/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharaj-s-letters/ar-AA1KISQ7</t>
+          <t>https://www.thehawk.in/news/states-and-uts/maharashtra/maha-govt-signs-mous-worth-rs-42000-crore-and-creation-of-28000-jobs</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Third Mumbai in Raigad to become Maharashtra’s new economic powerhouse: CM Fadnavis</t>
+          <t>पंतप्रधान नरेंद्र मोदी आणि व्लादिमीर पुतीन यांच्यात संवाद - संघर्षाच्या शांततामय तोडग्यासाठी भारताचा ठाम पाठिंबा</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>https://www.daijiworld.com/index.php/news/newsDisplay?newsID=1289652</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/dialogue-between-prime-minister-narendra-modi-and-vladimir-putin-indias-strong-support-for-peaceful-resolution.html</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Mumbai rains: Heavy showers flood roads, railway tracks; bring city to standstill - video</t>
+          <t>वैविध्यपूर्ण विषयांवरील पुस्तक प्रकाशित करणे हे चपराकचं साहित्यिक आंदोलन; लेखक अभिराम भडकमकर यांचे प्रतिपादन</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/mumbai-rains-heavy-showers-flood-roads-railway-tracks-bring-city-to-standstill-video/articleshow/123362740.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/publishing-books-on-diverse-topics-is-a-literary-movement-of-the-chaparak-author-abhiram-bhadkamkar-asserts.html</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Maratha general Raghuji Bhonsle's sword brought to Mumbai</t>
+          <t>ठाण्यात शालेय ९-साईड हॉकी लीगला सुरुवात ; ७६ संघांचा उत्साही सहभाग</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/maratha-general-raghuji-bhonsle's-sword-brought-to-mumbai/2833930</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/school-9-a-side-hockey-league-begins-in-thane-76-teams-participate-enthusiastically.html</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Mumbai reels under 177 mm rain in 8 hours; flights hit, schools shut as red alert issued</t>
+          <t>Those who speak of Maharashtra 'asmita' should support Radhakrishnan for VP post: Fadnavis</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Aug/18/mumbai-rains-flight-operations-hit-schools-colleges-shut-as-imd-issues-red-alert</t>
+          <t>https://www.ptinews.com/editor-detail/those-who-speak-of-maharashtra--asmita--should-support-radhakrishnan-for-vp-post--fadnavis/2832772</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Monday mayhem: Mumbai's suburbs recorded over 100 mm rainfall in 12 hours, says IMD</t>
+          <t>Rajanna’s conspiracy claim pits CM supporters against DKS’ camp</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/monday-mayhem:-mumbai's-suburbs-recorded-over-100-mm-rainfall-in-12-hours,-says-imd/2834156</t>
+          <t>https://timesofindia.indiatimes.com/city/bengaluru/rajannas-conspiracy-claim-pits-cm-supporters-against-dks-camp/articleshow/123348301.cms</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Mumbai rains: Torrential downpour cripples normal life; train services hit, roads flooded — see pics</t>
+          <t>Rain fury: 5 missing, 200 stranded in Nanded; local trains, flights hit in Mumbai</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/photos/mumbai-rains-torrential-downpour-cripples-normal-life-train-services-hit-roads-flooded-see-pics-11755525808666.html</t>
+          <t>https://www.ptinews.com/editor-detail/Rain-fury--5-missing--200-stranded-in-Nanded;-local-trains--flights-hit-in-Mumbai/2832995</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Rain fury: 5 missing, 200 stranded in Nanded; local trains, flights hit in Mumbai</t>
+          <t>Industries in Jalgaon should get power at subsidised rate, says Ajit Pawar</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>https://odishatv.in/news/national/rain-fury-5-missing-200-stranded-in-nanded-local-trains-flights-hit-in-mumbai-270189</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/industries-in-jalgaon-should-get-power-at-subsidised-rate-says-ajit-pawar/articleshow/123351430.cms</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Mumbai rains: Heavy rainfall batter city as Vihar lake overflows</t>
+          <t>One held for friend's murder</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-rains-heavy-rainfall-batter-city-as-vihar-lake-overflows-23590062</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/one-held-for-friends-murder/articleshow/123350586.cms</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>IndiGo Airlines issues travel advisory for passengers flying out of Mumbai due to heavy rainfall, waterlogging in the city</t>
+          <t>Congress vows to ‘douse fire’ amid rifts within party</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>https://newsroompost.com/india/indigo-airlines-issues-travel-advisory-for-passengers-flying-out-of-mumbai-due-to-heavy-rainfall-waterlogging-in-the-city/5347388.html</t>
+          <t>https://timesofindia.indiatimes.com/city/hyderabad/congress-vows-to-douse-fire-amid-rifts-within-party/articleshow/123350298.cms</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>मुंबई में भारी बारिश का कहर, 19 अगस्त को बंद रहेंगे सभी स्कूल-कॉलेज</t>
+          <t>Three of seven accused arrested in journalist attack case</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>https://hindi.news24online.com/india/mumbai-and-jammu-kashmir-heavy-rain-rain-school-and-college-closed/1288306/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/three-of-seven-accused-arrested-in-journalist-attack-case/articleshow/123350718.cms</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में भारी बारिश से सात लोगों की मौत, 200 ग्रामीण फंसे</t>
+          <t>Sindh Mukti Sangathan holds Akhand Bharat Sankalp Diwas programme</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AD-%E0%A4%B0-%E0%A4%AC-%E0%A4%B0-%E0%A4%B6-%E0%A4%B8%E0%A5%87-%E0%A4%B8-%E0%A4%A4-%E0%A4%B2-%E0%A4%97-%E0%A4%82-%E0%A4%95-%E0%A4%AE-%E0%A4%A4-200-%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%A3-%E0%A4%AB%E0%A4%82%E0%A4%B8%E0%A5%87/ar-AA1KKl3K</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/sindh-mukti-sangathan-holds-akhand-bharat-sankalp-diwas-programme/articleshow/123350984.cms</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>राज्यात अतिवृष्टीच्या पार्श्वभूमीवर मुख्यमंत्री देवेंद्र फडणवीस यांचे सर्व यंत्रणांना सतर्कतेचे निर्देश</t>
+          <t>Two bangladeshi nationals held for illegal stay</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176121/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/two-bangladeshi-nationals-held-for-illegal-stay/articleshow/123350437.cms</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>लाटा पाहण्याच्या मोहापाई लोक अडचणीत येतात....: तुफान पावसामुळे मुख्यमंत्री फडणवीसांनी केले आवाहन</t>
+          <t>Two more suspects held in Jalaun murder case</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/cm-devendra-fadnavis-live-press-on-mumbai-rain-update-red-alert-963319.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kanpur/two-more-suspects-held-in-jalaun-murder-case/articleshow/123350447.cms</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>‘तिसरी मुंबई’ घडवण्यासाठी महाराष्ट्र शासन कार्यरत</t>
+          <t>Uzbek institute to collaborate with IGKV in agri research</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/-mumbai-maharashtra-government-third-mumbai-devendra-fadnavis-worli-shivdi.html</t>
+          <t>https://timesofindia.indiatimes.com/city/raipur/uzbek-institute-to-collaborate-with-igkv-in-agri-research/articleshow/123350462.cms</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Mumbai Heavy Rain : मुंबईसाठी पुढील 10-12 तास धोक्याचे, मुख्यमंत्री फडणवीसांनी मुंबईकरांना केलं सावध</t>
+          <t>Tehsildar sings at farewell, revenue min suspends him for lack of ‘decorum’</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/heavy-rains-in-mumbai-next-48-hours-are-crucial-chief-minister-devendra-fadnavis-warns-citizens-to-be-alert/913099/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/tehsildar-sings-at-farewell-revenue-min-suspends-him-for-lack-of-decorum/articleshow/123350443.cms</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>मराठ्यांच्या इतिहासाची साक्षीदार; श्रीमंत राजे रघुजी भोसलेंच्या ऐतिहासिक तलवारीचं लोकार्पण, पाहा खास PHOTO</t>
+          <t>Heavy Rains in Nanded: Rescue operations on as 5 go missing, 225 trapped in floodwaters</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/photogallery/news/raghuji-bhosale-sword-inauguration-in-mumbai-by-cm-devendra-fadnavis/photoshow/123367923.cms</t>
+          <t>https://udayavani.com/national/heavy-rains-in-nanded-rescue-operations-on-as-5-go-missing-225-trapped-in-floodwaters-20250818T093308478Z?lang=en</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Mumbai Rain: मुंबईत उद्या शाळांना सुट्टी? पुढचे १२ तास महत्वाचे, मुख्यमंत्री नेमकं काय म्हणाले?</t>
+          <t>Yoga With Swami Ramdev : 63 करोड़ लोगों को स्पाइनल इंजरी..कैसे होगी सर्वाइकल, साइटिका की छुट्टी?</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/mumbai-pune/mumbai-rain-alert-cm-devendra-fadnavis-said-mumbai-schools-declared-holiday-on-tomorrow-bmc-to-decide-pvm91</t>
+          <t>https://www.indiatv.in/video/yoga/yoga-with-swami-ramdev-63-crore-people-have-spinal-injuries-how-will-cervical-and-sciatica-be-cured-2025-08-18-1156639</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Maharashtra Rains: राज्यात अतिवृष्टी, 7 जणांचा मृत्यू; मुख्यमंत्र्यांचे सर्व यंत्रणांना सतर्कतेचे निर्देश Maharashtra Rains: Heavy rains in the state, 7 people died; CM Devendra Fadnavis directs all agencies to be alert</t>
+          <t>Mumbai Rains: भारी बारिश का कहर, 7 की मौत, आदित्य ठाकरे ने BMC पर लगाए आरोप</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-rains-heavy-rains-in-the-state-7-people-died-cm-devendra-fadnavis-directs-all-agencies-to-be-alert-89603</t>
+          <t>https://www.thesandeshwahak.com/mumbai-rains-heavy-rain-wreaks-havoc-7-dead-aditya-thackeray-blames-bmc/</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>श्रीमंत राजे रघूजी भोसले यांची ऐतिहासिक तलवार उद्या मुंबईत दाखल</t>
+          <t>Vice Presidential Election : उपराष्ट्रपती पदासाठी विरोधकांचा उमेदवार कोण? दिल्लीत घडामोडींना वेग; राहुल गांधी काय भूमिका घेणार?</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176009/</t>
+          <t>https://www.loksatta.com/desh-videsh/who-is-the-opposition-candidate-for-the-post-of-vice-president-events-in-delhi-are-gaining-momentum-what-decision-will-mallikarjun-kharge-take-gkt-96-5313155/</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>LIVE Update : मुंबईतील सर्व शाळांना उद्या सुट्टी जाहीर</t>
+          <t>Maharashtra politics : मुख्यमंत्र्यांच्या पत्नी गायिका, तरीही गाणे गाणाऱ्या तहसीलदारांना शिक्षा? बावनकुळे या चुकीला माफी असायलाच हवी; सामनातून हल्लाबोल</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/live-update-mumbai-rain-best-co-operative-soc-election-live-maharashtra-update-political-rain-update-devendra-fadnavis-ajit-pawar-eknath-shinde-uddhav-thackeray-raj-thackeray/913004/</t>
+          <t>https://sarkarnama.esakal.com/mumbai/nanded-tehsildar-prashant-thorat-suspension-shiv-sena-ubt-criticism-sanjay-raut-devendra-fadnavis-jap93</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>CM Devendra Fadnavis : हिंदवी स्वराज्याचा इतिहास नवीन पिढीपर्यंत पोहोचेल; श्रीमंत राजे रघुजी भोसले यांच्या तलवारीचे स्वागत</t>
+          <t>पूजेसाठी परवानगी नाही, नमाजसाठी जागाच जागा; कम्युनिस्टांचा हिंदुविरोधी चेहरा पुन्हा समोर</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/legacy-of-hindavi-swarajya-rajarshi-raghuji-bhosales-sword-welcomed-history-cm-devendra-fadnavis-pjp78</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/no-permission-for-worship-plenty-of-space-for-namaz-cpims-different-rules-for-hindus-and-muslims-in-kerala-the.html</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>मुंबईत पुढील आठ ते दहा तासांसाठी रेड अलर्ट, महत्त्वाचे काम असल्यास घराबाहेर पडण्याचे मुख्यमंत्री फडणवीस यांचे आवाहन</t>
+          <t>Will Bajirao Mastani Come Alive in Movie Halls Today?</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/in-mumbai-people-have-been-told-to-step-out-only-if-it-is-needed-says-cm-devendra-fadnavis/</t>
+          <t>https://caleidoscope.in/art-culture/will-bajirao-mastani-come-alive-in-movie-halls-today</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Maharashtra Rain: राज्यात पावसाचा हाहाकार! १६ जिल्ह्यांना रेड- ऑरेंज अलर्ट, मुख्यमंत्र्यांकडून सतर्क राहण्याचे आवाहन</t>
+          <t>Controversy mars trailer launch of ‘Bengal Files’</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/mumbai-pune/maharashtra-floods-cm-fadnavis-reviews-situation-ndrf-and-army-deployed-16-districts-on-red-alert-latest-news-pvm91</t>
+          <t>https://timesofindia.indiatimes.com/city/kolkata/controversy-mars-trailer-launch-of-bengal-files/articleshow/123339117.cms</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>मुख्यमंत्री वैद्यकीय सहाय्यता निधीच्या पुढाकाराने चिमुकल्या देवांशीवर यशस्वी शस्त्रक्रिया</t>
+          <t>Red alert in Mumbai; BMC shuts all afternoon schools, colleges</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176143/</t>
+          <t>https://www.newsbytesapp.com/news/india/mumbai-rain-havoc-to-continue-for-next-4-days/story</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Mumbai Rain Update : मुंबईत धो-धो! वाहतुकीचा खोळंबा, लोकलसेवेला फटका; मुंबईकरांची पुरती दैना; पुढील 48 तासही धोक्याचे</t>
+          <t>Mumbai Rains: मुंबई में भारी बारिश से 12 लोगों की मौत, जगह-जगह कमर तक भरा पानी, स्कूल-कॉलेज बंद, फ्लाइट्स पर भी असर</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-rain-update-heavy-rainfall-started-in-city-resulted-in-disruption-of-life-and-mumbai-local-cm-fadnavis-reviewed/articleshow/123363662.cms</t>
+          <t>https://lalluram.com/mumbai-rains-7-people-died-due-to-rain-water-flooded-on-roads-schools-and-colleges-closed-flights-also-affected/</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Ashish Shelar : मुंबईत मुसळधार.. परिस्थितीचा आढावा घेतल्यानंतर शेलारांकडून मुंबईकरांना एकच आवाहन; आज,...</t>
+          <t>Nanded Rain: नांदेड़ में भारी बारिश के बाद 200 लोग बाढ़ में फंसे! बादल फटने से 5 लापता, रेस्क्यू के लिए सेना बुलाई गई</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/ashish-shelar-appeals-to-mumbaikars-after-review-of-rains-at-bmc-stay-at-house-during-mumbai-heavy-rains-1472440.html</t>
+          <t>https://hindi.moneycontrol.com/india/heavy-rains-in-maharashtra-nanded-leave-over-200-stranded-in-flood-waters-five-people-missing-article-2104052.html</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Maharashtra BIG Decisions : घरांपासून नोकऱ्यांपर्यंत… महाराष्ट्राचे दमदार महानिर्णय, हा व्हिडीओ...</t>
+          <t>फडणवीस ने राज्यपाल राधाकृष्णन से मुलाकात की, उन्हें शिवाजी महाराज के पत्रों की पुस्तक भेंट की</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/maharashtras-major-decisions-police-recruitment-housing-projects-and-historical-artefact-return-1472726.html</t>
+          <t>https://hindi.theprint.in/india/fadnavis-met-governor-radhakrishnan-presented-him-a-book-of-letters-of-shivaji-maharaj/856681/</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>तिसरी MUMBAI आर्थिक विकासाचा नवा अध्याय, गोल्डमन सॅक्सच्या नव्या मुंबई कार्यालयाचे उद्घाटन</t>
+          <t>IBM to support Maharashtra in developing quantum computing initiative</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/mumbai/third-mumbai-a-new-chapter-in-economic-development-goldman-sachs-new-mumbai-office-inaugurated/129385/</t>
+          <t>https://www.communicationstoday.co.in/ibm-to-support-maharashtra-in-developing-quantum-computing-initiative/</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Mumbai Rain : मुख्यमंत्री फडणवीस ॲक्शन मोडमध्ये! राज्यभरात पडत असलेल्या पावसामुळे प्रशासन अलर्ट</t>
+          <t>Heavy rainfall causes 7 deaths, crop loss in Maharashtra as alerts continue</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/mumbai-rain-cm-devendra-fadnavis-in-action-mode-administration-alert-due-to-rains-falling-across-the-state/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/heavy-rainfall-causes-7-deaths-crop-loss-in-maharashtra-as-alerts-continue/articleshow/123368187.cms</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>राज्यात अतिवृष्टीच्या पार्श्वभूमीवर CM DEVENDRA FADNAVIS यांचे सर्व यंत्रणांना सतर्कतेचे निर्देश</t>
+          <t>NDA’s Vice President nominee CP Radhakrishnan to reach Delhi today: sources</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/cm-devendra-fadnavis-instructs-all-agencies-to-be-alert-in-the-wake-of-heavy-rains-in-the-state/129378/</t>
+          <t>https://www.thestatesman.com/india/ndas-vice-president-nominee-cp-radhakrishnan-to-reach-delhi-today-sources-1503472953.html</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>'Third Mumbai' to boost metropolitan region development Fadnavis</t>
+          <t>Third Mumbai in Raigad to become Maharashtra’s new economic powerhouse: CM Fadnavis</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/business/2025/08/19/bom3-mh-third-mumbai-cm.html</t>
+          <t>https://www.daijiworld.com/index.php/news/newsDisplay?newsID=1289652</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Transformative Leadership: Sukhraj Nahar Steers CREDAI-MCHI Towards Urban Revolution</t>
+          <t>Mumbai rains: Heavy showers flood roads, railway tracks; bring city to standstill - video</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3545330-transformative-leadership-sukhraj-nahar-steers-credai-mchi-towards-urban-revolution</t>
+          <t>https://timesofindia.indiatimes.com/india/mumbai-rains-heavy-showers-flood-roads-railway-tracks-bring-city-to-standstill-video/articleshow/123362740.cms</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>The perks and costs of ‘Ladki Bahin’</t>
+          <t>Maratha general Raghuji Bhonsle's sword brought to Mumbai</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/the-perks-and-costs-of-ladki-bahin-101755575344332.html</t>
+          <t>https://www.ptinews.com/story/national/maratha-general-raghuji-bhonsle's-sword-brought-to-mumbai/2833930</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>LGEC 2025: 'लाडकी बहीण' योजनेमुळे महाराष्ट्रातील अर्थव्यवस्थेला चालनाच मिळाली; सुनील तटकरेंनी समजावलं 'गणित'</t>
+          <t>Mumbai reels under 177 mm rain in 8 hours; flights hit, schools shut as red alert issued</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/international/lgec-2025-ladki-bahin-scheme-has-given-a-boost-to-the-economy-of-maharashtra-sunil-tatkare-rahul-narvekar-explained-a-a629/</t>
+          <t>https://www.newindianexpress.com/nation/2025/Aug/18/mumbai-rains-flight-operations-hit-schools-colleges-shut-as-imd-issues-red-alert</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>महाराष्ट्र के नांदेड़ जिले में मूसलाधार बारिश से आई बाढ़ में 225 नागरिक फंसे,बचाव कार्य जारी</t>
+          <t>Mumbai rains: Torrential downpour cripples normal life; train services hit, roads flooded — see pics</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/8/18/nanded-flood-resues-continew.html</t>
+          <t>https://www.livemint.com/photos/mumbai-rains-torrential-downpour-cripples-normal-life-train-services-hit-roads-flooded-see-pics-11755525808666.html</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में भारी बारिश से सात लोगों की मौत, 200 ग्रामीण फंसे</t>
+          <t>Rain fury: 5 missing, 200 stranded in Nanded; local trains, flights hit in Mumbai</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/seven-people-died-due-to-heavy-rains-in-maharashtra-200-villagers-stranded/856903/</t>
+          <t>https://odishatv.in/news/national/rain-fury-5-missing-200-stranded-in-nanded-local-trains-flights-hit-in-mumbai-270189</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>Mumbai Rains: भारी बारिश का कहर, 7 की मौत, आदित्य ठाकरे ने BMC पर लगाए आरोप</t>
+          <t>Mumbai rains: Heavy rainfall batter city as Vihar lake overflows</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>https://www.thesandeshwahak.com/mumbai-rains-heavy-rain-wreaks-havoc-7-dead-aditya-thackeray-blames-bmc/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-rains-heavy-rainfall-batter-city-as-vihar-lake-overflows-23590062</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>रमेश बिधूड़ी ने राधाकृष्णन को दी शुभकामनाएं, कहा- 'अच्छे उपराष्ट्रपति साबित होंगे'</t>
+          <t>'Third Mumbai' Will Open A New Chapter Of Economic Development: Maha CM</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/delhi-ncr/delhi-news/news-ramesh-bidhuri-congratulated-radhakrishnan-said---he-will-prove-to-be-a-good-vice-president-news-hindi-1-745268-KKN.html</t>
+          <t>https://menafn.com/1109941619/Third-Mumbai-Will-Open-A-New-Chapter-Of-Economic-Development-Maha-CM</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>18.08.2025 : मुख्यमंत्री व सांस्कृतिक कार्य मंत्री यांनी घेतली राज्यपालांची भेट | राजभवन महाराष्ट्र | भारत</t>
+          <t>IndiGo Airlines issues travel advisory for passengers flying out of Mumbai due to heavy rainfall, waterlogging in the city</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>https://rajbhavan-maharashtra.gov.in/gallery/18-08-2025-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%B5-%E0%A4%B8%E0%A4%BE%E0%A4%82%E0%A4%B8%E0%A5%8D%E0%A4%95%E0%A5%83%E0%A4%A4/</t>
+          <t>https://newsroompost.com/india/indigo-airlines-issues-travel-advisory-for-passengers-flying-out-of-mumbai-due-to-heavy-rainfall-waterlogging-in-the-city/5347388.html</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>18.08.2025 : मुख्यमंत्री देवेंद्र फडणवीस व सांस्कृतिक कार्य मंत्री आशिष शेलार यांनी घेतली राज्यपालांची भेट</t>
+          <t>मुंबई में भारी बारिश का कहर, 19 अगस्त को बंद रहेंगे सभी स्कूल-कॉलेज</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>https://rajbhavan-maharashtra.gov.in/18-08-2025-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB/</t>
+          <t>https://hindi.news24online.com/india/mumbai-and-jammu-kashmir-heavy-rain-rain-school-and-college-closed/1288306/</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Cabinet sends back note regarding GMR with multiple queries</t>
+          <t>राज्यात अतिवृष्टीच्या पार्श्वभूमीवर मुख्यमंत्री देवेंद्र फडणवीस यांचे सर्व यंत्रणांना सतर्कतेचे निर्देश</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/18/cabinet-sends-back-note-regarding-gmr-with-multiple-queries.html</t>
+          <t>https://mahasamvad.in/176121/</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Rain wreaks havoc in Maharashtra, brings Mumbai to a standstill</t>
+          <t>लाटा पाहण्याच्या मोहापाई लोक अडचणीत येतात....: तुफान पावसामुळे मुख्यमंत्री फडणवीसांनी केले आवाहन</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/rain-wreaks-havoc-in-maharashtra-brings-mumbai-to-a-standstill/article69948564.ece</t>
+          <t>https://www.navarashtra.com/maharashtra/cm-devendra-fadnavis-live-press-on-mumbai-rain-update-red-alert-963319.html</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Mumbai rains: BMC announces holiday for schools, colleges on August 19</t>
+          <t>‘तिसरी मुंबई’ घडवण्यासाठी महाराष्ट्र शासन कार्यरत</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>https://www.cnbctv18.com/india/are-mumbai-schools-colleges-open-or-close-on-august-19-19655564.htm</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/-mumbai-maharashtra-government-third-mumbai-devendra-fadnavis-worli-shivdi.html</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>India monsoon updates: Heavy to very heavy rainfall at few places in Mumbai; residents told to ‘avoid unnecessary travel’</t>
+          <t>18.08.2025 : मुख्यमंत्री देवेंद्र फडणवीस व सांस्कृतिक कार्य मंत्री आशिष शेलार यांनी घेतली राज्यपालांची भेट</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/india-monsoon-live-mumbai-rains-yamuna-river-flood-alert-delhi-kashmir-cloudburst-updates-august-18/article69946105.ece</t>
+          <t>https://rajbhavan-maharashtra.gov.in/18-08-2025-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB/</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Maharashtra govt plans amnesty scheme to recover pending transport fines</t>
+          <t>Third Mumbai: महाराष्ट्राच्या विकासाचे नवे ग्रोथ सेंटर! काय म्हणाले CM फडणवीस?</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>https://auto.economictimes.indiatimes.com/news/industry/maharashtras-new-amnesty-scheme-settle-transport-fines-and-save-big/123364146</t>
+          <t>https://www.tendernama.com/tender-news/third-mumbai-new-growth-center-for-maharashtras-development-what-did-cm-fadnavis-say</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>Mumbai Rains Live News: Torrential rains cripple Mumbai; roads flooded, local trains delayed and schools, colleges closed amid ‘Red’ alert</t>
+          <t>Mumbai Heavy Rain : मुंबईसाठी पुढील 10-12 तास धोक्याचे, मुख्यमंत्री फडणवीसांनी मुंबईकरांना केलं सावध</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>https://www.thehindubusinessline.com/news/mumbai-weather-mumbai-rains-live-news-updates/article69946123.ece</t>
+          <t>https://www.mymahanagar.com/maharashtra/heavy-rains-in-mumbai-next-48-hours-are-crucial-chief-minister-devendra-fadnavis-warns-citizens-to-be-alert/913099/</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>School Holiday: Schools in Mumbai, Thane to remain closed on Tuesday amid IMD's Red Alert for heavy rains</t>
+          <t>Maharashtra Rains: राज्यात अतिवृष्टी, 7 जणांचा मृत्यू; मुख्यमंत्र्यांचे सर्व यंत्रणांना सतर्कतेचे निर्देश Maharashtra Rains: Heavy rains in the state, 7 people died; CM Devendra Fadnavis directs all agencies to be alert</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/news/india/school-holiday-schools-in-mumbai-thane-to-remain-closed-on-tuesday-amid-imds-red-alert-for-heavy-rains-11755527340477.html</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-rains-heavy-rains-in-the-state-7-people-died-cm-devendra-fadnavis-directs-all-agencies-to-be-alert-89603</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Pune Can Get Underground Road Network To Beat Traffic Woes</t>
+          <t>श्रीमंत राजे रघूजी भोसले यांची ऐतिहासिक तलवार उद्या मुंबईत दाखल</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>https://trak.in/stories/pune-can-get-underground-road-network-to-beat-traffic-woes/</t>
+          <t>https://mahasamvad.in/176009/</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>Rainfall Alert: All schools and colleges closed due to heavy rains, IMD issued red alert</t>
+          <t>मराठ्यांच्या इतिहासाची साक्षीदार; श्रीमंत राजे रघुजी भोसलेंच्या ऐतिहासिक तलवारीचं लोकार्पण, पाहा खास PHOTO</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>https://www.informalnewz.com/rainfall-alert-all-schools-and-colleges-closed-due-to-heavy-rains-imd-issued-red-alert/</t>
+          <t>https://marathi.indiatimes.com/photogallery/news/raghuji-bhosale-sword-inauguration-in-mumbai-by-cm-devendra-fadnavis/photoshow/123367923.cms</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>'मराठी'कडं दुर्लक्ष भोवणार; शासकीय, निमशासकीय कार्यालयांमधील अधिकाऱ्यांवर थेट न्यायिक कारवाई होणार</t>
+          <t>मुंबईत पुढील आठ ते दहा तासांसाठी रेड अलर्ट, महत्त्वाचे काम असल्यास घराबाहेर पडण्याचे मुख्यमंत्री फडणवीस यांचे आवाहन</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/penal-action-will-be-taken-against-those-who-ignore-the-marathi-language-in-government-and-semi-government-offices-in-maharashtra-maharashtra-news-mhs25081803599</t>
+          <t>https://www.saamana.com/in-mumbai-people-have-been-told-to-step-out-only-if-it-is-needed-says-cm-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>अतिवृष्टीमुळे होणाऱ्या नुकसानीचे तातडीने पंचनामे करा; मंत्री मकरंद जाधव-पाटील यांचे निर्देश</t>
+          <t>Maharashtra Rain: राज्यात पावसाचा हाहाकार! १६ जिल्ह्यांना रेड- ऑरेंज अलर्ट, मुख्यमंत्र्यांकडून सतर्क राहण्याचे आवाहन</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/immediately-conduct-a-panchnama-of-the-damage-caused-by-heavy-rains-minister-makarand-jadhav-patil-directs.html</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/maharashtra-floods-cm-fadnavis-reviews-situation-ndrf-and-army-deployed-16-districts-on-red-alert-latest-news-pvm91</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>सामाजिक कामात कार्यरत राहून मिळणारा आनंद मोठा: पांडुरंग चोरमले</t>
+          <t>Mumbai Rain Update : मुंबईत धो-धो! वाहतुकीचा खोळंबा, लोकलसेवेला फटका; मुंबईकरांची पुरती दैना; पुढील 48 तासही धोक्याचे</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/the-joy-of-working-in-social-work-is-immense-pandurang-chormale.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-rain-update-heavy-rainfall-started-in-city-resulted-in-disruption-of-life-and-mumbai-local-cm-fadnavis-reviewed/articleshow/123363662.cms</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>मराठी चित्रपटसृष्टीत भव्यतेचं नवं पर्व घेऊन येणाऱ्या ‘दशावतार’ चित्रपटाचं जबरदस्त ट्रेलर प्रदर्शित</t>
+          <t>Maharashtra BIG Decisions : घरांपासून नोकऱ्यांपर्यंत… महाराष्ट्राचे दमदार महानिर्णय, हा व्हिडीओ...</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!entertainment/trailer-of-the-film-dashavatar-which-brings-a-new-era-of-grandeur-to-marathi-cinema-is-released-maharashtra-news-mhs25081901382</t>
+          <t>https://www.tv9marathi.com/videos/maharashtras-major-decisions-police-recruitment-housing-projects-and-historical-artefact-return-1472726.html</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>शाळा अंतर्गत फेरीमध्ये विद्यार्थ्यांचा सत्कार सोहळा</t>
+          <t>रघुजीराजे भोसले यांची तलवार मुंबईत शौर्याचा वारसा इतिहाप्रेमींसाठी खुला; मराठा साम्राज्याचा वारसा परत मिळवण्याचा प्रयत्न – मुख्यमंत्री</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/student-felicitation-ceremony-during-the-schools-internal-parade.html</t>
+          <t>https://www.saamana.com/raghujiraje-bhosale-sword-a-legacy-of-bravery-is-open-to-history-lovers-in-mumbai-an-attempt-to-reclaim-the-legacy-of-the-maratha-empire-said-by-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Mumbai Rain Update: मुंबईत पुढील चार तास धो-धो, रेड अलर्ट जारी, लोकल ट्रेन उशिराने, नागरिकांना घराबाहेर न पडण्याचं आवाहन</t>
+          <t>तिसरी MUMBAI आर्थिक विकासाचा नवा अध्याय, गोल्डमन सॅक्सच्या नव्या मुंबई कार्यालयाचे उद्घाटन</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-heavy-rain-expected-by-imd-red-alert-heavy-rainfall-local-train-updates/articleshow/123376293.cms</t>
+          <t>https://www.timemaharashtra.com/maharashtra/mumbai/third-mumbai-a-new-chapter-in-economic-development-goldman-sachs-new-mumbai-office-inaugurated/129385/</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>Maharashtra Rain Update: 19 ऑगस्टलाही सावधान..., महाराष्ट्रातील 'या' जिल्ह्यांना रेड अलर्ट</t>
+          <t>राज्यात अतिवृष्टीच्या पार्श्वभूमीवर CM DEVENDRA FADNAVIS यांचे सर्व यंत्रणांना सतर्कतेचे निर्देश</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/mahrashtra-mumbai-rain-latest-update-orange-alert-till-august-20-red-alert-issued-in-several-districts-963438.html</t>
+          <t>https://www.timemaharashtra.com/maharashtra/cm-devendra-fadnavis-instructs-all-agencies-to-be-alert-in-the-wake-of-heavy-rains-in-the-state/129378/</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>रत्नागिरीत मुसळधार पावसानं हाहाकार: शाळा महाविद्यालयाला सुटी</t>
+          <t>'Third Mumbai' to boost metropolitan region development Fadnavis</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/holiday-for-schools-and-colleges-in-ratnagiri-due-to-heavy-rain-ratnagiri-district-administration-decision-orange-alert-weather-forecast-maharashtra-news-mhs25081806850</t>
+          <t>https://www.theweek.in/wire-updates/business/2025/08/19/bom3-mh-third-mumbai-cm.html</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>रायगड जिल्हा मुसळधार पावसानं झोडपला; सावित्री नदीचं पाणी महाड शहरात शिरलं</t>
+          <t>The perks and costs of ‘Ladki Bahin’</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/heavy-rain-in-raigad-district-savitri-river-flood-landslide-in-mangaon-maharashtra-news-mhs25081804820</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/the-perks-and-costs-of-ladki-bahin-101755575344332.html</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>मंत्री संजय शिरसाट यांच्याकडून अधिकारांचा गैरवापर; 5 हजार कोटींचा गोलमाल झाल्याचा रोहित पवारांचा आरोप</t>
+          <t>LGEC 2025: 'लाडकी बहीण' योजनेमुळे महाराष्ट्रातील अर्थव्यवस्थेला चालनाच मिळाली; सुनील तटकरेंनी समजावलं 'गणित'</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/minister-sanjay-shirsat-misuses-powers-rohit-pawar-alleges-rs-5000-crore-scam-mumbai-maharashtra-news-mhs25081804077</t>
+          <t>https://www.lokmat.com/international/lgec-2025-ladki-bahin-scheme-has-given-a-boost-to-the-economy-of-maharashtra-sunil-tatkare-rahul-narvekar-explained-a-a629/</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>Maharashtra on high alert as heavy rain leaves 6 dead</t>
+          <t>ShivBhojan Thali News: शिवभोजन थाळी योजना संकटात: करोडो रुपयांची बिलं राज्य शासनाने थकवली, केंद्र चालक आंदोलनाच्या पावित्र्यात</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/maharashtra-on-high-alert-as-heavy-rain-leaves-6-dead/articleshow/123371509.cms</t>
+          <t>https://pudhari.news/maharashtra/mumbai/shiv-bhojan-thali-scheme-crisis-maharashtra-government-pending-bills-protest-mk94</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Mumbai continues to be on red alert; heavy rain disrupts travel, shuts offices &amp; educational institutions</t>
+          <t>Rajnath reaches out to DMK, TMC, BJD for consensus on VP nominee</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/weather/mumbai-on-red-alert-for-second-consecutive-day-heavy-rain-disrupts-travel-shuts-educational-institutions/articleshow/123375296.cms</t>
+          <t>https://www.msn.com/en-in/news/other/rajnath-reaches-out-to-dmk-tmc-bjd-for-consensus-on-vp-nominee/ar-AA1KKGcl</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
+          <t>Clean image and cordial relations with netas across political parties paves Maharashtra governor CP Radha</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/clean-image-and-cordial-relations-with-netas-across-political-parties-paves-maharashtra-governor-cp-radhakrishnans-path-to-vice-presidents-office/articleshow/123350030.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>803 Families Stranded as Lokmanya Nagar Redevelopment Hits Political Roadblock</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>https://punemirror.com/city/civic/803-families-stranded-as-lokmanya-nagar-redevelopment-hits-political-roadblock/</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>महाराष्ट्र के नांदेड़ जिले में मूसलाधार बारिश से आई बाढ़ में 225 नागरिक फंसे,बचाव कार्य जारी</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>https://www.yugwarta.com/Encyc/2025/8/18/nanded-flood-resues-continew.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>मानसून में हाल बेहाल, भारी बारिश से इस राज्य में जगह-जगह भरा पानी, स्कूल-कॉलेज किए बंद</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>https://www.patrika.com/national-news/heavy-rain-alert-in-mumbai-monsoon-gained-momentum-know-imd-weather-update-19874723</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>महाराष्ट्र में भारी बारिश से सात लोगों की मौत, 200 ग्रामीण फंसे</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>https://hindi.theprint.in/india/seven-people-died-due-to-heavy-rains-in-maharashtra-200-villagers-stranded/856903/</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>रमेश बिधूड़ी ने राधाकृष्णन को दी शुभकामनाएं, कहा- 'अच्छे उपराष्ट्रपति साबित होंगे'</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>https://www.khaskhabar.com/local/delhi-ncr/delhi-news/news-ramesh-bidhuri-congratulated-radhakrishnan-said---he-will-prove-to-be-a-good-vice-president-news-hindi-1-745268-KKN.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>18.08.2025 : मुख्यमंत्री व सांस्कृतिक कार्य मंत्री यांनी घेतली राज्यपालांची भेट | राजभवन महाराष्ट्र | भारत</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>https://rajbhavan-maharashtra.gov.in/gallery/18-08-2025-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%B5-%E0%A4%B8%E0%A4%BE%E0%A4%82%E0%A4%B8%E0%A5%8D%E0%A4%95%E0%A5%83%E0%A4%A4/</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>Rain wreaks havoc in Maharashtra, brings Mumbai to a standstill</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/maharashtra/rain-wreaks-havoc-in-maharashtra-brings-mumbai-to-a-standstill/article69948564.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>Mumbai rains: BMC announces holiday for schools, colleges on August 19</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>https://www.cnbctv18.com/india/are-mumbai-schools-colleges-open-or-close-on-august-19-19655564.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>India monsoon updates: Heavy to very heavy rainfall at few places in Mumbai; residents told to ‘avoid unnecessary travel’</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/india-monsoon-live-mumbai-rains-yamuna-river-flood-alert-delhi-kashmir-cloudburst-updates-august-18/article69946105.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>Maharashtra rain fury: Seven dead, crops damaged; Mumbai, Thane, other districts on red alert</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>https://www.newindianexpress.com/nation/2025/Aug/18/maharashtra-rain-fury-seven-dead-crops-damaged-mumbai-thane-other-districts-on-red-alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>Mumbai Rains Live News: Torrential rains cripple Mumbai; roads flooded, local trains delayed and schools, colleges closed amid ‘Red’ alert</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>https://www.thehindubusinessline.com/news/mumbai-weather-mumbai-rains-live-news-updates/article69946123.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>School Holiday: Schools in Mumbai, Thane to remain closed on Tuesday amid IMD's Red Alert for heavy rains</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>https://www.livemint.com/news/india/school-holiday-schools-in-mumbai-thane-to-remain-closed-on-tuesday-amid-imds-red-alert-for-heavy-rains-11755527340477.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>Pune Can Get Underground Road Network To Beat Traffic Woes</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>https://trak.in/stories/pune-can-get-underground-road-network-to-beat-traffic-woes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>Rainfall Alert: All schools and colleges closed due to heavy rains, IMD issued red alert</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>https://www.informalnewz.com/rainfall-alert-all-schools-and-colleges-closed-due-to-heavy-rains-imd-issued-red-alert/</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>'मराठी'कडं दुर्लक्ष भोवणार; शासकीय, निमशासकीय कार्यालयांमधील अधिकाऱ्यांवर थेट न्यायिक कारवाई होणार</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/mr/!state/penal-action-will-be-taken-against-those-who-ignore-the-marathi-language-in-government-and-semi-government-offices-in-maharashtra-maharashtra-news-mhs25081803599</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>सामाजिक कामात कार्यरत राहून मिळणारा आनंद मोठा: पांडुरंग चोरमले</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/the-joy-of-working-in-social-work-is-immense-pandurang-chormale.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>मराठी चित्रपटसृष्टीत भव्यतेचं नवं पर्व घेऊन येणाऱ्या ‘दशावतार’ चित्रपटाचं जबरदस्त ट्रेलर प्रदर्शित</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/mr/!entertainment/trailer-of-the-film-dashavatar-which-brings-a-new-era-of-grandeur-to-marathi-cinema-is-released-maharashtra-news-mhs25081901382</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>शाळा अंतर्गत फेरीमध्ये विद्यार्थ्यांचा सत्कार सोहळा</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/student-felicitation-ceremony-during-the-schools-internal-parade.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>Mumbai Rain Update: मुंबईत पुढील चार तास धो-धो, रेड अलर्ट जारी, लोकल ट्रेन उशिराने, नागरिकांना घराबाहेर न पडण्याचं आवाहन</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-heavy-rain-expected-by-imd-red-alert-heavy-rainfall-local-train-updates/articleshow/123376293.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>Maharashtra Rain Update: 19 ऑगस्टलाही सावधान..., महाराष्ट्रातील 'या' जिल्ह्यांना रेड अलर्ट</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>https://www.navarashtra.com/maharashtra/mahrashtra-mumbai-rain-latest-update-orange-alert-till-august-20-red-alert-issued-in-several-districts-963438.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>रत्नागिरीत मुसळधार पावसानं हाहाकार: शाळा महाविद्यालयाला सुटी</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/mr/!state/holiday-for-schools-and-colleges-in-ratnagiri-due-to-heavy-rain-ratnagiri-district-administration-decision-orange-alert-weather-forecast-maharashtra-news-mhs25081806850</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>रायगड जिल्हा मुसळधार पावसानं झोडपला; सावित्री नदीचं पाणी महाड शहरात शिरलं</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/mr/!state/heavy-rain-in-raigad-district-savitri-river-flood-landslide-in-mangaon-maharashtra-news-mhs25081804820</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>मुखेड तालुक्यात ढगफुटी सदृश्य पाऊस; लेंडी धरणाचं पाणी शिरलं गावात, एसडीआरएफ पथकाकडून मदत कार्य सुरू</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/mr/!state/nanded-rain-update-cloudburst-and-heavy-rain-in-lendi-dam-mukhed-in-nanded-maharashtra-news-mhs25081802339</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>राज्यात पावसाचा हाहाकार! मुख्यमंत्री फडणवीस अॅक्टीव्ह मोडवर, सतर्क राहण्याचे आवाहन</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>https://civicmirror.in/maharashtra/maharashtra-rain-cm-fadnavis-reviews-situation-16-districts-on-red-alert/</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>FIR policy leads to 60% drop in city’s drunk driving cases</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/fir-policy-leads-to-60-drop-in-citys-drunk-driving-cases/articleshow/123351105.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>मंत्री संजय शिरसाट यांच्याकडून अधिकारांचा गैरवापर; 5 हजार कोटींचा गोलमाल झाल्याचा रोहित पवारांचा आरोप</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/mr/!state/minister-sanjay-shirsat-misuses-powers-rohit-pawar-alleges-rs-5000-crore-scam-mumbai-maharashtra-news-mhs25081804077</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>Mumbai on Red Alert After Over 500mm Rain in 84 Hours; Schools Shut, Flights Delayed, Traffic Paralyzed</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>https://thelogicalindian.com/mumbai-on-red-alert-after-over-500mm-rain-in-84-hours-schools-shut-flights-delayed-traffic-paralyzed/</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>Hebbal Flyover Inaugurated: ₹80 Crore Project Promises Traffic Relief in North Bengaluru</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>https://panasiabiz.com/111088/cm-siddaramaiah-and-dycm-dk-shivakumar-inaugurate-%E2%82%B980-crore-hebbal-flyover-to-ease-bengaluru-traffic/</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>'Third Mumbai' to boost MMR development says Fadnavis invites pvt sector to join in its creation</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>https://www.theweek.in/wire-updates/business/2025/08/18/bom51-mh-cm-third-mumbai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>Maharashtra on high alert as heavy rain leaves 6 dead</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/news/india/maharashtra-on-high-alert-as-heavy-rain-leaves-6-dead/articleshow/123371509.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>Mumbai continues to be on red alert; heavy rain disrupts travel, shuts offices &amp; educational institutions</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/news/weather/mumbai-on-red-alert-for-second-consecutive-day-heavy-rain-disrupts-travel-shuts-educational-institutions/articleshow/123375296.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
           <t>Maha CM asks agencies to be on alert mode after heavy rainfall and flash floods</t>
         </is>
       </c>
-      <c r="B512" t="inlineStr">
+      <c r="B544" t="inlineStr">
         <is>
           <t>https://www.lokmattimes.com/national/maha-cm-asks-agencies-to-be-on-alert-mode-after-heavy-rainfall-and-flash-floods/</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>Over ₹6.52 Crore Medical Aid Distributed To 5,000 Beneficiaries In Pune District</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>https://www.mypunepulse.com/over-%E2%82%B96-52-crore-medical-aid-distributed-to-5000-beneficiaries-in-pune-district/</t>
         </is>
       </c>
     </row>

--- a/Output/Devendra Fadnavis/extracted_links.xlsx
+++ b/Output/Devendra Fadnavis/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B545"/>
+  <dimension ref="A1:B510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,180 +443,180 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>'Third Mumbai' to boost MMR's development, CM Devendra Fadnavis says</t>
+          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by Maharashtra CM Devendra Fadnavis</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/business/third-mumbai-to-boost-mmrs-development-cm-devendra-fadnavis-says-101755577376569.html</t>
+          <t>https://www.tribuneindia.com/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by Maharashtra CM Devendra Fadnavis</t>
+          <t>Aurangzeb Tomb Row: VHP’s Statewide Protests Backed By RSS; CM Devendra Fadnavis Calls For Lawful Dismantling</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis/</t>
+          <t>https://www.msn.com/en-in/news/India/aurangzeb-tomb-row-vhp-s-statewide-protests-backed-by-rss-cm-devendra-fadnavis-calls-for-lawful-dismantling/ar-AA1Bfmct?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Maharashtra CM Devendra Fadnavis seeks Opposition backing for Radhakrishnan</t>
+          <t>Maharashtra CM Fadnavis, his Deputy CMs congratulate Radhakrishnan over V-P nomination</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-devendra-fadnavis-seeks-opposition-backing-for-radhakrishnan-23590051</t>
+          <t>https://www.thehindu.com/news/national/maharashtra-cm-fadnavis-his-deputy-cms-congratulate-radhakrishnan-over-v-p-nomination/article69945058.ece</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Maharashtra CM Fadnavis, his Deputy CMs congratulate Radhakrishnan over V-P nomination</t>
+          <t>Heavy rain lashes Marathwada; 5 missing in Nanded, says CM Devendra Fadnavis</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra-cm-fadnavis-his-deputy-cms-congratulate-radhakrishnan-over-v-p-nomination/article69945058.ece</t>
+          <t>https://indianexpress.com/article/cities/mumbai/heavy-rain-lashes-marathwada-5-missing-in-nanded-says-cm-devendra-fadnavis-10196321/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Aurangzeb Tomb Row: VHP’s Statewide Protests Backed By RSS; CM Devendra Fadnavis Calls For Lawful Dismantling</t>
+          <t>Maha CM asks agencies to be on alert mode after heavy rainfall and flash floods</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/aurangzeb-tomb-row-vhp-s-statewide-protests-backed-by-rss-cm-devendra-fadnavis-calls-for-lawful-dismantling/ar-AA1Bfmct?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.ap7am.com/en/107166/maha-cm-asks-agencies-to-be-on-alert-mode-after-heavy-rainfall-and-flash-floods</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Heavy rain lashes Marathwada; 5 missing in Nanded, says CM Devendra Fadnavis</t>
+          <t>'Positive about bringing a law to protect advocates:' Maharashtra CM Fadnavis</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/heavy-rain-lashes-marathwada-5-missing-in-nanded-says-cm-devendra-fadnavis-10196321/</t>
+          <t>https://legal.economictimes.indiatimes.com/news/industry/positive-about-bringing-a-law-to-protect-advocates-maharashtra-cm-fadnavis/123378199</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Maha CM asks agencies to be on alert mode after heavy rainfall and flash floods</t>
+          <t>18.08.2025 : CM Devendra Fadnavis and Cultural Affairs Minister Ashish Shelar meets Governor</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://www.ap7am.com/en/107166/maha-cm-asks-agencies-to-be-on-alert-mode-after-heavy-rainfall-and-flash-floods</t>
+          <t>https://rajbhavan-maharashtra.gov.in/en/18-08-2025-cm-devendra-fadnavis-and-cultural-affairs-minister-ashish-shelar-meets-governor/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
+          <t>Shiv Sena (UBT) Welcomes Radhakrishnan’s Nomination, Fadnavis Seeks All-Party Support</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://www.outlookbusiness.com/news/third-mumbai-to-boost-metropolitan-region-development-fadnavis</t>
+          <t>https://www.deccanchronicle.com/nation/shiv-sena-ubt-welcomes-rahakrishans-nomination-fadnavis-seeks-all-party-support-1898266</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>'Positive about bringing a law to protect advocates:' Maharashtra CM Fadnavis</t>
+          <t>VP Nominee CP Radhakrishnan Leaves for Delhi, Maha Yuti Leaders Pledge Support</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://legal.economictimes.indiatimes.com/news/industry/positive-about-bringing-a-law-to-protect-advocates-maharashtra-cm-fadnavis/123378199</t>
+          <t>https://www.deccanherald.com/india/maharashtra/vp-nominee-radhakrishnan-departs-for-delhi-maha-yuti-leaders-extend-support-3685392</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>18.08.2025 : CM Devendra Fadnavis and Cultural Affairs Minister Ashish Shelar meets Governor</t>
+          <t>Cannot achieve affordable housing with ‘business as usual’ approach: Maharashtra CM Fadnavis tells...</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://rajbhavan-maharashtra.gov.in/en/18-08-2025-cm-devendra-fadnavis-and-cultural-affairs-minister-ashish-shelar-meets-governor/</t>
+          <t>https://www.moneycontrol.com/news/business/real-estate/cannot-achieve-affordable-housing-with-business-as-usual-approach-maharashtra-cm-fadnavis-tells-realtors-13462328.html</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Shiv Sena (UBT) Welcomes Radhakrishnan’s Nomination, Fadnavis Seeks All-Party Support</t>
+          <t>Third Mumbai: Fadnavis Boosts MMR Development</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/nation/shiv-sena-ubt-welcomes-rahakrishans-nomination-fadnavis-seeks-all-party-support-1898266</t>
+          <t>https://money.rediff.com/news/market/third-mumbai-fadnavis-boosts-mmr-development/32201020250818</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>VP Nominee CP Radhakrishnan Leaves for Delhi, Maha Yuti Leaders Pledge Support</t>
+          <t>Fadnavis hails Maha Guv’s nomination as Vice Presidential candidate</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/vp-nominee-radhakrishnan-departs-for-delhi-maha-yuti-leaders-extend-support-3685392</t>
+          <t>https://www.thestatesman.com/india/fadnavis-hails-maha-guvs-nomination-as-vice-presidential-candidate-1503473264.html</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cannot achieve affordable housing with ‘business as usual’ approach: Maharashtra CM Fadnavis tells...</t>
+          <t>Those who speak of Maharashtra 'asmita' should support Radhakrishnan for VP post: Fadnavis</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/business/real-estate/cannot-achieve-affordable-housing-with-business-as-usual-approach-maharashtra-cm-fadnavis-tells-realtors-13462328.html</t>
+          <t>https://www.ptinews.com/story/national/Those-who-speak-of-Maharashtra--asmita--should-support-Radhakrishnan-for-VP-post--Fadnavis/2832772</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Fadnavis hails Maha Guv’s nomination as Vice Presidential candidate</t>
+          <t>Fadnavis questions rising prices of real estate in Mumbai</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://www.thestatesman.com/india/fadnavis-hails-maha-guvs-nomination-as-vice-presidential-candidate-1503473264.html</t>
+          <t>https://www.constructionweekonline.in/business/fadnavis-home</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis' first reaction to Raj Thackeray's reunion with Uddhav jibe</t>
+          <t>NDA Vice President-Nominee CP Radhakrishnan Expresses Gratitude To PM Modi, Amit Shah &amp; Devendra Fadnavis After VP Nomination</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/india/devendra-fadnavis-first-reaction-to-raj-thackeray-s-reunion-with-uddhav-jibe/ar-AA1I1jzW?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.msn.com/en-in/news/India/nda-vice-president-nominee-cp-radhakrishnan-expresses-gratitude-to-pm-modi-amit-shah-devendra-fadnavis-after-vp-nomination/ar-AA1KGvyO</t>
         </is>
       </c>
     </row>
@@ -635,12 +635,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NDA Vice President-Nominee CP Radhakrishnan Expresses Gratitude To PM Modi, Amit Shah &amp; Devendra Fadnavis After VP Nomination</t>
+          <t>Goldman Sachs opens new, expanded office in Mumbai</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/nda-vice-president-nominee-cp-radhakrishnan-expresses-gratitude-to-pm-modi-amit-shah-devendra-fadnavis-after-vp-nomination/ar-AA1KGvyO</t>
+          <t>https://www.thehindu.com/business/Industry/goldman-sachs-opens-new-expanded-office-in-mumbai/article69947256.ece</t>
         </is>
       </c>
     </row>
@@ -671,6298 +671,5878 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Third Mumbai: Fadnavis Boosts MMR Development</t>
+          <t>Shinde and BJP: The saga continues</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/third-mumbai-fadnavis-boosts-mmr-development/32201020250818</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/shinde-and-bjp-the-saga-continues-101755457833159.html</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Goldman Sachs opens new, expanded office in Mumbai</t>
+          <t>Mumbai received 177mm rain in just 6-8 hour period, says CM Fadnavis; more to come amid high tides</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/business/Industry/goldman-sachs-opens-new-expanded-office-in-mumbai/article69947256.ece</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/red-alert-for-mumbai-mumbai-got-177mm-rain-in-just-6-8-hour-period-says-cm-fadnavis-more-to-come-amid-high-tides-23589990</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Mumbai gets 300 mm rain in a day, Devendra Fadnavis warns next 48 hours critical</t>
+          <t>Maharashtra CM Fadnavis, Dy CM Shinde congratulate Governor CP Radhakrishnan on NDA's VP nomination</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/cities/mumbai/story/mumbai-heavy-rains-waterlogging-imd-red-alert-bmc-school-offices-holiday-work-from-home-2773291-2025-08-19</t>
+          <t>https://aninews.in/news/national/general-news/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination20250818033912/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sword of Raghuji Bhonsle Unveiled in Mumbai: ‘A Bridge Between Generations,’ Says CM Fadnavis</t>
+          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/sword-of-raghuji-bhonsle-unveiled-in-mumbai-a-bridge-between-generations-says-cm-fadnavis/articleshow/123372524.cms</t>
+          <t>https://www.ptinews.com/detail/business/-Third-Mumbai--to-boost-metropolitan-region-development--Fadnavis/2834902</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Shinde and BJP: The saga continues</t>
+          <t>Third Mumbai in Raigad to become Maharashtra’s new economic powerhouse: CM Fadnavis</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/shinde-and-bjp-the-saga-continues-101755457833159.html</t>
+          <t>https://daijiworld.com/news/newsDisplay?newsID=1289652</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Those who speak of Maharashtra 'asmita' should support Radhakrishnan for VP post: Fadnavis</t>
+          <t>Mumbai gets 177mm rain in 6-8 hour period, says CM; all agencies asked to remain alert</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/those-who-speak-of-maharashtra-asmita-should-support-radhakrishnan-for-vp-post-fadnavis/2832772</t>
+          <t>https://m.economictimes.com/news/india/mumbai-gets-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/articleshow/123365291.cms</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Why Eknath Shinde is covering little distance despite frequent visits to Delhi</t>
+          <t>Fadnavis govt’s big Maratha pride push: Legendary sword it ‘bought’ back from London, with a Rs 47L bid</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/political-pulse/why-eknath-shinde-is-covering-little-distance-despite-frequent-visits-to-delhi-10197218/</t>
+          <t>https://theprint.in/politics/fadnavis-govts-big-maratha-pride-push-legendary-sword-it-bought-back-from-london-with-a-rs-47l-bid/2723199/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Heavy Rains Ravage State, CM Fadnavis Orders Relief, Surveys Rain-Hit Areas</t>
+          <t>Rain fury leaves 7 dead in Maharashtra, 200 villagers stranded</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/heavy-rains-ravage-state-cm-fadnavis-orders-relief-surveys-rain-hit-areas/articleshow/123372550.cms</t>
+          <t>https://www.ptinews.com/story/national/rain-fury-leaves-7-dead-in-maharashtra,-200-villagers-stranded/2834213</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>'My karyakarta is with me': Hitendra Thakur shrugs off defections ahead of civic elections</t>
+          <t>"Observe precaution": Maharashtra CM warns about severe weather conditions in state</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/my-karyakarta-is-with-me-hitendra-thakur-shrugs-off-defections-ahead-of-civic-elections/ar-AA1KHNiH</t>
+          <t>https://www.aninews.in/news/national/general-news/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state20250819025510</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>‘Observe precaution’: Maharashtra CM warns about severe weather conditions in State</t>
+          <t>Find suitable land &amp; I will set up IT park through MIDC in Solapur: Fadnavis</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://www.thehindubusinessline.com/news/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state/article69950172.ece</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/find-suitable-land-i-will-set-up-it-park-through-midc-in-solapur-fadnavis/articleshow/123351422.cms</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Mumbai received 177mm rain in just 6-8 hour period, says CM Fadnavis; more to come amid high tides</t>
+          <t>Fadnavis meets Guv Radhakrishnan, presents him book of Shivaji Maharaj's letters</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/red-alert-for-mumbai-mumbai-got-177mm-rain-in-just-6-8-hour-period-says-cm-fadnavis-more-to-come-amid-high-tides-23589990</t>
+          <t>https://www.ptinews.com/story/national/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharaj-s-letters/2832582</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Third Mumbai in Raigad to become Maharashtra’s new economic powerhouse: CM Fadnavis</t>
+          <t>‘Third Mumbai’ takes shape as CM Fadnavis unveils mega MMR expansion plan</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://daijiworld.com/news/newsDisplay?newsID=1289652</t>
+          <t>https://www.moneycontrol.com/city/third-mumbai-takes-shape-as-cm-fadnavis-unveils-mega-mmr-expansion-plan-article-13465350.html</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Mumbai gets 177mm rain in 6-8 hour period, says CM; all agencies asked to remain alert</t>
+          <t>DH Evening Brief | NDA VP pick in Delhi to meet BJP top brass, Opposition yet to finalise their candidate; I.N.D.I.A. bloc continues attacking EC chief over SIR</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/mumbai-gets-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/articleshow/123365291.cms</t>
+          <t>https://www.deccanherald.com/india/dh-evening-brief-nda-vp-pick-in-delhi-to-meet-bjp-top-brass-opposition-yet-to-finalise-their-candidate-india-bloc-continues-attacking-ec-chief-over-sir-3685866</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Fadnavis govt’s big Maratha pride push: Legendary sword it ‘bought’ back from London, with a Rs 47L bid</t>
+          <t>Raghuji Bhonsle’s sword brought to India</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://theprint.in/politics/fadnavis-govts-big-maratha-pride-push-legendary-sword-it-bought-back-from-london-with-a-rs-47l-bid/2723199/</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/19/raghuji-bhonsles-sword-brought-to-india.html</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Rain fury leaves 7 dead in Maharashtra, 200 villagers stranded</t>
+          <t>Fadnavis Dedicates Goldman Sachs’ New Mumbai Office, Unveils Vision For ‘Third Mumbai’</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/rain-fury-leaves-7-dead-in-maharashtra,-200-villagers-stranded/2834213</t>
+          <t>https://www.businessworld.in/article/fadnavis-dedicates-goldman-sachs-new-mumbai-office-unveils-vision-for-third-mumbai-567845</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Maharashtra CM Fadnavis, Dy CM Shinde congratulate Governor CP Radhakrishnan on NDA's VP nomination</t>
+          <t>Schools shut, red alert as Mumbai braces for another day of heavy rain | Latest News India - Hindustan Times</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination-23589945</t>
+          <t>https://www.hindustantimes.com/india-news/mumbai-rains-schools-shut-as-mumbai-under-imd-red-alert-braces-for-another-day-of-heavy-rain-10-updates-101755564432674-amp.html</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Find suitable land &amp; I will set up IT park through MIDC in Solapur: Fadnavis</t>
+          <t>Maharashtra on high alert as heavy rains batter state; CM, Dy CM lead rescue efforts</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/find-suitable-land-i-will-set-up-it-park-through-midc-in-solapur-fadnavis/articleshow/123351422.cms</t>
+          <t>https://www.daijiworld.com/news/newsDisplay?newsID=1289634</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Fadnavis meets Guv Radhakrishnan, presents him book of Shivaji Maharaj's letters</t>
+          <t>Maratha general Raghuji Bhonsle's sword brought to Mumbai</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharaj-s-letters/2832582</t>
+          <t>https://www.ptinews.com/editor-detail/maratha-general-raghuji-bhonsle-s-sword-brought-to-mumbai/2833930</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>'Third Mumbai' to boost MMR development, says Fadnavis; invites pvt sector to join in its creation</t>
+          <t>Maharashtra rain: Mumbai flooded, 5 missing in Nanded, more showers in store</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/-third-mumbai--to-boost-mmr-development--says-fadnavis;-invites-pvt-sector-to-join-in-its-creation/2834267</t>
+          <t>https://thefederal.com/category/states/west/maharashtra/mumbai-flooded-nanded-5-missing-maharashtra-rain-202350</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
+          <t>Heavy rains lash Nanded Five missing scores stranded says CM Fadnavis Army unit deployed</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/-third-mumbai--to-boost-metropolitan-region-development--fadnavis/2834902</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom17-mh-rains-nanded.html</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>‘Third Mumbai’ takes shape as CM Fadnavis unveils mega MMR expansion plan</t>
+          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/city/third-mumbai-takes-shape-as-cm-fadnavis-unveils-mega-mmr-expansion-plan-article-13465350.html</t>
+          <t>https://www.millenniumpost.in/nation/third-mumbai-to-boost-metropolitan-region-development-fadnavis-623625</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Mumbai rains: Maharashtra CM says 'observe precautions', warns of heavy rainfall, high tide; check BMC's advisory</t>
+          <t>Observe precaution: Maharashtra CM warns about severe weather conditions in state</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/news/mumbai-rains-maharashtra-cm-says-observe-precautions-warns-of-heavy-rainfall-high-tide-check-bmcs-advisory-11755573270369.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state-23590120</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Raghuji Bhonsle’s sword brought to India</t>
+          <t>Rain fury leaves 7 dead in Maharashtra 200 villagers stranded</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/19/raghuji-bhonsles-sword-brought-to-india.html</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom50-mh-2nd-ldall-rains.html</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Mumbai got 177mm rain in 6-8 hour period, says CM; more to come amid high tides</t>
+          <t>Mumbai got 177mm rain in 6-8 hour period says CM more to come amid high tides</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/mumbai-got-177mm-rain-in-6-8-hour-period-says-cm-more-to-come-amid-high-tides/2832660</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom21-mh-rains-mumbai-cm.html</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Fadnavis Dedicates Goldman Sachs’ New Mumbai Office, Unveils Vision For ‘Third Mumbai’</t>
+          <t>Pune can get underground road network to beat traffic woes</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://www.businessworld.in/article/fadnavis-dedicates-goldman-sachs-new-mumbai-office-unveils-vision-for-third-mumbai-567845</t>
+          <t>https://inshorts.com/en/news/pune-can-get-underground-road-network-to-beat-traffic-woes-1755566759073</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Schools shut, red alert as Mumbai braces for another day of heavy rain | Latest News India - Hindustan Times</t>
+          <t>CM Devendra Fadnavis Meets Netherlands Yogasana Chief on Global Initiatives</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/mumbai-rains-schools-shut-as-mumbai-under-imd-red-alert-braces-for-another-day-of-heavy-rain-10-updates-101755564432674-amp.html</t>
+          <t>https://www.transcontinentaltimes.com/netherlands-yogasana-sports-nysa/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Maratha general Raghuji Bhonsle's sword brought to Mumbai</t>
+          <t>CM Devendra Fadnavis to Inaugurate India’s First ESG Lab at National STEM Challenge 2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/maratha-general-raghuji-bhonsle-s-sword-brought-to-mumbai/2833930</t>
+          <t>https://indiacsr.in/cm-devendra-fadnavis-to-inaugurate-indias-first-esg-lab-at-national-stem-challenge-2025/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by Maharashtra CM Devendra Fadnavis</t>
+          <t>'Third Mumbai' Initiative Sparks New Wave of Economic Growth in Maharashtra</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322/</t>
+          <t>https://www.devdiscourse.com/article/science-environment/3545659-third-mumbai-initiative-sparks-new-wave-of-economic-growth-in-maharashtra</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Maharashtra rain: Mumbai flooded, 5 missing in Nanded, more showers in store</t>
+          <t>Mumbai: CM Devendra Fadnavis meets C.P. Radhakrishnan #Gallery</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://thefederal.com/category/states/west/maharashtra/mumbai-flooded-nanded-5-missing-maharashtra-rain-202350</t>
+          <t>https://www.socialnews.xyz/2025/08/18/mumbai-cm-devendra-fadnavis-meets-c-p-radhakrishnan-gallery/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Heavy rains lash Nanded Five missing scores stranded says CM Fadnavis Army unit deployed</t>
+          <t>'Third Mumbai' Will Open A New Chapter Of Economic Development: Maha CM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom17-mh-rains-nanded.html</t>
+          <t>https://menafn.com/1109941619/Third-Mumbai-Will-Open-A-New-Chapter-Of-Economic-Development-Maha-CM</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
+          <t>Goldman Sachs Expands In Mumbai, Devendra Fadnavis Inaugurates New Worli Office</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://www.millenniumpost.in/nation/third-mumbai-to-boost-metropolitan-region-development-fadnavis-623625</t>
+          <t>https://www.freepressjournal.in/business/goldman-sachs-expands-in-mumbai-devendra-fadnavis-inaugurates-new-worli-office</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Mumbai rain Highlights: 7 people dead across Maharashtra, says CM Devendra Fadnavis</t>
+          <t>Vice-President Elections 2025: Maharashtra CM Devendra Fadnavis Presents Shawl to CP Radhakrishnan on</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://www.india.com/news/india/mumbai-rain-live-updates-heavy-rains-lashes-city-orange-alert-for-today-red-alert-in-pune-satara-ratnagiri-local-trains-delayed-traffic-jams-8017300/</t>
+          <t>https://www.latestly.com/agency-news/vice-president-elections-2025-maharashtra-cm-devendra-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vp-nomination-see-pics-7063864.html</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Observe precaution: Maharashtra CM warns about severe weather conditions in state</t>
+          <t>Mumbai Rains: Maharashtra CM Devendra Fadnavis Chairs Review Meeting On Excessive Rainfall At Mantralaya</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state-23590120</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-rains-cm-devendra-fadnavis-chairs-review-meeting-on-excessive-rainfall-at-mantralaya-video</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Mumbai got 177mm rain in 6-8 hour period says CM more to come amid high tides</t>
+          <t>India News | ⚡Devendra Fadnavis Says ‘Third Mumbai’ Will Open a New Chapter of Economic Development</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom21-mh-rains-mumbai-cm.html</t>
+          <t>https://www.latestly.com/quickly/india/news/devendra-fadnavis-says-third-mumbai-will-open-a-new-chapter-of-economic-development-7064927.html</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Pune can get underground road network to beat traffic woes</t>
+          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by...</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://inshorts.com/en/news/pune-can-get-underground-road-network-to-beat-traffic-woes-1755566759073</t>
+          <t>https://www.lokmattimes.com/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CM Devendra Fadnavis Meets Netherlands Yogasana Chief on Global Initiatives</t>
+          <t>Mumbai Records 177 mm Rain In 6 Hours, CM Devendra Fadnavis Urges Caution Amid High Tide Alert</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://www.transcontinentaltimes.com/netherlands-yogasana-sports-nysa/</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-records-177-mm-rain-in-6-hours-cm-devendra-fadnavis-urges-caution-amid-high-tide-alert</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CM Devendra Fadnavis to Inaugurate India’s First ESG Lab at National STEM Challenge 2025</t>
+          <t>Future-ready India lies in STEM and AI, says Devendra Fadnavis, Maharashtra CM</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://indiacsr.in/cm-devendra-fadnavis-to-inaugurate-indias-first-esg-lab-at-national-stem-challenge-2025/</t>
+          <t>https://indiacsr.in/brillio-national-stem-challenge-empowers-2500-underserved-students-to-innovate-for-indias-future/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>'Third Mumbai' Initiative Sparks New Wave of Economic Growth in Maharashtra</t>
+          <t>‘Third Mumbai’ will open a new chapter of economic development: Maha CM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/science-environment/3545659-third-mumbai-initiative-sparks-new-wave-of-economic-growth-in-maharashtra</t>
+          <t>https://www.lokmattimes.com/national/third-mumbai-will-open-a-new-chapter-of-economic-development-maha-cm/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Goldman Sachs Expands In Mumbai, Devendra Fadnavis Inaugurates New Worli Office</t>
+          <t>Mumbai: C.P. Radhakrishnan departs for Delhi #Gallery</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/business/goldman-sachs-expands-in-mumbai-devendra-fadnavis-inaugurates-new-worli-office</t>
+          <t>https://www.socialnews.xyz/2025/08/18/mumbai-c-p-radhakrishnan-departs-for-delhi-gallery/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Maharashtra CM Devendra Fadnavis Says ‘Third Mumbai’ Being Developed in Raigad District Will Open New</t>
+          <t>Maharashtra CM Fadnavis presents shawl to CP Radhakrishnan on NDA’s VP nomination</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/india/news/maharashtra-cm-devendra-fadnavis-says-third-mumbai-being-developed-in-raigad-district-will-open-new-chapter-of-economic-development-7064927.html</t>
+          <t>https://thenewsmill.com/2025/08/maharashtra-cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vp-nomination/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Mumbai Rains: Maharashtra CM Devendra Fadnavis Chairs Review Meeting On Excessive Rainfall At Mantralaya</t>
+          <t>VIDEO: Historic Sword Of Raghuji Bhonsle Connects Youth With Maharashtra’s Glorious History, Says CM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-rains-cm-devendra-fadnavis-chairs-review-meeting-on-excessive-rainfall-at-mantralaya-video</t>
+          <t>https://www.freepressjournal.in/mumbai/video-historic-sword-of-raghuji-bhonsle-connects-youth-with-maharashtras-glorious-history-says-cm-devendra-fadnavis</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>India News | ⚡Devendra Fadnavis Says ‘Third Mumbai’ Will Open a New Chapter of Economic Development</t>
+          <t>Heavy Rain Forecast for Mumbai: CM Fadnavis Reviews Flood Situation Across Maharashtra, with the Next 12...</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/quickly/india/news/devendra-fadnavis-says-third-mumbai-will-open-a-new-chapter-of-economic-development-7064927.html</t>
+          <t>https://www.lokmattimes.com/mumbai/heavy-rain-forecast-for-mumbai-cm-fadnavis-reviews-flood-situation-across-maharashtra-with-the-next-12-hours-critical-a475/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Mumbai Records 177 mm Rain In 6 Hours, CM Devendra Fadnavis Urges Caution Amid High Tide Alert</t>
+          <t>Those who speak of Maharashtra 'asmita' should support Radhakrishnan for VP post: Fadnavis</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-records-177-mm-rain-in-6-hours-cm-devendra-fadnavis-urges-caution-amid-high-tide-alert</t>
+          <t>https://www.newsdrum.in/national/those-who-speak-of-maharashtra-asmita-should-support-radhakrishnan-for-vp-post-fadnavis-9672630</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by...</t>
+          <t>'Observe precaution': Maharashtra CM warns about severe weather conditions in state</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis/</t>
+          <t>https://english.newsnationtv.com/national/general-news/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state20250819025510</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Future-ready India lies in STEM and AI, says Devendra Fadnavis, Maharashtra CM</t>
+          <t>Pune Patients Receive Over Rs 6.5 Crore in Medical Aid Under Chief Minister Devendra Fadnavis’ Initiative</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://indiacsr.in/brillio-national-stem-challenge-empowers-2500-underserved-students-to-innovate-for-indias-future/</t>
+          <t>https://www.punekarnews.in/pune-patients-receive-over-rs-6-5-crore-in-medical-aid-under-chief-minister-devendra-fadnavis-initiative/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>‘Third Mumbai’ will open a new chapter of economic development: Maha CM</t>
+          <t>Heavy rains in Mumbai: IndiGo, SpiceJet, Akasa issue travel advisories</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/third-mumbai-will-open-a-new-chapter-of-economic-development-maha-cm/</t>
+          <t>https://www.newsbytesapp.com/news/india/mumbai-flights-status-airlines-issue-key-advisory-for-passengers/story</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Mumbai: C.P. Radhakrishnan departs for Delhi #Gallery</t>
+          <t>Maharashtra Rains: 5 Missing in Nanded, Over 200 Stranded Across Several Districts; Army, NDRF Deployed</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/mumbai-c-p-radhakrishnan-departs-for-delhi-gallery/</t>
+          <t>https://www.lokmattimes.com/maharashtra/maharashtra-rains-5-missing-in-nanded-over-200-stranded-across-several-districts-army-ndrf-deployed-a517/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>VIDEO: Historic Sword Of Raghuji Bhonsle Connects Youth With Maharashtra’s Glorious History, Says CM</t>
+          <t>7 killed as heavy rain batters Maharashtr­a; 800 villages hit</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/video-historic-sword-of-raghuji-bhonsle-connects-youth-with-maharashtras-glorious-history-says-cm-devendra-fadnavis</t>
+          <t>https://www.pressreader.com/india/the-hindu-mangalore-9WWc/20250819/281947433944151</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Heavy Rain Forecast for Mumbai: CM Fadnavis Reviews Flood Situation Across Maharashtra, with the Next 12...</t>
+          <t>Business News</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/mumbai/heavy-rain-forecast-for-mumbai-cm-fadnavis-reviews-flood-situation-across-maharashtra-with-the-next-12-hours-critical-a475/</t>
+          <t>https://www.latestly.com/agency-news/business-news-credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis-7064653.html</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Those who speak of Maharashtra 'asmita' should support Radhakrishnan for VP post: Fadnavis</t>
+          <t>Amid heavy rains in Maharashtra, CM Fadnavis directs all agencies to be on alert</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/those-who-speak-of-maharashtra-asmita-should-support-radhakrishnan-for-vp-post-fadnavis-9672630</t>
+          <t>https://www.thehawk.in/news/india/amid-heavy-rains-in-maharashtra-cm-fadnavis-directs-all-agencies-to-be-on-alert</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>'Observe precaution': Maharashtra CM warns about severe weather conditions in state</t>
+          <t>Mumbai To Welcome Historic Sword Of Shrimant Raje Raghuji Bhonsale On August 18; To Be Ceremoniously Unveiled</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://english.newsnationtv.com/national/general-news/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state20250819025510</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-to-welcome-historic-sword-of-shrimant-raje-raghuji-bhonsale-on-august-18-to-be-ceremoniously-unveiled-by-cm-fadnavis</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Heavy rains in Mumbai: IndiGo, SpiceJet, Akasa issue travel advisories</t>
+          <t>Fadnavis meets Guv Radhakrishnan, presents him book of Shivaji Maharaj's letters</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://www.newsbytesapp.com/news/india/mumbai-flights-status-airlines-issue-key-advisory-for-passengers/story</t>
+          <t>https://www.newsdrum.in/national/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharajs-letters-9672415</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Maharashtra Rains: 5 Missing in Nanded, Over 200 Stranded Across Several Districts; Army, NDRF Deployed</t>
+          <t>Rain fury leaves 7 dead in Maharashtra, 200 villagers stranded</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/maharashtra/maharashtra-rains-5-missing-in-nanded-over-200-stranded-across-several-districts-army-ndrf-deployed-a517/</t>
+          <t>https://www.newsdrum.in/national/rain-fury-leaves-7-dead-in-maharashtra-200-villagers-stranded-9674070</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>7 killed as heavy rain batters Maharashtr­a; 800 villages hit</t>
+          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://www.pressreader.com/india/the-hindu-mangalore-9WWc/20250819/281947433944151</t>
+          <t>https://www.newsdrum.in/business/third-mumbai-to-boost-metropolitan-region-development-fadnavis-9674858</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Business News</t>
+          <t>NDA’s Vice President nominee CP Radhakrishnan to reach Delhi today: sources</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/business-news-credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis-7064653.html</t>
+          <t>https://thenewsmill.com/2025/08/ndas-vice-president-nominee-cp-radhakrishnan-to-reach-delhi-today-sources/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by Maharashtra CM Devendra Fadnavis</t>
+          <t>Fadnavis Gifts Unpublished Shivaji Maharaj Letters to Maharashtra Governor at Mumbai Airport</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://english.newsnationtv.com/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322</t>
+          <t>https://panasiabiz.com/111091/cm-devendra-fadnavis-presents-rare-shivaji-maharaj-letters-to-governor-cp-radhakrishnan/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Amid heavy rains in Maharashtra, CM Fadnavis directs all agencies to be on alert</t>
+          <t>CM Fadnavis unveils emblem for Ganeshotsav to be celebrated as Rajya Mahotsav</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/india/amid-heavy-rains-in-maharashtra-cm-fadnavis-directs-all-agencies-to-be-on-alert</t>
+          <t>https://www.thehawk.in/news/india/cm-fadnavis-unveils-emblem-for-ganeshotsav-to-be-celebrated-as-rajya-mahotsav</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Mumbai To Welcome Historic Sword Of Shrimant Raje Raghuji Bhonsale On August 18; To Be Ceremoniously Unveiled</t>
+          <t>Heavy rains lash Nanded: Five missing, scores stranded, says CM Fadnavis; Army unit deployed</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-to-welcome-historic-sword-of-shrimant-raje-raghuji-bhonsale-on-august-18-to-be-ceremoniously-unveiled-by-cm-fadnavis</t>
+          <t>https://www.newsdrum.in/national/heavy-rains-lash-nanded-five-missing-scores-stranded-says-cm-fadnavis-army-unit-deployed-9672306</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Fadnavis meets Guv Radhakrishnan, presents him book of Shivaji Maharaj's letters</t>
+          <t>Maharashtra government approves major infra projects</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharajs-letters-9672415</t>
+          <t>https://www.thehawk.in/news/india/maharashtra-government-approves-major-infra-projects</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Rain fury leaves 7 dead in Maharashtra, 200 villagers stranded</t>
+          <t>उप-राष्ट्रपति चुनाव: देवेंद्र फडणवीस का 'मराठी अस्मिता' वाला दांव, क्या करेंगे</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/rain-fury-leaves-7-dead-in-maharashtra-200-villagers-stranded-9674070</t>
+          <t>https://www.abplive.com/states/maharashtra/vice-president-election-2025-maharashtra-cm-devendra-fadnavis-request-uddhav-thackeray-and-sharad-pawar-2997542</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CM Fadnavis unveils emblem for Ganeshotsav to be celebrated as Rajya Mahotsav</t>
+          <t>लगता है वो लोग फडणवीस और शिंदे के बारे में नहीं जानते, CJI ने क्यों कहा ऐसा?</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/india/cm-fadnavis-unveils-emblem-for-ganeshotsav-to-be-celebrated-as-rajya-mahotsav</t>
+          <t>https://hindi.news18.com/news/nation/cji-br-gavai-take-devendra-fadnavis-eknath-shinde-name-bombay-high-court-new-circuit-bench-in-kolhapur-9520456.html</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Heavy rains lash Nanded: Five missing, scores stranded, says CM Fadnavis; Army unit deployed</t>
+          <t>Mumbai Maharashtra Rains: महाराष्ट्र में भारी बारिश पर सीएम देवेंद्र फडणवीस का सख्त निर्देश, सभी विभाग अलर्ट पर</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/heavy-rains-lash-nanded-five-missing-scores-stranded-says-cm-fadnavis-army-unit-deployed-9672306</t>
+          <t>https://thecsrjournal.in/mumbai-maharashtra-rains-cm-and-managment-on-alert-hindi/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Mumbai Weather Today LIVE Updates: Mithi River Crosses Danger Mark; Santacruz Records Highest Rainfall; 300</t>
+          <t>दिल्ली पहुंचे देवेंद्र फडणवीस, अमित शाह से मिले, जानें क्यों थी यह मुलाकात खास</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-rains-live-updates-heavy-showers-wreak-havoc-in-city-schools-colleges-shut-as-imd-issues-red-alert-sion-matunga-dadar-vile-parle-waterlogged-andheri-subway-closed</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B6-%E0%A4%B9-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A5%87-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%82-%E0%A4%A5-%E0%A4%AF%E0%A4%B9-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4-%E0%A4%96-%E0%A4%B8/ar-AA1Jjy9z</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Maharashtra government approves major infra projects</t>
+          <t>मुख्यमंत्री देवेंद्र फडणवीस ने दी राज्यपाल राधाकृष्णन को उपराष्ट्रपति पद की उम्मीदवारता पर बधाई</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/india/maharashtra-government-approves-major-infra-projects</t>
+          <t>https://hindi.mid-day.com/news/india-news/article/chief-minister-devendra-fadnavis-congratulated-governor-radhakrishnan-on-his-candidature-for-the-post-of-vice-president-11180</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>उप-राष्ट्रपति चुनाव: देवेंद्र फडणवीस का 'मराठी अस्मिता' वाला दांव, क्या करेंगे</t>
+          <t>Mumbai Rains News: भारी बारिश के चलते कल मुंबई के स्कूल-कॉलेजों में छुट्टी, नांदेड़ में 7 लोगों की मौत, CM फडणवीस ने की आपात बैठक</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/vice-president-election-2025-maharashtra-cm-devendra-fadnavis-request-uddhav-thackeray-and-sharad-pawar-2997542</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/heavy-rains-in-mumbai-schools-colleges-closed-7-deaths-in-maharashtra-5-missing-nanded-cm-fadnavis-emergency-meeting/articleshow/123366462.cms</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>महाराष्ट्र के इस जिले में बसाई जाएगी 'तीसरी मुंबई', मुख्यमंत्री देवेंद्र फडणवीस ने बताईं प्रोजेक्ट की अहम ब</t>
+          <t>मुख्यमंत्री देवेंद्र फडणवीस ने राज्य में भारी बारिश के मद्देनजर सभी एजेंसियों को सतर्क रहने के निर्देश दिए</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/paisa/business/third-mumbai-will-be-settled-in-raigad-district-of-maharashtra-chief-minister-devendra-fadnavis-told-the-important-points-of-the-project-2025-08-19-1156854</t>
+          <t>https://www.mumbailive.com/hi/civic/chief-minister-devendra-fadnavis-directed-all-agencies-to-remain-alert-in-view-of-heavy-rains-in-the-state-89633</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>लगता है वो लोग देवेंद्र फडणवीस और एकनाथ शिंदे के बारे में नहीं जानते, CJI बीआर गवई ने क्यों कहा ऐसा?</t>
+          <t>Mumbai Rain News : मुंबई में बारिश ने मचाया कोहराम, देवेंद्र फडणवीस का आया बयान</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/nation/cji-br-gavai-take-devendra-fadnavis-eknath-shinde-name-bombay-high-court-new-circuit-bench-in-kolhapur-9520456.html</t>
+          <t>https://hindi.oneindia.com/videos/mumbai-rain-news-rain-wreaked-havoc-in-mumbai-devendra-fadnavis-statement-came-4259449.html</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Mumbai Maharashtra Rains: महाराष्ट्र में भारी बारिश पर सीएम देवेंद्र फडणवीस का सख्त निर्देश, सभी विभाग अलर्ट पर</t>
+          <t>मुंबई में भारी भारिश ने मचाई तबाही, CM देवेंद्र फडणवीस ने बुलाई बैठक</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/mumbai-maharashtra-rains-cm-and-managment-on-alert-hindi/</t>
+          <t>https://www.patrika.com/videos/mumbai-news/heavy-rain-wreaks-havoc-in-mumbai-cm-devendra-fadnavis-calls-a-meeting-19874343</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>दिल्ली पहुंचे देवेंद्र फडणवीस, अमित शाह से मिले, जानें क्यों थी यह मुलाकात खास</t>
+          <t>फडणवीस ने कहा, ‘तीसरी मुंबई’ से एमएमआर का होगा विकास</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B6-%E0%A4%B9-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A5%87-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%82-%E0%A4%A5-%E0%A4%AF%E0%A4%B9-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4-%E0%A4%96-%E0%A4%B8/ar-AA1Jjy9z</t>
+          <t>https://hindi.theprint.in/india/economy/fadnavis-said-third-mumbai-will-lead-to-development-of-mmr/856867/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>मुख्यमंत्री देवेंद्र फडणवीस ने दी राज्यपाल राधाकृष्णन को उपराष्ट्रपति पद की उम्मीदवारता पर बधाई</t>
+          <t>Raghuji Bhosale: आज मुंबई आएगी रघुजी भोसले की की ऐतिहासिक तलवार, सीएम फडणवीस करेंगे स्वागत</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/news/india-news/article/chief-minister-devendra-fadnavis-congratulated-governor-radhakrishnan-on-his-candidature-for-the-post-of-vice-president-11180</t>
+          <t>https://zeenews.india.com/hindi/india/raghuji-bhosale-historic-sword-will-arrive-in-mumbai-today-cm-fadnavis-will-welcome-it/2886138</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>कैसी होगी तीसरी मुंबई, कितनी बड़ी और कहां बन रही, सुविधाओं से लेकर प्लानिंग तक, CM फडणवीस ने सब बताया</t>
+          <t>महाराष्ट्र के नांदेड़ में फटा बादल, 15-16 जिलो में अलर्ट, CM फडणवीस बोले- फसलों को नुकसान</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://ndtv.in/maharashtra-news/maharashtra-cmdevendra-fadnavis-told-third-mumbai-mmr-will-develop-with-this-know-how-it-will-be-9112502</t>
+          <t>https://www.abplive.com/states/maharashtra/weather-mumbai-rains-local-train-cloudburst-nanded-alert-in-15-16-districts-in-maharashtra-cm-devendra-fadnavis-said-damage-to-crops-2997472</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Vice President Election: उद्धव ठाकरे और शरद पवार से फडणवीस मांगेंगे सीपी राधाकृष्णन के लिए समर्थन, शिंदे सेना ने दिया सपोर्ट</t>
+          <t>'औरंगजेब भारत के किसी भी समाज का हीरो नहीं...', मजार को लेकर फडणवीस ने कही बड़ी बात</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-governor-radhakrishnan-gets-nda-backing-for-vice-president-post-devendra-fadnavis-uddhav-thackeray-sharad-pawar/articleshow/123371527.cms</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%AD-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AE%E0%A4%9C-%E0%A4%B0-%E0%A4%95-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC-%E0%A4%A4/ar-AA1IRFiN</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>मुख्यमंत्री देवेंद्र फडणवीस ने राज्य में भारी बारिश के मद्देनजर सभी एजेंसियों को सतर्क रहने के निर्देश दिए</t>
+          <t>मुंबई में सिर्फ 6-8 घंटे में 177 मिमी हुई बारिश, फडणवीस ने दिए सावधानी बरतने के निर्देश</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://www.mumbailive.com/hi/civic/chief-minister-devendra-fadnavis-directed-all-agencies-to-remain-alert-in-view-of-heavy-rains-in-the-state-89633</t>
+          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/mumbai-received-177-mm-of-rain-in-just-6-8-hours-fadnavis-gave-instructions-to-take-precautions-11195</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Mumbai Rain News : मुंबई में बारिश ने मचाया कोहराम, देवेंद्र फडणवीस का आया बयान</t>
+          <t>CP Radhakrishnan को लेकर CM फडणवीस ने बड़ा खुलासा कर चल दिया दांव, अब क्‍या करेंगे उद्धव ठाकरे और शरद पवार?</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/videos/mumbai-rain-news-rain-wreaked-havoc-in-mumbai-devendra-fadnavis-statement-came-4259449.html</t>
+          <t>https://hindi.oneindia.com/news/maharashtra/vice-presidential-election-cm-devendra-fadnavis-said-cp-radhakrishnan-is-a-mumbai-voter-support-him-1365243.html</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>मुंबई में भारी भारिश ने मचाई तबाही, CM देवेंद्र फडणवीस ने बुलाई बैठक</t>
+          <t>मुंबई में 6-8 घंटे में 177 मिलीमीटर बारिश हुई: फडणवीस</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/videos/mumbai-news/heavy-rain-wreaks-havoc-in-mumbai-cm-devendra-fadnavis-calls-a-meeting-19874343</t>
+          <t>https://hindi.theprint.in/india/mumbai-received-177-mm-of-rain-in-6-8-hours-fadnavis/856688/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>फडणवीस ने कहा, ‘तीसरी मुंबई’ से एमएमआर का होगा विकास</t>
+          <t>सिरदर्द है कृषि मंत्रालय...अजित पवार के मंत्री दत्तात्रेय भरणे को नहीं पसंद आई नई जिम्मेदारी, जानें क्या कहा?</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/economy/fadnavis-said-third-mumbai-will-lead-to-development-of-mmr/856867/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-manik-rao-kokate-successor-minister-dattatray-bharane-called-agriculture-ministry-is-a-headache-know-all/articleshow/123357471.cms</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>महाराष्ट्र के नांदेड़ में फटा बादल, 15-16 जिलो में अलर्ट, CM फडणवीस बोले- फसलों को नुकसान</t>
+          <t>फडणवीस की पत्नी के खिलाफ अपमानजनक पोस्ट : दो लोगों की अग्रिम जमानत अर्जी खारिज</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/weather-mumbai-rains-local-train-cloudburst-nanded-alert-in-15-16-districts-in-maharashtra-cm-devendra-fadnavis-said-damage-to-crops-2997472</t>
+          <t>http://www.msn.com/hi-in/news/other/%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%96-%E0%A4%B2-%E0%A4%AB-%E0%A4%85%E0%A4%AA%E0%A4%AE-%E0%A4%A8%E0%A4%9C%E0%A4%A8%E0%A4%95-%E0%A4%AA-%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%A6-%E0%A4%B2-%E0%A4%97-%E0%A4%82-%E0%A4%95-%E0%A4%85%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%9C%E0%A4%AE-%E0%A4%A8%E0%A4%A4-%E0%A4%85%E0%A4%B0%E0%A5%8D%E0%A4%9C-%E0%A4%96-%E0%A4%B0-%E0%A4%9C/ar-AA1Je80j?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>मैं आपकी वहिनी… देवेंद्र फडणविस के शपथ लेते ही पत्नी अमृता फडणवीस ने महाराष्ट्र से किया ये वादा</t>
+          <t>नांदेड़ में भारी बारिश के कारण पांच लोग लापता, कई व्यक्ति फंसे : मुख्यमंत्री फडणवीस</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%88%E0%A4%82-%E0%A4%86%E0%A4%AA%E0%A4%95-%E0%A4%B5%E0%A4%B9-%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%B6%E0%A4%AA%E0%A4%A5-%E0%A4%B2%E0%A5%87%E0%A4%A4%E0%A5%87-%E0%A4%B9-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A8-%E0%A4%85%E0%A4%AE%E0%A5%83%E0%A4%A4-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%AF%E0%A5%87-%E0%A4%B5-%E0%A4%A6/ar-AA1vljO5?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://hindi.theprint.in/india/five-people-missing-many-people-stranded-due-to-heavy-rains-in-nanded-chief-minister-fadnavis/856679/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Mumbai Rains News: भारी बारिश के चलते कल मुंबई के स्कूल-कॉलेजों में छुट्टी, नांदेड़ में 7 लोगों की मौत, CM फडणवीस ने की आपात बैठक</t>
+          <t>Mumbai Rain: 24 घंटे की बारिश से मुंबई की सांस फूली, CM देवेंद्र फडणवीस ने पड़ोसी राज्यों से किया संपर्क</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/heavy-rains-in-mumbai-schools-colleges-closed-7-deaths-in-maharashtra-5-missing-nanded-cm-fadnavis-emergency-meeting/articleshow/123366462.cms</t>
+          <t>https://zeenews.india.com/hindi/india/mumbai-rains-today-imd-red-alert-warning-waterlogging-traffic-update/2886161</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>मुंबई में सिर्फ 6-8 घंटे में 177 मिमी हुई बारिश, फडणवीस ने दिए सावधानी बरतने के निर्देश</t>
+          <t>महाराष्ट्र में भारी बारिश का कहर, 16 जिलों में रेड अलर्ट, बचाव दल तैनात</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/mumbai-received-177-mm-of-rain-in-just-6-8-hours-fadnavis-gave-instructions-to-take-precautions-11195</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-heavy-rainfall-flood-alert-red-and-orange-alerts-issued-relief-operations-mumbai-rain-ann-2997660</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>CP Radhakrishnan को लेकर CM फडणवीस ने बड़ा खुलासा कर चल दिया दांव, अब क्‍या करेंगे उद्धव ठाकरे और शरद पवार?</t>
+          <t>आज सपना पूरा हो गया... चीफ जस्टिस गवई ने ऐसा क्यों कहा, सीएम फडणवीस का लिया नाम</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/maharashtra/vice-presidential-election-cm-devendra-fadnavis-said-cp-radhakrishnan-is-a-mumbai-voter-support-him-1365243.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/cji-br-gavai-said-our-dream-has-been-fulfilled-over-bombay-high-court-new-circuit-bench-at-kolhapur-mention-cm-fadnavis-name-know-all/articleshow/123350750.cms</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>'औरंगजेब भारत के किसी भी समाज का हीरो नहीं...', मजार को लेकर फडणवीस ने कही बड़ी बात</t>
+          <t>वो ऐतिहासिक तलवार जिसके लिए बिछाया जा रहा मुंबई में रेड कारपेट… मराठा साम्राज्य से है कनेक्शन</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%AD-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AE%E0%A4%9C-%E0%A4%B0-%E0%A4%95-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC-%E0%A4%A4/ar-AA1IRFiN</t>
+          <t>https://www.tv9hindi.com/india/raje-raghuji-bhosale-sword-history-maharashtra-cm-fadnavis-grand-welcome-3441860.html</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>मराठा सेनापति रघुजी भोंसले की 200 साल पुरानी तलवार पहुंची मुंबई, CM फडणवीस बोले-</t>
+          <t>महाराष्ट्र में बन रही है तीसरी मुंबई, इस जिले का होगा आर्थिक विकास, जानें पूरी जानकारी | News Track in...</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/london-auction-historic-raghuji-bhosale-sword-brought-to-mumbai-devendra-fadnavis-says-indias-heritage-restored-2997814</t>
+          <t>https://newstrack.com/india/third-mumbai-being-built-maharashtra-district-have-economic-development-know-full-details-534715</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>इसमें उनका घाटा...हिंदी-मराठी भाषा विवाद के बीच फडणवीस का बड़ा दावा, बोले- मुंबई का मेयर तो हमारा ही होगा</t>
+          <t>CM फडणवीस ने खेला 'मराठी अस्मिता' का दांव, उपराष्ट्रपति चुनाव में उद्धव-पवार पर बना दबाव</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%87%E0%A4%B8%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%89%E0%A4%A8%E0%A4%95-%E0%A4%98-%E0%A4%9F-%E0%A4%B9-%E0%A4%82%E0%A4%A6-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%AD-%E0%A4%B7-%E0%A4%B5-%E0%A4%B5-%E0%A4%A6-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%9A-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%A6-%E0%A4%B5-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%95-%E0%A4%AE%E0%A5%87%E0%A4%AF%E0%A4%B0-%E0%A4%A4-%E0%A4%B9%E0%A4%AE-%E0%A4%B0-%E0%A4%B9-%E0%A4%B9-%E0%A4%97/ar-AA1ImpaC?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://navbharatlive.com/maharashtra/political-battle-over-nda-candidate-radhakrishnan-cm-fadnavis-seeks-support-from-uddhav-thackeray-and-sharad-pawar-1321873.html</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>मुंबई में 6-8 घंटे में 177 मिलीमीटर बारिश हुई: फडणवीस</t>
+          <t>महाराष्ट्र किसानों को मिलेगी बड़ी राहत, CM फडणवीस जल्द करेंगे कर्जमाफी की घोषणा</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/mumbai-received-177-mm-of-rain-in-6-8-hours-fadnavis/856688/</t>
+          <t>https://navbharatlive.com/maharashtra/guardian-minister-sanjay-rathore-claims-cm-fadnavis-may-announce-a-loan-waiver-for-farmers-1322081.html</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>फडणवीस की पत्नी के खिलाफ अपमानजनक पोस्ट : दो लोगों की अग्रिम जमानत अर्जी खारिज</t>
+          <t>बाढ़ संकट पर अबू आजमी का CM फडणवीस को पत्र, प्रभावितों तक तुरंत राहत पहुंचाने की मांग</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%96-%E0%A4%B2-%E0%A4%AB-%E0%A4%85%E0%A4%AA%E0%A4%AE-%E0%A4%A8%E0%A4%9C%E0%A4%A8%E0%A4%95-%E0%A4%AA-%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%A6-%E0%A4%B2-%E0%A4%97-%E0%A4%82-%E0%A4%95-%E0%A4%85%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%9C%E0%A4%AE-%E0%A4%A8%E0%A4%A4-%E0%A4%85%E0%A4%B0%E0%A5%8D%E0%A4%9C-%E0%A4%96-%E0%A4%B0-%E0%A4%9C/ar-AA1Je80j?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://navbharatlive.com/latest-news/abu-azmi-wrote-a-letter-to-cm-devendra-fadnavis-asking-him-to-send-relief-supplies-to-flood-affected-region-1322005.html</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>नांदेड़ में भारी बारिश के कारण पांच लोग लापता, कई व्यक्ति फंसे : मुख्यमंत्री फडणवीस</t>
+          <t>नांदेड़ में मूसलधार बारिश से हाहाकार, CM फडणवीस की निगरानी में राहत कार्य तेज</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/five-people-missing-many-people-stranded-due-to-heavy-rains-in-nanded-chief-minister-fadnavis/856679/</t>
+          <t>https://navbharatlive.com/maharashtra/heavy-rains-cause-havoc-in-nanded-rescue-operation-intensified-under-the-supervision-of-cm-fadnavis-1321752.html</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Raghuji Bhosale: आज मुंबई आएगी रघुजी भोसले की की ऐतिहासिक तलवार, सीएम फडणवीस करेंगे स्वागत</t>
+          <t>CM फडणवीस लगा रहे जोर, अधिकारी कर रहे मनामानी, FIA ने जतायी नाराजगी</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/india/raghuji-bhosale-historic-sword-will-arrive-in-mumbai-today-cm-fadnavis-will-welcome-it/2886138</t>
+          <t>https://navbharatlive.com/maharashtra/federation-of-industries-association-is-angry-due-to-ignorance-of-msme-sector-in-vidarbha-1322498.html</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Mumbai Rain: 24 घंटे की बारिश से मुंबई की सांस फूली, CM देवेंद्र फडणवीस ने पड़ोसी राज्यों से किया संपर्क</t>
+          <t>अबू आजमी ने सीएम देवेंद्र फडणवीस को लिखा पत्र, बाढ़ प्रभावित इलाकों में राहत सामग्री पहुंचाने की मांग की</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/india/mumbai-rains-today-imd-red-alert-warning-waterlogging-traffic-update/2886161</t>
+          <t>https://www.newsnationtv.com/abu-azmi-ne-cm-devendra-fadnavis-ko-likha-patra-badh-prabhavit-ilakon-mein-rahat-pahunchane-ki-mang-ki--20250818191027/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में भारी बारिश का कहर, 16 जिलों में रेड अलर्ट, बचाव दल तैनात</t>
+          <t>Maharashtra Live News 18 Aug: एक क्लिक में पढ़े महाराष्ट्र की दिन भर की बड़ी खब़रें...</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-heavy-rainfall-flood-alert-red-and-orange-alerts-issued-relief-operations-mumbai-rain-ann-2997660</t>
+          <t>https://navbharatlive.com/maharashtra/latest-live-updates-maharashtra-politics-crime-nagpur-news-mumbai-pune-18-august-1321138.html</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>आज सपना पूरा हो गया... चीफ जस्टिस गवई ने ऐसा क्यों कहा, सीएम फडणवीस का लिया नाम</t>
+          <t>Mumbai News: महाराष्ट्र में मूसलाधार बारिश से हाहाकार, मुख्यमंत्री की हाईलेवल बैठक, विशेष सत्र बुलाने की मांग | Heavy rains cause havoc in Maharashtra, high level meeting of Chief Minister, demand for calling special s</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/cji-br-gavai-said-our-dream-has-been-fulfilled-over-bombay-high-court-new-circuit-bench-at-kolhapur-mention-cm-fadnavis-name-know-all/articleshow/123350750.cms</t>
+          <t>https://www.bhaskarhindi.com/city/mumbai/mumbai-news-heavy-rains-cause-havoc-in-maharashtra-high-level-meeting-of-chief-minister-demand-for-calling-special-session-1174171</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में भारी बारिश से सात लोगों की मौत, 200 ग्रामीण फंसे</t>
+          <t>राष्ट्रीय: मुंबई में भारी बारिश के बीच सुचारू रूप से चल रही मेट्रो, सीएम फडणवीस ने की तारीफ</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AD-%E0%A4%B0-%E0%A4%AC-%E0%A4%B0-%E0%A4%B6-%E0%A4%B8%E0%A5%87-%E0%A4%B8-%E0%A4%A4-%E0%A4%B2-%E0%A4%97-%E0%A4%82-%E0%A4%95-%E0%A4%AE-%E0%A4%A4-200-%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%A3-%E0%A4%AB%E0%A4%82%E0%A4%B8%E0%A5%87/ar-AA1KKl3K</t>
+          <t>https://www.bhaskarhindi.com/other/news-1174019</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>वो ऐतिहासिक तलवार जिसके लिए बिछाया जा रहा मुंबई में रेड कारपेट… मराठा साम्राज्य से है कनेक्शन</t>
+          <t>महाराष्ट्र : भारी बारिश के बाद नांदेड़ में राहत कार्य तेज, प्रशासन के संपर्क में सीएम फडणवीस</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/india/raje-raghuji-bhosale-sword-history-maharashtra-cm-fadnavis-grand-welcome-3441860.html</t>
+          <t>https://www.newsnationtv.com/maharashtra-bhari-barish-ke-baad-nanded-mein-rahat-bachav-karya-tez-jiladhikariyon-ke-sampark-mein-cm-fadnavis--20250818144516/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में बन रही है तीसरी मुंबई, इस जिले का होगा आर्थिक विकास, जानें पूरी जानकारी | News Track in...</t>
+          <t>CM फडणवीस ने एनडीए के उपराष्ट्रपति पद के नामांकन पर सीपी राधाकृष्णन को शॉल भेंट की</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>https://newstrack.com/india/third-mumbai-being-built-maharashtra-district-have-economic-development-know-full-details-534715</t>
+          <t>https://jantaserishta.com/local/maharashtra/cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vice-president-nomination-4218433</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>CM फडणवीस ने खेला 'मराठी अस्मिता' का दांव, उपराष्ट्रपति चुनाव में उद्धव-पवार पर बना दबाव</t>
+          <t>राज्य को बाढ़ आपदा घोषित करो… विशेष अधिवेशन बुलाओ… एनसीपी प्रदेश अध्यक्ष ने की सीएम से मांग</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/political-battle-over-nda-candidate-radhakrishnan-cm-fadnavis-seeks-support-from-uddhav-thackeray-and-sharad-pawar-1321873.html</t>
+          <t>https://www.hindisaamana.com/declare-the-state-a-flood-disaster-call-a-special-session-ncp-state-president-made-a-demand-to-the-cm/</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>महाराष्ट्र किसानों को मिलेगी बड़ी राहत, CM फडणवीस जल्द करेंगे कर्जमाफी की घोषणा</t>
+          <t>(लीड)महाराष्ट्र में मूसलाधार बारिश से हाहाकार, सात लोगों की मौत</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/guardian-minister-sanjay-rathore-claims-cm-fadnavis-may-announce-a-loan-waiver-for-farmers-1322081.html</t>
+          <t>https://livevns.news/National/panic-in-maharashtra-due-to-heavy-rainphp/cid17258961.htm</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>बाढ़ संकट पर अबू आजमी का CM फडणवीस को पत्र, प्रभावितों तक तुरंत राहत पहुंचाने की मांग</t>
+          <t>Mumbai: राज्यपाल की उपराष्ट्रपति पद की उम्मीदवारी पर मुख्यमंत्री ने जताया हर्ष</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/latest-news/abu-azmi-wrote-a-letter-to-cm-devendra-fadnavis-asking-him-to-send-relief-supplies-to-flood-affected-region-1322005.html</t>
+          <t>https://jantaserishta.com/local/maharashtra/mumbai-chief-minister-expressed-happiness-over-the-candidature-of-the-governor-for-the-post-of-vice-president-mumbai--4218462</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>नांदेड़ में मूसलधार बारिश से हाहाकार, CM फडणवीस की निगरानी में राहत कार्य तेज</t>
+          <t>अटल सेतु के पास रायगढ़ में बसेगी तीसरी मुंबई, जानें महाराष्ट्र सरकार का पूरा मास्टर प्लान क्या</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/heavy-rains-cause-havoc-in-nanded-rescue-operation-intensified-under-the-supervision-of-cm-fadnavis-1321752.html</t>
+          <t>https://samacharnama.com/states/maharashtra-news/maharashtra-governments-master-plan-to-set-up-third-mumbai/cid17261301.htm</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>CM फडणवीस लगा रहे जोर, अधिकारी कर रहे मनामानी, FIA ने जतायी नाराजगी</t>
+          <t>लंदन से आई मराठा साम्राज्य की शान! रघुजी ?...</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/federation-of-industries-association-is-angry-due-to-ignorance-of-msme-sector-in-vidarbha-1322498.html</t>
+          <t>https://bharatexpress.com/india/raghuji-bhosale-historic-sword-returned-from-london-grand-welcome-in-mumbai-553050</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>कोल्हापुर में CJI गवई ने की सीएम और डिप्टी सीएम के सामने उनकी तारीफ, बोले- "जो लोग शिकायत कर रहे वे देवेंद्र फडणवीस और एकनाथ शिंदे के बारे में नहीं जानते…"</t>
+          <t>Aakar Patel| New Maharashtra Security Law Open To Abuse, Threatens Rights; Say ‘No’ To It</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>https://lalluram.com/in-kolhapur-cji-gavai-praised-him-in-front-of-cm-and-deputy-cm-said-those-who-are-complaining-do-not-know-about-devendra-fadnavis-and-eknath-shinde/</t>
+          <t>https://www.asianage.com/opinion/columnists/aakar-patel-new-maharashtra-security-law-open-to-abuse-threatens-rights-say-no-to-it-1898277</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>अबू आजमी ने सीएम देवेंद्र फडणवीस को लिखा पत्र, बाढ़ प्रभावित इलाकों में राहत सामग्री पहुंचाने की मांग की</t>
+          <t>Maharashtra CM Fadnavis, Dy CM Shinde congratulate Governor CP Radhakrishnan on NDA's VP nomination</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>https://www.newsnationtv.com/abu-azmi-ne-cm-devendra-fadnavis-ko-likha-patra-badh-prabhavit-ilakon-mein-rahat-pahunchane-ki-mang-ki--20250818191027/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination-23589945</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Maharashtra Live News 18 Aug: एक क्लिक में पढ़े महाराष्ट्र की दिन भर की बड़ी खब़रें...</t>
+          <t>Heavy rainfall causes 7 deaths, crop loss in Maharashtra as alerts continue</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/latest-live-updates-maharashtra-politics-crime-nagpur-news-mumbai-pune-18-august-1321138.html</t>
+          <t>https://www.msn.com/en-in/news/India/heavy-rainfall-causes-7-deaths-crop-loss-in-maharashtra-as-alerts-continue/ar-AA1KK6Zt</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Mumbai News: महाराष्ट्र में मूसलाधार बारिश से हाहाकार, मुख्यमंत्री की हाईलेवल बैठक, विशेष सत्र बुलाने की मांग | Heavy rains cause havoc in Maharashtra, high level meeting of Chief Minister, demand for calling special s</t>
+          <t>Maharashtra CM Devendra Fadnavis Says ‘Third Mumbai’ Being Developed in Raigad District Will Open New</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/city/mumbai/mumbai-news-heavy-rains-cause-havoc-in-maharashtra-high-level-meeting-of-chief-minister-demand-for-calling-special-session-1174171</t>
+          <t>https://www.latestly.com/india/news/maharashtra-cm-devendra-fadnavis-says-third-mumbai-being-developed-in-raigad-district-will-open-new-chapter-of-economic-development-7064927.html</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>राष्ट्रीय: मुंबई में भारी बारिश के बीच सुचारू रूप से चल रही मेट्रो, सीएम फडणवीस ने की तारीफ</t>
+          <t>Maharashtra CM Fadnavis, Dy CM Shinde congratulate Governor CP Radhakrishnan on NDA's VP nomination</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/news-1174019</t>
+          <t>https://thenewsmill.com/2025/08/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination/</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>फडणवीस ने कहा, 'तीसरी मुंबई' से एमएमआर का होगा विकास</t>
+          <t>"Observe precaution": Maharashtra CM warns about severe weather conditions in state</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/business/third-mumbai-will-lead-to-development-of-mmr-says-fadnavis-3213495.html</t>
+          <t>https://thenewsmill.com/2025/08/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state/</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>महाराष्ट्र : भारी बारिश के बाद नांदेड़ में राहत कार्य तेज, प्रशासन के संपर्क में सीएम फडणवीस</t>
+          <t>Mumbai got 177mm rain in 6-8 hour period, says CM; more to come amid high tides</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>https://www.newsnationtv.com/maharashtra-bhari-barish-ke-baad-nanded-mein-rahat-bachav-karya-tez-jiladhikariyon-ke-sampark-mein-cm-fadnavis--20250818144516/</t>
+          <t>https://www.newsdrum.in/national/mumbai-got-177mm-rain-in-6-8-hour-period-says-cm-more-to-come-amid-high-tides-9672488</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>CM फडणवीस ने एनडीए के उपराष्ट्रपति पद के नामांकन पर सीपी राधाकृष्णन को शॉल भेंट की</t>
+          <t>NCP (SP) targets Maha minister over Rs 5,000 cr scam in Navi Mumbai’s CIDCO land; demands his resignation</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vice-president-nomination-4218433</t>
+          <t>https://www.socialnews.xyz/2025/08/18/ncp-sp-targets-maha-minister-over-rs-5000-cr-scam-in-navi-mumbais-cidco-land-demands-his-resignation/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=ncp-sp-targets-maha-minister-over-rs-5000-cr-scam-in-navi-mumbais-cidco-land-demands-his-resignation</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>राज्य को बाढ़ आपदा घोषित करो… विशेष अधिवेशन बुलाओ… एनसीपी प्रदेश अध्यक्ष ने की सीएम से मांग</t>
+          <t>CM to inaugurate additional water supply scheme</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/declare-the-state-a-flood-disaster-call-a-special-session-ncp-state-president-made-a-demand-to-the-cm/</t>
+          <t>https://www.lokmattimes.com/aurangabad/cm-to-inaugurate-additional-water-supply-scheme/</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>(लीड)महाराष्ट्र में मूसलाधार बारिश से हाहाकार, सात लोगों की मौत</t>
+          <t>Mumbai Rains LIVE Updates: 250–300 mm Downpour Likely Tonight; Schools &amp; Colleges To Remain Shut On Tuesday</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>https://livevns.news/National/panic-in-maharashtra-due-to-heavy-rainphp/cid17258961.htm</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-live-updates-check-for-latest-updates-of-all-the-happeneings-in-mumbai</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>उपराष्ट्रपति चुनाव में भाजपा का दांव, सीपी राधाकृष्णन उम्मीदवार, महाराष्ट्र की राजनीति में बढ़ी हलचल</t>
+          <t>Mumbai rains: IMD issues red alert as downpour continues; schools, colleges &amp; Govt offices shut</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/maharashtra/vice-president-election-bjp-candidate-cp-radhakrishnan-devendra-fadnavis-54-803924</t>
+          <t>https://newslivetv.com/mumbai-rains-imd-issues-red-alert/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>किसानों को जल्द मिल सकता है कर्जमाफी का तोहफा, मंत्री संजय राठोड़ का बड़ा बयान</t>
+          <t>पुढील १२ तास मुंबईसाठी अत्यंत महत्त्वाचे, मुख्यमंत्री फडणवीस पावसाबाबत काय म्हणाले?</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/maharashtra/farmer-loan-waiver-maharashtra-sanjay-rathod-devendra-fadnavis-54-804134</t>
+          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-review-mumbai-rain-says-next-12-hours-important-for-mumbai-and-mmr-region-1460967.html</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Mumbai: राज्यपाल की उपराष्ट्रपति पद की उम्मीदवारी पर मुख्यमंत्री ने जताया हर्ष</t>
+          <t>राज्यात अतिवृष्टीमुळे मुख्यमंत्री देवेंद्र फडणवीस यांचे सर्व यंत्रणांना सतर्कतेचे निर्देश; नांदेड जिल्ह्यात लष्कराची मदत</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/mumbai-chief-minister-expressed-happiness-over-the-candidature-of-the-governor-for-the-post-of-vice-president-mumbai--4218462</t>
+          <t>https://www.loksatta.com/mumbai/chief-minister-devendra-fadnavis-has-directed-all-agencies-to-be-on-alert-due-to-heavy-rains-in-the-maharashtra-mumbai-print-news-amy-95-5313479/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>अटल सेतु के पास रायगढ़ में बसेगी तीसरी मुंबई, जानें महाराष्ट्र सरकार का पूरा मास्टर प्लान क्या</t>
+          <t>Mumbai Rain : मुंबईत संध्याकाळी समुद्राला भरती, पुढील 12 तास महत्त्वाचे, पावसाच्या थैमानानंतर</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>https://samacharnama.com/states/maharashtra-news/maharashtra-governments-master-plan-to-set-up-third-mumbai/cid17261301.htm</t>
+          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-on-mumbai-maharashtra-rain-today-visit-disaster-management-department-bmc-marathi-news-1377962</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>लंदन से आई मराठा साम्राज्य की शान! रघुजी ?...</t>
+          <t>राज्यभरात पावसाचा हाहाकार, मुख्यमंत्री देवेंद्र फडणवीस यांनी घेतला आढावा; सर्व यंत्रणांना सतर्कतेचे निर्देश</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>https://bharatexpress.com/india/raghuji-bhosale-historic-sword-returned-from-london-grand-welcome-in-mumbai-553050</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/rains-lashed-the-state-chief-minister-devendra-fadnavis-took-stock-instructed-all-agencies-to-be-alert.html</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Aakar Patel| New Maharashtra Security Law Open To Abuse, Threatens Rights; Say ‘No’ To It</t>
+          <t>Mumbai Rain Update : समुद्रातून येतंय मुंबईवर मोठं संकट, पुढच्या 12 तासांत तुफान पाऊस, फडणवीस काय...</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>https://www.asianage.com/opinion/columnists/aakar-patel-new-maharashtra-security-law-open-to-abuse-threatens-rights-say-no-to-it-1898277</t>
+          <t>https://www.tv9marathi.com/maharashtra/mumbai-rain-alert-cm-devendra-fadnavis-said-mumbai-have-red-alert-school-holiday-declared-know-detail-information-in-marathi-1472488.html</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by Maharashtra CM Devendra Fadnavis</t>
+          <t>Farmers Loan Waiver: बावनकुळेंनंतर महायुती सरकारमधील 'या' मंत्र्याची कर्जमाफीबाबत मोठी अपडेट; म्हणाले,'CM फडणवीस लवकरच...'</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/sanjay-rathod-update-farmer-loan-waiver-devendra-fadnavis-dk88</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>"Observe precaution": Maharashtra CM warns about severe weather conditions in state</t>
+          <t>राज्यात अतिवृष्टीच्या पार्श्वभूमीवर प्रशासन अलर्ट मोडवर! मुख्यमंत्री देवेंद्र फडणवीस यांचे सतर्कतेचे निर्देश</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/08/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state/</t>
+          <t>https://www.navarashtra.com/maharashtra/cm-devendra-fadnavis-took-review-of-rain-situation-at-state-disaster-management-centre-in-the-ministry-963383.html</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CM to inaugurate additional water supply scheme</t>
+          <t>Devendra Fadnavis : महाराष्ट्रातील माणसाला सर्वांनी समर्थन द्यावं; फडणवीस यांचे मविआला आवाहन</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/aurangabad/cm-to-inaugurate-additional-water-supply-scheme/</t>
+          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-appeals-to-maharashtra-mps-to-support-cp-radhakrishnan-for-vice-president/913103/</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Mumbai Rains LIVE Updates: 250–300 mm Downpour Likely Tonight; Schools &amp; Colleges To Remain Shut On Tuesday</t>
+          <t>सरदार रघुजी भोसले यांची ऐतिहासिक तलवार मुंबईत दाखल; मुख्यमंत्र्यांच्या हस्ते होणार लोकार्पण</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-news-live-updates-check-for-latest-updates-of-all-the-happeneings-in-mumbai</t>
+          <t>https://www.etvbharat.com/mr/!state/sword-of-maratha-commander-raghuji-bhosale-returns-to-mumbai-to-be-unveiled-at-exhibition-by-cm-fadnavis-maharashtra-news-mhs25081803521</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Mumbai rains: IMD issues red alert as downpour continues; schools, colleges &amp; Govt offices shut</t>
+          <t>नवीन पिढीला इतिहासाशी जोडण्याचे कार्य सुरू; मुख्यमंत्री देवेंद्र फडणवीस यांचे प्रतिपादन</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>https://newslivetv.com/mumbai-rains-imd-issues-red-alert/</t>
+          <t>https://www.loksatta.com/mumbai/devendra-fadnavis-asserts-that-the-work-of-connecting-the-new-generation-with-history-is-underway-mumbai-print-news-amy-95-5313830/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>राज्यात अतिवृष्टीमुळे मुख्यमंत्री देवेंद्र फडणवीस यांचे सर्व यंत्रणांना सतर्कतेचे निर्देश; नांदेड जिल्ह्यात लष्कराची मदत</t>
+          <t>Maharashtra Rain Updates: मुंबईसाठी पुढील 12 तास महत्त्वाचे, राज्यात स्थिती काय? CM फडणवीसांनी सगळं सांगितल...</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/chief-minister-devendra-fadnavis-has-directed-all-agencies-to-be-on-alert-due-to-heavy-rains-in-the-maharashtra-mumbai-print-news-amy-95-5313479/</t>
+          <t>https://news18marathi.com/maharashtra/maharashtra-rain-update-cm-devendra-fadnavis-hold-meeting-with-district-administration-1460734.html</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>पुढील १२ तास मुंबईसाठी अत्यंत महत्त्वाचे, मुख्यमंत्री फडणवीस पावसाबाबत काय म्हणाले?</t>
+          <t>CM देवेंद्र फडणवीस लवकरच कर्जमाफीची घोषणा करतील महायुतीच्या मंत्र्यांनी दिली</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-review-mumbai-rain-says-next-12-hours-important-for-mumbai-and-mmr-region-1460967.html</t>
+          <t>https://marathi.abplive.com/news/politics/cm-devendra-fadnavis-will-soon-announce-loan-waiver-farmers-mahayuti-ministers-sanjay-rathod-gave-information-yavatmal-1377983</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Mumbai Rain : मुंबईत संध्याकाळी समुद्राला भरती, पुढील 12 तास महत्त्वाचे, पावसाच्या थैमानानंतर</t>
+          <t>Mumbai Rain: मुंबईत उद्या शाळांना सुट्टी? पुढचे १२ तास महत्वाचे, मुख्यमंत्री नेमकं काय म्हणाले?</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-on-mumbai-maharashtra-rain-today-visit-disaster-management-department-bmc-marathi-news-1377962</t>
+          <t>https://saamtv.esakal.com/amp/story/mumbai-pune/mumbai-rain-alert-cm-devendra-fadnavis-said-mumbai-schools-declared-holiday-on-tomorrow-bmc-to-decide-pvm91</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Mumbai Rain Update : समुद्रातून येतंय मुंबईवर मोठं संकट, पुढच्या 12 तासांत तुफान पाऊस, फडणवीस काय...</t>
+          <t>सरगुन मेहता आणि रवी दुबे यांनी दिली आनंदाची बातमी, वाचा सविस्तर...</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/mumbai-rain-alert-cm-devendra-fadnavis-said-mumbai-have-red-alert-school-holiday-declared-know-detail-information-in-marathi-1472488.html</t>
+          <t>https://www.etvbharat.com/mr/!entertainment/ravi-dubey-and-sargun-mehta-are-making-headlines-with-their-new-home-maharashtra-news-mhs25081802265</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>राज्यभरात पावसाचा हाहाकार, मुख्यमंत्री देवेंद्र फडणवीस यांनी घेतला आढावा; सर्व यंत्रणांना सतर्कतेचे निर्देश</t>
+          <t>मोठी बातमी! शेतकऱ्यांची कर्जमाफी होणार, मुख्यमंत्री घोषणा करणार, बड्या मंत्र्याने दिली माहिती</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/rains-lashed-the-state-chief-minister-devendra-fadnavis-took-stock-instructed-all-agencies-to-be-alert.html</t>
+          <t>https://www.tv9marathi.com/maharashtra/big-update-on-farmer-loan-waiver-cm-fadnavis-will-do-announcement-says-minister-sanjay-rathod-1472819.html</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>राज्यात अतिवृष्टीच्या पार्श्वभूमीवर प्रशासन अलर्ट मोडवर! मुख्यमंत्री देवेंद्र फडणवीस यांचे सतर्कतेचे निर्देश</t>
+          <t>गौरवशाली इतिहासाशी नव्या पीढीला जोडण्याचं काम रघुजीराजे भोसल्यांची ऐतिहासिक</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/cm-devendra-fadnavis-took-review-of-rain-situation-at-state-disaster-management-centre-in-the-ministry-963383.html</t>
+          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-mumbai-exhibition-of-nagpur-raghuji-raje-bhosle-historical-sword-marathi-news-1378075</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Farmers Loan Waiver: बावनकुळेंनंतर महायुती सरकारमधील 'या' मंत्र्याची कर्जमाफीबाबत मोठी अपडेट; म्हणाले,'CM फडणवीस लवकरच...'</t>
+          <t>Mumbai Rain Updates : सात जणांचा मृत्यू ते शेकडो गावे बाधित; राज्यभरात अतिवृष्टीमुळे कुठे काय घडलं?</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/amp/story/maharashtra/vidarbha/sanjay-rathod-update-farmer-loan-waiver-devendra-fadnavis-dk88</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-updates-18-august-heavy-rainfall-mumbai-navi-mumbai-kolhapur-raigad-sindhudurag-local-train-latest-updates-traffic-news-rak-94-5312079/</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis : महाराष्ट्रातील माणसाला सर्वांनी समर्थन द्यावं; फडणवीस यांचे मविआला आवाहन</t>
+          <t>मोठी बातमी! नाराजी भोवली, शिवसेना शिंदे गटाला सर्वात मोठा धक्का, बड्या नेत्यानं सोडली एकनाथ शिंदेंची...</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-appeals-to-maharashtra-mps-to-support-cp-radhakrishnan-for-vice-president/913103/</t>
+          <t>https://www.tv9marathi.com/maharashtra/big-blow-to-eknath-shinde-big-leader-of-shiv-sena-shinde-group-will-join-bjp-1472541.html</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>सरदार रघुजी भोसले यांची ऐतिहासिक तलवार मुंबईत दाखल; मुख्यमंत्र्यांच्या हस्ते होणार लोकार्पण</t>
+          <t>प्रशासन सतर्क : नागरिकांनी घराबाहेर पडू नये: मुख्यमंत्री फडणवीस !</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/sword-of-maratha-commander-raghuji-bhosale-returns-to-mumbai-to-be-unveiled-at-exhibition-by-cm-fadnavis-maharashtra-news-mhs25081803521</t>
+          <t>https://vishwanewsmarathi.com/administrator-citizens-should-not-stay-home-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis : अख्खा पक्ष विरोधात, पण या दिग्गज नेत्याचा फडणवीसांना पाठिंबा, एका पत्राने राजकीय वर्तु...</t>
+          <t>मुख्यमंत्री लवकरच शेतकरी कर्जमाफीची घोषणा करणार ; शिंदेंच्या मंत्र्यांचा दावा !</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/cm-devendra-fadnavis-gets-support-from-congress-leader-nitin-raut-letter-goes-viral-1461146.html</t>
+          <t>https://vishwanewsmarathi.com/chief-minister-will-soon-announce-farmer-loan-waiver-shindes-ministers-claim/</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>नवीन पिढीला इतिहासाशी जोडण्याचे कार्य सुरू; मुख्यमंत्री देवेंद्र फडणवीस यांचे प्रतिपादन</t>
+          <t>लवकरच कर्जमाफीची घोषणा होणार? महायुती सरकारमधील मंत्र्यांनी दिले संकेत</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/devendra-fadnavis-asserts-that-the-work-of-connecting-the-new-generation-with-history-is-underway-mumbai-print-news-amy-95-5313830/</t>
+          <t>https://marathi.oneindia.com/maharashtra/maharashtra-cm-fadnavis-loan-waiver-announcement-035127.html</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>CM देवेंद्र फडणवीस लवकरच कर्जमाफीची घोषणा करतील महायुतीच्या मंत्र्यांनी दिली</t>
+          <t>Devendra Fadnavis : महाराष्ट्रातील माणसाला सर्वांनी समर्थन द्यावे; मुख्यमंत्री फडणवीस यांचे मविआच्या खासदारांना आवाहन</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/cm-devendra-fadnavis-will-soon-announce-loan-waiver-farmers-mahayuti-ministers-sanjay-rathod-gave-information-yavatmal-1377983</t>
+          <t>https://www.dainikprabhat.com/devendra-fadnavis-everyone-should-support-the-people-of-maharashtra-chief-minister-fadnavis-appeals-to-m-v-a-mps/</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Mumbai Rain: मुंबईत उद्या शाळांना सुट्टी? पुढचे १२ तास महत्वाचे, मुख्यमंत्री नेमकं काय म्हणाले?</t>
+          <t>मुख्यमंत्री फडणवीस लवकरच शेतकरी कर्जमाफीची घोषणा करण्याची शक्यता</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/mumbai-pune/mumbai-rain-alert-cm-devendra-fadnavis-said-mumbai-schools-declared-holiday-on-tomorrow-bmc-to-decide-pvm91</t>
+          <t>https://www.dainikprabhat.com/cm-fadnavis-likely-to-announce-farm-loan-waiver-soon/</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>मोठी बातमी! नाराजी भोवली, शिवसेना शिंदे गटाला सर्वात मोठा धक्का, बड्या नेत्यानं सोडली एकनाथ शिंदेंची...</t>
+          <t>महाराष्ट्रातील शेतकऱ्यांना मोठा दिलासा, मुख्यमंत्री फडणवीस लवकरच कर्जमाफीची घोषणा करणार</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/big-blow-to-eknath-shinde-big-leader-of-shiv-sena-shinde-group-will-join-bjp-1472541.html</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/big-relief-for-farmers-in-maharashtra-chief-minister-fadnavis-will-soon-announce-loan-waiver-125081900014_1.html</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Maharashtra Rain Updates: मुंबईसाठी पुढील 12 तास महत्त्वाचे, राज्यात स्थिती काय? CM फडणवीसांनी सगळं सांगितल...</t>
+          <t>एकनाथ शिंदेंना सोलापुरात मोठा धक्का : नेत्यांने सोडली साथ !</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/maharashtra-rain-update-cm-devendra-fadnavis-hold-meeting-with-district-administration-1460734.html</t>
+          <t>https://vishwanewsmarathi.com/big-setback-for-eknath-shinde-in-solapur-leaders-leave-support/</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>गौरवशाली इतिहासाशी नव्या पीढीला जोडण्याचं काम रघुजीराजे भोसल्यांची ऐतिहासिक</t>
+          <t>युवकांसाठी सुवर्णसंधी! महाराष्ट्रातील 'या' जिल्ह्यात आयटी पार्क होणार, मुख्यमंत्र्यांचा मोठा निर्णय</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-mumbai-exhibition-of-nagpur-raghuji-raje-bhosle-historical-sword-marathi-news-1378075</t>
+          <t>https://www.thodkyaat.com/it-park-in-solapur-announced-by-cm-devendra-fadnavis-boost-to-jobs-and-development/</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Mumbai Rain Updates : सात जणांचा मृत्यू ते शेकडो गावे बाधित; राज्यभरात अतिवृष्टीमुळे कुठे काय घडलं?</t>
+          <t>School Closed | मोठी बातमी! पावसामुळे आज महाराष्ट्रातील 'या' जिल्ह्यातील शाळा बंद</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-updates-18-august-heavy-rainfall-mumbai-navi-mumbai-kolhapur-raigad-sindhudurag-local-train-latest-updates-traffic-news-rak-94-5312079/</t>
+          <t>https://www.thodkyaat.com/maharashtra-school-closed-tomorrow/</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>मोठी बातमी! शेतकऱ्यांची कर्जमाफी होणार, मुख्यमंत्री घोषणा करणार, बड्या मंत्र्याने दिली माहिती</t>
+          <t>ना. पंकजाताई मुंडे यांना ‘कोहिनूर ऑफ इंडिया’ अवाॅर्ड, लोकमत वृतपत्र समुहाने केला सन्मान; लंडन येथे पार पडला दिमाखदार सोहळा</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/big-update-on-farmer-loan-waiver-cm-fadnavis-will-do-announcement-says-minister-sanjay-rathod-1472819.html</t>
+          <t>https://lokashanews.com/28165/</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>प्रशासन सतर्क : नागरिकांनी घराबाहेर पडू नये: मुख्यमंत्री फडणवीस !</t>
+          <t>Mumbai Rains : गुडघाभर पाणी, समोर रस्ताही दिसेना, लोकल रखडल्या आठवड्याच्या सुरुवातीला पावसानं मुंबईकरांची दाणादाण, पहा PHOTO</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/administrator-citizens-should-not-stay-home-chief-minister/</t>
+          <t>https://marathi.asianetnews.com/mumbai/mumbai-heavy-rain-waterlogging-local-delays-school-shutdown/photoshow-at2tgam</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>मुख्यमंत्री लवकरच शेतकरी कर्जमाफीची घोषणा करणार ; शिंदेंच्या मंत्र्यांचा दावा !</t>
+          <t>Mumbai News: गोल्डमन सॅक्सचे मुंबई नवे कार्यालय तिसऱ्या मुंबईचा नवा अध्याय - देवेंद्र फडणवीस</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/chief-minister-will-soon-announce-farmer-loan-waiver-shindes-ministers-claim/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/goldman-sachs-new-mumbai-office-is-a-new-chapter-for-third-mumbai-devendra-fadnavis-89597</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>लवकरच कर्जमाफीची घोषणा होणार? महायुती सरकारमधील मंत्र्यांनी दिले संकेत</t>
+          <t>Mumbai Rain News: मुंबईत किती ठिकाणी पाणी साचलं? ट्राफिकची स्थिती काय? मुख्यमंत्र्यांनी दिली A to Z माहिती</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>https://marathi.oneindia.com/maharashtra/maharashtra-cm-fadnavis-loan-waiver-announcement-035127.html</t>
+          <t>https://marathi.ndtv.com/cities/mumbai-rain-news-chief-minister-devendra-fadnavis-gave-information-about-the-rainfall-situation-in-mumbai-9107883</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>मुख्यमंत्री फडणवीस लवकरच शेतकरी कर्जमाफीची घोषणा करण्याची शक्यता</t>
+          <t>“मुंबईत पुढच्या १२ तासांत तुफान पाऊस, रेड अलर्ट आणि…”; मुख्यमंत्री देवेंद्र फडणवीस यांनी काय माहिती दिली?</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/cm-fadnavis-likely-to-announce-farm-loan-waiver-soon/</t>
+          <t>https://www.loksatta.com/maharashtra/mumbai-rain-alert-cm-devendra-fadnavis-said-mumbai-have-red-alert-school-holiday-declared-know-details-scj-81-5312934/</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>शेतकरी कर्जमाफीबाबत महायुतीमधील मंत्र्याने दिली महत्त्वाची माहिती; “देवेंद्र फडणवीस लवकरच….”</t>
+          <t>Pune News : मुख्यमंत्री फडणवीसांमुळे पुणेकरांना रोज मनस्ताप? काँग्रेसचा गंभीर आरोप</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/mahayuti-minister-gives-important-information-regarding-farmer-loan-waiver-devendra-fadnavis-soon/</t>
+          <t>https://sarkarnama.esakal.com/pune/devendra-fadnavis-pune-flyover-inauguration-delay-dk88-sm89</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>महाराष्ट्रातील शेतकऱ्यांना मोठा दिलासा, मुख्यमंत्री फडणवीस लवकरच कर्जमाफीची घोषणा करणार</t>
+          <t>Devendra Fadanvis on Rain Update : मुंबईला रेड अलर्ट ! मुख्यमंत्री देवेंद्र फडणवीस यांनी पावसाबद्दल दिली महत्त्वाची अपडेट</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/big-relief-for-farmers-in-maharashtra-chief-minister-fadnavis-will-soon-announce-loan-waiver-125081900014_1.html</t>
+          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/maharashtra-hevey-rain-update-cm-devendra-fadanvis-gives-important-information-know-about-more-/40070</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>एकनाथ शिंदेंना सोलापुरात मोठा धक्का : नेत्यांने सोडली साथ !</t>
+          <t>महाराष्ट्रात महाभयानक पाऊस! मुख्यमंत्री देवेंद्र फडणवीस यांनी तातडीने साधला शेजारील राज्यांशी संपर्क? कारण अतिशय चिंताजनक</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/big-setback-for-eknath-shinde-in-solapur-leaders-leave-support/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/maharashtra-mumbai-rain-alert-update-chief-minister-devendra-fadnavis-immediately-contacted-the-neighboring-states/933328</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>युवकांसाठी सुवर्णसंधी! महाराष्ट्रातील 'या' जिल्ह्यात आयटी पार्क होणार, मुख्यमंत्र्यांचा मोठा निर्णय</t>
+          <t>Third Mumbai News: तिसरी मुंबई आणि आर्थिक विकासाबाबत CM फडणवीसांचे मोठे विधान</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>https://www.thodkyaat.com/it-park-in-solapur-announced-by-cm-devendra-fadnavis-boost-to-jobs-and-development/</t>
+          <t>https://marathi.ndtv.com/maharashtra/third-mumbai-will-open-a-new-chapter-of-economic-development-says-cm-devendra-fadnavis-9110192</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>School Closed | मोठी बातमी! पावसामुळे आज महाराष्ट्रातील 'या' जिल्ह्यातील शाळा बंद</t>
+          <t>Maharashtra Rain : राज्यासाठी पुढचे दोन दिवस चिंतेचे, 15-16 जिल्ह्यांना अलर्ट, कुठे होणार अतिवृष्टी?...</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>https://www.thodkyaat.com/maharashtra-school-closed-tomorrow/</t>
+          <t>https://www.tv9marathi.com/videos/maharashtra-imd-issues-red-alert-for-16-districts-big-information-by-cm-devendra-fadnavis-reviews-heavy-rains-in-1472606.html</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ना. पंकजाताई मुंडे यांना ‘कोहिनूर ऑफ इंडिया’ अवाॅर्ड, लोकमत वृतपत्र समुहाने केला सन्मान; लंडन येथे पार पडला दिमाखदार सोहळा</t>
+          <t>Mumbai Rains Updates: मुंबईकरांनो पुढील 12 तास अतिशय महत्त्वाचे, CM फडणवीसांनी केले हे आवाहन</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>https://lokashanews.com/28165/</t>
+          <t>https://marathi.ndtv.com/maharashtra/mumbai-rains-update-next-12-hours-are-important-for-mumbai-7-people-died-across-state-in-2-days-cm-fadnavis-appeals-to-citizens-9109288</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Mumbai Rains : गुडघाभर पाणी, समोर रस्ताही दिसेना, लोकल रखडल्या आठवड्याच्या सुरुवातीला पावसानं मुंबईकरांची दाणादाण, पहा PHOTO</t>
+          <t>16 जिल्ह्यांना रेड अलर्ट! राज्याच्या ‘या’ भागात अतिवृष्टी, बचाव पथक सज्ज; CM फडणवीसांची...</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>https://marathi.asianetnews.com/mumbai/mumbai-heavy-rain-waterlogging-local-delays-school-shutdown/photoshow-at2tgam</t>
+          <t>https://www.tv9marathi.com/maharashtra/rain-alert-in-16-districts-heavy-rainfall-in-this-part-of-state-cm-fadnavis-give-information-1472499.html</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Mumbai News: गोल्डमन सॅक्सचे मुंबई नवे कार्यालय तिसऱ्या मुंबईचा नवा अध्याय - देवेंद्र फडणवीस</t>
+          <t>पुण्यात नवीन महापालिकांवरून देवेंद्र फडणवीस आणि अजित पवार यांच्यात मतभेद का?</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/goldman-sachs-new-mumbai-office-is-a-new-chapter-for-third-mumbai-devendra-fadnavis-89597</t>
+          <t>https://www.loksatta.com/pune/devendra-fadnavis-ajit-pawar-dispute-over-new-municipal-corporations-in-pune-district-print-politics-news-css-98-5314697/</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Mumbai Rain News: मुंबईत किती ठिकाणी पाणी साचलं? ट्राफिकची स्थिती काय? मुख्यमंत्र्यांनी दिली A to Z माहिती</t>
+          <t>मुख्यमंत्री देवेंद्र फडणवीसांकडून पावसाचा आढावा: महाराष्ट्रात 4 लाख हेक्टरवरील पिके पाण्यात, उपाययोजनांचे ज...</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/mumbai-rain-news-chief-minister-devendra-fadnavis-gave-information-about-the-rainfall-situation-in-mumbai-9107883</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/cm-devendra-fadnavis-review-maharashtra-flood-135703334.html</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>“मुंबईत पुढच्या १२ तासांत तुफान पाऊस, रेड अलर्ट आणि…”; मुख्यमंत्री देवेंद्र फडणवीस यांनी काय माहिती दिली?</t>
+          <t>Devendra Fadnavis| मुख्यमंत्री देवेंद्र फडणवीस १९ रोजी पैठण तालुक्यात</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/mumbai-rain-alert-cm-devendra-fadnavis-said-mumbai-have-red-alert-school-holiday-declared-know-details-scj-81-5312934/</t>
+          <t>https://pudhari.news/maharashtra/marathwada/chhatrapati-sambhajinagar/devendra-fadnavis-visit-paithan-taluka-19-august-ng81</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Pune News : मुख्यमंत्री फडणवीसांमुळे पुणेकरांना रोज मनस्ताप? काँग्रेसचा गंभीर आरोप</t>
+          <t>तिसरी मुंबई आर्थिक विकासाचा नवा अध्याय – मुख्यमंत्री देवेंद्र फडणवीस</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/pune/devendra-fadnavis-pune-flyover-inauguration-delay-dk88-sm89</t>
+          <t>https://mahasamvad.in/176127/</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Devendra Fadanvis on Rain Update : मुंबईला रेड अलर्ट ! मुख्यमंत्री देवेंद्र फडणवीस यांनी पावसाबद्दल दिली महत्त्वाची अपडेट</t>
+          <t>Maharashtra Politics : एकनाथ शिंदेंची कोण करतंय कोंडी? दिल्ली दौरे वाढण्यामागचं काय कारण?</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/maharashtra-hevey-rain-update-cm-devendra-fadanvis-gives-important-information-know-about-more-/40070</t>
+          <t>https://www.loksatta.com/politics/maharashtra-politics-shiv-sena-eknath-shinde-bjp-devendra-fadnavis-conflict-before-bmc-election-sdp-92-5314661/lite/</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>महाराष्ट्रात महाभयानक पाऊस! मुख्यमंत्री देवेंद्र फडणवीस यांनी तातडीने साधला शेजारील राज्यांशी संपर्क? कारण अतिशय चिंताजनक</t>
+          <t>Maharashtra Heavy Rainfall | राज्यभरात अतिवृष्टीचा कहर; १५ जिल्ह्यांत रेड आणि ऑरेंज अलर्ट, नागरिकांनी घराबाहेर पडू नये: मुख्यमंत्री फडणवीस</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/maharashtra-mumbai-rain-alert-update-chief-minister-devendra-fadnavis-immediately-contacted-the-neighboring-states/933328</t>
+          <t>https://pudhari.news/maharashtra/mumbai/maharashtra-heavy-rainfall-red-orange-alert-15-districts-cm-fadnavis-advisory-as80</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Crop damage : 4 लाख हेक्टर क्षेत्रावरील पिकांची हानी</t>
+          <t>Farmers Loan Waiver: बावनकुळेंनंतर महायुती सरकारमधील 'या' मंत्र्याची कर्जमाफीबाबत मोठी अपडेट; म्हणाले,'CM फडणवीस लवकरच...'</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/crop-damage-4-lakh-hectares-ab96</t>
+          <t>https://sarkarnama.esakal.com/amp/story/maharashtra/vidarbha/sanjay-rathod-update-farmer-loan-waiver-devendra-fadnavis-dk88</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Third Mumbai News: तिसरी मुंबई आणि आर्थिक विकासाबाबत CM फडणवीसांचे मोठे विधान</t>
+          <t>महाराष्ट्रातील खासदारांनी राधाकृष्णन यांना समर्थन द्यावे: मुख्यमंत्री देवेंद्र फडणवीसांचे आवाहन; ठाकरे गट अ...</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/third-mumbai-will-open-a-new-chapter-of-economic-development-says-cm-devendra-fadnavis-9110192</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/c-p-radhakrishnan-vice-president-candidate-fadnavis-urges-support-135703533.html</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Maharashtra Rain : राज्यासाठी पुढचे दोन दिवस चिंतेचे, 15-16 जिल्ह्यांना अलर्ट, कुठे होणार अतिवृष्टी?...</t>
+          <t>पुण्यात मुसळधार पाऊस पडतोय, आम्हाला वर्क फ्रॉम होम द्या! थेट मुख्यमंत्र्यांकडे आयटी कर्मचाऱ्यांची मागणी</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/maharashtra-imd-issues-red-alert-for-16-districts-big-information-by-cm-devendra-fadnavis-reviews-heavy-rains-in-1472606.html</t>
+          <t>https://www.loksatta.com/pune/it-company-employees-demand-work-from-home-due-to-heavy-rain-appeals-cm-devendra-fadnavis-pune-print-news-css-98-5314597/</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Mumbai Rains Updates: मुंबईकरांनो पुढील 12 तास अतिशय महत्त्वाचे, CM फडणवीसांनी केले हे आवाहन</t>
+          <t>पूरस्थितीचा सामना करण्यासाठी सरकारकडून सर्वतोपरी प्रयत्न, अतिवृष्टीचा धोका लक्षात घेऊन लोकांनी खबरदारी घ्यावी, मुख्यमंत्र्यांचं आवाहन</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/mumbai-rains-update-next-12-hours-are-important-for-mumbai-7-people-died-across-state-in-2-days-cm-fadnavis-appeals-to-citizens-9109288</t>
+          <t>https://www.etvbharat.com/mr/!state/maharashtra-government-is-making-every-effort-to-deal-with-the-flood-situation-the-chief-minister-appeals-to-people-to-be-careful-considering-the-risk-of-heavy-rains-maharashtra-news-mhs25081804221</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>पुण्यात नवीन महापालिकांवरून देवेंद्र फडणवीस आणि अजित पवार यांच्यात मतभेद का?</t>
+          <t>CM Relief Fund: रुग्णांसाठी सरकारचा 'हा' विभाग ठरतोय मदतशीर; अमरावती विभागात तब्बल १०.६१ कोटींची मदत</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/devendra-fadnavis-ajit-pawar-dispute-over-new-municipal-corporations-in-pune-district-print-politics-news-css-98-5314697/</t>
+          <t>https://www.navarashtra.com/maharashtra/amravati/cm-devendra-fadnavis-cm-relief-fund-help-amravati-1187-patients-for-10-crore-rs-health-marathi-news-963412.html</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>16 जिल्ह्यांना रेड अलर्ट! राज्याच्या ‘या’ भागात अतिवृष्टी, बचाव पथक सज्ज; CM फडणवीसांची...</t>
+          <t>Nanded Breaking : मोठी बातमी! नांदेडमध्ये अनेक गाव पाण्याखाली, 15 जण अडकले तर 40 ते 50 म्हशीचा पाण्यात बुडून मृत्यू</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/rain-alert-in-16-districts-heavy-rainfall-in-this-part-of-state-cm-fadnavis-give-information-1472499.html</t>
+          <t>https://www.lokshahi.com/news/rains-in-nandeds-mukhed-taluka-have-caused-flash-floods-in-many-villages-and-information-has-emerged-that-15-people-from-the-village-are-stranded</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>मुख्यमंत्री देवेंद्र फडणवीसांकडून पावसाचा आढावा: महाराष्ट्रात 4 लाख हेक्टरवरील पिके पाण्यात, उपाययोजनांचे ज...</t>
+          <t>लातूर जिल्ह्यात मुसळधार पाऊस; लेंडी नदीला पूर आल्यानं तेलंगाणातील चार प्रवासी गेले वाहून; मुख्यमंत्र्यांनी घेतला आढावा</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/cm-devendra-fadnavis-review-maharashtra-flood-135703334.html</t>
+          <t>https://www.etvbharat.com/mr/!state/heavy-rains-in-latur-district-cause-flooding-in-many-rivers-cm-devendra-fadnavis-took-a-review-lendi-river-flood-maharashtra-news-mhs25081802447</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Cji Bhushan Gavai : सरन्यायाधीशांनी केले शिवेंद्रसिंहराजेंचे जाहीरपणे कौतुक; म्हणाले, ‘गिनिज बुकमध्ये नोंद करण्यासारखे काम...’</t>
+          <t>इतिहासाची अमूल्य खुण भारतात! इतिहासाशी पुन्हा जोडणारा क्षण, मुख्यमंत्री फडणवीसांची भावनिक प्रतिक्रिया</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chief-justice-bhushan-gavai-praised-shivendrasinghraje-bhosale-vd83</t>
+          <t>https://www.esakal.com/maharashtra/chief-minister-devendra-fadnavis-statement-after-bringing-sword-of-raje-raghuji-bhosale-to-india-vru98</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis| मुख्यमंत्री देवेंद्र फडणवीस १९ रोजी पैठण तालुक्यात</t>
+          <t>Rohit Pawar on Sanjay Shirsat : संजय शिरसाटांकडून 5 हजार कोटींचा भ्रष्टाचार, रोहित पवारांच्या आरोपाने</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/marathwada/chhatrapati-sambhajinagar/devendra-fadnavis-visit-paithan-taluka-19-august-ng81</t>
+          <t>https://marathi.abplive.com/news/politics/rohit-pawar-accuses-sanjay-shirsat-of-5000-crores-of-corruption-big-demand-to-devendra-fadnavis-maharashtra-politics-marathi-news-1377888</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>तिसरी मुंबई आर्थिक विकासाचा नवा अध्याय – मुख्यमंत्री देवेंद्र फडणवीस</t>
+          <t>Marathwada Rain : मराठवाड्यात शेतीचे सर्वाधिक नुकसान, 800 गावं जलबाधित; नांदेडमध्ये ढगफुटी, 5 जणांचा मृत्यू</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176127/</t>
+          <t>https://www.mymahanagar.com/maharashtra/cloudburst-rain-in-mukhed-nanded-district-five-people-missing-chief-minister-devendra-fadnavis-gave-information/913157/</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Maharashtra Politics : एकनाथ शिंदेंची कोण करतंय कोंडी? दिल्ली दौरे वाढण्यामागचं काय कारण?</t>
+          <t>Maharashtra Politics Live Updates : जगनमोहन रेड्डींच्या पक्षाचा सीपी राधाकृष्णन यांना जाहीर पाठिंबा</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/maharashtra-politics-shiv-sena-eknath-shinde-bjp-devendra-fadnavis-conflict-before-bmc-election-sdp-92-5314661/lite/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-18-august-2025-latest-marathi-political-news-eknath-shinde-mumbai-mahayuti-rahul-gandhi-congress-india-aghadi-election-commission-devendra-fadnavis-uddhav-thackeray-india-alliance-mumbai-pune-ajit-pawar-ncp-local-elections-rahul-gandhi-vote-adhikar-yatra-nda-cp-radhakrishnan-vice-presidential-candidat</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Maharashtra Heavy Rainfall | राज्यभरात अतिवृष्टीचा कहर; १५ जिल्ह्यांत रेड आणि ऑरेंज अलर्ट, नागरिकांनी घराबाहेर पडू नये: मुख्यमंत्री फडणवीस</t>
+          <t>CM Devendra Fadnavis: राज्यातील चार लाख हेक्टर क्षेत्रावरील पिकांना फटका; पिकांचे पंचनामे करण्याचे आदेश</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/maharashtra-heavy-rainfall-red-orange-alert-15-districts-cm-fadnavis-advisory-as80</t>
+          <t>https://deshdoot.com/crops-affected-on-four-lakh-hectares-of-land-in-the-state-orders-to-conduct-crop-surveys/</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>महाराष्ट्रातील खासदारांनी राधाकृष्णन यांना समर्थन द्यावे: मुख्यमंत्री देवेंद्र फडणवीसांचे आवाहन; ठाकरे गट अ...</t>
+          <t>CM Devendra Fadnavis: मुख्यमंत्र्यांनी राज्यातील पावसाचा घेतला आढावा; 'इतक्या' जिल्ह्यांना पावसाचा रेड अलर्ट, सतर्क राहण्याचे केले आवाहन</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/c-p-radhakrishnan-vice-president-candidate-fadnavis-urges-support-135703533.html</t>
+          <t>https://deshdoot.com/cm-fadnavis-takes-reiew-situation-ndrf-and-army-deployed-16-districts-on-red-alert/</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>पूरस्थितीचा सामना करण्यासाठी सरकारकडून सर्वतोपरी प्रयत्न, अतिवृष्टीचा धोका लक्षात घेऊन लोकांनी खबरदारी घ्यावी, मुख्यमंत्र्यांचं आवाहन</t>
+          <t>Shivaji Sawant : तानाजी सावंतांचे बंधू शिवाजी सावंतांचा भाजप प्रवेश निश्चित; मुख्यमंत्र्यांच्या भेटीनंतर जाहीर केला निर्णय</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/maharashtra-government-is-making-every-effort-to-deal-with-the-flood-situation-the-chief-minister-appeals-to-people-to-be-careful-considering-the-risk-of-heavy-rains-maharashtra-news-mhs25081804221</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/shivaji-sawants-entry-into-bjp-confirmed-decision-announced-after-meeting-with-chief-minister-vd83</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Marathwada Rain : मराठवाड्यात शेतीचे सर्वाधिक नुकसान, 800 गावं जलबाधित; नांदेडमध्ये ढगफुटी, 5 जणांचा मृत्यू</t>
+          <t>Solapur News : शिंदेंच्या सेनेत राज्यातून ‘इन्कमिंग’ पण सोलापुरात गळती, तानाजी सावंतांच्या बंधूंचा भाजप प्रवेश ठरला</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/cloudburst-rain-in-mukhed-nanded-district-five-people-missing-chief-minister-devendra-fadnavis-gave-information/913157/</t>
+          <t>https://www.mymahanagar.com/maharashtra/tanaji-sawant-brother-shivajirao-sawant-resign-eknath-shinde-sena-join-bjp-after-meet-fadnavis/913179/</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>CM Relief Fund: रुग्णांसाठी सरकारचा 'हा' विभाग ठरतोय मदतशीर; अमरावती विभागात तब्बल १०.६१ कोटींची मदत</t>
+          <t>मोदींचा निर्णय, उमेदवार ठरला अन् अडचणीत उद्धवसेना; 18 वर्षांनी पुन्हा तेच, ठाकरेंसमोर पेच?</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/amravati/cm-devendra-fadnavis-cm-relief-fund-help-amravati-1187-patients-for-10-crore-rs-health-marathi-news-963412.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-picks-cp-radhakrishnan-for-vice-president-post-cm-devendra-fadnavis-ask-uddhav-thackeray-for-support/articleshow/123362737.cms</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Nanded Breaking : मोठी बातमी! नांदेडमध्ये अनेक गाव पाण्याखाली, 15 जण अडकले तर 40 ते 50 म्हशीचा पाण्यात बुडून मृत्यू</t>
+          <t>महायुतीच्या 'या' मंत्र्यावर 5 हजार कोटींच्या भ्रष्टाचाराचा आरोप; रोहित पवारांची मुख्यमंत्री फडणवीसांकडे राजीनाम्याची मागणी</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>https://www.lokshahi.com/news/rains-in-nandeds-mukhed-taluka-have-caused-flash-floods-in-many-villages-and-information-has-emerged-that-15-people-from-the-village-are-stranded</t>
+          <t>https://puneprimenews.com/mumbai/this-minister-of-mahayuti-accused-of-corruption-worth-rs-5000-crores-rohit-pawar-demands-resignation-from-chief-minister-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>लातूर जिल्ह्यात मुसळधार पाऊस; लेंडी नदीला पूर आल्यानं तेलंगाणातील चार प्रवासी गेले वाहून; मुख्यमंत्र्यांनी घेतला आढावा</t>
+          <t>Maharashtra Rain Update : शाळांना सुट्टी आहे की नाही? नेमका निर्णय काय? फडणवीसांनीच संभ्रम संपवला;...</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/heavy-rains-in-latur-district-cause-flooding-in-many-rivers-cm-devendra-fadnavis-took-a-review-lendi-river-flood-maharashtra-news-mhs25081802447</t>
+          <t>https://www.tv9marathi.com/photo-gallery/maharashtra-rain-update-mumbai-rain-school-and-college-holiday-decision-will-be-taken-after-weather-forecast-1472649.html</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>इतिहासाची अमूल्य खुण भारतात! इतिहासाशी पुन्हा जोडणारा क्षण, मुख्यमंत्री फडणवीसांची भावनिक प्रतिक्रिया</t>
+          <t>राजधानीत पावसाचा कहर! मुंबई विद्यापीठाचा परीक्षांबाबत तडकाफडकी मोठा निर्णय!</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/chief-minister-devendra-fadnavis-statement-after-bringing-sword-of-raje-raghuji-bhosale-to-india-vru98</t>
+          <t>https://www.tv9marathi.com/maharashtra/mumbai-university-postponed-its-all-exam-to-be-held-on-19-august-due-to-heavy-rain-marathi-news-1472932.html/amp</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Rohit Pawar on Sanjay Shirsat : संजय शिरसाटांकडून 5 हजार कोटींचा भ्रष्टाचार, रोहित पवारांच्या आरोपाने</t>
+          <t>Mukhed cloudburst: मुखेडमध्ये ढगफुटी! 800 गावांना फटका, 226 लोकांची सुटका, 4 गावातले लोक फसले, सैन्याला पाचारण</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/rohit-pawar-accuses-sanjay-shirsat-of-5000-crores-of-corruption-big-demand-to-devendra-fadnavis-maharashtra-politics-marathi-news-1377888</t>
+          <t>https://marathi.ndtv.com/maharashtra/rain-big-news-mukhed-cloudburst-nanded-rain-news-calling-out-the-army-maharashtra-rain-alert-9107388</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Maharashtra Politics Live Updates : जगनमोहन रेड्डींच्या पक्षाचा सीपी राधाकृष्णन यांना जाहीर पाठिंबा</t>
+          <t>Mumbai Rains News: मुंबई ठाण्याला पुढील 48 तासांसाठी रेड अलर्ट, शाळांना सुट्टी जाहीर, मुख्यमंत्र्यांकडून</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-18-august-2025-latest-marathi-political-news-eknath-shinde-mumbai-mahayuti-rahul-gandhi-congress-india-aghadi-election-commission-devendra-fadnavis-uddhav-thackeray-india-alliance-mumbai-pune-ajit-pawar-ncp-local-elections-rahul-gandhi-vote-adhikar-yatra-nda-cp-radhakrishnan-vice-presidential-candidat</t>
+          <t>https://marathi.abplive.com/news/mumbai-rain-news-update-red-alert-for-mumbai-thane-for-next-48-hours-imd-forecast-holiday-declared-for-schools-cm-devendra-fadnavis-reviews-flood-hit-areas-1377881</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>CM Devendra Fadnavis: राज्यातील चार लाख हेक्टर क्षेत्रावरील पिकांना फटका; पिकांचे पंचनामे करण्याचे आदेश</t>
+          <t>Mumbai Rains News: मुंबईसह महाराष्ट्रात 3 जिल्ह्यात शाळा-कॉलेज बंद, पावसाने सामान्यांचे झाले हाल; तलाव भरले</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/crops-affected-on-four-lakh-hectares-of-land-in-the-state-orders-to-conduct-crop-surveys/</t>
+          <t>https://www.navarashtra.com/maharashtra/mumbai-rains-news-updates-school-college-closed-due-to-heavy-rains-thane-palghar-has-problem-963739.html</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>CM Devendra Fadnavis: मुख्यमंत्र्यांनी राज्यातील पावसाचा घेतला आढावा; 'इतक्या' जिल्ह्यांना पावसाचा रेड अलर्ट, सतर्क राहण्याचे केले आवाहन</t>
+          <t>मराठ्यांच्या इतिहासाचं सोनेरी पान उलगडलं, मुख्यमंत्र्यांच्या हस्ते सरदार रघुजी राजे भोसले यांच्या ऐतिहासिक तलवारीचं लोकार्पण</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/cm-fadnavis-takes-reiew-situation-ndrf-and-army-deployed-16-districts-on-red-alert/</t>
+          <t>https://www.etvbharat.com/mr/!state/unveiling-the-historic-sword-of-sardar-raghuji-raje-bhosale-in-mumbai-presence-of-chief-minister-devendra-fadnavis-know-history-of-raghuji-raje-sword-maharashtra-news-mhs25081900619</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Solapur News : शिंदेंच्या सेनेत राज्यातून ‘इन्कमिंग’ पण सोलापुरात गळती, तानाजी सावंतांच्या बंधूंचा भाजप प्रवेश ठरला</t>
+          <t>Rain Update : मराठवाड्यात मृत्यूचं तांडव, तुफान पावसाने सगळं उद्ध्वस्त; मदतीसाठी थेट मिलिटरी दाखल!</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/tanaji-sawant-brother-shivajirao-sawant-resign-eknath-shinde-sena-join-bjp-after-meet-fadnavis/913179/</t>
+          <t>https://www.tv9marathi.com/maharashtra/maharashtra-rain-update-marathwada-all-district-affected-by-heavy-rain-total-6-people-died-marathi-news-1472571.html</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Shivaji Sawant : तानाजी सावंतांचे बंधू शिवाजी सावंतांचा भाजप प्रवेश निश्चित; मुख्यमंत्र्यांच्या भेटीनंतर जाहीर केला निर्णय</t>
+          <t>सी. पी. राधाकृष्णन यांना उपराष्ट्रपती पदाची उमेदवारी देण्यामागं भाजपाची काय आहेत राजकीय गणितं? जाणून घ्या, सविस्तर माहिती</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/shivaji-sawants-entry-into-bjp-confirmed-decision-announced-after-meeting-with-chief-minister-vd83</t>
+          <t>https://www.etvbharat.com/mr/!bharat/vice-president-of-india-election-2025-why-modi-of-tamil-nadu-cp-radhakrishnan-is-ndas-vice-presidential-pick-know-his-profile-from-tiruppur-roots-to-ndas-vice-presidential-candidate-maharashtra-news-mhs25081800641</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>मोदींचा निर्णय, उमेदवार ठरला अन् अडचणीत उद्धवसेना; 18 वर्षांनी पुन्हा तेच, ठाकरेंसमोर पेच?</t>
+          <t>ठाण्याला 100 टक्के नियोजित शहर बनवण्याचं मिशन हाती, 227 बेकायदा इमारतींवर पडणार हातोडा, ठाणे महानगरपालिकेची हायकोर्टात माहिती</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-picks-cp-radhakrishnan-for-vice-president-post-cm-devendra-fadnavis-ask-uddhav-thackeray-for-support/articleshow/123362737.cms</t>
+          <t>https://www.etvbharat.com/mr/!state/tmc-identified-227-illegal-buildings-strict-action-will-be-taken-to-make-thane-a-well-planed-city-tmc-assures-bombay-high-court-maharashtra-news-mhs25081802854</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Maharashtra Rain Update : शाळांना सुट्टी आहे की नाही? नेमका निर्णय काय? फडणवीसांनीच संभ्रम संपवला;...</t>
+          <t>'उपराष्ट्रपती'साठी महाराष्ट्राच्या राज्यपालांचे नाव; फडणवीसांचे खासदारांना आवाहन, पवार-ठाकरेंना टोला</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/photo-gallery/maharashtra-rain-update-mumbai-rain-school-and-college-holiday-decision-will-be-taken-after-weather-forecast-1472649.html</t>
+          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-urges-mps-to-support-radhakrishnan-targets-uddhav-thackeray-and-sharad-pawar-035137.html</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Mumbai Rains News: मुंबईसह महाराष्ट्रात 3 जिल्ह्यात शाळा-कॉलेज बंद, पावसाने सामान्यांचे झाले हाल; तलाव भरले</t>
+          <t>नांदेडमध्ये मुसळधार पावसाने हाहाकार,मुख्यमंत्री फडणवीस यांच्या देखरेखीखाली मदतकार्य तीव्र</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/mumbai-rains-news-updates-school-college-closed-due-to-heavy-rains-thane-palghar-has-problem-963739.html</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/heavy-rains-wreak-havoc-in-nanded-relief-work-intensified-under-the-supervision-of-chief-minister-fadnavis-125081800046_1.html</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>मराठ्यांच्या इतिहासाचं सोनेरी पान उलगडलं, मुख्यमंत्र्यांच्या हस्ते सरदार रघुजी राजे भोसले यांच्या ऐतिहासिक तलवारीचं लोकार्पण</t>
+          <t>महाराष्ट्रात सर्वदूर पावसामुळे हाहाकार; मोठ्या प्रमाणात जीवित आणि वित्तहानी, बळीराज अडचणीत!</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/unveiling-the-historic-sword-of-sardar-raghuji-raje-bhosale-in-mumbai-presence-of-chief-minister-devendra-fadnavis-know-history-of-raghuji-raje-sword-maharashtra-news-mhs25081900619</t>
+          <t>https://mpbreakingnews.in/marathi/maharashtra/rains-wreak-havoc-across-maharashtra-massive-loss-of-life-and-property-farmers-in-trouble-06-692619</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Rain Update : मराठवाड्यात मृत्यूचं तांडव, तुफान पावसाने सगळं उद्ध्वस्त; मदतीसाठी थेट मिलिटरी दाखल!</t>
+          <t>युवकांसाठी मोठी खुशखबर; ‘या’ ठिकाणी आयटी पार्क उभारणार; मुख्यमंत्र्यांची घोषणा</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/maharashtra-rain-update-marathwada-all-district-affected-by-heavy-rain-total-6-people-died-marathi-news-1472571.html</t>
+          <t>https://www.nagpurtoday.in/great-news-for-youth-it-park-will-be-set-up-at-this-place-chief-ministers-announcement/08181712</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Jalgaon mob lynching Case: जामनेर मॉब लिंचिंग: युवकाच्या हत्येत मंत्री गिरीश महाजनांच्या ड्रायव्हरचा मुलगा मास्टर माईंड?</t>
+          <t>10 रुपयांत ‘शिवभोजन थाळी’ योजना थांबणार? शिवभोजन केंद्र चालकांची कोट्यवधींची बिलं थकली</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/maharashtra-news-jalgaon-jamner-mob-lynching-girish-mahajan-driver-son-mastermind-youth-killed-mm76-sd67</t>
+          <t>https://mpbreakingnews.in/marathi/maharashtra/will-the-shiv-bhojan-thali-scheme-for-10-rupees-stop-shiv-bhojan-center-operators-are-facing-bills-worth-crores-02-692694</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>सी. पी. राधाकृष्णन यांना उपराष्ट्रपती पदाची उमेदवारी देण्यामागं भाजपाची काय आहेत राजकीय गणितं? जाणून घ्या, सविस्तर माहिती</t>
+          <t>Schools shut, red alert as Mumbai braces for another day of heavy rain | Latest News India - Hindustan Times</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!bharat/vice-president-of-india-election-2025-why-modi-of-tamil-nadu-cp-radhakrishnan-is-ndas-vice-presidential-pick-know-his-profile-from-tiruppur-roots-to-ndas-vice-presidential-candidate-maharashtra-news-mhs25081800641</t>
+          <t>https://www.hindustantimes.com/india-news/mumbai-rains-schools-shut-as-mumbai-under-imd-red-alert-braces-for-another-day-of-heavy-rain-10-updates-101755564432674.html</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>'उपराष्ट्रपती'साठी महाराष्ट्राच्या राज्यपालांचे नाव; फडणवीसांचे खासदारांना आवाहन, पवार-ठाकरेंना टोला</t>
+          <t>Nanded rains latest UPDATES: Water from Karnataka reach district; Indian Army, SDRF deployed for rescue missions as villagers trapped</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-urges-mps-to-support-radhakrishnan-targets-uddhav-thackeray-and-sharad-pawar-035137.html</t>
+          <t>https://www.theweek.in/news/india/2025/08/18/mumbai-rain-news-nanded-rains-latest-updates-water-from-karnataka-reach-district-indian-army-sdrf-deployed-for-rescue-missions-and-villagers-trapped.html</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>नांदेडमध्ये मुसळधार पावसाने हाहाकार,मुख्यमंत्री फडणवीस यांच्या देखरेखीखाली मदतकार्य तीव्र</t>
+          <t>CM hands over keys to new police housing</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/heavy-rains-wreak-havoc-in-nanded-relief-work-intensified-under-the-supervision-of-chief-minister-fadnavis-125081800046_1.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/cm-hands-over-keys-to-new-police-housing/articleshow/123350974.cms</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>युवकांसाठी मोठी खुशखबर; ‘या’ ठिकाणी आयटी पार्क उभारणार; मुख्यमंत्र्यांची घोषणा</t>
+          <t>Sword of Raghuji Bhonsle arrives in Mumbai and will be on display till Aug 25</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/great-news-for-youth-it-park-will-be-set-up-at-this-place-chief-ministers-announcement/08181712</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/sword-of-raghuji-bhonsle-arrives-in-mumbai-and-will-be-on-display-till-aug-25/articleshow/123371745.cms</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Eknath Shinde : एकनाथ शिंदेंना मोठा धक्का ! ‘या’ नेत्याने निवडणुकीच्या तोंडावर सोडली साथ</t>
+          <t>Mumbai rains HIGHLIGHTS: Civic body declares holiday for all schools on August 19</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/big-blow-to-eknath-shinde-big-leader-of-shiv-sena-shinde-group-will-join-bjp/</t>
+          <t>https://www.business-standard.com/india-news/live-news-updates-mumbai-rain-waterlogging-traffic-heavy-rain-orange-alert-125081800291_1.html</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>10 रुपयांत ‘शिवभोजन थाळी’ योजना थांबणार? शिवभोजन केंद्र चालकांची कोट्यवधींची बिलं थकली</t>
+          <t>Monsoon mayhem: Heavy rains flood this state, schools and colleges shut</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/marathi/maharashtra/will-the-shiv-bhojan-thali-scheme-for-10-rupees-stop-shiv-bhojan-center-operators-are-facing-bills-worth-crores-02-692694</t>
+          <t>https://www.patrika.com/en/national-news/monsoon-mayhem-heavy-rains-flood-this-state-schools-and-colleges-shut-19874810</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>महाराष्ट्रात सर्वदूर पावसामुळे हाहाकार; मोठ्या प्रमाणात जीवित आणि वित्तहानी, बळीराज अडचणीत!</t>
+          <t>15 Maharashtra Districts Under Red and Orange Alert as Heavy Rains Continue; Mumbai Records 177 mm in Hours</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/marathi/maharashtra/rains-wreak-havoc-across-maharashtra-massive-loss-of-life-and-property-farmers-in-trouble-06-692619</t>
+          <t>https://www.mypunepulse.com/15-maharashtra-districts-under-red-and-orange-alert-as-heavy-rains-continue-mumbai-records-177-mm-in-hours/</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Schools shut, red alert as Mumbai braces for another day of heavy rain | Latest News India - Hindustan Times</t>
+          <t>Raghuji Bhosale Sword: रघुजी भोसलेंची ऐतिहासिक तलवार आज मुंबईत; मुख्यमंत्र्यांच्या हस्ते होणार लोकार्पण</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/mumbai-rains-schools-shut-as-mumbai-under-imd-red-alert-braces-for-another-day-of-heavy-rain-10-updates-101755564432674.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/raghuji-bhosale-sword-to-arrive-in-mumbai-today-18-august-inauguration-ceremony-by-cm-devendra-fadnavis/articleshow/123353790.cms</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Rain fury leaves 7 dead in Maharashtra, 200 villagers stranded</t>
+          <t>मुंबईतील सर्व शासकीय आणि निमशासकीय कार्यालयांना आज सुट्टी जाहीर!</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/rain-fury-leaves-7-dead-in-maharashtra-200-villagers-stranded/2834213</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/19/mumbai-rains-govt-declares-holiday-for-all-government-and-private-offices-amid-heavy-rainfall.html</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Maharashtra on high alert as heavy rains batter state; CM, Dy CM lead rescue efforts</t>
+          <t>Mumbai Rain Alert:मुंबईत पावसाची धुवाँधार बॅटिंग;शाळांना सुट्टी जाहीर</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>https://www.daijiworld.com/news/newsDisplay?newsID=1289634</t>
+          <t>https://ilovenagar.com/mumbai-rain-alert-schools-declare-holiday-today/</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Nanded rains latest UPDATES: Water from Karnataka reach district; Indian Army, SDRF deployed for rescue missions as villagers trapped</t>
+          <t>Super 100: आज इंडिया गठबंधन कर सकता है उपराष्ट्रपति चुनाव के लिए उम्मीदवार का एलान.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/news/india/2025/08/18/mumbai-rain-news-nanded-rains-latest-updates-water-from-karnataka-reach-district-indian-army-sdrf-deployed-for-rescue-missions-and-villagers-trapped.html</t>
+          <t>https://www.indiatv.in/video/news-bulletin/super-100-today-india-alliance-can-announce-its-candidate-for-vice-presidential-election-2025-08-18-1156635</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>CM hands over keys to new police housing</t>
+          <t>Breaking News Maharashtra LIVE : संतोष देशमुख प्रकरण, सोमवारी सुनावणी</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/cm-hands-over-keys-to-new-police-housing/articleshow/123350974.cms</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-maharashtra-politics-rain-flood-updates-election-commission-press-conference-thalak-batmya-sunday-17th-august-2025-1471433.html</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Low-key launch of Raghuji Bhonsle’s sword in rain-lashed city</t>
+          <t>Maharashtra Breaking News LIVE : दिवसभरातील महत्त्वाच्या घडामोडी, ब्रेकिंग न्यूजचा आढावा एका क्लिकवर</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/lowkey-launch-of-raghuji-bhonsle-s-sword-in-rain-lashed-city-101755543235713.html</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-august-18-political-news-in-marathi-933194</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>CREDAI-MCHI appoints Sukhraj Nahar as 18th President</t>
+          <t>Mumbai gets 177mm rain in 6-8 hour period, says CM; all agencies asked to remain alert</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>https://housing.com/news/credai-mchi-appoints-sukhraj-nahar-as-president/</t>
+          <t>https://m.economictimes.com/news/india/mumbai-gets-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/amp_articleshow/123365291.cms</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Mumbai rain highlights: BMC declares holiday for schools, colleges today amid heavy rain forecast</t>
+          <t>Upcoming ‘Third Mumbai’ will spur economic growth, says Maharashtra chief minister</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/mumbai-rain-live-updates-red-alert-school-closed-heavy-rains-august-18-weather-waterlogging-borivali-thane-powai-bmc-101755498397210.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/upcoming-third-mumbai-will-spur-economic-growth-says-maharashtra-chief-minister/articleshow/123368667.cms</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Monsoon mayhem: Heavy rains flood this state, schools and colleges shut</t>
+          <t>CM’s nod for new terminal bldg at Nashik airport received: Min</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/en/national-news/monsoon-mayhem-heavy-rains-flood-this-state-schools-and-colleges-shut-19874810</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/cms-nod-for-new-terminal-bldg-at-nashik-airport-received-min/articleshow/123372835.cms</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Mumbai got 177mm rain in 6-8 hour period, says CM; more to come amid high tides</t>
+          <t>Maharashtra rains: Five missing, several stranded as heavy rains lash Nanded, rescue operations underway</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/mumbai-got-177mm-rain-in-6-8-hour-period-says-cm-more-to-come-amid-high-tides-9672488</t>
+          <t>https://www.indiatvnews.com/maharashtra/maharashtra-rains-five-missing-several-stranded-as-heavy-rains-lash-nanded-rescue-operations-underway-2025-08-18-1004046</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Raghuji Bhosale Sword: रघुजी भोसलेंची ऐतिहासिक तलवार आज मुंबईत; मुख्यमंत्र्यांच्या हस्ते होणार लोकार्पण</t>
+          <t>Heavy rains lash Mumbai; red alert issued, Vihar Lake overflows, CM urges caution</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/raghuji-bhosale-sword-to-arrive-in-mumbai-today-18-august-inauguration-ceremony-by-cm-devendra-fadnavis/articleshow/123353790.cms</t>
+          <t>https://www.thehindu.com/news/cities/mumbai/mumbai-rain-updates-august-18-2025/article69946286.ece</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>मुंबईतील सर्व शासकीय आणि निमशासकीय कार्यालयांना आज सुट्टी जाहीर!</t>
+          <t>Maha CM asks agencies to be on alert mode after heavy rainfall and flash floods</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/19/mumbai-rains-govt-declares-holiday-for-all-government-and-private-offices-amid-heavy-rainfall.html</t>
+          <t>https://www.socialnews.xyz/2025/08/18/maha-cm-asks-agencies-to-be-on-alert-mode-after-heavy-rainfall-and-flash-floods/</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Thane Rain: ठाणे जिल्ह्यात झोडपणी; ठाणे, कल्याण, डोंबिवलीतील सखल भाग जलमय, आज शाळांना सुट्टी</t>
+          <t>देवेंद्र फडणवीस यांच्यासोबतच्या कोल्ड वॉरच्या चर्चेवर एकनाथ शिंदे यांची प्रतिक्रिया, स्पष्टच म्हणाले....</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/thane/waterlogging-in-thane-kalyan-dombivali-schools-closed-today-19-august/articleshow/123374806.cms</t>
+          <t>https://www.msn.com/mr-in/news/national/%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%AC%E0%A4%A4%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%A1-%E0%A4%B5-%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A%E0%A5%87%E0%A4%B5%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A4%9A-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1zqXD8?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Mumbai Rain Alert:मुंबईत पावसाची धुवाँधार बॅटिंग;शाळांना सुट्टी जाहीर</t>
+          <t>मुंबईतील पावसाचा मुख्यमंत्र्यांकडून सातत्याने आढावा</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>https://ilovenagar.com/mumbai-rain-alert-schools-declare-holiday-today/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/19/the-chief-minister-is-continuously-reviewing-the-rainfall-in-mumbai.html</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Super 100: आज इंडिया गठबंधन कर सकता है उपराष्ट्रपति चुनाव के लिए उम्मीदवार का एलान.</t>
+          <t>BJP ने शिंदे गुट में लगाई सेंध! कट्टर शिवसैनिक छोड़ेंगे पार्टी, निकाय चुनाव से पहले दिया बड़ा झटका</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/news-bulletin/super-100-today-india-alliance-can-announce-its-candidate-for-vice-presidential-election-2025-08-18-1156635</t>
+          <t>https://www.patrika.com/mumbai-news/maharashtra-politics-bjp-gives-setback-to-eknath-shinde-shiv-sena-before-civic-polls-19873589</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>मुंबई में आज शाम हाई टाइड, लोगों से सावधानी की अपील, भारी बारिश का लोकल ट्रेनों</t>
+          <t>महाराष्ट्र में भारी बारिश से सात लोगों की मौत, 200 ग्रामीण फंसे</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/photo-gallery/states/maharashtra-mumbai-heavy-rainfall-waterlogging-imd-red-alert-local-train-delayed-photos-maharashtra-news-2997487</t>
+          <t>https://hindi.theprint.in/india/seven-people-died-due-to-heavy-rains-in-maharashtra-200-villagers-stranded/856903/?amp</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>समाचार संध्या</t>
+          <t>महाराष्ट्र में मानसून का कहर: मुखेड तालुका में बादल फटने जैसी घटना, 200 से ज्यादा गांवों में बाढ़</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/bulletins-detail/%E0%A4%B8%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%BE%E0%A4%B0-%E0%A4%B8%E0%A4%82%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%BE-508/</t>
+          <t>https://hindi.dynamitenews.com/maharashtra/cloudburst-in-mukhed-taluka-in-maharashtra-flood-in-more-than-200-villages</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>SUPER 100 : राष्ट्रपति ट्रंप की जेलेंस्की और यूरोपीय नेताओं की साथ बैठक में अमेरिका, रूस और यूक्रेन के बीच त्रिपक्षीय वार्ता पर बनी सहमति...</t>
+          <t>CM फडणवीस ने खेला 'मराठी अस्मिता' का दांव, उपराष्ट्रपति चुनाव में उद्धव-पवार पर बना दबाव</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/news-bulletin/super-100-in-the-meeting-of-president-trump-with-zelensky-and-european-leaders-an-agreement-was-reached-on-trilateral-talks-between-america-russia-2025-08-19-1156864</t>
+          <t>https://navbharatlive.com/maharashtra/political-battle-over-nda-candidate-radhakrishnan-cm-fadnavis-seeks-support-from-uddhav-thackeray-and-sharad-pawar-1321873.html/amp</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Modi Aur Musalman: मुस्लिम वोट की 'SIR गर्मी' ठंडी ?</t>
+          <t>Mumbai News: चव्हाण ने कहा - श्रमिकों की एक साल में दो बार होगी वेतन वृद्धि</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/news-bulletin/modi-aur-musalman-sir-2025-08-18-1156613</t>
+          <t>https://www.bhaskarhindi.com/city/mumbai/mumbai-news-chavan-said-workers-will-get-salary-hike-twice-in-a-year-1174137</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>नवीन पिढीला इतिहासाशी जोडण्याचे कार्य सुरू – मुख्यमंत्री देवेंद्र फडणवीस</t>
+          <t>नांदेड़ में भारी बारिश के कारण पांच लोग लापता, कई व्यक्ति फंसे : मुख्यमंत्री फडणवीस</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176229/</t>
+          <t>https://www.ibc24.in/maharashtra/five-people-missing-several-stranded-due-to-heavy-rains-in-nanded-cm-fadnavis-3212983.html</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>CM Devendra Fadnavis यांच्या हस्ते अद्ययावत पोलीस सदनिकेचे उद्घाटन</t>
+          <t>Devendra Fadanvis: राज्यात अतिवृष्टीचा ४ लाख हेक्टरवर फटका; मुख्यमंत्री दिले पंचनाम्याचे आदेश</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/cm-devendra-fadnavis-inauguration-of-new-police-building-kolhapur-marathi-news/</t>
+          <t>https://agrowon.esakal.com/video/maharashtra-crop-loss-4-lakh-hectares-cm-orders-panchanama</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Maharashtra Rain Live News: लातूरच्या अहमदपूरमधून जाणाऱ्या मन्याड नदीला पूर</t>
+          <t>Heavy Rainfall : रेड ॲलर्ट घोषित केलेल्या ठिकाणी सतर्कता बाळगण्याचे मुख्यमंत्री फडणवीसांचे निर्देश</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/maharashtra-marathi-latest-live-news-updates-18th-augest-2025-ajchya-tajya-batmya-maharashtra-rain-update-rahul-gandhi-election-commission-raj-uddhav-thackeray-news-politics-cm-devendra-fadnavis-mumbai-thane-nagpur-pune-nashik-weather-forecast-rain-update-rains-live-news-today-pune-local-crime-top-headlines</t>
+          <t>https://www.marathi.hindusthanpost.com/social/heavy-rainfall-cm-devendra-fadnavis-instructs-to-remain-vigilant-in-places-where-red-alert-has-been-declared/</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>मुंबईत सर्व शासकीय-निमशासकीय कार्यालयांना सुट्टी जाहीर, फॉर्सबेरी जलाशयाजवळ चार तासात 109 मिमी पावसाची नोंद</t>
+          <t>Congress Should Check Voter Lists Now, quips Chandrashekhar Bawankule</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/mumbai-rain-news-all-government-semi-government-offices-in-mumbai-remain-closed-today-mumbai-local-tracks-under-water-amid-imd-red-alert-for-extremely-heavy-rainfall-maharashtra-news-mhs25081901225</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/congress-should-check-voter-lists-now-quips-chandrashekhar-bawankule/articleshow/123351307.cms</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Maharashtra Breaking News LIVE : दिवसभरातील महत्त्वाच्या घडामोडी, ब्रेकिंग न्यूजचा आढावा एका क्लिकवर</t>
+          <t>After Shankar Dayal Sharma, Another Maharashtra Governor Eyes V-P Post As BJP Picks Radhakrishnan</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-august-18-political-news-in-marathi-933194</t>
+          <t>https://www.news18.com/india/after-shankar-dayal-sharma-another-maharashtra-governor-eyes-v-p-post-as-bjp-picks-radhakrishnan-ws-kl-9511316.html</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Mumbai Rains News: मुंबई ठाण्याला पुढील 48 तासांसाठी रेड अलर्ट, शाळांना सुट्टी जाहीर, मुख्यमंत्र्यांकडून</t>
+          <t>Shiv Sena, NCP Support Maha Governor’s Nomination For Vice President</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai-rain-news-update-red-alert-for-mumbai-thane-for-next-48-hours-imd-forecast-holiday-declared-for-schools-cm-devendra-fadnavis-reviews-flood-hit-areas-1377881</t>
+          <t>https://ommcomnews.com/india-news/shiv-sena-ncp-support-maha-governors-nomination-for-vice-president/</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>नेवासा येथे फर्निचर दुकानाला भीषण आग; दुकान मालकासह कुटुंबातील चौघांचा मृत्यू</t>
+          <t>NDA's Vice President nominee CP Radhakrishnan to reach Delhi today: sources</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/ahilyanagar-fire-news-massive-fire-breaks-out-at-furniture-shop-in-nevasa-several-dead-including-furniture-shop-owner-wife-two-his-kids-maharashtra-news-mhs25081800839</t>
+          <t>https://www.aninews.in/news/national/general-news/ndas-vice-president-nominee-cp-radhakrishnan-to-reach-delhi-today-sources20250818101908</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>मुंबईत सकाळपासून मुसळधार पाऊस, दुपारच्या सर्व शाळांसह महाविद्यालयांना सुट्टी जाहीर</t>
+          <t>NCP must get Nashik guardian minister post: Bhujbal</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/mumbai-rains-updates-bmc-declared-holiday-today-for-afternoon-shift-for-all-schools-and-colleges-in-mumbai-amid-imd-red-alert-for-thane-raigad-navi-mumbai-maharashtra-news-mhs25081802005</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/ncp-must-get-nashik-guardian-minister-post-bhujbal-101755457413078.html</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Kolhapur Weather Update: कोल्हापूर जिल्ह्याला आज रेड अलर्ट मोसमात प्रथमच राधानगरी धरणाचे सर्व</t>
+          <t>Clean image and cordial relations with netas across political parties paves Maharashtra governor CP Radha</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/kolhapur-weather-red-alert-for-kolhapur-district-today-all-automatic-gates-of-radhanagari-dam-opened-for-the-first-time-in-the-season-1377818</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/clean-image-and-cordial-relations-with-netas-across-political-parties-paves-maharashtra-governor-cp-radhakrishnans-path-to-vice-presidents-office/articleshow/123350030.cms</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>School Student Stuck in Bus : बसमध्ये अडकलेल्या लहानग्यांना गुढघाभर पाण्यातून काढले बाहेर, पोलिसांच्या कृतीचे कौतुक, Video Viral</t>
+          <t>Rajnath reaches out to DMK, TMC, BJD for consensus on VP nominee</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/maharashtra-rain-news-update-mumbai-matunga-school-bus-stuck-children-rescued-by-police-video-viral-/40071</t>
+          <t>https://www.msn.com/en-in/news/other/rajnath-reaches-out-to-dmk-tmc-bjd-for-consensus-on-vp-nominee/ar-AA1KKGcl</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>नागपूरच्या राजे रघुजी भोसलेंची तलवार लंडनमधून मुंबईत, इतिहासाशी नवीन पिढीला जोडण्याचं कामं, मुख्यमंत्र्यांकडून कौतुक</t>
+          <t>'Destroying constitutional institutions': Nishikant Dubey slams Rahul Gandhi as SC dismisses plea challenging 2024 Maharashtra polls</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/marathi/maharashtra/nagpurs-raja-raghuji-bhosales-sword-arrives-in-mumbai-from-london-02-692697</t>
+          <t>https://www.aninews.in/news/national/politics/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls20250819085747</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>कोल्हापूर सर्किट बेंच झाले, आता खंडपीठाचा प्रस्ताव द्या; सरन्यायाधीश भूषण गवईंची सूचना</t>
+          <t>NDA’s VP nominee CP Radhakrishnan meets PM Modi in Delhi</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/74340/</t>
+          <t>https://www.news9live.com/india/ndas-vp-nominee-cp-radhakrishnan-meets-pm-modi-in-delhi-2883321</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Mumbai gets 177mm rain in 6-8 hour period, says CM; all agencies asked to remain alert</t>
+          <t>Devendra Fadnavis asks agencies to be on alert mode after heavy rainfall and flash floods</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/mumbai-gets-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/amp_articleshow/123365291.cms</t>
+          <t>https://www.5dariyanews.com/news/464951-Devendra-Fadnavis-asks-agencies-to-be-on-alert-mode-after-heavy-rainfall-and-flash-floods</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Upcoming ‘Third Mumbai’ will spur economic growth, says Maharashtra chief minister</t>
+          <t>BJP names CP Radhakrishnan as NDA Vice President candidate, replacing Jagdeep Dhankhar</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/upcoming-third-mumbai-will-spur-economic-growth-says-maharashtra-chief-minister/articleshow/123368667.cms</t>
+          <t>https://apnlive.com/politics/cp-radhakrishnan-nda-vice-president-candidate/</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>CM’s nod for new terminal bldg at Nashik airport received: Min</t>
+          <t>BJP man accuses Trinamool leaders of supporting Rohingyas, threatens to bulldoze them into Bangladesh</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/cms-nod-for-new-terminal-bldg-at-nashik-airport-received-min/articleshow/123372835.cms</t>
+          <t>https://www.socialnews.xyz/2025/08/18/bjp-man-accuses-trinamool-leaders-of-supporting-rohingyas-threatens-to-bulldoze-them-into-bangladesh/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=bjp-man-accuses-trinamool-leaders-of-supporting-rohingyas-threatens-to-bulldoze-them-into-bangladesh</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Maharashtra rains: Five missing, several stranded as heavy rains lash Nanded, rescue operations underway</t>
+          <t>Shivaji Sawant : शिवाजी सावंतांचा भाजपा प्रवेश निश्चित !</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/maharashtra/maharashtra-rains-five-missing-several-stranded-as-heavy-rains-lash-nanded-rescue-operations-underway-2025-08-18-1004046</t>
+          <t>https://thefocusindia.com/maharashtra-news/shivaji-sawants-admission-to-bjp-is-certain-281398/amp/</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Heavy rains lash Mumbai; red alert issued, Vihar Lake overflows, CM urges caution</t>
+          <t>Eknath Shinde : एकनाथ शिंदेंना मोठा धक्का ! ‘या’ नेत्याने निवडणुकीच्या तोंडावर सोडली साथ</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/cities/mumbai/mumbai-rain-updates-august-18-2025/article69946286.ece</t>
+          <t>https://www.dainikprabhat.com/big-blow-to-eknath-shinde-big-leader-of-shiv-sena-shinde-group-will-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Mumbai rains HIGHLIGHTS: Civic body declares holiday for all schools on August 19</t>
+          <t>Guardian Minister of Nashik : नाशिकच्या पालकमंत्रीपदाचा वाद पेटला!</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/live-news-updates-mumbai-rain-waterlogging-traffic-heavy-rain-orange-alert-125081800291_1.html</t>
+          <t>https://pudhari.news/maharashtra/north-maharashtra/nashik/guardian-minister-of-nashik-controversy-over-the-post-of-guardian-minister-of-nashik-has-flared-up-ar84</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>NCP (SP) targets Maha minister over Rs 5,000 cr scam in Navi Mumbai’s CIDCO land; demands his resignation</t>
+          <t>Devendra Fadnavis Politics : देवेंद्र फडणवीसांचा 'मोठा गेम'; अजितदादा, एकनाथ शिंदे गाफील!</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/ncp-sp-targets-maha-minister-over-rs-5000-cr-scam-in-navi-mumbais-cidco-land-demands-his-resignation/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=ncp-sp-targets-maha-minister-over-rs-5000-cr-scam-in-navi-mumbais-cidco-land-demands-his-resignation</t>
+          <t>https://sarkarnama.esakal.com/vishleshan/devendra-fadnavis-politics-ajit-pawar-eknath-shinde-unaware-bjp-incoming-rm89</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Maha CM asks agencies to be on alert mode after heavy rainfall and flash floods</t>
+          <t>Mumbai Rain Alert : मुंबईकरांनो सावध रहा.. पुढील 4 तास धोक्याचे… रेड अलर्ट अन् हवामान खात्याचा...</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/maha-cm-asks-agencies-to-be-on-alert-mode-after-heavy-rainfall-and-flash-floods/</t>
+          <t>https://www.tv9marathi.com/videos/mumbai-weather-forecast-imd-red-alert-for-mumbai-for-next-4-hours-extremely-important-for-mumbaikars-1473139.html/amp</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>देवेंद्र फडणवीस यांच्यासोबतच्या कोल्ड वॉरच्या चर्चेवर एकनाथ शिंदे यांची प्रतिक्रिया, स्पष्टच म्हणाले....</t>
+          <t>Uddhav Thackeray: मनसेसोबत युती महापालिका निवडणुकीत घातक ठरणार; उद्धव ठाकरेंना 'या' नेत्यानं केलं सावध?</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/national/%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%AC%E0%A4%A4%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%A1-%E0%A4%B5-%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A%E0%A5%87%E0%A4%B5%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A4%9A-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1zqXD8?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/mns-alliance-risk-municipal-elections-uddhav-thackeray-warning-dk88-rc70</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis | डॉ. आंबेडकर महाविद्यालयाने समाज परिवर्तनाचे केंद्र बनावे : मुख्यमंत्री देवेंद्र फडणवीस</t>
+          <t>भाजपला स्थानिक ची निवडणूक महायुती म्हणूनच का लढवायची आहे?</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-%E0%A4%A1-%E0%A4%86%E0%A4%82%E0%A4%AC%E0%A5%87%E0%A4%A1%E0%A4%95%E0%A4%B0-%E0%A4%AE%E0%A4%B9-%E0%A4%B5-%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%B2%E0%A4%AF-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%AA%E0%A4%B0-%E0%A4%B5%E0%A4%B0%E0%A5%8D%E0%A4%A4%E0%A4%A8-%E0%A4%9A%E0%A5%87-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AC%E0%A4%A8-%E0%A4%B5%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8/ar-AA1JMyQJ</t>
+          <t>https://aaplaawajnews.com/2025/34070/</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>मुंबईतील पावसाचा मुख्यमंत्र्यांकडून सातत्याने आढावा</t>
+          <t>Congress Mohan Joshi Pune | Don't wait for BJP's 'event', open the flyover</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/19/the-chief-minister-is-continuously-reviewing-the-rainfall-in-mumbai.html</t>
+          <t>https://policenama.com/congress-mohan-joshi-pune-dont-wait-for-bjps-event-open-the-flyover-former-mla-mohan-joshis-letter-to-the-municipal-commissioner/</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>BJP ने शिंदे गुट में लगाई सेंध! कट्टर शिवसैनिक छोड़ेंगे पार्टी, निकाय चुनाव से पहले दिया बड़ा झटका</t>
+          <t>प्रशांत यादव यांचा आज भाजप प्रवेश</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/maharashtra-politics-bjp-gives-setback-to-eknath-shinde-shiv-sena-before-civic-polls-19873589</t>
+          <t>https://ratnagirikhabardar.com/news/74397/</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में मानसून का कहर: मुखेड तालुका में बादल फटने जैसी घटना, 200 से ज्यादा गांवों में बाढ़</t>
+          <t>‘गँग्स ऑफ गद्दार’: शिंदेचा मंत्री ‘रोहित पवारांच्या’ निशाण्यावर</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>https://hindi.dynamitenews.com/maharashtra/cloudburst-in-mukhed-taluka-in-maharashtra-flood-in-more-than-200-villages</t>
+          <t>https://politicalmaharashtra.in/gangs-of-traitors-shindes-minister-targeted-by-rohit-pawar-97619/</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>CM फडणवीस ने खेला 'मराठी अस्मिता' का दांव, उपराष्ट्रपति चुनाव में उद्धव-पवार पर बना दबाव</t>
+          <t>To collect outstanding transportation fines, the Maha government is planning an amnesty scheme</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/political-battle-over-nda-candidate-radhakrishnan-cm-fadnavis-seeks-support-from-uddhav-thackeray-and-sharad-pawar-1321873.html/amp</t>
+          <t>https://assamtribune.com/national/to-collect-outstanding-transportation-fines-the-mahagovernment-is-planning-an-amnesty-scheme-1588536</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Mumbai News: चव्हाण ने कहा - श्रमिकों की एक साल में दो बार होगी वेतन वृद्धि</t>
+          <t>Modi Aur Musalman: मुस्लिम वोट की 'SIR गर्मी' ठंडी ?</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/city/mumbai/mumbai-news-chavan-said-workers-will-get-salary-hike-twice-in-a-year-1174137</t>
+          <t>https://www.indiatv.in/video/news-bulletin/modi-aur-musalman-sir-2025-08-18-1156613</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>नांदेड़ में भारी बारिश के कारण पांच लोग लापता, कई व्यक्ति फंसे : मुख्यमंत्री फडणवीस</t>
+          <t>Muqabla: 'वोट चोरी' पर जीत किसकी...Rahul Gandhi या Election Commission?</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/maharashtra/five-people-missing-several-stranded-due-to-heavy-rains-in-nanded-cm-fadnavis-3212983.html</t>
+          <t>https://www.indiatv.in/video/news-bulletin/muqabla-rahul-gandhi-or-the-election-commission-who-wins-the-vote-theft-battle-2025-08-19-1156831</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Vidarbha Crop Loss: विदर्भात दोन लाख हेक्टरवर पीक नुकसान</t>
+          <t>'ऑपरेशन लोटस वगैरे काही नाही; लवकरच ऑपरेशन टायगर दिसेल', सोलापूरच्या राजकारणात पडद्यामागे काय घडतंय?</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/crop-damage-on-two-lakh-hectares-in-vidarbha-rat16</t>
+          <t>https://marathi.indiatimes.com/maharashtra/solapur/solapur-politics-over-shiv-sena-leader-shivaji-sawant-may-join-bjp/articleshow/123369493.cms</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>मुख्यमंत्री फडणवीस यांची माहिती, राज्यात अतिवृष्टी, ८०० गावे बाधित, मुंबईत १७० एमएम पाऊस</t>
+          <t>Coffee Par Kurukshetra: उपराष्ट्रपति के नाम पर INDI अलायंस टूट जाएगा?</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/cm-fadnavis-said-heavy-rains-in-the-state-800-villages-affected-170-mm-rain/</t>
+          <t>https://www.indiatv.in/video/kurukshetra/coffee-par-kurukshetra-indi-2025-08-19-1156832</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Congress Should Check Voter Lists Now, quips Chandrashekhar Bawankule</t>
+          <t>Aaj Ki Baat: Mumbai में बारिश का Red Alert...48 घंटे संभलकर</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/congress-should-check-voter-lists-now-quips-chandrashekhar-bawankule/articleshow/123351307.cms</t>
+          <t>https://www.indiatv.in/video/aaj-ki-baat/aaj-ki-baat-red-alert-for-rain-in-mumbai-be-careful-for-48-hours-2025-08-19-1156835</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>After Shankar Dayal Sharma, Another Maharashtra Governor Eyes V-P Post As BJP Picks Radhakrishnan</t>
+          <t>जनसंघ से लेकर राज्यपाल तक का सफर! अब CP राधाकृष्णन बने उपराष्ट्रपति के उम्मीदवार, कैसा रहा नेताओं का रिएक्शन?</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>https://www.news18.com/india/after-shankar-dayal-sharma-another-maharashtra-governor-eyes-v-p-post-as-bjp-picks-radhakrishnan-ws-kl-9511316.html</t>
+          <t>https://hindi.oneindia.com/news/india/maharashtra-governor-cp-radhakrishnan-nda-vice-presidential-candidate-leaders-congratulate-1364687.html</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Shiv Sena, NCP Support Maha Governor’s Nomination For Vice President</t>
+          <t>Amravati Politics: अमरावती के दरियापुर में कांग्रेस को बड़ा झटका, सलीम घनीवाला भाजपा में शामिल</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>https://ommcomnews.com/india-news/shiv-sena-ncp-support-maha-governors-nomination-for-vice-president/</t>
+          <t>https://navbharatlive.com/maharashtra/amravati/major-blow-to-congress-in-dariyapur-of-amravati-salim-ghaniwala-joins-bjp-1321794.html/amp</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>NDA's Vice President nominee CP Radhakrishnan to reach Delhi today: sources</t>
+          <t>शिवसेना शिंदे गुट को बड़ा झटका, बड़ा नेता छोड़ेगा एकनाथ शिंदे का साथ</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/ndas-vice-president-nominee-cp-radhakrishnan-to-reach-delhi-today-sources20250818101908</t>
+          <t>https://mpbreakingnews.in/maharashtra/shivaji-sawant-bjp-solapur-eknath-shinde-54-804117</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>NCP must get Nashik guardian minister post: Bhujbal</t>
+          <t>नीतिमूल्य समितीला मुहूर्त मिळेना! आमदारांबाबत घोषणा करुन महिना उलटूनही बैठकच नाही</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/ncp-must-get-nashik-guardian-minister-post-bhujbal-101755457413078.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/no-meeting-even-after-month-of-announcement-regarding-ethic-committee-mlas/articleshow/123356125.cms</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>DH Evening Brief | NDA VP pick in Delhi to meet BJP top brass, Opposition yet to finalise their candidate; I.N.D.I.A. bloc continues attacking EC chief over SIR</t>
+          <t>CM Devendra Fadnavis यांच्या हस्ते अद्ययावत पोलीस सदनिकेचे उद्घाटन</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/dh-evening-brief-nda-vp-pick-in-delhi-to-meet-bjp-top-brass-opposition-yet-to-finalise-their-candidate-india-bloc-continues-attacking-ec-chief-over-sir-3685866</t>
+          <t>https://www.tarunbharat.com/cm-devendra-fadnavis-inauguration-of-new-police-building-kolhapur-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Rajnath reaches out to DMK, TMC, BJD for consensus on VP nominee</t>
+          <t>Amravati News : अमरावतीच्या दर्यापुरात काँग्रेसला मोठा धक्का, सलीम घाणीवालांचा भाजपमध्ये प्रवेश</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/rajnath-reaches-out-to-dmk-tmc-bjd-for-consensus-on-vp-nominee/articleshow/123373035.cms</t>
+          <t>https://marathi.ndtv.com/politics/salim-ghaniwala-joins-bjp-big-blow-to-congress-in-daryapur-amravati-9106782</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Breaking News Highlights Updates: Ukrainian President Zelenskyy hails 'historic' US decision to offer sec...</t>
+          <t>ABP Majha Top 10 Headlines : ABP माझा टॉप 10 हेडलाईन्स | 18 ऑगस्ट 2025 | सोमवार</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/newsblogs/india-news-live-updates-17-august-2025-earthquake-sikkim-rain-weather-mumbai-delhi-pm-modi-trump-putin-russia-israel-gaza-ukraine/liveblog/123340718.cms</t>
+          <t>https://marathi.abplive.com/news/maharashtra/abp-majha-top-10-headlines-18-august-2025-monday-latest-marathi-news-update-maharashtra-politics-marathi-news-1378004</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>NDA’s VP nominee CP Radhakrishnan meets PM Modi in Delhi</t>
+          <t>मंत्री आशीष शेलार यांनी घेतला आपात्कालीन व्यवस्थापनाचा आढावा</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>https://www.news9live.com/india/ndas-vp-nominee-cp-radhakrishnan-meets-pm-modi-in-delhi-2883321</t>
+          <t>https://www.jpnnews.in/2025/08/Ashish-Shelar-reviews-emergency-management.html</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis asks agencies to be on alert mode after heavy rainfall and flash floods</t>
+          <t>TDR Scam: साडेसातशे कोटींच्या टीडीआर घोटाळ्याचा ‘आका’ कोण?</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>https://www.5dariyanews.com/news/464951-Devendra-Fadnavis-asks-agencies-to-be-on-alert-mode-after-heavy-rainfall-and-flash-floods</t>
+          <t>https://pudhari.news/maharashtra/pune/750-crore-land-tdr-scam-ac90</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>BJP names CP Radhakrishnan as NDA Vice President candidate, replacing Jagdeep Dhankhar</t>
+          <t>मुख्यमंत्री फडणवीस यांची माहिती, राज्यात अतिवृष्टी, ८०० गावे बाधित, मुंबईत १७० एमएम पाऊस</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>https://apnlive.com/politics/cp-radhakrishnan-nda-vice-president-candidate/</t>
+          <t>https://www.marathiebatmya.com/political/cm-fadnavis-said-heavy-rains-in-the-state-800-villages-affected-170-mm-rain/</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>'Destroying constitutional institutions': Nishikant Dubey slams Rahul Gandhi as SC dismisses plea challenging 2024 Maharashtra polls</t>
+          <t>Seize assets of school directors in Shalarth ID scam: Bawankule</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/seize-assets-of-school-directors-in-shalarth-id-scam-bawankule/articleshow/123371134.cms</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>'Destroying constitutional institutions': Nishikant Dubey slams Rahul Gandhi as SC dismisses plea challenging 2024 Maharashtra polls</t>
+          <t>Nagpur Smart City projects near closure with 7 works still pending</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>https://www.malaysiasun.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
+          <t>https://infra.economictimes.indiatimes.com/news/urban-infrastructure/nagpur-smart-city-projects-face-delay-7-projects-pending-completion/123360909</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>BJP man accuses Trinamool leaders of supporting Rohingyas, threatens to bulldoze them into Bangladesh</t>
+          <t>Heritage India: Iconic Sword of Maratha Commander Raghuji Raje Bhonsle Arrives in Mumbai</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/bjp-man-accuses-trinamool-leaders-of-supporting-rohingyas-threatens-to-bulldoze-them-into-bangladesh/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=bjp-man-accuses-trinamool-leaders-of-supporting-rohingyas-threatens-to-bulldoze-them-into-bangladesh</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-govt-brings-back-iconic-sword-of-maratha-commander-raghuji-raje-bhonsle-auctioned-for-rs-4715-lakh-to-mumbai-3685565</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Shivaji Sawant : शिवाजी सावंतांचा भाजपा प्रवेश निश्चित !</t>
+          <t>Raghuji Bhonsle’s Sword To Reach Mum Today, Mudhoji Raje To Attend Ceremony</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/shivaji-sawants-admission-to-bjp-is-certain-281398/amp/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/raghuji-bhonsles-sword-to-reach-mum-today-mudhoji-raje-to-attend-ceremony/articleshow/123351204.cms</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>राष्ट्रवादीचे प्रशांत यादव यांचा आज भाजप प्रवेश</t>
+          <t>Now, Bachchu Kadu claims offer to ‘delete thousands of names’ from voters’ list</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kokan/ratnagiri/ncp-prashant-yadav-joins-bjp-today-dc95</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/now-bachchu-kadu-claims-offer-to-delete-thousands-of-names-from-voters-list/articleshow/123351305.cms</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Guardian Minister of Nashik : नाशिकच्या पालकमंत्रीपदाचा वाद पेटला!</t>
+          <t>Historic sword of Raje Raghuji Bhonsle arrives in Mumbai to royal welcome</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/north-maharashtra/nashik/guardian-minister-of-nashik-controversy-over-the-post-of-guardian-minister-of-nashik-has-flared-up-ar84</t>
+          <t>https://www.nagpurtoday.in/historic-sword-of-raje-raghuji-bhonsle-arrives-in-mumbai-to-royal-welcome/08181446</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis Politics : देवेंद्र फडणवीसांचा 'मोठा गेम'; अजितदादा, एकनाथ शिंदे गाफील!</t>
+          <t>'Destroying constitutional institutions': Nishikant Dubey slams Rahul Gandhi as SC dismisses plea challenging 2024 Maharashtra polls</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/vishleshan/devendra-fadnavis-politics-ajit-pawar-eknath-shinde-unaware-bjp-incoming-rm89</t>
+          <t>https://www.bignewsnetwork.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>भाजपला स्थानिक ची निवडणूक महायुती म्हणूनच का लढवायची आहे?</t>
+          <t>'Destroying constitutional institutions': Nishikant Dubey slams Rahul Gandhi as SC dismisses plea challenging 2024 Maharashtra polls</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>https://aaplaawajnews.com/2025/34070/</t>
+          <t>https://www.malaysiasun.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Congress Mohan Joshi Pune | Don't wait for BJP's 'event', open the flyover</t>
+          <t>३१ खासदार निवडून आले तेव्हा मतदारयाद्या बरोबर होत्या का ?</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>https://policenama.com/congress-mohan-joshi-pune-dont-wait-for-bjps-event-open-the-flyover-former-mla-mohan-joshis-letter-to-the-municipal-commissioner/</t>
+          <t>https://www.lokmat.com/nagpur/were-the-voter-lists-correct-when-31-mps-were-elected-a-a1000/</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>राज्यात ‘ओला दुष्काळ’ जाहीर करा, एकरी ५० हजार रुपयांची मदत द्या -शशिकांत शिंदे</t>
+          <t>'एआय' तंत्रज्ञानाचा वापर करून नागपूर ग्रामीण पोलिसांनी केली गुन्ह्याची उकल, 'हिट अँड रन' प्रकरणी आरोपी अटकेत</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>https://politicalmaharashtra.in/declare-wet-drought-in-the-state-provide-assistance-of-rs-50000-per-acre-shashikant-shinde-97623/</t>
+          <t>https://www.etvbharat.com/mr/!state/truck-hits-bike-husband-carried-wife-on-bike-nagpur-rural-police-arrests-accused-truck-driver-using-ai-technology-maharashtra-news-mhs25081805869</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
+          <t>रघुजी राजे यांची तलवार आणि ‘स्व’चा बोध</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/business/-Third-Mumbai--to-boost-metropolitan-region-development--Fadnavis/2834902</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/historic-sword-of-shrimant-raghuji-bhosle-back-in-mumbai.html</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Cases from 6 districts to be heard | ‘A dream comes true after 40-45 years of struggle’: CJI inaugurates HC bench in Kolhapur</t>
+          <t>Chandrashekhar Bawankule: 'आताच मतदार याद्या तपासा', महसूल मंत्र्यांचा काँग्रेस नेत्यांना टोला</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/pune/cases-dream-struggle-cji-inaugurates-hc-bench-kolhapur-10195928/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/chandrashekhar-bawankule-demands-to-check-voter-lists-against-congress-allegations/articleshow/123356783.cms</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>To collect outstanding transportation fines, the Maha government is planning an amnesty scheme</t>
+          <t>Teacher Recruitment Scam: बोगस शालार्थ आयडी घोटाळ्यातील संचालकांची मालमत्ता जप्त होणार !</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>https://assamtribune.com/national/to-collect-outstanding-transportation-fines-the-mahagovernment-is-planning-an-amnesty-scheme-1588536</t>
+          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/bogus-teacher-scam-school-id-fraud-directors-property-to-be-seized-ng81</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>NCP (SP) targets Maha minister over Rs 5,000 cr scam in Navi Mumbai’s CIDCO land; demands his resignation</t>
+          <t>Nagpur Accident : नागपुरातील हिट अँड रन प्रकरणाचा AI तंत्रज्ञानाच्या मदतीने उलगडा राज्यातील</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/ncp-sp-targets-maha-minister-over-rs-5000-cr-scam-in-navi-mumbais-cidco-land-demands-his-resignation/</t>
+          <t>https://marathi.abplive.com/crime/nagpur-hit-and-run-accident-news-update-case-solved-with-the-help-of-ai-technology-first-experiment-in-the-state-driver-arrested-from-uttar-pradesh-1377914</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Heavy rain: Dy CM asks Maha, district agencies to coordinate, prioritise rescue works</t>
+          <t>शालार्थ घोटाळ्यातील संचालकांची मालमत्ता जप्त करा; पालकमंत्री चंद्रशेखर बावनकुळे यांचे निर्देश</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/heavy-rain-dy-cm-asks-maha-district-agencies-to-coordinate-prioritise-rescue-works/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/seize-the-assets-of-directors-involved-in-the-school-id-scam.html</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Ahead of Civic Polls, Hitendra Thakur Backs Loyalists: ‘My Karyakarta Is With Me, They Ensure Our Party Wins</t>
+          <t>Sambhajinagar News : आता शहरवासीयांना मिळणार अतिरिक्त २६ एमएलडी पाणी</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/maharashtra/ahead-of-civic-polls-hitendra-thakur-backs-loyalists-my-karyakarta-is-with-me-they-ensure-our-party-wins-a475/</t>
+          <t>https://pudhari.news/amp/story/maharashtra/marathwada/chhatrapati-sambhajinagar/now-city-residents-will-get-additional-26-mld-of-water-np88</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Red alert issued as heavy rain batters Mumbai, schools and colleges closed due to waterlogging</t>
+          <t>वरूणराजा कोपला! पिकांमध्ये पाणीच पाणी, पुढील 48 तासांत या जिल्ह्यांना पुन्हा रेड अलर्ट</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/red-alert-issued-as-heavy-rain-batters-mumbai-schools-and-colleges-closed-due-to-waterlogging/</t>
+          <t>https://news18marathi.com/agriculture/18-august-maharashtra-heavy-rain-update-monsoon-2025-mumbai-red-alert-1460576.html</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Muqabla: 'वोट चोरी' पर जीत किसकी...Rahul Gandhi या Election Commission?</t>
+          <t>kolhapur | सर्किट बेंचचे स्वप्न साकारले; न्यायाचे दरवाजे खुले झाले!</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/news-bulletin/muqabla-rahul-gandhi-or-the-election-commission-who-wins-the-vote-theft-battle-2025-08-19-1156831</t>
+          <t>https://pudhari.news/amp/story/maharashtra/kolhapur/circuit-bench-dream-realized-doors-of-justice-now-open-ap84</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>सिरदर्द है कृषि मंत्रालय...अजित पवार के मंत्री दत्तात्रेय भरणे को नहीं पसंद आई नई जिम्मेदारी, जानें क्या कहा?</t>
+          <t>Mumbai reels under 177 mm rain in 8 hours; flights hit, schools shut as red alert issued</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-manik-rao-kokate-successor-minister-dattatray-bharane-called-agriculture-ministry-is-a-headache-know-all/articleshow/123357471.cms</t>
+          <t>https://www.newindianexpress.com/nation/2025/Aug/18/mumbai-rains-flight-operations-hit-schools-colleges-shut-as-imd-issues-red-alert</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Nagpur Politics | भाईंनी घातला पक्ष प्रवेशाचा दुपट्टा,आता शिवसेनेचे घुमजाव</t>
+          <t>Vice Presidential Election: सीपी राधाकृष्णन को NDA उम्मीदवार बनाने पर कांग्रेस को लगी मिर्ची, INDI गठबंधन कैंडिडेट पर खोले पत्ते</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/nagpur-politics-%E0%A4%AD-%E0%A4%88%E0%A4%82%E0%A4%A8-%E0%A4%98-%E0%A4%A4%E0%A4%B2-%E0%A4%AA%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6-%E0%A4%9A-%E0%A4%A6%E0%A5%81%E0%A4%AA%E0%A4%9F%E0%A5%8D%E0%A4%9F-%E0%A4%86%E0%A4%A4-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%9A%E0%A5%87-%E0%A4%98%E0%A5%81%E0%A4%AE%E0%A4%9C-%E0%A4%B5/ar-AA1HHJp9</t>
+          <t>https://www.republicbharat.com/india/congress-angry-cp-radhakrishnan-nda-vice-presidential-candidate-opened-cards-on-indi-alliance-meeting</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Haqiqat Kya Hai: मुनीर के मरने की तारीख भी आने वाली है ?</t>
+          <t>VIDEO: महाराष्ट्र में भारी बारिश के बीच एक्शन में डिप्टी CM अजित पवार, मंत्रालय के आपदा नियंत्रण</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/hakikat-kya-hai/haqiqat-kya-hai-2025-08-19-1156836</t>
+          <t>https://hindi.latestly.com/india/maharashtra-deputy-cm-ajit-pawar-visits-mantralaya-disaster-control-room-to-review-heavy-rain-situation-2732241.html</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>जनसंघ से लेकर राज्यपाल तक का सफर! अब CP राधाकृष्णन बने उपराष्ट्रपति के उम्मीदवार, कैसा रहा नेताओं का रिएक्शन?</t>
+          <t>India News | 12-day Himachal Pradesh Assembly Session Opens; Opposition Seeks Adjournment on Disaster</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/india/maharashtra-governor-cp-radhakrishnan-nda-vice-presidential-candidate-leaders-congratulate-1364687.html</t>
+          <t>https://www.latestly.com/agency-news/india-news-12-day-himachal-pradesh-assembly-session-opens-opposition-seeks-adjournment-on-disaster-7064955.html</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में मौसम बरपा रहा कहर: नांदेड़ में फटा बादल, बारिश के चलते 15 से 16 जिलो में अलर्ट, CM फडणवीस ने फसलों से लेकर लोकल ट्रेनों के बारे में दिया ये बड़ा अपडेट | Devendra Fadnavis, Cloudburst, Nan</t>
+          <t>Vice President Election: NDA उम्मीदवार सीपी राधाकृष्णन को मिल सकता है विपक्षी दलों का समर्थन, इन पार्टियों पर सबकी नजर</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/politics/devendra-fadnavis-cloudburst-nanded-maharashtra-news-maharashtra-1174025</t>
+          <t>https://www.jagran.com/politics/national-rajya-sabha-election-opposition-parties-may-support-nda-candidate-cp-radhakrishnan-24017212.html</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Amravati Politics: अमरावती के दरियापुर में कांग्रेस को बड़ा झटका, सलीम घनीवाला भाजपा में शामिल</t>
+          <t>महाराष्ट्र की ‘अस्मिता’ की बात करने वाले उपराष्ट्रपति पद के लिए राधाकृष्णन का समर्थन करें : फडणवीस</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/amravati/major-blow-to-congress-in-dariyapur-of-amravati-salim-ghaniwala-joins-bjp-1321794.html/amp</t>
+          <t>https://hindi.theprint.in/india/support-radhakrishnan-for-the-post-of-vice-president-who-talks-about-maharashtras-identity-fadnavis/856729/</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>शिवसेना शिंदे गुट को बड़ा झटका, बड़ा नेता छोड़ेगा एकनाथ शिंदे का साथ</t>
+          <t>कौन लेगा CP राधाकृष्णन की जगह? BJP की एक खोज खत्म होते ही शुरू हुई दूसरी तलाश</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/maharashtra/shivaji-sawant-bjp-solapur-eknath-shinde-54-804117</t>
+          <t>https://navbharatlive.com/maharashtra/maharashtra-new-governor-who-will-replace-cp-radhakrishnan-bjp-new-search-begins-1321951.html</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>नीतिमूल्य समितीला मुहूर्त मिळेना! आमदारांबाबत घोषणा करुन महिना उलटूनही बैठकच नाही</t>
+          <t>अब कोल्हापुर भी सुनेगा न्याय की पुकार, CJI गवई ने किया बॉम्बे हाई कोर्ट चौथी खंडपीठ का उद्घाटन</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/no-meeting-even-after-month-of-announcement-regarding-ethic-committee-mlas/articleshow/123356125.cms</t>
+          <t>https://navbharatlive.com/maharashtra/kolhapur/cji-br-gavai-inaugurates-bombay-high-court-bench-at-kolhapur-1321186.html</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>'ऑपरेशन लोटस वगैरे काही नाही; लवकरच ऑपरेशन टायगर दिसेल', सोलापूरच्या राजकारणात पडद्यामागे काय घडतंय?</t>
+          <t>मत चोरी प्रकरण : विरोधी पक्ष मुख्य निवडणूक आयुक्तांविरुद्ध महाभियोग आणण्याच्या तयारीत</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/solapur/solapur-politics-over-shiv-sena-leader-shivaji-sawant-may-join-bjp/articleshow/123369493.cms</t>
+          <t>https://www.etvbharat.com/mr/!bharat/opposition-parties-likely-to-bring-impeachment-motion-notice-against-cec-over-vote-theft-maharashtra-news-mhs25081803712</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Amravati News : अमरावतीच्या दर्यापुरात काँग्रेसला मोठा धक्का, सलीम घाणीवालांचा भाजपमध्ये प्रवेश</t>
+          <t>Election Commission Of India &amp; The “Politics Of Jugaad”</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/salim-ghaniwala-joins-bjp-big-blow-to-congress-in-daryapur-amravati-9106782</t>
+          <t>https://madrascourier.com/opinion/election-commission-of-india-the-politics-of-jugaad/</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Breaking News Maharashtra LIVE : संतोष देशमुख प्रकरण, सोमवारी सुनावणी</t>
+          <t>CP Radhakrishnan vs who? Why DMK’s pushing INDIA bloc for a Tamil vs Tamil contest for India’s V-P</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-maharashtra-politics-rain-flood-updates-election-commission-press-conference-thalak-batmya-sunday-17th-august-2025-1471433.html</t>
+          <t>https://theprint.in/india/cp-radhakrishnan-vs-who-why-dmks-pushing-india-bloc-for-a-tamil-vs-tamil-contest-for-indias-v-p/2723136/</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis: चार लाख हेक्टर क्षेत्रावरील पिकांना फटका; मुख्यमंत्र्यांनी घेतला राज्यातील स्थितीचा आढावा</t>
+          <t>'Political opinions or...': Supreme Court quashes plea challenging validity of Maharashtra Assembly polls</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/heavy-rains-damage-crops-on-4-lakh-hectares-cm-devendra-fadnaivs-reviews-situation-in-maharashtra/articleshow/123379831.cms</t>
+          <t>https://www.deccanherald.com/india/political-opinions-or-supreme-court-quashes-plea-challenging-validity-of-maharashtra-assembly-polls-3686244</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>मंत्री आशीष शेलार यांनी घेतला आपात्कालीन व्यवस्थापनाचा आढावा</t>
+          <t>Fadnavis meets Guv Radhakrishnan, presents him book of Shivaji Maharaj's letters</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>https://www.jpnnews.in/2025/08/Ashish-Shelar-reviews-emergency-management.html</t>
+          <t>https://www.ptinews.com/detail/national/Fadnavis-meets-Guv-Radhakrishnan--presents-him-book-of-Shivaji-Maharaj-s-letters/2832581</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>TDR Scam: साडेसातशे कोटींच्या टीडीआर घोटाळ्याचा ‘आका’ कोण?</t>
+          <t>Shiv Sena, NCP support Maha Governor’s nomination for Vice President</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/750-crore-land-tdr-scam-ac90</t>
+          <t>https://morungexpress.com/shiv-sena-ncp-support-maha-governors-nomination-for-vice-president</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>‘शिंदेंच्या सेनेला’ दे धक्का : या आमदार बंधूंनी सोडला पक्ष</t>
+          <t>NDA's VP Candidate CP Radhakrishnan Heads to Delhi Amid Criticism</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>https://politicalmaharashtra.in/a-blow-to-shindes-army-these-mla-brothers-left-the-party-97625/</t>
+          <t>https://www.devdiscourse.com/article/headlines/3545060-ndas-vp-candidate-cp-radhakrishnan-heads-to-delhi-amid-criticism</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Nagpur Smart City projects near closure with 7 works still pending</t>
+          <t>सीपी राधाकृष्णन के उपराष्ट्रपति उम्मीदवार बनाने पर कांग्रेस को लगी मिर्ची; INDI ब्लॉक भी जल्द कर सकता है प्रत्याशी का ऐलान</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>https://infra.economictimes.indiatimes.com/news/urban-infrastructure/nagpur-smart-city-projects-face-delay-7-projects-pending-completion/123360909</t>
+          <t>https://www.sudarshannews.in/news-detail.aspx?id=131383</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Seize assets of school directors in Shalarth ID scam: Bawankule</t>
+          <t>शिवसेना एकनाथ शिंदे गुट को बड़ा झटका, शिवाजी सावंत भाजपा में होगें शामिल | Maharastra - Paliwalwani - Latest Hindi News</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/seize-assets-of-school-directors-in-shalarth-id-scam-bawankule/articleshow/123371134.cms</t>
+          <t>https://paliwalwani.com/maharastra/shiv-sena-eknath-shinde-faction-is-a-big-shock-shivaji-sawant-will-be-involved-in-bjp</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Raghuji Bhonsle’s Sword To Reach Mum Today, Mudhoji Raje To Attend Ceremony</t>
+          <t>चुनाव आयोग की प्रेस कॉन्फ्रेंस में इन दो पत्रकारों के सवालों ने बोलती बंद कर दी, देखें वीडियो – No. 1 Indian Media News Portal</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/raghuji-bhonsles-sword-to-reach-mum-today-mudhoji-raje-to-attend-ceremony/articleshow/123351204.cms</t>
+          <t>https://www.bhadas4media.com/eci-press-confrence-journalist-question/</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Now, Bachchu Kadu claims offer to ‘delete thousands of names’ from voters’ list</t>
+          <t>अभी जांच लें वोटर लिस्ट, बाद में दोष न दें, बावनकुले का कांग्रेस को आह्वान, कहा- वोट बढ़ने का मतलब..</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/now-bachchu-kadu-claims-offer-to-delete-thousands-of-names-from-voters-list/articleshow/123351305.cms</t>
+          <t>https://navbharatlive.com/maharashtra/nagpur/check-voter-list-now-revenue-minister-chandrashekhar-bawankule-appeal-congress-1321254.html</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Historic sword of Raje Raghuji Bhonsle arrives in Mumbai to royal welcome</t>
+          <t>उपराष्ट्रपतीपदाचे उमेदवार राधाकृष्णन यांना पाठिंबा द्या; देवेंद्र फडणवीस यांची शरद पवार आणि उद्धव ठाकरे यांना साद</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/historic-sword-of-raje-raghuji-bhonsle-arrives-in-mumbai-to-royal-welcome/08181446</t>
+          <t>https://marathi.freepressjournal.in/maharashtra/cp-radhakrishnan-vice-president-candidate-fadnavis-appeal-pawar-thackeray</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>NMC pushes ahead with land acquisition for 2 STPs amid reluctance from VNIT, PKV</t>
+          <t>राहुल गांधी पक्ष टिकवण्यासाठी निवडणूक आयोगाचा आधार घेतात; मंत्री चंद्रशेखर बावनकुळे यांची टीका</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/nmc-pushes-ahead-with-land-acquisition-for-2-stps-amid-reluctance-from-vnit-pkv/articleshow/123372521.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/rahul-gandhi-takes-support-from-election-commission-to-save-party-minister-chandrashekhar-bawankule-criticizes.html</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>MBBS admission quota in unaided colleges cut by 50%, students erupt</t>
+          <t>Pravin Darekar: राज्य सहकारी संघाच्या अध्यक्षपदी आमदार प्रवीण दरेकर</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/mbbs-admission-quota-in-unaided-colleges-cut-by-50-students-erupt/articleshow/123372541.cms</t>
+          <t>https://pudhari.news/maharashtra/pune/pravin-darekar-elected-cooperative-president-maharashtra-ac90</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>३१ खासदार निवडून आले तेव्हा मतदारयाद्या बरोबर होत्या का ?</t>
+          <t>संवैधानिक पदाच्या निवडणुका बिनविरोध व्हाव्यात-संजय राऊत</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/nagpur/were-the-voter-lists-correct-when-31-mps-were-elected-a-a1000/</t>
+          <t>https://www.etvbharat.com/mr/!bharat/vice-president-election-2025-sanjay-raut-says-elections-to-constitutional-posts-should-be-unopposed-maharashtra-news-mhs25081801506</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>रघुजी राजे यांची तलवार आणि ‘स्व’चा बोध</t>
+          <t>१९८७च्या काश्मीर निवडणूक गैरप्रकाराचा काँग्रेसला विसर - राजीव गांधींकडून विरोधकांच्या आरोपांकडे दुर्लक्ष</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/historic-sword-of-shrimant-raghuji-bhosle-back-in-mumbai.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/congress-forgets-1987-kashmir-election-malpractices-rajiv-gandhi-ignores-opposition-allegations.html</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Chandrashekhar Bawankule: 'आताच मतदार याद्या तपासा', महसूल मंत्र्यांचा काँग्रेस नेत्यांना टोला</t>
+          <t>महाराष्ट्र कंगाल, पण मंत्री परदेशात; संजय राऊत कडाडले</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/chandrashekhar-bawankule-demands-to-check-voter-lists-against-congress-allegations/articleshow/123356783.cms</t>
+          <t>https://www.etvbharat.com/mr/!bharat/maharashtra-is-poor-but-ministers-are-abroad-sanjay-raut-lashed-out-maharashtra-news-mhs25081801861</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Teacher Recruitment Scam: बोगस शालार्थ आयडी घोटाळ्यातील संचालकांची मालमत्ता जप्त होणार !</t>
+          <t>हवामानाचा अंदाज: आजही पावसाचा कहर? मुंबई, पुण्यासह 7 जिल्ह्यांना रेड अलर्ट; गडचिरोलीसह 4 जिल्ह्यांना यलो अलर्ट</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/bogus-teacher-scam-school-id-fraud-directors-property-to-be-seized-ng81</t>
+          <t>https://thefocusindia.com/national-news/maharashtra-weather-red-alert-mumbai-pune-7-districts-281414/</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Nagpur Accident : नागपुरातील हिट अँड रन प्रकरणाचा AI तंत्रज्ञानाच्या मदतीने उलगडा राज्यातील</t>
+          <t>Girish Mahajan Chagan Bhujbal Clash Nashik Minister Post नाशिकच्या पालकमंत्रिपदावर गिरीश महाजनांचा दावा</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/crime/nagpur-hit-and-run-accident-news-update-case-solved-with-the-help-of-ai-technology-first-experiment-in-the-state-driver-arrested-from-uttar-pradesh-1377914</t>
+          <t>https://thefocusindia.com/maharashtra-news/girish-mahajan-chagan-bhujbal-clash-nashik-guardian-minister-281360/amp/</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>शालार्थ घोटाळ्यातील संचालकांची मालमत्ता जप्त करा; पालकमंत्री चंद्रशेखर बावनकुळे यांचे निर्देश</t>
+          <t>Potholes Persist, Rekha Orders Fresh Campaign</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/seize-the-assets-of-directors-involved-in-the-school-id-scam.html</t>
+          <t>https://timesofindia.indiatimes.com/city/delhi/potholes-persist-rekha-orders-fresh-campaign/articleshow/123349516.cms</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Sambhajinagar News : आता शहरवासीयांना मिळणार अतिरिक्त २६ एमएलडी पाणी</t>
+          <t>Cong calls Bhind rally over police ‘assault’ on journalists</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>https://pudhari.news/amp/story/maharashtra/marathwada/chhatrapati-sambhajinagar/now-city-residents-will-get-additional-26-mld-of-water-np88</t>
+          <t>https://timesofindia.indiatimes.com/city/bhopal/cong-calls-bhind-rally-over-police-assault-on-journalists/articleshow/123350977.cms</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>kolhapur | सर्किट बेंचचे स्वप्न साकारले; न्यायाचे दरवाजे खुले झाले!</t>
+          <t>Mumbai: Iconic Sword of Raghuji Bhonsle Arrives from London; Bike Rally Cancelled Due to Rains, Grand...</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>https://pudhari.news/amp/story/maharashtra/kolhapur/circuit-bench-dream-realized-doors-of-justice-now-open-ap84</t>
+          <t>https://www.lokmattimes.com/mumbai/mumbai-iconic-sword-of-raghuji-bhonsle-arrives-from-london-bike-rally-cancelled-due-to-rains-grand-inauguration-tonight-a525/</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>वरूणराजा कोपला! पिकांमध्ये पाणीच पाणी, पुढील 48 तासांत या जिल्ह्यांना पुन्हा रेड अलर्ट</t>
+          <t>Historic Sword Of Raje Raghuji Bhonsle To Arrive In Mumbai On August 18</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/agriculture/18-august-maharashtra-heavy-rain-update-monsoon-2025-mumbai-red-alert-1460576.html</t>
+          <t>https://www.freepressjournal.in/mumbai/historic-sword-of-raje-raghuji-bhonsle-to-arrive-in-mumbai-on-august-18</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>kolhapur | सर्किट बेंचचे स्वप्न साकारले; न्यायाचे दरवाजे खुले झाले!</t>
+          <t>Breaking News Highlights Updates: Ukrainian President Zelenskyy hails 'historic' US decision to offer sec...</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/circuit-bench-dream-realized-doors-of-justice-now-open-ap84</t>
+          <t>https://m.economictimes.com/news/newsblogs/india-news-live-updates-17-august-2025-earthquake-sikkim-rain-weather-mumbai-delhi-pm-modi-trump-putin-russia-israel-gaza-ukraine/liveblog/123340718.cms</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Vice Presidential Election: सीपी राधाकृष्णन को NDA उम्मीदवार बनाने पर कांग्रेस को लगी मिर्ची, INDI गठबंधन कैंडिडेट पर खोले पत्ते</t>
+          <t>CP Radhakrishnan: A Swayamsevak, Grassroots BJP Organiser, Former MP, Governor - Now NDA’s Pick For Vice</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>https://www.republicbharat.com/india/congress-angry-cp-radhakrishnan-nda-vice-presidential-candidate-opened-cards-on-indi-alliance-meeting</t>
+          <t>https://thecommunemag.com/cp-radhakrishnan-grassroots-bjp-organiser-former-mp-governor-now-ndas-pick-for-vice-president/</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>VIDEO: महाराष्ट्र में भारी बारिश के बीच एक्शन में डिप्टी CM अजित पवार, मंत्रालय के आपदा नियंत्रण</t>
+          <t>राजधानीत पावसाचा कहर! मुंबई विद्यापीठाचा परीक्षांबाबत तडकाफडकी मोठा निर्णय!</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>https://hindi.latestly.com/india/maharashtra-deputy-cm-ajit-pawar-visits-mantralaya-disaster-control-room-to-review-heavy-rain-situation-2732241.html</t>
+          <t>https://www.tv9marathi.com/maharashtra/mumbai-university-postponed-its-all-exam-to-be-held-on-19-august-due-to-heavy-rain-marathi-news-1472932.html</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>India News | 12-day Himachal Pradesh Assembly Session Opens; Opposition Seeks Adjournment on Disaster</t>
+          <t>पश्चिम महाराष्ट्रात शिंदेंना भाजपचा धक्का, आमदाराच्या भावासह ४० पदाधिकाऱ्यांचा शिवसेनेला जय महाराष्ट्र!</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/india-news-12-day-himachal-pradesh-assembly-session-opens-opposition-seeks-adjournment-on-disaster-7064955.html</t>
+          <t>https://saamtv.esakal.com/maharashtra/solapur-political-news-bjp-strengthens-in-solapur-as-40-sena-leaders-join-with-shivaji-sawant-bdk97</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Vice President Election: NDA उम्मीदवार सीपी राधाकृष्णन को मिल सकता है विपक्षी दलों का समर्थन, इन पार्टियों पर सबकी नजर</t>
+          <t>सोलापुरात भाजपची शिंदेंच्या शिवसेनावर कुरघोडी शिवाजी सावंतांनी शिवसेना सोडली,</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/politics/national-rajya-sabha-election-opposition-parties-may-support-nda-candidate-cp-radhakrishnan-24017212.html</t>
+          <t>https://marathi.abplive.com/news/politics/solapur-shivaji-sawant-leaves-shiv-sena-and-bjp-entry-confirmed-devendra-fadnavis-bjp-attack-on-eknath-shinde-shiv-sena-in-solapur-1377928</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Coffee Par Kurukshetra: उपराष्ट्रपति के नाम पर INDI अलायंस टूट जाएगा?</t>
+          <t>सोलापूरच्या राजकारणात मोठी खळबळ; तानाजी सावंत यांचा भाऊ करणार भाजपात प्रवेश</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/kurukshetra/coffee-par-kurukshetra-indi-2025-08-19-1156832</t>
+          <t>https://www.timemaharashtra.com/politics/big-stir-in-solapur-politics-tanaji-sawants-brother-to-join-bjp/129377/</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>महाराष्ट्र की ‘अस्मिता’ की बात करने वाले उपराष्ट्रपति पद के लिए राधाकृष्णन का समर्थन करें : फडणवीस</t>
+          <t>Rohit Pawar on Sanjay Shirsath: रोहित पवारांचे मंत्री संजय शिरसाटांवर भ्रष्टाचाराचे गंभीर आरोप; पहा काय म्हणाले</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/support-radhakrishnan-for-the-post-of-vice-president-who-talks-about-maharashtras-identity-fadnavis/856729/</t>
+          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/amp</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Aaj Ki Baat: Mumbai में बारिश का Red Alert...48 घंटे संभलकर</t>
+          <t>Rohit Pawar: मंत्री संजय शिरसाटांनी केला ५ हजार कोटींचा घोटाळा; आमदार रोहित पवारांच्या आरोपाने खळबळ</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/aaj-ki-baat/aaj-ki-baat-red-alert-for-rain-in-mumbai-be-careful-for-48-hours-2025-08-19-1156835</t>
+          <t>https://deshdoot.com/rohit-pawar-alleges-sanjay-shirsat-over-5000-crore-worth-land-to-bivalkar-family/</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Aaj Ka Rashifal, 19 Aug, 2025 : आचार्य इंदु प्रकाश जी से जानिए आज क्या कह रहे हैं आपके सितारे</t>
+          <t>Shivsena | नाराजी भोवली! शिंदे गटातून बड्या नेत्याचा राजीनामा, राजकीय वर्तुळात खळबळ</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/bhavishyawani/aaj-ka-rashifal-19-aug-2025-know-from-acharya-indu-prakash-ji-what-your-stars-are-saying-today-2025-08-19-1156865</t>
+          <t>https://www.thodkyaat.com/big-setback-for-eknath-shinde-faction-as-senior-leader-shivaji-sawant-joins-bjp-ahead-of-local-body-polls/</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>कौन लेगा CP राधाकृष्णन की जगह? BJP की एक खोज खत्म होते ही शुरू हुई दूसरी तलाश</t>
+          <t>Rohit Pawar on Sanjay Shirsath: रोहित पवारांचे मंत्री संजय शिरसाटांवर भ्रष्टाचाराचे गंभीर आरोप; पहा काय म्हणाले</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/maharashtra-new-governor-who-will-replace-cp-radhakrishnan-bjp-new-search-begins-1321951.html</t>
+          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Farmers Loan Waiver: बावनकुळेंनंतर महायुती सरकारमधील 'या' मंत्र्याची कर्जमाफीबाबत मोठी अपडेट; म्हणाले,'CM फडणवीस लवकरच...'</t>
+          <t>Ekanath Shinde Shivsena : शिंदे गटाला धक्का; आमदाराचा भाऊ व 40 पदाधिकाऱ्यांचा पक्षप्रवेश</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/sanjay-rathod-update-farmer-loan-waiver-devendra-fadnavis-dk88</t>
+          <t>https://www.lokshahi.com/news/mla-tanaji-sawants-brother-shivaji-sawant-has-decided-to-quit-the-group-and-join-the-bjp</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Election Commission Of India &amp; The “Politics Of Jugaad”</t>
+          <t>NCP demands : राज्यात ओला दुष्काळ जाहीर करा अन्…; राष्ट्रवादी शरद पवार गटाची मागणी</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>https://madrascourier.com/opinion/election-commission-of-india-the-politics-of-jugaad/</t>
+          <t>https://deshdoot.com/heavy-rains-wreak-havoc-in-maharashtra-sharad-pawar-ncp-demands-wet-drought-declaration-and-farmer-relief/</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>'Destroying constitutional institutions': Nishikant Dubey slams Rahul Gandhi as SC dismisses plea challenging 2024 Maharashtra polls</t>
+          <t>शिंदे गटाचे आमदार तानाजी सावंतांचे बंधू भाजपच्या वाटेवर</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/politics/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls20250819085747/</t>
+          <t>https://pcbtoday.in/%E0%A4%B6%E0%A4%BF%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%97%E0%A4%9F%E0%A4%BE%E0%A4%9A%E0%A5%87-%E0%A4%86%E0%A4%AE%E0%A4%A6%E0%A4%BE%E0%A4%B0-%E0%A4%A4%E0%A4%BE%E0%A4%A8%E0%A4%BE%E0%A4%9C%E0%A5%80/</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>CP Radhakrishnan vs who? Why DMK’s pushing INDIA bloc for a Tamil vs Tamil contest for India’s V-P</t>
+          <t>Kokan Politics : शरद पवार गटाला धक्का; प्रदेश सरचिटणीस प्रशांत यादव भाजपाच्या वाटेवर</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/cp-radhakrishnan-vs-who-why-dmks-pushing-india-bloc-for-a-tamil-vs-tamil-contest-for-indias-v-p/2723136/</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/kokan-politics-sharad-pawar-group-suffers-setback-state-general-secretary-prashant-yadav-on-bjps-path/</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>'Political opinions or...': Supreme Court quashes plea challenging validity of Maharashtra Assembly polls</t>
+          <t>Mumbai receives over 200 mm rainfall in 24 hours</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/political-opinions-or-supreme-court-quashes-plea-challenging-validity-of-maharashtra-assembly-polls-3686244</t>
+          <t>https://thefederal.com/category/states/west/maharashtra/mumbai-receives-over-200-mm-rainfall-in-24-hours-202405</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Fadnavis meets Guv Radhakrishnan, presents him book of Shivaji Maharaj's letters</t>
+          <t>मुंबई में आज शाम हाई टाइड, लोगों से सावधानी की अपील, भारी बारिश का लोकल ट्रेनों</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/national/Fadnavis-meets-Guv-Radhakrishnan--presents-him-book-of-Shivaji-Maharaj-s-letters/2832581</t>
+          <t>https://www.abplive.com/photo-gallery/states/maharashtra-mumbai-heavy-rainfall-waterlogging-imd-red-alert-local-train-delayed-photos-maharashtra-news-2997487</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Shiv Sena, NCP support Maha Governor’s nomination for Vice President</t>
+          <t>What happened in the Trump-Putin meeting? | Chandrashekhar Nene Maha MTB</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>https://morungexpress.com/shiv-sena-ncp-support-maha-governors-nomination-for-vice-president</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/what-happened-in-the-trump-putin-meeting-chandrashekhar-nene-maha-mtb.html</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Supreme Court dismisses plea alleging 75 lakh bogus votes in Maharashtra Assembly polls</t>
+          <t>Sanjay Raut : निसाकाचा संघर्ष उफाळला, अनिल कदमांनी साकडं घातलं आता संजय राऊत मैदानात</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>https://organiser.org/2025/08/19/308844/bharat/supreme-court-dismisses-plea-alleging-75-lakh-bogus-votes-in-maharashtra-assembly-polls/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/niphad-sugar-factory-crisis-sanjay-raut-anil-kadam-memorandum-farmers-workers-protest-nashik-gs97</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Alcaraz wins the Cincinnati Open after Sinner retires in the first set because of illness</t>
+          <t>संघशताब्दी म्हणजे सिंहावलोकन आणि भविष्यवेधाचा काळ – सरसंघचालक डॉ. मोहनजी भागवत</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>https://english.varthabharati.in/sports/alcaraz-wins-the-cincinnati-open-after-sinner-retires-in-the-first-set-because-of-illness</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/sangh-centenary-is-a-time-of-review-and-foresight-sarsanghchalak-dr-mohanji-bhagwat.html</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>खरगे, स्टॉलिन, नवीन पटनायक... उपराष्ट्रपति चुनाव से पहले राजनाथ सिंह को बीजेपी ने दी खास जिम्मेदारी</t>
+          <t>मुंबई : 20 अगस्त तक भारी बारिश; मौसम विज्ञान विभाग ने जारी किया ऑरेंज अलर्ट</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/india/vice-president-election-defence-minister-rajnath-singh-reaches-out-to-dmk-tmc-bjd-for-consensus-for-cp-radhakrishnan/articleshow/123375990.cms</t>
+          <t>https://www.rokthoklekhani.com/article/43134/mumbai--heavy-rains-till-august-20--meteorological-department-issued-orange-alert</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>'संवैधानिक संस्थाओं को कर रहे हैं नष्ट...' भाजपा सांसद निशिकांत दुबे ने राहुल गांधी पर साधा निशाना</t>
+          <t>उपराष्ट्रपतीपदाचे एनडीए उमेदवार सीपी राधाकृष्णन यांच्यावर राजकीय पक्षांच्या प्रतिक्रिया</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>https://www.timesnowhindi.com/india/constitutional-institutions-are-being-destroyed-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls-article-152485768</t>
+          <t>https://www.dainikprabhat.com/parties-reaction-to-nda-vice-presidential-candidate-cp-radhakrishnan/</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>शिवसेना एकनाथ शिंदे गुट को बड़ा झटका, शिवाजी सावंत भाजपा में होगें शामिल | Maharastra - Paliwalwani - Latest Hindi News</t>
+          <t>22-kg Golden Kalash Installed at Sant Dnyaneshwar Temple, Crafted by Shripad Shankar Nagarkar Jewellers Pune</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>https://paliwalwani.com/maharastra/shiv-sena-eknath-shinde-faction-is-a-big-shock-shivaji-sawant-will-be-involved-in-bjp</t>
+          <t>https://www.ptinews.com/press-release/22-kg-golden-kalash-installed-at-sant-dnyaneshwar-temple,-crafted-by-shripad-shankar-nagarkar-jewellers-pune/2835628</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>चुनाव आयोग की प्रेस कॉन्फ्रेंस में इन दो पत्रकारों के सवालों ने बोलती बंद कर दी, देखें वीडियो – No. 1 Indian Media News Portal</t>
+          <t>Demand to release list of property-holders affected due to road-widening in 5 days</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>https://www.bhadas4media.com/eci-press-confrence-journalist-question/</t>
+          <t>https://www.lokmattimes.com/aurangabad/demand-to-release-list-of-property-holders-affected-due-to-road-widening-in-5-days/</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>उपराष्ट्रपतीपदाचे उमेदवार राधाकृष्णन यांना पाठिंबा द्या; देवेंद्र फडणवीस यांची शरद पवार आणि उद्धव ठाकरे यांना साद</t>
+          <t>Sanjay Shirsat : मंत्री शिरसाट यांच्यावर ५ हजार कोटींच्या जमीन घोटाळ्याचा आरोप</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/maharashtra/cp-radhakrishnan-vice-president-candidate-fadnavis-appeal-pawar-thackeray</t>
+          <t>https://pudhari.news/maharashtra/mumbai/minister-shirsat-accused-of-rs-5000-crore-land-scam-np88</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>राहुल गांधी पक्ष टिकवण्यासाठी निवडणूक आयोगाचा आधार घेतात; मंत्री चंद्रशेखर बावनकुळे यांची टीका</t>
+          <t>'ऑपरेशन लोटस वगैरे काही नाही; लवकरच ऑपरेशन टायगर दिसेल', सोलापूरच्या राजकारणात पडद्यामागे काय घडतंय?</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/rahul-gandhi-takes-support-from-election-commission-to-save-party-minister-chandrashekhar-bawankule-criticizes.html</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%B2-%E0%A4%9F%E0%A4%B8-%E0%A4%B5%E0%A4%97%E0%A5%88%E0%A4%B0%E0%A5%87-%E0%A4%95-%E0%A4%B9-%E0%A4%A8-%E0%A4%B9-%E0%A4%B2%E0%A4%B5%E0%A4%95%E0%A4%B0%E0%A4%9A-%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%9F-%E0%A4%AF%E0%A4%97%E0%A4%B0-%E0%A4%A6-%E0%A4%B8%E0%A5%87%E0%A4%B2-%E0%A4%B8-%E0%A4%B2-%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B0-%E0%A4%9C%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A4-%E0%A4%AA%E0%A4%A1%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%AE-%E0%A4%97%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%98%E0%A4%A1%E0%A4%A4%E0%A4%82%E0%A4%AF/ar-AA1KKoUc</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Pravin Darekar: राज्य सहकारी संघाच्या अध्यक्षपदी आमदार प्रवीण दरेकर</t>
+          <t>Mumbai Rain Mayhem: City Comes To Standstill As Life Thrown Out Of Gear; MonoRail Gets Stuck</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/pravin-darekar-elected-cooperative-president-maharashtra-ac90</t>
+          <t>https://www.etvbharat.com/en/!state/mumbai-rains-update-august-19-govt-semi-govt-offices-shut-bmc-urges-wfh-for-pvt-employees-enn25081901231</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>१९८७च्या काश्मीर निवडणूक गैरप्रकाराचा काँग्रेसला विसर - राजीव गांधींकडून विरोधकांच्या आरोपांकडे दुर्लक्ष</t>
+          <t>Shortage of teachers hits rollout of NEP in govt, aided Maha colleges</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/congress-forgets-1987-kashmir-election-malpractices-rajiv-gandhi-ignores-opposition-allegations.html</t>
+          <t>https://www.pressreader.com/india/hindustan-times-st-jaipur/20250819/281681145971378</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>हवामानाचा अंदाज: आजही पावसाचा कहर? मुंबई, पुण्यासह 7 जिल्ह्यांना रेड अलर्ट; गडचिरोलीसह 4 जिल्ह्यांना यलो अलर्ट</t>
+          <t>Maha govt signs MoUs worth Rs 42,000 crore and creation of 28,000 jobs</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/national-news/maharashtra-weather-red-alert-mumbai-pune-7-districts-281414/</t>
+          <t>https://www.thehawk.in/news/states-and-uts/maharashtra/maha-govt-signs-mous-worth-rs-42000-crore-and-creation-of-28000-jobs</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Potholes Persist, Rekha Orders Fresh Campaign</t>
+          <t>Maha govt waives Stamp Duty worth Rs 38.99 lakh for Tata Cancer Hospital in Raigad (Ld)</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/delhi/potholes-persist-rekha-orders-fresh-campaign/articleshow/123349516.cms</t>
+          <t>https://www.thehawk.in/news/india/maha-govt-waives-stamp-duty-worth-rs-3899-lakh-for-tata-cancer-hospital-in-raigad-ld</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Maharashtra News: Dy CM Eknath Shinde Launches ‘Ladki Sun – Surakshit Sun’ Campaign To Protect Women</t>
+          <t>शाहू महाराज की तरह करना होगा न्याय, कोल्हापुर में HC की नई सर्किट बेंच के उद्घाटन पर बोले CJI गवई</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-dy-cm-eknath-shinde-launches-ladki-sun-surakshit-sun-campaign-to-protect-women-victims</t>
+          <t>https://www.tv9hindi.com/state/maharashtra/cji-inaugurated-new-circuit-bench-said-a-big-thing-about-maharashtra-government-3441714.html</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Teachers planning violent protest: Cops</t>
+          <t>महाराष्ट्र में भारी बारिश से सात लोगों की मौत, 200 ग्रामीण फंसे</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolkata/teachers-planning-violent-protest-cops/articleshow/123350909.cms</t>
+          <t>https://hindi.theprint.in/india/seven-people-died-due-to-heavy-rains-in-maharashtra-200-villagers-stranded/856903/</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>'Slap, but don't make video': Raj Thackeray's blunt advice to MNS workers after Marathi 'slapgate' case</t>
+          <t>मराठा सेनापति रघुजी भोंसले की तलवार मुंबई पहुंची</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/slap-but-dont-make-video-raj-thackerays-blunt-advice-to-mns-workers-after-marathi-slapgate-case/ar-AA1I11OF</t>
+          <t>https://www.livehindustan.com/ncr/new-delhi/story-historic-sword-of-maratha-general-raghuji-bhosale-i-repatriated-to-mumbai-201755537654676.html</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Mumbai: Iconic Sword of Raghuji Bhonsle Arrives from London; Bike Rally Cancelled Due to Rains, Grand...</t>
+          <t>महाराष्ट्र में माफ हो सकते हैं पुराने ट्रैफिक चालान, माफी योजना लाने की तैयारी में सरकार</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/mumbai/mumbai-iconic-sword-of-raghuji-bhonsle-arrives-from-london-bike-rally-cancelled-due-to-rains-grand-inauguration-tonight-a525/</t>
+          <t>https://navbharattimes.indiatimes.com/government-schemes/others/maharashtra-government-is-set-to-roll-out-an-amnesty-scheme-for-one-time-settlement-of-pending-traffic-challan/articleshow/123367444.cms</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>How CP Radhakrishnan Broke The Taboo Around Modi And Changed The Narrative After 2002 Gujarat Episode - The</t>
+          <t>Third Mumbai महानगर क्षेत्राच्या विकासाचा नवा अध्याय असेल; मुख्यमंत्र्यांनी सांगितलं कशी असेल ‘तिसरी मुंबई’ Third Mumbai in Raigad district to boost metropolitan region development said Devendra Fadnavis</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>https://thecommunemag.com/how-cpr-broke-the-taboo-around-modi/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/third-mumbai-in-raigad-district-to-boost-metropolitan-region-development-said-devendra-fadnavis-89724</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>CP Radhakrishnan: A Swayamsevak, Grassroots BJP Organiser, Former MP, Governor - Now NDA’s Pick For Vice</t>
+          <t>राज्यातील पूरस्थितीवर सरकारचे लक्ष, मदत कार्य सुरू – बावनकुळे</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>https://thecommunemag.com/cp-radhakrishnan-grassroots-bjp-organiser-former-mp-governor-now-ndas-pick-for-vice-president/</t>
+          <t>https://www.loksatta.com/nagpur/governments-attention-on-flood-situation-in-the-state-information-from-chandrashekhar-bawankule-amy-95-5313292/</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>पश्चिम महाराष्ट्रात शिंदेंना भाजपचा धक्का, आमदाराच्या भावासह ४० पदाधिकाऱ्यांचा शिवसेनेला जय महाराष्ट्र!</t>
+          <t>‘पीएम आवास’च्या तीस लाख घरांना मोफत वीज; राज्य सरकार देणार ५० हजारांचे अनुदान: मुख्यमंत्री</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/solapur-political-news-bjp-strengthens-in-solapur-as-40-sena-leaders-join-with-shivaji-sawant-bdk97</t>
+          <t>https://www.lokmat.com/maharashtra/free-electricity-to-three-lakh-houses-of-pm-awas-yojana-state-government-will-provide-subsidy-of-rs-50-thousand-chief-minister-a-a747/</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>सोलापुरात भाजपची शिंदेंच्या शिवसेनावर कुरघोडी शिवाजी सावंतांनी शिवसेना सोडली,</t>
+          <t>Maharashtra Government: शेतकऱ्यांना मिळणार गुड न्यूज: बळीराजासाठी सरकार मोठा निर्णय घेण्याच्या तयारीत</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/solapur-shivaji-sawant-leaves-shiv-sena-and-bjp-entry-confirmed-devendra-fadnavis-bjp-attack-on-eknath-shinde-shiv-sena-in-solapur-1377928</t>
+          <t>https://saamtv.esakal.com/maharashtra/sanjay-rathod-big-statement-on-loan-waiver-maharashtra-farmers-get-loan-waiver-minister-give-hint-in-award-ceremony-program-yavatmal-pusad-bbj88</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>सोलापूरच्या राजकारणात मोठी खळबळ; तानाजी सावंत यांचा भाऊ करणार भाजपात प्रवेश</t>
+          <t>Crop Loss: महाराष्‍ट्र में बारिश ने किया किसानों को बर्बाद, विदर्भ से लेकर मराठवाड़ा तक फसलें चौपट</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/big-stir-in-solapur-politics-tanaji-sawants-brother-to-join-bjp/129377/</t>
+          <t>https://www.kisantak.in/crops/story/heavy-rains-in-maharashtra-cause-huge-damage-to-farmers-after-crop-loss-and-land-submerged-in-water-1263471-2025-08-19</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Rohit Pawar on Sanjay Shirsath: रोहित पवारांचे मंत्री संजय शिरसाटांवर भ्रष्टाचाराचे गंभीर आरोप; पहा काय म्हणाले</t>
+          <t>कोल्हापुर में शुरू हुई बॉम्बे हाईकोर्ट की नई खंडपीठ, सीजेआई बोले– महाराष्ट्र न्यायिक ढांचे में आगे</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/amp</t>
+          <t>https://mpbreakingnews.in/maharashtra/bombay-high-court-kolhapur-bench-cji-b-r-gavai-maharashtra-government-54-803927</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>राजधानीत पावसाचा कहर! मुंबई विद्यापीठाचा परीक्षांबाबत तडकाफडकी मोठा निर्णय!</t>
+          <t>श्रीमती प्रज्ञा वाळकेंचा भ्रष्टाचारामध्ये उच्चांक ; सरकारविरोधी चळवळीतीही सक्रिय सहभाग ?</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/mumbai-university-postponed-its-all-exam-to-be-held-on-19-august-due-to-heavy-rain-marathi-news-1472932.html</t>
+          <t>https://lokmanthan.com/mrs-pragya-walkens-high-score-in-corruption-active-participation-in-anti-government-movement/</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Rohit Pawar: मंत्री संजय शिरसाटांनी केला ५ हजार कोटींचा घोटाळा; आमदार रोहित पवारांच्या आरोपाने खळबळ</t>
+          <t>Sharad Pawar | शासन विमानतळ करणारच ; तर मोबदलासाठी आग्रह धरा – शरद पवार</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/rohit-pawar-alleges-sanjay-shirsat-over-5000-crore-worth-land-to-bivalkar-family/</t>
+          <t>https://www.dainikprabhat.com/sharad-pawar-government-will-build-airport-so-insist-on-compensation-sharad-pawar/</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Mumbai Rain Red Alert : पावसामुळे आतापर्यंत 7 जणांचा मृत्यू; साचलेल्या पाण्यामुळे प्रवाशांचे हाल अन् राजकारणही तापलं</t>
+          <t>Third Mumbai in Raigad to become Maharashtra’s new economic powerhouse: CM Fadnavis</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/mumbai-rain-red-alert-heavy-rainfall-maharashtra-floods-bmc-pune-schooll-jap93</t>
+          <t>https://www.daijiworld.com/index.php/news/newsDisplay?newsID=1289652</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Shivsena | नाराजी भोवली! शिंदे गटातून बड्या नेत्याचा राजीनामा, राजकीय वर्तुळात खळबळ</t>
+          <t>MMRDA launches SCLR bridge, metro institute and flyovers to ease city commute</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>https://www.thodkyaat.com/big-setback-for-eknath-shinde-faction-as-senior-leader-shivaji-sawant-joins-bjp-ahead-of-local-body-polls/</t>
+          <t>https://propnewstime.com/getdetailsStories/MjA1NTQ=/mmrda-launches-sclr-bridge-metro-institute-and-flyovers-to-ease-city-commute</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Rohit Pawar on Sanjay Shirsath: रोहित पवारांचे मंत्री संजय शिरसाटांवर भ्रष्टाचाराचे गंभीर आरोप; पहा काय म्हणाले</t>
+          <t>Cabinet sends back note regarding GMR with multiple queries</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/18/cabinet-sends-back-note-regarding-gmr-with-multiple-queries.html</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Ekanath Shinde Shivsena : शिंदे गटाला धक्का; आमदाराचा भाऊ व 40 पदाधिकाऱ्यांचा पक्षप्रवेश</t>
+          <t>Maharashtra, Singapore Review Progress of Mega Container Port Project</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>https://www.lokshahi.com/news/mla-tanaji-sawants-brother-shivaji-sawant-has-decided-to-quit-the-group-and-join-the-bjp</t>
+          <t>https://www.constructionworld.in/transport-infrastructure/ports-and-shipping/maharashtra--singapore-review-progress-of-mega-container-port-project/77682</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>शिंदे गटाचे आमदार तानाजी सावंतांचे बंधू भाजपच्या वाटेवर</t>
+          <t>Mumbai To Get 238 New AC Local Trains In Three Years; Check List Of Features</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>https://pcbtoday.in/%E0%A4%B6%E0%A4%BF%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%97%E0%A4%9F%E0%A4%BE%E0%A4%9A%E0%A5%87-%E0%A4%86%E0%A4%AE%E0%A4%A6%E0%A4%BE%E0%A4%B0-%E0%A4%A4%E0%A4%BE%E0%A4%A8%E0%A4%BE%E0%A4%9C%E0%A5%80/</t>
+          <t>https://timesproperty.com/news/post/mumbai-to-get-238-new-ac-local-trains-in-three-yrs-blid10400</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Kokan Politics : शरद पवार गटाला धक्का; प्रदेश सरचिटणीस प्रशांत यादव भाजपाच्या वाटेवर</t>
+          <t>मुंबई झोपडपट्टीमुक्त होणार का? जलद पुनर्विकासाचा मुख्यमंत्र्यांनी काय सांगितला प्लॅन?</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/kokan-politics-sharad-pawar-group-suffers-setback-state-general-secretary-prashant-yadav-on-bjps-path/</t>
+          <t>https://www.tendernama.com/mahatender/mumbai/will-mumbai-become-slum-free-what-is-the-chief-ministers-plan-for-rapid-redevelopment</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Uddhav Thackeray: मनसेसोबत युती महापालिका निवडणुकीत घातक ठरणार; उद्धव ठाकरेंना 'या' नेत्यानं केलं सावध?</t>
+          <t>Mumbai Local Train: मुंबईतील लोकल प्रवाशांना मोठा दिलासा! एमआरव्हीसीकडून 15,000 कोटींचा नवा प्रकल्पाचा प्रस्ताव</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/mns-alliance-risk-municipal-elections-uddhav-thackeray-warning-dk88-rc70</t>
+          <t>https://www.msn.com/mr-in/news/other/mumbai-local-train-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%A4-%E0%A4%B2-%E0%A4%B2-%E0%A4%95%E0%A4%B2-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%B6-%E0%A4%82%E0%A4%A8-%E0%A4%AE-%E0%A4%A0-%E0%A4%A6-%E0%A4%B2-%E0%A4%B8-%E0%A4%8F%E0%A4%AE%E0%A4%86%E0%A4%B0%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%B8-%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-15-000-%E0%A4%95-%E0%A4%9F-%E0%A4%82%E0%A4%9A-%E0%A4%A8%E0%A4%B5-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95%E0%A4%B2%E0%A5%8D%E0%A4%AA-%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%B5/ar-AA1KHzxV?ocid=finance-verthp-feeds</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Mumbai Rain Alert : मुंबईकरांनो सावध रहा.. पुढील 4 तास धोक्याचे… रेड अलर्ट अन् हवामान खात्याचा...</t>
+          <t>नई दिल्ली : दिव्यांग सैन्य कैडेट्स के मुद्दे पर सुप्रीम कोर्ट सख्त; पुनर्वास योजना पर केंद्र करे विचार,</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/mumbai-weather-forecast-imd-red-alert-for-mumbai-for-next-4-hours-extremely-important-for-mumbaikars-1473139.html/amp</t>
+          <t>https://www.rokthoklekhani.com/article/43152/new-delhanew-delhi--supreme-court-strict-on-the-issue-of-disabled-military-cadets--center-should-consider-rehabilitation-plan-i-consider-supreme-court-strict-rehabilitation-scheme-on-the</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>अमित शहा हे महाराष्ट्रातल्या गुंडांचे आणि भ्रष्टाचाऱ्यांचे दिल्लीतले सेनापती, संजय राऊत यांचा घणाघात</t>
+          <t>Mumbai Chawl Redevelopment | चाळ झाली आधुनिक वस्ती</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/amit-shah-is-leader-of-maharashtra-corrupt-leader-says-sanjay-raut/</t>
+          <t>https://pudhari.news/sampadakiy/mumbai-chawl-redevelopment-displaced-workers-problem-sp96</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>What happened in the Trump-Putin meeting? | Chandrashekhar Nene Maha MTB</t>
+          <t>Heavy Rains Batter Mumbai: Red Alert Issued, Schools and Colleges Closed on August 19 in Thane and...</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/what-happened-in-the-trump-putin-meeting-chandrashekhar-nene-maha-mtb.html</t>
+          <t>https://www.thehansindia.com/news/national/heavy-rains-batter-mumbai-red-alert-issued-schools-and-colleges-closed-on-august-19-in-thane-and-palghar-998357</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Sanjay Raut : निसाकाचा संघर्ष उफाळला, अनिल कदमांनी साकडं घातलं आता संजय राऊत मैदानात</t>
+          <t>Mumbai Rains: Are Private and Public offices shut today? BMC issues statement, says...</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/niphad-sugar-factory-crisis-sanjay-raut-anil-kadam-memorandum-farmers-workers-protest-nashik-gs97</t>
+          <t>https://www.india.com/news/india/mumbai-rains-are-private-and-public-offices-shut-today-bmc-work-from-home-schools-colleges-devendra-fadnavis-markets-8019561/</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>उपराष्ट्रपतीपदाचे एनडीए उमेदवार सीपी राधाकृष्णन यांच्यावर राजकीय पक्षांच्या प्रतिक्रिया</t>
+          <t>Business Expansion, Investments &amp; Financial News</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/parties-reaction-to-nda-vice-presidential-candidate-cp-radhakrishnan/</t>
+          <t>https://money.rediff.com/news/market/business-expansion-investments-financial-news/32187520250818</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>‘गँग्स ऑफ गद्दार’: शिंदेचा मंत्री ‘रोहित पवारांच्या’ निशाण्यावर</t>
+          <t>'Third Mumbai' to boost MMR development, says Fadnavis; invites pvt sector to join in its creation</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>https://politicalmaharashtra.in/gangs-of-traitors-shindes-minister-targeted-by-rohit-pawar-97619/</t>
+          <t>https://www.newsdrum.in/business/third-mumbai-to-boost-mmr-development-says-fadnavis-invites-pvt-sector-to-join-in-its-creation-9674122</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>22-kg Golden Kalash Installed at Sant Dnyaneshwar Temple, Crafted by Shripad Shankar Nagarkar Jewellers Pune</t>
+          <t>Mumbai got 177mm rain in 6-8 hour period, says CM; all agencies asked to remain alert</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/business/22-kg-golden-kalash-installed-at-sant-dnyaneshwar-temple-crafted-by-shripad-shankar-nagarkar-jewellers-pune/</t>
+          <t>https://www.newsdrum.in/national/mumbai-got-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert-9673094</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Demand to release list of property-holders affected due to road-widening in 5 days</t>
+          <t>मुंबई में भारी बारिश के बीच सुचारू रूप से चल रही मेट्रो, सीएम फडणवीस ने की तारीफ</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/aurangabad/demand-to-release-list-of-property-holders-affected-due-to-road-widening-in-5-days/</t>
+          <t>https://www.m.khaskhabar.com/news/news-metro-running-smoothly-amid-heavy-rains-in-mumbai-cm-fadnavis-praised-news-hindi-1-745323-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: Rohit Pawar Alleges ₹5,000-Crore Land Scam Against Minister Sanjay Shirsat</t>
+          <t>Asia Cup 2025: पाकिस्तान क्रिकेट के मुख्य चयनकर्ता का बड़ा बयान, बोले- भारत को हराएगा पाकिस्तान</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-rohit-pawar-alleges-5000-crore-land-scam-against-minister-sanjay-shirsat</t>
+          <t>https://www.indiatv.in/video/sports/asia-cup-2025-2025-08-18-1156799</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Sanjay Shirsat : मंत्री शिरसाट यांच्यावर ५ हजार कोटींच्या जमीन घोटाळ्याचा आरोप</t>
+          <t>‘Third Mumbai’ will open a new chapter of economic development: Maha CM</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/minister-shirsat-accused-of-rs-5000-crore-land-scam-np88</t>
+          <t>https://www.ap7am.com/en/107162/third-mumbai-will-open-a-new-chapter-of-economic-development-maha-cm</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
+          <t>How much rain did Mumbai receive on Monday? Check area-wise list</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/business/'third-mumbai'-to-boost-metropolitan-region-development:-fadnavis/2834902</t>
+          <t>https://indianexpress.com/article/cities/mumbai/how-much-rain-did-mumbai-areas-receive-on-monday-check-list-bandra-juhu-chembur-10196732/</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Heritage India: Iconic Sword of Maratha Commander Raghuji Raje Bhonsle Arrives in Mumbai</t>
+          <t>Ahead of Civic Polls, Hitendra Thakur Backs Loyalists: ‘My Karyakarta Is With Me, They Ensure Our Party Wins</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-govt-brings-back-iconic-sword-of-maratha-commander-raghuji-raje-bhonsle-auctioned-for-rs-4715-lakh-to-mumbai-3685565</t>
+          <t>https://www.lokmattimes.com/maharashtra/ahead-of-civic-polls-hitendra-thakur-backs-loyalists-my-karyakarta-is-with-me-they-ensure-our-party-wins-a475/</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Mumbai Rain Mayhem: City Comes To Standstill As Life Thrown Out Of Gear; MonoRail Gets Stuck</t>
+          <t>CM to join Kawad yatra, TV center chowk shut for 5 hours</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!state/mumbai-rains-update-august-19-govt-semi-govt-offices-shut-bmc-urges-wfh-for-pvt-employees-enn25081901231</t>
+          <t>https://www.lokmattimes.com/aurangabad/cm-to-join-kawad-yatra-tv-center-chowk-shut-for-5-hours/</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Shortage of teachers hits rollout of NEP in govt, aided Maha colleges</t>
+          <t>Maha govt plans amnesty scheme to recover pending transport fines</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>https://www.pressreader.com/india/hindustan-times-st-jaipur/20250819/281681145971378</t>
+          <t>https://www.socialnews.xyz/2025/08/18/maha-govt-plans-amnesty-scheme-to-recover-pending-transport-fines/</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Maha govt waives Stamp Duty worth Rs 38.99 lakh for Tata Cancer Hospital in Raigad (Ld)</t>
+          <t>महाराष्ट्र में मौसम बरपा रहा कहर: नांदेड़ में फटा बादल, बारिश के चलते 15 से 16 जिलो में अलर्ट, CM फडणवीस ने फसलों से लेकर लोकल ट्रेनों के बारे में दिया ये बड़ा अपडेट | Devendra Fadnavis, Cloudburst, Nan</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/india/maha-govt-waives-stamp-duty-worth-rs-3899-lakh-for-tata-cancer-hospital-in-raigad-ld</t>
+          <t>https://www.bhaskarhindi.com/politics/devendra-fadnavis-cloudburst-nanded-maharashtra-news-maharashtra-1174025</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>कैसी होगी तीसरी मुंबई, कितनी बड़ी और कहां बन रही, सुविधाओं से लेकर प्लानिंग तक, CM फडणवीस ने सब बताया</t>
+          <t>चुनाव के बाद होगा महामंडलों का वितरण, महायुति के इच्छुक नेताओं पर प्रदर्शन का दबाव</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%95%E0%A5%88%E0%A4%B8-%E0%A4%B9-%E0%A4%97-%E0%A4%A4-%E0%A4%B8%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%95-%E0%A4%A4%E0%A4%A8-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%94%E0%A4%B0-%E0%A4%95%E0%A4%B9-%E0%A4%82-%E0%A4%AC%E0%A4%A8-%E0%A4%B0%E0%A4%B9-%E0%A4%B8%E0%A5%81%E0%A4%B5-%E0%A4%A7-%E0%A4%93%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AA%E0%A5%8D%E0%A4%B2-%E0%A4%A8-%E0%A4%82%E0%A4%97-%E0%A4%A4%E0%A4%95-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%AF/ar-AA1KLMl6?ocid=finance-verthp-feeds</t>
+          <t>https://navbharatlive.com/maharashtra/nagpur/distribution-of-maha-mandals-will-happen-after-the-elections-pressure-of-demonstration-on-the-aspiring-leaders-of-mahayuti-1322474.html</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>शाहू महाराज की तरह करना होगा न्याय, कोल्हापुर में HC की नई सर्किट बेंच के उद्घाटन पर बोले CJI गवई</t>
+          <t>राज्यात ओला दुष्काळ जाहीर करा, विशेष अधिवेशन बोलवा मुसळधार पावसानंतर शरद पवारांच्या</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/state/maharashtra/cji-inaugurated-new-circuit-bench-said-a-big-thing-about-maharashtra-government-3441714.html</t>
+          <t>https://marathi.abplive.com/news/politics/sharad-pawar-ncp-demands-after-heavy-rains-declaring-a-wet-drought-in-the-state-calling-a-special-session-shashikant-shinde-1377947</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में भारी बारिश से सात लोगों की मौत, 200 ग्रामीण फंसे</t>
+          <t>Sanjay Shirsat: संजय शिरसाठ पुन्हा अडचणीत, रोहित पवारांचा नवा आरोप, 15 एकर जमिनीचा वाद काय आहे?</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/seven-people-died-due-to-heavy-rains-in-maharashtra-200-villagers-stranded/856903/?amp</t>
+          <t>https://pudhari.news/maharashtra/mumbai/sanjay-shirsat-land-dispute-rohit-pawar-allegations-mk94</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>महाराष्ट्र के बीड, लातूर और नांदेड में भारी बारिश से बाढ़ की स्थिति गंभीर, NDRF और सेना तैनात</t>
+          <t>सिडको जमिन वाटप प्रकरणावरून राजकारण तापले; पवारांचा शिरसाठांवर घणाघाती हल्ला</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/maharashtra/pune/heavy-rains-in-maharashtra-flood-havoc-in-beed-latur-and-nanded-ndrf-and-army-deployed/articleshow/123370629.cms</t>
+          <t>https://civicmirror.in/maharashtra/politics-heats-up-over-cidco-land-allocation-issue-pawar-attacks-shirsath/</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में माफ हो सकते हैं पुराने ट्रैफिक चालान, माफी योजना लाने की तैयारी में सरकार</t>
+          <t>एनडीएचे उपराष्ट्रपतीपदाचे उमेदवार सीपी राधाकृष्णन यांनी घेतली पंतप्रधानांची भेट; मोदी म्हणाले, ‘त्यांच्या अनुभवाचा देशाला फायदा होणार…’</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/government-schemes/others/maharashtra-government-is-set-to-roll-out-an-amnesty-scheme-for-one-time-settlement-of-pending-traffic-challan/articleshow/123367444.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%8F%E0%A4%A8%E0%A4%A1-%E0%A4%8F%E0%A4%9A%E0%A5%87-%E0%A4%89%E0%A4%AA%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A4%AA%E0%A4%A4-%E0%A4%AA%E0%A4%A6-%E0%A4%9A%E0%A5%87-%E0%A4%89%E0%A4%AE%E0%A5%87%E0%A4%A6%E0%A4%B5-%E0%A4%B0-%E0%A4%B8-%E0%A4%AA-%E0%A4%B0-%E0%A4%A7-%E0%A4%95%E0%A5%83%E0%A4%B7%E0%A5%8D%E0%A4%A3%E0%A4%A8-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%98%E0%A5%87%E0%A4%A4%E0%A4%B2-%E0%A4%AA%E0%A4%82%E0%A4%A4%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A7-%E0%A4%A8-%E0%A4%82%E0%A4%9A-%E0%A4%AD%E0%A5%87%E0%A4%9F-%E0%A4%AE-%E0%A4%A6-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%85%E0%A4%A8%E0%A5%81%E0%A4%AD%E0%A4%B5-%E0%A4%9A-%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%B2-%E0%A4%AB-%E0%A4%AF%E0%A4%A6-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0/ar-AA1KJ7hd</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Maharashtra Rains: महाराष्ट्र में बाढ़ से हालात गंभीर, मराठवाड़ा में NDRF और सेना तैनात, सरकार की क्या है तैयारी?</t>
+          <t>Mumbai Rain LIVE Updates: मुंबईत सखल भागात साचलेल्या पाण्याचा निचरा</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/mumbai-heavy-rain-maharashtra-flood-situation-serious-ndrf-and-indian-army-deployed-in-marathwada/articleshow/123370824.cms</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/mumbai-rain-live-updates-18-august-imd-red-alert-in-mumbai-weather-waterlogging-traffic-jam-local-train-train-latest-updates-in-marathi-933169</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>मराठा सेनापति रघुजी भोंसले की तलवार मुंबई पहुंची</t>
+          <t>'उपराष्ट्रपती'साठी महाराष्ट्राच्या राज्यपालांचे नाव; फडणवीसांचे खासदारांना आवाहन, पवार-ठाकरेंना टोला</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/ncr/new-delhi/story-historic-sword-of-maratha-general-raghuji-bhosale-i-repatriated-to-mumbai-201755537654676.html</t>
+          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-urges-mps-to-support-radhakrishnan-targets-uddhav-thackeray-and-sharad-pawar-035137.html?ref_source=OI-MR&amp;ref_medium=Home-Page&amp;ref_campaign=News-Cards</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Third Mumbai महानगर क्षेत्राच्या विकासाचा नवा अध्याय असेल; मुख्यमंत्र्यांनी सांगितलं कशी असेल ‘तिसरी मुंबई’ Third Mumbai in Raigad district to boost metropolitan region development said Devendra Fadnavis</t>
+          <t>मुंबई में कबूतरखानों पर विवाद, महापालिका ने नागरिकों से आपत्तियां और सुझाव मांगे</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/third-mumbai-in-raigad-district-to-boost-metropolitan-region-development-said-devendra-fadnavis-89724</t>
+          <t>https://mpbreakingnews.in/maharashtra/mumbai-municipal-corporation-pigeon-shelters-public-consultation-high-court-54-803921</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>राज्यातील पूरस्थितीवर सरकारचे लक्ष, मदत कार्य सुरू – बावनकुळे</t>
+          <t>Maharashtra govt plans amnesty scheme to recover pending transport fines</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/governments-attention-on-flood-situation-in-the-state-information-from-chandrashekhar-bawankule-amy-95-5313292/</t>
+          <t>https://auto.economictimes.indiatimes.com/amp/news/industry/maharashtras-new-amnesty-scheme-settle-transport-fines-and-save-big/123364146</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>‘पीएम आवास’च्या तीस लाख घरांना मोफत वीज; राज्य सरकार देणार ५० हजारांचे अनुदान: मुख्यमंत्री</t>
+          <t>नवीन पिढीला इतिहासाशी जोडण्याचे कार्य सुरू – मुख्यमंत्री देवेंद्र फडणवीस</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/free-electricity-to-three-lakh-houses-of-pm-awas-yojana-state-government-will-provide-subsidy-of-rs-50-thousand-chief-minister-a-a747/</t>
+          <t>https://mahasamvad.in/176229/</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Maharashtra Government: शेतकऱ्यांना मिळणार गुड न्यूज: बळीराजासाठी सरकार मोठा निर्णय घेण्याच्या तयारीत</t>
+          <t>Sickle cell patients await BMT as govt scheme, centres yet to take off in Nagpur</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/sanjay-rathod-big-statement-on-loan-waiver-maharashtra-farmers-get-loan-waiver-minister-give-hint-in-award-ceremony-program-yavatmal-pusad-bbj88</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/sickle-cell-patients-await-bmt-as-govt-scheme-centres-yet-to-take-off-in-nagpur/articleshow/123351316.cms</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>कोल्हापुर में शुरू हुई बॉम्बे हाईकोर्ट की नई खंडपीठ, सीजेआई बोले– महाराष्ट्र न्यायिक ढांचे में आगे</t>
+          <t>सरकारी नौकरी: इस राज्य में पुलिस के 15 हजार से ज्यादा पदों पर होगी भर्ती, mahapolice.gov.in पर मिलेगा नोटिफ...</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/maharashtra/bombay-high-court-kolhapur-bench-cji-b-r-gavai-maharashtra-government-54-803927</t>
+          <t>https://hindi.news18.com/news/career/jobs-maharashtra-police-recruitment-2025-notification-for-more-than-15000-vacancy-mahapolice-gov-in-9518146.html</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>श्रीमती प्रज्ञा वाळकेंचा भ्रष्टाचारामध्ये उच्चांक ; सरकारविरोधी चळवळीतीही सक्रिय सहभाग ?</t>
+          <t>Pratap Sarnaik : राज्यातील वाहनांवर तब्‍बल 2500 कोटींचा दंड; सरकार एकरकमी परतफेडीची अभय योजना आणणार</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>https://lokmanthan.com/mrs-pragya-walkens-high-score-in-corruption-active-participation-in-anti-government-movement/</t>
+          <t>https://www.dainikprabhat.com/fines-of-around-rs-2500-crore-on-vehicles-in-the-state-government-to-introduce-a-lump-sum-repayment-scheme/</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Sharad Pawar | शासन विमानतळ करणारच ; तर मोबदलासाठी आग्रह धरा – शरद पवार</t>
+          <t>Nagpur’s Councils Starved Again: Pennies for a Region in Ruin</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/sharad-pawar-government-will-build-airport-so-insist-on-compensation-sharad-pawar/</t>
+          <t>https://thelivenagpur.com/2025/08/18/nagpurs-councils-starved-again-pennies-for-a-region-in-ruin/</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>देशभर में बारिश का कहर: मुंबई-बेहद जाम, दिल्ली में यमुना उफान पर, स्कूल-कॉलेज बंद</t>
+          <t>Cases from 6 districts to be heard | ‘A dream comes true after 40-45 years of struggle’: CJI inaugurates HC bench in Kolhapur</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>https://dainikdehat.com/india/rain-wreaks-havoc-across-the-country-mumbai-is-jam-packed-yamuna-is-in-spate-in-delhi-schools-and-colleges-are-closed/</t>
+          <t>https://indianexpress.com/article/cities/pune/cases-dream-struggle-cji-inaugurates-hc-bench-kolhapur-10195928/</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Maharashtra approves amendments for Dharavi project land transfer</t>
+          <t>Maratha commander Raghuji Bhonsle's sword brought to Mumbai!!</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/maharashtra-approves-amendments-for-dharavi-project-land-transfer/ar-AA1G1ze9</t>
+          <t>https://www.indiaherald.com/Breaking/Read/994842382/Maratha-commander-Raghuji-Bhonsles-sword-brought-to-Mumbai</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Cabinet sends back note regarding GMR with multiple queries</t>
+          <t>CJI Gavai: "Maharashtra Govt At Forefront Of Efforts To Provide Infrastructure For Judiciary"</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/18/cabinet-sends-back-note-regarding-gmr-with-multiple-queries.html</t>
+          <t>https://lawchakra.in/legal-updates/cji-gavai-infrastructure-for-judiciary/</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>मुंबई झोपडपट्टीमुक्त होणार का? जलद पुनर्विकासाचा मुख्यमंत्र्यांनी काय सांगितला प्लॅन?</t>
+          <t>Maratha general Raghuji Bhonsle's sword brought to Mumbai</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>https://www.tendernama.com/mahatender/mumbai/will-mumbai-become-slum-free-what-is-the-chief-ministers-plan-for-rapid-redevelopment</t>
+          <t>https://english.metrovaartha.com/news/mumbai/maratha-general-raghuji-bhonsles-sword-brought-to-mumbai</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Mumbai Local Train: मुंबईतील लोकल प्रवाशांना मोठा दिलासा! एमआरव्हीसीकडून 15,000 कोटींचा नवा प्रकल्पाचा प्रस्ताव</t>
+          <t>मराठा सेनापति रघुजी भोंसले की तलवार मुंबई लाई गई</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/mumbai-local-train-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%A4-%E0%A4%B2-%E0%A4%B2-%E0%A4%95%E0%A4%B2-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%B6-%E0%A4%82%E0%A4%A8-%E0%A4%AE-%E0%A4%A0-%E0%A4%A6-%E0%A4%B2-%E0%A4%B8-%E0%A4%8F%E0%A4%AE%E0%A4%86%E0%A4%B0%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%B8-%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-15-000-%E0%A4%95-%E0%A4%9F-%E0%A4%82%E0%A4%9A-%E0%A4%A8%E0%A4%B5-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95%E0%A4%B2%E0%A5%8D%E0%A4%AA-%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%B5/ar-AA1KHzxV?ocid=finance-verthp-feeds</t>
+          <t>https://hindi.theprint.in/india/maratha-commander-raghuji-bhosales-sword-brought-to-mumbai/856774/</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Mumbai Chawl Redevelopment | चाळ झाली आधुनिक वस्ती</t>
+          <t>Kolhapur : सरन्यायाधीश Bhushan Gavai यांच्या हस्ते सर्किट बेंच इमारतीचे उद्घाटन</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>https://pudhari.news/sampadakiy/mumbai-chawl-redevelopment-displaced-workers-problem-sp96</t>
+          <t>https://www.tarunbharat.com/kolhapur-circuit-bench-inauguration-with-chief-justice-bhushan-gavai-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Heavy Rains Batter Mumbai: Red Alert Issued, Schools and Colleges Closed on August 19 in Thane and...</t>
+          <t>Shashikant Shinde on Heavy Rain: राज्यात अतिवृष्टीमुळे ओला दुष्काळ जाहीर करण्याची मागणी तीव्र</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/news/national/heavy-rains-batter-mumbai-red-alert-issued-schools-and-colleges-closed-on-august-19-in-thane-and-palghar-998357</t>
+          <t>https://www.timemaharashtra.com/maharashtra/demand-to-declare-a-wet-drought-due-to-heavy-rains-in-the-state-is-strong/129359/</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Mumbai Rains: Are Private and Public offices shut today? BMC issues statement, says...</t>
+          <t>राज्यात ओला दुष्काळ जाहीर करा</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>https://www.india.com/news/india/mumbai-rains-are-private-and-public-offices-shut-today-bmc-work-from-home-schools-colleges-devendra-fadnavis-markets-8019561/</t>
+          <t>https://dainikekmat.com/%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%A4-%E0%A4%93%E0%A4%B2%E0%A4%BE-%E0%A4%A6%E0%A5%81%E0%A4%B7%E0%A5%8D%E0%A4%95%E0%A4%BE%E0%A4%B3-%E0%A4%9C%E0%A4%BE%E0%A4%B9%E0%A5%80/114152/</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Ajit Pawar ‘torturing’ me, claims Ram Shinde</t>
+          <t>Ganesh Naik, Eknath Shinde, Thane, Maharashtra Politics</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/ajit-pawar-torturing-me-claims-ram-shinde/articleshow/123372969.cms</t>
+          <t>https://mpbreakingnews.in/maharashtra/ganesh-naik-eknath-shinde-thane-maharashtra-politics-54-804112</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Surya Roshni to invest Rs 25 cr for biz expansion</t>
+          <t>मराठा सेनापति रघुजी भोंसले की तलवार मुंबई लाई गई, लंदन में हुई नीलामी में महाराष्ट्र सरकार ने हासिल की</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/business/2025/08/18/dcm62-biz-briefs-3.html</t>
+          <t>https://samarsaleel.com/%E0%A4%AE%E0%A4%B0%E0%A4%BE%E0%A4%A0%E0%A4%BE-%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A4%BE%E0%A4%AA%E0%A4%A4%E0%A4%BF-%E0%A4%B0%E0%A4%98%E0%A5%81%E0%A4%9C%E0%A5%80-%E0%A4%AD%E0%A5%8B%E0%A4%82%E0%A4%B8/490978</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
+          <t>मराठा सेनापती रघुजी भोसले यांची तलवार मुंबईत आणली, लंडनमध्ये झालेल्या लिलावात महाराष्ट्र सरकारने घेतली</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/business/third-mumbai-to-boost-metropolitan-region-development-fadnavis-9674858</t>
+          <t>https://marathi.webdunia.com/article/mumbai-news/maratha-commander-raghuji-bhonsle-s-sword-brought-to-mumbai-125081800027_1.html</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>'Third Mumbai' to boost MMR development, says Fadnavis; invites pvt sector to join in its creation</t>
+          <t>How CP Radhakrishnan Broke The Taboo Around Modi And Changed The Narrative After 2002 Gujarat Episode - The</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/business/third-mumbai-to-boost-mmr-development-says-fadnavis-invites-pvt-sector-to-join-in-its-creation-9674122</t>
+          <t>https://thecommunemag.com/how-cpr-broke-the-taboo-around-modi/</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>मुंबई में भारी बारिश के बीच सुचारू रूप से चल रही मेट्रो, सीएम फडणवीस ने की तारीफ</t>
+          <t>मुंबईत सकाळपासून मुसळधार पाऊस, दुपारच्या सर्व शाळांसह महाविद्यालयांना सुट्टी जाहीर</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>https://www.m.khaskhabar.com/news/news-metro-running-smoothly-amid-heavy-rains-in-mumbai-cm-fadnavis-praised-news-hindi-1-745323-KKN.html</t>
+          <t>https://www.etvbharat.com/mr/!state/mumbai-rains-updates-bmc-declared-holiday-today-for-afternoon-shift-for-all-schools-and-colleges-in-mumbai-amid-imd-red-alert-for-thane-raigad-navi-mumbai-maharashtra-news-mhs25081802005</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Asia Cup 2025: पाकिस्तान क्रिकेट के मुख्य चयनकर्ता का बड़ा बयान, बोले- भारत को हराएगा पाकिस्तान</t>
+          <t>MONSOON UPDATE: १५ ते १६ जिल्ह्यांत रेड आणि ऑरेंज अलर्ट; CM DEVENDRA FADNAVIS म्हणाले…</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/sports/asia-cup-2025-2025-08-18-1156799</t>
+          <t>https://www.timemaharashtra.com/maharashtra/monsoon-update-red-and-orange-alert-in-15-to-16-districts-cm-devendra-fadnavis-said/129346/</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Nagpur’s Councils Starved Again: Pennies for a Region in Ruin</t>
+          <t>Those who speak of Maharashtra 'asmita' should support Radhakrishnan for VP post Fadnavis</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/08/18/nagpurs-councils-starved-again-pennies-for-a-region-in-ruin/</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom25-mh-governor-ld-fadnavis.html</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Those who speak of Maharashtra 'asmita' should support Radhakrishnan for VP post Fadnavis</t>
+          <t>मनसे कामगार संघटनेच्या अनेक पदाधिका-यांचा भाजपामध्ये प्रवेश</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom25-mh-governor-ld-fadnavis.html</t>
+          <t>https://www.marathiebatmya.com/political/many-office-bearers-of-mns-workers-organization-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>How much rain did Mumbai receive on Monday? Check area-wise list</t>
+          <t>भाजप आमदाराचा डाव प्रशासनाने हाणून पाडला, आईच्या नावाने बांधलेले अम्मा स्मारक अवैध ठरवून हटवले</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/how-much-rain-did-mumbai-areas-receive-on-monday-check-list-bandra-juhu-chembur-10196732/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/chandrapur-bjp-mla-kishor-jorgewar-faces-setback-as-administration-demolishes-illegal-amma-memorial-construction-as11-rc70</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>CM to join Kawad yatra, TV center chowk shut for 5 hours</t>
+          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by Maharashtra CM Devendra Fadnavis</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/aurangabad/cm-to-join-kawad-yatra-tv-center-chowk-shut-for-5-hours/</t>
+          <t>https://www.tribuneindia.com/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis/amp/?utm=relatedarticles</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Maha govt plans amnesty scheme to recover pending transport fines</t>
+          <t>उत्तरकाशीतील धारली पूर : पर्वतीय विकासात हवामान धोक्यांचा समावेश करायला लावणारा आरसा</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/maha-govt-plans-amnesty-scheme-to-recover-pending-transport-fines/</t>
+          <t>https://www.etvbharat.com/mr/!opinion/uttarkashi-floods-show-why-india-must-integrate-climate-risks-into-mountain-development-mhs25081806533</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>चुनाव के बाद होगा महामंडलों का वितरण, महायुति के इच्छुक नेताओं पर प्रदर्शन का दबाव</t>
+          <t>'Modi Govt Selling Dreams Of 2047, Ignoring Present': Rahul Gandhi Slams Centre After Maharashtra's Thane Train Tragedy</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/nagpur/distribution-of-maha-mandals-will-happen-after-the-elections-pressure-of-demonstration-on-the-aspiring-leaders-of-mahayuti-1322474.html</t>
+          <t>http://www.msn.com/en-in/news/India/modi-govt-selling-dreams-of-2047-ignoring-present-rahul-gandhi-slams-centre-after-maharashtras-thane-train-tragedy/ar-AA1Gm3WY?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>राज्यात ओला दुष्काळ जाहीर करा, विशेष अधिवेशन बोलवा मुसळधार पावसानंतर शरद पवारांच्या</t>
+          <t>Rs 40kcr of investors’ money stuck with credit societies, Maharashtra govt to announce SOP for recovery</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/sharad-pawar-ncp-demands-after-heavy-rains-declaring-a-wet-drought-in-the-state-calling-a-special-session-shashikant-shinde-1377947</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/rs-40kcr-of-investors-money-stuck-with-credit-societies-maharashtra-govt-to-announce-sop-for-recovery/articleshow/123367502.cms</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Sanjay Shirsat: संजय शिरसाठ पुन्हा अडचणीत, रोहित पवारांचा नवा आरोप, 15 एकर जमिनीचा वाद काय आहे?</t>
+          <t>पंतप्रधान नरेंद्र मोदी आणि व्लादिमीर पुतीन यांच्यात संवाद - संघर्षाच्या शांततामय तोडग्यासाठी भारताचा ठाम पाठिंबा</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/sanjay-shirsat-land-dispute-rohit-pawar-allegations-mk94</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/dialogue-between-prime-minister-narendra-modi-and-vladimir-putin-indias-strong-support-for-peaceful-resolution.html</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>सिडको जमिन वाटप प्रकरणावरून राजकारण तापले; पवारांचा शिरसाठांवर घणाघाती हल्ला</t>
+          <t>वैविध्यपूर्ण विषयांवरील पुस्तक प्रकाशित करणे हे चपराकचं साहित्यिक आंदोलन; लेखक अभिराम भडकमकर यांचे प्रतिपादन</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/politics-heats-up-over-cidco-land-allocation-issue-pawar-attacks-shirsath/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/publishing-books-on-diverse-topics-is-a-literary-movement-of-the-chaparak-author-abhiram-bhadkamkar-asserts.html</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>India News | SC Dismisses Plea Alleging Discrepancies in 2024 Maharashtra Assembly Polls</t>
+          <t>ठाण्यात शालेय ९-साईड हॉकी लीगला सुरुवात ; ७६ संघांचा उत्साही सहभाग</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/india-news-sc-dismisses-plea-alleging-discrepancies-in-2024-maharashtra-assembly-polls-7065753.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/school-9-a-side-hockey-league-begins-in-thane-76-teams-participate-enthusiastically.html</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Mumbai Rain LIVE Updates: मुंबईत सखल भागात साचलेल्या पाण्याचा निचरा</t>
+          <t>Those who speak of Maharashtra 'asmita' should support Radhakrishnan for VP post: Fadnavis</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/mumbai-rain-live-updates-18-august-imd-red-alert-in-mumbai-weather-waterlogging-traffic-jam-local-train-train-latest-updates-in-marathi-933169</t>
+          <t>https://www.ptinews.com/editor-detail/those-who-speak-of-maharashtra--asmita--should-support-radhakrishnan-for-vp-post--fadnavis/2832772</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>'उपराष्ट्रपती'साठी महाराष्ट्राच्या राज्यपालांचे नाव; फडणवीसांचे खासदारांना आवाहन, पवार-ठाकरेंना टोला</t>
+          <t>Rajanna’s conspiracy claim pits CM supporters against DKS’ camp</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-urges-mps-to-support-radhakrishnan-targets-uddhav-thackeray-and-sharad-pawar-035137.html?ref_source=OI-MR&amp;ref_medium=Home-Page&amp;ref_campaign=News-Cards</t>
+          <t>https://timesofindia.indiatimes.com/city/bengaluru/rajannas-conspiracy-claim-pits-cm-supporters-against-dks-camp/articleshow/123348301.cms</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>मुंबई में कबूतरखानों पर विवाद, महापालिका ने नागरिकों से आपत्तियां और सुझाव मांगे</t>
+          <t>Rain fury: 5 missing, 200 stranded in Nanded; local trains, flights hit in Mumbai</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/maharashtra/mumbai-municipal-corporation-pigeon-shelters-public-consultation-high-court-54-803921</t>
+          <t>https://www.ptinews.com/editor-detail/Rain-fury--5-missing--200-stranded-in-Nanded;-local-trains--flights-hit-in-Mumbai/2832995</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Maharashtra govt plans amnesty scheme to recover pending transport fines</t>
+          <t>Industries in Jalgaon should get power at subsidised rate, says Ajit Pawar</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>https://auto.economictimes.indiatimes.com/amp/news/industry/maharashtras-new-amnesty-scheme-settle-transport-fines-and-save-big/123364146</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/industries-in-jalgaon-should-get-power-at-subsidised-rate-says-ajit-pawar/articleshow/123351430.cms</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Sickle cell patients await BMT as govt scheme, centres yet to take off in Nagpur</t>
+          <t>One held for friend's murder</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/sickle-cell-patients-await-bmt-as-govt-scheme-centres-yet-to-take-off-in-nagpur/articleshow/123351316.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/one-held-for-friends-murder/articleshow/123350586.cms</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>सरकारी नौकरी: इस राज्य में पुलिस के 15 हजार से ज्यादा पदों पर होगी भर्ती, mahapolice.gov.in पर मिलेगा नोटिफ...</t>
+          <t>Congress vows to ‘douse fire’ amid rifts within party</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/career/jobs-maharashtra-police-recruitment-2025-notification-for-more-than-15000-vacancy-mahapolice-gov-in-9518146.html</t>
+          <t>https://timesofindia.indiatimes.com/city/hyderabad/congress-vows-to-douse-fire-amid-rifts-within-party/articleshow/123350298.cms</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Pratap Sarnaik : राज्यातील वाहनांवर तब्‍बल 2500 कोटींचा दंड; सरकार एकरकमी परतफेडीची अभय योजना आणणार</t>
+          <t>Three of seven accused arrested in journalist attack case</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/fines-of-around-rs-2500-crore-on-vehicles-in-the-state-government-to-introduce-a-lump-sum-repayment-scheme/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/three-of-seven-accused-arrested-in-journalist-attack-case/articleshow/123350718.cms</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>CJI Gavai: "Maharashtra Govt At Forefront Of Efforts To Provide Infrastructure For Judiciary"</t>
+          <t>Jaipur-Abu Dhabi flight cancelled</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>https://lawchakra.in/legal-updates/cji-gavai-infrastructure-for-judiciary/</t>
+          <t>https://timesofindia.indiatimes.com/city/jaipur/jaipur-abu-dhabi-flight-cancelled/articleshow/123350813.cms</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Maratha general Raghuji Bhonsle's sword brought to Mumbai</t>
+          <t>Two more suspects held in Jalaun murder case</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>https://english.metrovaartha.com/news/mumbai/maratha-general-raghuji-bhonsles-sword-brought-to-mumbai</t>
+          <t>https://timesofindia.indiatimes.com/city/kanpur/two-more-suspects-held-in-jalaun-murder-case/articleshow/123350447.cms</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>महाराष्ट्रातील 'या' जिल्ह्यात उभारणार 'स्टॅच्यू ऑफ युनिटी'; सरकारचा काय आहे प्लॅन?</t>
+          <t>Uzbek institute to collaborate with IGKV in agri research</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>https://www.tendernama.com/mahatender/paschim-maharashtra/statue-of-unity-style-memorial-in-maharashtra-soon</t>
+          <t>https://timesofindia.indiatimes.com/city/raipur/uzbek-institute-to-collaborate-with-igkv-in-agri-research/articleshow/123350462.cms</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>मराठा सेनापति रघुजी भोंसले की तलवार मुंबई लाई गई</t>
+          <t>Concrete from Bengaluru’s Ejipura flyover slab falls on autorickshaw, injures driver</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/maratha-commander-raghuji-bhosales-sword-brought-to-mumbai/856774/</t>
+          <t>https://timesofindia.indiatimes.com/city/bengaluru/concrete-from-bengalurus-ejipura-flyover-slab-falls-on-autorickshaw-injures-driver/articleshow/123350812.cms</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Kolhapur : सरन्यायाधीश Bhushan Gavai यांच्या हस्ते सर्किट बेंच इमारतीचे उद्घाटन</t>
+          <t>Tehsildar sings at farewell, revenue min suspends him for lack of ‘decorum’</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/kolhapur-circuit-bench-inauguration-with-chief-justice-bhushan-gavai-marathi-news/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/tehsildar-sings-at-farewell-revenue-min-suspends-him-for-lack-of-decorum/articleshow/123350443.cms</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Shashikant Shinde on Heavy Rain: राज्यात अतिवृष्टीमुळे ओला दुष्काळ जाहीर करण्याची मागणी तीव्र</t>
+          <t>Raisoni College of Business Management hosts NPTEL Awareness Workshop</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/demand-to-declare-a-wet-drought-due-to-heavy-rains-in-the-state-is-strong/129359/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/raisoni-college-of-business-management-hosts-nptel-awareness-workshop/articleshow/123351088.cms</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Ganesh Naik, Eknath Shinde, Thane, Maharashtra Politics</t>
+          <t>Nashik cops start e-meeting with police commissioner facility</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/maharashtra/ganesh-naik-eknath-shinde-thane-maharashtra-politics-54-804112</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/nashik-cops-start-e-meeting-with-police-commissioner-facility/articleshow/123351427.cms</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>मराठा सेनापति रघुजी भोंसले की तलवार मुंबई लाई गई, लंदन में हुई नीलामी में महाराष्ट्र सरकार ने हासिल की</t>
+          <t>Heavy Rains in Nanded: Rescue operations on as 5 go missing, 225 trapped in floodwaters</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>https://samarsaleel.com/%E0%A4%AE%E0%A4%B0%E0%A4%BE%E0%A4%A0%E0%A4%BE-%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A4%BE%E0%A4%AA%E0%A4%A4%E0%A4%BF-%E0%A4%B0%E0%A4%98%E0%A5%81%E0%A4%9C%E0%A5%80-%E0%A4%AD%E0%A5%8B%E0%A4%82%E0%A4%B8/490978</t>
+          <t>https://udayavani.com/national/heavy-rains-in-nanded-rescue-operations-on-as-5-go-missing-225-trapped-in-floodwaters-20250818T093308478Z?lang=en</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>मराठा सेनापती रघुजी भोसले यांची तलवार मुंबईत आणली, लंडनमध्ये झालेल्या लिलावात महाराष्ट्र सरकारने घेतली</t>
+          <t>महाराष्ट्र विधानसभा चुनाव को लेकर सुप्रीम कोर्ट का बड़ा फैसला, खारिज की परिणाम रद्द करने वाली याचिका</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/mumbai-news/maratha-commander-raghuji-bhonsle-s-sword-brought-to-mumbai-125081800027_1.html</t>
+          <t>https://hindi.news24online.com/india/supreme-court-rejects-maharashtra-assembly-election-2024-result-cancellation-petition/1288385/</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>MONSOON UPDATE: १५ ते १६ जिल्ह्यांत रेड आणि ऑरेंज अलर्ट; CM DEVENDRA FADNAVIS म्हणाले…</t>
+          <t>Yoga With Swami Ramdev : 63 करोड़ लोगों को स्पाइनल इंजरी..कैसे होगी सर्वाइकल, साइटिका की छुट्टी?</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/monsoon-update-red-and-orange-alert-in-15-to-16-districts-cm-devendra-fadnavis-said/129346/</t>
+          <t>https://www.indiatv.in/video/yoga/yoga-with-swami-ramdev-63-crore-people-have-spinal-injuries-how-will-cervical-and-sciatica-be-cured-2025-08-18-1156639</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>मनसे कामगार संघटनेच्या अनेक पदाधिका-यांचा भाजपामध्ये प्रवेश</t>
+          <t>सुप्रीम कोर्ट ने महाराष्ट्र विधानसभा चुनाव रद्द करने की मांग वाली याचिका की खारिज, विपक्ष को बड़ा झटका</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/many-office-bearers-of-mns-workers-organization-join-bjp/</t>
+          <t>https://samacharnama.com/states/maharashtra-news/supreme-court-dismisses-plea-seeking-cancellation-of/cid17260970.htm</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Ashish Shelar: मुंबईत जोरदार पाऊस! पावसाचा आढावा घेतल्यानंतर मंत्री शेलार म्हणाले, 'अत्यंत गरज असल्यास...'</t>
+          <t>Vice Presidential Election : उपराष्ट्रपती पदासाठी विरोधकांचा उमेदवार कोण? दिल्लीत घडामोडींना वेग; राहुल गांधी काय भूमिका घेणार?</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/mumbai-rain-updates-ashish-shelar-reviewed-the-rainfall-and-said-stay-safe-at-home/40069</t>
+          <t>https://www.loksatta.com/desh-videsh/who-is-the-opposition-candidate-for-the-post-of-vice-president-events-in-delhi-are-gaining-momentum-what-decision-will-mallikarjun-kharge-take-gkt-96-5313155/</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>सीपी राधाकृष्णन के उपराष्ट्रपति उम्मीदवार बनाने पर कांग्रेस को लगी मिर्ची; INDI ब्लॉक भी जल्द कर सकता है प्रत्याशी का ऐलान</t>
+          <t>हवामानाचा अंदाज: आजही पावसाचा कहर? मुंबई, पुण्यासह 7 जिल्ह्यांना रेड अलर्ट; गडचिरोलीसह 4 जिल्ह्यांना यलो अलर्ट</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>https://www.sudarshannews.in/news-detail.aspx?id=131383</t>
+          <t>https://thefocusindia.com/national-news/maharashtra-weather-red-alert-mumbai-pune-7-districts-281414/amp/</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>MMRDA launches SCLR bridge, metro institute and flyovers to ease city commute</t>
+          <t>'90 वर्षांनंतरही मी लढतो आणि तुम्ही झोपून रहा', पुण्यातील फ्लेक्सवर अण्णा हजारेंची संतप्त प्रतिक्रिया</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>https://propnewstime.com/getdetailsStories/MjA1NTQ=/mmrda-launches-sclr-bridge-metro-institute-and-flyovers-to-ease-city-commute</t>
+          <t>https://www.etvbharat.com/mr/!state/anna-hazare-outburst-on-flex-boards-in-pune-maharashtra-news-mhs25081801191</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>उत्तरकाशीतील धारली पूर : पर्वतीय विकासात हवामान धोक्यांचा समावेश करायला लावणारा आरसा</t>
+          <t>पूजेसाठी परवानगी नाही, नमाजसाठी जागाच जागा; कम्युनिस्टांचा हिंदुविरोधी चेहरा पुन्हा समोर</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!opinion/uttarkashi-floods-show-why-india-must-integrate-climate-risks-into-mountain-development-mhs25081806533</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/no-permission-for-worship-plenty-of-space-for-namaz-cpims-different-rules-for-hindus-and-muslims-in-kerala-the.html</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>'Modi Govt Selling Dreams Of 2047, Ignoring Present': Rahul Gandhi Slams Centre After Maharashtra's Thane Train Tragedy</t>
+          <t>"मला पण होती मत गायब करायची ऑफर": शरद पवारांनंतर आता बच्चू कडूंचा आरोप</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/India/modi-govt-selling-dreams-of-2047-ignoring-present-rahul-gandhi-slams-centre-after-maharashtras-thane-train-tragedy/ar-AA1Gm3WY?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.etvbharat.com/mr/!state/i-got-offer-to-remove-10000-names-from-voter-list-before-assembly-elections-bachchu-kadu-claim-maharashtra-news-mhs25081703006</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Sword of Raghuji Bhonsle arrives in Mumbai and will be on display till Aug 25</t>
+          <t>Will Bajirao Mastani Come Alive in Movie Halls Today?</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/sword-of-raghuji-bhonsle-arrives-in-mumbai-and-will-be-on-display-till-aug-25/articleshow/123371745.cms</t>
+          <t>https://caleidoscope.in/art-culture/will-bajirao-mastani-come-alive-in-movie-halls-today</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Red alert issued as heavy rain batters Mumbai; schools and colleges closed due to waterlogging</t>
+          <t>Controversy mars trailer launch of ‘Bengal Files’</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/en/red-alert-issued-as-heavy-rain-batters-mumbai-schools-and-colleges-closed-due-to-waterlogging/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolkata/controversy-mars-trailer-launch-of-bengal-files/articleshow/123339117.cms</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Rs 40kcr of investors’ money stuck with credit societies, Maharashtra govt to announce SOP for recovery</t>
+          <t>Red alert in Mumbai; BMC shuts all afternoon schools, colleges</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/rs-40kcr-of-investors-money-stuck-with-credit-societies-maharashtra-govt-to-announce-sop-for-recovery/articleshow/123367502.cms</t>
+          <t>https://www.newsbytesapp.com/news/india/mumbai-rain-havoc-to-continue-for-next-4-days/story</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Maha govt signs MoUs worth Rs 42,000 crore and creation of 28,000 jobs</t>
+          <t>Mumbai Rains: मुंबई में भारी बारिश से 12 लोगों की मौत, जगह-जगह कमर तक भरा पानी, स्कूल-कॉलेज बंद, फ्लाइट्स पर भी असर</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/states-and-uts/maharashtra/maha-govt-signs-mous-worth-rs-42000-crore-and-creation-of-28000-jobs</t>
+          <t>https://lalluram.com/mumbai-rains-7-people-died-due-to-rain-water-flooded-on-roads-schools-and-colleges-closed-flights-also-affected/</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>पंतप्रधान नरेंद्र मोदी आणि व्लादिमीर पुतीन यांच्यात संवाद - संघर्षाच्या शांततामय तोडग्यासाठी भारताचा ठाम पाठिंबा</t>
+          <t>Nanded Rain: नांदेड़ में भारी बारिश के बाद 200 लोग बाढ़ में फंसे! बादल फटने से 5 लापता, रेस्क्यू के लिए सेना बुलाई गई</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/dialogue-between-prime-minister-narendra-modi-and-vladimir-putin-indias-strong-support-for-peaceful-resolution.html</t>
+          <t>https://hindi.moneycontrol.com/india/heavy-rains-in-maharashtra-nanded-leave-over-200-stranded-in-flood-waters-five-people-missing-article-2104052.html</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>वैविध्यपूर्ण विषयांवरील पुस्तक प्रकाशित करणे हे चपराकचं साहित्यिक आंदोलन; लेखक अभिराम भडकमकर यांचे प्रतिपादन</t>
+          <t>फडणवीस ने राज्यपाल राधाकृष्णन से मुलाकात की, उन्हें शिवाजी महाराज के पत्रों की पुस्तक भेंट की</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/publishing-books-on-diverse-topics-is-a-literary-movement-of-the-chaparak-author-abhiram-bhadkamkar-asserts.html</t>
+          <t>https://hindi.theprint.in/india/fadnavis-met-governor-radhakrishnan-presented-him-a-book-of-letters-of-shivaji-maharaj/856681/</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>ठाण्यात शालेय ९-साईड हॉकी लीगला सुरुवात ; ७६ संघांचा उत्साही सहभाग</t>
+          <t>IBM to support Maharashtra in developing quantum computing initiative</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/school-9-a-side-hockey-league-begins-in-thane-76-teams-participate-enthusiastically.html</t>
+          <t>https://www.communicationstoday.co.in/ibm-to-support-maharashtra-in-developing-quantum-computing-initiative/</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Those who speak of Maharashtra 'asmita' should support Radhakrishnan for VP post: Fadnavis</t>
+          <t>CREDAI-MCHI appoints Sukhraj Nahar as 18th President</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/those-who-speak-of-maharashtra--asmita--should-support-radhakrishnan-for-vp-post--fadnavis/2832772</t>
+          <t>https://housing.com/news/credai-mchi-appoints-sukhraj-nahar-as-president/</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Rajanna’s conspiracy claim pits CM supporters against DKS’ camp</t>
+          <t>Maratha general Raghuji Bhonsle's sword brought to Mumbai</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/bengaluru/rajannas-conspiracy-claim-pits-cm-supporters-against-dks-camp/articleshow/123348301.cms</t>
+          <t>https://www.ptinews.com/story/national/maratha-general-raghuji-bhonsle's-sword-brought-to-mumbai/2833930</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Rain fury: 5 missing, 200 stranded in Nanded; local trains, flights hit in Mumbai</t>
+          <t>Mumbai rains: Heavy showers flood roads, railway tracks; bring city to standstill - video</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Rain-fury--5-missing--200-stranded-in-Nanded;-local-trains--flights-hit-in-Mumbai/2832995</t>
+          <t>https://timesofindia.indiatimes.com/india/mumbai-rains-heavy-showers-flood-roads-railway-tracks-bring-city-to-standstill-video/articleshow/123362740.cms</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Industries in Jalgaon should get power at subsidised rate, says Ajit Pawar</t>
+          <t>Mumbai rains: Torrential downpour cripples normal life; train services hit, roads flooded — see pics</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/industries-in-jalgaon-should-get-power-at-subsidised-rate-says-ajit-pawar/articleshow/123351430.cms</t>
+          <t>https://www.livemint.com/photos/mumbai-rains-torrential-downpour-cripples-normal-life-train-services-hit-roads-flooded-see-pics-11755525808666.html</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>One held for friend's murder</t>
+          <t>Rain fury: 5 missing, 200 stranded in Nanded; local trains, flights hit in Mumbai</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/one-held-for-friends-murder/articleshow/123350586.cms</t>
+          <t>https://odishatv.in/news/national/rain-fury-5-missing-200-stranded-in-nanded-local-trains-flights-hit-in-mumbai-270189</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Congress vows to ‘douse fire’ amid rifts within party</t>
+          <t>Mumbai rains: Heavy rainfall batter city as Vihar lake overflows</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/hyderabad/congress-vows-to-douse-fire-amid-rifts-within-party/articleshow/123350298.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-rains-heavy-rainfall-batter-city-as-vihar-lake-overflows-23590062</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Three of seven accused arrested in journalist attack case</t>
+          <t>IndiGo Airlines issues travel advisory for passengers flying out of Mumbai due to heavy rainfall, waterlogging in the city</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/three-of-seven-accused-arrested-in-journalist-attack-case/articleshow/123350718.cms</t>
+          <t>https://newsroompost.com/india/indigo-airlines-issues-travel-advisory-for-passengers-flying-out-of-mumbai-due-to-heavy-rainfall-waterlogging-in-the-city/5347388.html</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Sindh Mukti Sangathan holds Akhand Bharat Sankalp Diwas programme</t>
+          <t>राज्यात अतिवृष्टीच्या पार्श्वभूमीवर मुख्यमंत्री देवेंद्र फडणवीस यांचे सर्व यंत्रणांना सतर्कतेचे निर्देश</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/sindh-mukti-sangathan-holds-akhand-bharat-sankalp-diwas-programme/articleshow/123350984.cms</t>
+          <t>https://mahasamvad.in/176121/</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Two bangladeshi nationals held for illegal stay</t>
+          <t>लाटा पाहण्याच्या मोहापाई लोक अडचणीत येतात....: तुफान पावसामुळे मुख्यमंत्री फडणवीसांनी केले आवाहन</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/two-bangladeshi-nationals-held-for-illegal-stay/articleshow/123350437.cms</t>
+          <t>https://www.navarashtra.com/maharashtra/cm-devendra-fadnavis-live-press-on-mumbai-rain-update-red-alert-963319.html</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Two more suspects held in Jalaun murder case</t>
+          <t>‘तिसरी मुंबई’ घडवण्यासाठी महाराष्ट्र शासन कार्यरत</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kanpur/two-more-suspects-held-in-jalaun-murder-case/articleshow/123350447.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/-mumbai-maharashtra-government-third-mumbai-devendra-fadnavis-worli-shivdi.html</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Uzbek institute to collaborate with IGKV in agri research</t>
+          <t>18.08.2025 : मुख्यमंत्री देवेंद्र फडणवीस व सांस्कृतिक कार्य मंत्री आशिष शेलार यांनी घेतली राज्यपालांची भेट</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/raipur/uzbek-institute-to-collaborate-with-igkv-in-agri-research/articleshow/123350462.cms</t>
+          <t>https://rajbhavan-maharashtra.gov.in/18-08-2025-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB/</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Tehsildar sings at farewell, revenue min suspends him for lack of ‘decorum’</t>
+          <t>Third Mumbai: महाराष्ट्राच्या विकासाचे नवे ग्रोथ सेंटर! काय म्हणाले CM फडणवीस?</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/tehsildar-sings-at-farewell-revenue-min-suspends-him-for-lack-of-decorum/articleshow/123350443.cms</t>
+          <t>https://www.tendernama.com/tender-news/third-mumbai-new-growth-center-for-maharashtras-development-what-did-cm-fadnavis-say</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Heavy Rains in Nanded: Rescue operations on as 5 go missing, 225 trapped in floodwaters</t>
+          <t>CM Devendra Fadnavis : ‘तिसरी मुंबई’ नवा अध्याय उघडेल; रायगड जिल्ह्यात होणार विकसित</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>https://udayavani.com/national/heavy-rains-in-nanded-rescue-operations-on-as-5-go-missing-225-trapped-in-floodwaters-20250818T093308478Z?lang=en</t>
+          <t>https://www.esakal.com/mumbai/navi-mumbais-successor-the-rise-of-third-mumbai-in-raigad-district-cm-devendra-fadnavis-pjp78</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Yoga With Swami Ramdev : 63 करोड़ लोगों को स्पाइनल इंजरी..कैसे होगी सर्वाइकल, साइटिका की छुट्टी?</t>
+          <t>मराठ्यांच्या इतिहासाची साक्षीदार; श्रीमंत राजे रघुजी भोसलेंच्या ऐतिहासिक तलवारीचं लोकार्पण, पाहा खास PHOTO</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/yoga/yoga-with-swami-ramdev-63-crore-people-have-spinal-injuries-how-will-cervical-and-sciatica-be-cured-2025-08-18-1156639</t>
+          <t>https://marathi.indiatimes.com/photogallery/news/raghuji-bhosale-sword-inauguration-in-mumbai-by-cm-devendra-fadnavis/photoshow/123367923.cms</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Mumbai Rains: भारी बारिश का कहर, 7 की मौत, आदित्य ठाकरे ने BMC पर लगाए आरोप</t>
+          <t>Maharashtra Rains: राज्यात अतिवृष्टी, 7 जणांचा मृत्यू; मुख्यमंत्र्यांचे सर्व यंत्रणांना सतर्कतेचे निर्देश Maharashtra Rains: Heavy rains in the state, 7 people died; CM Devendra Fadnavis directs all agencies to be alert</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>https://www.thesandeshwahak.com/mumbai-rains-heavy-rain-wreaks-havoc-7-dead-aditya-thackeray-blames-bmc/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-rains-heavy-rains-in-the-state-7-people-died-cm-devendra-fadnavis-directs-all-agencies-to-be-alert-89603</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Vice Presidential Election : उपराष्ट्रपती पदासाठी विरोधकांचा उमेदवार कोण? दिल्लीत घडामोडींना वेग; राहुल गांधी काय भूमिका घेणार?</t>
+          <t>श्रीमंत राजे रघूजी भोसले यांची ऐतिहासिक तलवार उद्या मुंबईत दाखल</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/desh-videsh/who-is-the-opposition-candidate-for-the-post-of-vice-president-events-in-delhi-are-gaining-momentum-what-decision-will-mallikarjun-kharge-take-gkt-96-5313155/</t>
+          <t>https://mahasamvad.in/176009/</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Maharashtra politics : मुख्यमंत्र्यांच्या पत्नी गायिका, तरीही गाणे गाणाऱ्या तहसीलदारांना शिक्षा? बावनकुळे या चुकीला माफी असायलाच हवी; सामनातून हल्लाबोल</t>
+          <t>LIVE Update : मुंबईतील सर्व शाळांना उद्या सुट्टी जाहीर</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/nanded-tehsildar-prashant-thorat-suspension-shiv-sena-ubt-criticism-sanjay-raut-devendra-fadnavis-jap93</t>
+          <t>https://www.mymahanagar.com/maharashtra/live-update-mumbai-rain-best-co-operative-soc-election-live-maharashtra-update-political-rain-update-devendra-fadnavis-ajit-pawar-eknath-shinde-uddhav-thackeray-raj-thackeray/913004/</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>पूजेसाठी परवानगी नाही, नमाजसाठी जागाच जागा; कम्युनिस्टांचा हिंदुविरोधी चेहरा पुन्हा समोर</t>
+          <t>Mumbai Heavy Rain : मुंबईसाठी पुढील 10-12 तास धोक्याचे, मुख्यमंत्री फडणवीसांनी मुंबईकरांना केलं सावध</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/no-permission-for-worship-plenty-of-space-for-namaz-cpims-different-rules-for-hindus-and-muslims-in-kerala-the.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/heavy-rains-in-mumbai-next-48-hours-are-crucial-chief-minister-devendra-fadnavis-warns-citizens-to-be-alert/913099/</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Will Bajirao Mastani Come Alive in Movie Halls Today?</t>
+          <t>CM Devendra Fadnavis : हिंदवी स्वराज्याचा इतिहास नवीन पिढीपर्यंत पोहोचेल; श्रीमंत राजे रघुजी भोसले यांच्या तलवारीचे स्वागत</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>https://caleidoscope.in/art-culture/will-bajirao-mastani-come-alive-in-movie-halls-today</t>
+          <t>https://www.esakal.com/mumbai/legacy-of-hindavi-swarajya-rajarshi-raghuji-bhosales-sword-welcomed-history-cm-devendra-fadnavis-pjp78</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Controversy mars trailer launch of ‘Bengal Files’</t>
+          <t>मुंबईत पुढील आठ ते दहा तासांसाठी रेड अलर्ट, महत्त्वाचे काम असल्यास घराबाहेर पडण्याचे मुख्यमंत्री फडणवीस यांचे आवाहन</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolkata/controversy-mars-trailer-launch-of-bengal-files/articleshow/123339117.cms</t>
+          <t>https://www.saamana.com/in-mumbai-people-have-been-told-to-step-out-only-if-it-is-needed-says-cm-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Red alert in Mumbai; BMC shuts all afternoon schools, colleges</t>
+          <t>Maharashtra Rain: राज्यात पावसाचा हाहाकार! १६ जिल्ह्यांना रेड- ऑरेंज अलर्ट, मुख्यमंत्र्यांकडून सतर्क राहण्याचे आवाहन</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>https://www.newsbytesapp.com/news/india/mumbai-rain-havoc-to-continue-for-next-4-days/story</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/maharashtra-floods-cm-fadnavis-reviews-situation-ndrf-and-army-deployed-16-districts-on-red-alert-latest-news-pvm91</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Mumbai Rains: मुंबई में भारी बारिश से 12 लोगों की मौत, जगह-जगह कमर तक भरा पानी, स्कूल-कॉलेज बंद, फ्लाइट्स पर भी असर</t>
+          <t>मुख्यमंत्री वैद्यकीय सहाय्यता निधीच्या पुढाकाराने चिमुकल्या देवांशीवर यशस्वी शस्त्रक्रिया</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>https://lalluram.com/mumbai-rains-7-people-died-due-to-rain-water-flooded-on-roads-schools-and-colleges-closed-flights-also-affected/</t>
+          <t>https://mahasamvad.in/176143/</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Nanded Rain: नांदेड़ में भारी बारिश के बाद 200 लोग बाढ़ में फंसे! बादल फटने से 5 लापता, रेस्क्यू के लिए सेना बुलाई गई</t>
+          <t>Mumbai Rain Update : मुंबईत धो-धो! वाहतुकीचा खोळंबा, लोकलसेवेला फटका; मुंबईकरांची पुरती दैना; पुढील 48 तासही धोक्याचे</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>https://hindi.moneycontrol.com/india/heavy-rains-in-maharashtra-nanded-leave-over-200-stranded-in-flood-waters-five-people-missing-article-2104052.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-rain-update-heavy-rainfall-started-in-city-resulted-in-disruption-of-life-and-mumbai-local-cm-fadnavis-reviewed/articleshow/123363662.cms</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>फडणवीस ने राज्यपाल राधाकृष्णन से मुलाकात की, उन्हें शिवाजी महाराज के पत्रों की पुस्तक भेंट की</t>
+          <t>Ashish Shelar : मुंबईत मुसळधार.. परिस्थितीचा आढावा घेतल्यानंतर शेलारांकडून मुंबईकरांना एकच आवाहन; आज,...</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/fadnavis-met-governor-radhakrishnan-presented-him-a-book-of-letters-of-shivaji-maharaj/856681/</t>
+          <t>https://www.tv9marathi.com/videos/ashish-shelar-appeals-to-mumbaikars-after-review-of-rains-at-bmc-stay-at-house-during-mumbai-heavy-rains-1472440.html</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>IBM to support Maharashtra in developing quantum computing initiative</t>
+          <t>रघुजीराजे भोसले यांची तलवार मुंबईत शौर्याचा वारसा इतिहाप्रेमींसाठी खुला; मराठा साम्राज्याचा वारसा परत मिळवण्याचा प्रयत्न – मुख्यमंत्री</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>https://www.communicationstoday.co.in/ibm-to-support-maharashtra-in-developing-quantum-computing-initiative/</t>
+          <t>https://www.saamana.com/raghujiraje-bhosale-sword-a-legacy-of-bravery-is-open-to-history-lovers-in-mumbai-an-attempt-to-reclaim-the-legacy-of-the-maratha-empire-said-by-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Heavy rainfall causes 7 deaths, crop loss in Maharashtra as alerts continue</t>
+          <t>तिसरी MUMBAI आर्थिक विकासाचा नवा अध्याय, गोल्डमन सॅक्सच्या नव्या मुंबई कार्यालयाचे उद्घाटन</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/heavy-rainfall-causes-7-deaths-crop-loss-in-maharashtra-as-alerts-continue/articleshow/123368187.cms</t>
+          <t>https://www.timemaharashtra.com/maharashtra/mumbai/third-mumbai-a-new-chapter-in-economic-development-goldman-sachs-new-mumbai-office-inaugurated/129385/</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>NDA’s Vice President nominee CP Radhakrishnan to reach Delhi today: sources</t>
+          <t>राज्यात अतिवृष्टीच्या पार्श्वभूमीवर CM DEVENDRA FADNAVIS यांचे सर्व यंत्रणांना सतर्कतेचे निर्देश</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>https://www.thestatesman.com/india/ndas-vice-president-nominee-cp-radhakrishnan-to-reach-delhi-today-sources-1503472953.html</t>
+          <t>https://www.timemaharashtra.com/maharashtra/cm-devendra-fadnavis-instructs-all-agencies-to-be-alert-in-the-wake-of-heavy-rains-in-the-state/129378/</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Third Mumbai in Raigad to become Maharashtra’s new economic powerhouse: CM Fadnavis</t>
+          <t>'Third Mumbai' to boost metropolitan region development Fadnavis</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>https://www.daijiworld.com/index.php/news/newsDisplay?newsID=1289652</t>
+          <t>https://www.theweek.in/wire-updates/business/2025/08/19/bom3-mh-third-mumbai-cm.html</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Mumbai rains: Heavy showers flood roads, railway tracks; bring city to standstill - video</t>
+          <t>Transformative Leadership: Sukhraj Nahar Steers CREDAI-MCHI Towards Urban Revolution</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/mumbai-rains-heavy-showers-flood-roads-railway-tracks-bring-city-to-standstill-video/articleshow/123362740.cms</t>
+          <t>https://www.devdiscourse.com/article/business/3545330-transformative-leadership-sukhraj-nahar-steers-credai-mchi-towards-urban-revolution</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Maratha general Raghuji Bhonsle's sword brought to Mumbai</t>
+          <t>The perks and costs of ‘Ladki Bahin’</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/maratha-general-raghuji-bhonsle's-sword-brought-to-mumbai/2833930</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/the-perks-and-costs-of-ladki-bahin-101755575344332.html</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Mumbai reels under 177 mm rain in 8 hours; flights hit, schools shut as red alert issued</t>
+          <t>LGEC 2025: 'लाडकी बहीण' योजनेमुळे महाराष्ट्रातील अर्थव्यवस्थेला चालनाच मिळाली; सुनील तटकरेंनी समजावलं 'गणित'</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Aug/18/mumbai-rains-flight-operations-hit-schools-colleges-shut-as-imd-issues-red-alert</t>
+          <t>https://www.lokmat.com/international/lgec-2025-ladki-bahin-scheme-has-given-a-boost-to-the-economy-of-maharashtra-sunil-tatkare-rahul-narvekar-explained-a-a629/</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Mumbai rains: Torrential downpour cripples normal life; train services hit, roads flooded — see pics</t>
+          <t>ShivBhojan Thali News: शिवभोजन थाळी योजना संकटात: करोडो रुपयांची बिलं राज्य शासनाने थकवली, केंद्र चालक आंदोलनाच्या पावित्र्यात</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/photos/mumbai-rains-torrential-downpour-cripples-normal-life-train-services-hit-roads-flooded-see-pics-11755525808666.html</t>
+          <t>https://pudhari.news/maharashtra/mumbai/shiv-bhojan-thali-scheme-crisis-maharashtra-government-pending-bills-protest-mk94</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Rain fury: 5 missing, 200 stranded in Nanded; local trains, flights hit in Mumbai</t>
+          <t>803 Families Stranded as Lokmanya Nagar Redevelopment Hits Political Roadblock</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>https://odishatv.in/news/national/rain-fury-5-missing-200-stranded-in-nanded-local-trains-flights-hit-in-mumbai-270189</t>
+          <t>https://punemirror.com/city/civic/803-families-stranded-as-lokmanya-nagar-redevelopment-hits-political-roadblock/</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>Mumbai rains: Heavy rainfall batter city as Vihar lake overflows</t>
+          <t>महाराष्ट्र के नांदेड़ जिले में मूसलाधार बारिश से आई बाढ़ में 225 नागरिक फंसे,बचाव कार्य जारी</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-rains-heavy-rainfall-batter-city-as-vihar-lake-overflows-23590062</t>
+          <t>https://www.yugwarta.com/Encyc/2025/8/18/nanded-flood-resues-continew.html</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>'Third Mumbai' Will Open A New Chapter Of Economic Development: Maha CM</t>
+          <t>जन्माष्टमीच्या मिरवणुकीत रथाला वीजेच्या तारेला स्पर्श होताच पाच जणांचा मृत्यू, चार जण जखमी</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>https://menafn.com/1109941619/Third-Mumbai-Will-Open-A-New-Chapter-Of-Economic-Development-Maha-CM</t>
+          <t>https://www.etvbharat.com/mr/!bharat/krishna-janmashtami-2025-celebrations-procession-turn-tragic-in-hyderabad-five-devotees-electrocuted-to-death-after-chariot-comes-in-contact-electric-wire-maharashtra-news-mhs25081800993</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>IndiGo Airlines issues travel advisory for passengers flying out of Mumbai due to heavy rainfall, waterlogging in the city</t>
+          <t>18.08.2025 : मुख्यमंत्री व सांस्कृतिक कार्य मंत्री यांनी घेतली राज्यपालांची भेट | राजभवन महाराष्ट्र | भारत</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>https://newsroompost.com/india/indigo-airlines-issues-travel-advisory-for-passengers-flying-out-of-mumbai-due-to-heavy-rainfall-waterlogging-in-the-city/5347388.html</t>
+          <t>https://rajbhavan-maharashtra.gov.in/gallery/18-08-2025-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%B5-%E0%A4%B8%E0%A4%BE%E0%A4%82%E0%A4%B8%E0%A5%8D%E0%A4%95%E0%A5%83%E0%A4%A4/</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>मुंबई में भारी बारिश का कहर, 19 अगस्त को बंद रहेंगे सभी स्कूल-कॉलेज</t>
+          <t>Rain wreaks havoc in Maharashtra, brings Mumbai to a standstill</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>https://hindi.news24online.com/india/mumbai-and-jammu-kashmir-heavy-rain-rain-school-and-college-closed/1288306/</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/rain-wreaks-havoc-in-maharashtra-brings-mumbai-to-a-standstill/article69948564.ece</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>राज्यात अतिवृष्टीच्या पार्श्वभूमीवर मुख्यमंत्री देवेंद्र फडणवीस यांचे सर्व यंत्रणांना सतर्कतेचे निर्देश</t>
+          <t>Mumbai rains: BMC announces holiday for schools, colleges on August 19</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176121/</t>
+          <t>https://www.cnbctv18.com/india/are-mumbai-schools-colleges-open-or-close-on-august-19-19655564.htm</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>लाटा पाहण्याच्या मोहापाई लोक अडचणीत येतात....: तुफान पावसामुळे मुख्यमंत्री फडणवीसांनी केले आवाहन</t>
+          <t>Mumbai Rains Live News: Torrential rains cripple Mumbai; roads flooded, local trains delayed and schools, colleges closed amid ‘Red’ alert</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/cm-devendra-fadnavis-live-press-on-mumbai-rain-update-red-alert-963319.html</t>
+          <t>https://www.thehindubusinessline.com/news/mumbai-weather-mumbai-rains-live-news-updates/article69946123.ece</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>‘तिसरी मुंबई’ घडवण्यासाठी महाराष्ट्र शासन कार्यरत</t>
+          <t>School Holiday: Schools in Mumbai, Thane to remain closed on Tuesday amid IMD's Red Alert for heavy rains</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/-mumbai-maharashtra-government-third-mumbai-devendra-fadnavis-worli-shivdi.html</t>
+          <t>https://www.livemint.com/news/india/school-holiday-schools-in-mumbai-thane-to-remain-closed-on-tuesday-amid-imds-red-alert-for-heavy-rains-11755527340477.html</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>18.08.2025 : मुख्यमंत्री देवेंद्र फडणवीस व सांस्कृतिक कार्य मंत्री आशिष शेलार यांनी घेतली राज्यपालांची भेट</t>
+          <t>Pune Can Get Underground Road Network To Beat Traffic Woes</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>https://rajbhavan-maharashtra.gov.in/18-08-2025-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB/</t>
+          <t>https://trak.in/stories/pune-can-get-underground-road-network-to-beat-traffic-woes/</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Third Mumbai: महाराष्ट्राच्या विकासाचे नवे ग्रोथ सेंटर! काय म्हणाले CM फडणवीस?</t>
+          <t>'मराठी'कडं दुर्लक्ष भोवणार; शासकीय, निमशासकीय कार्यालयांमधील अधिकाऱ्यांवर थेट न्यायिक कारवाई होणार</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>https://www.tendernama.com/tender-news/third-mumbai-new-growth-center-for-maharashtras-development-what-did-cm-fadnavis-say</t>
+          <t>https://www.etvbharat.com/mr/!state/penal-action-will-be-taken-against-those-who-ignore-the-marathi-language-in-government-and-semi-government-offices-in-maharashtra-maharashtra-news-mhs25081803599</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>Mumbai Heavy Rain : मुंबईसाठी पुढील 10-12 तास धोक्याचे, मुख्यमंत्री फडणवीसांनी मुंबईकरांना केलं सावध</t>
+          <t>अतिवृष्टीमुळे होणाऱ्या नुकसानीचे तातडीने पंचनामे करा; मंत्री मकरंद जाधव-पाटील यांचे निर्देश</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/heavy-rains-in-mumbai-next-48-hours-are-crucial-chief-minister-devendra-fadnavis-warns-citizens-to-be-alert/913099/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/immediately-conduct-a-panchnama-of-the-damage-caused-by-heavy-rains-minister-makarand-jadhav-patil-directs.html</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>Maharashtra Rains: राज्यात अतिवृष्टी, 7 जणांचा मृत्यू; मुख्यमंत्र्यांचे सर्व यंत्रणांना सतर्कतेचे निर्देश Maharashtra Rains: Heavy rains in the state, 7 people died; CM Devendra Fadnavis directs all agencies to be alert</t>
+          <t>सामाजिक कामात कार्यरत राहून मिळणारा आनंद मोठा: पांडुरंग चोरमले</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-rains-heavy-rains-in-the-state-7-people-died-cm-devendra-fadnavis-directs-all-agencies-to-be-alert-89603</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/the-joy-of-working-in-social-work-is-immense-pandurang-chormale.html</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>श्रीमंत राजे रघूजी भोसले यांची ऐतिहासिक तलवार उद्या मुंबईत दाखल</t>
+          <t>Highlights Mumbai Rains: मुंबईसह राज्यात पावसाचा धुमाकूळ; अनेक गावांचा संपर्क तुटला</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176009/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/mumbai-rains-live-updates-mumbai-red-alert-issue-streets-inundated-and-hits-local-trains-lb-89483</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>मराठ्यांच्या इतिहासाची साक्षीदार; श्रीमंत राजे रघुजी भोसलेंच्या ऐतिहासिक तलवारीचं लोकार्पण, पाहा खास PHOTO</t>
+          <t>शाळा अंतर्गत फेरीमध्ये विद्यार्थ्यांचा सत्कार सोहळा</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/photogallery/news/raghuji-bhosale-sword-inauguration-in-mumbai-by-cm-devendra-fadnavis/photoshow/123367923.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/student-felicitation-ceremony-during-the-schools-internal-parade.html</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>मुंबईत पुढील आठ ते दहा तासांसाठी रेड अलर्ट, महत्त्वाचे काम असल्यास घराबाहेर पडण्याचे मुख्यमंत्री फडणवीस यांचे आवाहन</t>
+          <t>Maharashtra Rain Update: 19 ऑगस्टलाही सावधान..., महाराष्ट्रातील 'या' जिल्ह्यांना रेड अलर्ट</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/in-mumbai-people-have-been-told-to-step-out-only-if-it-is-needed-says-cm-devendra-fadnavis/</t>
+          <t>https://www.navarashtra.com/maharashtra/mahrashtra-mumbai-rain-latest-update-orange-alert-till-august-20-red-alert-issued-in-several-districts-963438.html</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>Maharashtra Rain: राज्यात पावसाचा हाहाकार! १६ जिल्ह्यांना रेड- ऑरेंज अलर्ट, मुख्यमंत्र्यांकडून सतर्क राहण्याचे आवाहन</t>
+          <t>रत्नागिरीत मुसळधार पावसानं हाहाकार: शाळा महाविद्यालयाला सुटी</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/mumbai-pune/maharashtra-floods-cm-fadnavis-reviews-situation-ndrf-and-army-deployed-16-districts-on-red-alert-latest-news-pvm91</t>
+          <t>https://www.etvbharat.com/mr/!state/holiday-for-schools-and-colleges-in-ratnagiri-due-to-heavy-rain-ratnagiri-district-administration-decision-orange-alert-weather-forecast-maharashtra-news-mhs25081806850</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>Mumbai Rain Update : मुंबईत धो-धो! वाहतुकीचा खोळंबा, लोकलसेवेला फटका; मुंबईकरांची पुरती दैना; पुढील 48 तासही धोक्याचे</t>
+          <t>रायगड जिल्हा मुसळधार पावसानं झोडपला; सावित्री नदीचं पाणी महाड शहरात शिरलं</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-rain-update-heavy-rainfall-started-in-city-resulted-in-disruption-of-life-and-mumbai-local-cm-fadnavis-reviewed/articleshow/123363662.cms</t>
+          <t>https://www.etvbharat.com/mr/!state/heavy-rain-in-raigad-district-savitri-river-flood-landslide-in-mangaon-maharashtra-news-mhs25081804820</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>Maharashtra BIG Decisions : घरांपासून नोकऱ्यांपर्यंत… महाराष्ट्राचे दमदार महानिर्णय, हा व्हिडीओ...</t>
+          <t>मुखेड तालुक्यात ढगफुटी सदृश्य पाऊस; लेंडी धरणाचं पाणी शिरलं गावात, एसडीआरएफ पथकाकडून मदत कार्य सुरू</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/maharashtras-major-decisions-police-recruitment-housing-projects-and-historical-artefact-return-1472726.html</t>
+          <t>https://www.etvbharat.com/mr/!state/nanded-rain-update-cloudburst-and-heavy-rain-in-lendi-dam-mukhed-in-nanded-maharashtra-news-mhs25081802339</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>रघुजीराजे भोसले यांची तलवार मुंबईत शौर्याचा वारसा इतिहाप्रेमींसाठी खुला; मराठा साम्राज्याचा वारसा परत मिळवण्याचा प्रयत्न – मुख्यमंत्री</t>
+          <t>FIR policy leads to 60% drop in city’s drunk driving cases</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/raghujiraje-bhosale-sword-a-legacy-of-bravery-is-open-to-history-lovers-in-mumbai-an-attempt-to-reclaim-the-legacy-of-the-maratha-empire-said-by-chief-minister-devendra-fadnavis/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/fir-policy-leads-to-60-drop-in-citys-drunk-driving-cases/articleshow/123351105.cms</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>तिसरी MUMBAI आर्थिक विकासाचा नवा अध्याय, गोल्डमन सॅक्सच्या नव्या मुंबई कार्यालयाचे उद्घाटन</t>
+          <t>मंत्री संजय शिरसाट यांच्याकडून अधिकारांचा गैरवापर; 5 हजार कोटींचा गोलमाल झाल्याचा रोहित पवारांचा आरोप</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/mumbai/third-mumbai-a-new-chapter-in-economic-development-goldman-sachs-new-mumbai-office-inaugurated/129385/</t>
+          <t>https://www.etvbharat.com/mr/!state/minister-sanjay-shirsat-misuses-powers-rohit-pawar-alleges-rs-5000-crore-scam-mumbai-maharashtra-news-mhs25081804077</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>राज्यात अतिवृष्टीच्या पार्श्वभूमीवर CM DEVENDRA FADNAVIS यांचे सर्व यंत्रणांना सतर्कतेचे निर्देश</t>
+          <t>Hebbal Flyover Inaugurated: ₹80 Crore Project Promises Traffic Relief in North Bengaluru</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/cm-devendra-fadnavis-instructs-all-agencies-to-be-alert-in-the-wake-of-heavy-rains-in-the-state/129378/</t>
+          <t>https://panasiabiz.com/111088/cm-siddaramaiah-and-dycm-dk-shivakumar-inaugurate-%E2%82%B980-crore-hebbal-flyover-to-ease-bengaluru-traffic/</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>'Third Mumbai' to boost metropolitan region development Fadnavis</t>
+          <t>'Third Mumbai' to boost MMR development says Fadnavis invites pvt sector to join in its creation</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/business/2025/08/19/bom3-mh-third-mumbai-cm.html</t>
+          <t>https://www.theweek.in/wire-updates/business/2025/08/18/bom51-mh-cm-third-mumbai.html</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>The perks and costs of ‘Ladki Bahin’</t>
+          <t>Mumbai continues to be on red alert; heavy rain disrupts travel, shuts offices &amp; educational institutions</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/the-perks-and-costs-of-ladki-bahin-101755575344332.html</t>
+          <t>https://m.economictimes.com/news/weather/mumbai-on-red-alert-for-second-consecutive-day-heavy-rain-disrupts-travel-shuts-educational-institutions/articleshow/123375296.cms</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>LGEC 2025: 'लाडकी बहीण' योजनेमुळे महाराष्ट्रातील अर्थव्यवस्थेला चालनाच मिळाली; सुनील तटकरेंनी समजावलं 'गणित'</t>
+          <t>Maha CM asks agencies to be on alert mode after heavy rainfall and flash floods</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/international/lgec-2025-ladki-bahin-scheme-has-given-a-boost-to-the-economy-of-maharashtra-sunil-tatkare-rahul-narvekar-explained-a-a629/</t>
+          <t>https://www.lokmattimes.com/national/maha-cm-asks-agencies-to-be-on-alert-mode-after-heavy-rainfall-and-flash-floods/</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>ShivBhojan Thali News: शिवभोजन थाळी योजना संकटात: करोडो रुपयांची बिलं राज्य शासनाने थकवली, केंद्र चालक आंदोलनाच्या पावित्र्यात</t>
+          <t>Over ₹6.52 Crore Medical Aid Distributed To 5,000 Beneficiaries In Pune District</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
-        <is>
-          <t>https://pudhari.news/maharashtra/mumbai/shiv-bhojan-thali-scheme-crisis-maharashtra-government-pending-bills-protest-mk94</t>
-        </is>
-      </c>
-    </row>
-    <row r="511">
-      <c r="A511" t="inlineStr">
-        <is>
-          <t>Rajnath reaches out to DMK, TMC, BJD for consensus on VP nominee</t>
-        </is>
-      </c>
-      <c r="B511" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/en-in/news/other/rajnath-reaches-out-to-dmk-tmc-bjd-for-consensus-on-vp-nominee/ar-AA1KKGcl</t>
-        </is>
-      </c>
-    </row>
-    <row r="512">
-      <c r="A512" t="inlineStr">
-        <is>
-          <t>Clean image and cordial relations with netas across political parties paves Maharashtra governor CP Radha</t>
-        </is>
-      </c>
-      <c r="B512" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/clean-image-and-cordial-relations-with-netas-across-political-parties-paves-maharashtra-governor-cp-radhakrishnans-path-to-vice-presidents-office/articleshow/123350030.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="513">
-      <c r="A513" t="inlineStr">
-        <is>
-          <t>803 Families Stranded as Lokmanya Nagar Redevelopment Hits Political Roadblock</t>
-        </is>
-      </c>
-      <c r="B513" t="inlineStr">
-        <is>
-          <t>https://punemirror.com/city/civic/803-families-stranded-as-lokmanya-nagar-redevelopment-hits-political-roadblock/</t>
-        </is>
-      </c>
-    </row>
-    <row r="514">
-      <c r="A514" t="inlineStr">
-        <is>
-          <t>महाराष्ट्र के नांदेड़ जिले में मूसलाधार बारिश से आई बाढ़ में 225 नागरिक फंसे,बचाव कार्य जारी</t>
-        </is>
-      </c>
-      <c r="B514" t="inlineStr">
-        <is>
-          <t>https://www.yugwarta.com/Encyc/2025/8/18/nanded-flood-resues-continew.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="515">
-      <c r="A515" t="inlineStr">
-        <is>
-          <t>मानसून में हाल बेहाल, भारी बारिश से इस राज्य में जगह-जगह भरा पानी, स्कूल-कॉलेज किए बंद</t>
-        </is>
-      </c>
-      <c r="B515" t="inlineStr">
-        <is>
-          <t>https://www.patrika.com/national-news/heavy-rain-alert-in-mumbai-monsoon-gained-momentum-know-imd-weather-update-19874723</t>
-        </is>
-      </c>
-    </row>
-    <row r="516">
-      <c r="A516" t="inlineStr">
-        <is>
-          <t>महाराष्ट्र में भारी बारिश से सात लोगों की मौत, 200 ग्रामीण फंसे</t>
-        </is>
-      </c>
-      <c r="B516" t="inlineStr">
-        <is>
-          <t>https://hindi.theprint.in/india/seven-people-died-due-to-heavy-rains-in-maharashtra-200-villagers-stranded/856903/</t>
-        </is>
-      </c>
-    </row>
-    <row r="517">
-      <c r="A517" t="inlineStr">
-        <is>
-          <t>रमेश बिधूड़ी ने राधाकृष्णन को दी शुभकामनाएं, कहा- 'अच्छे उपराष्ट्रपति साबित होंगे'</t>
-        </is>
-      </c>
-      <c r="B517" t="inlineStr">
-        <is>
-          <t>https://www.khaskhabar.com/local/delhi-ncr/delhi-news/news-ramesh-bidhuri-congratulated-radhakrishnan-said---he-will-prove-to-be-a-good-vice-president-news-hindi-1-745268-KKN.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="518">
-      <c r="A518" t="inlineStr">
-        <is>
-          <t>18.08.2025 : मुख्यमंत्री व सांस्कृतिक कार्य मंत्री यांनी घेतली राज्यपालांची भेट | राजभवन महाराष्ट्र | भारत</t>
-        </is>
-      </c>
-      <c r="B518" t="inlineStr">
-        <is>
-          <t>https://rajbhavan-maharashtra.gov.in/gallery/18-08-2025-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%B5-%E0%A4%B8%E0%A4%BE%E0%A4%82%E0%A4%B8%E0%A5%8D%E0%A4%95%E0%A5%83%E0%A4%A4/</t>
-        </is>
-      </c>
-    </row>
-    <row r="519">
-      <c r="A519" t="inlineStr">
-        <is>
-          <t>Rain wreaks havoc in Maharashtra, brings Mumbai to a standstill</t>
-        </is>
-      </c>
-      <c r="B519" t="inlineStr">
-        <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/rain-wreaks-havoc-in-maharashtra-brings-mumbai-to-a-standstill/article69948564.ece</t>
-        </is>
-      </c>
-    </row>
-    <row r="520">
-      <c r="A520" t="inlineStr">
-        <is>
-          <t>Mumbai rains: BMC announces holiday for schools, colleges on August 19</t>
-        </is>
-      </c>
-      <c r="B520" t="inlineStr">
-        <is>
-          <t>https://www.cnbctv18.com/india/are-mumbai-schools-colleges-open-or-close-on-august-19-19655564.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="521">
-      <c r="A521" t="inlineStr">
-        <is>
-          <t>India monsoon updates: Heavy to very heavy rainfall at few places in Mumbai; residents told to ‘avoid unnecessary travel’</t>
-        </is>
-      </c>
-      <c r="B521" t="inlineStr">
-        <is>
-          <t>https://www.thehindu.com/news/national/india-monsoon-live-mumbai-rains-yamuna-river-flood-alert-delhi-kashmir-cloudburst-updates-august-18/article69946105.ece</t>
-        </is>
-      </c>
-    </row>
-    <row r="522">
-      <c r="A522" t="inlineStr">
-        <is>
-          <t>Maharashtra rain fury: Seven dead, crops damaged; Mumbai, Thane, other districts on red alert</t>
-        </is>
-      </c>
-      <c r="B522" t="inlineStr">
-        <is>
-          <t>https://www.newindianexpress.com/nation/2025/Aug/18/maharashtra-rain-fury-seven-dead-crops-damaged-mumbai-thane-other-districts-on-red-alert</t>
-        </is>
-      </c>
-    </row>
-    <row r="523">
-      <c r="A523" t="inlineStr">
-        <is>
-          <t>Mumbai Rains Live News: Torrential rains cripple Mumbai; roads flooded, local trains delayed and schools, colleges closed amid ‘Red’ alert</t>
-        </is>
-      </c>
-      <c r="B523" t="inlineStr">
-        <is>
-          <t>https://www.thehindubusinessline.com/news/mumbai-weather-mumbai-rains-live-news-updates/article69946123.ece</t>
-        </is>
-      </c>
-    </row>
-    <row r="524">
-      <c r="A524" t="inlineStr">
-        <is>
-          <t>School Holiday: Schools in Mumbai, Thane to remain closed on Tuesday amid IMD's Red Alert for heavy rains</t>
-        </is>
-      </c>
-      <c r="B524" t="inlineStr">
-        <is>
-          <t>https://www.livemint.com/news/india/school-holiday-schools-in-mumbai-thane-to-remain-closed-on-tuesday-amid-imds-red-alert-for-heavy-rains-11755527340477.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="525">
-      <c r="A525" t="inlineStr">
-        <is>
-          <t>Pune Can Get Underground Road Network To Beat Traffic Woes</t>
-        </is>
-      </c>
-      <c r="B525" t="inlineStr">
-        <is>
-          <t>https://trak.in/stories/pune-can-get-underground-road-network-to-beat-traffic-woes/</t>
-        </is>
-      </c>
-    </row>
-    <row r="526">
-      <c r="A526" t="inlineStr">
-        <is>
-          <t>Rainfall Alert: All schools and colleges closed due to heavy rains, IMD issued red alert</t>
-        </is>
-      </c>
-      <c r="B526" t="inlineStr">
-        <is>
-          <t>https://www.informalnewz.com/rainfall-alert-all-schools-and-colleges-closed-due-to-heavy-rains-imd-issued-red-alert/</t>
-        </is>
-      </c>
-    </row>
-    <row r="527">
-      <c r="A527" t="inlineStr">
-        <is>
-          <t>'मराठी'कडं दुर्लक्ष भोवणार; शासकीय, निमशासकीय कार्यालयांमधील अधिकाऱ्यांवर थेट न्यायिक कारवाई होणार</t>
-        </is>
-      </c>
-      <c r="B527" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/mr/!state/penal-action-will-be-taken-against-those-who-ignore-the-marathi-language-in-government-and-semi-government-offices-in-maharashtra-maharashtra-news-mhs25081803599</t>
-        </is>
-      </c>
-    </row>
-    <row r="528">
-      <c r="A528" t="inlineStr">
-        <is>
-          <t>सामाजिक कामात कार्यरत राहून मिळणारा आनंद मोठा: पांडुरंग चोरमले</t>
-        </is>
-      </c>
-      <c r="B528" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/the-joy-of-working-in-social-work-is-immense-pandurang-chormale.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="529">
-      <c r="A529" t="inlineStr">
-        <is>
-          <t>मराठी चित्रपटसृष्टीत भव्यतेचं नवं पर्व घेऊन येणाऱ्या ‘दशावतार’ चित्रपटाचं जबरदस्त ट्रेलर प्रदर्शित</t>
-        </is>
-      </c>
-      <c r="B529" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/mr/!entertainment/trailer-of-the-film-dashavatar-which-brings-a-new-era-of-grandeur-to-marathi-cinema-is-released-maharashtra-news-mhs25081901382</t>
-        </is>
-      </c>
-    </row>
-    <row r="530">
-      <c r="A530" t="inlineStr">
-        <is>
-          <t>शाळा अंतर्गत फेरीमध्ये विद्यार्थ्यांचा सत्कार सोहळा</t>
-        </is>
-      </c>
-      <c r="B530" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/student-felicitation-ceremony-during-the-schools-internal-parade.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="531">
-      <c r="A531" t="inlineStr">
-        <is>
-          <t>Mumbai Rain Update: मुंबईत पुढील चार तास धो-धो, रेड अलर्ट जारी, लोकल ट्रेन उशिराने, नागरिकांना घराबाहेर न पडण्याचं आवाहन</t>
-        </is>
-      </c>
-      <c r="B531" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-heavy-rain-expected-by-imd-red-alert-heavy-rainfall-local-train-updates/articleshow/123376293.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="532">
-      <c r="A532" t="inlineStr">
-        <is>
-          <t>Maharashtra Rain Update: 19 ऑगस्टलाही सावधान..., महाराष्ट्रातील 'या' जिल्ह्यांना रेड अलर्ट</t>
-        </is>
-      </c>
-      <c r="B532" t="inlineStr">
-        <is>
-          <t>https://www.navarashtra.com/maharashtra/mahrashtra-mumbai-rain-latest-update-orange-alert-till-august-20-red-alert-issued-in-several-districts-963438.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="533">
-      <c r="A533" t="inlineStr">
-        <is>
-          <t>रत्नागिरीत मुसळधार पावसानं हाहाकार: शाळा महाविद्यालयाला सुटी</t>
-        </is>
-      </c>
-      <c r="B533" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/mr/!state/holiday-for-schools-and-colleges-in-ratnagiri-due-to-heavy-rain-ratnagiri-district-administration-decision-orange-alert-weather-forecast-maharashtra-news-mhs25081806850</t>
-        </is>
-      </c>
-    </row>
-    <row r="534">
-      <c r="A534" t="inlineStr">
-        <is>
-          <t>रायगड जिल्हा मुसळधार पावसानं झोडपला; सावित्री नदीचं पाणी महाड शहरात शिरलं</t>
-        </is>
-      </c>
-      <c r="B534" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/mr/!state/heavy-rain-in-raigad-district-savitri-river-flood-landslide-in-mangaon-maharashtra-news-mhs25081804820</t>
-        </is>
-      </c>
-    </row>
-    <row r="535">
-      <c r="A535" t="inlineStr">
-        <is>
-          <t>मुखेड तालुक्यात ढगफुटी सदृश्य पाऊस; लेंडी धरणाचं पाणी शिरलं गावात, एसडीआरएफ पथकाकडून मदत कार्य सुरू</t>
-        </is>
-      </c>
-      <c r="B535" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/mr/!state/nanded-rain-update-cloudburst-and-heavy-rain-in-lendi-dam-mukhed-in-nanded-maharashtra-news-mhs25081802339</t>
-        </is>
-      </c>
-    </row>
-    <row r="536">
-      <c r="A536" t="inlineStr">
-        <is>
-          <t>राज्यात पावसाचा हाहाकार! मुख्यमंत्री फडणवीस अॅक्टीव्ह मोडवर, सतर्क राहण्याचे आवाहन</t>
-        </is>
-      </c>
-      <c r="B536" t="inlineStr">
-        <is>
-          <t>https://civicmirror.in/maharashtra/maharashtra-rain-cm-fadnavis-reviews-situation-16-districts-on-red-alert/</t>
-        </is>
-      </c>
-    </row>
-    <row r="537">
-      <c r="A537" t="inlineStr">
-        <is>
-          <t>FIR policy leads to 60% drop in city’s drunk driving cases</t>
-        </is>
-      </c>
-      <c r="B537" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/fir-policy-leads-to-60-drop-in-citys-drunk-driving-cases/articleshow/123351105.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="538">
-      <c r="A538" t="inlineStr">
-        <is>
-          <t>मंत्री संजय शिरसाट यांच्याकडून अधिकारांचा गैरवापर; 5 हजार कोटींचा गोलमाल झाल्याचा रोहित पवारांचा आरोप</t>
-        </is>
-      </c>
-      <c r="B538" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/mr/!state/minister-sanjay-shirsat-misuses-powers-rohit-pawar-alleges-rs-5000-crore-scam-mumbai-maharashtra-news-mhs25081804077</t>
-        </is>
-      </c>
-    </row>
-    <row r="539">
-      <c r="A539" t="inlineStr">
-        <is>
-          <t>Mumbai on Red Alert After Over 500mm Rain in 84 Hours; Schools Shut, Flights Delayed, Traffic Paralyzed</t>
-        </is>
-      </c>
-      <c r="B539" t="inlineStr">
-        <is>
-          <t>https://thelogicalindian.com/mumbai-on-red-alert-after-over-500mm-rain-in-84-hours-schools-shut-flights-delayed-traffic-paralyzed/</t>
-        </is>
-      </c>
-    </row>
-    <row r="540">
-      <c r="A540" t="inlineStr">
-        <is>
-          <t>Hebbal Flyover Inaugurated: ₹80 Crore Project Promises Traffic Relief in North Bengaluru</t>
-        </is>
-      </c>
-      <c r="B540" t="inlineStr">
-        <is>
-          <t>https://panasiabiz.com/111088/cm-siddaramaiah-and-dycm-dk-shivakumar-inaugurate-%E2%82%B980-crore-hebbal-flyover-to-ease-bengaluru-traffic/</t>
-        </is>
-      </c>
-    </row>
-    <row r="541">
-      <c r="A541" t="inlineStr">
-        <is>
-          <t>'Third Mumbai' to boost MMR development says Fadnavis invites pvt sector to join in its creation</t>
-        </is>
-      </c>
-      <c r="B541" t="inlineStr">
-        <is>
-          <t>https://www.theweek.in/wire-updates/business/2025/08/18/bom51-mh-cm-third-mumbai.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="542">
-      <c r="A542" t="inlineStr">
-        <is>
-          <t>Maharashtra on high alert as heavy rain leaves 6 dead</t>
-        </is>
-      </c>
-      <c r="B542" t="inlineStr">
-        <is>
-          <t>https://m.economictimes.com/news/india/maharashtra-on-high-alert-as-heavy-rain-leaves-6-dead/articleshow/123371509.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="543">
-      <c r="A543" t="inlineStr">
-        <is>
-          <t>Mumbai continues to be on red alert; heavy rain disrupts travel, shuts offices &amp; educational institutions</t>
-        </is>
-      </c>
-      <c r="B543" t="inlineStr">
-        <is>
-          <t>https://m.economictimes.com/news/weather/mumbai-on-red-alert-for-second-consecutive-day-heavy-rain-disrupts-travel-shuts-educational-institutions/articleshow/123375296.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="544">
-      <c r="A544" t="inlineStr">
-        <is>
-          <t>Maha CM asks agencies to be on alert mode after heavy rainfall and flash floods</t>
-        </is>
-      </c>
-      <c r="B544" t="inlineStr">
-        <is>
-          <t>https://www.lokmattimes.com/national/maha-cm-asks-agencies-to-be-on-alert-mode-after-heavy-rainfall-and-flash-floods/</t>
-        </is>
-      </c>
-    </row>
-    <row r="545">
-      <c r="A545" t="inlineStr">
-        <is>
-          <t>Over ₹6.52 Crore Medical Aid Distributed To 5,000 Beneficiaries In Pune District</t>
-        </is>
-      </c>
-      <c r="B545" t="inlineStr">
         <is>
           <t>https://www.mypunepulse.com/over-%E2%82%B96-52-crore-medical-aid-distributed-to-5000-beneficiaries-in-pune-district/</t>
         </is>

--- a/Output/Devendra Fadnavis/extracted_links.xlsx
+++ b/Output/Devendra Fadnavis/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B510"/>
+  <dimension ref="A1:B476"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,12 +455,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Aurangzeb Tomb Row: VHP’s Statewide Protests Backed By RSS; CM Devendra Fadnavis Calls For Lawful Dismantling</t>
+          <t>Heavy rain lashes Marathwada; 5 missing in Nanded, says CM Devendra Fadnavis</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/aurangzeb-tomb-row-vhp-s-statewide-protests-backed-by-rss-cm-devendra-fadnavis-calls-for-lawful-dismantling/ar-AA1Bfmct?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://indianexpress.com/article/cities/mumbai/heavy-rain-lashes-marathwada-5-missing-in-nanded-says-cm-devendra-fadnavis-10196321/</t>
         </is>
       </c>
     </row>
@@ -479,12 +479,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Heavy rain lashes Marathwada; 5 missing in Nanded, says CM Devendra Fadnavis</t>
+          <t>Aurangzeb Tomb Row: VHP’s Statewide Protests Backed By RSS; CM Devendra Fadnavis Calls For Lawful Dismantling</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/heavy-rain-lashes-marathwada-5-missing-in-nanded-says-cm-devendra-fadnavis-10196321/</t>
+          <t>https://www.msn.com/en-in/news/India/aurangzeb-tomb-row-vhp-s-statewide-protests-backed-by-rss-cm-devendra-fadnavis-calls-for-lawful-dismantling/ar-AA1Bfmct?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
@@ -599,60 +599,60 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Fadnavis questions rising prices of real estate in Mumbai</t>
+          <t>NDA Vice President-Nominee CP Radhakrishnan Expresses Gratitude To PM Modi, Amit Shah &amp; Devendra Fadnavis After VP Nomination</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://www.constructionweekonline.in/business/fadnavis-home</t>
+          <t>https://www.msn.com/en-in/news/India/nda-vice-president-nominee-cp-radhakrishnan-expresses-gratitude-to-pm-modi-amit-shah-devendra-fadnavis-after-vp-nomination/ar-AA1KGvyO</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NDA Vice President-Nominee CP Radhakrishnan Expresses Gratitude To PM Modi, Amit Shah &amp; Devendra Fadnavis After VP Nomination</t>
+          <t>Aakar Patel| New Maharashtra Security Law Open To Abuse, Threatens Rights; Say ‘No’ To It</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/nda-vice-president-nominee-cp-radhakrishnan-expresses-gratitude-to-pm-modi-amit-shah-devendra-fadnavis-after-vp-nomination/ar-AA1KGvyO</t>
+          <t>https://www.deccanchronicle.com/opinion/columnists/aakar-patel-new-maharashtra-security-law-open-to-abuse-threatens-rights-say-no-to-it-1898276</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Aakar Patel| New Maharashtra Security Law Open To Abuse, Threatens Rights; Say ‘No’ To It</t>
+          <t>Goldman Sachs opens new, expanded office in Mumbai</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/opinion/columnists/aakar-patel-new-maharashtra-security-law-open-to-abuse-threatens-rights-say-no-to-it-1898276</t>
+          <t>https://www.thehindu.com/business/Industry/goldman-sachs-opens-new-expanded-office-in-mumbai/article69947256.ece</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Goldman Sachs opens new, expanded office in Mumbai</t>
+          <t>MNS Morcha: Raj Thackeray's party workers detained; CM Fadnavis says such experiments won’t work here</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/business/Industry/goldman-sachs-opens-new-expanded-office-in-mumbai/article69947256.ece</t>
+          <t>https://www.msn.com/en-in/news/India/mns-morcha-raj-thackerays-party-workers-detained-cm-fadnavis-says-such-experiments-won-t-work-here/ar-AA1Iaint</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MNS Morcha: Raj Thackeray's party workers detained; CM Fadnavis says such experiments won’t work here</t>
+          <t>Mumbai AQI: Dia Mirza expresses her concern with CM Devendra Fadnavis to act on city's air pollution</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/mns-morcha-raj-thackerays-party-workers-detained-cm-fadnavis-says-such-experiments-won-t-work-here/ar-AA1Iaint</t>
+          <t>https://www.msn.com/en-in/public-safety-and-emergencies/health-and-safety-alerts/mumbai-aqi-dia-mirza-expresses-her-concern-with-cm-devendra-fadnavis-to-act-on-city-s-air-pollution/ar-AA1xZ0xs?ocid=BingNewsVerp&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
@@ -671,5880 +671,5472 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Shinde and BJP: The saga continues</t>
+          <t>Fadnavis questions rising prices of real estate in Mumbai</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/shinde-and-bjp-the-saga-continues-101755457833159.html</t>
+          <t>https://www.constructionweekonline.in/business/fadnavis-home</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Mumbai received 177mm rain in just 6-8 hour period, says CM Fadnavis; more to come amid high tides</t>
+          <t>Shinde and BJP: The saga continues</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/red-alert-for-mumbai-mumbai-got-177mm-rain-in-just-6-8-hour-period-says-cm-fadnavis-more-to-come-amid-high-tides-23589990</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/shinde-and-bjp-the-saga-continues-101755457833159.html</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Maharashtra CM Fadnavis, Dy CM Shinde congratulate Governor CP Radhakrishnan on NDA's VP nomination</t>
+          <t>'Third Mumbai' to boost MMR development, says Fadnavis; invites pvt sector to join in its creation</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/national/general-news/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination20250818033912/</t>
+          <t>https://www.ptinews.com/story/business/-Third-Mumbai--to-boost-MMR-development--says-Fadnavis;-invites-pvt-sector-to-join-in-its-creation=/2834267</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
+          <t>Mumbai received 177mm rain in just 6-8 hour period, says CM Fadnavis; more to come amid high tides</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/business/-Third-Mumbai--to-boost-metropolitan-region-development--Fadnavis/2834902</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/red-alert-for-mumbai-mumbai-got-177mm-rain-in-just-6-8-hour-period-says-cm-fadnavis-more-to-come-amid-high-tides-23589990</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Third Mumbai in Raigad to become Maharashtra’s new economic powerhouse: CM Fadnavis</t>
+          <t>Maharashtra CM Fadnavis, Dy CM Shinde congratulate Governor CP Radhakrishnan on NDA's VP nomination</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://daijiworld.com/news/newsDisplay?newsID=1289652</t>
+          <t>https://aninews.in/news/national/general-news/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination20250818033912/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Mumbai gets 177mm rain in 6-8 hour period, says CM; all agencies asked to remain alert</t>
+          <t>Third Mumbai in Raigad to become Maharashtra’s new economic powerhouse: CM Fadnavis</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/mumbai-gets-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/articleshow/123365291.cms</t>
+          <t>https://daijiworld.com/news/newsDisplay?newsID=1289652</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Fadnavis govt’s big Maratha pride push: Legendary sword it ‘bought’ back from London, with a Rs 47L bid</t>
+          <t>Rain fury leaves 7 dead in Maharashtra, 200 villagers stranded</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://theprint.in/politics/fadnavis-govts-big-maratha-pride-push-legendary-sword-it-bought-back-from-london-with-a-rs-47l-bid/2723199/</t>
+          <t>https://www.ptinews.com/story/national/rain-fury-leaves-7-dead-in-maharashtra,-200-villagers-stranded/2834213</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rain fury leaves 7 dead in Maharashtra, 200 villagers stranded</t>
+          <t>Find suitable land &amp; I will set up IT park through MIDC in Solapur: Fadnavis</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/rain-fury-leaves-7-dead-in-maharashtra,-200-villagers-stranded/2834213</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/find-suitable-land-i-will-set-up-it-park-through-midc-in-solapur-fadnavis/articleshow/123351422.cms</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>"Observe precaution": Maharashtra CM warns about severe weather conditions in state</t>
+          <t>Fadnavis meets Guv Radhakrishnan, presents him book of Shivaji Maharaj's letters</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state20250819025510</t>
+          <t>https://www.ptinews.com/story/national/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharaj-s-letters/2832582</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Find suitable land &amp; I will set up IT park through MIDC in Solapur: Fadnavis</t>
+          <t>‘Third Mumbai’ takes shape as CM Fadnavis unveils mega MMR expansion plan</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/find-suitable-land-i-will-set-up-it-park-through-midc-in-solapur-fadnavis/articleshow/123351422.cms</t>
+          <t>https://www.moneycontrol.com/city/third-mumbai-takes-shape-as-cm-fadnavis-unveils-mega-mmr-expansion-plan-article-13465350.html</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Fadnavis meets Guv Radhakrishnan, presents him book of Shivaji Maharaj's letters</t>
+          <t>Raghuji Bhonsle’s sword brought to India</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharaj-s-letters/2832582</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/19/raghuji-bhonsles-sword-brought-to-india.html</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>‘Third Mumbai’ takes shape as CM Fadnavis unveils mega MMR expansion plan</t>
+          <t>Fadnavis Dedicates Goldman Sachs’ New Mumbai Office, Unveils Vision For ‘Third Mumbai’</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/city/third-mumbai-takes-shape-as-cm-fadnavis-unveils-mega-mmr-expansion-plan-article-13465350.html</t>
+          <t>https://www.businessworld.in/article/fadnavis-dedicates-goldman-sachs-new-mumbai-office-unveils-vision-for-third-mumbai-567845</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DH Evening Brief | NDA VP pick in Delhi to meet BJP top brass, Opposition yet to finalise their candidate; I.N.D.I.A. bloc continues attacking EC chief over SIR</t>
+          <t>Mumbai gets 177mm rain in 6-8 hour period, says CM; all agencies asked to remain alert</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/dh-evening-brief-nda-vp-pick-in-delhi-to-meet-bjp-top-brass-opposition-yet-to-finalise-their-candidate-india-bloc-continues-attacking-ec-chief-over-sir-3685866</t>
+          <t>https://m.economictimes.com/news/india/mumbai-gets-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/articleshow/123365291.cms</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Raghuji Bhonsle’s sword brought to India</t>
+          <t>Maharashtra on high alert as heavy rains batter state; CM, Dy CM lead rescue efforts</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/19/raghuji-bhonsles-sword-brought-to-india.html</t>
+          <t>https://daijiworld.com/news/newsDisplay?newsID=1289634</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Fadnavis Dedicates Goldman Sachs’ New Mumbai Office, Unveils Vision For ‘Third Mumbai’</t>
+          <t>Maharashtra rain: Mumbai flooded, 5 missing in Nanded, more showers in store</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://www.businessworld.in/article/fadnavis-dedicates-goldman-sachs-new-mumbai-office-unveils-vision-for-third-mumbai-567845</t>
+          <t>https://thefederal.com/category/states/west/maharashtra/mumbai-flooded-nanded-5-missing-maharashtra-rain-202350</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Schools shut, red alert as Mumbai braces for another day of heavy rain | Latest News India - Hindustan Times</t>
+          <t>Mumbai rain: 177 mm recorded in 6-8 hours, public advised to reach homes before 6.30 pm</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/mumbai-rains-schools-shut-as-mumbai-under-imd-red-alert-braces-for-another-day-of-heavy-rain-10-updates-101755564432674-amp.html</t>
+          <t>https://www.onmanorama.com/news/india/2025/08/18/mumbai-rains-flooding-high-tide-warning-live.html</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Maharashtra on high alert as heavy rains batter state; CM, Dy CM lead rescue efforts</t>
+          <t>Heavy rains lash Nanded Five missing scores stranded says CM Fadnavis Army unit deployed</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://www.daijiworld.com/news/newsDisplay?newsID=1289634</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom17-mh-rains-nanded.html</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Maratha general Raghuji Bhonsle's sword brought to Mumbai</t>
+          <t>Rain fury leaves 7 dead in Maharashtra 200 villagers stranded</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/maratha-general-raghuji-bhonsle-s-sword-brought-to-mumbai/2833930</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom50-mh-2nd-ldall-rains.html</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Maharashtra rain: Mumbai flooded, 5 missing in Nanded, more showers in store</t>
+          <t>NDA's Vice Presidential candidate CP Radhakrishnan to travel to Delhi today</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://thefederal.com/category/states/west/maharashtra/mumbai-flooded-nanded-5-missing-maharashtra-rain-202350</t>
+          <t>https://www.prameyanews.com/ndas-vice-presidential-candidate-cp-radhakrishnan-to-travel-to-delhi-today</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Heavy rains lash Nanded Five missing scores stranded says CM Fadnavis Army unit deployed</t>
+          <t>Pune can get underground road network to beat traffic woes</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom17-mh-rains-nanded.html</t>
+          <t>https://inshorts.com/en/news/pune-can-get-underground-road-network-to-beat-traffic-woes-1755566759073</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
+          <t>CM Devendra Fadnavis Meets Netherlands Yogasana Chief on Global Initiatives</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://www.millenniumpost.in/nation/third-mumbai-to-boost-metropolitan-region-development-fadnavis-623625</t>
+          <t>https://www.transcontinentaltimes.com/netherlands-yogasana-sports-nysa/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Observe precaution: Maharashtra CM warns about severe weather conditions in state</t>
+          <t>CM Devendra Fadnavis to Inaugurate India’s First ESG Lab at National STEM Challenge 2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state-23590120</t>
+          <t>https://indiacsr.in/cm-devendra-fadnavis-to-inaugurate-indias-first-esg-lab-at-national-stem-challenge-2025/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Rain fury leaves 7 dead in Maharashtra 200 villagers stranded</t>
+          <t>'Third Mumbai' Initiative Sparks New Wave of Economic Growth in Maharashtra</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom50-mh-2nd-ldall-rains.html</t>
+          <t>https://www.devdiscourse.com/article/science-environment/3545659-third-mumbai-initiative-sparks-new-wave-of-economic-growth-in-maharashtra</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Mumbai got 177mm rain in 6-8 hour period says CM more to come amid high tides</t>
+          <t>Mumbai: CM Devendra Fadnavis meets C.P. Radhakrishnan #Gallery</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom21-mh-rains-mumbai-cm.html</t>
+          <t>https://www.socialnews.xyz/2025/08/18/mumbai-cm-devendra-fadnavis-meets-c-p-radhakrishnan-gallery/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Pune can get underground road network to beat traffic woes</t>
+          <t>'Third Mumbai' Will Open A New Chapter Of Economic Development: Maha CM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://inshorts.com/en/news/pune-can-get-underground-road-network-to-beat-traffic-woes-1755566759073</t>
+          <t>https://menafn.com/1109941619/Third-Mumbai-Will-Open-A-New-Chapter-Of-Economic-Development-Maha-CM</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CM Devendra Fadnavis Meets Netherlands Yogasana Chief on Global Initiatives</t>
+          <t>Goldman Sachs Expands In Mumbai, Devendra Fadnavis Inaugurates New Worli Office</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://www.transcontinentaltimes.com/netherlands-yogasana-sports-nysa/</t>
+          <t>https://www.freepressjournal.in/business/goldman-sachs-expands-in-mumbai-devendra-fadnavis-inaugurates-new-worli-office</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CM Devendra Fadnavis to Inaugurate India’s First ESG Lab at National STEM Challenge 2025</t>
+          <t>Vice-President Elections 2025: Maharashtra CM Devendra Fadnavis Presents Shawl to CP Radhakrishnan on</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://indiacsr.in/cm-devendra-fadnavis-to-inaugurate-indias-first-esg-lab-at-national-stem-challenge-2025/</t>
+          <t>https://www.latestly.com/agency-news/vice-president-elections-2025-maharashtra-cm-devendra-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vp-nomination-see-pics-7063864.html</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>'Third Mumbai' Initiative Sparks New Wave of Economic Growth in Maharashtra</t>
+          <t>Mumbai Rains: Maharashtra CM Devendra Fadnavis Chairs Review Meeting On Excessive Rainfall At Mantralaya</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/science-environment/3545659-third-mumbai-initiative-sparks-new-wave-of-economic-growth-in-maharashtra</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-rains-cm-devendra-fadnavis-chairs-review-meeting-on-excessive-rainfall-at-mantralaya-video</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Mumbai: CM Devendra Fadnavis meets C.P. Radhakrishnan #Gallery</t>
+          <t>India News | ⚡Devendra Fadnavis Says ‘Third Mumbai’ Will Open a New Chapter of Economic Development</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/mumbai-cm-devendra-fadnavis-meets-c-p-radhakrishnan-gallery/</t>
+          <t>https://www.latestly.com/quickly/india/news/devendra-fadnavis-says-third-mumbai-will-open-a-new-chapter-of-economic-development-7064927.html</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>'Third Mumbai' Will Open A New Chapter Of Economic Development: Maha CM</t>
+          <t>Mumbai Records 177 mm Rain In 6 Hours, CM Devendra Fadnavis Urges Caution Amid High Tide Alert</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://menafn.com/1109941619/Third-Mumbai-Will-Open-A-New-Chapter-Of-Economic-Development-Maha-CM</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-records-177-mm-rain-in-6-hours-cm-devendra-fadnavis-urges-caution-amid-high-tide-alert</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Goldman Sachs Expands In Mumbai, Devendra Fadnavis Inaugurates New Worli Office</t>
+          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by...</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/business/goldman-sachs-expands-in-mumbai-devendra-fadnavis-inaugurates-new-worli-office</t>
+          <t>https://www.lokmattimes.com/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Vice-President Elections 2025: Maharashtra CM Devendra Fadnavis Presents Shawl to CP Radhakrishnan on</t>
+          <t>Future-ready India lies in STEM and AI, says Devendra Fadnavis, Maharashtra CM</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/vice-president-elections-2025-maharashtra-cm-devendra-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vp-nomination-see-pics-7063864.html</t>
+          <t>https://indiacsr.in/brillio-national-stem-challenge-empowers-2500-underserved-students-to-innovate-for-indias-future/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Mumbai Rains: Maharashtra CM Devendra Fadnavis Chairs Review Meeting On Excessive Rainfall At Mantralaya</t>
+          <t>‘Third Mumbai’ will open a new chapter of economic development: Maha CM</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-rains-cm-devendra-fadnavis-chairs-review-meeting-on-excessive-rainfall-at-mantralaya-video</t>
+          <t>https://www.lokmattimes.com/national/third-mumbai-will-open-a-new-chapter-of-economic-development-maha-cm/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>India News | ⚡Devendra Fadnavis Says ‘Third Mumbai’ Will Open a New Chapter of Economic Development</t>
+          <t>Mumbai: C.P. Radhakrishnan departs for Delhi #Gallery</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/quickly/india/news/devendra-fadnavis-says-third-mumbai-will-open-a-new-chapter-of-economic-development-7064927.html</t>
+          <t>https://www.socialnews.xyz/2025/08/18/mumbai-c-p-radhakrishnan-departs-for-delhi-gallery/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CREDAI-MCHI appoints Mr. Sukhraj Nahar as 18th President in the Change of Guard Ceremony graced by...</t>
+          <t>Maharashtra CM Fadnavis presents shawl to CP Radhakrishnan on NDA’s VP nomination</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis/</t>
+          <t>https://thenewsmill.com/2025/08/maharashtra-cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vp-nomination/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Mumbai Records 177 mm Rain In 6 Hours, CM Devendra Fadnavis Urges Caution Amid High Tide Alert</t>
+          <t>VIDEO: Historic Sword Of Raghuji Bhonsle Connects Youth With Maharashtra’s Glorious History, Says CM</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-records-177-mm-rain-in-6-hours-cm-devendra-fadnavis-urges-caution-amid-high-tide-alert</t>
+          <t>https://www.freepressjournal.in/mumbai/video-historic-sword-of-raghuji-bhonsle-connects-youth-with-maharashtras-glorious-history-says-cm-devendra-fadnavis</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Future-ready India lies in STEM and AI, says Devendra Fadnavis, Maharashtra CM</t>
+          <t>NDA's VP Candidate CP Radhakrishnan Heads to Delhi Amid Criticism</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://indiacsr.in/brillio-national-stem-challenge-empowers-2500-underserved-students-to-innovate-for-indias-future/</t>
+          <t>https://www.devdiscourse.com/article/headlines/3545060-ndas-vp-candidate-cp-radhakrishnan-heads-to-delhi-amid-criticism</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>‘Third Mumbai’ will open a new chapter of economic development: Maha CM</t>
+          <t>Heavy Rain Forecast for Mumbai: CM Fadnavis Reviews Flood Situation Across Maharashtra, with the Next 12...</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/third-mumbai-will-open-a-new-chapter-of-economic-development-maha-cm/</t>
+          <t>https://www.lokmattimes.com/mumbai/heavy-rain-forecast-for-mumbai-cm-fadnavis-reviews-flood-situation-across-maharashtra-with-the-next-12-hours-critical-a475/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Mumbai: C.P. Radhakrishnan departs for Delhi #Gallery</t>
+          <t>Maharashtra CM Fadnavis, Dy CM Shinde congratulate Governor CP Radhakrishnan on NDA's VP nomination</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/mumbai-c-p-radhakrishnan-departs-for-delhi-gallery/</t>
+          <t>https://thenewsmill.com/2025/08/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Maharashtra CM Fadnavis presents shawl to CP Radhakrishnan on NDA’s VP nomination</t>
+          <t>Those who speak of Maharashtra 'asmita' should support Radhakrishnan for VP post: Fadnavis</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/08/maharashtra-cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vp-nomination/</t>
+          <t>https://www.newsdrum.in/national/those-who-speak-of-maharashtra-asmita-should-support-radhakrishnan-for-vp-post-fadnavis-9672630</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>VIDEO: Historic Sword Of Raghuji Bhonsle Connects Youth With Maharashtra’s Glorious History, Says CM</t>
+          <t>'Observe precaution': Maharashtra CM warns about severe weather conditions in state</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/video-historic-sword-of-raghuji-bhonsle-connects-youth-with-maharashtras-glorious-history-says-cm-devendra-fadnavis</t>
+          <t>https://english.newsnationtv.com/national/general-news/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state20250819025510</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Heavy Rain Forecast for Mumbai: CM Fadnavis Reviews Flood Situation Across Maharashtra, with the Next 12...</t>
+          <t>Pune Patients Receive Over Rs 6.5 Crore in Medical Aid Under Chief Minister Devendra Fadnavis’ Initiative</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/mumbai/heavy-rain-forecast-for-mumbai-cm-fadnavis-reviews-flood-situation-across-maharashtra-with-the-next-12-hours-critical-a475/</t>
+          <t>https://www.punekarnews.in/pune-patients-receive-over-rs-6-5-crore-in-medical-aid-under-chief-minister-devendra-fadnavis-initiative/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Those who speak of Maharashtra 'asmita' should support Radhakrishnan for VP post: Fadnavis</t>
+          <t>Maharashtra Rains: 5 Missing in Nanded, Over 200 Stranded Across Several Districts; Army, NDRF Deployed</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/those-who-speak-of-maharashtra-asmita-should-support-radhakrishnan-for-vp-post-fadnavis-9672630</t>
+          <t>https://www.lokmattimes.com/maharashtra/maharashtra-rains-5-missing-in-nanded-over-200-stranded-across-several-districts-army-ndrf-deployed-a517/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>'Observe precaution': Maharashtra CM warns about severe weather conditions in state</t>
+          <t>Business News</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://english.newsnationtv.com/national/general-news/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state20250819025510</t>
+          <t>https://www.latestly.com/agency-news/business-news-credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis-7064653.html</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Pune Patients Receive Over Rs 6.5 Crore in Medical Aid Under Chief Minister Devendra Fadnavis’ Initiative</t>
+          <t>Amid heavy rains in Maharashtra, CM Fadnavis directs all agencies to be on alert</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-patients-receive-over-rs-6-5-crore-in-medical-aid-under-chief-minister-devendra-fadnavis-initiative/</t>
+          <t>https://www.thehawk.in/news/india/amid-heavy-rains-in-maharashtra-cm-fadnavis-directs-all-agencies-to-be-on-alert</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Heavy rains in Mumbai: IndiGo, SpiceJet, Akasa issue travel advisories</t>
+          <t>Mumbai To Welcome Historic Sword Of Shrimant Raje Raghuji Bhonsale On August 18; To Be Ceremoniously Unveiled</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://www.newsbytesapp.com/news/india/mumbai-flights-status-airlines-issue-key-advisory-for-passengers/story</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-to-welcome-historic-sword-of-shrimant-raje-raghuji-bhonsale-on-august-18-to-be-ceremoniously-unveiled-by-cm-fadnavis</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Maharashtra Rains: 5 Missing in Nanded, Over 200 Stranded Across Several Districts; Army, NDRF Deployed</t>
+          <t>Rain fury leaves 7 dead in Maharashtra, 200 villagers stranded</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/maharashtra/maharashtra-rains-5-missing-in-nanded-over-200-stranded-across-several-districts-army-ndrf-deployed-a517/</t>
+          <t>https://www.newsdrum.in/national/rain-fury-leaves-7-dead-in-maharashtra-200-villagers-stranded-9674070</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>7 killed as heavy rain batters Maharashtr­a; 800 villages hit</t>
+          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://www.pressreader.com/india/the-hindu-mangalore-9WWc/20250819/281947433944151</t>
+          <t>https://www.newsdrum.in/business/third-mumbai-to-boost-metropolitan-region-development-fadnavis-9674858</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Business News</t>
+          <t>Fadnavis Gifts Unpublished Shivaji Maharaj Letters to Maharashtra Governor at Mumbai Airport</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/business-news-credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis-7064653.html</t>
+          <t>https://panasiabiz.com/111091/cm-devendra-fadnavis-presents-rare-shivaji-maharaj-letters-to-governor-cp-radhakrishnan/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Amid heavy rains in Maharashtra, CM Fadnavis directs all agencies to be on alert</t>
+          <t>CM Fadnavis unveils emblem for Ganeshotsav to be celebrated as Rajya Mahotsav</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/india/amid-heavy-rains-in-maharashtra-cm-fadnavis-directs-all-agencies-to-be-on-alert</t>
+          <t>https://www.thehawk.in/news/india/cm-fadnavis-unveils-emblem-for-ganeshotsav-to-be-celebrated-as-rajya-mahotsav</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Mumbai To Welcome Historic Sword Of Shrimant Raje Raghuji Bhonsale On August 18; To Be Ceremoniously Unveiled</t>
+          <t>Heavy rains lash Nanded: Five missing, scores stranded, says CM Fadnavis; Army unit deployed</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-to-welcome-historic-sword-of-shrimant-raje-raghuji-bhonsale-on-august-18-to-be-ceremoniously-unveiled-by-cm-fadnavis</t>
+          <t>https://www.newsdrum.in/national/heavy-rains-lash-nanded-five-missing-scores-stranded-says-cm-fadnavis-army-unit-deployed-9672306</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Fadnavis meets Guv Radhakrishnan, presents him book of Shivaji Maharaj's letters</t>
+          <t>Maharashtra government approves major infra projects</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharajs-letters-9672415</t>
+          <t>https://www.thehawk.in/news/india/maharashtra-government-approves-major-infra-projects</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Rain fury leaves 7 dead in Maharashtra, 200 villagers stranded</t>
+          <t>उप-राष्ट्रपति चुनाव: देवेंद्र फडणवीस का 'मराठी अस्मिता' वाला दांव, क्या करेंगे</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/rain-fury-leaves-7-dead-in-maharashtra-200-villagers-stranded-9674070</t>
+          <t>https://www.abplive.com/states/maharashtra/vice-president-election-2025-maharashtra-cm-devendra-fadnavis-request-uddhav-thackeray-and-sharad-pawar-2997542</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>'Third Mumbai' to boost metropolitan region development: Fadnavis</t>
+          <t>लगता है वो लोग देवेंद्र फडणवीस और एकनाथ शिंदे के बारे में नहीं जानते, CJI बीआर गवई ने क्यों कहा ऐसा?</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/business/third-mumbai-to-boost-metropolitan-region-development-fadnavis-9674858</t>
+          <t>https://hindi.news18.com/news/nation/cji-br-gavai-take-devendra-fadnavis-eknath-shinde-name-bombay-high-court-new-circuit-bench-in-kolhapur-9520456.html</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>NDA’s Vice President nominee CP Radhakrishnan to reach Delhi today: sources</t>
+          <t>Mumbai Maharashtra Rains: महाराष्ट्र में भारी बारिश पर सीएम देवेंद्र फडणवीस का सख्त निर्देश, सभी विभाग अलर्ट पर</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/08/ndas-vice-president-nominee-cp-radhakrishnan-to-reach-delhi-today-sources/</t>
+          <t>https://thecsrjournal.in/mumbai-maharashtra-rains-cm-and-managment-on-alert-hindi/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Fadnavis Gifts Unpublished Shivaji Maharaj Letters to Maharashtra Governor at Mumbai Airport</t>
+          <t>दिल्ली पहुंचे देवेंद्र फडणवीस, अमित शाह से मिले, जानें क्यों थी यह मुलाकात खास</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://panasiabiz.com/111091/cm-devendra-fadnavis-presents-rare-shivaji-maharaj-letters-to-governor-cp-radhakrishnan/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B6-%E0%A4%B9-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A5%87-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%82-%E0%A4%A5-%E0%A4%AF%E0%A4%B9-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4-%E0%A4%96-%E0%A4%B8/ar-AA1Jjy9z</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CM Fadnavis unveils emblem for Ganeshotsav to be celebrated as Rajya Mahotsav</t>
+          <t>मुख्यमंत्री देवेंद्र फडणवीस ने दी राज्यपाल राधाकृष्णन को उपराष्ट्रपति पद की उम्मीदवारता पर बधाई</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/india/cm-fadnavis-unveils-emblem-for-ganeshotsav-to-be-celebrated-as-rajya-mahotsav</t>
+          <t>https://hindi.mid-day.com/news/india-news/article/chief-minister-devendra-fadnavis-congratulated-governor-radhakrishnan-on-his-candidature-for-the-post-of-vice-president-11180</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Heavy rains lash Nanded: Five missing, scores stranded, says CM Fadnavis; Army unit deployed</t>
+          <t>Mumbai Rains News: भारी बारिश के चलते कल मुंबई के स्कूल-कॉलेजों में छुट्टी, नांदेड़ में 7 लोगों की मौत, CM फडणवीस ने की आपात बैठक</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/heavy-rains-lash-nanded-five-missing-scores-stranded-says-cm-fadnavis-army-unit-deployed-9672306</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/heavy-rains-in-mumbai-schools-colleges-closed-7-deaths-in-maharashtra-5-missing-nanded-cm-fadnavis-emergency-meeting/articleshow/123366462.cms</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Maharashtra government approves major infra projects</t>
+          <t>मुख्यमंत्री देवेंद्र फडणवीस ने राज्य में भारी बारिश के मद्देनजर सभी एजेंसियों को सतर्क रहने के निर्देश दिए</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/india/maharashtra-government-approves-major-infra-projects</t>
+          <t>https://www.mumbailive.com/hi/civic/chief-minister-devendra-fadnavis-directed-all-agencies-to-remain-alert-in-view-of-heavy-rains-in-the-state-89633</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>उप-राष्ट्रपति चुनाव: देवेंद्र फडणवीस का 'मराठी अस्मिता' वाला दांव, क्या करेंगे</t>
+          <t>Mumbai Rain News : मुंबई में बारिश ने मचाया कोहराम, देवेंद्र फडणवीस का आया बयान</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/vice-president-election-2025-maharashtra-cm-devendra-fadnavis-request-uddhav-thackeray-and-sharad-pawar-2997542</t>
+          <t>https://hindi.oneindia.com/videos/mumbai-rain-news-rain-wreaked-havoc-in-mumbai-devendra-fadnavis-statement-came-4259449.html</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>लगता है वो लोग फडणवीस और शिंदे के बारे में नहीं जानते, CJI ने क्यों कहा ऐसा?</t>
+          <t>मुंबई में भारी भारिश ने मचाई तबाही, CM देवेंद्र फडणवीस ने बुलाई बैठक</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/nation/cji-br-gavai-take-devendra-fadnavis-eknath-shinde-name-bombay-high-court-new-circuit-bench-in-kolhapur-9520456.html</t>
+          <t>https://www.patrika.com/videos/mumbai-news/heavy-rain-wreaks-havoc-in-mumbai-cm-devendra-fadnavis-calls-a-meeting-19874343</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Mumbai Maharashtra Rains: महाराष्ट्र में भारी बारिश पर सीएम देवेंद्र फडणवीस का सख्त निर्देश, सभी विभाग अलर्ट पर</t>
+          <t>फडणवीस ने कहा, ‘तीसरी मुंबई’ से एमएमआर का होगा विकास</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/mumbai-maharashtra-rains-cm-and-managment-on-alert-hindi/</t>
+          <t>https://hindi.theprint.in/india/economy/fadnavis-said-third-mumbai-will-lead-to-development-of-mmr/856867/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>दिल्ली पहुंचे देवेंद्र फडणवीस, अमित शाह से मिले, जानें क्यों थी यह मुलाकात खास</t>
+          <t>Raghuji Bhosale: आज मुंबई आएगी रघुजी भोसले की की ऐतिहासिक तलवार, सीएम फडणवीस करेंगे स्वागत</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B6-%E0%A4%B9-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A5%87-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%82-%E0%A4%A5-%E0%A4%AF%E0%A4%B9-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4-%E0%A4%96-%E0%A4%B8/ar-AA1Jjy9z</t>
+          <t>https://zeenews.india.com/hindi/india/raghuji-bhosale-historic-sword-will-arrive-in-mumbai-today-cm-fadnavis-will-welcome-it/2886138</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>मुख्यमंत्री देवेंद्र फडणवीस ने दी राज्यपाल राधाकृष्णन को उपराष्ट्रपति पद की उम्मीदवारता पर बधाई</t>
+          <t>महाराष्ट्र के नांदेड़ में फटा बादल, 15-16 जिलो में अलर्ट, CM फडणवीस बोले- फसलों को नुकसान</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/news/india-news/article/chief-minister-devendra-fadnavis-congratulated-governor-radhakrishnan-on-his-candidature-for-the-post-of-vice-president-11180</t>
+          <t>https://www.abplive.com/states/maharashtra/weather-mumbai-rains-local-train-cloudburst-nanded-alert-in-15-16-districts-in-maharashtra-cm-devendra-fadnavis-said-damage-to-crops-2997472</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Mumbai Rains News: भारी बारिश के चलते कल मुंबई के स्कूल-कॉलेजों में छुट्टी, नांदेड़ में 7 लोगों की मौत, CM फडणवीस ने की आपात बैठक</t>
+          <t>'औरंगजेब भारत के किसी भी समाज का हीरो नहीं...', मजार को लेकर फडणवीस ने कही बड़ी बात</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/heavy-rains-in-mumbai-schools-colleges-closed-7-deaths-in-maharashtra-5-missing-nanded-cm-fadnavis-emergency-meeting/articleshow/123366462.cms</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%AD-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AE%E0%A4%9C-%E0%A4%B0-%E0%A4%95-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC-%E0%A4%A4/ar-AA1IRFiN</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>मुख्यमंत्री देवेंद्र फडणवीस ने राज्य में भारी बारिश के मद्देनजर सभी एजेंसियों को सतर्क रहने के निर्देश दिए</t>
+          <t>मुंबई में सिर्फ 6-8 घंटे में 177 मिमी हुई बारिश, फडणवीस ने दिए सावधानी बरतने के निर्देश</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://www.mumbailive.com/hi/civic/chief-minister-devendra-fadnavis-directed-all-agencies-to-remain-alert-in-view-of-heavy-rains-in-the-state-89633</t>
+          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/mumbai-received-177-mm-of-rain-in-just-6-8-hours-fadnavis-gave-instructions-to-take-precautions-11195</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Mumbai Rain News : मुंबई में बारिश ने मचाया कोहराम, देवेंद्र फडणवीस का आया बयान</t>
+          <t>CP Radhakrishnan को लेकर CM फडणवीस ने बड़ा खुलासा कर चल दिया दांव, अब क्‍या करेंगे उद्धव ठाकरे और शरद पवार?</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/videos/mumbai-rain-news-rain-wreaked-havoc-in-mumbai-devendra-fadnavis-statement-came-4259449.html</t>
+          <t>https://hindi.oneindia.com/news/maharashtra/vice-presidential-election-cm-devendra-fadnavis-said-cp-radhakrishnan-is-a-mumbai-voter-support-him-1365243.html</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>मुंबई में भारी भारिश ने मचाई तबाही, CM देवेंद्र फडणवीस ने बुलाई बैठक</t>
+          <t>मुंबई में 6-8 घंटे में 177 मिलीमीटर बारिश हुई: फडणवीस</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/videos/mumbai-news/heavy-rain-wreaks-havoc-in-mumbai-cm-devendra-fadnavis-calls-a-meeting-19874343</t>
+          <t>https://hindi.theprint.in/india/mumbai-received-177-mm-of-rain-in-6-8-hours-fadnavis/856688/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>फडणवीस ने कहा, ‘तीसरी मुंबई’ से एमएमआर का होगा विकास</t>
+          <t>सिरदर्द है कृषि मंत्रालय...अजित पवार के मंत्री दत्तात्रेय भरणे को नहीं पसंद आई नई जिम्मेदारी, जानें क्या कहा?</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/economy/fadnavis-said-third-mumbai-will-lead-to-development-of-mmr/856867/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-manik-rao-kokate-successor-minister-dattatray-bharane-called-agriculture-ministry-is-a-headache-know-all/articleshow/123357471.cms</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Raghuji Bhosale: आज मुंबई आएगी रघुजी भोसले की की ऐतिहासिक तलवार, सीएम फडणवीस करेंगे स्वागत</t>
+          <t>Mumbai Rain: 24 घंटे की बारिश से मुंबई की सांस फूली, CM देवेंद्र फडणवीस ने पड़ोसी राज्यों से किया संपर्क</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/india/raghuji-bhosale-historic-sword-will-arrive-in-mumbai-today-cm-fadnavis-will-welcome-it/2886138</t>
+          <t>https://zeenews.india.com/hindi/india/mumbai-rains-today-imd-red-alert-warning-waterlogging-traffic-update/2886161</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>महाराष्ट्र के नांदेड़ में फटा बादल, 15-16 जिलो में अलर्ट, CM फडणवीस बोले- फसलों को नुकसान</t>
+          <t>नांदेड़ में भारी बारिश के कारण पांच लोग लापता, कई व्यक्ति फंसे : मुख्यमंत्री फडणवीस</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/weather-mumbai-rains-local-train-cloudburst-nanded-alert-in-15-16-districts-in-maharashtra-cm-devendra-fadnavis-said-damage-to-crops-2997472</t>
+          <t>https://hindi.theprint.in/india/five-people-missing-many-people-stranded-due-to-heavy-rains-in-nanded-chief-minister-fadnavis/856679/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>'औरंगजेब भारत के किसी भी समाज का हीरो नहीं...', मजार को लेकर फडणवीस ने कही बड़ी बात</t>
+          <t>महाराष्ट्र में भारी बारिश का कहर, 16 जिलों में रेड अलर्ट, बचाव दल तैनात</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%AD-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AE%E0%A4%9C-%E0%A4%B0-%E0%A4%95-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC-%E0%A4%A4/ar-AA1IRFiN</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-heavy-rainfall-flood-alert-red-and-orange-alerts-issued-relief-operations-mumbai-rain-ann-2997660</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>मुंबई में सिर्फ 6-8 घंटे में 177 मिमी हुई बारिश, फडणवीस ने दिए सावधानी बरतने के निर्देश</t>
+          <t>आज सपना पूरा हो गया... चीफ जस्टिस गवई ने ऐसा क्यों कहा, सीएम फडणवीस का लिया नाम</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/mumbai-received-177-mm-of-rain-in-just-6-8-hours-fadnavis-gave-instructions-to-take-precautions-11195</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/cji-br-gavai-said-our-dream-has-been-fulfilled-over-bombay-high-court-new-circuit-bench-at-kolhapur-mention-cm-fadnavis-name-know-all/articleshow/123350750.cms</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CP Radhakrishnan को लेकर CM फडणवीस ने बड़ा खुलासा कर चल दिया दांव, अब क्‍या करेंगे उद्धव ठाकरे और शरद पवार?</t>
+          <t>महाराष्ट्र में भारी बारिश से सात लोगों की मौत, 200 ग्रामीण फंसे</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/maharashtra/vice-presidential-election-cm-devendra-fadnavis-said-cp-radhakrishnan-is-a-mumbai-voter-support-him-1365243.html</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AD-%E0%A4%B0-%E0%A4%AC-%E0%A4%B0-%E0%A4%B6-%E0%A4%B8%E0%A5%87-%E0%A4%B8-%E0%A4%A4-%E0%A4%B2-%E0%A4%97-%E0%A4%82-%E0%A4%95-%E0%A4%AE-%E0%A4%A4-200-%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%A3-%E0%A4%AB%E0%A4%82%E0%A4%B8%E0%A5%87/ar-AA1KKl3K</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>मुंबई में 6-8 घंटे में 177 मिलीमीटर बारिश हुई: फडणवीस</t>
+          <t>वो ऐतिहासिक तलवार जिसके लिए बिछाया जा रहा मुंबई में रेड कारपेट… मराठा साम्राज्य से है कनेक्शन</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/mumbai-received-177-mm-of-rain-in-6-8-hours-fadnavis/856688/</t>
+          <t>https://www.tv9hindi.com/india/raje-raghuji-bhosale-sword-history-maharashtra-cm-fadnavis-grand-welcome-3441860.html</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>सिरदर्द है कृषि मंत्रालय...अजित पवार के मंत्री दत्तात्रेय भरणे को नहीं पसंद आई नई जिम्मेदारी, जानें क्या कहा?</t>
+          <t>महाराष्ट्र में बन रही है तीसरी मुंबई, इस जिले का होगा आर्थिक विकास, जानें पूरी जानकारी | News Track in...</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-manik-rao-kokate-successor-minister-dattatray-bharane-called-agriculture-ministry-is-a-headache-know-all/articleshow/123357471.cms</t>
+          <t>https://newstrack.com/india/third-mumbai-being-built-maharashtra-district-have-economic-development-know-full-details-534715</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>फडणवीस की पत्नी के खिलाफ अपमानजनक पोस्ट : दो लोगों की अग्रिम जमानत अर्जी खारिज</t>
+          <t>CM फडणवीस ने खेला 'मराठी अस्मिता' का दांव, उपराष्ट्रपति चुनाव में उद्धव-पवार पर बना दबाव</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%96-%E0%A4%B2-%E0%A4%AB-%E0%A4%85%E0%A4%AA%E0%A4%AE-%E0%A4%A8%E0%A4%9C%E0%A4%A8%E0%A4%95-%E0%A4%AA-%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%A6-%E0%A4%B2-%E0%A4%97-%E0%A4%82-%E0%A4%95-%E0%A4%85%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%9C%E0%A4%AE-%E0%A4%A8%E0%A4%A4-%E0%A4%85%E0%A4%B0%E0%A5%8D%E0%A4%9C-%E0%A4%96-%E0%A4%B0-%E0%A4%9C/ar-AA1Je80j?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://navbharatlive.com/maharashtra/political-battle-over-nda-candidate-radhakrishnan-cm-fadnavis-seeks-support-from-uddhav-thackeray-and-sharad-pawar-1321873.html</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>नांदेड़ में भारी बारिश के कारण पांच लोग लापता, कई व्यक्ति फंसे : मुख्यमंत्री फडणवीस</t>
+          <t>महाराष्ट्र किसानों को मिलेगी बड़ी राहत, CM फडणवीस जल्द करेंगे कर्जमाफी की घोषणा</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/five-people-missing-many-people-stranded-due-to-heavy-rains-in-nanded-chief-minister-fadnavis/856679/</t>
+          <t>https://navbharatlive.com/maharashtra/guardian-minister-sanjay-rathore-claims-cm-fadnavis-may-announce-a-loan-waiver-for-farmers-1322081.html</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Mumbai Rain: 24 घंटे की बारिश से मुंबई की सांस फूली, CM देवेंद्र फडणवीस ने पड़ोसी राज्यों से किया संपर्क</t>
+          <t>बाढ़ संकट पर अबू आजमी का CM फडणवीस को पत्र, प्रभावितों तक तुरंत राहत पहुंचाने की मांग</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/india/mumbai-rains-today-imd-red-alert-warning-waterlogging-traffic-update/2886161</t>
+          <t>https://navbharatlive.com/latest-news/abu-azmi-wrote-a-letter-to-cm-devendra-fadnavis-asking-him-to-send-relief-supplies-to-flood-affected-region-1322005.html</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में भारी बारिश का कहर, 16 जिलों में रेड अलर्ट, बचाव दल तैनात</t>
+          <t>नांदेड़ में मूसलधार बारिश से हाहाकार, CM फडणवीस की निगरानी में राहत कार्य तेज</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-heavy-rainfall-flood-alert-red-and-orange-alerts-issued-relief-operations-mumbai-rain-ann-2997660</t>
+          <t>https://navbharatlive.com/maharashtra/heavy-rains-cause-havoc-in-nanded-rescue-operation-intensified-under-the-supervision-of-cm-fadnavis-1321752.html</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>आज सपना पूरा हो गया... चीफ जस्टिस गवई ने ऐसा क्यों कहा, सीएम फडणवीस का लिया नाम</t>
+          <t>CM फडणवीस लगा रहे जोर, अधिकारी कर रहे मनामानी, FIA ने जतायी नाराजगी</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/cji-br-gavai-said-our-dream-has-been-fulfilled-over-bombay-high-court-new-circuit-bench-at-kolhapur-mention-cm-fadnavis-name-know-all/articleshow/123350750.cms</t>
+          <t>https://navbharatlive.com/maharashtra/federation-of-industries-association-is-angry-due-to-ignorance-of-msme-sector-in-vidarbha-1322498.html</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>वो ऐतिहासिक तलवार जिसके लिए बिछाया जा रहा मुंबई में रेड कारपेट… मराठा साम्राज्य से है कनेक्शन</t>
+          <t>अबू आजमी ने सीएम देवेंद्र फडणवीस को लिखा पत्र, बाढ़ प्रभावित इलाकों में राहत सामग्री पहुंचाने की मांग की</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/india/raje-raghuji-bhosale-sword-history-maharashtra-cm-fadnavis-grand-welcome-3441860.html</t>
+          <t>https://www.newsnationtv.com/abu-azmi-ne-cm-devendra-fadnavis-ko-likha-patra-badh-prabhavit-ilakon-mein-rahat-pahunchane-ki-mang-ki--20250818191027/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में बन रही है तीसरी मुंबई, इस जिले का होगा आर्थिक विकास, जानें पूरी जानकारी | News Track in...</t>
+          <t>Maharashtra Live News 18 Aug: एक क्लिक में पढ़े महाराष्ट्र की दिन भर की बड़ी खब़रें...</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>https://newstrack.com/india/third-mumbai-being-built-maharashtra-district-have-economic-development-know-full-details-534715</t>
+          <t>https://navbharatlive.com/maharashtra/latest-live-updates-maharashtra-politics-crime-nagpur-news-mumbai-pune-18-august-1321138.html</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>CM फडणवीस ने खेला 'मराठी अस्मिता' का दांव, उपराष्ट्रपति चुनाव में उद्धव-पवार पर बना दबाव</t>
+          <t>Mumbai News: महाराष्ट्र में मूसलाधार बारिश से हाहाकार, मुख्यमंत्री की हाईलेवल बैठक, विशेष सत्र बुलाने की मांग | Heavy rains cause havoc in Maharashtra, high level meeting of Chief Minister, demand for calling special s</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/political-battle-over-nda-candidate-radhakrishnan-cm-fadnavis-seeks-support-from-uddhav-thackeray-and-sharad-pawar-1321873.html</t>
+          <t>https://www.bhaskarhindi.com/city/mumbai/mumbai-news-heavy-rains-cause-havoc-in-maharashtra-high-level-meeting-of-chief-minister-demand-for-calling-special-session-1174171</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>महाराष्ट्र किसानों को मिलेगी बड़ी राहत, CM फडणवीस जल्द करेंगे कर्जमाफी की घोषणा</t>
+          <t>राष्ट्रीय: मुंबई में भारी बारिश के बीच सुचारू रूप से चल रही मेट्रो, सीएम फडणवीस ने की तारीफ</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/guardian-minister-sanjay-rathore-claims-cm-fadnavis-may-announce-a-loan-waiver-for-farmers-1322081.html</t>
+          <t>https://www.bhaskarhindi.com/other/news-1174019</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>बाढ़ संकट पर अबू आजमी का CM फडणवीस को पत्र, प्रभावितों तक तुरंत राहत पहुंचाने की मांग</t>
+          <t>महाराष्ट्र : भारी बारिश के बाद नांदेड़ में राहत कार्य तेज, प्रशासन के संपर्क में सीएम फडणवीस</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/latest-news/abu-azmi-wrote-a-letter-to-cm-devendra-fadnavis-asking-him-to-send-relief-supplies-to-flood-affected-region-1322005.html</t>
+          <t>https://www.newsnationtv.com/maharashtra-bhari-barish-ke-baad-nanded-mein-rahat-bachav-karya-tez-jiladhikariyon-ke-sampark-mein-cm-fadnavis--20250818144516/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>नांदेड़ में मूसलधार बारिश से हाहाकार, CM फडणवीस की निगरानी में राहत कार्य तेज</t>
+          <t>CM फडणवीस ने एनडीए के उपराष्ट्रपति पद के नामांकन पर सीपी राधाकृष्णन को शॉल भेंट की</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/heavy-rains-cause-havoc-in-nanded-rescue-operation-intensified-under-the-supervision-of-cm-fadnavis-1321752.html</t>
+          <t>https://jantaserishta.com/local/maharashtra/cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vice-president-nomination-4218433</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CM फडणवीस लगा रहे जोर, अधिकारी कर रहे मनामानी, FIA ने जतायी नाराजगी</t>
+          <t>(लीड)महाराष्ट्र में मूसलाधार बारिश से हाहाकार, सात लोगों की मौत</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/federation-of-industries-association-is-angry-due-to-ignorance-of-msme-sector-in-vidarbha-1322498.html</t>
+          <t>https://livevns.news/National/panic-in-maharashtra-due-to-heavy-rainphp/cid17258961.htm</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>अबू आजमी ने सीएम देवेंद्र फडणवीस को लिखा पत्र, बाढ़ प्रभावित इलाकों में राहत सामग्री पहुंचाने की मांग की</t>
+          <t>Mumbai: राज्यपाल की उपराष्ट्रपति पद की उम्मीदवारी पर मुख्यमंत्री ने जताया हर्ष</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>https://www.newsnationtv.com/abu-azmi-ne-cm-devendra-fadnavis-ko-likha-patra-badh-prabhavit-ilakon-mein-rahat-pahunchane-ki-mang-ki--20250818191027/</t>
+          <t>https://jantaserishta.com/local/maharashtra/mumbai-chief-minister-expressed-happiness-over-the-candidature-of-the-governor-for-the-post-of-vice-president-mumbai--4218462</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Maharashtra Live News 18 Aug: एक क्लिक में पढ़े महाराष्ट्र की दिन भर की बड़ी खब़रें...</t>
+          <t>अटल सेतु के पास रायगढ़ में बसेगी तीसरी मुंबई, जानें महाराष्ट्र सरकार का पूरा मास्टर प्लान क्या</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/latest-live-updates-maharashtra-politics-crime-nagpur-news-mumbai-pune-18-august-1321138.html</t>
+          <t>https://samacharnama.com/states/maharashtra-news/maharashtra-governments-master-plan-to-set-up-third-mumbai/cid17261301.htm</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Mumbai News: महाराष्ट्र में मूसलाधार बारिश से हाहाकार, मुख्यमंत्री की हाईलेवल बैठक, विशेष सत्र बुलाने की मांग | Heavy rains cause havoc in Maharashtra, high level meeting of Chief Minister, demand for calling special s</t>
+          <t>लंदन से आई मराठा साम्राज्य की शान! रघुजी ?...</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/city/mumbai/mumbai-news-heavy-rains-cause-havoc-in-maharashtra-high-level-meeting-of-chief-minister-demand-for-calling-special-session-1174171</t>
+          <t>https://bharatexpress.com/india/raghuji-bhosale-historic-sword-returned-from-london-grand-welcome-in-mumbai-553050</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>राष्ट्रीय: मुंबई में भारी बारिश के बीच सुचारू रूप से चल रही मेट्रो, सीएम फडणवीस ने की तारीफ</t>
+          <t>Aakar Patel| New Maharashtra Security Law Open To Abuse, Threatens Rights; Say ‘No’ To It</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/news-1174019</t>
+          <t>https://www.asianage.com/opinion/columnists/aakar-patel-new-maharashtra-security-law-open-to-abuse-threatens-rights-say-no-to-it-1898277</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>महाराष्ट्र : भारी बारिश के बाद नांदेड़ में राहत कार्य तेज, प्रशासन के संपर्क में सीएम फडणवीस</t>
+          <t>Maharashtra CM Fadnavis, Dy CM Shinde congratulate Governor CP Radhakrishnan on NDA's VP nomination</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>https://www.newsnationtv.com/maharashtra-bhari-barish-ke-baad-nanded-mein-rahat-bachav-karya-tez-jiladhikariyon-ke-sampark-mein-cm-fadnavis--20250818144516/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination-23589945</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>CM फडणवीस ने एनडीए के उपराष्ट्रपति पद के नामांकन पर सीपी राधाकृष्णन को शॉल भेंट की</t>
+          <t>Heavy rainfall causes 7 deaths, crop loss in Maharashtra as alerts continue</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vice-president-nomination-4218433</t>
+          <t>https://www.msn.com/en-in/news/India/heavy-rainfall-causes-7-deaths-crop-loss-in-maharashtra-as-alerts-continue/ar-AA1KK6Zt</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>राज्य को बाढ़ आपदा घोषित करो… विशेष अधिवेशन बुलाओ… एनसीपी प्रदेश अध्यक्ष ने की सीएम से मांग</t>
+          <t>Maharashtra CM Devendra Fadnavis Says ‘Third Mumbai’ Being Developed in Raigad District Will Open New</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/declare-the-state-a-flood-disaster-call-a-special-session-ncp-state-president-made-a-demand-to-the-cm/</t>
+          <t>https://www.latestly.com/india/news/maharashtra-cm-devendra-fadnavis-says-third-mumbai-being-developed-in-raigad-district-will-open-new-chapter-of-economic-development-7064927.html</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>(लीड)महाराष्ट्र में मूसलाधार बारिश से हाहाकार, सात लोगों की मौत</t>
+          <t>Mumbai got 177mm rain in 6-8 hour period, says CM; more to come amid high tides</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>https://livevns.news/National/panic-in-maharashtra-due-to-heavy-rainphp/cid17258961.htm</t>
+          <t>https://www.newsdrum.in/national/mumbai-got-177mm-rain-in-6-8-hour-period-says-cm-more-to-come-amid-high-tides-9672488</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Mumbai: राज्यपाल की उपराष्ट्रपति पद की उम्मीदवारी पर मुख्यमंत्री ने जताया हर्ष</t>
+          <t>Mumbai Rains LIVE Updates: 250–300 mm Downpour Likely Tonight; Schools &amp; Colleges To Remain Shut On Tuesday</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/mumbai-chief-minister-expressed-happiness-over-the-candidature-of-the-governor-for-the-post-of-vice-president-mumbai--4218462</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-live-updates-check-for-latest-updates-of-all-the-happeneings-in-mumbai</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>अटल सेतु के पास रायगढ़ में बसेगी तीसरी मुंबई, जानें महाराष्ट्र सरकार का पूरा मास्टर प्लान क्या</t>
+          <t>"Deliver justice in spirit of Shahu Maharaj's vision": CJI Gavai inaugurates Bombay High Court circuit bench at Kolhapur</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>https://samacharnama.com/states/maharashtra-news/maharashtra-governments-master-plan-to-set-up-third-mumbai/cid17261301.htm</t>
+          <t>https://thenewsmill.com/2025/08/deliver-justice-in-spirit-of-shahu-maharajs-vision-cji-gavai-inaugurates-bombay-high-court-circuit-bench-at-kolhapur/</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>लंदन से आई मराठा साम्राज्य की शान! रघुजी ?...</t>
+          <t>पुढील १२ तास मुंबईसाठी अत्यंत महत्त्वाचे, मुख्यमंत्री फडणवीस पावसाबाबत काय म्हणाले?</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>https://bharatexpress.com/india/raghuji-bhosale-historic-sword-returned-from-london-grand-welcome-in-mumbai-553050</t>
+          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-review-mumbai-rain-says-next-12-hours-important-for-mumbai-and-mmr-region-1460967.html</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Aakar Patel| New Maharashtra Security Law Open To Abuse, Threatens Rights; Say ‘No’ To It</t>
+          <t>राज्यात अतिवृष्टीमुळे मुख्यमंत्री देवेंद्र फडणवीस यांचे सर्व यंत्रणांना सतर्कतेचे निर्देश; नांदेड जिल्ह्यात लष्कराची मदत</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>https://www.asianage.com/opinion/columnists/aakar-patel-new-maharashtra-security-law-open-to-abuse-threatens-rights-say-no-to-it-1898277</t>
+          <t>https://www.loksatta.com/mumbai/chief-minister-devendra-fadnavis-has-directed-all-agencies-to-be-on-alert-due-to-heavy-rains-in-the-maharashtra-mumbai-print-news-amy-95-5313479/</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Maharashtra CM Fadnavis, Dy CM Shinde congratulate Governor CP Radhakrishnan on NDA's VP nomination</t>
+          <t>Mumbai Rain : मुंबईत संध्याकाळी समुद्राला भरती, पुढील 12 तास महत्त्वाचे, पावसाच्या थैमानानंतर</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination-23589945</t>
+          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-on-mumbai-maharashtra-rain-today-visit-disaster-management-department-bmc-marathi-news-1377962</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Heavy rainfall causes 7 deaths, crop loss in Maharashtra as alerts continue</t>
+          <t>राज्यभरात पावसाचा हाहाकार, मुख्यमंत्री देवेंद्र फडणवीस यांनी घेतला आढावा; सर्व यंत्रणांना सतर्कतेचे निर्देश</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/heavy-rainfall-causes-7-deaths-crop-loss-in-maharashtra-as-alerts-continue/ar-AA1KK6Zt</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/rains-lashed-the-state-chief-minister-devendra-fadnavis-took-stock-instructed-all-agencies-to-be-alert.html</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Maharashtra CM Devendra Fadnavis Says ‘Third Mumbai’ Being Developed in Raigad District Will Open New</t>
+          <t>Mumbai Rain Update : समुद्रातून येतंय मुंबईवर मोठं संकट, पुढच्या 12 तासांत तुफान पाऊस, फडणवीस काय...</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/india/news/maharashtra-cm-devendra-fadnavis-says-third-mumbai-being-developed-in-raigad-district-will-open-new-chapter-of-economic-development-7064927.html</t>
+          <t>https://www.tv9marathi.com/maharashtra/mumbai-rain-alert-cm-devendra-fadnavis-said-mumbai-have-red-alert-school-holiday-declared-know-detail-information-in-marathi-1472488.html</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Maharashtra CM Fadnavis, Dy CM Shinde congratulate Governor CP Radhakrishnan on NDA's VP nomination</t>
+          <t>राज्यात अतिवृष्टीच्या पार्श्वभूमीवर प्रशासन अलर्ट मोडवर! मुख्यमंत्री देवेंद्र फडणवीस यांचे सतर्कतेचे निर्देश</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/08/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination/</t>
+          <t>https://www.navarashtra.com/maharashtra/cm-devendra-fadnavis-took-review-of-rain-situation-at-state-disaster-management-centre-in-the-ministry-963383.html</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>"Observe precaution": Maharashtra CM warns about severe weather conditions in state</t>
+          <t>Farmers Loan Waiver: बावनकुळेंनंतर महायुती सरकारमधील 'या' मंत्र्याची कर्जमाफीबाबत मोठी अपडेट; म्हणाले,'CM फडणवीस लवकरच...'</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/08/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state/</t>
+          <t>https://sarkarnama.esakal.com/amp/story/maharashtra/vidarbha/sanjay-rathod-update-farmer-loan-waiver-devendra-fadnavis-dk88</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Mumbai got 177mm rain in 6-8 hour period, says CM; more to come amid high tides</t>
+          <t>Devendra Fadnavis : महाराष्ट्रातील माणसाला सर्वांनी समर्थन द्यावं; फडणवीस यांचे मविआला आवाहन</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/mumbai-got-177mm-rain-in-6-8-hour-period-says-cm-more-to-come-amid-high-tides-9672488</t>
+          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-appeals-to-maharashtra-mps-to-support-cp-radhakrishnan-for-vice-president/913103/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>NCP (SP) targets Maha minister over Rs 5,000 cr scam in Navi Mumbai’s CIDCO land; demands his resignation</t>
+          <t>सरदार रघुजी भोसले यांची ऐतिहासिक तलवार मुंबईत दाखल; मुख्यमंत्र्यांच्या हस्ते होणार लोकार्पण</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/ncp-sp-targets-maha-minister-over-rs-5000-cr-scam-in-navi-mumbais-cidco-land-demands-his-resignation/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=ncp-sp-targets-maha-minister-over-rs-5000-cr-scam-in-navi-mumbais-cidco-land-demands-his-resignation</t>
+          <t>https://www.etvbharat.com/mr/!state/sword-of-maratha-commander-raghuji-bhosale-returns-to-mumbai-to-be-unveiled-at-exhibition-by-cm-fadnavis-maharashtra-news-mhs25081803521</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CM to inaugurate additional water supply scheme</t>
+          <t>नवीन पिढीला इतिहासाशी जोडण्याचे कार्य सुरू; मुख्यमंत्री देवेंद्र फडणवीस यांचे प्रतिपादन</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/aurangabad/cm-to-inaugurate-additional-water-supply-scheme/</t>
+          <t>https://www.loksatta.com/mumbai/devendra-fadnavis-asserts-that-the-work-of-connecting-the-new-generation-with-history-is-underway-mumbai-print-news-amy-95-5313830/</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Mumbai Rains LIVE Updates: 250–300 mm Downpour Likely Tonight; Schools &amp; Colleges To Remain Shut On Tuesday</t>
+          <t>Maharashtra Rain Updates: मुंबईसाठी पुढील 12 तास महत्त्वाचे, राज्यात स्थिती काय? CM फडणवीसांनी सगळं सांगितल...</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-news-live-updates-check-for-latest-updates-of-all-the-happeneings-in-mumbai</t>
+          <t>https://news18marathi.com/maharashtra/maharashtra-rain-update-cm-devendra-fadnavis-hold-meeting-with-district-administration-1460734.html</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Mumbai rains: IMD issues red alert as downpour continues; schools, colleges &amp; Govt offices shut</t>
+          <t>CM देवेंद्र फडणवीस लवकरच कर्जमाफीची घोषणा करतील महायुतीच्या मंत्र्यांनी दिली</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>https://newslivetv.com/mumbai-rains-imd-issues-red-alert/</t>
+          <t>https://marathi.abplive.com/news/politics/cm-devendra-fadnavis-will-soon-announce-loan-waiver-farmers-mahayuti-ministers-sanjay-rathod-gave-information-yavatmal-1377983</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>पुढील १२ तास मुंबईसाठी अत्यंत महत्त्वाचे, मुख्यमंत्री फडणवीस पावसाबाबत काय म्हणाले?</t>
+          <t>Mumbai Rain: मुंबईत उद्या शाळांना सुट्टी? पुढचे १२ तास महत्वाचे, मुख्यमंत्री नेमकं काय म्हणाले?</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-review-mumbai-rain-says-next-12-hours-important-for-mumbai-and-mmr-region-1460967.html</t>
+          <t>https://saamtv.esakal.com/amp/story/mumbai-pune/mumbai-rain-alert-cm-devendra-fadnavis-said-mumbai-schools-declared-holiday-on-tomorrow-bmc-to-decide-pvm91</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>राज्यात अतिवृष्टीमुळे मुख्यमंत्री देवेंद्र फडणवीस यांचे सर्व यंत्रणांना सतर्कतेचे निर्देश; नांदेड जिल्ह्यात लष्कराची मदत</t>
+          <t>सरगुन मेहता आणि रवी दुबे यांनी दिली आनंदाची बातमी, वाचा सविस्तर...</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/chief-minister-devendra-fadnavis-has-directed-all-agencies-to-be-on-alert-due-to-heavy-rains-in-the-maharashtra-mumbai-print-news-amy-95-5313479/</t>
+          <t>https://www.etvbharat.com/mr/!entertainment/ravi-dubey-and-sargun-mehta-are-making-headlines-with-their-new-home-maharashtra-news-mhs25081802265</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Mumbai Rain : मुंबईत संध्याकाळी समुद्राला भरती, पुढील 12 तास महत्त्वाचे, पावसाच्या थैमानानंतर</t>
+          <t>मोठी बातमी! शेतकऱ्यांची कर्जमाफी होणार, मुख्यमंत्री घोषणा करणार, बड्या मंत्र्याने दिली माहिती</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-on-mumbai-maharashtra-rain-today-visit-disaster-management-department-bmc-marathi-news-1377962</t>
+          <t>https://www.tv9marathi.com/maharashtra/big-update-on-farmer-loan-waiver-cm-fadnavis-will-do-announcement-says-minister-sanjay-rathod-1472819.html</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>राज्यभरात पावसाचा हाहाकार, मुख्यमंत्री देवेंद्र फडणवीस यांनी घेतला आढावा; सर्व यंत्रणांना सतर्कतेचे निर्देश</t>
+          <t>Mumbai Rain Updates : सात जणांचा मृत्यू ते शेकडो गावे बाधित; राज्यभरात अतिवृष्टीमुळे कुठे काय घडलं?</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/rains-lashed-the-state-chief-minister-devendra-fadnavis-took-stock-instructed-all-agencies-to-be-alert.html</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-updates-18-august-heavy-rainfall-mumbai-navi-mumbai-kolhapur-raigad-sindhudurag-local-train-latest-updates-traffic-news-rak-94-5312079/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Mumbai Rain Update : समुद्रातून येतंय मुंबईवर मोठं संकट, पुढच्या 12 तासांत तुफान पाऊस, फडणवीस काय...</t>
+          <t>मोठी बातमी! नाराजी भोवली, शिवसेना शिंदे गटाला सर्वात मोठा धक्का, बड्या नेत्यानं सोडली एकनाथ शिंदेंची...</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/mumbai-rain-alert-cm-devendra-fadnavis-said-mumbai-have-red-alert-school-holiday-declared-know-detail-information-in-marathi-1472488.html</t>
+          <t>https://www.tv9marathi.com/maharashtra/big-blow-to-eknath-shinde-big-leader-of-shiv-sena-shinde-group-will-join-bjp-1472541.html</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Farmers Loan Waiver: बावनकुळेंनंतर महायुती सरकारमधील 'या' मंत्र्याची कर्जमाफीबाबत मोठी अपडेट; म्हणाले,'CM फडणवीस लवकरच...'</t>
+          <t>प्रशासन सतर्क : नागरिकांनी घराबाहेर पडू नये: मुख्यमंत्री फडणवीस !</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/sanjay-rathod-update-farmer-loan-waiver-devendra-fadnavis-dk88</t>
+          <t>https://vishwanewsmarathi.com/administrator-citizens-should-not-stay-home-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>राज्यात अतिवृष्टीच्या पार्श्वभूमीवर प्रशासन अलर्ट मोडवर! मुख्यमंत्री देवेंद्र फडणवीस यांचे सतर्कतेचे निर्देश</t>
+          <t>लवकरच कर्जमाफीची घोषणा होणार? महायुती सरकारमधील मंत्र्यांनी दिले संकेत</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/cm-devendra-fadnavis-took-review-of-rain-situation-at-state-disaster-management-centre-in-the-ministry-963383.html</t>
+          <t>https://marathi.oneindia.com/maharashtra/maharashtra-cm-fadnavis-loan-waiver-announcement-035127.html</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis : महाराष्ट्रातील माणसाला सर्वांनी समर्थन द्यावं; फडणवीस यांचे मविआला आवाहन</t>
+          <t>मुख्यमंत्री लवकरच शेतकरी कर्जमाफीची घोषणा करणार ; शिंदेंच्या मंत्र्यांचा दावा !</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-appeals-to-maharashtra-mps-to-support-cp-radhakrishnan-for-vice-president/913103/</t>
+          <t>https://vishwanewsmarathi.com/chief-minister-will-soon-announce-farmer-loan-waiver-shindes-ministers-claim/</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>सरदार रघुजी भोसले यांची ऐतिहासिक तलवार मुंबईत दाखल; मुख्यमंत्र्यांच्या हस्ते होणार लोकार्पण</t>
+          <t>मुख्यमंत्री फडणवीस लवकरच शेतकरी कर्जमाफीची घोषणा करण्याची शक्यता</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/sword-of-maratha-commander-raghuji-bhosale-returns-to-mumbai-to-be-unveiled-at-exhibition-by-cm-fadnavis-maharashtra-news-mhs25081803521</t>
+          <t>https://www.dainikprabhat.com/cm-fadnavis-likely-to-announce-farm-loan-waiver-soon/</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>नवीन पिढीला इतिहासाशी जोडण्याचे कार्य सुरू; मुख्यमंत्री देवेंद्र फडणवीस यांचे प्रतिपादन</t>
+          <t>महाराष्ट्रातील शेतकऱ्यांना मोठा दिलासा, मुख्यमंत्री फडणवीस लवकरच कर्जमाफीची घोषणा करणार</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/devendra-fadnavis-asserts-that-the-work-of-connecting-the-new-generation-with-history-is-underway-mumbai-print-news-amy-95-5313830/</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/big-relief-for-farmers-in-maharashtra-chief-minister-fadnavis-will-soon-announce-loan-waiver-125081900014_1.html</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Maharashtra Rain Updates: मुंबईसाठी पुढील 12 तास महत्त्वाचे, राज्यात स्थिती काय? CM फडणवीसांनी सगळं सांगितल...</t>
+          <t>एकनाथ शिंदेंना सोलापुरात मोठा धक्का : नेत्यांने सोडली साथ !</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/maharashtra-rain-update-cm-devendra-fadnavis-hold-meeting-with-district-administration-1460734.html</t>
+          <t>https://vishwanewsmarathi.com/big-setback-for-eknath-shinde-in-solapur-leaders-leave-support/</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>CM देवेंद्र फडणवीस लवकरच कर्जमाफीची घोषणा करतील महायुतीच्या मंत्र्यांनी दिली</t>
+          <t>युवकांसाठी सुवर्णसंधी! महाराष्ट्रातील 'या' जिल्ह्यात आयटी पार्क होणार, मुख्यमंत्र्यांचा मोठा निर्णय</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/cm-devendra-fadnavis-will-soon-announce-loan-waiver-farmers-mahayuti-ministers-sanjay-rathod-gave-information-yavatmal-1377983</t>
+          <t>https://www.thodkyaat.com/it-park-in-solapur-announced-by-cm-devendra-fadnavis-boost-to-jobs-and-development/</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Mumbai Rain: मुंबईत उद्या शाळांना सुट्टी? पुढचे १२ तास महत्वाचे, मुख्यमंत्री नेमकं काय म्हणाले?</t>
+          <t>ना. पंकजाताई मुंडे यांना ‘कोहिनूर ऑफ इंडिया’ अवाॅर्ड, लोकमत वृतपत्र समुहाने केला सन्मान; लंडन येथे पार पडला दिमाखदार सोहळा</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/mumbai-pune/mumbai-rain-alert-cm-devendra-fadnavis-said-mumbai-schools-declared-holiday-on-tomorrow-bmc-to-decide-pvm91</t>
+          <t>https://lokashanews.com/28165/</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>सरगुन मेहता आणि रवी दुबे यांनी दिली आनंदाची बातमी, वाचा सविस्तर...</t>
+          <t>Mumbai Rains : गुडघाभर पाणी, समोर रस्ताही दिसेना, लोकल रखडल्या आठवड्याच्या सुरुवातीला पावसानं मुंबईकरांची दाणादाण, पहा PHOTO</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!entertainment/ravi-dubey-and-sargun-mehta-are-making-headlines-with-their-new-home-maharashtra-news-mhs25081802265</t>
+          <t>https://marathi.asianetnews.com/mumbai/mumbai-heavy-rain-waterlogging-local-delays-school-shutdown/photoshow-at2tgam</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>मोठी बातमी! शेतकऱ्यांची कर्जमाफी होणार, मुख्यमंत्री घोषणा करणार, बड्या मंत्र्याने दिली माहिती</t>
+          <t>Mumbai News: गोल्डमन सॅक्सचे मुंबई नवे कार्यालय तिसऱ्या मुंबईचा नवा अध्याय - देवेंद्र फडणवीस</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/big-update-on-farmer-loan-waiver-cm-fadnavis-will-do-announcement-says-minister-sanjay-rathod-1472819.html</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/goldman-sachs-new-mumbai-office-is-a-new-chapter-for-third-mumbai-devendra-fadnavis-89597</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>गौरवशाली इतिहासाशी नव्या पीढीला जोडण्याचं काम रघुजीराजे भोसल्यांची ऐतिहासिक</t>
+          <t>Mumbai Rain News: मुंबईत किती ठिकाणी पाणी साचलं? ट्राफिकची स्थिती काय? मुख्यमंत्र्यांनी दिली A to Z माहिती</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-mumbai-exhibition-of-nagpur-raghuji-raje-bhosle-historical-sword-marathi-news-1378075</t>
+          <t>https://marathi.ndtv.com/cities/mumbai-rain-news-chief-minister-devendra-fadnavis-gave-information-about-the-rainfall-situation-in-mumbai-9107883</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Mumbai Rain Updates : सात जणांचा मृत्यू ते शेकडो गावे बाधित; राज्यभरात अतिवृष्टीमुळे कुठे काय घडलं?</t>
+          <t>“मुंबईत पुढच्या १२ तासांत तुफान पाऊस, रेड अलर्ट आणि…”; मुख्यमंत्री देवेंद्र फडणवीस यांनी काय माहिती दिली?</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-updates-18-august-heavy-rainfall-mumbai-navi-mumbai-kolhapur-raigad-sindhudurag-local-train-latest-updates-traffic-news-rak-94-5312079/</t>
+          <t>https://www.loksatta.com/maharashtra/mumbai-rain-alert-cm-devendra-fadnavis-said-mumbai-have-red-alert-school-holiday-declared-know-details-scj-81-5312934/</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>मोठी बातमी! नाराजी भोवली, शिवसेना शिंदे गटाला सर्वात मोठा धक्का, बड्या नेत्यानं सोडली एकनाथ शिंदेंची...</t>
+          <t>Pune News : मुख्यमंत्री फडणवीसांमुळे पुणेकरांना रोज मनस्ताप? काँग्रेसचा गंभीर आरोप</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/big-blow-to-eknath-shinde-big-leader-of-shiv-sena-shinde-group-will-join-bjp-1472541.html</t>
+          <t>https://sarkarnama.esakal.com/pune/devendra-fadnavis-pune-flyover-inauguration-delay-dk88-sm89</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>प्रशासन सतर्क : नागरिकांनी घराबाहेर पडू नये: मुख्यमंत्री फडणवीस !</t>
+          <t>महाराष्ट्रात महाभयानक पाऊस! मुख्यमंत्री देवेंद्र फडणवीस यांनी तातडीने साधला शेजारील राज्यांशी संपर्क? कारण अतिशय चिंताजनक</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/administrator-citizens-should-not-stay-home-chief-minister/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/maharashtra-mumbai-rain-alert-update-chief-minister-devendra-fadnavis-immediately-contacted-the-neighboring-states/933328</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>मुख्यमंत्री लवकरच शेतकरी कर्जमाफीची घोषणा करणार ; शिंदेंच्या मंत्र्यांचा दावा !</t>
+          <t>मुख्यमंत्री देवेंद्र फडणवीसांकडून पावसाचा आढावा: महाराष्ट्रात 4 लाख हेक्टरवरील पिके पाण्यात, उपाययोजनांचे ज...</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/chief-minister-will-soon-announce-farmer-loan-waiver-shindes-ministers-claim/</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/cm-devendra-fadnavis-review-maharashtra-flood-135703334.html</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>लवकरच कर्जमाफीची घोषणा होणार? महायुती सरकारमधील मंत्र्यांनी दिले संकेत</t>
+          <t>Third Mumbai News: तिसरी मुंबई आणि आर्थिक विकासाबाबत CM फडणवीसांचे मोठे विधान</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>https://marathi.oneindia.com/maharashtra/maharashtra-cm-fadnavis-loan-waiver-announcement-035127.html</t>
+          <t>https://marathi.ndtv.com/maharashtra/third-mumbai-will-open-a-new-chapter-of-economic-development-says-cm-devendra-fadnavis-9110192</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis : महाराष्ट्रातील माणसाला सर्वांनी समर्थन द्यावे; मुख्यमंत्री फडणवीस यांचे मविआच्या खासदारांना आवाहन</t>
+          <t>Maharashtra Rain : राज्यासाठी पुढचे दोन दिवस चिंतेचे, 15-16 जिल्ह्यांना अलर्ट, कुठे होणार अतिवृष्टी?...</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/devendra-fadnavis-everyone-should-support-the-people-of-maharashtra-chief-minister-fadnavis-appeals-to-m-v-a-mps/</t>
+          <t>https://www.tv9marathi.com/videos/maharashtra-imd-issues-red-alert-for-16-districts-big-information-by-cm-devendra-fadnavis-reviews-heavy-rains-in-1472606.html</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>मुख्यमंत्री फडणवीस लवकरच शेतकरी कर्जमाफीची घोषणा करण्याची शक्यता</t>
+          <t>Mumbai Rains Updates: मुंबईकरांनो पुढील 12 तास अतिशय महत्त्वाचे, CM फडणवीसांनी केले हे आवाहन</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/cm-fadnavis-likely-to-announce-farm-loan-waiver-soon/</t>
+          <t>https://marathi.ndtv.com/maharashtra/mumbai-rains-update-next-12-hours-are-important-for-mumbai-7-people-died-across-state-in-2-days-cm-fadnavis-appeals-to-citizens-9109288</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>महाराष्ट्रातील शेतकऱ्यांना मोठा दिलासा, मुख्यमंत्री फडणवीस लवकरच कर्जमाफीची घोषणा करणार</t>
+          <t>16 जिल्ह्यांना रेड अलर्ट! राज्याच्या ‘या’ भागात अतिवृष्टी, बचाव पथक सज्ज; CM फडणवीसांची...</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/big-relief-for-farmers-in-maharashtra-chief-minister-fadnavis-will-soon-announce-loan-waiver-125081900014_1.html</t>
+          <t>https://www.tv9marathi.com/maharashtra/rain-alert-in-16-districts-heavy-rainfall-in-this-part-of-state-cm-fadnavis-give-information-1472499.html</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>एकनाथ शिंदेंना सोलापुरात मोठा धक्का : नेत्यांने सोडली साथ !</t>
+          <t>पुण्यात नवीन महापालिकांवरून देवेंद्र फडणवीस आणि अजित पवार यांच्यात मतभेद का?</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/big-setback-for-eknath-shinde-in-solapur-leaders-leave-support/</t>
+          <t>https://www.loksatta.com/pune/devendra-fadnavis-ajit-pawar-dispute-over-new-municipal-corporations-in-pune-district-print-politics-news-css-98-5314697/</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>युवकांसाठी सुवर्णसंधी! महाराष्ट्रातील 'या' जिल्ह्यात आयटी पार्क होणार, मुख्यमंत्र्यांचा मोठा निर्णय</t>
+          <t>Devendra Fadnavis| मुख्यमंत्री देवेंद्र फडणवीस १९ रोजी पैठण तालुक्यात</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>https://www.thodkyaat.com/it-park-in-solapur-announced-by-cm-devendra-fadnavis-boost-to-jobs-and-development/</t>
+          <t>https://pudhari.news/maharashtra/marathwada/chhatrapati-sambhajinagar/devendra-fadnavis-visit-paithan-taluka-19-august-ng81</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>School Closed | मोठी बातमी! पावसामुळे आज महाराष्ट्रातील 'या' जिल्ह्यातील शाळा बंद</t>
+          <t>तिसरी मुंबई आर्थिक विकासाचा नवा अध्याय – मुख्यमंत्री देवेंद्र फडणवीस</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>https://www.thodkyaat.com/maharashtra-school-closed-tomorrow/</t>
+          <t>https://mahasamvad.in/176127/</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ना. पंकजाताई मुंडे यांना ‘कोहिनूर ऑफ इंडिया’ अवाॅर्ड, लोकमत वृतपत्र समुहाने केला सन्मान; लंडन येथे पार पडला दिमाखदार सोहळा</t>
+          <t>Maharashtra Heavy Rainfall | राज्यभरात अतिवृष्टीचा कहर; १५ जिल्ह्यांत रेड आणि ऑरेंज अलर्ट, नागरिकांनी घराबाहेर पडू नये: मुख्यमंत्री फडणवीस</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>https://lokashanews.com/28165/</t>
+          <t>https://pudhari.news/maharashtra/mumbai/maharashtra-heavy-rainfall-red-orange-alert-15-districts-cm-fadnavis-advisory-as80</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Mumbai Rains : गुडघाभर पाणी, समोर रस्ताही दिसेना, लोकल रखडल्या आठवड्याच्या सुरुवातीला पावसानं मुंबईकरांची दाणादाण, पहा PHOTO</t>
+          <t>गौरवशाली इतिहासाशी नव्या पीढीला जोडण्याचं काम रघुजीराजे भोसल्यांची ऐतिहासिक</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>https://marathi.asianetnews.com/mumbai/mumbai-heavy-rain-waterlogging-local-delays-school-shutdown/photoshow-at2tgam</t>
+          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-mumbai-exhibition-of-nagpur-raghuji-raje-bhosle-historical-sword-marathi-news-1378075</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Mumbai News: गोल्डमन सॅक्सचे मुंबई नवे कार्यालय तिसऱ्या मुंबईचा नवा अध्याय - देवेंद्र फडणवीस</t>
+          <t>महाराष्ट्रातील खासदारांनी राधाकृष्णन यांना समर्थन द्यावे: मुख्यमंत्री देवेंद्र फडणवीसांचे आवाहन; ठाकरे गट अ...</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/goldman-sachs-new-mumbai-office-is-a-new-chapter-for-third-mumbai-devendra-fadnavis-89597</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/c-p-radhakrishnan-vice-president-candidate-fadnavis-urges-support-135703533.html</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Mumbai Rain News: मुंबईत किती ठिकाणी पाणी साचलं? ट्राफिकची स्थिती काय? मुख्यमंत्र्यांनी दिली A to Z माहिती</t>
+          <t>पूरस्थितीचा सामना करण्यासाठी सरकारकडून सर्वतोपरी प्रयत्न, अतिवृष्टीचा धोका लक्षात घेऊन लोकांनी खबरदारी घ्यावी, मुख्यमंत्र्यांचं आवाहन</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/mumbai-rain-news-chief-minister-devendra-fadnavis-gave-information-about-the-rainfall-situation-in-mumbai-9107883</t>
+          <t>https://www.etvbharat.com/mr/!state/maharashtra-government-is-making-every-effort-to-deal-with-the-flood-situation-the-chief-minister-appeals-to-people-to-be-careful-considering-the-risk-of-heavy-rains-maharashtra-news-mhs25081804221</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>“मुंबईत पुढच्या १२ तासांत तुफान पाऊस, रेड अलर्ट आणि…”; मुख्यमंत्री देवेंद्र फडणवीस यांनी काय माहिती दिली?</t>
+          <t>CM Relief Fund: रुग्णांसाठी सरकारचा 'हा' विभाग ठरतोय मदतशीर; अमरावती विभागात तब्बल १०.६१ कोटींची मदत</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/mumbai-rain-alert-cm-devendra-fadnavis-said-mumbai-have-red-alert-school-holiday-declared-know-details-scj-81-5312934/</t>
+          <t>https://www.navarashtra.com/maharashtra/amravati/cm-devendra-fadnavis-cm-relief-fund-help-amravati-1187-patients-for-10-crore-rs-health-marathi-news-963412.html</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Pune News : मुख्यमंत्री फडणवीसांमुळे पुणेकरांना रोज मनस्ताप? काँग्रेसचा गंभीर आरोप</t>
+          <t>Nanded Breaking : मोठी बातमी! नांदेडमध्ये अनेक गाव पाण्याखाली, 15 जण अडकले तर 40 ते 50 म्हशीचा पाण्यात बुडून मृत्यू</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/pune/devendra-fadnavis-pune-flyover-inauguration-delay-dk88-sm89</t>
+          <t>https://www.lokshahi.com/news/rains-in-nandeds-mukhed-taluka-have-caused-flash-floods-in-many-villages-and-information-has-emerged-that-15-people-from-the-village-are-stranded</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Devendra Fadanvis on Rain Update : मुंबईला रेड अलर्ट ! मुख्यमंत्री देवेंद्र फडणवीस यांनी पावसाबद्दल दिली महत्त्वाची अपडेट</t>
+          <t>लातूर जिल्ह्यात मुसळधार पाऊस; लेंडी नदीला पूर आल्यानं तेलंगाणातील चार प्रवासी गेले वाहून; मुख्यमंत्र्यांनी घेतला आढावा</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/maharashtra-hevey-rain-update-cm-devendra-fadanvis-gives-important-information-know-about-more-/40070</t>
+          <t>https://www.etvbharat.com/mr/!state/heavy-rains-in-latur-district-cause-flooding-in-many-rivers-cm-devendra-fadnavis-took-a-review-lendi-river-flood-maharashtra-news-mhs25081802447</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>महाराष्ट्रात महाभयानक पाऊस! मुख्यमंत्री देवेंद्र फडणवीस यांनी तातडीने साधला शेजारील राज्यांशी संपर्क? कारण अतिशय चिंताजनक</t>
+          <t>इतिहासाची अमूल्य खुण भारतात! इतिहासाशी पुन्हा जोडणारा क्षण, मुख्यमंत्री फडणवीसांची भावनिक प्रतिक्रिया</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/maharashtra-mumbai-rain-alert-update-chief-minister-devendra-fadnavis-immediately-contacted-the-neighboring-states/933328</t>
+          <t>https://www.esakal.com/maharashtra/chief-minister-devendra-fadnavis-statement-after-bringing-sword-of-raje-raghuji-bhosale-to-india-vru98</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Third Mumbai News: तिसरी मुंबई आणि आर्थिक विकासाबाबत CM फडणवीसांचे मोठे विधान</t>
+          <t>Rohit Pawar on Sanjay Shirsat : संजय शिरसाटांकडून 5 हजार कोटींचा भ्रष्टाचार, रोहित पवारांच्या आरोपाने</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/third-mumbai-will-open-a-new-chapter-of-economic-development-says-cm-devendra-fadnavis-9110192</t>
+          <t>https://marathi.abplive.com/news/politics/rohit-pawar-accuses-sanjay-shirsat-of-5000-crores-of-corruption-big-demand-to-devendra-fadnavis-maharashtra-politics-marathi-news-1377888</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Maharashtra Rain : राज्यासाठी पुढचे दोन दिवस चिंतेचे, 15-16 जिल्ह्यांना अलर्ट, कुठे होणार अतिवृष्टी?...</t>
+          <t>Marathwada Rain : मराठवाड्यात शेतीचे सर्वाधिक नुकसान, 800 गावं जलबाधित; नांदेडमध्ये ढगफुटी, 5 जणांचा मृत्यू</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/maharashtra-imd-issues-red-alert-for-16-districts-big-information-by-cm-devendra-fadnavis-reviews-heavy-rains-in-1472606.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/cloudburst-rain-in-mukhed-nanded-district-five-people-missing-chief-minister-devendra-fadnavis-gave-information/913157/</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Mumbai Rains Updates: मुंबईकरांनो पुढील 12 तास अतिशय महत्त्वाचे, CM फडणवीसांनी केले हे आवाहन</t>
+          <t>CM Devendra Fadnavis: राज्यातील चार लाख हेक्टर क्षेत्रावरील पिकांना फटका; पिकांचे पंचनामे करण्याचे आदेश</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/mumbai-rains-update-next-12-hours-are-important-for-mumbai-7-people-died-across-state-in-2-days-cm-fadnavis-appeals-to-citizens-9109288</t>
+          <t>https://deshdoot.com/crops-affected-on-four-lakh-hectares-of-land-in-the-state-orders-to-conduct-crop-surveys/</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>16 जिल्ह्यांना रेड अलर्ट! राज्याच्या ‘या’ भागात अतिवृष्टी, बचाव पथक सज्ज; CM फडणवीसांची...</t>
+          <t>Maharashtra Politics Live Updates : जगनमोहन रेड्डींच्या पक्षाचा सीपी राधाकृष्णन यांना जाहीर पाठिंबा</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/rain-alert-in-16-districts-heavy-rainfall-in-this-part-of-state-cm-fadnavis-give-information-1472499.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-18-august-2025-latest-marathi-political-news-eknath-shinde-mumbai-mahayuti-rahul-gandhi-congress-india-aghadi-election-commission-devendra-fadnavis-uddhav-thackeray-india-alliance-mumbai-pune-ajit-pawar-ncp-local-elections-rahul-gandhi-vote-adhikar-yatra-nda-cp-radhakrishnan-vice-presidential-candidat</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>पुण्यात नवीन महापालिकांवरून देवेंद्र फडणवीस आणि अजित पवार यांच्यात मतभेद का?</t>
+          <t>CM Devendra Fadnavis: मुख्यमंत्र्यांनी राज्यातील पावसाचा घेतला आढावा; 'इतक्या' जिल्ह्यांना पावसाचा रेड अलर्ट, सतर्क राहण्याचे केले आवाहन</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/devendra-fadnavis-ajit-pawar-dispute-over-new-municipal-corporations-in-pune-district-print-politics-news-css-98-5314697/</t>
+          <t>https://deshdoot.com/cm-fadnavis-takes-reiew-situation-ndrf-and-army-deployed-16-districts-on-red-alert/</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>मुख्यमंत्री देवेंद्र फडणवीसांकडून पावसाचा आढावा: महाराष्ट्रात 4 लाख हेक्टरवरील पिके पाण्यात, उपाययोजनांचे ज...</t>
+          <t>Solapur News : शिंदेंच्या सेनेत राज्यातून ‘इन्कमिंग’ पण सोलापुरात गळती, तानाजी सावंतांच्या बंधूंचा भाजप प्रवेश ठरला</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/cm-devendra-fadnavis-review-maharashtra-flood-135703334.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/tanaji-sawant-brother-shivajirao-sawant-resign-eknath-shinde-sena-join-bjp-after-meet-fadnavis/913179/</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis| मुख्यमंत्री देवेंद्र फडणवीस १९ रोजी पैठण तालुक्यात</t>
+          <t>Shivaji Sawant : तानाजी सावंतांचे बंधू शिवाजी सावंतांचा भाजप प्रवेश निश्चित; मुख्यमंत्र्यांच्या भेटीनंतर जाहीर केला निर्णय</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/marathwada/chhatrapati-sambhajinagar/devendra-fadnavis-visit-paithan-taluka-19-august-ng81</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/shivaji-sawants-entry-into-bjp-confirmed-decision-announced-after-meeting-with-chief-minister-vd83</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>तिसरी मुंबई आर्थिक विकासाचा नवा अध्याय – मुख्यमंत्री देवेंद्र फडणवीस</t>
+          <t>मोदींचा निर्णय, उमेदवार ठरला अन् अडचणीत उद्धवसेना; 18 वर्षांनी पुन्हा तेच, ठाकरेंसमोर पेच?</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176127/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-picks-cp-radhakrishnan-for-vice-president-post-cm-devendra-fadnavis-ask-uddhav-thackeray-for-support/articleshow/123362737.cms</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Maharashtra Politics : एकनाथ शिंदेंची कोण करतंय कोंडी? दिल्ली दौरे वाढण्यामागचं काय कारण?</t>
+          <t>Maharashtra Rain Update : शाळांना सुट्टी आहे की नाही? नेमका निर्णय काय? फडणवीसांनीच संभ्रम संपवला;...</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/maharashtra-politics-shiv-sena-eknath-shinde-bjp-devendra-fadnavis-conflict-before-bmc-election-sdp-92-5314661/lite/</t>
+          <t>https://www.tv9marathi.com/photo-gallery/maharashtra-rain-update-mumbai-rain-school-and-college-holiday-decision-will-be-taken-after-weather-forecast-1472649.html</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Maharashtra Heavy Rainfall | राज्यभरात अतिवृष्टीचा कहर; १५ जिल्ह्यांत रेड आणि ऑरेंज अलर्ट, नागरिकांनी घराबाहेर पडू नये: मुख्यमंत्री फडणवीस</t>
+          <t>Mukhed cloudburst: मुखेडमध्ये ढगफुटी! 800 गावांना फटका, 226 लोकांची सुटका, 4 गावातले लोक फसले, सैन्याला पाचारण</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/maharashtra-heavy-rainfall-red-orange-alert-15-districts-cm-fadnavis-advisory-as80</t>
+          <t>https://marathi.ndtv.com/maharashtra/rain-big-news-mukhed-cloudburst-nanded-rain-news-calling-out-the-army-maharashtra-rain-alert-9107388</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Farmers Loan Waiver: बावनकुळेंनंतर महायुती सरकारमधील 'या' मंत्र्याची कर्जमाफीबाबत मोठी अपडेट; म्हणाले,'CM फडणवीस लवकरच...'</t>
+          <t>राजधानीत पावसाचा कहर! मुंबई विद्यापीठाचा परीक्षांबाबत तडकाफडकी मोठा निर्णय!</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/amp/story/maharashtra/vidarbha/sanjay-rathod-update-farmer-loan-waiver-devendra-fadnavis-dk88</t>
+          <t>https://www.tv9marathi.com/maharashtra/mumbai-university-postponed-its-all-exam-to-be-held-on-19-august-due-to-heavy-rain-marathi-news-1472932.html</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>महाराष्ट्रातील खासदारांनी राधाकृष्णन यांना समर्थन द्यावे: मुख्यमंत्री देवेंद्र फडणवीसांचे आवाहन; ठाकरे गट अ...</t>
+          <t>मराठ्यांच्या इतिहासाचं सोनेरी पान उलगडलं, मुख्यमंत्र्यांच्या हस्ते सरदार रघुजी राजे भोसले यांच्या ऐतिहासिक तलवारीचं लोकार्पण</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/c-p-radhakrishnan-vice-president-candidate-fadnavis-urges-support-135703533.html</t>
+          <t>https://www.etvbharat.com/mr/!state/unveiling-the-historic-sword-of-sardar-raghuji-raje-bhosale-in-mumbai-presence-of-chief-minister-devendra-fadnavis-know-history-of-raghuji-raje-sword-maharashtra-news-mhs25081900619</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>पुण्यात मुसळधार पाऊस पडतोय, आम्हाला वर्क फ्रॉम होम द्या! थेट मुख्यमंत्र्यांकडे आयटी कर्मचाऱ्यांची मागणी</t>
+          <t>Mumbai Rains News: मुंबई ठाण्याला पुढील 48 तासांसाठी रेड अलर्ट, शाळांना सुट्टी जाहीर, मुख्यमंत्र्यांकडून</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/it-company-employees-demand-work-from-home-due-to-heavy-rain-appeals-cm-devendra-fadnavis-pune-print-news-css-98-5314597/</t>
+          <t>https://marathi.abplive.com/news/mumbai-rain-news-update-red-alert-for-mumbai-thane-for-next-48-hours-imd-forecast-holiday-declared-for-schools-cm-devendra-fadnavis-reviews-flood-hit-areas-1377881</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>पूरस्थितीचा सामना करण्यासाठी सरकारकडून सर्वतोपरी प्रयत्न, अतिवृष्टीचा धोका लक्षात घेऊन लोकांनी खबरदारी घ्यावी, मुख्यमंत्र्यांचं आवाहन</t>
+          <t>Rain Update : मराठवाड्यात मृत्यूचं तांडव, तुफान पावसाने सगळं उद्ध्वस्त; मदतीसाठी थेट मिलिटरी दाखल!</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/maharashtra-government-is-making-every-effort-to-deal-with-the-flood-situation-the-chief-minister-appeals-to-people-to-be-careful-considering-the-risk-of-heavy-rains-maharashtra-news-mhs25081804221</t>
+          <t>https://www.tv9marathi.com/maharashtra/maharashtra-rain-update-marathwada-all-district-affected-by-heavy-rain-total-6-people-died-marathi-news-1472571.html</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>CM Relief Fund: रुग्णांसाठी सरकारचा 'हा' विभाग ठरतोय मदतशीर; अमरावती विभागात तब्बल १०.६१ कोटींची मदत</t>
+          <t>सी. पी. राधाकृष्णन यांना उपराष्ट्रपती पदाची उमेदवारी देण्यामागं भाजपाची काय आहेत राजकीय गणितं? जाणून घ्या, सविस्तर माहिती</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/amravati/cm-devendra-fadnavis-cm-relief-fund-help-amravati-1187-patients-for-10-crore-rs-health-marathi-news-963412.html</t>
+          <t>https://www.etvbharat.com/mr/!bharat/vice-president-of-india-election-2025-why-modi-of-tamil-nadu-cp-radhakrishnan-is-ndas-vice-presidential-pick-know-his-profile-from-tiruppur-roots-to-ndas-vice-presidential-candidate-maharashtra-news-mhs25081800641</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Nanded Breaking : मोठी बातमी! नांदेडमध्ये अनेक गाव पाण्याखाली, 15 जण अडकले तर 40 ते 50 म्हशीचा पाण्यात बुडून मृत्यू</t>
+          <t>ठाण्याला 100 टक्के नियोजित शहर बनवण्याचं मिशन हाती, 227 बेकायदा इमारतींवर पडणार हातोडा, ठाणे महानगरपालिकेची हायकोर्टात माहिती</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>https://www.lokshahi.com/news/rains-in-nandeds-mukhed-taluka-have-caused-flash-floods-in-many-villages-and-information-has-emerged-that-15-people-from-the-village-are-stranded</t>
+          <t>https://www.etvbharat.com/mr/!state/tmc-identified-227-illegal-buildings-strict-action-will-be-taken-to-make-thane-a-well-planed-city-tmc-assures-bombay-high-court-maharashtra-news-mhs25081802854</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>लातूर जिल्ह्यात मुसळधार पाऊस; लेंडी नदीला पूर आल्यानं तेलंगाणातील चार प्रवासी गेले वाहून; मुख्यमंत्र्यांनी घेतला आढावा</t>
+          <t>'उपराष्ट्रपती'साठी महाराष्ट्राच्या राज्यपालांचे नाव; फडणवीसांचे खासदारांना आवाहन, पवार-ठाकरेंना टोला</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/heavy-rains-in-latur-district-cause-flooding-in-many-rivers-cm-devendra-fadnavis-took-a-review-lendi-river-flood-maharashtra-news-mhs25081802447</t>
+          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-urges-mps-to-support-radhakrishnan-targets-uddhav-thackeray-and-sharad-pawar-035137.html</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>इतिहासाची अमूल्य खुण भारतात! इतिहासाशी पुन्हा जोडणारा क्षण, मुख्यमंत्री फडणवीसांची भावनिक प्रतिक्रिया</t>
+          <t>नांदेडमध्ये मुसळधार पावसाने हाहाकार,मुख्यमंत्री फडणवीस यांच्या देखरेखीखाली मदतकार्य तीव्र</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/chief-minister-devendra-fadnavis-statement-after-bringing-sword-of-raje-raghuji-bhosale-to-india-vru98</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/heavy-rains-wreak-havoc-in-nanded-relief-work-intensified-under-the-supervision-of-chief-minister-fadnavis-125081800046_1.html</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Rohit Pawar on Sanjay Shirsat : संजय शिरसाटांकडून 5 हजार कोटींचा भ्रष्टाचार, रोहित पवारांच्या आरोपाने</t>
+          <t>महाराष्ट्रात सर्वदूर पावसामुळे हाहाकार; मोठ्या प्रमाणात जीवित आणि वित्तहानी, बळीराज अडचणीत!</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/rohit-pawar-accuses-sanjay-shirsat-of-5000-crores-of-corruption-big-demand-to-devendra-fadnavis-maharashtra-politics-marathi-news-1377888</t>
+          <t>https://mpbreakingnews.in/marathi/maharashtra/rains-wreak-havoc-across-maharashtra-massive-loss-of-life-and-property-farmers-in-trouble-06-692619</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Marathwada Rain : मराठवाड्यात शेतीचे सर्वाधिक नुकसान, 800 गावं जलबाधित; नांदेडमध्ये ढगफुटी, 5 जणांचा मृत्यू</t>
+          <t>युवकांसाठी मोठी खुशखबर; ‘या’ ठिकाणी आयटी पार्क उभारणार; मुख्यमंत्र्यांची घोषणा</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/cloudburst-rain-in-mukhed-nanded-district-five-people-missing-chief-minister-devendra-fadnavis-gave-information/913157/</t>
+          <t>https://www.nagpurtoday.in/great-news-for-youth-it-park-will-be-set-up-at-this-place-chief-ministers-announcement/08181712</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Maharashtra Politics Live Updates : जगनमोहन रेड्डींच्या पक्षाचा सीपी राधाकृष्णन यांना जाहीर पाठिंबा</t>
+          <t>10 रुपयांत ‘शिवभोजन थाळी’ योजना थांबणार? शिवभोजन केंद्र चालकांची कोट्यवधींची बिलं थकली</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-18-august-2025-latest-marathi-political-news-eknath-shinde-mumbai-mahayuti-rahul-gandhi-congress-india-aghadi-election-commission-devendra-fadnavis-uddhav-thackeray-india-alliance-mumbai-pune-ajit-pawar-ncp-local-elections-rahul-gandhi-vote-adhikar-yatra-nda-cp-radhakrishnan-vice-presidential-candidat</t>
+          <t>https://mpbreakingnews.in/marathi/maharashtra/will-the-shiv-bhojan-thali-scheme-for-10-rupees-stop-shiv-bhojan-center-operators-are-facing-bills-worth-crores-02-692694</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>CM Devendra Fadnavis: राज्यातील चार लाख हेक्टर क्षेत्रावरील पिकांना फटका; पिकांचे पंचनामे करण्याचे आदेश</t>
+          <t>Nanded rains latest UPDATES: Water from Karnataka reach district; Indian Army, SDRF deployed for rescue missions as villagers trapped</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/crops-affected-on-four-lakh-hectares-of-land-in-the-state-orders-to-conduct-crop-surveys/</t>
+          <t>https://www.theweek.in/news/india/2025/08/18/mumbai-rain-news-nanded-rains-latest-updates-water-from-karnataka-reach-district-indian-army-sdrf-deployed-for-rescue-missions-and-villagers-trapped.html</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>CM Devendra Fadnavis: मुख्यमंत्र्यांनी राज्यातील पावसाचा घेतला आढावा; 'इतक्या' जिल्ह्यांना पावसाचा रेड अलर्ट, सतर्क राहण्याचे केले आवाहन</t>
+          <t>CM hands over keys to new police housing</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/cm-fadnavis-takes-reiew-situation-ndrf-and-army-deployed-16-districts-on-red-alert/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/cm-hands-over-keys-to-new-police-housing/articleshow/123350974.cms</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Shivaji Sawant : तानाजी सावंतांचे बंधू शिवाजी सावंतांचा भाजप प्रवेश निश्चित; मुख्यमंत्र्यांच्या भेटीनंतर जाहीर केला निर्णय</t>
+          <t>15 Maharashtra Districts Under Red and Orange Alert as Heavy Rains Continue; Mumbai Records 177 mm in Hours</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/shivaji-sawants-entry-into-bjp-confirmed-decision-announced-after-meeting-with-chief-minister-vd83</t>
+          <t>https://www.mypunepulse.com/15-maharashtra-districts-under-red-and-orange-alert-as-heavy-rains-continue-mumbai-records-177-mm-in-hours/</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Solapur News : शिंदेंच्या सेनेत राज्यातून ‘इन्कमिंग’ पण सोलापुरात गळती, तानाजी सावंतांच्या बंधूंचा भाजप प्रवेश ठरला</t>
+          <t>Raghuji Bhosale Sword: रघुजी भोसलेंची ऐतिहासिक तलवार आज मुंबईत; मुख्यमंत्र्यांच्या हस्ते होणार लोकार्पण</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/tanaji-sawant-brother-shivajirao-sawant-resign-eknath-shinde-sena-join-bjp-after-meet-fadnavis/913179/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/raghuji-bhosale-sword-to-arrive-in-mumbai-today-18-august-inauguration-ceremony-by-cm-devendra-fadnavis/articleshow/123353790.cms</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>मोदींचा निर्णय, उमेदवार ठरला अन् अडचणीत उद्धवसेना; 18 वर्षांनी पुन्हा तेच, ठाकरेंसमोर पेच?</t>
+          <t>चौथा श्रावणी सोमवार: 'या' राशींसाठी शुभ संयोग, महादेवाची राहणार कृपा, वाचा राशीभविष्य</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-picks-cp-radhakrishnan-for-vice-president-post-cm-devendra-fadnavis-ask-uddhav-thackeray-for-support/articleshow/123362737.cms</t>
+          <t>https://www.etvbharat.com/mr/!spiritual/shravan-2025-fourth-shravan-somwar-horoscope-rashi-bhavishya-for-18-august-2025-in-marathi-mhs25081704098</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>महायुतीच्या 'या' मंत्र्यावर 5 हजार कोटींच्या भ्रष्टाचाराचा आरोप; रोहित पवारांची मुख्यमंत्री फडणवीसांकडे राजीनाम्याची मागणी</t>
+          <t>मुंबईतील सर्व शासकीय आणि निमशासकीय कार्यालयांना आज सुट्टी जाहीर!</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>https://puneprimenews.com/mumbai/this-minister-of-mahayuti-accused-of-corruption-worth-rs-5000-crores-rohit-pawar-demands-resignation-from-chief-minister-fadnavis/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/19/mumbai-rains-govt-declares-holiday-for-all-government-and-private-offices-amid-heavy-rainfall.html</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Maharashtra Rain Update : शाळांना सुट्टी आहे की नाही? नेमका निर्णय काय? फडणवीसांनीच संभ्रम संपवला;...</t>
+          <t>Mumbai Rain Alert:मुंबईत पावसाची धुवाँधार बॅटिंग;शाळांना सुट्टी जाहीर</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/photo-gallery/maharashtra-rain-update-mumbai-rain-school-and-college-holiday-decision-will-be-taken-after-weather-forecast-1472649.html</t>
+          <t>https://ilovenagar.com/mumbai-rain-alert-schools-declare-holiday-today/</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>राजधानीत पावसाचा कहर! मुंबई विद्यापीठाचा परीक्षांबाबत तडकाफडकी मोठा निर्णय!</t>
+          <t>Super 100: आज इंडिया गठबंधन कर सकता है उपराष्ट्रपति चुनाव के लिए उम्मीदवार का एलान.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/mumbai-university-postponed-its-all-exam-to-be-held-on-19-august-due-to-heavy-rain-marathi-news-1472932.html/amp</t>
+          <t>https://www.indiatv.in/video/news-bulletin/super-100-today-india-alliance-can-announce-its-candidate-for-vice-presidential-election-2025-08-18-1156635</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Mukhed cloudburst: मुखेडमध्ये ढगफुटी! 800 गावांना फटका, 226 लोकांची सुटका, 4 गावातले लोक फसले, सैन्याला पाचारण</t>
+          <t>मुंबई में आज शाम हाई टाइड, लोगों से सावधानी की अपील, भारी बारिश का लोकल ट्रेनों</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/rain-big-news-mukhed-cloudburst-nanded-rain-news-calling-out-the-army-maharashtra-rain-alert-9107388</t>
+          <t>https://www.abplive.com/photo-gallery/states/maharashtra-mumbai-heavy-rainfall-waterlogging-imd-red-alert-local-train-delayed-photos-maharashtra-news-2997487</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Mumbai Rains News: मुंबई ठाण्याला पुढील 48 तासांसाठी रेड अलर्ट, शाळांना सुट्टी जाहीर, मुख्यमंत्र्यांकडून</t>
+          <t>समाचार संध्या</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai-rain-news-update-red-alert-for-mumbai-thane-for-next-48-hours-imd-forecast-holiday-declared-for-schools-cm-devendra-fadnavis-reviews-flood-hit-areas-1377881</t>
+          <t>https://www.newsonair.gov.in/bulletins-detail/%E0%A4%B8%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%BE%E0%A4%B0-%E0%A4%B8%E0%A4%82%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%BE-508/</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Mumbai Rains News: मुंबईसह महाराष्ट्रात 3 जिल्ह्यात शाळा-कॉलेज बंद, पावसाने सामान्यांचे झाले हाल; तलाव भरले</t>
+          <t>नवीन पिढीला इतिहासाशी जोडण्याचे कार्य सुरू – मुख्यमंत्री देवेंद्र फडणवीस</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/mumbai-rains-news-updates-school-college-closed-due-to-heavy-rains-thane-palghar-has-problem-963739.html</t>
+          <t>https://mahasamvad.in/176229/</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>मराठ्यांच्या इतिहासाचं सोनेरी पान उलगडलं, मुख्यमंत्र्यांच्या हस्ते सरदार रघुजी राजे भोसले यांच्या ऐतिहासिक तलवारीचं लोकार्पण</t>
+          <t>Modi Aur Musalman: मुस्लिम वोट की 'SIR गर्मी' ठंडी ?</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/unveiling-the-historic-sword-of-sardar-raghuji-raje-bhosale-in-mumbai-presence-of-chief-minister-devendra-fadnavis-know-history-of-raghuji-raje-sword-maharashtra-news-mhs25081900619</t>
+          <t>https://www.indiatv.in/video/news-bulletin/modi-aur-musalman-sir-2025-08-18-1156613</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Rain Update : मराठवाड्यात मृत्यूचं तांडव, तुफान पावसाने सगळं उद्ध्वस्त; मदतीसाठी थेट मिलिटरी दाखल!</t>
+          <t>Muqabla: 'वोट चोरी' पर जीत किसकी...Rahul Gandhi या Election Commission?</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/maharashtra-rain-update-marathwada-all-district-affected-by-heavy-rain-total-6-people-died-marathi-news-1472571.html</t>
+          <t>https://www.indiatv.in/video/news-bulletin/muqabla-rahul-gandhi-or-the-election-commission-who-wins-the-vote-theft-battle-2025-08-19-1156831</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>सी. पी. राधाकृष्णन यांना उपराष्ट्रपती पदाची उमेदवारी देण्यामागं भाजपाची काय आहेत राजकीय गणितं? जाणून घ्या, सविस्तर माहिती</t>
+          <t>ऐतिहासिक तलवार : इतिहासाशी नवीन पिढीला जोडण्याचे कार्य सुरू- मुख्यमंत्री देवेंद्र फडणवीस</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!bharat/vice-president-of-india-election-2025-why-modi-of-tamil-nadu-cp-radhakrishnan-is-ndas-vice-presidential-pick-know-his-profile-from-tiruppur-roots-to-ndas-vice-presidential-candidate-maharashtra-news-mhs25081800641</t>
+          <t>https://www.esakal.com/mumbai/todays-latest-marathi-news-mbi25b27280-txt-mumbai-20250818044851</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ठाण्याला 100 टक्के नियोजित शहर बनवण्याचं मिशन हाती, 227 बेकायदा इमारतींवर पडणार हातोडा, ठाणे महानगरपालिकेची हायकोर्टात माहिती</t>
+          <t>CM Devendra Fadnavis यांच्या हस्ते अद्ययावत पोलीस सदनिकेचे उद्घाटन</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/tmc-identified-227-illegal-buildings-strict-action-will-be-taken-to-make-thane-a-well-planed-city-tmc-assures-bombay-high-court-maharashtra-news-mhs25081802854</t>
+          <t>https://www.tarunbharat.com/cm-devendra-fadnavis-inauguration-of-new-police-building-kolhapur-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>'उपराष्ट्रपती'साठी महाराष्ट्राच्या राज्यपालांचे नाव; फडणवीसांचे खासदारांना आवाहन, पवार-ठाकरेंना टोला</t>
+          <t>Maharashtra Rain Live News: लातूरच्या अहमदपूरमधून जाणाऱ्या मन्याड नदीला पूर</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-urges-mps-to-support-radhakrishnan-targets-uddhav-thackeray-and-sharad-pawar-035137.html</t>
+          <t>https://saamtv.esakal.com/maharashtra/maharashtra-marathi-latest-live-news-updates-18th-augest-2025-ajchya-tajya-batmya-maharashtra-rain-update-rahul-gandhi-election-commission-raj-uddhav-thackeray-news-politics-cm-devendra-fadnavis-mumbai-thane-nagpur-pune-nashik-weather-forecast-rain-update-rains-live-news-today-pune-local-crime-top-headlines</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>नांदेडमध्ये मुसळधार पावसाने हाहाकार,मुख्यमंत्री फडणवीस यांच्या देखरेखीखाली मदतकार्य तीव्र</t>
+          <t>Devendra Fadanvis on Rain Update : मुंबईला रेड अलर्ट ! मुख्यमंत्री देवेंद्र फडणवीस यांनी पावसाबद्दल दिली महत्त्वाची अपडेट</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/heavy-rains-wreak-havoc-in-nanded-relief-work-intensified-under-the-supervision-of-chief-minister-fadnavis-125081800046_1.html</t>
+          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/maharashtra-hevey-rain-update-cm-devendra-fadanvis-gives-important-information-know-about-more-/40070</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>महाराष्ट्रात सर्वदूर पावसामुळे हाहाकार; मोठ्या प्रमाणात जीवित आणि वित्तहानी, बळीराज अडचणीत!</t>
+          <t>Maharashtra Breaking News LIVE : दिवसभरातील महत्त्वाच्या घडामोडी, ब्रेकिंग न्यूजचा आढावा एका क्लिकवर</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/marathi/maharashtra/rains-wreak-havoc-across-maharashtra-massive-loss-of-life-and-property-farmers-in-trouble-06-692619</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-august-18-political-news-in-marathi-933194</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>युवकांसाठी मोठी खुशखबर; ‘या’ ठिकाणी आयटी पार्क उभारणार; मुख्यमंत्र्यांची घोषणा</t>
+          <t>नेवासा येथे फर्निचर दुकानाला भीषण आग; दुकान मालकासह कुटुंबातील चौघांचा मृत्यू</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/great-news-for-youth-it-park-will-be-set-up-at-this-place-chief-ministers-announcement/08181712</t>
+          <t>https://www.etvbharat.com/mr/!state/ahilyanagar-fire-news-massive-fire-breaks-out-at-furniture-shop-in-nevasa-several-dead-including-furniture-shop-owner-wife-two-his-kids-maharashtra-news-mhs25081800839</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>10 रुपयांत ‘शिवभोजन थाळी’ योजना थांबणार? शिवभोजन केंद्र चालकांची कोट्यवधींची बिलं थकली</t>
+          <t>मुंबईत सकाळपासून मुसळधार पाऊस, दुपारच्या सर्व शाळांसह महाविद्यालयांना सुट्टी जाहीर</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/marathi/maharashtra/will-the-shiv-bhojan-thali-scheme-for-10-rupees-stop-shiv-bhojan-center-operators-are-facing-bills-worth-crores-02-692694</t>
+          <t>https://www.etvbharat.com/mr/!state/mumbai-rains-updates-bmc-declared-holiday-today-for-afternoon-shift-for-all-schools-and-colleges-in-mumbai-amid-imd-red-alert-for-thane-raigad-navi-mumbai-maharashtra-news-mhs25081802005</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Schools shut, red alert as Mumbai braces for another day of heavy rain | Latest News India - Hindustan Times</t>
+          <t>Kolhapur Weather Update: कोल्हापूर जिल्ह्याला आज रेड अलर्ट मोसमात प्रथमच राधानगरी धरणाचे सर्व</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/mumbai-rains-schools-shut-as-mumbai-under-imd-red-alert-braces-for-another-day-of-heavy-rain-10-updates-101755564432674.html</t>
+          <t>https://marathi.abplive.com/news/kolhapur/kolhapur-weather-red-alert-for-kolhapur-district-today-all-automatic-gates-of-radhanagari-dam-opened-for-the-first-time-in-the-season-1377818</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Nanded rains latest UPDATES: Water from Karnataka reach district; Indian Army, SDRF deployed for rescue missions as villagers trapped</t>
+          <t>कोल्हापूर सर्किट बेंच झाले, आता खंडपीठाचा प्रस्ताव द्या; सरन्यायाधीश भूषण गवईंची सूचना</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/news/india/2025/08/18/mumbai-rain-news-nanded-rains-latest-updates-water-from-karnataka-reach-district-indian-army-sdrf-deployed-for-rescue-missions-and-villagers-trapped.html</t>
+          <t>https://ratnagirikhabardar.com/news/74340/</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>CM hands over keys to new police housing</t>
+          <t>Mumbai gets 177mm rain in 6-8 hour period, says CM; all agencies asked to remain alert</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/cm-hands-over-keys-to-new-police-housing/articleshow/123350974.cms</t>
+          <t>https://m.economictimes.com/news/india/mumbai-gets-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/amp_articleshow/123365291.cms</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Sword of Raghuji Bhonsle arrives in Mumbai and will be on display till Aug 25</t>
+          <t>Upcoming ‘Third Mumbai’ will spur economic growth, says Maharashtra chief minister</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/sword-of-raghuji-bhonsle-arrives-in-mumbai-and-will-be-on-display-till-aug-25/articleshow/123371745.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/upcoming-third-mumbai-will-spur-economic-growth-says-maharashtra-chief-minister/articleshow/123368667.cms</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Mumbai rains HIGHLIGHTS: Civic body declares holiday for all schools on August 19</t>
+          <t>BJP ने शिंदे गुट में लगाई सेंध! कट्टर शिवसैनिक छोड़ेंगे पार्टी, निकाय चुनाव से पहले दिया बड़ा झटका</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/live-news-updates-mumbai-rain-waterlogging-traffic-heavy-rain-orange-alert-125081800291_1.html</t>
+          <t>https://www.patrika.com/mumbai-news/maharashtra-politics-bjp-gives-setback-to-eknath-shinde-shiv-sena-before-civic-polls-19873589</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Monsoon mayhem: Heavy rains flood this state, schools and colleges shut</t>
+          <t>नांदेड़ में भारी बारिश के कारण पांच लोग लापता, कई व्यक्ति फंसे : मुख्यमंत्री फडणवीस</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/en/national-news/monsoon-mayhem-heavy-rains-flood-this-state-schools-and-colleges-shut-19874810</t>
+          <t>https://www.ibc24.in/maharashtra/five-people-missing-several-stranded-due-to-heavy-rains-in-nanded-cm-fadnavis-3212983.html</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>15 Maharashtra Districts Under Red and Orange Alert as Heavy Rains Continue; Mumbai Records 177 mm in Hours</t>
+          <t>Devendra Fadanvis: राज्यात अतिवृष्टीचा ४ लाख हेक्टरवर फटका; मुख्यमंत्री दिले पंचनाम्याचे आदेश</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/15-maharashtra-districts-under-red-and-orange-alert-as-heavy-rains-continue-mumbai-records-177-mm-in-hours/</t>
+          <t>https://agrowon.esakal.com/video/maharashtra-crop-loss-4-lakh-hectares-cm-orders-panchanama</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Raghuji Bhosale Sword: रघुजी भोसलेंची ऐतिहासिक तलवार आज मुंबईत; मुख्यमंत्र्यांच्या हस्ते होणार लोकार्पण</t>
+          <t>Heavy Rainfall : रेड ॲलर्ट घोषित केलेल्या ठिकाणी सतर्कता बाळगण्याचे मुख्यमंत्री फडणवीसांचे निर्देश</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/raghuji-bhosale-sword-to-arrive-in-mumbai-today-18-august-inauguration-ceremony-by-cm-devendra-fadnavis/articleshow/123353790.cms</t>
+          <t>https://www.marathi.hindusthanpost.com/social/heavy-rainfall-cm-devendra-fadnavis-instructs-to-remain-vigilant-in-places-where-red-alert-has-been-declared/</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>मुंबईतील सर्व शासकीय आणि निमशासकीय कार्यालयांना आज सुट्टी जाहीर!</t>
+          <t>Congress Should Check Voter Lists Now, quips Chandrashekhar Bawankule</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/19/mumbai-rains-govt-declares-holiday-for-all-government-and-private-offices-amid-heavy-rainfall.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/congress-should-check-voter-lists-now-quips-chandrashekhar-bawankule/articleshow/123351307.cms</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Mumbai Rain Alert:मुंबईत पावसाची धुवाँधार बॅटिंग;शाळांना सुट्टी जाहीर</t>
+          <t>After Shankar Dayal Sharma, Another Maharashtra Governor Eyes V-P Post As BJP Picks Radhakrishnan</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>https://ilovenagar.com/mumbai-rain-alert-schools-declare-holiday-today/</t>
+          <t>https://www.news18.com/india/after-shankar-dayal-sharma-another-maharashtra-governor-eyes-v-p-post-as-bjp-picks-radhakrishnan-ws-kl-9511316.html</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Super 100: आज इंडिया गठबंधन कर सकता है उपराष्ट्रपति चुनाव के लिए उम्मीदवार का एलान.</t>
+          <t>Shiv Sena, NCP Support Maha Governor’s Nomination For Vice President</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/news-bulletin/super-100-today-india-alliance-can-announce-its-candidate-for-vice-presidential-election-2025-08-18-1156635</t>
+          <t>https://ommcomnews.com/india-news/shiv-sena-ncp-support-maha-governors-nomination-for-vice-president/</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Breaking News Maharashtra LIVE : संतोष देशमुख प्रकरण, सोमवारी सुनावणी</t>
+          <t>NDA's Vice President nominee CP Radhakrishnan to reach Delhi today: sources</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-maharashtra-politics-rain-flood-updates-election-commission-press-conference-thalak-batmya-sunday-17th-august-2025-1471433.html</t>
+          <t>https://www.aninews.in/news/national/general-news/ndas-vice-president-nominee-cp-radhakrishnan-to-reach-delhi-today-sources20250818101908</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Maharashtra Breaking News LIVE : दिवसभरातील महत्त्वाच्या घडामोडी, ब्रेकिंग न्यूजचा आढावा एका क्लिकवर</t>
+          <t>NCP must get Nashik guardian minister post: Bhujbal</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-august-18-political-news-in-marathi-933194</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/ncp-must-get-nashik-guardian-minister-post-bhujbal-101755457413078.html</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Mumbai gets 177mm rain in 6-8 hour period, says CM; all agencies asked to remain alert</t>
+          <t>DH Evening Brief | NDA VP pick in Delhi to meet BJP top brass, Opposition yet to finalise their candidate; I.N.D.I.A. bloc continues attacking EC chief over SIR</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/mumbai-gets-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/amp_articleshow/123365291.cms</t>
+          <t>https://www.deccanherald.com/india/dh-evening-brief-nda-vp-pick-in-delhi-to-meet-bjp-top-brass-opposition-yet-to-finalise-their-candidate-india-bloc-continues-attacking-ec-chief-over-sir-3685866</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Upcoming ‘Third Mumbai’ will spur economic growth, says Maharashtra chief minister</t>
+          <t>Clean image and cordial relations with netas across political parties paves Maharashtra governor CP Radha</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/upcoming-third-mumbai-will-spur-economic-growth-says-maharashtra-chief-minister/articleshow/123368667.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/clean-image-and-cordial-relations-with-netas-across-political-parties-paves-maharashtra-governor-cp-radhakrishnans-path-to-vice-presidents-office/articleshow/123350030.cms</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>CM’s nod for new terminal bldg at Nashik airport received: Min</t>
+          <t>'My karyakarta is with me': Hitendra Thakur shrugs off defections ahead of civic elections</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/cms-nod-for-new-terminal-bldg-at-nashik-airport-received-min/articleshow/123372835.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/my-karyakarta-is-with-me-hitendra-thakur-shrugs-off-defections-ahead-of-civic-elections/articleshow/123354325.cms</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Maharashtra rains: Five missing, several stranded as heavy rains lash Nanded, rescue operations underway</t>
+          <t>NDA’s VP nominee CP Radhakrishnan meets PM Modi in Delhi</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/maharashtra/maharashtra-rains-five-missing-several-stranded-as-heavy-rains-lash-nanded-rescue-operations-underway-2025-08-18-1004046</t>
+          <t>https://www.news9live.com/india/ndas-vp-nominee-cp-radhakrishnan-meets-pm-modi-in-delhi-2883321</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Heavy rains lash Mumbai; red alert issued, Vihar Lake overflows, CM urges caution</t>
+          <t>Devendra Fadnavis asks agencies to be on alert mode after heavy rainfall and flash floods</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/cities/mumbai/mumbai-rain-updates-august-18-2025/article69946286.ece</t>
+          <t>https://www.5dariyanews.com/news/464951-Devendra-Fadnavis-asks-agencies-to-be-on-alert-mode-after-heavy-rainfall-and-flash-floods</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Maha CM asks agencies to be on alert mode after heavy rainfall and flash floods</t>
+          <t>BJP names CP Radhakrishnan as NDA Vice President candidate, replacing Jagdeep Dhankhar</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/maha-cm-asks-agencies-to-be-on-alert-mode-after-heavy-rainfall-and-flash-floods/</t>
+          <t>https://apnlive.com/politics/cp-radhakrishnan-nda-vice-president-candidate/</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>देवेंद्र फडणवीस यांच्यासोबतच्या कोल्ड वॉरच्या चर्चेवर एकनाथ शिंदे यांची प्रतिक्रिया, स्पष्टच म्हणाले....</t>
+          <t>'Destroying constitutional institutions': Nishikant Dubey slams Rahul Gandhi as SC dismisses plea challenging 2024 Maharashtra polls</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/national/%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%AC%E0%A4%A4%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%A1-%E0%A4%B5-%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A%E0%A5%87%E0%A4%B5%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A4%9A-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1zqXD8?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.malaysiasun.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>मुंबईतील पावसाचा मुख्यमंत्र्यांकडून सातत्याने आढावा</t>
+          <t>'Destroying constitutional institutions': Nishikant Dubey slams Rahul Gandhi as SC dismisses plea challenging 2024 Maharashtra polls</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/19/the-chief-minister-is-continuously-reviewing-the-rainfall-in-mumbai.html</t>
+          <t>https://www.bignewsnetwork.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>BJP ने शिंदे गुट में लगाई सेंध! कट्टर शिवसैनिक छोड़ेंगे पार्टी, निकाय चुनाव से पहले दिया बड़ा झटका</t>
+          <t>Shivaji Sawant : शिवाजी सावंतांचा भाजपा प्रवेश निश्चित !</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/maharashtra-politics-bjp-gives-setback-to-eknath-shinde-shiv-sena-before-civic-polls-19873589</t>
+          <t>https://thefocusindia.com/maharashtra-news/shivaji-sawants-admission-to-bjp-is-certain-281398/amp/</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में भारी बारिश से सात लोगों की मौत, 200 ग्रामीण फंसे</t>
+          <t>Eknath Shinde : एकनाथ शिंदेंना मोठा धक्का ! ‘या’ नेत्याने निवडणुकीच्या तोंडावर सोडली साथ</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/seven-people-died-due-to-heavy-rains-in-maharashtra-200-villagers-stranded/856903/?amp</t>
+          <t>https://www.dainikprabhat.com/big-blow-to-eknath-shinde-big-leader-of-shiv-sena-shinde-group-will-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में मानसून का कहर: मुखेड तालुका में बादल फटने जैसी घटना, 200 से ज्यादा गांवों में बाढ़</t>
+          <t>Devendra Fadnavis Politics : देवेंद्र फडणवीसांचा 'मोठा गेम'; अजितदादा, एकनाथ शिंदे गाफील!</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>https://hindi.dynamitenews.com/maharashtra/cloudburst-in-mukhed-taluka-in-maharashtra-flood-in-more-than-200-villages</t>
+          <t>https://sarkarnama.esakal.com/vishleshan/devendra-fadnavis-politics-ajit-pawar-eknath-shinde-unaware-bjp-incoming-rm89</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>CM फडणवीस ने खेला 'मराठी अस्मिता' का दांव, उपराष्ट्रपति चुनाव में उद्धव-पवार पर बना दबाव</t>
+          <t>Guardian Minister of Nashik : नाशिकच्या पालकमंत्रीपदाचा वाद पेटला!</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/political-battle-over-nda-candidate-radhakrishnan-cm-fadnavis-seeks-support-from-uddhav-thackeray-and-sharad-pawar-1321873.html/amp</t>
+          <t>https://pudhari.news/maharashtra/north-maharashtra/nashik/guardian-minister-of-nashik-controversy-over-the-post-of-guardian-minister-of-nashik-has-flared-up-ar84</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Mumbai News: चव्हाण ने कहा - श्रमिकों की एक साल में दो बार होगी वेतन वृद्धि</t>
+          <t>सोलापुरात भाजपची शिंदेंच्या शिवसेनावर कुरघोडी शिवाजी सावंतांनी शिवसेना सोडली,</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/city/mumbai/mumbai-news-chavan-said-workers-will-get-salary-hike-twice-in-a-year-1174137</t>
+          <t>https://marathi.abplive.com/news/politics/solapur-shivaji-sawant-leaves-shiv-sena-and-bjp-entry-confirmed-devendra-fadnavis-bjp-attack-on-eknath-shinde-shiv-sena-in-solapur-1377928</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>नांदेड़ में भारी बारिश के कारण पांच लोग लापता, कई व्यक्ति फंसे : मुख्यमंत्री फडणवीस</t>
+          <t>Ashish Shelar: मुंबईत जोरदार पाऊस! पावसाचा आढावा घेतल्यानंतर मंत्री शेलार म्हणाले, 'अत्यंत गरज असल्यास...'</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/maharashtra/five-people-missing-several-stranded-due-to-heavy-rains-in-nanded-cm-fadnavis-3212983.html</t>
+          <t>https://www.jaimaharashtranews.com/politics/mumbai-rain-updates-ashish-shelar-reviewed-the-rainfall-and-said-stay-safe-at-home/40069</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Devendra Fadanvis: राज्यात अतिवृष्टीचा ४ लाख हेक्टरवर फटका; मुख्यमंत्री दिले पंचनाम्याचे आदेश</t>
+          <t>Uddhav Thackeray: मनसेसोबत युती महापालिका निवडणुकीत घातक ठरणार; उद्धव ठाकरेंना 'या' नेत्यानं केलं सावध?</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/video/maharashtra-crop-loss-4-lakh-hectares-cm-orders-panchanama</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/mns-alliance-risk-municipal-elections-uddhav-thackeray-warning-dk88-rc70</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Heavy Rainfall : रेड ॲलर्ट घोषित केलेल्या ठिकाणी सतर्कता बाळगण्याचे मुख्यमंत्री फडणवीसांचे निर्देश</t>
+          <t>भाजप आमदाराचा डाव प्रशासनाने हाणून पाडला, आईच्या नावाने बांधलेले अम्मा स्मारक अवैध ठरवून हटवले</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/heavy-rainfall-cm-devendra-fadnavis-instructs-to-remain-vigilant-in-places-where-red-alert-has-been-declared/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/chandrapur-bjp-mla-kishor-jorgewar-faces-setback-as-administration-demolishes-illegal-amma-memorial-construction-as11-rc70</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Congress Should Check Voter Lists Now, quips Chandrashekhar Bawankule</t>
+          <t>भाजपला स्थानिक ची निवडणूक महायुती म्हणूनच का लढवायची आहे?</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/congress-should-check-voter-lists-now-quips-chandrashekhar-bawankule/articleshow/123351307.cms</t>
+          <t>https://aaplaawajnews.com/2025/34070/</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>After Shankar Dayal Sharma, Another Maharashtra Governor Eyes V-P Post As BJP Picks Radhakrishnan</t>
+          <t>Congress Mohan Joshi Pune | Don't wait for BJP's 'event', open the flyover</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>https://www.news18.com/india/after-shankar-dayal-sharma-another-maharashtra-governor-eyes-v-p-post-as-bjp-picks-radhakrishnan-ws-kl-9511316.html</t>
+          <t>https://policenama.com/congress-mohan-joshi-pune-dont-wait-for-bjps-event-open-the-flyover-former-mla-mohan-joshis-letter-to-the-municipal-commissioner/</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Shiv Sena, NCP Support Maha Governor’s Nomination For Vice President</t>
+          <t>प्रशांत यादव यांचा आज भाजप प्रवेश</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>https://ommcomnews.com/india-news/shiv-sena-ncp-support-maha-governors-nomination-for-vice-president/</t>
+          <t>https://ratnagirikhabardar.com/news/74397/</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>NDA's Vice President nominee CP Radhakrishnan to reach Delhi today: sources</t>
+          <t>‘गँग्स ऑफ गद्दार’: शिंदेचा मंत्री ‘रोहित पवारांच्या’ निशाण्यावर</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/ndas-vice-president-nominee-cp-radhakrishnan-to-reach-delhi-today-sources20250818101908</t>
+          <t>https://politicalmaharashtra.in/gangs-of-traitors-shindes-minister-targeted-by-rohit-pawar-97619/</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>NCP must get Nashik guardian minister post: Bhujbal</t>
+          <t>To collect outstanding transportation fines, the Maha government is planning an amnesty scheme</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/ncp-must-get-nashik-guardian-minister-post-bhujbal-101755457413078.html</t>
+          <t>https://assamtribune.com/national/to-collect-outstanding-transportation-fines-the-mahagovernment-is-planning-an-amnesty-scheme-1588536</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Clean image and cordial relations with netas across political parties paves Maharashtra governor CP Radha</t>
+          <t>Heritage India: Iconic Sword of Maratha Commander Raghuji Raje Bhonsle Arrives in Mumbai</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/clean-image-and-cordial-relations-with-netas-across-political-parties-paves-maharashtra-governor-cp-radhakrishnans-path-to-vice-presidents-office/articleshow/123350030.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-govt-brings-back-iconic-sword-of-maratha-commander-raghuji-raje-bhonsle-auctioned-for-rs-4715-lakh-to-mumbai-3685565</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Rajnath reaches out to DMK, TMC, BJD for consensus on VP nominee</t>
+          <t>Maha CM asks agencies to be on alert mode after heavy rainfall and flash floods</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/other/rajnath-reaches-out-to-dmk-tmc-bjd-for-consensus-on-vp-nominee/ar-AA1KKGcl</t>
+          <t>https://www.socialnews.xyz/2025/08/18/maha-cm-asks-agencies-to-be-on-alert-mode-after-heavy-rainfall-and-flash-floods/</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>'Destroying constitutional institutions': Nishikant Dubey slams Rahul Gandhi as SC dismisses plea challenging 2024 Maharashtra polls</t>
+          <t>Heavy rain: Dy CM asks Maha, district agencies to coordinate, prioritise rescue works</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/politics/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls20250819085747</t>
+          <t>https://www.socialnews.xyz/2025/08/18/heavy-rain-dy-cm-asks-maha-district-agencies-to-coordinate-prioritise-rescue-works/</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>NDA’s VP nominee CP Radhakrishnan meets PM Modi in Delhi</t>
+          <t>Ahead of Civic Polls, Hitendra Thakur Backs Loyalists: ‘My Karyakarta Is With Me, They Ensure Our Party Wins</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>https://www.news9live.com/india/ndas-vp-nominee-cp-radhakrishnan-meets-pm-modi-in-delhi-2883321</t>
+          <t>https://www.lokmattimes.com/maharashtra/ahead-of-civic-polls-hitendra-thakur-backs-loyalists-my-karyakarta-is-with-me-they-ensure-our-party-wins-a475/</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis asks agencies to be on alert mode after heavy rainfall and flash floods</t>
+          <t>'ऑपरेशन लोटस वगैरे काही नाही; लवकरच ऑपरेशन टायगर दिसेल', सोलापूरच्या राजकारणात पडद्यामागे काय घडतंय?</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>https://www.5dariyanews.com/news/464951-Devendra-Fadnavis-asks-agencies-to-be-on-alert-mode-after-heavy-rainfall-and-flash-floods</t>
+          <t>https://marathi.indiatimes.com/maharashtra/solapur/solapur-politics-over-shiv-sena-leader-shivaji-sawant-may-join-bjp/articleshow/123369493.cms</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>BJP names CP Radhakrishnan as NDA Vice President candidate, replacing Jagdeep Dhankhar</t>
+          <t>Coffee Par Kurukshetra: उपराष्ट्रपति के नाम पर INDI अलायंस टूट जाएगा?</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>https://apnlive.com/politics/cp-radhakrishnan-nda-vice-president-candidate/</t>
+          <t>https://www.indiatv.in/video/kurukshetra/coffee-par-kurukshetra-indi-2025-08-19-1156832</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>BJP man accuses Trinamool leaders of supporting Rohingyas, threatens to bulldoze them into Bangladesh</t>
+          <t>Aaj Ki Baat: Mumbai में बारिश का Red Alert...48 घंटे संभलकर</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/bjp-man-accuses-trinamool-leaders-of-supporting-rohingyas-threatens-to-bulldoze-them-into-bangladesh/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=bjp-man-accuses-trinamool-leaders-of-supporting-rohingyas-threatens-to-bulldoze-them-into-bangladesh</t>
+          <t>https://www.indiatv.in/video/aaj-ki-baat/aaj-ki-baat-red-alert-for-rain-in-mumbai-be-careful-for-48-hours-2025-08-19-1156835</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Shivaji Sawant : शिवाजी सावंतांचा भाजपा प्रवेश निश्चित !</t>
+          <t>जनसंघ से लेकर राज्यपाल तक का सफर! अब CP राधाकृष्णन बने उपराष्ट्रपति के उम्मीदवार, कैसा रहा नेताओं का रिएक्शन?</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/shivaji-sawants-admission-to-bjp-is-certain-281398/amp/</t>
+          <t>https://hindi.oneindia.com/news/india/maharashtra-governor-cp-radhakrishnan-nda-vice-presidential-candidate-leaders-congratulate-1364687.html</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Eknath Shinde : एकनाथ शिंदेंना मोठा धक्का ! ‘या’ नेत्याने निवडणुकीच्या तोंडावर सोडली साथ</t>
+          <t>महाराष्ट्र में मौसम बरपा रहा कहर: नांदेड़ में फटा बादल, बारिश के चलते 15 से 16 जिलो में अलर्ट, CM फडणवीस ने फसलों से लेकर लोकल ट्रेनों के बारे में दिया ये बड़ा अपडेट | Devendra Fadnavis, Cloudburst, Nan</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/big-blow-to-eknath-shinde-big-leader-of-shiv-sena-shinde-group-will-join-bjp/</t>
+          <t>https://www.bhaskarhindi.com/politics/devendra-fadnavis-cloudburst-nanded-maharashtra-news-maharashtra-1174025</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Guardian Minister of Nashik : नाशिकच्या पालकमंत्रीपदाचा वाद पेटला!</t>
+          <t>Amravati Politics: अमरावती के दरियापुर में कांग्रेस को बड़ा झटका, सलीम घनीवाला भाजपा में शामिल</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/north-maharashtra/nashik/guardian-minister-of-nashik-controversy-over-the-post-of-guardian-minister-of-nashik-has-flared-up-ar84</t>
+          <t>https://navbharatlive.com/maharashtra/amravati/major-blow-to-congress-in-dariyapur-of-amravati-salim-ghaniwala-joins-bjp-1321794.html</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis Politics : देवेंद्र फडणवीसांचा 'मोठा गेम'; अजितदादा, एकनाथ शिंदे गाफील!</t>
+          <t>शिवसेना शिंदे गुट को बड़ा झटका, बड़ा नेता छोड़ेगा एकनाथ शिंदे का साथ</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/vishleshan/devendra-fadnavis-politics-ajit-pawar-eknath-shinde-unaware-bjp-incoming-rm89</t>
+          <t>https://mpbreakingnews.in/maharashtra/shivaji-sawant-bjp-solapur-eknath-shinde-54-804117</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Mumbai Rain Alert : मुंबईकरांनो सावध रहा.. पुढील 4 तास धोक्याचे… रेड अलर्ट अन् हवामान खात्याचा...</t>
+          <t>Breaking News Maharashtra LIVE : संतोष देशमुख प्रकरण, सोमवारी सुनावणी</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/mumbai-weather-forecast-imd-red-alert-for-mumbai-for-next-4-hours-extremely-important-for-mumbaikars-1473139.html/amp</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-maharashtra-politics-rain-flood-updates-election-commission-press-conference-thalak-batmya-sunday-17th-august-2025-1471433.html</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Uddhav Thackeray: मनसेसोबत युती महापालिका निवडणुकीत घातक ठरणार; उद्धव ठाकरेंना 'या' नेत्यानं केलं सावध?</t>
+          <t>नीतिमूल्य समितीला मुहूर्त मिळेना! आमदारांबाबत घोषणा करुन महिना उलटूनही बैठकच नाही</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/mns-alliance-risk-municipal-elections-uddhav-thackeray-warning-dk88-rc70</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/no-meeting-even-after-month-of-announcement-regarding-ethic-committee-mlas/articleshow/123356125.cms</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>भाजपला स्थानिक ची निवडणूक महायुती म्हणूनच का लढवायची आहे?</t>
+          <t>Mumbai Rains News: मुंबईसह महाराष्ट्रात 3 जिल्ह्यात शाळा-कॉलेज बंद, पावसाने सामान्यांचे झाले हाल; तलाव भरले</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>https://aaplaawajnews.com/2025/34070/</t>
+          <t>https://www.navarashtra.com/maharashtra/mumbai-rains-news-updates-school-college-closed-due-to-heavy-rains-thane-palghar-has-problem-963739.html</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Congress Mohan Joshi Pune | Don't wait for BJP's 'event', open the flyover</t>
+          <t>Amravati News : अमरावतीच्या दर्यापुरात काँग्रेसला मोठा धक्का, सलीम घाणीवालांचा भाजपमध्ये प्रवेश</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>https://policenama.com/congress-mohan-joshi-pune-dont-wait-for-bjps-event-open-the-flyover-former-mla-mohan-joshis-letter-to-the-municipal-commissioner/</t>
+          <t>https://marathi.ndtv.com/politics/salim-ghaniwala-joins-bjp-big-blow-to-congress-in-daryapur-amravati-9106782</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>प्रशांत यादव यांचा आज भाजप प्रवेश</t>
+          <t>ABP Majha Top 10 Headlines : ABP माझा टॉप 10 हेडलाईन्स | 18 ऑगस्ट 2025 | सोमवार</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/74397/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/abp-majha-top-10-headlines-18-august-2025-monday-latest-marathi-news-update-maharashtra-politics-marathi-news-1378004</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>‘गँग्स ऑफ गद्दार’: शिंदेचा मंत्री ‘रोहित पवारांच्या’ निशाण्यावर</t>
+          <t>मंत्री आशीष शेलार यांनी घेतला आपात्कालीन व्यवस्थापनाचा आढावा</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>https://politicalmaharashtra.in/gangs-of-traitors-shindes-minister-targeted-by-rohit-pawar-97619/</t>
+          <t>https://www.jpnnews.in/2025/08/Ashish-Shelar-reviews-emergency-management.html</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>To collect outstanding transportation fines, the Maha government is planning an amnesty scheme</t>
+          <t>राज्यात ओला दुष्काळ जाहीर करा, विशेष अधिवेशन बोलवा मुसळधार पावसानंतर शरद पवारांच्या</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>https://assamtribune.com/national/to-collect-outstanding-transportation-fines-the-mahagovernment-is-planning-an-amnesty-scheme-1588536</t>
+          <t>https://marathi.abplive.com/news/politics/sharad-pawar-ncp-demands-after-heavy-rains-declaring-a-wet-drought-in-the-state-calling-a-special-session-shashikant-shinde-1377947</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Modi Aur Musalman: मुस्लिम वोट की 'SIR गर्मी' ठंडी ?</t>
+          <t>TDR Scam: साडेसातशे कोटींच्या टीडीआर घोटाळ्याचा ‘आका’ कोण?</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/news-bulletin/modi-aur-musalman-sir-2025-08-18-1156613</t>
+          <t>https://pudhari.news/maharashtra/pune/750-crore-land-tdr-scam-ac90</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Muqabla: 'वोट चोरी' पर जीत किसकी...Rahul Gandhi या Election Commission?</t>
+          <t>Sanjay Shirsat: संजय शिरसाठ पुन्हा अडचणीत, रोहित पवारांचा नवा आरोप, 15 एकर जमिनीचा वाद काय आहे?</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/news-bulletin/muqabla-rahul-gandhi-or-the-election-commission-who-wins-the-vote-theft-battle-2025-08-19-1156831</t>
+          <t>https://pudhari.news/maharashtra/mumbai/sanjay-shirsat-land-dispute-rohit-pawar-allegations-mk94</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>'ऑपरेशन लोटस वगैरे काही नाही; लवकरच ऑपरेशन टायगर दिसेल', सोलापूरच्या राजकारणात पडद्यामागे काय घडतंय?</t>
+          <t>Seize assets of school directors in Shalarth ID scam: Bawankule</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/solapur/solapur-politics-over-shiv-sena-leader-shivaji-sawant-may-join-bjp/articleshow/123369493.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/seize-assets-of-school-directors-in-shalarth-id-scam-bawankule/articleshow/123371134.cms</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Coffee Par Kurukshetra: उपराष्ट्रपति के नाम पर INDI अलायंस टूट जाएगा?</t>
+          <t>Nagpur Smart City projects near closure with 7 works still pending</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/kurukshetra/coffee-par-kurukshetra-indi-2025-08-19-1156832</t>
+          <t>https://infra.economictimes.indiatimes.com/news/urban-infrastructure/nagpur-smart-city-projects-face-delay-7-projects-pending-completion/123360909</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Aaj Ki Baat: Mumbai में बारिश का Red Alert...48 घंटे संभलकर</t>
+          <t>Raghuji Bhonsle’s Sword To Reach Mum Today, Mudhoji Raje To Attend Ceremony</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/aaj-ki-baat/aaj-ki-baat-red-alert-for-rain-in-mumbai-be-careful-for-48-hours-2025-08-19-1156835</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/raghuji-bhonsles-sword-to-reach-mum-today-mudhoji-raje-to-attend-ceremony/articleshow/123351204.cms</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>जनसंघ से लेकर राज्यपाल तक का सफर! अब CP राधाकृष्णन बने उपराष्ट्रपति के उम्मीदवार, कैसा रहा नेताओं का रिएक्शन?</t>
+          <t>Now, Bachchu Kadu claims offer to ‘delete thousands of names’ from voters’ list</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/india/maharashtra-governor-cp-radhakrishnan-nda-vice-presidential-candidate-leaders-congratulate-1364687.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/now-bachchu-kadu-claims-offer-to-delete-thousands-of-names-from-voters-list/articleshow/123351305.cms</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Amravati Politics: अमरावती के दरियापुर में कांग्रेस को बड़ा झटका, सलीम घनीवाला भाजपा में शामिल</t>
+          <t>Owners threaten to shut bars from Aug 25 over high taxes on liquor</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/amravati/major-blow-to-congress-in-dariyapur-of-amravati-salim-ghaniwala-joins-bjp-1321794.html/amp</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/owners-threaten-to-shut-bars-from-aug-25-over-high-taxes-on-liquor/articleshow/123351216.cms</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>शिवसेना शिंदे गुट को बड़ा झटका, बड़ा नेता छोड़ेगा एकनाथ शिंदे का साथ</t>
+          <t>Historic sword of Raje Raghuji Bhonsle arrives in Mumbai to royal welcome</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/maharashtra/shivaji-sawant-bjp-solapur-eknath-shinde-54-804117</t>
+          <t>https://www.nagpurtoday.in/historic-sword-of-raje-raghuji-bhonsle-arrives-in-mumbai-to-royal-welcome/08181446</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>नीतिमूल्य समितीला मुहूर्त मिळेना! आमदारांबाबत घोषणा करुन महिना उलटूनही बैठकच नाही</t>
+          <t>३१ खासदार निवडून आले तेव्हा मतदारयाद्या बरोबर होत्या का ?</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/no-meeting-even-after-month-of-announcement-regarding-ethic-committee-mlas/articleshow/123356125.cms</t>
+          <t>https://www.lokmat.com/nagpur/were-the-voter-lists-correct-when-31-mps-were-elected-a-a1000/</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>CM Devendra Fadnavis यांच्या हस्ते अद्ययावत पोलीस सदनिकेचे उद्घाटन</t>
+          <t>'एआय' तंत्रज्ञानाचा वापर करून नागपूर ग्रामीण पोलिसांनी केली गुन्ह्याची उकल, 'हिट अँड रन' प्रकरणी आरोपी अटकेत</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/cm-devendra-fadnavis-inauguration-of-new-police-building-kolhapur-marathi-news/</t>
+          <t>https://www.etvbharat.com/mr/!state/truck-hits-bike-husband-carried-wife-on-bike-nagpur-rural-police-arrests-accused-truck-driver-using-ai-technology-maharashtra-news-mhs25081805869</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Amravati News : अमरावतीच्या दर्यापुरात काँग्रेसला मोठा धक्का, सलीम घाणीवालांचा भाजपमध्ये प्रवेश</t>
+          <t>रघुजी राजे यांची तलवार आणि ‘स्व’चा बोध</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/salim-ghaniwala-joins-bjp-big-blow-to-congress-in-daryapur-amravati-9106782</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/historic-sword-of-shrimant-raghuji-bhosle-back-in-mumbai.html</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>ABP Majha Top 10 Headlines : ABP माझा टॉप 10 हेडलाईन्स | 18 ऑगस्ट 2025 | सोमवार</t>
+          <t>Teacher Recruitment Scam: बोगस शालार्थ आयडी घोटाळ्यातील संचालकांची मालमत्ता जप्त होणार !</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/abp-majha-top-10-headlines-18-august-2025-monday-latest-marathi-news-update-maharashtra-politics-marathi-news-1378004</t>
+          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/bogus-teacher-scam-school-id-fraud-directors-property-to-be-seized-ng81</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>मंत्री आशीष शेलार यांनी घेतला आपात्कालीन व्यवस्थापनाचा आढावा</t>
+          <t>Chandrashekhar Bawankule: 'आताच मतदार याद्या तपासा', महसूल मंत्र्यांचा काँग्रेस नेत्यांना टोला</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>https://www.jpnnews.in/2025/08/Ashish-Shelar-reviews-emergency-management.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/chandrashekhar-bawankule-demands-to-check-voter-lists-against-congress-allegations/articleshow/123356783.cms</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>TDR Scam: साडेसातशे कोटींच्या टीडीआर घोटाळ्याचा ‘आका’ कोण?</t>
+          <t>Nagpur Accident : नागपुरातील हिट अँड रन प्रकरणाचा AI तंत्रज्ञानाच्या मदतीने उलगडा राज्यातील</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/750-crore-land-tdr-scam-ac90</t>
+          <t>https://marathi.abplive.com/crime/nagpur-hit-and-run-accident-news-update-case-solved-with-the-help-of-ai-technology-first-experiment-in-the-state-driver-arrested-from-uttar-pradesh-1377914</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>मुख्यमंत्री फडणवीस यांची माहिती, राज्यात अतिवृष्टी, ८०० गावे बाधित, मुंबईत १७० एमएम पाऊस</t>
+          <t>शालार्थ घोटाळ्यातील संचालकांची मालमत्ता जप्त करा; पालकमंत्री चंद्रशेखर बावनकुळे यांचे निर्देश</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/cm-fadnavis-said-heavy-rains-in-the-state-800-villages-affected-170-mm-rain/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/seize-the-assets-of-directors-involved-in-the-school-id-scam.html</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Seize assets of school directors in Shalarth ID scam: Bawankule</t>
+          <t>बनावट शालार्थ आयडीद्वारे ४१ लाख रुपयांची शासनाची फसवणूक; दोन लिपीक बंधुंना अटक</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/seize-assets-of-school-directors-in-shalarth-id-scam-bawankule/articleshow/123371134.cms</t>
+          <t>https://www.etvbharat.com/mr/!state/fake-shalarth-id-recruitment-scam-nagpur-two-clerk-brothers-arrested-in-cheating-case-total-number-of-accused-arrested-in-reached-to-20-maharashtra-news-mhs25081800757</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Nagpur Smart City projects near closure with 7 works still pending</t>
+          <t>वरूणराजा कोपला! पिकांमध्ये पाणीच पाणी, पुढील 48 तासांत या जिल्ह्यांना पुन्हा रेड अलर्ट</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>https://infra.economictimes.indiatimes.com/news/urban-infrastructure/nagpur-smart-city-projects-face-delay-7-projects-pending-completion/123360909</t>
+          <t>https://news18marathi.com/agriculture/18-august-maharashtra-heavy-rain-update-monsoon-2025-mumbai-red-alert-1460576.html</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Heritage India: Iconic Sword of Maratha Commander Raghuji Raje Bhonsle Arrives in Mumbai</t>
+          <t>पावसाने प्रभावित शेतकऱ्यांना मिळणार मदत; पालकमंत्री चंद्रशेखर बावनकुळे यांची घोषणा</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-govt-brings-back-iconic-sword-of-maratha-commander-raghuji-raje-bhonsle-auctioned-for-rs-4715-lakh-to-mumbai-3685565</t>
+          <t>https://www.nagpurtoday.in/help-for-rain-affected-farmers-announcement-of-guardian-minister-chandrasekhar-bawankule/08181141</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Raghuji Bhonsle’s Sword To Reach Mum Today, Mudhoji Raje To Attend Ceremony</t>
+          <t>Mumbai reels under 177 mm rain in 8 hours; flights hit, schools shut as red alert issued</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/raghuji-bhonsles-sword-to-reach-mum-today-mudhoji-raje-to-attend-ceremony/articleshow/123351204.cms</t>
+          <t>https://www.newindianexpress.com/nation/2025/Aug/18/mumbai-rains-flight-operations-hit-schools-colleges-shut-as-imd-issues-red-alert</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Now, Bachchu Kadu claims offer to ‘delete thousands of names’ from voters’ list</t>
+          <t>Vice Presidential Election: सीपी राधाकृष्णन को NDA उम्मीदवार बनाने पर कांग्रेस को लगी मिर्ची, INDI गठबंधन कैंडिडेट पर खोले पत्ते</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/now-bachchu-kadu-claims-offer-to-delete-thousands-of-names-from-voters-list/articleshow/123351305.cms</t>
+          <t>https://www.republicbharat.com/india/congress-angry-cp-radhakrishnan-nda-vice-presidential-candidate-opened-cards-on-indi-alliance-meeting</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Historic sword of Raje Raghuji Bhonsle arrives in Mumbai to royal welcome</t>
+          <t>VIDEO: महाराष्ट्र में भारी बारिश के बीच एक्शन में डिप्टी CM अजित पवार, मंत्रालय के आपदा नियंत्रण</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/historic-sword-of-raje-raghuji-bhonsle-arrives-in-mumbai-to-royal-welcome/08181446</t>
+          <t>https://hindi.latestly.com/india/maharashtra-deputy-cm-ajit-pawar-visits-mantralaya-disaster-control-room-to-review-heavy-rain-situation-2732241.html</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>'Destroying constitutional institutions': Nishikant Dubey slams Rahul Gandhi as SC dismisses plea challenging 2024 Maharashtra polls</t>
+          <t>India News | 12-day Himachal Pradesh Assembly Session Opens; Opposition Seeks Adjournment on Disaster</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
+          <t>https://www.latestly.com/agency-news/india-news-12-day-himachal-pradesh-assembly-session-opens-opposition-seeks-adjournment-on-disaster-7064955.html</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>'Destroying constitutional institutions': Nishikant Dubey slams Rahul Gandhi as SC dismisses plea challenging 2024 Maharashtra polls</t>
+          <t>Vice President Election: NDA उम्मीदवार सीपी राधाकृष्णन को मिल सकता है विपक्षी दलों का समर्थन, इन पार्टियों पर सबकी नजर</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>https://www.malaysiasun.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
+          <t>https://www.jagran.com/politics/national-rajya-sabha-election-opposition-parties-may-support-nda-candidate-cp-radhakrishnan-24017212.html</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>३१ खासदार निवडून आले तेव्हा मतदारयाद्या बरोबर होत्या का ?</t>
+          <t>कौन लेगा CP राधाकृष्णन की जगह? BJP की एक खोज खत्म होते ही शुरू हुई दूसरी तलाश</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/nagpur/were-the-voter-lists-correct-when-31-mps-were-elected-a-a1000/</t>
+          <t>https://navbharatlive.com/maharashtra/maharashtra-new-governor-who-will-replace-cp-radhakrishnan-bjp-new-search-begins-1321951.html</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>'एआय' तंत्रज्ञानाचा वापर करून नागपूर ग्रामीण पोलिसांनी केली गुन्ह्याची उकल, 'हिट अँड रन' प्रकरणी आरोपी अटकेत</t>
+          <t>अब कोल्हापुर भी सुनेगा न्याय की पुकार, CJI गवई ने किया बॉम्बे हाई कोर्ट चौथी खंडपीठ का उद्घाटन</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/truck-hits-bike-husband-carried-wife-on-bike-nagpur-rural-police-arrests-accused-truck-driver-using-ai-technology-maharashtra-news-mhs25081805869</t>
+          <t>https://navbharatlive.com/maharashtra/kolhapur/cji-br-gavai-inaugurates-bombay-high-court-bench-at-kolhapur-1321186.html</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>रघुजी राजे यांची तलवार आणि ‘स्व’चा बोध</t>
+          <t>मत चोरी प्रकरण : विरोधी पक्ष मुख्य निवडणूक आयुक्तांविरुद्ध महाभियोग आणण्याच्या तयारीत</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/historic-sword-of-shrimant-raghuji-bhosle-back-in-mumbai.html</t>
+          <t>https://www.etvbharat.com/mr/!bharat/opposition-parties-likely-to-bring-impeachment-motion-notice-against-cec-over-vote-theft-maharashtra-news-mhs25081803712</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Chandrashekhar Bawankule: 'आताच मतदार याद्या तपासा', महसूल मंत्र्यांचा काँग्रेस नेत्यांना टोला</t>
+          <t>Farmers Loan Waiver: बावनकुळेंनंतर महायुती सरकारमधील 'या' मंत्र्याची कर्जमाफीबाबत मोठी अपडेट; म्हणाले,'CM फडणवीस लवकरच...'</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/chandrashekhar-bawankule-demands-to-check-voter-lists-against-congress-allegations/articleshow/123356783.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/sanjay-rathod-update-farmer-loan-waiver-devendra-fadnavis-dk88</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Teacher Recruitment Scam: बोगस शालार्थ आयडी घोटाळ्यातील संचालकांची मालमत्ता जप्त होणार !</t>
+          <t>Election Commission Of India &amp; The “Politics Of Jugaad”</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/bogus-teacher-scam-school-id-fraud-directors-property-to-be-seized-ng81</t>
+          <t>https://madrascourier.com/opinion/election-commission-of-india-the-politics-of-jugaad/</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Nagpur Accident : नागपुरातील हिट अँड रन प्रकरणाचा AI तंत्रज्ञानाच्या मदतीने उलगडा राज्यातील</t>
+          <t>'Political opinions or...': Supreme Court quashes plea challenging validity of Maharashtra Assembly polls</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/crime/nagpur-hit-and-run-accident-news-update-case-solved-with-the-help-of-ai-technology-first-experiment-in-the-state-driver-arrested-from-uttar-pradesh-1377914</t>
+          <t>https://www.deccanherald.com/india/political-opinions-or-supreme-court-quashes-plea-challenging-validity-of-maharashtra-assembly-polls-3686244</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>शालार्थ घोटाळ्यातील संचालकांची मालमत्ता जप्त करा; पालकमंत्री चंद्रशेखर बावनकुळे यांचे निर्देश</t>
+          <t>Fadnavis meets Guv Radhakrishnan, presents him book of Shivaji Maharaj's letters</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/seize-the-assets-of-directors-involved-in-the-school-id-scam.html</t>
+          <t>https://www.ptinews.com/detail/national/Fadnavis-meets-Guv-Radhakrishnan--presents-him-book-of-Shivaji-Maharaj-s-letters/2832581</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Sambhajinagar News : आता शहरवासीयांना मिळणार अतिरिक्त २६ एमएलडी पाणी</t>
+          <t>Shiv Sena, NCP support Maha Governor’s nomination for Vice President</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>https://pudhari.news/amp/story/maharashtra/marathwada/chhatrapati-sambhajinagar/now-city-residents-will-get-additional-26-mld-of-water-np88</t>
+          <t>https://morungexpress.com/shiv-sena-ncp-support-maha-governors-nomination-for-vice-president</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>वरूणराजा कोपला! पिकांमध्ये पाणीच पाणी, पुढील 48 तासांत या जिल्ह्यांना पुन्हा रेड अलर्ट</t>
+          <t>Rajnath reaches out to DMK, TMC, BJD for consensus on VP nominee</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/agriculture/18-august-maharashtra-heavy-rain-update-monsoon-2025-mumbai-red-alert-1460576.html</t>
+          <t>https://www.msn.com/en-in/news/other/rajnath-reaches-out-to-dmk-tmc-bjd-for-consensus-on-vp-nominee/ar-AA1KKGcl</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>kolhapur | सर्किट बेंचचे स्वप्न साकारले; न्यायाचे दरवाजे खुले झाले!</t>
+          <t>सीपी राधाकृष्णन के उपराष्ट्रपति उम्मीदवार बनाने पर कांग्रेस को लगी मिर्ची; INDI ब्लॉक भी जल्द कर सकता है प्रत्याशी का ऐलान</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>https://pudhari.news/amp/story/maharashtra/kolhapur/circuit-bench-dream-realized-doors-of-justice-now-open-ap84</t>
+          <t>https://www.sudarshannews.in/news-detail.aspx?id=131383</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Mumbai reels under 177 mm rain in 8 hours; flights hit, schools shut as red alert issued</t>
+          <t>शिवसेना एकनाथ शिंदे गुट को बड़ा झटका, शिवाजी सावंत भाजपा में होगें शामिल | Maharastra - Paliwalwani - Latest Hindi News</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Aug/18/mumbai-rains-flight-operations-hit-schools-colleges-shut-as-imd-issues-red-alert</t>
+          <t>https://paliwalwani.com/maharastra/shiv-sena-eknath-shinde-faction-is-a-big-shock-shivaji-sawant-will-be-involved-in-bjp</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Vice Presidential Election: सीपी राधाकृष्णन को NDA उम्मीदवार बनाने पर कांग्रेस को लगी मिर्ची, INDI गठबंधन कैंडिडेट पर खोले पत्ते</t>
+          <t>चुनाव आयोग की प्रेस कॉन्फ्रेंस में इन दो पत्रकारों के सवालों ने बोलती बंद कर दी, देखें वीडियो – No. 1 Indian Media News Portal</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>https://www.republicbharat.com/india/congress-angry-cp-radhakrishnan-nda-vice-presidential-candidate-opened-cards-on-indi-alliance-meeting</t>
+          <t>https://www.bhadas4media.com/eci-press-confrence-journalist-question/</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>VIDEO: महाराष्ट्र में भारी बारिश के बीच एक्शन में डिप्टी CM अजित पवार, मंत्रालय के आपदा नियंत्रण</t>
+          <t>अभी जांच लें वोटर लिस्ट, बाद में दोष न दें, बावनकुले का कांग्रेस को आह्वान, कहा- वोट बढ़ने का मतलब..</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>https://hindi.latestly.com/india/maharashtra-deputy-cm-ajit-pawar-visits-mantralaya-disaster-control-room-to-review-heavy-rain-situation-2732241.html</t>
+          <t>https://navbharatlive.com/maharashtra/nagpur/check-voter-list-now-revenue-minister-chandrashekhar-bawankule-appeal-congress-1321254.html</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>India News | 12-day Himachal Pradesh Assembly Session Opens; Opposition Seeks Adjournment on Disaster</t>
+          <t>उपराष्ट्रपतीपदाचे उमेदवार राधाकृष्णन यांना पाठिंबा द्या; देवेंद्र फडणवीस यांची शरद पवार आणि उद्धव ठाकरे यांना साद</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/india-news-12-day-himachal-pradesh-assembly-session-opens-opposition-seeks-adjournment-on-disaster-7064955.html</t>
+          <t>https://marathi.freepressjournal.in/maharashtra/cp-radhakrishnan-vice-president-candidate-fadnavis-appeal-pawar-thackeray</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Vice President Election: NDA उम्मीदवार सीपी राधाकृष्णन को मिल सकता है विपक्षी दलों का समर्थन, इन पार्टियों पर सबकी नजर</t>
+          <t>राहुल गांधी पक्ष टिकवण्यासाठी निवडणूक आयोगाचा आधार घेतात; मंत्री चंद्रशेखर बावनकुळे यांची टीका</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/politics/national-rajya-sabha-election-opposition-parties-may-support-nda-candidate-cp-radhakrishnan-24017212.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/rahul-gandhi-takes-support-from-election-commission-to-save-party-minister-chandrashekhar-bawankule-criticizes.html</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>महाराष्ट्र की ‘अस्मिता’ की बात करने वाले उपराष्ट्रपति पद के लिए राधाकृष्णन का समर्थन करें : फडणवीस</t>
+          <t>बेस्ट पतपेढी कोणाच्या ताब्यात? आज मतदान, उद्या फैसला! ठाकरे बंधूंच्या युतीची पहिली कसोटी Mumbai Marathi News | BEST Patpedhi elections today uddhav thackeray raj thackery alliance on the line | Latest Mumbai News at</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/support-radhakrishnan-for-the-post-of-vice-president-who-talks-about-maharashtras-identity-fadnavis/856729/</t>
+          <t>https://www.lokmat.com/shorts/mumbai/best-credit-society-election-thackeray-brothers-unite-vs-bjp-results-tomorrow/</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>कौन लेगा CP राधाकृष्णन की जगह? BJP की एक खोज खत्म होते ही शुरू हुई दूसरी तलाश</t>
+          <t>Pravin Darekar: राज्य सहकारी संघाच्या अध्यक्षपदी आमदार प्रवीण दरेकर</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/maharashtra-new-governor-who-will-replace-cp-radhakrishnan-bjp-new-search-begins-1321951.html</t>
+          <t>https://pudhari.news/maharashtra/pune/pravin-darekar-elected-cooperative-president-maharashtra-ac90</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>अब कोल्हापुर भी सुनेगा न्याय की पुकार, CJI गवई ने किया बॉम्बे हाई कोर्ट चौथी खंडपीठ का उद्घाटन</t>
+          <t>संवैधानिक पदाच्या निवडणुका बिनविरोध व्हाव्यात-संजय राऊत</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/kolhapur/cji-br-gavai-inaugurates-bombay-high-court-bench-at-kolhapur-1321186.html</t>
+          <t>https://www.etvbharat.com/mr/!bharat/vice-president-election-2025-sanjay-raut-says-elections-to-constitutional-posts-should-be-unopposed-maharashtra-news-mhs25081801506</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>मत चोरी प्रकरण : विरोधी पक्ष मुख्य निवडणूक आयुक्तांविरुद्ध महाभियोग आणण्याच्या तयारीत</t>
+          <t>१९८७च्या काश्मीर निवडणूक गैरप्रकाराचा काँग्रेसला विसर - राजीव गांधींकडून विरोधकांच्या आरोपांकडे दुर्लक्ष</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!bharat/opposition-parties-likely-to-bring-impeachment-motion-notice-against-cec-over-vote-theft-maharashtra-news-mhs25081803712</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/congress-forgets-1987-kashmir-election-malpractices-rajiv-gandhi-ignores-opposition-allegations.html</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Election Commission Of India &amp; The “Politics Of Jugaad”</t>
+          <t>महाराष्ट्र कंगाल, पण मंत्री परदेशात; संजय राऊत कडाडले</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>https://madrascourier.com/opinion/election-commission-of-india-the-politics-of-jugaad/</t>
+          <t>https://www.etvbharat.com/mr/!bharat/maharashtra-is-poor-but-ministers-are-abroad-sanjay-raut-lashed-out-maharashtra-news-mhs25081801861</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>CP Radhakrishnan vs who? Why DMK’s pushing INDIA bloc for a Tamil vs Tamil contest for India’s V-P</t>
+          <t>हवामानाचा अंदाज: आजही पावसाचा कहर? मुंबई, पुण्यासह 7 जिल्ह्यांना रेड अलर्ट; गडचिरोलीसह 4 जिल्ह्यांना यलो अलर्ट</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/cp-radhakrishnan-vs-who-why-dmks-pushing-india-bloc-for-a-tamil-vs-tamil-contest-for-indias-v-p/2723136/</t>
+          <t>https://thefocusindia.com/national-news/maharashtra-weather-red-alert-mumbai-pune-7-districts-281414/</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>'Political opinions or...': Supreme Court quashes plea challenging validity of Maharashtra Assembly polls</t>
+          <t>Girish Mahajan Chagan Bhujbal Clash Nashik Minister Post नाशिकच्या पालकमंत्रिपदावर गिरीश महाजनांचा दावा</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/political-opinions-or-supreme-court-quashes-plea-challenging-validity-of-maharashtra-assembly-polls-3686244</t>
+          <t>https://thefocusindia.com/maharashtra-news/girish-mahajan-chagan-bhujbal-clash-nashik-guardian-minister-281360/amp/</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Fadnavis meets Guv Radhakrishnan, presents him book of Shivaji Maharaj's letters</t>
+          <t>Potholes Persist, Rekha Orders Fresh Campaign</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/national/Fadnavis-meets-Guv-Radhakrishnan--presents-him-book-of-Shivaji-Maharaj-s-letters/2832581</t>
+          <t>https://timesofindia.indiatimes.com/city/delhi/potholes-persist-rekha-orders-fresh-campaign/articleshow/123349516.cms</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Shiv Sena, NCP support Maha Governor’s nomination for Vice President</t>
+          <t>Cong calls Bhind rally over police ‘assault’ on journalists</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>https://morungexpress.com/shiv-sena-ncp-support-maha-governors-nomination-for-vice-president</t>
+          <t>https://timesofindia.indiatimes.com/city/bhopal/cong-calls-bhind-rally-over-police-assault-on-journalists/articleshow/123350977.cms</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>NDA's VP Candidate CP Radhakrishnan Heads to Delhi Amid Criticism</t>
+          <t>Mumbai: Iconic Sword of Raghuji Bhonsle Arrives from London; Bike Rally Cancelled Due to Rains, Grand...</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3545060-ndas-vp-candidate-cp-radhakrishnan-heads-to-delhi-amid-criticism</t>
+          <t>https://www.lokmattimes.com/mumbai/mumbai-iconic-sword-of-raghuji-bhonsle-arrives-from-london-bike-rally-cancelled-due-to-rains-grand-inauguration-tonight-a525/</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>सीपी राधाकृष्णन के उपराष्ट्रपति उम्मीदवार बनाने पर कांग्रेस को लगी मिर्ची; INDI ब्लॉक भी जल्द कर सकता है प्रत्याशी का ऐलान</t>
+          <t>Historic Sword Of Raje Raghuji Bhonsle To Arrive In Mumbai On August 18</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>https://www.sudarshannews.in/news-detail.aspx?id=131383</t>
+          <t>https://www.freepressjournal.in/mumbai/historic-sword-of-raje-raghuji-bhonsle-to-arrive-in-mumbai-on-august-18</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>शिवसेना एकनाथ शिंदे गुट को बड़ा झटका, शिवाजी सावंत भाजपा में होगें शामिल | Maharastra - Paliwalwani - Latest Hindi News</t>
+          <t>Breaking News Highlights Updates: Ukrainian President Zelenskyy hails 'historic' US decision to offer sec...</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>https://paliwalwani.com/maharastra/shiv-sena-eknath-shinde-faction-is-a-big-shock-shivaji-sawant-will-be-involved-in-bjp</t>
+          <t>https://m.economictimes.com/news/newsblogs/india-news-live-updates-17-august-2025-earthquake-sikkim-rain-weather-mumbai-delhi-pm-modi-trump-putin-russia-israel-gaza-ukraine/liveblog/123340718.cms</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>चुनाव आयोग की प्रेस कॉन्फ्रेंस में इन दो पत्रकारों के सवालों ने बोलती बंद कर दी, देखें वीडियो – No. 1 Indian Media News Portal</t>
+          <t>CP Radhakrishnan: A Swayamsevak, Grassroots BJP Organiser, Former MP, Governor - Now NDA’s Pick For Vice</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>https://www.bhadas4media.com/eci-press-confrence-journalist-question/</t>
+          <t>https://thecommunemag.com/cp-radhakrishnan-grassroots-bjp-organiser-former-mp-governor-now-ndas-pick-for-vice-president/</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>अभी जांच लें वोटर लिस्ट, बाद में दोष न दें, बावनकुले का कांग्रेस को आह्वान, कहा- वोट बढ़ने का मतलब..</t>
+          <t>पश्चिम महाराष्ट्रात शिंदेंना भाजपचा धक्का, आमदाराच्या भावासह ४० पदाधिकाऱ्यांचा शिवसेनेला जय महाराष्ट्र!</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/nagpur/check-voter-list-now-revenue-minister-chandrashekhar-bawankule-appeal-congress-1321254.html</t>
+          <t>https://saamtv.esakal.com/maharashtra/solapur-political-news-bjp-strengthens-in-solapur-as-40-sena-leaders-join-with-shivaji-sawant-bdk97</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>उपराष्ट्रपतीपदाचे उमेदवार राधाकृष्णन यांना पाठिंबा द्या; देवेंद्र फडणवीस यांची शरद पवार आणि उद्धव ठाकरे यांना साद</t>
+          <t>सोलापूरच्या राजकारणात मोठी खळबळ; तानाजी सावंत यांचा भाऊ करणार भाजपात प्रवेश</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/maharashtra/cp-radhakrishnan-vice-president-candidate-fadnavis-appeal-pawar-thackeray</t>
+          <t>https://www.timemaharashtra.com/politics/big-stir-in-solapur-politics-tanaji-sawants-brother-to-join-bjp/129377/</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>राहुल गांधी पक्ष टिकवण्यासाठी निवडणूक आयोगाचा आधार घेतात; मंत्री चंद्रशेखर बावनकुळे यांची टीका</t>
+          <t>Rohit Pawar on Sanjay Shirsath: रोहित पवारांचे मंत्री संजय शिरसाटांवर भ्रष्टाचाराचे गंभीर आरोप; पहा काय म्हणाले</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/rahul-gandhi-takes-support-from-election-commission-to-save-party-minister-chandrashekhar-bawankule-criticizes.html</t>
+          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/amp</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Pravin Darekar: राज्य सहकारी संघाच्या अध्यक्षपदी आमदार प्रवीण दरेकर</t>
+          <t>Rohit Pawar: मंत्री संजय शिरसाटांनी केला ५ हजार कोटींचा घोटाळा; आमदार रोहित पवारांच्या आरोपाने खळबळ</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/pravin-darekar-elected-cooperative-president-maharashtra-ac90</t>
+          <t>https://deshdoot.com/rohit-pawar-alleges-sanjay-shirsat-over-5000-crore-worth-land-to-bivalkar-family/</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>संवैधानिक पदाच्या निवडणुका बिनविरोध व्हाव्यात-संजय राऊत</t>
+          <t>Shivsena | नाराजी भोवली! शिंदे गटातून बड्या नेत्याचा राजीनामा, राजकीय वर्तुळात खळबळ</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!bharat/vice-president-election-2025-sanjay-raut-says-elections-to-constitutional-posts-should-be-unopposed-maharashtra-news-mhs25081801506</t>
+          <t>https://www.thodkyaat.com/big-setback-for-eknath-shinde-faction-as-senior-leader-shivaji-sawant-joins-bjp-ahead-of-local-body-polls/</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>१९८७च्या काश्मीर निवडणूक गैरप्रकाराचा काँग्रेसला विसर - राजीव गांधींकडून विरोधकांच्या आरोपांकडे दुर्लक्ष</t>
+          <t>शिंदे गटाचे आमदार तानाजी सावंतांचे बंधू भाजपच्या वाटेवर</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/congress-forgets-1987-kashmir-election-malpractices-rajiv-gandhi-ignores-opposition-allegations.html</t>
+          <t>https://pcbtoday.in/%E0%A4%B6%E0%A4%BF%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%97%E0%A4%9F%E0%A4%BE%E0%A4%9A%E0%A5%87-%E0%A4%86%E0%A4%AE%E0%A4%A6%E0%A4%BE%E0%A4%B0-%E0%A4%A4%E0%A4%BE%E0%A4%A8%E0%A4%BE%E0%A4%9C%E0%A5%80/</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>महाराष्ट्र कंगाल, पण मंत्री परदेशात; संजय राऊत कडाडले</t>
+          <t>Rohit Pawar on Sanjay Shirsath: रोहित पवारांचे मंत्री संजय शिरसाटांवर भ्रष्टाचाराचे गंभीर आरोप; पहा काय म्हणाले</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!bharat/maharashtra-is-poor-but-ministers-are-abroad-sanjay-raut-lashed-out-maharashtra-news-mhs25081801861</t>
+          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>हवामानाचा अंदाज: आजही पावसाचा कहर? मुंबई, पुण्यासह 7 जिल्ह्यांना रेड अलर्ट; गडचिरोलीसह 4 जिल्ह्यांना यलो अलर्ट</t>
+          <t>Ekanath Shinde Shivsena : शिंदे गटाला धक्का; आमदाराचा भाऊ व 40 पदाधिकाऱ्यांचा पक्षप्रवेश</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/national-news/maharashtra-weather-red-alert-mumbai-pune-7-districts-281414/</t>
+          <t>https://www.lokshahi.com/news/mla-tanaji-sawants-brother-shivaji-sawant-has-decided-to-quit-the-group-and-join-the-bjp</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Girish Mahajan Chagan Bhujbal Clash Nashik Minister Post नाशिकच्या पालकमंत्रिपदावर गिरीश महाजनांचा दावा</t>
+          <t>Kokan Politics : शरद पवार गटाला धक्का; प्रदेश सरचिटणीस प्रशांत यादव भाजपाच्या वाटेवर</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/girish-mahajan-chagan-bhujbal-clash-nashik-guardian-minister-281360/amp/</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/kokan-politics-sharad-pawar-group-suffers-setback-state-general-secretary-prashant-yadav-on-bjps-path/</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Potholes Persist, Rekha Orders Fresh Campaign</t>
+          <t>MSRTC और पुलिस की पहल, गढ़चिरौली के आदिवासी गांव को मिला पहला सार्वजनिक परिवहन, ग्रामीणों ने लहराया तिरंगा</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/delhi/potholes-persist-rekha-orders-fresh-campaign/articleshow/123349516.cms</t>
+          <t>https://hindi.mid-day.com/news/india-news/photo/initiative-of-msrtc-and-police-tribal-village-of-gadchiroli-gets-first-public-transport-1558</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Cong calls Bhind rally over police ‘assault’ on journalists</t>
+          <t>Sanjay Raut : निसाकाचा संघर्ष उफाळला, अनिल कदमांनी साकडं घातलं आता संजय राऊत मैदानात</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/bhopal/cong-calls-bhind-rally-over-police-assault-on-journalists/articleshow/123350977.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/niphad-sugar-factory-crisis-sanjay-raut-anil-kadam-memorandum-farmers-workers-protest-nashik-gs97</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Mumbai: Iconic Sword of Raghuji Bhonsle Arrives from London; Bike Rally Cancelled Due to Rains, Grand...</t>
+          <t>मुंबई : चीरा बाज़ार में टल गया बड़ा हादसा; दो मंजिला पुरानी इमारत की सीढ़ियां अचानक ढह गईं</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/mumbai/mumbai-iconic-sword-of-raghuji-bhonsle-arrives-from-london-bike-rally-cancelled-due-to-rains-grand-inauguration-tonight-a525/</t>
+          <t>https://www.rokthoklekhani.com/article/43138/mumbai--a-major-accident-was-averted-in-chira-bazaar--stairs-of-a-two-storey-old-building-suddenly-collapsed</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Historic Sword Of Raje Raghuji Bhonsle To Arrive In Mumbai On August 18</t>
+          <t>मुंबई : गणेश भक्तों का उत्साह चरम पर, मुंबई की बारिश हुई बेअसर</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/historic-sword-of-raje-raghuji-bhonsle-to-arrive-in-mumbai-on-august-18</t>
+          <t>https://www.rokthoklekhani.com/article/43136/mumbai--enthusiasm-of-ganesh-devotees-is-at-its-peak--mumbai-s-rain-has-no-effect</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Breaking News Highlights Updates: Ukrainian President Zelenskyy hails 'historic' US decision to offer sec...</t>
+          <t>मुंबई : 20 अगस्त तक भारी बारिश; मौसम विज्ञान विभाग ने जारी किया ऑरेंज अलर्ट</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/newsblogs/india-news-live-updates-17-august-2025-earthquake-sikkim-rain-weather-mumbai-delhi-pm-modi-trump-putin-russia-israel-gaza-ukraine/liveblog/123340718.cms</t>
+          <t>https://www.rokthoklekhani.com/article/43134/mumbai--heavy-rains-till-august-20--meteorological-department-issued-orange-alert</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>CP Radhakrishnan: A Swayamsevak, Grassroots BJP Organiser, Former MP, Governor - Now NDA’s Pick For Vice</t>
+          <t>जे.जे अस्पताल से फरार बांग्लादेशी महिला आरोपी मुंबई पुलिस के हत्थे चढ़ी</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>https://thecommunemag.com/cp-radhakrishnan-grassroots-bjp-organiser-former-mp-governor-now-ndas-pick-for-vice-president/</t>
+          <t>https://www.rokthoklekhani.com/article/43150/bangladeshi-woman-accused-who-escaped-from-jj-hospital-arrested-by-mumbai-police</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>राजधानीत पावसाचा कहर! मुंबई विद्यापीठाचा परीक्षांबाबत तडकाफडकी मोठा निर्णय!</t>
+          <t>उपराष्ट्रपतीपदाचे एनडीए उमेदवार सीपी राधाकृष्णन यांच्यावर राजकीय पक्षांच्या प्रतिक्रिया</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/mumbai-university-postponed-its-all-exam-to-be-held-on-19-august-due-to-heavy-rain-marathi-news-1472932.html</t>
+          <t>https://www.dainikprabhat.com/parties-reaction-to-nda-vice-presidential-candidate-cp-radhakrishnan/</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>पश्चिम महाराष्ट्रात शिंदेंना भाजपचा धक्का, आमदाराच्या भावासह ४० पदाधिकाऱ्यांचा शिवसेनेला जय महाराष्ट्र!</t>
+          <t>22-kg Golden Kalash Installed at Sant Dnyaneshwar Temple, Crafted by Shripad Shankar Nagarkar Jewellers Pune</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/solapur-political-news-bjp-strengthens-in-solapur-as-40-sena-leaders-join-with-shivaji-sawant-bdk97</t>
+          <t>https://aninews.in/news/business/22-kg-golden-kalash-installed-at-sant-dnyaneshwar-temple-crafted-by-shripad-shankar-nagarkar-jewellers-pune20250819111423</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>सोलापुरात भाजपची शिंदेंच्या शिवसेनावर कुरघोडी शिवाजी सावंतांनी शिवसेना सोडली,</t>
+          <t>Mumbai: 45-Year-Old Police Constable Dies By Suicide In Andheri, Cites Illness &amp; Family Issues</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/solapur-shivaji-sawant-leaves-shiv-sena-and-bjp-entry-confirmed-devendra-fadnavis-bjp-attack-on-eknath-shinde-shiv-sena-in-solapur-1377928</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-45-year-old-police-constable-dies-by-suicide-in-andheri-cites-illness-family-issues</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>सोलापूरच्या राजकारणात मोठी खळबळ; तानाजी सावंत यांचा भाऊ करणार भाजपात प्रवेश</t>
+          <t>Demand to release list of property-holders affected due to road-widening in 5 days</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/big-stir-in-solapur-politics-tanaji-sawants-brother-to-join-bjp/129377/</t>
+          <t>https://www.lokmattimes.com/aurangabad/demand-to-release-list-of-property-holders-affected-due-to-road-widening-in-5-days/</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Rohit Pawar on Sanjay Shirsath: रोहित पवारांचे मंत्री संजय शिरसाटांवर भ्रष्टाचाराचे गंभीर आरोप; पहा काय म्हणाले</t>
+          <t>'ऑपरेशन लोटस वगैरे काही नाही; लवकरच ऑपरेशन टायगर दिसेल', सोलापूरच्या राजकारणात पडद्यामागे काय घडतंय?</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/amp</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%B2-%E0%A4%9F%E0%A4%B8-%E0%A4%B5%E0%A4%97%E0%A5%88%E0%A4%B0%E0%A5%87-%E0%A4%95-%E0%A4%B9-%E0%A4%A8-%E0%A4%B9-%E0%A4%B2%E0%A4%B5%E0%A4%95%E0%A4%B0%E0%A4%9A-%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%9F-%E0%A4%AF%E0%A4%97%E0%A4%B0-%E0%A4%A6-%E0%A4%B8%E0%A5%87%E0%A4%B2-%E0%A4%B8-%E0%A4%B2-%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B0-%E0%A4%9C%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A4-%E0%A4%AA%E0%A4%A1%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%AE-%E0%A4%97%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%98%E0%A4%A1%E0%A4%A4%E0%A4%82%E0%A4%AF/ar-AA1KKoUc</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Rohit Pawar: मंत्री संजय शिरसाटांनी केला ५ हजार कोटींचा घोटाळा; आमदार रोहित पवारांच्या आरोपाने खळबळ</t>
+          <t>Cabinet sends back note regarding GMR with multiple queries</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/rohit-pawar-alleges-sanjay-shirsat-over-5000-crore-worth-land-to-bivalkar-family/</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/18/cabinet-sends-back-note-regarding-gmr-with-multiple-queries.html</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Shivsena | नाराजी भोवली! शिंदे गटातून बड्या नेत्याचा राजीनामा, राजकीय वर्तुळात खळबळ</t>
+          <t>Maharashtra rain fury: Seven dead, crops damaged; Mumbai, Thane, other districts on red alert</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>https://www.thodkyaat.com/big-setback-for-eknath-shinde-faction-as-senior-leader-shivaji-sawant-joins-bjp-ahead-of-local-body-polls/</t>
+          <t>https://www.newindianexpress.com/nation/2025/Aug/18/maharashtra-rain-fury-seven-dead-crops-damaged-mumbai-thane-other-districts-on-red-alert</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Rohit Pawar on Sanjay Shirsath: रोहित पवारांचे मंत्री संजय शिरसाटांवर भ्रष्टाचाराचे गंभीर आरोप; पहा काय म्हणाले</t>
+          <t>Maha govt signs MoUs worth Rs 42,000 crore and creation of 28,000 jobs</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/</t>
+          <t>https://www.thehawk.in/news/states-and-uts/maharashtra/maha-govt-signs-mous-worth-rs-42000-crore-and-creation-of-28000-jobs</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Ekanath Shinde Shivsena : शिंदे गटाला धक्का; आमदाराचा भाऊ व 40 पदाधिकाऱ्यांचा पक्षप्रवेश</t>
+          <t>Maha govt waives Stamp Duty worth Rs 38.99 lakh for Tata Cancer Hospital in Raigad (Ld)</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>https://www.lokshahi.com/news/mla-tanaji-sawants-brother-shivaji-sawant-has-decided-to-quit-the-group-and-join-the-bjp</t>
+          <t>https://www.thehawk.in/news/india/maha-govt-waives-stamp-duty-worth-rs-3899-lakh-for-tata-cancer-hospital-in-raigad-ld</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>NCP demands : राज्यात ओला दुष्काळ जाहीर करा अन्…; राष्ट्रवादी शरद पवार गटाची मागणी</t>
+          <t>शाहू महाराज की तरह करना होगा न्याय, कोल्हापुर में HC की नई सर्किट बेंच के उद्घाटन पर बोले CJI गवई</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/heavy-rains-wreak-havoc-in-maharashtra-sharad-pawar-ncp-demands-wet-drought-declaration-and-farmer-relief/</t>
+          <t>https://www.tv9hindi.com/state/maharashtra/cji-inaugurated-new-circuit-bench-said-a-big-thing-about-maharashtra-government-3441714.html</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>शिंदे गटाचे आमदार तानाजी सावंतांचे बंधू भाजपच्या वाटेवर</t>
+          <t>महाराष्ट्र में भारी बारिश से सात लोगों की मौत, 200 ग्रामीण फंसे</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>https://pcbtoday.in/%E0%A4%B6%E0%A4%BF%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%97%E0%A4%9F%E0%A4%BE%E0%A4%9A%E0%A5%87-%E0%A4%86%E0%A4%AE%E0%A4%A6%E0%A4%BE%E0%A4%B0-%E0%A4%A4%E0%A4%BE%E0%A4%A8%E0%A4%BE%E0%A4%9C%E0%A5%80/</t>
+          <t>https://hindi.theprint.in/india/seven-people-died-due-to-heavy-rains-in-maharashtra-200-villagers-stranded/856903/</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Kokan Politics : शरद पवार गटाला धक्का; प्रदेश सरचिटणीस प्रशांत यादव भाजपाच्या वाटेवर</t>
+          <t>महाराष्ट्र में मानसून का कहर: मुखेड तालुका में बादल फटने जैसी घटना, 200 से ज्यादा गांवों में बाढ़</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/kokan-politics-sharad-pawar-group-suffers-setback-state-general-secretary-prashant-yadav-on-bjps-path/</t>
+          <t>https://hindi.dynamitenews.com/maharashtra/cloudburst-in-mukhed-taluka-in-maharashtra-flood-in-more-than-200-villages</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Mumbai receives over 200 mm rainfall in 24 hours</t>
+          <t>मराठा सेनापति रघुजी भोंसले की तलवार मुंबई पहुंची</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>https://thefederal.com/category/states/west/maharashtra/mumbai-receives-over-200-mm-rainfall-in-24-hours-202405</t>
+          <t>https://www.livehindustan.com/ncr/new-delhi/story-historic-sword-of-maratha-general-raghuji-bhosale-i-repatriated-to-mumbai-201755537654676.html</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>मुंबई में आज शाम हाई टाइड, लोगों से सावधानी की अपील, भारी बारिश का लोकल ट्रेनों</t>
+          <t>महाराष्ट्र में माफ हो सकते हैं पुराने ट्रैफिक चालान, माफी योजना लाने की तैयारी में सरकार</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/photo-gallery/states/maharashtra-mumbai-heavy-rainfall-waterlogging-imd-red-alert-local-train-delayed-photos-maharashtra-news-2997487</t>
+          <t>https://navbharattimes.indiatimes.com/government-schemes/others/maharashtra-government-is-set-to-roll-out-an-amnesty-scheme-for-one-time-settlement-of-pending-traffic-challan/articleshow/123367444.cms</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>What happened in the Trump-Putin meeting? | Chandrashekhar Nene Maha MTB</t>
+          <t>राज्यातील पूरस्थितीवर सरकारचे लक्ष, मदत कार्य सुरू – बावनकुळे</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/what-happened-in-the-trump-putin-meeting-chandrashekhar-nene-maha-mtb.html</t>
+          <t>https://www.loksatta.com/nagpur/governments-attention-on-flood-situation-in-the-state-information-from-chandrashekhar-bawankule-amy-95-5313292/</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Sanjay Raut : निसाकाचा संघर्ष उफाळला, अनिल कदमांनी साकडं घातलं आता संजय राऊत मैदानात</t>
+          <t>‘पीएम आवास’च्या तीस लाख घरांना मोफत वीज; राज्य सरकार देणार ५० हजारांचे अनुदान: मुख्यमंत्री</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/niphad-sugar-factory-crisis-sanjay-raut-anil-kadam-memorandum-farmers-workers-protest-nashik-gs97</t>
+          <t>https://www.lokmat.com/maharashtra/free-electricity-to-three-lakh-houses-of-pm-awas-yojana-state-government-will-provide-subsidy-of-rs-50-thousand-chief-minister-a-a747/</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>संघशताब्दी म्हणजे सिंहावलोकन आणि भविष्यवेधाचा काळ – सरसंघचालक डॉ. मोहनजी भागवत</t>
+          <t>Maharashtra Government: शेतकऱ्यांना मिळणार गुड न्यूज: बळीराजासाठी सरकार मोठा निर्णय घेण्याच्या तयारीत</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/sangh-centenary-is-a-time-of-review-and-foresight-sarsanghchalak-dr-mohanji-bhagwat.html</t>
+          <t>https://saamtv.esakal.com/maharashtra/sanjay-rathod-big-statement-on-loan-waiver-maharashtra-farmers-get-loan-waiver-minister-give-hint-in-award-ceremony-program-yavatmal-pusad-bbj88</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>मुंबई : 20 अगस्त तक भारी बारिश; मौसम विज्ञान विभाग ने जारी किया ऑरेंज अलर्ट</t>
+          <t>Crop Loss: महाराष्‍ट्र में बारिश ने किया किसानों को बर्बाद, विदर्भ से लेकर मराठवाड़ा तक फसलें चौपट</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>https://www.rokthoklekhani.com/article/43134/mumbai--heavy-rains-till-august-20--meteorological-department-issued-orange-alert</t>
+          <t>https://www.kisantak.in/crops/story/heavy-rains-in-maharashtra-cause-huge-damage-to-farmers-after-crop-loss-and-land-submerged-in-water-1263471-2025-08-19</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>उपराष्ट्रपतीपदाचे एनडीए उमेदवार सीपी राधाकृष्णन यांच्यावर राजकीय पक्षांच्या प्रतिक्रिया</t>
+          <t>कोल्हापुर में शुरू हुई बॉम्बे हाईकोर्ट की नई खंडपीठ, सीजेआई बोले– महाराष्ट्र न्यायिक ढांचे में आगे</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/parties-reaction-to-nda-vice-presidential-candidate-cp-radhakrishnan/</t>
+          <t>https://mpbreakingnews.in/maharashtra/bombay-high-court-kolhapur-bench-cji-b-r-gavai-maharashtra-government-54-803927</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>22-kg Golden Kalash Installed at Sant Dnyaneshwar Temple, Crafted by Shripad Shankar Nagarkar Jewellers Pune</t>
+          <t>Sharad Pawar | शासन विमानतळ करणारच ; तर मोबदलासाठी आग्रह धरा – शरद पवार</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/press-release/22-kg-golden-kalash-installed-at-sant-dnyaneshwar-temple,-crafted-by-shripad-shankar-nagarkar-jewellers-pune/2835628</t>
+          <t>https://www.dainikprabhat.com/sharad-pawar-government-will-build-airport-so-insist-on-compensation-sharad-pawar/</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Demand to release list of property-holders affected due to road-widening in 5 days</t>
+          <t>MMRDA launches SCLR bridge, metro institute and flyovers to ease city commute</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/aurangabad/demand-to-release-list-of-property-holders-affected-due-to-road-widening-in-5-days/</t>
+          <t>https://propnewstime.com/getdetailsStories/MjA1NTQ=/mmrda-launches-sclr-bridge-metro-institute-and-flyovers-to-ease-city-commute</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Sanjay Shirsat : मंत्री शिरसाट यांच्यावर ५ हजार कोटींच्या जमीन घोटाळ्याचा आरोप</t>
+          <t>Maharashtra, Singapore Review Progress of Mega Container Port Project</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/minister-shirsat-accused-of-rs-5000-crore-land-scam-np88</t>
+          <t>https://www.constructionworld.in/transport-infrastructure/ports-and-shipping/maharashtra--singapore-review-progress-of-mega-container-port-project/77682</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>'ऑपरेशन लोटस वगैरे काही नाही; लवकरच ऑपरेशन टायगर दिसेल', सोलापूरच्या राजकारणात पडद्यामागे काय घडतंय?</t>
+          <t>मुंबई झोपडपट्टीमुक्त होणार का? जलद पुनर्विकासाचा मुख्यमंत्र्यांनी काय सांगितला प्लॅन?</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%B2-%E0%A4%9F%E0%A4%B8-%E0%A4%B5%E0%A4%97%E0%A5%88%E0%A4%B0%E0%A5%87-%E0%A4%95-%E0%A4%B9-%E0%A4%A8-%E0%A4%B9-%E0%A4%B2%E0%A4%B5%E0%A4%95%E0%A4%B0%E0%A4%9A-%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%9F-%E0%A4%AF%E0%A4%97%E0%A4%B0-%E0%A4%A6-%E0%A4%B8%E0%A5%87%E0%A4%B2-%E0%A4%B8-%E0%A4%B2-%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B0-%E0%A4%9C%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A4-%E0%A4%AA%E0%A4%A1%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%AE-%E0%A4%97%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%98%E0%A4%A1%E0%A4%A4%E0%A4%82%E0%A4%AF/ar-AA1KKoUc</t>
+          <t>https://www.tendernama.com/mahatender/mumbai/will-mumbai-become-slum-free-what-is-the-chief-ministers-plan-for-rapid-redevelopment</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Mumbai Rain Mayhem: City Comes To Standstill As Life Thrown Out Of Gear; MonoRail Gets Stuck</t>
+          <t>Mumbai Local Train: मुंबईतील लोकल प्रवाशांना मोठा दिलासा! एमआरव्हीसीकडून 15,000 कोटींचा नवा प्रकल्पाचा प्रस्ताव</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!state/mumbai-rains-update-august-19-govt-semi-govt-offices-shut-bmc-urges-wfh-for-pvt-employees-enn25081901231</t>
+          <t>https://www.msn.com/mr-in/news/other/mumbai-local-train-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%A4-%E0%A4%B2-%E0%A4%B2-%E0%A4%95%E0%A4%B2-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%B6-%E0%A4%82%E0%A4%A8-%E0%A4%AE-%E0%A4%A0-%E0%A4%A6-%E0%A4%B2-%E0%A4%B8-%E0%A4%8F%E0%A4%AE%E0%A4%86%E0%A4%B0%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%B8-%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-15-000-%E0%A4%95-%E0%A4%9F-%E0%A4%82%E0%A4%9A-%E0%A4%A8%E0%A4%B5-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95%E0%A4%B2%E0%A5%8D%E0%A4%AA-%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%B5/ar-AA1KHzxV?ocid=finance-verthp-feeds</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Shortage of teachers hits rollout of NEP in govt, aided Maha colleges</t>
+          <t>नई दिल्ली : दिव्यांग सैन्य कैडेट्स के मुद्दे पर सुप्रीम कोर्ट सख्त; पुनर्वास योजना पर केंद्र करे विचार,</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>https://www.pressreader.com/india/hindustan-times-st-jaipur/20250819/281681145971378</t>
+          <t>https://www.rokthoklekhani.com/article/43152/new-delhanew-delhi--supreme-court-strict-on-the-issue-of-disabled-military-cadets--center-should-consider-rehabilitation-plan-i-consider-supreme-court-strict-rehabilitation-scheme-on-the</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Maha govt signs MoUs worth Rs 42,000 crore and creation of 28,000 jobs</t>
+          <t>Mumbai Chawl Redevelopment | चाळ झाली आधुनिक वस्ती</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/states-and-uts/maharashtra/maha-govt-signs-mous-worth-rs-42000-crore-and-creation-of-28000-jobs</t>
+          <t>https://pudhari.news/sampadakiy/mumbai-chawl-redevelopment-displaced-workers-problem-sp96</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Maha govt waives Stamp Duty worth Rs 38.99 lakh for Tata Cancer Hospital in Raigad (Ld)</t>
+          <t>Heavy Rains Batter Mumbai: Red Alert Issued, Schools and Colleges Closed on August 19 in Thane and...</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/india/maha-govt-waives-stamp-duty-worth-rs-3899-lakh-for-tata-cancer-hospital-in-raigad-ld</t>
+          <t>https://www.thehansindia.com/news/national/heavy-rains-batter-mumbai-red-alert-issued-schools-and-colleges-closed-on-august-19-in-thane-and-palghar-998357</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>शाहू महाराज की तरह करना होगा न्याय, कोल्हापुर में HC की नई सर्किट बेंच के उद्घाटन पर बोले CJI गवई</t>
+          <t>Business Expansion, Investments &amp; Financial News</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/state/maharashtra/cji-inaugurated-new-circuit-bench-said-a-big-thing-about-maharashtra-government-3441714.html</t>
+          <t>https://money.rediff.com/news/market/business-expansion-investments-financial-news/32187520250818</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में भारी बारिश से सात लोगों की मौत, 200 ग्रामीण फंसे</t>
+          <t>Did Mahesh Shetty Timarodi really say CM Siddaramaiah killed 24 people? Here’s the truth</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/seven-people-died-due-to-heavy-rains-in-maharashtra-200-villagers-stranded/856903/</t>
+          <t>https://english.varthabharati.in/karnataka/did-mahesh-shetty-timarodi-really-say-cm-siddaramaiah-killed-24-people-heres-the-truth</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>मराठा सेनापति रघुजी भोंसले की तलवार मुंबई पहुंची</t>
+          <t>'Third Mumbai' to boost MMR development, says Fadnavis; invites pvt sector to join in its creation</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/ncr/new-delhi/story-historic-sword-of-maratha-general-raghuji-bhosale-i-repatriated-to-mumbai-201755537654676.html</t>
+          <t>https://www.newsdrum.in/business/third-mumbai-to-boost-mmr-development-says-fadnavis-invites-pvt-sector-to-join-in-its-creation-9674122</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में माफ हो सकते हैं पुराने ट्रैफिक चालान, माफी योजना लाने की तैयारी में सरकार</t>
+          <t>Mumbai got 177mm rain in 6-8 hour period, says CM; all agencies asked to remain alert</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/government-schemes/others/maharashtra-government-is-set-to-roll-out-an-amnesty-scheme-for-one-time-settlement-of-pending-traffic-challan/articleshow/123367444.cms</t>
+          <t>https://www.newsdrum.in/national/mumbai-got-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert-9673094</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Third Mumbai महानगर क्षेत्राच्या विकासाचा नवा अध्याय असेल; मुख्यमंत्र्यांनी सांगितलं कशी असेल ‘तिसरी मुंबई’ Third Mumbai in Raigad district to boost metropolitan region development said Devendra Fadnavis</t>
+          <t>मुंबई में भारी बारिश के बीच सुचारू रूप से चल रही मेट्रो, सीएम फडणवीस ने की तारीफ</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/third-mumbai-in-raigad-district-to-boost-metropolitan-region-development-said-devendra-fadnavis-89724</t>
+          <t>https://www.m.khaskhabar.com/news/news-metro-running-smoothly-amid-heavy-rains-in-mumbai-cm-fadnavis-praised-news-hindi-1-745323-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>राज्यातील पूरस्थितीवर सरकारचे लक्ष, मदत कार्य सुरू – बावनकुळे</t>
+          <t>Asia Cup 2025: पाकिस्तान क्रिकेट के मुख्य चयनकर्ता का बड़ा बयान, बोले- भारत को हराएगा पाकिस्तान</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/governments-attention-on-flood-situation-in-the-state-information-from-chandrashekhar-bawankule-amy-95-5313292/</t>
+          <t>https://www.indiatv.in/video/sports/asia-cup-2025-2025-08-18-1156799</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>‘पीएम आवास’च्या तीस लाख घरांना मोफत वीज; राज्य सरकार देणार ५० हजारांचे अनुदान: मुख्यमंत्री</t>
+          <t>Nagpur’s Councils Starved Again: Pennies for a Region in Ruin</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/free-electricity-to-three-lakh-houses-of-pm-awas-yojana-state-government-will-provide-subsidy-of-rs-50-thousand-chief-minister-a-a747/</t>
+          <t>https://thelivenagpur.com/2025/08/18/nagpurs-councils-starved-again-pennies-for-a-region-in-ruin/</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Maharashtra Government: शेतकऱ्यांना मिळणार गुड न्यूज: बळीराजासाठी सरकार मोठा निर्णय घेण्याच्या तयारीत</t>
+          <t>Those who speak of Maharashtra 'asmita' should support Radhakrishnan for VP post Fadnavis</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/sanjay-rathod-big-statement-on-loan-waiver-maharashtra-farmers-get-loan-waiver-minister-give-hint-in-award-ceremony-program-yavatmal-pusad-bbj88</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom25-mh-governor-ld-fadnavis.html</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Crop Loss: महाराष्‍ट्र में बारिश ने किया किसानों को बर्बाद, विदर्भ से लेकर मराठवाड़ा तक फसलें चौपट</t>
+          <t>How much rain did Mumbai receive on Monday? Check area-wise list</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/heavy-rains-in-maharashtra-cause-huge-damage-to-farmers-after-crop-loss-and-land-submerged-in-water-1263471-2025-08-19</t>
+          <t>https://indianexpress.com/article/cities/mumbai/how-much-rain-did-mumbai-areas-receive-on-monday-check-list-bandra-juhu-chembur-10196732/</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>कोल्हापुर में शुरू हुई बॉम्बे हाईकोर्ट की नई खंडपीठ, सीजेआई बोले– महाराष्ट्र न्यायिक ढांचे में आगे</t>
+          <t>Maha govt plans amnesty scheme to recover pending transport fines</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/maharashtra/bombay-high-court-kolhapur-bench-cji-b-r-gavai-maharashtra-government-54-803927</t>
+          <t>https://www.socialnews.xyz/2025/08/18/maha-govt-plans-amnesty-scheme-to-recover-pending-transport-fines/</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>श्रीमती प्रज्ञा वाळकेंचा भ्रष्टाचारामध्ये उच्चांक ; सरकारविरोधी चळवळीतीही सक्रिय सहभाग ?</t>
+          <t>CM to join Kawad yatra, TV center chowk shut for 5 hours</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>https://lokmanthan.com/mrs-pragya-walkens-high-score-in-corruption-active-participation-in-anti-government-movement/</t>
+          <t>https://www.lokmattimes.com/aurangabad/cm-to-join-kawad-yatra-tv-center-chowk-shut-for-5-hours/</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Sharad Pawar | शासन विमानतळ करणारच ; तर मोबदलासाठी आग्रह धरा – शरद पवार</t>
+          <t>चुनाव के बाद होगा महामंडलों का वितरण, महायुति के इच्छुक नेताओं पर प्रदर्शन का दबाव</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/sharad-pawar-government-will-build-airport-so-insist-on-compensation-sharad-pawar/</t>
+          <t>https://navbharatlive.com/maharashtra/nagpur/distribution-of-maha-mandals-will-happen-after-the-elections-pressure-of-demonstration-on-the-aspiring-leaders-of-mahayuti-1322474.html</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Third Mumbai in Raigad to become Maharashtra’s new economic powerhouse: CM Fadnavis</t>
+          <t>सिडको जमिन वाटप प्रकरणावरून राजकारण तापले; पवारांचा शिरसाठांवर घणाघाती हल्ला</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>https://www.daijiworld.com/index.php/news/newsDisplay?newsID=1289652</t>
+          <t>https://civicmirror.in/maharashtra/politics-heats-up-over-cidco-land-allocation-issue-pawar-attacks-shirsath/</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>MMRDA launches SCLR bridge, metro institute and flyovers to ease city commute</t>
+          <t>एनडीएचे उपराष्ट्रपतीपदाचे उमेदवार सीपी राधाकृष्णन यांनी घेतली पंतप्रधानांची भेट; मोदी म्हणाले, ‘त्यांच्या अनुभवाचा देशाला फायदा होणार…’</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>https://propnewstime.com/getdetailsStories/MjA1NTQ=/mmrda-launches-sclr-bridge-metro-institute-and-flyovers-to-ease-city-commute</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%8F%E0%A4%A8%E0%A4%A1-%E0%A4%8F%E0%A4%9A%E0%A5%87-%E0%A4%89%E0%A4%AA%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A4%AA%E0%A4%A4-%E0%A4%AA%E0%A4%A6-%E0%A4%9A%E0%A5%87-%E0%A4%89%E0%A4%AE%E0%A5%87%E0%A4%A6%E0%A4%B5-%E0%A4%B0-%E0%A4%B8-%E0%A4%AA-%E0%A4%B0-%E0%A4%A7-%E0%A4%95%E0%A5%83%E0%A4%B7%E0%A5%8D%E0%A4%A3%E0%A4%A8-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%98%E0%A5%87%E0%A4%A4%E0%A4%B2-%E0%A4%AA%E0%A4%82%E0%A4%A4%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A7-%E0%A4%A8-%E0%A4%82%E0%A4%9A-%E0%A4%AD%E0%A5%87%E0%A4%9F-%E0%A4%AE-%E0%A4%A6-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%85%E0%A4%A8%E0%A5%81%E0%A4%AD%E0%A4%B5-%E0%A4%9A-%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%B2-%E0%A4%AB-%E0%A4%AF%E0%A4%A6-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0/ar-AA1KJ7hd</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Cabinet sends back note regarding GMR with multiple queries</t>
+          <t>'उपराष्ट्रपती'साठी महाराष्ट्राच्या राज्यपालांचे नाव; फडणवीसांचे खासदारांना आवाहन, पवार-ठाकरेंना टोला</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/18/cabinet-sends-back-note-regarding-gmr-with-multiple-queries.html</t>
+          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-urges-mps-to-support-radhakrishnan-targets-uddhav-thackeray-and-sharad-pawar-035137.html?ref_source=OI-MR&amp;ref_medium=Home-Page&amp;ref_campaign=News-Cards</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Maharashtra, Singapore Review Progress of Mega Container Port Project</t>
+          <t>मुंबई में कबूतरखानों पर विवाद, महापालिका ने नागरिकों से आपत्तियां और सुझाव मांगे</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/transport-infrastructure/ports-and-shipping/maharashtra--singapore-review-progress-of-mega-container-port-project/77682</t>
+          <t>https://mpbreakingnews.in/maharashtra/mumbai-municipal-corporation-pigeon-shelters-public-consultation-high-court-54-803921</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Mumbai To Get 238 New AC Local Trains In Three Years; Check List Of Features</t>
+          <t>India’s 7th rank in US scheme for children sparks fraud concerns</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>https://timesproperty.com/news/post/mumbai-to-get-238-new-ac-local-trains-in-three-yrs-blid10400</t>
+          <t>https://timesofindia.indiatimes.com/city/ahmedabad/indias-7th-rank-in-us-scheme-for-children-sparks-fraud-concerns/articleshow/123350715.cms</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>मुंबई झोपडपट्टीमुक्त होणार का? जलद पुनर्विकासाचा मुख्यमंत्र्यांनी काय सांगितला प्लॅन?</t>
+          <t>CREDAI-MCHI appoints Sukhraj Nahar as 18th President</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>https://www.tendernama.com/mahatender/mumbai/will-mumbai-become-slum-free-what-is-the-chief-ministers-plan-for-rapid-redevelopment</t>
+          <t>https://housing.com/news/credai-mchi-appoints-sukhraj-nahar-as-president/</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Mumbai Local Train: मुंबईतील लोकल प्रवाशांना मोठा दिलासा! एमआरव्हीसीकडून 15,000 कोटींचा नवा प्रकल्पाचा प्रस्ताव</t>
+          <t>Sickle cell patients await BMT as govt scheme, centres yet to take off in Nagpur</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/mumbai-local-train-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%A4-%E0%A4%B2-%E0%A4%B2-%E0%A4%95%E0%A4%B2-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%B6-%E0%A4%82%E0%A4%A8-%E0%A4%AE-%E0%A4%A0-%E0%A4%A6-%E0%A4%B2-%E0%A4%B8-%E0%A4%8F%E0%A4%AE%E0%A4%86%E0%A4%B0%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%B8-%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-15-000-%E0%A4%95-%E0%A4%9F-%E0%A4%82%E0%A4%9A-%E0%A4%A8%E0%A4%B5-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95%E0%A4%B2%E0%A5%8D%E0%A4%AA-%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%B5/ar-AA1KHzxV?ocid=finance-verthp-feeds</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/sickle-cell-patients-await-bmt-as-govt-scheme-centres-yet-to-take-off-in-nagpur/articleshow/123351316.cms</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>नई दिल्ली : दिव्यांग सैन्य कैडेट्स के मुद्दे पर सुप्रीम कोर्ट सख्त; पुनर्वास योजना पर केंद्र करे विचार,</t>
+          <t>सरकारी नौकरी: इस राज्य में पुलिस के 15 हजार से ज्यादा पदों पर होगी भर्ती, mahapolice.gov.in पर मिलेगा नोटिफ...</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>https://www.rokthoklekhani.com/article/43152/new-delhanew-delhi--supreme-court-strict-on-the-issue-of-disabled-military-cadets--center-should-consider-rehabilitation-plan-i-consider-supreme-court-strict-rehabilitation-scheme-on-the</t>
+          <t>https://hindi.news18.com/news/career/jobs-maharashtra-police-recruitment-2025-notification-for-more-than-15000-vacancy-mahapolice-gov-in-9518146.html</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Mumbai Chawl Redevelopment | चाळ झाली आधुनिक वस्ती</t>
+          <t>Cases from 6 districts to be heard | ‘A dream comes true after 40-45 years of struggle’: CJI inaugurates HC bench in Kolhapur</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>https://pudhari.news/sampadakiy/mumbai-chawl-redevelopment-displaced-workers-problem-sp96</t>
+          <t>https://indianexpress.com/article/cities/pune/cases-dream-struggle-cji-inaugurates-hc-bench-kolhapur-10195928/</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Heavy Rains Batter Mumbai: Red Alert Issued, Schools and Colleges Closed on August 19 in Thane and...</t>
+          <t>Maratha commander Raghuji Bhonsle's sword brought to Mumbai!!</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/news/national/heavy-rains-batter-mumbai-red-alert-issued-schools-and-colleges-closed-on-august-19-in-thane-and-palghar-998357</t>
+          <t>https://www.indiaherald.com/Breaking/Read/994842382/Maratha-commander-Raghuji-Bhonsles-sword-brought-to-Mumbai</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Mumbai Rains: Are Private and Public offices shut today? BMC issues statement, says...</t>
+          <t>CJI Gavai: "Maharashtra Govt At Forefront Of Efforts To Provide Infrastructure For Judiciary"</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>https://www.india.com/news/india/mumbai-rains-are-private-and-public-offices-shut-today-bmc-work-from-home-schools-colleges-devendra-fadnavis-markets-8019561/</t>
+          <t>https://lawchakra.in/legal-updates/cji-gavai-infrastructure-for-judiciary/</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Business Expansion, Investments &amp; Financial News</t>
+          <t>Maratha general Raghuji Bhonsle's sword brought to Mumbai</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/business-expansion-investments-financial-news/32187520250818</t>
+          <t>https://english.metrovaartha.com/news/mumbai/maratha-general-raghuji-bhonsles-sword-brought-to-mumbai</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>'Third Mumbai' to boost MMR development, says Fadnavis; invites pvt sector to join in its creation</t>
+          <t>Mumbai: मराठा सेनापति रघुजी भोंसले की तलवार मुंबई लाई गई, लंदन में हुई नीलामी में महाराष्ट्र सरकार ने हासिल की</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/business/third-mumbai-to-boost-mmr-development-says-fadnavis-invites-pvt-sector-to-join-in-its-creation-9674122</t>
+          <t>https://www.amarujala.com/india-news/maratha-general-raghuji-bhonsle-sword-brought-to-mumbai-maharashtra-government-acquired-in-auction-2025-08-18</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Mumbai got 177mm rain in 6-8 hour period, says CM; all agencies asked to remain alert</t>
+          <t>Kolhapur : सरन्यायाधीश Bhushan Gavai यांच्या हस्ते सर्किट बेंच इमारतीचे उद्घाटन</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/mumbai-got-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert-9673094</t>
+          <t>https://www.tarunbharat.com/kolhapur-circuit-bench-inauguration-with-chief-justice-bhushan-gavai-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>मुंबई में भारी बारिश के बीच सुचारू रूप से चल रही मेट्रो, सीएम फडणवीस ने की तारीफ</t>
+          <t>मराठा सेनापती रघुजी भोसले यांची तलवार मुंबईत आणली, लंडनमध्ये झालेल्या लिलावात महाराष्ट्र सरकारने घेतली</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>https://www.m.khaskhabar.com/news/news-metro-running-smoothly-amid-heavy-rains-in-mumbai-cm-fadnavis-praised-news-hindi-1-745323-KKN.html</t>
+          <t>https://marathi.webdunia.com/article/mumbai-news/maratha-commander-raghuji-bhonsle-s-sword-brought-to-mumbai-125081800027_1.html</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Asia Cup 2025: पाकिस्तान क्रिकेट के मुख्य चयनकर्ता का बड़ा बयान, बोले- भारत को हराएगा पाकिस्तान</t>
+          <t>राज्यात ओला दुष्काळ जाहीर करा</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/sports/asia-cup-2025-2025-08-18-1156799</t>
+          <t>https://dainikekmat.com/%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%A4-%E0%A4%93%E0%A4%B2%E0%A4%BE-%E0%A4%A6%E0%A5%81%E0%A4%B7%E0%A5%8D%E0%A4%95%E0%A4%BE%E0%A4%B3-%E0%A4%9C%E0%A4%BE%E0%A4%B9%E0%A5%80/114152/</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>‘Third Mumbai’ will open a new chapter of economic development: Maha CM</t>
+          <t>Ganesh Naik, Eknath Shinde, Thane, Maharashtra Politics</t>
         </is>
       </c>
       <c r="B380